--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="77">
+  <fonts count="79">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -464,6 +464,16 @@
       <color rgb="001B3A6B"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -698,7 +708,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="271">
+  <borders count="293">
     <border>
       <left/>
       <right/>
@@ -3617,11 +3627,227 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="338">
+  <cellXfs count="425">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4398,6 +4624,246 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="279" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="276" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="276" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="275" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="276" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="279" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="273" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="282" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="277" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="283" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="278" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="289" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="290" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="289" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="290" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="285" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="286" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="287" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="288" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="291" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="284" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="292" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4472,39 +4938,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>0</row>
-      <rowOff>257175</rowOff>
-    </from>
-    <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4874,1924 +5307,2181 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="267" t="inlineStr"/>
-      <c r="B1" s="268" t="n"/>
-      <c r="C1" s="268" t="n"/>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
-      <c r="I1" s="268" t="n"/>
-      <c r="J1" s="268" t="n"/>
-      <c r="K1" s="268" t="n"/>
-      <c r="L1" s="269" t="inlineStr">
+      <c r="A1" s="338" t="inlineStr"/>
+      <c r="B1" s="419" t="n"/>
+      <c r="C1" s="419" t="n"/>
+      <c r="D1" s="419" t="n"/>
+      <c r="E1" s="419" t="n"/>
+      <c r="F1" s="419" t="n"/>
+      <c r="G1" s="419" t="n"/>
+      <c r="H1" s="419" t="n"/>
+      <c r="I1" s="419" t="n"/>
+      <c r="J1" s="419" t="n"/>
+      <c r="K1" s="419" t="n"/>
+      <c r="L1" s="340" t="inlineStr">
         <is>
           <t>Final Inspection Report</t>
         </is>
       </c>
-      <c r="M1" s="268" t="n"/>
-      <c r="N1" s="268" t="n"/>
-      <c r="O1" s="268" t="n"/>
-      <c r="P1" s="268" t="n"/>
-      <c r="Q1" s="268" t="n"/>
-      <c r="R1" s="268" t="n"/>
-      <c r="S1" s="268" t="n"/>
-      <c r="T1" s="268" t="n"/>
-      <c r="U1" s="268" t="n"/>
-      <c r="V1" s="268" t="n"/>
-      <c r="W1" s="268" t="n"/>
-      <c r="X1" s="268" t="n"/>
-      <c r="Y1" s="268" t="n"/>
-      <c r="Z1" s="268" t="n"/>
-      <c r="AA1" s="268" t="n"/>
-      <c r="AB1" s="268" t="n"/>
-      <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="268" t="n"/>
-      <c r="AE1" s="268" t="n"/>
-      <c r="AF1" s="268" t="n"/>
-      <c r="AG1" s="268" t="n"/>
-      <c r="AH1" s="268" t="n"/>
-      <c r="AI1" s="268" t="n"/>
-      <c r="AJ1" s="268" t="n"/>
-      <c r="AK1" s="268" t="n"/>
-      <c r="AL1" s="268" t="n"/>
-      <c r="AM1" s="268" t="n"/>
-      <c r="AN1" s="268" t="n"/>
-      <c r="AO1" s="268" t="n"/>
-      <c r="AP1" s="268" t="n"/>
-      <c r="AQ1" s="270" t="inlineStr">
+      <c r="M1" s="419" t="n"/>
+      <c r="N1" s="419" t="n"/>
+      <c r="O1" s="419" t="n"/>
+      <c r="P1" s="419" t="n"/>
+      <c r="Q1" s="419" t="n"/>
+      <c r="R1" s="419" t="n"/>
+      <c r="S1" s="419" t="n"/>
+      <c r="T1" s="419" t="n"/>
+      <c r="U1" s="419" t="n"/>
+      <c r="V1" s="419" t="n"/>
+      <c r="W1" s="419" t="n"/>
+      <c r="X1" s="419" t="n"/>
+      <c r="Y1" s="419" t="n"/>
+      <c r="Z1" s="419" t="n"/>
+      <c r="AA1" s="419" t="n"/>
+      <c r="AB1" s="419" t="n"/>
+      <c r="AC1" s="419" t="n"/>
+      <c r="AD1" s="419" t="n"/>
+      <c r="AE1" s="419" t="n"/>
+      <c r="AF1" s="419" t="n"/>
+      <c r="AG1" s="419" t="n"/>
+      <c r="AH1" s="419" t="n"/>
+      <c r="AI1" s="419" t="n"/>
+      <c r="AJ1" s="419" t="n"/>
+      <c r="AK1" s="419" t="n"/>
+      <c r="AL1" s="419" t="n"/>
+      <c r="AM1" s="419" t="n"/>
+      <c r="AN1" s="419" t="n"/>
+      <c r="AO1" s="419" t="n"/>
+      <c r="AP1" s="419" t="n"/>
+      <c r="AQ1" s="341" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="271" t="n"/>
-      <c r="AS1" s="271" t="n"/>
-      <c r="AT1" s="271" t="n"/>
-      <c r="AU1" s="271" t="n"/>
-      <c r="AV1" s="272" t="n"/>
-      <c r="AW1" s="273" t="inlineStr">
+      <c r="AR1" s="420" t="n"/>
+      <c r="AS1" s="420" t="n"/>
+      <c r="AT1" s="420" t="n"/>
+      <c r="AU1" s="420" t="n"/>
+      <c r="AV1" s="421" t="n"/>
+      <c r="AW1" s="344" t="inlineStr">
         <is>
           <t>FRM-641</t>
         </is>
       </c>
-      <c r="AX1" s="271" t="n"/>
-      <c r="AY1" s="271" t="n"/>
-      <c r="AZ1" s="271" t="n"/>
-      <c r="BA1" s="271" t="n"/>
-      <c r="BB1" s="271" t="n"/>
-      <c r="BC1" s="271" t="n"/>
-      <c r="BD1" s="274" t="n"/>
+      <c r="AX1" s="420" t="n"/>
+      <c r="AY1" s="420" t="n"/>
+      <c r="AZ1" s="420" t="n"/>
+      <c r="BA1" s="420" t="n"/>
+      <c r="BB1" s="420" t="n"/>
+      <c r="BC1" s="420" t="n"/>
+      <c r="BD1" s="421" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="L2" s="275" t="n"/>
-      <c r="AQ2" s="270" t="inlineStr">
+      <c r="A2" s="422" t="n"/>
+      <c r="L2" s="422" t="n"/>
+      <c r="AQ2" s="341" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="271" t="n"/>
-      <c r="AS2" s="271" t="n"/>
-      <c r="AT2" s="271" t="n"/>
-      <c r="AU2" s="271" t="n"/>
-      <c r="AV2" s="272" t="n"/>
-      <c r="AW2" s="273" t="inlineStr">
+      <c r="AR2" s="420" t="n"/>
+      <c r="AS2" s="420" t="n"/>
+      <c r="AT2" s="420" t="n"/>
+      <c r="AU2" s="420" t="n"/>
+      <c r="AV2" s="421" t="n"/>
+      <c r="AW2" s="344" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="271" t="n"/>
-      <c r="AY2" s="271" t="n"/>
-      <c r="AZ2" s="271" t="n"/>
-      <c r="BA2" s="271" t="n"/>
-      <c r="BB2" s="271" t="n"/>
-      <c r="BC2" s="271" t="n"/>
-      <c r="BD2" s="274" t="n"/>
+      <c r="AX2" s="420" t="n"/>
+      <c r="AY2" s="420" t="n"/>
+      <c r="AZ2" s="420" t="n"/>
+      <c r="BA2" s="420" t="n"/>
+      <c r="BB2" s="420" t="n"/>
+      <c r="BC2" s="420" t="n"/>
+      <c r="BD2" s="421" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="L3" s="279" t="n"/>
-      <c r="M3" s="276" t="n"/>
-      <c r="N3" s="276" t="n"/>
-      <c r="O3" s="276" t="n"/>
-      <c r="P3" s="276" t="n"/>
-      <c r="Q3" s="276" t="n"/>
-      <c r="R3" s="276" t="n"/>
-      <c r="S3" s="276" t="n"/>
-      <c r="T3" s="276" t="n"/>
-      <c r="U3" s="276" t="n"/>
-      <c r="V3" s="276" t="n"/>
-      <c r="W3" s="276" t="n"/>
-      <c r="X3" s="276" t="n"/>
-      <c r="Y3" s="276" t="n"/>
-      <c r="Z3" s="276" t="n"/>
-      <c r="AA3" s="276" t="n"/>
-      <c r="AB3" s="276" t="n"/>
-      <c r="AC3" s="276" t="n"/>
-      <c r="AD3" s="276" t="n"/>
-      <c r="AE3" s="276" t="n"/>
-      <c r="AF3" s="276" t="n"/>
-      <c r="AG3" s="276" t="n"/>
-      <c r="AH3" s="276" t="n"/>
-      <c r="AI3" s="276" t="n"/>
-      <c r="AJ3" s="276" t="n"/>
-      <c r="AK3" s="276" t="n"/>
-      <c r="AL3" s="276" t="n"/>
-      <c r="AM3" s="276" t="n"/>
-      <c r="AN3" s="276" t="n"/>
-      <c r="AO3" s="276" t="n"/>
-      <c r="AP3" s="276" t="n"/>
-      <c r="AQ3" s="270" t="inlineStr">
+      <c r="A3" s="422" t="n"/>
+      <c r="L3" s="423" t="n"/>
+      <c r="M3" s="424" t="n"/>
+      <c r="N3" s="424" t="n"/>
+      <c r="O3" s="424" t="n"/>
+      <c r="P3" s="424" t="n"/>
+      <c r="Q3" s="424" t="n"/>
+      <c r="R3" s="424" t="n"/>
+      <c r="S3" s="424" t="n"/>
+      <c r="T3" s="424" t="n"/>
+      <c r="U3" s="424" t="n"/>
+      <c r="V3" s="424" t="n"/>
+      <c r="W3" s="424" t="n"/>
+      <c r="X3" s="424" t="n"/>
+      <c r="Y3" s="424" t="n"/>
+      <c r="Z3" s="424" t="n"/>
+      <c r="AA3" s="424" t="n"/>
+      <c r="AB3" s="424" t="n"/>
+      <c r="AC3" s="424" t="n"/>
+      <c r="AD3" s="424" t="n"/>
+      <c r="AE3" s="424" t="n"/>
+      <c r="AF3" s="424" t="n"/>
+      <c r="AG3" s="424" t="n"/>
+      <c r="AH3" s="424" t="n"/>
+      <c r="AI3" s="424" t="n"/>
+      <c r="AJ3" s="424" t="n"/>
+      <c r="AK3" s="424" t="n"/>
+      <c r="AL3" s="424" t="n"/>
+      <c r="AM3" s="424" t="n"/>
+      <c r="AN3" s="424" t="n"/>
+      <c r="AO3" s="424" t="n"/>
+      <c r="AP3" s="424" t="n"/>
+      <c r="AQ3" s="341" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="271" t="n"/>
-      <c r="AS3" s="271" t="n"/>
-      <c r="AT3" s="271" t="n"/>
-      <c r="AU3" s="271" t="n"/>
-      <c r="AV3" s="272" t="n"/>
-      <c r="AW3" s="273" t="inlineStr">
+      <c r="AR3" s="420" t="n"/>
+      <c r="AS3" s="420" t="n"/>
+      <c r="AT3" s="420" t="n"/>
+      <c r="AU3" s="420" t="n"/>
+      <c r="AV3" s="421" t="n"/>
+      <c r="AW3" s="344" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="271" t="n"/>
-      <c r="AY3" s="271" t="n"/>
-      <c r="AZ3" s="271" t="n"/>
-      <c r="BA3" s="271" t="n"/>
-      <c r="BB3" s="271" t="n"/>
-      <c r="BC3" s="271" t="n"/>
-      <c r="BD3" s="274" t="n"/>
+      <c r="AX3" s="420" t="n"/>
+      <c r="AY3" s="420" t="n"/>
+      <c r="AZ3" s="420" t="n"/>
+      <c r="BA3" s="420" t="n"/>
+      <c r="BB3" s="420" t="n"/>
+      <c r="BC3" s="420" t="n"/>
+      <c r="BD3" s="421" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="A4" s="422" t="n"/>
+      <c r="L4" s="349" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="270" t="inlineStr">
+      <c r="AQ4" s="341" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="271" t="n"/>
-      <c r="AS4" s="271" t="n"/>
-      <c r="AT4" s="271" t="n"/>
-      <c r="AU4" s="271" t="n"/>
-      <c r="AV4" s="272" t="n"/>
-      <c r="AW4" s="273" t="inlineStr">
+      <c r="AR4" s="420" t="n"/>
+      <c r="AS4" s="420" t="n"/>
+      <c r="AT4" s="420" t="n"/>
+      <c r="AU4" s="420" t="n"/>
+      <c r="AV4" s="421" t="n"/>
+      <c r="AW4" s="344" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="271" t="n"/>
-      <c r="AY4" s="271" t="n"/>
-      <c r="AZ4" s="271" t="n"/>
-      <c r="BA4" s="271" t="n"/>
-      <c r="BB4" s="271" t="n"/>
-      <c r="BC4" s="271" t="n"/>
-      <c r="BD4" s="274" t="n"/>
+      <c r="AX4" s="420" t="n"/>
+      <c r="AY4" s="420" t="n"/>
+      <c r="AZ4" s="420" t="n"/>
+      <c r="BA4" s="420" t="n"/>
+      <c r="BB4" s="420" t="n"/>
+      <c r="BC4" s="420" t="n"/>
+      <c r="BD4" s="421" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="280" t="n"/>
-      <c r="B5" s="281" t="n"/>
-      <c r="C5" s="281" t="n"/>
-      <c r="D5" s="281" t="n"/>
-      <c r="E5" s="281" t="n"/>
-      <c r="F5" s="281" t="n"/>
-      <c r="G5" s="281" t="n"/>
-      <c r="H5" s="281" t="n"/>
-      <c r="I5" s="281" t="n"/>
-      <c r="J5" s="281" t="n"/>
-      <c r="K5" s="281" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="A5" s="423" t="n"/>
+      <c r="B5" s="424" t="n"/>
+      <c r="C5" s="424" t="n"/>
+      <c r="D5" s="424" t="n"/>
+      <c r="E5" s="424" t="n"/>
+      <c r="F5" s="424" t="n"/>
+      <c r="G5" s="424" t="n"/>
+      <c r="H5" s="424" t="n"/>
+      <c r="I5" s="424" t="n"/>
+      <c r="J5" s="424" t="n"/>
+      <c r="K5" s="424" t="n"/>
+      <c r="L5" s="350" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="281" t="n"/>
-      <c r="N5" s="281" t="n"/>
-      <c r="O5" s="281" t="n"/>
-      <c r="P5" s="281" t="n"/>
-      <c r="Q5" s="281" t="n"/>
-      <c r="R5" s="281" t="n"/>
-      <c r="S5" s="281" t="n"/>
-      <c r="T5" s="281" t="n"/>
-      <c r="U5" s="281" t="n"/>
-      <c r="V5" s="281" t="n"/>
-      <c r="W5" s="281" t="n"/>
-      <c r="X5" s="281" t="n"/>
-      <c r="Y5" s="281" t="n"/>
-      <c r="Z5" s="281" t="n"/>
-      <c r="AA5" s="281" t="n"/>
-      <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="n"/>
-      <c r="AD5" s="281" t="n"/>
-      <c r="AE5" s="281" t="n"/>
-      <c r="AF5" s="281" t="n"/>
-      <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
-      <c r="AI5" s="281" t="n"/>
-      <c r="AJ5" s="281" t="n"/>
-      <c r="AK5" s="281" t="n"/>
-      <c r="AL5" s="281" t="n"/>
-      <c r="AM5" s="281" t="n"/>
-      <c r="AN5" s="281" t="n"/>
-      <c r="AO5" s="281" t="n"/>
-      <c r="AP5" s="281" t="n"/>
-      <c r="AQ5" s="270" t="inlineStr">
+      <c r="M5" s="424" t="n"/>
+      <c r="N5" s="424" t="n"/>
+      <c r="O5" s="424" t="n"/>
+      <c r="P5" s="424" t="n"/>
+      <c r="Q5" s="424" t="n"/>
+      <c r="R5" s="424" t="n"/>
+      <c r="S5" s="424" t="n"/>
+      <c r="T5" s="424" t="n"/>
+      <c r="U5" s="424" t="n"/>
+      <c r="V5" s="424" t="n"/>
+      <c r="W5" s="424" t="n"/>
+      <c r="X5" s="424" t="n"/>
+      <c r="Y5" s="424" t="n"/>
+      <c r="Z5" s="424" t="n"/>
+      <c r="AA5" s="424" t="n"/>
+      <c r="AB5" s="424" t="n"/>
+      <c r="AC5" s="424" t="n"/>
+      <c r="AD5" s="424" t="n"/>
+      <c r="AE5" s="424" t="n"/>
+      <c r="AF5" s="424" t="n"/>
+      <c r="AG5" s="424" t="n"/>
+      <c r="AH5" s="424" t="n"/>
+      <c r="AI5" s="424" t="n"/>
+      <c r="AJ5" s="424" t="n"/>
+      <c r="AK5" s="424" t="n"/>
+      <c r="AL5" s="424" t="n"/>
+      <c r="AM5" s="424" t="n"/>
+      <c r="AN5" s="424" t="n"/>
+      <c r="AO5" s="424" t="n"/>
+      <c r="AP5" s="424" t="n"/>
+      <c r="AQ5" s="341" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="271" t="n"/>
-      <c r="AS5" s="271" t="n"/>
-      <c r="AT5" s="271" t="n"/>
-      <c r="AU5" s="271" t="n"/>
-      <c r="AV5" s="272" t="n"/>
-      <c r="AW5" s="273" t="inlineStr">
+      <c r="AR5" s="420" t="n"/>
+      <c r="AS5" s="420" t="n"/>
+      <c r="AT5" s="420" t="n"/>
+      <c r="AU5" s="420" t="n"/>
+      <c r="AV5" s="421" t="n"/>
+      <c r="AW5" s="344" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="271" t="n"/>
-      <c r="AY5" s="271" t="n"/>
-      <c r="AZ5" s="271" t="n"/>
-      <c r="BA5" s="271" t="n"/>
-      <c r="BB5" s="271" t="n"/>
-      <c r="BC5" s="271" t="n"/>
-      <c r="BD5" s="274" t="n"/>
+      <c r="AX5" s="420" t="n"/>
+      <c r="AY5" s="420" t="n"/>
+      <c r="AZ5" s="420" t="n"/>
+      <c r="BA5" s="420" t="n"/>
+      <c r="BB5" s="420" t="n"/>
+      <c r="BC5" s="420" t="n"/>
+      <c r="BD5" s="421" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="25" t="inlineStr"/>
+      <c r="A6" s="351" t="inlineStr"/>
+      <c r="B6" s="418" t="n"/>
+      <c r="C6" s="418" t="n"/>
+      <c r="D6" s="418" t="n"/>
+      <c r="E6" s="418" t="n"/>
+      <c r="F6" s="418" t="n"/>
+      <c r="G6" s="418" t="n"/>
+      <c r="H6" s="418" t="n"/>
+      <c r="I6" s="418" t="n"/>
+      <c r="J6" s="418" t="n"/>
+      <c r="K6" s="418" t="n"/>
+      <c r="L6" s="418" t="n"/>
+      <c r="M6" s="418" t="n"/>
+      <c r="N6" s="418" t="n"/>
+      <c r="O6" s="418" t="n"/>
+      <c r="P6" s="418" t="n"/>
+      <c r="Q6" s="418" t="n"/>
+      <c r="R6" s="418" t="n"/>
+      <c r="S6" s="418" t="n"/>
+      <c r="T6" s="418" t="n"/>
+      <c r="U6" s="418" t="n"/>
+      <c r="V6" s="418" t="n"/>
+      <c r="W6" s="418" t="n"/>
+      <c r="X6" s="418" t="n"/>
+      <c r="Y6" s="418" t="n"/>
+      <c r="Z6" s="418" t="n"/>
+      <c r="AA6" s="418" t="n"/>
+      <c r="AB6" s="418" t="n"/>
+      <c r="AC6" s="418" t="n"/>
+      <c r="AD6" s="418" t="n"/>
+      <c r="AE6" s="418" t="n"/>
+      <c r="AF6" s="418" t="n"/>
+      <c r="AG6" s="418" t="n"/>
+      <c r="AH6" s="418" t="n"/>
+      <c r="AI6" s="418" t="n"/>
+      <c r="AJ6" s="418" t="n"/>
+      <c r="AK6" s="418" t="n"/>
+      <c r="AL6" s="418" t="n"/>
+      <c r="AM6" s="418" t="n"/>
+      <c r="AN6" s="418" t="n"/>
+      <c r="AO6" s="418" t="n"/>
+      <c r="AP6" s="418" t="n"/>
+      <c r="AQ6" s="418" t="n"/>
+      <c r="AR6" s="418" t="n"/>
+      <c r="AS6" s="418" t="n"/>
+      <c r="AT6" s="418" t="n"/>
+      <c r="AU6" s="418" t="n"/>
+      <c r="AV6" s="418" t="n"/>
+      <c r="AW6" s="418" t="n"/>
+      <c r="AX6" s="418" t="n"/>
+      <c r="AY6" s="418" t="n"/>
+      <c r="AZ6" s="418" t="n"/>
+      <c r="BA6" s="418" t="n"/>
+      <c r="BB6" s="418" t="n"/>
+      <c r="BC6" s="418" t="n"/>
+      <c r="BD6" s="418" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="284" t="inlineStr">
+      <c r="A7" s="352" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="285" t="n"/>
-      <c r="AO7" s="285" t="n"/>
-      <c r="AP7" s="285" t="n"/>
-      <c r="AQ7" s="285" t="n"/>
-      <c r="AR7" s="285" t="n"/>
-      <c r="AS7" s="285" t="n"/>
-      <c r="AT7" s="285" t="n"/>
-      <c r="AU7" s="285" t="n"/>
-      <c r="AV7" s="285" t="n"/>
-      <c r="AW7" s="285" t="n"/>
-      <c r="AX7" s="285" t="n"/>
-      <c r="AY7" s="285" t="n"/>
-      <c r="AZ7" s="285" t="n"/>
-      <c r="BA7" s="285" t="n"/>
-      <c r="BB7" s="285" t="n"/>
-      <c r="BC7" s="285" t="n"/>
-      <c r="BD7" s="286" t="n"/>
+      <c r="B7" s="420" t="n"/>
+      <c r="C7" s="420" t="n"/>
+      <c r="D7" s="420" t="n"/>
+      <c r="E7" s="420" t="n"/>
+      <c r="F7" s="420" t="n"/>
+      <c r="G7" s="420" t="n"/>
+      <c r="H7" s="420" t="n"/>
+      <c r="I7" s="420" t="n"/>
+      <c r="J7" s="420" t="n"/>
+      <c r="K7" s="420" t="n"/>
+      <c r="L7" s="420" t="n"/>
+      <c r="M7" s="420" t="n"/>
+      <c r="N7" s="420" t="n"/>
+      <c r="O7" s="420" t="n"/>
+      <c r="P7" s="420" t="n"/>
+      <c r="Q7" s="420" t="n"/>
+      <c r="R7" s="420" t="n"/>
+      <c r="S7" s="420" t="n"/>
+      <c r="T7" s="420" t="n"/>
+      <c r="U7" s="420" t="n"/>
+      <c r="V7" s="420" t="n"/>
+      <c r="W7" s="420" t="n"/>
+      <c r="X7" s="420" t="n"/>
+      <c r="Y7" s="420" t="n"/>
+      <c r="Z7" s="420" t="n"/>
+      <c r="AA7" s="420" t="n"/>
+      <c r="AB7" s="420" t="n"/>
+      <c r="AC7" s="420" t="n"/>
+      <c r="AD7" s="420" t="n"/>
+      <c r="AE7" s="420" t="n"/>
+      <c r="AF7" s="420" t="n"/>
+      <c r="AG7" s="420" t="n"/>
+      <c r="AH7" s="420" t="n"/>
+      <c r="AI7" s="420" t="n"/>
+      <c r="AJ7" s="420" t="n"/>
+      <c r="AK7" s="420" t="n"/>
+      <c r="AL7" s="420" t="n"/>
+      <c r="AM7" s="420" t="n"/>
+      <c r="AN7" s="420" t="n"/>
+      <c r="AO7" s="420" t="n"/>
+      <c r="AP7" s="420" t="n"/>
+      <c r="AQ7" s="420" t="n"/>
+      <c r="AR7" s="420" t="n"/>
+      <c r="AS7" s="420" t="n"/>
+      <c r="AT7" s="420" t="n"/>
+      <c r="AU7" s="420" t="n"/>
+      <c r="AV7" s="420" t="n"/>
+      <c r="AW7" s="420" t="n"/>
+      <c r="AX7" s="420" t="n"/>
+      <c r="AY7" s="420" t="n"/>
+      <c r="AZ7" s="420" t="n"/>
+      <c r="BA7" s="420" t="n"/>
+      <c r="BB7" s="420" t="n"/>
+      <c r="BC7" s="420" t="n"/>
+      <c r="BD7" s="421" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="287" t="inlineStr">
+      <c r="A8" s="353" t="inlineStr">
         <is>
           <t>Final Inspection Report ID</t>
         </is>
       </c>
-      <c r="B8" s="271" t="n"/>
-      <c r="C8" s="271" t="n"/>
-      <c r="D8" s="271" t="n"/>
-      <c r="E8" s="271" t="n"/>
-      <c r="F8" s="271" t="n"/>
-      <c r="G8" s="271" t="n"/>
-      <c r="H8" s="271" t="n"/>
-      <c r="I8" s="271" t="n"/>
-      <c r="J8" s="272" t="n"/>
-      <c r="K8" s="288" t="n"/>
-      <c r="L8" s="321" t="n"/>
-      <c r="M8" s="321" t="n"/>
-      <c r="N8" s="321" t="n"/>
-      <c r="O8" s="321" t="n"/>
-      <c r="P8" s="321" t="n"/>
-      <c r="Q8" s="321" t="n"/>
-      <c r="R8" s="321" t="n"/>
-      <c r="S8" s="321" t="n"/>
-      <c r="T8" s="321" t="n"/>
-      <c r="U8" s="321" t="n"/>
-      <c r="V8" s="321" t="n"/>
-      <c r="W8" s="321" t="n"/>
-      <c r="X8" s="321" t="n"/>
-      <c r="Y8" s="321" t="n"/>
-      <c r="Z8" s="321" t="n"/>
-      <c r="AA8" s="321" t="n"/>
-      <c r="AB8" s="322" t="n"/>
-      <c r="AC8" s="289" t="inlineStr">
+      <c r="B8" s="403" t="n"/>
+      <c r="C8" s="403" t="n"/>
+      <c r="D8" s="403" t="n"/>
+      <c r="E8" s="403" t="n"/>
+      <c r="F8" s="403" t="n"/>
+      <c r="G8" s="403" t="n"/>
+      <c r="H8" s="403" t="n"/>
+      <c r="I8" s="403" t="n"/>
+      <c r="J8" s="404" t="n"/>
+      <c r="K8" s="356" t="n"/>
+      <c r="L8" s="405" t="n"/>
+      <c r="M8" s="405" t="n"/>
+      <c r="N8" s="405" t="n"/>
+      <c r="O8" s="405" t="n"/>
+      <c r="P8" s="405" t="n"/>
+      <c r="Q8" s="405" t="n"/>
+      <c r="R8" s="405" t="n"/>
+      <c r="S8" s="405" t="n"/>
+      <c r="T8" s="405" t="n"/>
+      <c r="U8" s="405" t="n"/>
+      <c r="V8" s="405" t="n"/>
+      <c r="W8" s="405" t="n"/>
+      <c r="X8" s="405" t="n"/>
+      <c r="Y8" s="405" t="n"/>
+      <c r="Z8" s="405" t="n"/>
+      <c r="AA8" s="405" t="n"/>
+      <c r="AB8" s="406" t="n"/>
+      <c r="AC8" s="359" t="inlineStr">
         <is>
           <t>Final Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="271" t="n"/>
-      <c r="AE8" s="271" t="n"/>
-      <c r="AF8" s="271" t="n"/>
-      <c r="AG8" s="271" t="n"/>
-      <c r="AH8" s="271" t="n"/>
-      <c r="AI8" s="271" t="n"/>
-      <c r="AJ8" s="271" t="n"/>
-      <c r="AK8" s="271" t="n"/>
-      <c r="AL8" s="272" t="n"/>
-      <c r="AM8" s="290" t="n"/>
-      <c r="AN8" s="321" t="n"/>
-      <c r="AO8" s="321" t="n"/>
-      <c r="AP8" s="321" t="n"/>
-      <c r="AQ8" s="321" t="n"/>
-      <c r="AR8" s="321" t="n"/>
-      <c r="AS8" s="321" t="n"/>
-      <c r="AT8" s="321" t="n"/>
-      <c r="AU8" s="321" t="n"/>
-      <c r="AV8" s="321" t="n"/>
-      <c r="AW8" s="321" t="n"/>
-      <c r="AX8" s="321" t="n"/>
-      <c r="AY8" s="321" t="n"/>
-      <c r="AZ8" s="321" t="n"/>
-      <c r="BA8" s="321" t="n"/>
-      <c r="BB8" s="321" t="n"/>
-      <c r="BC8" s="321" t="n"/>
-      <c r="BD8" s="323" t="n"/>
+      <c r="AD8" s="403" t="n"/>
+      <c r="AE8" s="403" t="n"/>
+      <c r="AF8" s="403" t="n"/>
+      <c r="AG8" s="403" t="n"/>
+      <c r="AH8" s="403" t="n"/>
+      <c r="AI8" s="403" t="n"/>
+      <c r="AJ8" s="403" t="n"/>
+      <c r="AK8" s="403" t="n"/>
+      <c r="AL8" s="404" t="n"/>
+      <c r="AM8" s="356" t="n"/>
+      <c r="AN8" s="405" t="n"/>
+      <c r="AO8" s="405" t="n"/>
+      <c r="AP8" s="405" t="n"/>
+      <c r="AQ8" s="405" t="n"/>
+      <c r="AR8" s="405" t="n"/>
+      <c r="AS8" s="405" t="n"/>
+      <c r="AT8" s="405" t="n"/>
+      <c r="AU8" s="405" t="n"/>
+      <c r="AV8" s="405" t="n"/>
+      <c r="AW8" s="405" t="n"/>
+      <c r="AX8" s="405" t="n"/>
+      <c r="AY8" s="405" t="n"/>
+      <c r="AZ8" s="405" t="n"/>
+      <c r="BA8" s="405" t="n"/>
+      <c r="BB8" s="405" t="n"/>
+      <c r="BC8" s="405" t="n"/>
+      <c r="BD8" s="406" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="287" t="inlineStr">
+      <c r="A9" s="353" t="inlineStr">
         <is>
           <t>Job / Shipment</t>
         </is>
       </c>
-      <c r="B9" s="271" t="n"/>
-      <c r="C9" s="271" t="n"/>
-      <c r="D9" s="271" t="n"/>
-      <c r="E9" s="271" t="n"/>
-      <c r="F9" s="271" t="n"/>
-      <c r="G9" s="271" t="n"/>
-      <c r="H9" s="271" t="n"/>
-      <c r="I9" s="271" t="n"/>
-      <c r="J9" s="272" t="n"/>
-      <c r="K9" s="288" t="n"/>
-      <c r="L9" s="321" t="n"/>
-      <c r="M9" s="321" t="n"/>
-      <c r="N9" s="321" t="n"/>
-      <c r="O9" s="321" t="n"/>
-      <c r="P9" s="321" t="n"/>
-      <c r="Q9" s="321" t="n"/>
-      <c r="R9" s="321" t="n"/>
-      <c r="S9" s="321" t="n"/>
-      <c r="T9" s="321" t="n"/>
-      <c r="U9" s="321" t="n"/>
-      <c r="V9" s="321" t="n"/>
-      <c r="W9" s="321" t="n"/>
-      <c r="X9" s="321" t="n"/>
-      <c r="Y9" s="321" t="n"/>
-      <c r="Z9" s="321" t="n"/>
-      <c r="AA9" s="321" t="n"/>
-      <c r="AB9" s="322" t="n"/>
-      <c r="AC9" s="289" t="inlineStr">
+      <c r="B9" s="403" t="n"/>
+      <c r="C9" s="403" t="n"/>
+      <c r="D9" s="403" t="n"/>
+      <c r="E9" s="403" t="n"/>
+      <c r="F9" s="403" t="n"/>
+      <c r="G9" s="403" t="n"/>
+      <c r="H9" s="403" t="n"/>
+      <c r="I9" s="403" t="n"/>
+      <c r="J9" s="404" t="n"/>
+      <c r="K9" s="356" t="n"/>
+      <c r="L9" s="405" t="n"/>
+      <c r="M9" s="405" t="n"/>
+      <c r="N9" s="405" t="n"/>
+      <c r="O9" s="405" t="n"/>
+      <c r="P9" s="405" t="n"/>
+      <c r="Q9" s="405" t="n"/>
+      <c r="R9" s="405" t="n"/>
+      <c r="S9" s="405" t="n"/>
+      <c r="T9" s="405" t="n"/>
+      <c r="U9" s="405" t="n"/>
+      <c r="V9" s="405" t="n"/>
+      <c r="W9" s="405" t="n"/>
+      <c r="X9" s="405" t="n"/>
+      <c r="Y9" s="405" t="n"/>
+      <c r="Z9" s="405" t="n"/>
+      <c r="AA9" s="405" t="n"/>
+      <c r="AB9" s="406" t="n"/>
+      <c r="AC9" s="359" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="AD9" s="271" t="n"/>
-      <c r="AE9" s="271" t="n"/>
-      <c r="AF9" s="271" t="n"/>
-      <c r="AG9" s="271" t="n"/>
-      <c r="AH9" s="271" t="n"/>
-      <c r="AI9" s="271" t="n"/>
-      <c r="AJ9" s="271" t="n"/>
-      <c r="AK9" s="271" t="n"/>
-      <c r="AL9" s="272" t="n"/>
-      <c r="AM9" s="290" t="n"/>
-      <c r="AN9" s="321" t="n"/>
-      <c r="AO9" s="321" t="n"/>
-      <c r="AP9" s="321" t="n"/>
-      <c r="AQ9" s="321" t="n"/>
-      <c r="AR9" s="321" t="n"/>
-      <c r="AS9" s="321" t="n"/>
-      <c r="AT9" s="321" t="n"/>
-      <c r="AU9" s="321" t="n"/>
-      <c r="AV9" s="321" t="n"/>
-      <c r="AW9" s="321" t="n"/>
-      <c r="AX9" s="321" t="n"/>
-      <c r="AY9" s="321" t="n"/>
-      <c r="AZ9" s="321" t="n"/>
-      <c r="BA9" s="321" t="n"/>
-      <c r="BB9" s="321" t="n"/>
-      <c r="BC9" s="321" t="n"/>
-      <c r="BD9" s="323" t="n"/>
+      <c r="AD9" s="403" t="n"/>
+      <c r="AE9" s="403" t="n"/>
+      <c r="AF9" s="403" t="n"/>
+      <c r="AG9" s="403" t="n"/>
+      <c r="AH9" s="403" t="n"/>
+      <c r="AI9" s="403" t="n"/>
+      <c r="AJ9" s="403" t="n"/>
+      <c r="AK9" s="403" t="n"/>
+      <c r="AL9" s="404" t="n"/>
+      <c r="AM9" s="356" t="n"/>
+      <c r="AN9" s="405" t="n"/>
+      <c r="AO9" s="405" t="n"/>
+      <c r="AP9" s="405" t="n"/>
+      <c r="AQ9" s="405" t="n"/>
+      <c r="AR9" s="405" t="n"/>
+      <c r="AS9" s="405" t="n"/>
+      <c r="AT9" s="405" t="n"/>
+      <c r="AU9" s="405" t="n"/>
+      <c r="AV9" s="405" t="n"/>
+      <c r="AW9" s="405" t="n"/>
+      <c r="AX9" s="405" t="n"/>
+      <c r="AY9" s="405" t="n"/>
+      <c r="AZ9" s="405" t="n"/>
+      <c r="BA9" s="405" t="n"/>
+      <c r="BB9" s="405" t="n"/>
+      <c r="BC9" s="405" t="n"/>
+      <c r="BD9" s="406" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="287" t="inlineStr">
+      <c r="A10" s="353" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="B10" s="271" t="n"/>
-      <c r="C10" s="271" t="n"/>
-      <c r="D10" s="271" t="n"/>
-      <c r="E10" s="271" t="n"/>
-      <c r="F10" s="271" t="n"/>
-      <c r="G10" s="271" t="n"/>
-      <c r="H10" s="271" t="n"/>
-      <c r="I10" s="271" t="n"/>
-      <c r="J10" s="272" t="n"/>
-      <c r="K10" s="288" t="n"/>
-      <c r="L10" s="321" t="n"/>
-      <c r="M10" s="321" t="n"/>
-      <c r="N10" s="321" t="n"/>
-      <c r="O10" s="321" t="n"/>
-      <c r="P10" s="321" t="n"/>
-      <c r="Q10" s="321" t="n"/>
-      <c r="R10" s="321" t="n"/>
-      <c r="S10" s="321" t="n"/>
-      <c r="T10" s="321" t="n"/>
-      <c r="U10" s="321" t="n"/>
-      <c r="V10" s="321" t="n"/>
-      <c r="W10" s="321" t="n"/>
-      <c r="X10" s="321" t="n"/>
-      <c r="Y10" s="321" t="n"/>
-      <c r="Z10" s="321" t="n"/>
-      <c r="AA10" s="321" t="n"/>
-      <c r="AB10" s="322" t="n"/>
-      <c r="AC10" s="289" t="inlineStr">
+      <c r="B10" s="403" t="n"/>
+      <c r="C10" s="403" t="n"/>
+      <c r="D10" s="403" t="n"/>
+      <c r="E10" s="403" t="n"/>
+      <c r="F10" s="403" t="n"/>
+      <c r="G10" s="403" t="n"/>
+      <c r="H10" s="403" t="n"/>
+      <c r="I10" s="403" t="n"/>
+      <c r="J10" s="404" t="n"/>
+      <c r="K10" s="356" t="n"/>
+      <c r="L10" s="405" t="n"/>
+      <c r="M10" s="405" t="n"/>
+      <c r="N10" s="405" t="n"/>
+      <c r="O10" s="405" t="n"/>
+      <c r="P10" s="405" t="n"/>
+      <c r="Q10" s="405" t="n"/>
+      <c r="R10" s="405" t="n"/>
+      <c r="S10" s="405" t="n"/>
+      <c r="T10" s="405" t="n"/>
+      <c r="U10" s="405" t="n"/>
+      <c r="V10" s="405" t="n"/>
+      <c r="W10" s="405" t="n"/>
+      <c r="X10" s="405" t="n"/>
+      <c r="Y10" s="405" t="n"/>
+      <c r="Z10" s="405" t="n"/>
+      <c r="AA10" s="405" t="n"/>
+      <c r="AB10" s="406" t="n"/>
+      <c r="AC10" s="359" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="AD10" s="271" t="n"/>
-      <c r="AE10" s="271" t="n"/>
-      <c r="AF10" s="271" t="n"/>
-      <c r="AG10" s="271" t="n"/>
-      <c r="AH10" s="271" t="n"/>
-      <c r="AI10" s="271" t="n"/>
-      <c r="AJ10" s="271" t="n"/>
-      <c r="AK10" s="271" t="n"/>
-      <c r="AL10" s="272" t="n"/>
-      <c r="AM10" s="290" t="n"/>
-      <c r="AN10" s="321" t="n"/>
-      <c r="AO10" s="321" t="n"/>
-      <c r="AP10" s="321" t="n"/>
-      <c r="AQ10" s="321" t="n"/>
-      <c r="AR10" s="321" t="n"/>
-      <c r="AS10" s="321" t="n"/>
-      <c r="AT10" s="321" t="n"/>
-      <c r="AU10" s="321" t="n"/>
-      <c r="AV10" s="321" t="n"/>
-      <c r="AW10" s="321" t="n"/>
-      <c r="AX10" s="321" t="n"/>
-      <c r="AY10" s="321" t="n"/>
-      <c r="AZ10" s="321" t="n"/>
-      <c r="BA10" s="321" t="n"/>
-      <c r="BB10" s="321" t="n"/>
-      <c r="BC10" s="321" t="n"/>
-      <c r="BD10" s="323" t="n"/>
+      <c r="AD10" s="403" t="n"/>
+      <c r="AE10" s="403" t="n"/>
+      <c r="AF10" s="403" t="n"/>
+      <c r="AG10" s="403" t="n"/>
+      <c r="AH10" s="403" t="n"/>
+      <c r="AI10" s="403" t="n"/>
+      <c r="AJ10" s="403" t="n"/>
+      <c r="AK10" s="403" t="n"/>
+      <c r="AL10" s="404" t="n"/>
+      <c r="AM10" s="356" t="n"/>
+      <c r="AN10" s="405" t="n"/>
+      <c r="AO10" s="405" t="n"/>
+      <c r="AP10" s="405" t="n"/>
+      <c r="AQ10" s="405" t="n"/>
+      <c r="AR10" s="405" t="n"/>
+      <c r="AS10" s="405" t="n"/>
+      <c r="AT10" s="405" t="n"/>
+      <c r="AU10" s="405" t="n"/>
+      <c r="AV10" s="405" t="n"/>
+      <c r="AW10" s="405" t="n"/>
+      <c r="AX10" s="405" t="n"/>
+      <c r="AY10" s="405" t="n"/>
+      <c r="AZ10" s="405" t="n"/>
+      <c r="BA10" s="405" t="n"/>
+      <c r="BB10" s="405" t="n"/>
+      <c r="BC10" s="405" t="n"/>
+      <c r="BD10" s="406" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="287" t="inlineStr">
+      <c r="A11" s="353" t="inlineStr">
         <is>
           <t>Inspection Basis</t>
         </is>
       </c>
-      <c r="B11" s="271" t="n"/>
-      <c r="C11" s="271" t="n"/>
-      <c r="D11" s="271" t="n"/>
-      <c r="E11" s="271" t="n"/>
-      <c r="F11" s="271" t="n"/>
-      <c r="G11" s="271" t="n"/>
-      <c r="H11" s="271" t="n"/>
-      <c r="I11" s="271" t="n"/>
-      <c r="J11" s="272" t="n"/>
-      <c r="K11" s="288" t="n"/>
-      <c r="L11" s="321" t="n"/>
-      <c r="M11" s="321" t="n"/>
-      <c r="N11" s="321" t="n"/>
-      <c r="O11" s="321" t="n"/>
-      <c r="P11" s="321" t="n"/>
-      <c r="Q11" s="321" t="n"/>
-      <c r="R11" s="321" t="n"/>
-      <c r="S11" s="321" t="n"/>
-      <c r="T11" s="321" t="n"/>
-      <c r="U11" s="321" t="n"/>
-      <c r="V11" s="321" t="n"/>
-      <c r="W11" s="321" t="n"/>
-      <c r="X11" s="321" t="n"/>
-      <c r="Y11" s="321" t="n"/>
-      <c r="Z11" s="321" t="n"/>
-      <c r="AA11" s="321" t="n"/>
-      <c r="AB11" s="322" t="n"/>
-      <c r="AC11" s="289" t="inlineStr">
+      <c r="B11" s="403" t="n"/>
+      <c r="C11" s="403" t="n"/>
+      <c r="D11" s="403" t="n"/>
+      <c r="E11" s="403" t="n"/>
+      <c r="F11" s="403" t="n"/>
+      <c r="G11" s="403" t="n"/>
+      <c r="H11" s="403" t="n"/>
+      <c r="I11" s="403" t="n"/>
+      <c r="J11" s="404" t="n"/>
+      <c r="K11" s="356" t="n"/>
+      <c r="L11" s="405" t="n"/>
+      <c r="M11" s="405" t="n"/>
+      <c r="N11" s="405" t="n"/>
+      <c r="O11" s="405" t="n"/>
+      <c r="P11" s="405" t="n"/>
+      <c r="Q11" s="405" t="n"/>
+      <c r="R11" s="405" t="n"/>
+      <c r="S11" s="405" t="n"/>
+      <c r="T11" s="405" t="n"/>
+      <c r="U11" s="405" t="n"/>
+      <c r="V11" s="405" t="n"/>
+      <c r="W11" s="405" t="n"/>
+      <c r="X11" s="405" t="n"/>
+      <c r="Y11" s="405" t="n"/>
+      <c r="Z11" s="405" t="n"/>
+      <c r="AA11" s="405" t="n"/>
+      <c r="AB11" s="406" t="n"/>
+      <c r="AC11" s="359" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="AD11" s="271" t="n"/>
-      <c r="AE11" s="271" t="n"/>
-      <c r="AF11" s="271" t="n"/>
-      <c r="AG11" s="271" t="n"/>
-      <c r="AH11" s="271" t="n"/>
-      <c r="AI11" s="271" t="n"/>
-      <c r="AJ11" s="271" t="n"/>
-      <c r="AK11" s="271" t="n"/>
-      <c r="AL11" s="272" t="n"/>
-      <c r="AM11" s="290" t="n"/>
-      <c r="AN11" s="321" t="n"/>
-      <c r="AO11" s="321" t="n"/>
-      <c r="AP11" s="321" t="n"/>
-      <c r="AQ11" s="321" t="n"/>
-      <c r="AR11" s="321" t="n"/>
-      <c r="AS11" s="321" t="n"/>
-      <c r="AT11" s="321" t="n"/>
-      <c r="AU11" s="321" t="n"/>
-      <c r="AV11" s="321" t="n"/>
-      <c r="AW11" s="321" t="n"/>
-      <c r="AX11" s="321" t="n"/>
-      <c r="AY11" s="321" t="n"/>
-      <c r="AZ11" s="321" t="n"/>
-      <c r="BA11" s="321" t="n"/>
-      <c r="BB11" s="321" t="n"/>
-      <c r="BC11" s="321" t="n"/>
-      <c r="BD11" s="323" t="n"/>
+      <c r="AD11" s="403" t="n"/>
+      <c r="AE11" s="403" t="n"/>
+      <c r="AF11" s="403" t="n"/>
+      <c r="AG11" s="403" t="n"/>
+      <c r="AH11" s="403" t="n"/>
+      <c r="AI11" s="403" t="n"/>
+      <c r="AJ11" s="403" t="n"/>
+      <c r="AK11" s="403" t="n"/>
+      <c r="AL11" s="404" t="n"/>
+      <c r="AM11" s="356" t="n"/>
+      <c r="AN11" s="405" t="n"/>
+      <c r="AO11" s="405" t="n"/>
+      <c r="AP11" s="405" t="n"/>
+      <c r="AQ11" s="405" t="n"/>
+      <c r="AR11" s="405" t="n"/>
+      <c r="AS11" s="405" t="n"/>
+      <c r="AT11" s="405" t="n"/>
+      <c r="AU11" s="405" t="n"/>
+      <c r="AV11" s="405" t="n"/>
+      <c r="AW11" s="405" t="n"/>
+      <c r="AX11" s="405" t="n"/>
+      <c r="AY11" s="405" t="n"/>
+      <c r="AZ11" s="405" t="n"/>
+      <c r="BA11" s="405" t="n"/>
+      <c r="BB11" s="405" t="n"/>
+      <c r="BC11" s="405" t="n"/>
+      <c r="BD11" s="406" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="287" t="inlineStr">
+      <c r="A12" s="353" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B12" s="271" t="n"/>
-      <c r="C12" s="271" t="n"/>
-      <c r="D12" s="271" t="n"/>
-      <c r="E12" s="271" t="n"/>
-      <c r="F12" s="271" t="n"/>
-      <c r="G12" s="271" t="n"/>
-      <c r="H12" s="271" t="n"/>
-      <c r="I12" s="271" t="n"/>
-      <c r="J12" s="272" t="n"/>
-      <c r="K12" s="288" t="n"/>
-      <c r="L12" s="321" t="n"/>
-      <c r="M12" s="321" t="n"/>
-      <c r="N12" s="321" t="n"/>
-      <c r="O12" s="321" t="n"/>
-      <c r="P12" s="321" t="n"/>
-      <c r="Q12" s="321" t="n"/>
-      <c r="R12" s="321" t="n"/>
-      <c r="S12" s="321" t="n"/>
-      <c r="T12" s="321" t="n"/>
-      <c r="U12" s="321" t="n"/>
-      <c r="V12" s="321" t="n"/>
-      <c r="W12" s="321" t="n"/>
-      <c r="X12" s="321" t="n"/>
-      <c r="Y12" s="321" t="n"/>
-      <c r="Z12" s="321" t="n"/>
-      <c r="AA12" s="321" t="n"/>
-      <c r="AB12" s="322" t="n"/>
-      <c r="AC12" s="289" t="inlineStr">
+      <c r="B12" s="398" t="n"/>
+      <c r="C12" s="398" t="n"/>
+      <c r="D12" s="398" t="n"/>
+      <c r="E12" s="398" t="n"/>
+      <c r="F12" s="398" t="n"/>
+      <c r="G12" s="398" t="n"/>
+      <c r="H12" s="398" t="n"/>
+      <c r="I12" s="398" t="n"/>
+      <c r="J12" s="399" t="n"/>
+      <c r="K12" s="356" t="n"/>
+      <c r="L12" s="407" t="n"/>
+      <c r="M12" s="407" t="n"/>
+      <c r="N12" s="407" t="n"/>
+      <c r="O12" s="407" t="n"/>
+      <c r="P12" s="407" t="n"/>
+      <c r="Q12" s="407" t="n"/>
+      <c r="R12" s="407" t="n"/>
+      <c r="S12" s="407" t="n"/>
+      <c r="T12" s="407" t="n"/>
+      <c r="U12" s="407" t="n"/>
+      <c r="V12" s="407" t="n"/>
+      <c r="W12" s="407" t="n"/>
+      <c r="X12" s="407" t="n"/>
+      <c r="Y12" s="407" t="n"/>
+      <c r="Z12" s="407" t="n"/>
+      <c r="AA12" s="407" t="n"/>
+      <c r="AB12" s="408" t="n"/>
+      <c r="AC12" s="359" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="271" t="n"/>
-      <c r="AE12" s="271" t="n"/>
-      <c r="AF12" s="271" t="n"/>
-      <c r="AG12" s="271" t="n"/>
-      <c r="AH12" s="271" t="n"/>
-      <c r="AI12" s="271" t="n"/>
-      <c r="AJ12" s="271" t="n"/>
-      <c r="AK12" s="271" t="n"/>
-      <c r="AL12" s="272" t="n"/>
-      <c r="AM12" s="290" t="n"/>
-      <c r="AN12" s="321" t="n"/>
-      <c r="AO12" s="321" t="n"/>
-      <c r="AP12" s="321" t="n"/>
-      <c r="AQ12" s="321" t="n"/>
-      <c r="AR12" s="321" t="n"/>
-      <c r="AS12" s="321" t="n"/>
-      <c r="AT12" s="321" t="n"/>
-      <c r="AU12" s="321" t="n"/>
-      <c r="AV12" s="321" t="n"/>
-      <c r="AW12" s="321" t="n"/>
-      <c r="AX12" s="321" t="n"/>
-      <c r="AY12" s="321" t="n"/>
-      <c r="AZ12" s="321" t="n"/>
-      <c r="BA12" s="321" t="n"/>
-      <c r="BB12" s="321" t="n"/>
-      <c r="BC12" s="321" t="n"/>
-      <c r="BD12" s="323" t="n"/>
+      <c r="AD12" s="398" t="n"/>
+      <c r="AE12" s="398" t="n"/>
+      <c r="AF12" s="398" t="n"/>
+      <c r="AG12" s="398" t="n"/>
+      <c r="AH12" s="398" t="n"/>
+      <c r="AI12" s="398" t="n"/>
+      <c r="AJ12" s="398" t="n"/>
+      <c r="AK12" s="398" t="n"/>
+      <c r="AL12" s="399" t="n"/>
+      <c r="AM12" s="356" t="n"/>
+      <c r="AN12" s="407" t="n"/>
+      <c r="AO12" s="407" t="n"/>
+      <c r="AP12" s="407" t="n"/>
+      <c r="AQ12" s="407" t="n"/>
+      <c r="AR12" s="407" t="n"/>
+      <c r="AS12" s="407" t="n"/>
+      <c r="AT12" s="407" t="n"/>
+      <c r="AU12" s="407" t="n"/>
+      <c r="AV12" s="407" t="n"/>
+      <c r="AW12" s="407" t="n"/>
+      <c r="AX12" s="407" t="n"/>
+      <c r="AY12" s="407" t="n"/>
+      <c r="AZ12" s="407" t="n"/>
+      <c r="BA12" s="407" t="n"/>
+      <c r="BB12" s="407" t="n"/>
+      <c r="BC12" s="407" t="n"/>
+      <c r="BD12" s="408" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="25" t="n"/>
+      <c r="A13" s="351" t="n"/>
+      <c r="B13" s="351" t="n"/>
+      <c r="C13" s="351" t="n"/>
+      <c r="D13" s="351" t="n"/>
+      <c r="E13" s="351" t="n"/>
+      <c r="F13" s="351" t="n"/>
+      <c r="G13" s="351" t="n"/>
+      <c r="H13" s="351" t="n"/>
+      <c r="I13" s="351" t="n"/>
+      <c r="J13" s="351" t="n"/>
+      <c r="K13" s="351" t="n"/>
+      <c r="L13" s="351" t="n"/>
+      <c r="M13" s="351" t="n"/>
+      <c r="N13" s="351" t="n"/>
+      <c r="O13" s="351" t="n"/>
+      <c r="P13" s="351" t="n"/>
+      <c r="Q13" s="351" t="n"/>
+      <c r="R13" s="351" t="n"/>
+      <c r="S13" s="351" t="n"/>
+      <c r="T13" s="351" t="n"/>
+      <c r="U13" s="351" t="n"/>
+      <c r="V13" s="351" t="n"/>
+      <c r="W13" s="351" t="n"/>
+      <c r="X13" s="351" t="n"/>
+      <c r="Y13" s="351" t="n"/>
+      <c r="Z13" s="351" t="n"/>
+      <c r="AA13" s="351" t="n"/>
+      <c r="AB13" s="351" t="n"/>
+      <c r="AC13" s="351" t="n"/>
+      <c r="AD13" s="351" t="n"/>
+      <c r="AE13" s="351" t="n"/>
+      <c r="AF13" s="351" t="n"/>
+      <c r="AG13" s="351" t="n"/>
+      <c r="AH13" s="351" t="n"/>
+      <c r="AI13" s="351" t="n"/>
+      <c r="AJ13" s="351" t="n"/>
+      <c r="AK13" s="351" t="n"/>
+      <c r="AL13" s="351" t="n"/>
+      <c r="AM13" s="351" t="n"/>
+      <c r="AN13" s="351" t="n"/>
+      <c r="AO13" s="351" t="n"/>
+      <c r="AP13" s="351" t="n"/>
+      <c r="AQ13" s="351" t="n"/>
+      <c r="AR13" s="351" t="n"/>
+      <c r="AS13" s="351" t="n"/>
+      <c r="AT13" s="351" t="n"/>
+      <c r="AU13" s="351" t="n"/>
+      <c r="AV13" s="351" t="n"/>
+      <c r="AW13" s="351" t="n"/>
+      <c r="AX13" s="351" t="n"/>
+      <c r="AY13" s="351" t="n"/>
+      <c r="AZ13" s="351" t="n"/>
+      <c r="BA13" s="351" t="n"/>
+      <c r="BB13" s="351" t="n"/>
+      <c r="BC13" s="351" t="n"/>
+      <c r="BD13" s="351" t="n"/>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="284" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="352" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B14" s="285" t="n"/>
-      <c r="C14" s="285" t="n"/>
-      <c r="D14" s="285" t="n"/>
-      <c r="E14" s="285" t="n"/>
-      <c r="F14" s="285" t="n"/>
-      <c r="G14" s="285" t="n"/>
-      <c r="H14" s="285" t="n"/>
-      <c r="I14" s="285" t="n"/>
-      <c r="J14" s="285" t="n"/>
-      <c r="K14" s="285" t="n"/>
-      <c r="L14" s="285" t="n"/>
-      <c r="M14" s="285" t="n"/>
-      <c r="N14" s="285" t="n"/>
-      <c r="O14" s="285" t="n"/>
-      <c r="P14" s="285" t="n"/>
-      <c r="Q14" s="285" t="n"/>
-      <c r="R14" s="285" t="n"/>
-      <c r="S14" s="285" t="n"/>
-      <c r="T14" s="285" t="n"/>
-      <c r="U14" s="285" t="n"/>
-      <c r="V14" s="285" t="n"/>
-      <c r="W14" s="285" t="n"/>
-      <c r="X14" s="285" t="n"/>
-      <c r="Y14" s="285" t="n"/>
-      <c r="Z14" s="285" t="n"/>
-      <c r="AA14" s="285" t="n"/>
-      <c r="AB14" s="285" t="n"/>
-      <c r="AC14" s="285" t="n"/>
-      <c r="AD14" s="285" t="n"/>
-      <c r="AE14" s="285" t="n"/>
-      <c r="AF14" s="285" t="n"/>
-      <c r="AG14" s="285" t="n"/>
-      <c r="AH14" s="285" t="n"/>
-      <c r="AI14" s="285" t="n"/>
-      <c r="AJ14" s="285" t="n"/>
-      <c r="AK14" s="285" t="n"/>
-      <c r="AL14" s="285" t="n"/>
-      <c r="AM14" s="285" t="n"/>
-      <c r="AN14" s="285" t="n"/>
-      <c r="AO14" s="285" t="n"/>
-      <c r="AP14" s="285" t="n"/>
-      <c r="AQ14" s="285" t="n"/>
-      <c r="AR14" s="285" t="n"/>
-      <c r="AS14" s="285" t="n"/>
-      <c r="AT14" s="285" t="n"/>
-      <c r="AU14" s="285" t="n"/>
-      <c r="AV14" s="285" t="n"/>
-      <c r="AW14" s="285" t="n"/>
-      <c r="AX14" s="285" t="n"/>
-      <c r="AY14" s="285" t="n"/>
-      <c r="AZ14" s="285" t="n"/>
-      <c r="BA14" s="285" t="n"/>
-      <c r="BB14" s="285" t="n"/>
-      <c r="BC14" s="285" t="n"/>
-      <c r="BD14" s="286" t="n"/>
+      <c r="B14" s="403" t="n"/>
+      <c r="C14" s="403" t="n"/>
+      <c r="D14" s="403" t="n"/>
+      <c r="E14" s="403" t="n"/>
+      <c r="F14" s="403" t="n"/>
+      <c r="G14" s="403" t="n"/>
+      <c r="H14" s="403" t="n"/>
+      <c r="I14" s="403" t="n"/>
+      <c r="J14" s="403" t="n"/>
+      <c r="K14" s="403" t="n"/>
+      <c r="L14" s="403" t="n"/>
+      <c r="M14" s="403" t="n"/>
+      <c r="N14" s="403" t="n"/>
+      <c r="O14" s="403" t="n"/>
+      <c r="P14" s="403" t="n"/>
+      <c r="Q14" s="403" t="n"/>
+      <c r="R14" s="403" t="n"/>
+      <c r="S14" s="403" t="n"/>
+      <c r="T14" s="403" t="n"/>
+      <c r="U14" s="403" t="n"/>
+      <c r="V14" s="403" t="n"/>
+      <c r="W14" s="403" t="n"/>
+      <c r="X14" s="403" t="n"/>
+      <c r="Y14" s="403" t="n"/>
+      <c r="Z14" s="403" t="n"/>
+      <c r="AA14" s="403" t="n"/>
+      <c r="AB14" s="403" t="n"/>
+      <c r="AC14" s="403" t="n"/>
+      <c r="AD14" s="403" t="n"/>
+      <c r="AE14" s="403" t="n"/>
+      <c r="AF14" s="403" t="n"/>
+      <c r="AG14" s="403" t="n"/>
+      <c r="AH14" s="403" t="n"/>
+      <c r="AI14" s="403" t="n"/>
+      <c r="AJ14" s="403" t="n"/>
+      <c r="AK14" s="403" t="n"/>
+      <c r="AL14" s="403" t="n"/>
+      <c r="AM14" s="403" t="n"/>
+      <c r="AN14" s="403" t="n"/>
+      <c r="AO14" s="403" t="n"/>
+      <c r="AP14" s="403" t="n"/>
+      <c r="AQ14" s="403" t="n"/>
+      <c r="AR14" s="403" t="n"/>
+      <c r="AS14" s="403" t="n"/>
+      <c r="AT14" s="403" t="n"/>
+      <c r="AU14" s="403" t="n"/>
+      <c r="AV14" s="403" t="n"/>
+      <c r="AW14" s="403" t="n"/>
+      <c r="AX14" s="403" t="n"/>
+      <c r="AY14" s="403" t="n"/>
+      <c r="AZ14" s="403" t="n"/>
+      <c r="BA14" s="403" t="n"/>
+      <c r="BB14" s="403" t="n"/>
+      <c r="BC14" s="403" t="n"/>
+      <c r="BD14" s="404" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="291" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="362" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="271" t="n"/>
-      <c r="C15" s="272" t="n"/>
-      <c r="D15" s="292" t="inlineStr">
+      <c r="B15" s="403" t="n"/>
+      <c r="C15" s="404" t="n"/>
+      <c r="D15" s="363" t="inlineStr">
         <is>
           <t>Check Group</t>
         </is>
       </c>
-      <c r="E15" s="271" t="n"/>
-      <c r="F15" s="271" t="n"/>
-      <c r="G15" s="272" t="n"/>
-      <c r="H15" s="292" t="inlineStr">
+      <c r="E15" s="403" t="n"/>
+      <c r="F15" s="403" t="n"/>
+      <c r="G15" s="404" t="n"/>
+      <c r="H15" s="363" t="inlineStr">
         <is>
           <t>Characteristic / Requirement</t>
         </is>
       </c>
-      <c r="I15" s="271" t="n"/>
-      <c r="J15" s="271" t="n"/>
-      <c r="K15" s="271" t="n"/>
-      <c r="L15" s="271" t="n"/>
-      <c r="M15" s="271" t="n"/>
-      <c r="N15" s="271" t="n"/>
-      <c r="O15" s="271" t="n"/>
-      <c r="P15" s="271" t="n"/>
-      <c r="Q15" s="271" t="n"/>
-      <c r="R15" s="271" t="n"/>
-      <c r="S15" s="271" t="n"/>
-      <c r="T15" s="271" t="n"/>
-      <c r="U15" s="271" t="n"/>
-      <c r="V15" s="271" t="n"/>
-      <c r="W15" s="271" t="n"/>
-      <c r="X15" s="271" t="n"/>
-      <c r="Y15" s="271" t="n"/>
-      <c r="Z15" s="272" t="n"/>
-      <c r="AA15" s="292" t="inlineStr">
+      <c r="I15" s="403" t="n"/>
+      <c r="J15" s="403" t="n"/>
+      <c r="K15" s="403" t="n"/>
+      <c r="L15" s="403" t="n"/>
+      <c r="M15" s="403" t="n"/>
+      <c r="N15" s="403" t="n"/>
+      <c r="O15" s="403" t="n"/>
+      <c r="P15" s="403" t="n"/>
+      <c r="Q15" s="403" t="n"/>
+      <c r="R15" s="403" t="n"/>
+      <c r="S15" s="403" t="n"/>
+      <c r="T15" s="403" t="n"/>
+      <c r="U15" s="403" t="n"/>
+      <c r="V15" s="403" t="n"/>
+      <c r="W15" s="403" t="n"/>
+      <c r="X15" s="403" t="n"/>
+      <c r="Y15" s="403" t="n"/>
+      <c r="Z15" s="404" t="n"/>
+      <c r="AA15" s="363" t="inlineStr">
         <is>
           <t>Method / Inspection Basis</t>
         </is>
       </c>
-      <c r="AB15" s="271" t="n"/>
-      <c r="AC15" s="271" t="n"/>
-      <c r="AD15" s="271" t="n"/>
-      <c r="AE15" s="271" t="n"/>
-      <c r="AF15" s="271" t="n"/>
-      <c r="AG15" s="271" t="n"/>
-      <c r="AH15" s="271" t="n"/>
-      <c r="AI15" s="271" t="n"/>
-      <c r="AJ15" s="271" t="n"/>
-      <c r="AK15" s="271" t="n"/>
-      <c r="AL15" s="271" t="n"/>
-      <c r="AM15" s="271" t="n"/>
-      <c r="AN15" s="271" t="n"/>
-      <c r="AO15" s="271" t="n"/>
-      <c r="AP15" s="271" t="n"/>
-      <c r="AQ15" s="272" t="n"/>
-      <c r="AR15" s="292" t="inlineStr">
+      <c r="AB15" s="403" t="n"/>
+      <c r="AC15" s="403" t="n"/>
+      <c r="AD15" s="403" t="n"/>
+      <c r="AE15" s="403" t="n"/>
+      <c r="AF15" s="403" t="n"/>
+      <c r="AG15" s="403" t="n"/>
+      <c r="AH15" s="403" t="n"/>
+      <c r="AI15" s="403" t="n"/>
+      <c r="AJ15" s="403" t="n"/>
+      <c r="AK15" s="403" t="n"/>
+      <c r="AL15" s="403" t="n"/>
+      <c r="AM15" s="403" t="n"/>
+      <c r="AN15" s="403" t="n"/>
+      <c r="AO15" s="403" t="n"/>
+      <c r="AP15" s="403" t="n"/>
+      <c r="AQ15" s="404" t="n"/>
+      <c r="AR15" s="363" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="271" t="n"/>
-      <c r="AT15" s="271" t="n"/>
-      <c r="AU15" s="271" t="n"/>
-      <c r="AV15" s="271" t="n"/>
-      <c r="AW15" s="272" t="n"/>
-      <c r="AX15" s="292" t="inlineStr">
+      <c r="AS15" s="403" t="n"/>
+      <c r="AT15" s="403" t="n"/>
+      <c r="AU15" s="403" t="n"/>
+      <c r="AV15" s="403" t="n"/>
+      <c r="AW15" s="404" t="n"/>
+      <c r="AX15" s="363" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY15" s="271" t="n"/>
-      <c r="AZ15" s="271" t="n"/>
-      <c r="BA15" s="272" t="n"/>
-      <c r="BB15" s="293" t="inlineStr">
+      <c r="AY15" s="403" t="n"/>
+      <c r="AZ15" s="403" t="n"/>
+      <c r="BA15" s="404" t="n"/>
+      <c r="BB15" s="363" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="271" t="n"/>
-      <c r="BD15" s="274" t="n"/>
+      <c r="BC15" s="403" t="n"/>
+      <c r="BD15" s="404" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="294">
+      <c r="A16" s="364">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="276" t="n"/>
-      <c r="C16" s="277" t="n"/>
-      <c r="D16" s="295" t="inlineStr">
+      <c r="B16" s="409" t="n"/>
+      <c r="C16" s="410" t="n"/>
+      <c r="D16" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="324" t="n"/>
-      <c r="F16" s="324" t="n"/>
-      <c r="G16" s="325" t="n"/>
-      <c r="H16" s="296" t="n"/>
-      <c r="I16" s="324" t="n"/>
-      <c r="J16" s="324" t="n"/>
-      <c r="K16" s="324" t="n"/>
-      <c r="L16" s="324" t="n"/>
-      <c r="M16" s="324" t="n"/>
-      <c r="N16" s="324" t="n"/>
-      <c r="O16" s="324" t="n"/>
-      <c r="P16" s="324" t="n"/>
-      <c r="Q16" s="324" t="n"/>
-      <c r="R16" s="324" t="n"/>
-      <c r="S16" s="324" t="n"/>
-      <c r="T16" s="324" t="n"/>
-      <c r="U16" s="324" t="n"/>
-      <c r="V16" s="324" t="n"/>
-      <c r="W16" s="324" t="n"/>
-      <c r="X16" s="324" t="n"/>
-      <c r="Y16" s="324" t="n"/>
-      <c r="Z16" s="325" t="n"/>
-      <c r="AA16" s="297" t="n"/>
-      <c r="AB16" s="324" t="n"/>
-      <c r="AC16" s="324" t="n"/>
-      <c r="AD16" s="324" t="n"/>
-      <c r="AE16" s="324" t="n"/>
-      <c r="AF16" s="324" t="n"/>
-      <c r="AG16" s="324" t="n"/>
-      <c r="AH16" s="324" t="n"/>
-      <c r="AI16" s="324" t="n"/>
-      <c r="AJ16" s="324" t="n"/>
-      <c r="AK16" s="324" t="n"/>
-      <c r="AL16" s="324" t="n"/>
-      <c r="AM16" s="324" t="n"/>
-      <c r="AN16" s="324" t="n"/>
-      <c r="AO16" s="324" t="n"/>
-      <c r="AP16" s="324" t="n"/>
-      <c r="AQ16" s="325" t="n"/>
-      <c r="AR16" s="296" t="n"/>
-      <c r="AS16" s="324" t="n"/>
-      <c r="AT16" s="324" t="n"/>
-      <c r="AU16" s="324" t="n"/>
-      <c r="AV16" s="324" t="n"/>
-      <c r="AW16" s="325" t="n"/>
-      <c r="AX16" s="296" t="n"/>
-      <c r="AY16" s="324" t="n"/>
-      <c r="AZ16" s="324" t="n"/>
-      <c r="BA16" s="325" t="n"/>
-      <c r="BB16" s="298" t="n"/>
-      <c r="BC16" s="324" t="n"/>
-      <c r="BD16" s="326" t="n"/>
+      <c r="E16" s="411" t="n"/>
+      <c r="F16" s="411" t="n"/>
+      <c r="G16" s="412" t="n"/>
+      <c r="H16" s="370" t="n"/>
+      <c r="I16" s="411" t="n"/>
+      <c r="J16" s="411" t="n"/>
+      <c r="K16" s="411" t="n"/>
+      <c r="L16" s="411" t="n"/>
+      <c r="M16" s="411" t="n"/>
+      <c r="N16" s="411" t="n"/>
+      <c r="O16" s="411" t="n"/>
+      <c r="P16" s="411" t="n"/>
+      <c r="Q16" s="411" t="n"/>
+      <c r="R16" s="411" t="n"/>
+      <c r="S16" s="411" t="n"/>
+      <c r="T16" s="411" t="n"/>
+      <c r="U16" s="411" t="n"/>
+      <c r="V16" s="411" t="n"/>
+      <c r="W16" s="411" t="n"/>
+      <c r="X16" s="411" t="n"/>
+      <c r="Y16" s="411" t="n"/>
+      <c r="Z16" s="412" t="n"/>
+      <c r="AA16" s="371" t="n"/>
+      <c r="AB16" s="411" t="n"/>
+      <c r="AC16" s="411" t="n"/>
+      <c r="AD16" s="411" t="n"/>
+      <c r="AE16" s="411" t="n"/>
+      <c r="AF16" s="411" t="n"/>
+      <c r="AG16" s="411" t="n"/>
+      <c r="AH16" s="411" t="n"/>
+      <c r="AI16" s="411" t="n"/>
+      <c r="AJ16" s="411" t="n"/>
+      <c r="AK16" s="411" t="n"/>
+      <c r="AL16" s="411" t="n"/>
+      <c r="AM16" s="411" t="n"/>
+      <c r="AN16" s="411" t="n"/>
+      <c r="AO16" s="411" t="n"/>
+      <c r="AP16" s="411" t="n"/>
+      <c r="AQ16" s="412" t="n"/>
+      <c r="AR16" s="370" t="n"/>
+      <c r="AS16" s="411" t="n"/>
+      <c r="AT16" s="411" t="n"/>
+      <c r="AU16" s="411" t="n"/>
+      <c r="AV16" s="411" t="n"/>
+      <c r="AW16" s="412" t="n"/>
+      <c r="AX16" s="370" t="n"/>
+      <c r="AY16" s="411" t="n"/>
+      <c r="AZ16" s="411" t="n"/>
+      <c r="BA16" s="412" t="n"/>
+      <c r="BB16" s="372" t="n"/>
+      <c r="BC16" s="411" t="n"/>
+      <c r="BD16" s="412" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="294">
+      <c r="A17" s="364">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="276" t="n"/>
-      <c r="C17" s="277" t="n"/>
-      <c r="D17" s="295" t="inlineStr">
+      <c r="B17" s="409" t="n"/>
+      <c r="C17" s="410" t="n"/>
+      <c r="D17" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="324" t="n"/>
-      <c r="F17" s="324" t="n"/>
-      <c r="G17" s="325" t="n"/>
-      <c r="H17" s="296" t="n"/>
-      <c r="I17" s="324" t="n"/>
-      <c r="J17" s="324" t="n"/>
-      <c r="K17" s="324" t="n"/>
-      <c r="L17" s="324" t="n"/>
-      <c r="M17" s="324" t="n"/>
-      <c r="N17" s="324" t="n"/>
-      <c r="O17" s="324" t="n"/>
-      <c r="P17" s="324" t="n"/>
-      <c r="Q17" s="324" t="n"/>
-      <c r="R17" s="324" t="n"/>
-      <c r="S17" s="324" t="n"/>
-      <c r="T17" s="324" t="n"/>
-      <c r="U17" s="324" t="n"/>
-      <c r="V17" s="324" t="n"/>
-      <c r="W17" s="324" t="n"/>
-      <c r="X17" s="324" t="n"/>
-      <c r="Y17" s="324" t="n"/>
-      <c r="Z17" s="325" t="n"/>
-      <c r="AA17" s="297" t="n"/>
-      <c r="AB17" s="324" t="n"/>
-      <c r="AC17" s="324" t="n"/>
-      <c r="AD17" s="324" t="n"/>
-      <c r="AE17" s="324" t="n"/>
-      <c r="AF17" s="324" t="n"/>
-      <c r="AG17" s="324" t="n"/>
-      <c r="AH17" s="324" t="n"/>
-      <c r="AI17" s="324" t="n"/>
-      <c r="AJ17" s="324" t="n"/>
-      <c r="AK17" s="324" t="n"/>
-      <c r="AL17" s="324" t="n"/>
-      <c r="AM17" s="324" t="n"/>
-      <c r="AN17" s="324" t="n"/>
-      <c r="AO17" s="324" t="n"/>
-      <c r="AP17" s="324" t="n"/>
-      <c r="AQ17" s="325" t="n"/>
-      <c r="AR17" s="296" t="n"/>
-      <c r="AS17" s="324" t="n"/>
-      <c r="AT17" s="324" t="n"/>
-      <c r="AU17" s="324" t="n"/>
-      <c r="AV17" s="324" t="n"/>
-      <c r="AW17" s="325" t="n"/>
-      <c r="AX17" s="296" t="n"/>
-      <c r="AY17" s="324" t="n"/>
-      <c r="AZ17" s="324" t="n"/>
-      <c r="BA17" s="325" t="n"/>
-      <c r="BB17" s="298" t="n"/>
-      <c r="BC17" s="324" t="n"/>
-      <c r="BD17" s="326" t="n"/>
+      <c r="E17" s="411" t="n"/>
+      <c r="F17" s="411" t="n"/>
+      <c r="G17" s="412" t="n"/>
+      <c r="H17" s="370" t="n"/>
+      <c r="I17" s="411" t="n"/>
+      <c r="J17" s="411" t="n"/>
+      <c r="K17" s="411" t="n"/>
+      <c r="L17" s="411" t="n"/>
+      <c r="M17" s="411" t="n"/>
+      <c r="N17" s="411" t="n"/>
+      <c r="O17" s="411" t="n"/>
+      <c r="P17" s="411" t="n"/>
+      <c r="Q17" s="411" t="n"/>
+      <c r="R17" s="411" t="n"/>
+      <c r="S17" s="411" t="n"/>
+      <c r="T17" s="411" t="n"/>
+      <c r="U17" s="411" t="n"/>
+      <c r="V17" s="411" t="n"/>
+      <c r="W17" s="411" t="n"/>
+      <c r="X17" s="411" t="n"/>
+      <c r="Y17" s="411" t="n"/>
+      <c r="Z17" s="412" t="n"/>
+      <c r="AA17" s="371" t="n"/>
+      <c r="AB17" s="411" t="n"/>
+      <c r="AC17" s="411" t="n"/>
+      <c r="AD17" s="411" t="n"/>
+      <c r="AE17" s="411" t="n"/>
+      <c r="AF17" s="411" t="n"/>
+      <c r="AG17" s="411" t="n"/>
+      <c r="AH17" s="411" t="n"/>
+      <c r="AI17" s="411" t="n"/>
+      <c r="AJ17" s="411" t="n"/>
+      <c r="AK17" s="411" t="n"/>
+      <c r="AL17" s="411" t="n"/>
+      <c r="AM17" s="411" t="n"/>
+      <c r="AN17" s="411" t="n"/>
+      <c r="AO17" s="411" t="n"/>
+      <c r="AP17" s="411" t="n"/>
+      <c r="AQ17" s="412" t="n"/>
+      <c r="AR17" s="370" t="n"/>
+      <c r="AS17" s="411" t="n"/>
+      <c r="AT17" s="411" t="n"/>
+      <c r="AU17" s="411" t="n"/>
+      <c r="AV17" s="411" t="n"/>
+      <c r="AW17" s="412" t="n"/>
+      <c r="AX17" s="370" t="n"/>
+      <c r="AY17" s="411" t="n"/>
+      <c r="AZ17" s="411" t="n"/>
+      <c r="BA17" s="412" t="n"/>
+      <c r="BB17" s="372" t="n"/>
+      <c r="BC17" s="411" t="n"/>
+      <c r="BD17" s="412" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="294">
+      <c r="A18" s="364">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="276" t="n"/>
-      <c r="C18" s="277" t="n"/>
-      <c r="D18" s="295" t="inlineStr">
+      <c r="B18" s="409" t="n"/>
+      <c r="C18" s="410" t="n"/>
+      <c r="D18" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="324" t="n"/>
-      <c r="F18" s="324" t="n"/>
-      <c r="G18" s="325" t="n"/>
-      <c r="H18" s="296" t="n"/>
-      <c r="I18" s="324" t="n"/>
-      <c r="J18" s="324" t="n"/>
-      <c r="K18" s="324" t="n"/>
-      <c r="L18" s="324" t="n"/>
-      <c r="M18" s="324" t="n"/>
-      <c r="N18" s="324" t="n"/>
-      <c r="O18" s="324" t="n"/>
-      <c r="P18" s="324" t="n"/>
-      <c r="Q18" s="324" t="n"/>
-      <c r="R18" s="324" t="n"/>
-      <c r="S18" s="324" t="n"/>
-      <c r="T18" s="324" t="n"/>
-      <c r="U18" s="324" t="n"/>
-      <c r="V18" s="324" t="n"/>
-      <c r="W18" s="324" t="n"/>
-      <c r="X18" s="324" t="n"/>
-      <c r="Y18" s="324" t="n"/>
-      <c r="Z18" s="325" t="n"/>
-      <c r="AA18" s="297" t="n"/>
-      <c r="AB18" s="324" t="n"/>
-      <c r="AC18" s="324" t="n"/>
-      <c r="AD18" s="324" t="n"/>
-      <c r="AE18" s="324" t="n"/>
-      <c r="AF18" s="324" t="n"/>
-      <c r="AG18" s="324" t="n"/>
-      <c r="AH18" s="324" t="n"/>
-      <c r="AI18" s="324" t="n"/>
-      <c r="AJ18" s="324" t="n"/>
-      <c r="AK18" s="324" t="n"/>
-      <c r="AL18" s="324" t="n"/>
-      <c r="AM18" s="324" t="n"/>
-      <c r="AN18" s="324" t="n"/>
-      <c r="AO18" s="324" t="n"/>
-      <c r="AP18" s="324" t="n"/>
-      <c r="AQ18" s="325" t="n"/>
-      <c r="AR18" s="296" t="n"/>
-      <c r="AS18" s="324" t="n"/>
-      <c r="AT18" s="324" t="n"/>
-      <c r="AU18" s="324" t="n"/>
-      <c r="AV18" s="324" t="n"/>
-      <c r="AW18" s="325" t="n"/>
-      <c r="AX18" s="296" t="n"/>
-      <c r="AY18" s="324" t="n"/>
-      <c r="AZ18" s="324" t="n"/>
-      <c r="BA18" s="325" t="n"/>
-      <c r="BB18" s="298" t="n"/>
-      <c r="BC18" s="324" t="n"/>
-      <c r="BD18" s="326" t="n"/>
+      <c r="E18" s="411" t="n"/>
+      <c r="F18" s="411" t="n"/>
+      <c r="G18" s="412" t="n"/>
+      <c r="H18" s="370" t="n"/>
+      <c r="I18" s="411" t="n"/>
+      <c r="J18" s="411" t="n"/>
+      <c r="K18" s="411" t="n"/>
+      <c r="L18" s="411" t="n"/>
+      <c r="M18" s="411" t="n"/>
+      <c r="N18" s="411" t="n"/>
+      <c r="O18" s="411" t="n"/>
+      <c r="P18" s="411" t="n"/>
+      <c r="Q18" s="411" t="n"/>
+      <c r="R18" s="411" t="n"/>
+      <c r="S18" s="411" t="n"/>
+      <c r="T18" s="411" t="n"/>
+      <c r="U18" s="411" t="n"/>
+      <c r="V18" s="411" t="n"/>
+      <c r="W18" s="411" t="n"/>
+      <c r="X18" s="411" t="n"/>
+      <c r="Y18" s="411" t="n"/>
+      <c r="Z18" s="412" t="n"/>
+      <c r="AA18" s="371" t="n"/>
+      <c r="AB18" s="411" t="n"/>
+      <c r="AC18" s="411" t="n"/>
+      <c r="AD18" s="411" t="n"/>
+      <c r="AE18" s="411" t="n"/>
+      <c r="AF18" s="411" t="n"/>
+      <c r="AG18" s="411" t="n"/>
+      <c r="AH18" s="411" t="n"/>
+      <c r="AI18" s="411" t="n"/>
+      <c r="AJ18" s="411" t="n"/>
+      <c r="AK18" s="411" t="n"/>
+      <c r="AL18" s="411" t="n"/>
+      <c r="AM18" s="411" t="n"/>
+      <c r="AN18" s="411" t="n"/>
+      <c r="AO18" s="411" t="n"/>
+      <c r="AP18" s="411" t="n"/>
+      <c r="AQ18" s="412" t="n"/>
+      <c r="AR18" s="370" t="n"/>
+      <c r="AS18" s="411" t="n"/>
+      <c r="AT18" s="411" t="n"/>
+      <c r="AU18" s="411" t="n"/>
+      <c r="AV18" s="411" t="n"/>
+      <c r="AW18" s="412" t="n"/>
+      <c r="AX18" s="370" t="n"/>
+      <c r="AY18" s="411" t="n"/>
+      <c r="AZ18" s="411" t="n"/>
+      <c r="BA18" s="412" t="n"/>
+      <c r="BB18" s="372" t="n"/>
+      <c r="BC18" s="411" t="n"/>
+      <c r="BD18" s="412" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="294">
+      <c r="A19" s="364">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="276" t="n"/>
-      <c r="C19" s="277" t="n"/>
-      <c r="D19" s="295" t="inlineStr">
+      <c r="B19" s="409" t="n"/>
+      <c r="C19" s="410" t="n"/>
+      <c r="D19" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="324" t="n"/>
-      <c r="F19" s="324" t="n"/>
-      <c r="G19" s="325" t="n"/>
-      <c r="H19" s="296" t="n"/>
-      <c r="I19" s="324" t="n"/>
-      <c r="J19" s="324" t="n"/>
-      <c r="K19" s="324" t="n"/>
-      <c r="L19" s="324" t="n"/>
-      <c r="M19" s="324" t="n"/>
-      <c r="N19" s="324" t="n"/>
-      <c r="O19" s="324" t="n"/>
-      <c r="P19" s="324" t="n"/>
-      <c r="Q19" s="324" t="n"/>
-      <c r="R19" s="324" t="n"/>
-      <c r="S19" s="324" t="n"/>
-      <c r="T19" s="324" t="n"/>
-      <c r="U19" s="324" t="n"/>
-      <c r="V19" s="324" t="n"/>
-      <c r="W19" s="324" t="n"/>
-      <c r="X19" s="324" t="n"/>
-      <c r="Y19" s="324" t="n"/>
-      <c r="Z19" s="325" t="n"/>
-      <c r="AA19" s="297" t="n"/>
-      <c r="AB19" s="324" t="n"/>
-      <c r="AC19" s="324" t="n"/>
-      <c r="AD19" s="324" t="n"/>
-      <c r="AE19" s="324" t="n"/>
-      <c r="AF19" s="324" t="n"/>
-      <c r="AG19" s="324" t="n"/>
-      <c r="AH19" s="324" t="n"/>
-      <c r="AI19" s="324" t="n"/>
-      <c r="AJ19" s="324" t="n"/>
-      <c r="AK19" s="324" t="n"/>
-      <c r="AL19" s="324" t="n"/>
-      <c r="AM19" s="324" t="n"/>
-      <c r="AN19" s="324" t="n"/>
-      <c r="AO19" s="324" t="n"/>
-      <c r="AP19" s="324" t="n"/>
-      <c r="AQ19" s="325" t="n"/>
-      <c r="AR19" s="296" t="n"/>
-      <c r="AS19" s="324" t="n"/>
-      <c r="AT19" s="324" t="n"/>
-      <c r="AU19" s="324" t="n"/>
-      <c r="AV19" s="324" t="n"/>
-      <c r="AW19" s="325" t="n"/>
-      <c r="AX19" s="296" t="n"/>
-      <c r="AY19" s="324" t="n"/>
-      <c r="AZ19" s="324" t="n"/>
-      <c r="BA19" s="325" t="n"/>
-      <c r="BB19" s="298" t="n"/>
-      <c r="BC19" s="324" t="n"/>
-      <c r="BD19" s="326" t="n"/>
+      <c r="E19" s="411" t="n"/>
+      <c r="F19" s="411" t="n"/>
+      <c r="G19" s="412" t="n"/>
+      <c r="H19" s="370" t="n"/>
+      <c r="I19" s="411" t="n"/>
+      <c r="J19" s="411" t="n"/>
+      <c r="K19" s="411" t="n"/>
+      <c r="L19" s="411" t="n"/>
+      <c r="M19" s="411" t="n"/>
+      <c r="N19" s="411" t="n"/>
+      <c r="O19" s="411" t="n"/>
+      <c r="P19" s="411" t="n"/>
+      <c r="Q19" s="411" t="n"/>
+      <c r="R19" s="411" t="n"/>
+      <c r="S19" s="411" t="n"/>
+      <c r="T19" s="411" t="n"/>
+      <c r="U19" s="411" t="n"/>
+      <c r="V19" s="411" t="n"/>
+      <c r="W19" s="411" t="n"/>
+      <c r="X19" s="411" t="n"/>
+      <c r="Y19" s="411" t="n"/>
+      <c r="Z19" s="412" t="n"/>
+      <c r="AA19" s="371" t="n"/>
+      <c r="AB19" s="411" t="n"/>
+      <c r="AC19" s="411" t="n"/>
+      <c r="AD19" s="411" t="n"/>
+      <c r="AE19" s="411" t="n"/>
+      <c r="AF19" s="411" t="n"/>
+      <c r="AG19" s="411" t="n"/>
+      <c r="AH19" s="411" t="n"/>
+      <c r="AI19" s="411" t="n"/>
+      <c r="AJ19" s="411" t="n"/>
+      <c r="AK19" s="411" t="n"/>
+      <c r="AL19" s="411" t="n"/>
+      <c r="AM19" s="411" t="n"/>
+      <c r="AN19" s="411" t="n"/>
+      <c r="AO19" s="411" t="n"/>
+      <c r="AP19" s="411" t="n"/>
+      <c r="AQ19" s="412" t="n"/>
+      <c r="AR19" s="370" t="n"/>
+      <c r="AS19" s="411" t="n"/>
+      <c r="AT19" s="411" t="n"/>
+      <c r="AU19" s="411" t="n"/>
+      <c r="AV19" s="411" t="n"/>
+      <c r="AW19" s="412" t="n"/>
+      <c r="AX19" s="370" t="n"/>
+      <c r="AY19" s="411" t="n"/>
+      <c r="AZ19" s="411" t="n"/>
+      <c r="BA19" s="412" t="n"/>
+      <c r="BB19" s="372" t="n"/>
+      <c r="BC19" s="411" t="n"/>
+      <c r="BD19" s="412" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="294">
+      <c r="A20" s="364">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="276" t="n"/>
-      <c r="C20" s="277" t="n"/>
-      <c r="D20" s="295" t="inlineStr">
+      <c r="B20" s="409" t="n"/>
+      <c r="C20" s="410" t="n"/>
+      <c r="D20" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="324" t="n"/>
-      <c r="F20" s="324" t="n"/>
-      <c r="G20" s="325" t="n"/>
-      <c r="H20" s="296" t="n"/>
-      <c r="I20" s="324" t="n"/>
-      <c r="J20" s="324" t="n"/>
-      <c r="K20" s="324" t="n"/>
-      <c r="L20" s="324" t="n"/>
-      <c r="M20" s="324" t="n"/>
-      <c r="N20" s="324" t="n"/>
-      <c r="O20" s="324" t="n"/>
-      <c r="P20" s="324" t="n"/>
-      <c r="Q20" s="324" t="n"/>
-      <c r="R20" s="324" t="n"/>
-      <c r="S20" s="324" t="n"/>
-      <c r="T20" s="324" t="n"/>
-      <c r="U20" s="324" t="n"/>
-      <c r="V20" s="324" t="n"/>
-      <c r="W20" s="324" t="n"/>
-      <c r="X20" s="324" t="n"/>
-      <c r="Y20" s="324" t="n"/>
-      <c r="Z20" s="325" t="n"/>
-      <c r="AA20" s="297" t="n"/>
-      <c r="AB20" s="324" t="n"/>
-      <c r="AC20" s="324" t="n"/>
-      <c r="AD20" s="324" t="n"/>
-      <c r="AE20" s="324" t="n"/>
-      <c r="AF20" s="324" t="n"/>
-      <c r="AG20" s="324" t="n"/>
-      <c r="AH20" s="324" t="n"/>
-      <c r="AI20" s="324" t="n"/>
-      <c r="AJ20" s="324" t="n"/>
-      <c r="AK20" s="324" t="n"/>
-      <c r="AL20" s="324" t="n"/>
-      <c r="AM20" s="324" t="n"/>
-      <c r="AN20" s="324" t="n"/>
-      <c r="AO20" s="324" t="n"/>
-      <c r="AP20" s="324" t="n"/>
-      <c r="AQ20" s="325" t="n"/>
-      <c r="AR20" s="296" t="n"/>
-      <c r="AS20" s="324" t="n"/>
-      <c r="AT20" s="324" t="n"/>
-      <c r="AU20" s="324" t="n"/>
-      <c r="AV20" s="324" t="n"/>
-      <c r="AW20" s="325" t="n"/>
-      <c r="AX20" s="296" t="n"/>
-      <c r="AY20" s="324" t="n"/>
-      <c r="AZ20" s="324" t="n"/>
-      <c r="BA20" s="325" t="n"/>
-      <c r="BB20" s="298" t="n"/>
-      <c r="BC20" s="324" t="n"/>
-      <c r="BD20" s="326" t="n"/>
+      <c r="E20" s="411" t="n"/>
+      <c r="F20" s="411" t="n"/>
+      <c r="G20" s="412" t="n"/>
+      <c r="H20" s="370" t="n"/>
+      <c r="I20" s="411" t="n"/>
+      <c r="J20" s="411" t="n"/>
+      <c r="K20" s="411" t="n"/>
+      <c r="L20" s="411" t="n"/>
+      <c r="M20" s="411" t="n"/>
+      <c r="N20" s="411" t="n"/>
+      <c r="O20" s="411" t="n"/>
+      <c r="P20" s="411" t="n"/>
+      <c r="Q20" s="411" t="n"/>
+      <c r="R20" s="411" t="n"/>
+      <c r="S20" s="411" t="n"/>
+      <c r="T20" s="411" t="n"/>
+      <c r="U20" s="411" t="n"/>
+      <c r="V20" s="411" t="n"/>
+      <c r="W20" s="411" t="n"/>
+      <c r="X20" s="411" t="n"/>
+      <c r="Y20" s="411" t="n"/>
+      <c r="Z20" s="412" t="n"/>
+      <c r="AA20" s="371" t="n"/>
+      <c r="AB20" s="411" t="n"/>
+      <c r="AC20" s="411" t="n"/>
+      <c r="AD20" s="411" t="n"/>
+      <c r="AE20" s="411" t="n"/>
+      <c r="AF20" s="411" t="n"/>
+      <c r="AG20" s="411" t="n"/>
+      <c r="AH20" s="411" t="n"/>
+      <c r="AI20" s="411" t="n"/>
+      <c r="AJ20" s="411" t="n"/>
+      <c r="AK20" s="411" t="n"/>
+      <c r="AL20" s="411" t="n"/>
+      <c r="AM20" s="411" t="n"/>
+      <c r="AN20" s="411" t="n"/>
+      <c r="AO20" s="411" t="n"/>
+      <c r="AP20" s="411" t="n"/>
+      <c r="AQ20" s="412" t="n"/>
+      <c r="AR20" s="370" t="n"/>
+      <c r="AS20" s="411" t="n"/>
+      <c r="AT20" s="411" t="n"/>
+      <c r="AU20" s="411" t="n"/>
+      <c r="AV20" s="411" t="n"/>
+      <c r="AW20" s="412" t="n"/>
+      <c r="AX20" s="370" t="n"/>
+      <c r="AY20" s="411" t="n"/>
+      <c r="AZ20" s="411" t="n"/>
+      <c r="BA20" s="412" t="n"/>
+      <c r="BB20" s="372" t="n"/>
+      <c r="BC20" s="411" t="n"/>
+      <c r="BD20" s="412" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="294">
+      <c r="A21" s="364">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="276" t="n"/>
-      <c r="C21" s="277" t="n"/>
-      <c r="D21" s="295" t="inlineStr">
+      <c r="B21" s="409" t="n"/>
+      <c r="C21" s="410" t="n"/>
+      <c r="D21" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="324" t="n"/>
-      <c r="F21" s="324" t="n"/>
-      <c r="G21" s="325" t="n"/>
-      <c r="H21" s="296" t="n"/>
-      <c r="I21" s="324" t="n"/>
-      <c r="J21" s="324" t="n"/>
-      <c r="K21" s="324" t="n"/>
-      <c r="L21" s="324" t="n"/>
-      <c r="M21" s="324" t="n"/>
-      <c r="N21" s="324" t="n"/>
-      <c r="O21" s="324" t="n"/>
-      <c r="P21" s="324" t="n"/>
-      <c r="Q21" s="324" t="n"/>
-      <c r="R21" s="324" t="n"/>
-      <c r="S21" s="324" t="n"/>
-      <c r="T21" s="324" t="n"/>
-      <c r="U21" s="324" t="n"/>
-      <c r="V21" s="324" t="n"/>
-      <c r="W21" s="324" t="n"/>
-      <c r="X21" s="324" t="n"/>
-      <c r="Y21" s="324" t="n"/>
-      <c r="Z21" s="325" t="n"/>
-      <c r="AA21" s="297" t="n"/>
-      <c r="AB21" s="324" t="n"/>
-      <c r="AC21" s="324" t="n"/>
-      <c r="AD21" s="324" t="n"/>
-      <c r="AE21" s="324" t="n"/>
-      <c r="AF21" s="324" t="n"/>
-      <c r="AG21" s="324" t="n"/>
-      <c r="AH21" s="324" t="n"/>
-      <c r="AI21" s="324" t="n"/>
-      <c r="AJ21" s="324" t="n"/>
-      <c r="AK21" s="324" t="n"/>
-      <c r="AL21" s="324" t="n"/>
-      <c r="AM21" s="324" t="n"/>
-      <c r="AN21" s="324" t="n"/>
-      <c r="AO21" s="324" t="n"/>
-      <c r="AP21" s="324" t="n"/>
-      <c r="AQ21" s="325" t="n"/>
-      <c r="AR21" s="296" t="n"/>
-      <c r="AS21" s="324" t="n"/>
-      <c r="AT21" s="324" t="n"/>
-      <c r="AU21" s="324" t="n"/>
-      <c r="AV21" s="324" t="n"/>
-      <c r="AW21" s="325" t="n"/>
-      <c r="AX21" s="296" t="n"/>
-      <c r="AY21" s="324" t="n"/>
-      <c r="AZ21" s="324" t="n"/>
-      <c r="BA21" s="325" t="n"/>
-      <c r="BB21" s="298" t="n"/>
-      <c r="BC21" s="324" t="n"/>
-      <c r="BD21" s="326" t="n"/>
+      <c r="E21" s="411" t="n"/>
+      <c r="F21" s="411" t="n"/>
+      <c r="G21" s="412" t="n"/>
+      <c r="H21" s="370" t="n"/>
+      <c r="I21" s="411" t="n"/>
+      <c r="J21" s="411" t="n"/>
+      <c r="K21" s="411" t="n"/>
+      <c r="L21" s="411" t="n"/>
+      <c r="M21" s="411" t="n"/>
+      <c r="N21" s="411" t="n"/>
+      <c r="O21" s="411" t="n"/>
+      <c r="P21" s="411" t="n"/>
+      <c r="Q21" s="411" t="n"/>
+      <c r="R21" s="411" t="n"/>
+      <c r="S21" s="411" t="n"/>
+      <c r="T21" s="411" t="n"/>
+      <c r="U21" s="411" t="n"/>
+      <c r="V21" s="411" t="n"/>
+      <c r="W21" s="411" t="n"/>
+      <c r="X21" s="411" t="n"/>
+      <c r="Y21" s="411" t="n"/>
+      <c r="Z21" s="412" t="n"/>
+      <c r="AA21" s="371" t="n"/>
+      <c r="AB21" s="411" t="n"/>
+      <c r="AC21" s="411" t="n"/>
+      <c r="AD21" s="411" t="n"/>
+      <c r="AE21" s="411" t="n"/>
+      <c r="AF21" s="411" t="n"/>
+      <c r="AG21" s="411" t="n"/>
+      <c r="AH21" s="411" t="n"/>
+      <c r="AI21" s="411" t="n"/>
+      <c r="AJ21" s="411" t="n"/>
+      <c r="AK21" s="411" t="n"/>
+      <c r="AL21" s="411" t="n"/>
+      <c r="AM21" s="411" t="n"/>
+      <c r="AN21" s="411" t="n"/>
+      <c r="AO21" s="411" t="n"/>
+      <c r="AP21" s="411" t="n"/>
+      <c r="AQ21" s="412" t="n"/>
+      <c r="AR21" s="370" t="n"/>
+      <c r="AS21" s="411" t="n"/>
+      <c r="AT21" s="411" t="n"/>
+      <c r="AU21" s="411" t="n"/>
+      <c r="AV21" s="411" t="n"/>
+      <c r="AW21" s="412" t="n"/>
+      <c r="AX21" s="370" t="n"/>
+      <c r="AY21" s="411" t="n"/>
+      <c r="AZ21" s="411" t="n"/>
+      <c r="BA21" s="412" t="n"/>
+      <c r="BB21" s="372" t="n"/>
+      <c r="BC21" s="411" t="n"/>
+      <c r="BD21" s="412" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="294">
+      <c r="A22" s="364">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="276" t="n"/>
-      <c r="C22" s="277" t="n"/>
-      <c r="D22" s="295" t="inlineStr">
+      <c r="B22" s="409" t="n"/>
+      <c r="C22" s="410" t="n"/>
+      <c r="D22" s="367" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="324" t="n"/>
-      <c r="F22" s="324" t="n"/>
-      <c r="G22" s="325" t="n"/>
-      <c r="H22" s="296" t="n"/>
-      <c r="I22" s="324" t="n"/>
-      <c r="J22" s="324" t="n"/>
-      <c r="K22" s="324" t="n"/>
-      <c r="L22" s="324" t="n"/>
-      <c r="M22" s="324" t="n"/>
-      <c r="N22" s="324" t="n"/>
-      <c r="O22" s="324" t="n"/>
-      <c r="P22" s="324" t="n"/>
-      <c r="Q22" s="324" t="n"/>
-      <c r="R22" s="324" t="n"/>
-      <c r="S22" s="324" t="n"/>
-      <c r="T22" s="324" t="n"/>
-      <c r="U22" s="324" t="n"/>
-      <c r="V22" s="324" t="n"/>
-      <c r="W22" s="324" t="n"/>
-      <c r="X22" s="324" t="n"/>
-      <c r="Y22" s="324" t="n"/>
-      <c r="Z22" s="325" t="n"/>
-      <c r="AA22" s="297" t="n"/>
-      <c r="AB22" s="324" t="n"/>
-      <c r="AC22" s="324" t="n"/>
-      <c r="AD22" s="324" t="n"/>
-      <c r="AE22" s="324" t="n"/>
-      <c r="AF22" s="324" t="n"/>
-      <c r="AG22" s="324" t="n"/>
-      <c r="AH22" s="324" t="n"/>
-      <c r="AI22" s="324" t="n"/>
-      <c r="AJ22" s="324" t="n"/>
-      <c r="AK22" s="324" t="n"/>
-      <c r="AL22" s="324" t="n"/>
-      <c r="AM22" s="324" t="n"/>
-      <c r="AN22" s="324" t="n"/>
-      <c r="AO22" s="324" t="n"/>
-      <c r="AP22" s="324" t="n"/>
-      <c r="AQ22" s="325" t="n"/>
-      <c r="AR22" s="296" t="n"/>
-      <c r="AS22" s="324" t="n"/>
-      <c r="AT22" s="324" t="n"/>
-      <c r="AU22" s="324" t="n"/>
-      <c r="AV22" s="324" t="n"/>
-      <c r="AW22" s="325" t="n"/>
-      <c r="AX22" s="296" t="n"/>
-      <c r="AY22" s="324" t="n"/>
-      <c r="AZ22" s="324" t="n"/>
-      <c r="BA22" s="325" t="n"/>
-      <c r="BB22" s="298" t="n"/>
-      <c r="BC22" s="324" t="n"/>
-      <c r="BD22" s="326" t="n"/>
+      <c r="E22" s="411" t="n"/>
+      <c r="F22" s="411" t="n"/>
+      <c r="G22" s="412" t="n"/>
+      <c r="H22" s="370" t="n"/>
+      <c r="I22" s="411" t="n"/>
+      <c r="J22" s="411" t="n"/>
+      <c r="K22" s="411" t="n"/>
+      <c r="L22" s="411" t="n"/>
+      <c r="M22" s="411" t="n"/>
+      <c r="N22" s="411" t="n"/>
+      <c r="O22" s="411" t="n"/>
+      <c r="P22" s="411" t="n"/>
+      <c r="Q22" s="411" t="n"/>
+      <c r="R22" s="411" t="n"/>
+      <c r="S22" s="411" t="n"/>
+      <c r="T22" s="411" t="n"/>
+      <c r="U22" s="411" t="n"/>
+      <c r="V22" s="411" t="n"/>
+      <c r="W22" s="411" t="n"/>
+      <c r="X22" s="411" t="n"/>
+      <c r="Y22" s="411" t="n"/>
+      <c r="Z22" s="412" t="n"/>
+      <c r="AA22" s="371" t="n"/>
+      <c r="AB22" s="411" t="n"/>
+      <c r="AC22" s="411" t="n"/>
+      <c r="AD22" s="411" t="n"/>
+      <c r="AE22" s="411" t="n"/>
+      <c r="AF22" s="411" t="n"/>
+      <c r="AG22" s="411" t="n"/>
+      <c r="AH22" s="411" t="n"/>
+      <c r="AI22" s="411" t="n"/>
+      <c r="AJ22" s="411" t="n"/>
+      <c r="AK22" s="411" t="n"/>
+      <c r="AL22" s="411" t="n"/>
+      <c r="AM22" s="411" t="n"/>
+      <c r="AN22" s="411" t="n"/>
+      <c r="AO22" s="411" t="n"/>
+      <c r="AP22" s="411" t="n"/>
+      <c r="AQ22" s="412" t="n"/>
+      <c r="AR22" s="370" t="n"/>
+      <c r="AS22" s="411" t="n"/>
+      <c r="AT22" s="411" t="n"/>
+      <c r="AU22" s="411" t="n"/>
+      <c r="AV22" s="411" t="n"/>
+      <c r="AW22" s="412" t="n"/>
+      <c r="AX22" s="370" t="n"/>
+      <c r="AY22" s="411" t="n"/>
+      <c r="AZ22" s="411" t="n"/>
+      <c r="BA22" s="412" t="n"/>
+      <c r="BB22" s="372" t="n"/>
+      <c r="BC22" s="411" t="n"/>
+      <c r="BD22" s="412" t="n"/>
     </row>
     <row r="23" ht="4" customHeight="1">
-      <c r="A23" s="294" t="n"/>
-      <c r="D23" s="299" t="n"/>
-      <c r="H23" s="300" t="n"/>
-      <c r="AA23" s="301" t="n"/>
-      <c r="AR23" s="302" t="n"/>
-      <c r="AX23" s="302" t="n"/>
-      <c r="BB23" s="303" t="n"/>
+      <c r="A23" s="373" t="n"/>
+      <c r="B23" s="351" t="n"/>
+      <c r="C23" s="351" t="n"/>
+      <c r="D23" s="374" t="n"/>
+      <c r="E23" s="351" t="n"/>
+      <c r="F23" s="351" t="n"/>
+      <c r="G23" s="351" t="n"/>
+      <c r="H23" s="375" t="n"/>
+      <c r="I23" s="351" t="n"/>
+      <c r="J23" s="351" t="n"/>
+      <c r="K23" s="351" t="n"/>
+      <c r="L23" s="351" t="n"/>
+      <c r="M23" s="351" t="n"/>
+      <c r="N23" s="351" t="n"/>
+      <c r="O23" s="351" t="n"/>
+      <c r="P23" s="351" t="n"/>
+      <c r="Q23" s="351" t="n"/>
+      <c r="R23" s="351" t="n"/>
+      <c r="S23" s="351" t="n"/>
+      <c r="T23" s="351" t="n"/>
+      <c r="U23" s="351" t="n"/>
+      <c r="V23" s="351" t="n"/>
+      <c r="W23" s="351" t="n"/>
+      <c r="X23" s="351" t="n"/>
+      <c r="Y23" s="351" t="n"/>
+      <c r="Z23" s="351" t="n"/>
+      <c r="AA23" s="376" t="n"/>
+      <c r="AB23" s="351" t="n"/>
+      <c r="AC23" s="351" t="n"/>
+      <c r="AD23" s="351" t="n"/>
+      <c r="AE23" s="351" t="n"/>
+      <c r="AF23" s="351" t="n"/>
+      <c r="AG23" s="351" t="n"/>
+      <c r="AH23" s="351" t="n"/>
+      <c r="AI23" s="351" t="n"/>
+      <c r="AJ23" s="351" t="n"/>
+      <c r="AK23" s="351" t="n"/>
+      <c r="AL23" s="351" t="n"/>
+      <c r="AM23" s="351" t="n"/>
+      <c r="AN23" s="351" t="n"/>
+      <c r="AO23" s="351" t="n"/>
+      <c r="AP23" s="351" t="n"/>
+      <c r="AQ23" s="351" t="n"/>
+      <c r="AR23" s="377" t="n"/>
+      <c r="AS23" s="351" t="n"/>
+      <c r="AT23" s="351" t="n"/>
+      <c r="AU23" s="351" t="n"/>
+      <c r="AV23" s="351" t="n"/>
+      <c r="AW23" s="351" t="n"/>
+      <c r="AX23" s="377" t="n"/>
+      <c r="AY23" s="351" t="n"/>
+      <c r="AZ23" s="351" t="n"/>
+      <c r="BA23" s="351" t="n"/>
+      <c r="BB23" s="378" t="n"/>
+      <c r="BC23" s="351" t="n"/>
+      <c r="BD23" s="351" t="n"/>
     </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="284" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="352" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B24" s="285" t="n"/>
-      <c r="C24" s="285" t="n"/>
-      <c r="D24" s="285" t="n"/>
-      <c r="E24" s="285" t="n"/>
-      <c r="F24" s="285" t="n"/>
-      <c r="G24" s="285" t="n"/>
-      <c r="H24" s="285" t="n"/>
-      <c r="I24" s="285" t="n"/>
-      <c r="J24" s="285" t="n"/>
-      <c r="K24" s="285" t="n"/>
-      <c r="L24" s="285" t="n"/>
-      <c r="M24" s="285" t="n"/>
-      <c r="N24" s="285" t="n"/>
-      <c r="O24" s="285" t="n"/>
-      <c r="P24" s="285" t="n"/>
-      <c r="Q24" s="285" t="n"/>
-      <c r="R24" s="285" t="n"/>
-      <c r="S24" s="285" t="n"/>
-      <c r="T24" s="285" t="n"/>
-      <c r="U24" s="285" t="n"/>
-      <c r="V24" s="285" t="n"/>
-      <c r="W24" s="285" t="n"/>
-      <c r="X24" s="285" t="n"/>
-      <c r="Y24" s="285" t="n"/>
-      <c r="Z24" s="285" t="n"/>
-      <c r="AA24" s="285" t="n"/>
-      <c r="AB24" s="285" t="n"/>
-      <c r="AC24" s="285" t="n"/>
-      <c r="AD24" s="285" t="n"/>
-      <c r="AE24" s="285" t="n"/>
-      <c r="AF24" s="285" t="n"/>
-      <c r="AG24" s="285" t="n"/>
-      <c r="AH24" s="285" t="n"/>
-      <c r="AI24" s="285" t="n"/>
-      <c r="AJ24" s="285" t="n"/>
-      <c r="AK24" s="285" t="n"/>
-      <c r="AL24" s="285" t="n"/>
-      <c r="AM24" s="285" t="n"/>
-      <c r="AN24" s="285" t="n"/>
-      <c r="AO24" s="285" t="n"/>
-      <c r="AP24" s="285" t="n"/>
-      <c r="AQ24" s="285" t="n"/>
-      <c r="AR24" s="285" t="n"/>
-      <c r="AS24" s="285" t="n"/>
-      <c r="AT24" s="285" t="n"/>
-      <c r="AU24" s="285" t="n"/>
-      <c r="AV24" s="285" t="n"/>
-      <c r="AW24" s="285" t="n"/>
-      <c r="AX24" s="285" t="n"/>
-      <c r="AY24" s="285" t="n"/>
-      <c r="AZ24" s="285" t="n"/>
-      <c r="BA24" s="285" t="n"/>
-      <c r="BB24" s="285" t="n"/>
-      <c r="BC24" s="285" t="n"/>
-      <c r="BD24" s="286" t="n"/>
+      <c r="B24" s="403" t="n"/>
+      <c r="C24" s="403" t="n"/>
+      <c r="D24" s="403" t="n"/>
+      <c r="E24" s="403" t="n"/>
+      <c r="F24" s="403" t="n"/>
+      <c r="G24" s="403" t="n"/>
+      <c r="H24" s="403" t="n"/>
+      <c r="I24" s="403" t="n"/>
+      <c r="J24" s="403" t="n"/>
+      <c r="K24" s="403" t="n"/>
+      <c r="L24" s="403" t="n"/>
+      <c r="M24" s="403" t="n"/>
+      <c r="N24" s="403" t="n"/>
+      <c r="O24" s="403" t="n"/>
+      <c r="P24" s="403" t="n"/>
+      <c r="Q24" s="403" t="n"/>
+      <c r="R24" s="403" t="n"/>
+      <c r="S24" s="403" t="n"/>
+      <c r="T24" s="403" t="n"/>
+      <c r="U24" s="403" t="n"/>
+      <c r="V24" s="403" t="n"/>
+      <c r="W24" s="403" t="n"/>
+      <c r="X24" s="403" t="n"/>
+      <c r="Y24" s="403" t="n"/>
+      <c r="Z24" s="403" t="n"/>
+      <c r="AA24" s="403" t="n"/>
+      <c r="AB24" s="403" t="n"/>
+      <c r="AC24" s="403" t="n"/>
+      <c r="AD24" s="403" t="n"/>
+      <c r="AE24" s="403" t="n"/>
+      <c r="AF24" s="403" t="n"/>
+      <c r="AG24" s="403" t="n"/>
+      <c r="AH24" s="403" t="n"/>
+      <c r="AI24" s="403" t="n"/>
+      <c r="AJ24" s="403" t="n"/>
+      <c r="AK24" s="403" t="n"/>
+      <c r="AL24" s="403" t="n"/>
+      <c r="AM24" s="403" t="n"/>
+      <c r="AN24" s="403" t="n"/>
+      <c r="AO24" s="403" t="n"/>
+      <c r="AP24" s="403" t="n"/>
+      <c r="AQ24" s="403" t="n"/>
+      <c r="AR24" s="403" t="n"/>
+      <c r="AS24" s="403" t="n"/>
+      <c r="AT24" s="403" t="n"/>
+      <c r="AU24" s="403" t="n"/>
+      <c r="AV24" s="403" t="n"/>
+      <c r="AW24" s="403" t="n"/>
+      <c r="AX24" s="403" t="n"/>
+      <c r="AY24" s="403" t="n"/>
+      <c r="AZ24" s="403" t="n"/>
+      <c r="BA24" s="403" t="n"/>
+      <c r="BB24" s="403" t="n"/>
+      <c r="BC24" s="403" t="n"/>
+      <c r="BD24" s="404" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="287" t="inlineStr">
+      <c r="A25" s="353" t="inlineStr">
         <is>
           <t>Disposition / Release Decision</t>
         </is>
       </c>
-      <c r="B25" s="271" t="n"/>
-      <c r="C25" s="271" t="n"/>
-      <c r="D25" s="271" t="n"/>
-      <c r="E25" s="271" t="n"/>
-      <c r="F25" s="271" t="n"/>
-      <c r="G25" s="271" t="n"/>
-      <c r="H25" s="271" t="n"/>
-      <c r="I25" s="271" t="n"/>
-      <c r="J25" s="272" t="n"/>
-      <c r="K25" s="288" t="n"/>
-      <c r="L25" s="321" t="n"/>
-      <c r="M25" s="321" t="n"/>
-      <c r="N25" s="321" t="n"/>
-      <c r="O25" s="321" t="n"/>
-      <c r="P25" s="321" t="n"/>
-      <c r="Q25" s="321" t="n"/>
-      <c r="R25" s="321" t="n"/>
-      <c r="S25" s="321" t="n"/>
-      <c r="T25" s="321" t="n"/>
-      <c r="U25" s="321" t="n"/>
-      <c r="V25" s="321" t="n"/>
-      <c r="W25" s="321" t="n"/>
-      <c r="X25" s="321" t="n"/>
-      <c r="Y25" s="321" t="n"/>
-      <c r="Z25" s="321" t="n"/>
-      <c r="AA25" s="321" t="n"/>
-      <c r="AB25" s="322" t="n"/>
-      <c r="AC25" s="289" t="inlineStr">
+      <c r="B25" s="403" t="n"/>
+      <c r="C25" s="403" t="n"/>
+      <c r="D25" s="403" t="n"/>
+      <c r="E25" s="403" t="n"/>
+      <c r="F25" s="403" t="n"/>
+      <c r="G25" s="403" t="n"/>
+      <c r="H25" s="403" t="n"/>
+      <c r="I25" s="403" t="n"/>
+      <c r="J25" s="404" t="n"/>
+      <c r="K25" s="356" t="n"/>
+      <c r="L25" s="405" t="n"/>
+      <c r="M25" s="405" t="n"/>
+      <c r="N25" s="405" t="n"/>
+      <c r="O25" s="405" t="n"/>
+      <c r="P25" s="405" t="n"/>
+      <c r="Q25" s="405" t="n"/>
+      <c r="R25" s="405" t="n"/>
+      <c r="S25" s="405" t="n"/>
+      <c r="T25" s="405" t="n"/>
+      <c r="U25" s="405" t="n"/>
+      <c r="V25" s="405" t="n"/>
+      <c r="W25" s="405" t="n"/>
+      <c r="X25" s="405" t="n"/>
+      <c r="Y25" s="405" t="n"/>
+      <c r="Z25" s="405" t="n"/>
+      <c r="AA25" s="405" t="n"/>
+      <c r="AB25" s="406" t="n"/>
+      <c r="AC25" s="359" t="inlineStr">
         <is>
           <t>Linked NCR / Concession</t>
         </is>
       </c>
-      <c r="AD25" s="271" t="n"/>
-      <c r="AE25" s="271" t="n"/>
-      <c r="AF25" s="271" t="n"/>
-      <c r="AG25" s="271" t="n"/>
-      <c r="AH25" s="271" t="n"/>
-      <c r="AI25" s="271" t="n"/>
-      <c r="AJ25" s="271" t="n"/>
-      <c r="AK25" s="271" t="n"/>
-      <c r="AL25" s="272" t="n"/>
-      <c r="AM25" s="290" t="n"/>
-      <c r="AN25" s="321" t="n"/>
-      <c r="AO25" s="321" t="n"/>
-      <c r="AP25" s="321" t="n"/>
-      <c r="AQ25" s="321" t="n"/>
-      <c r="AR25" s="321" t="n"/>
-      <c r="AS25" s="321" t="n"/>
-      <c r="AT25" s="321" t="n"/>
-      <c r="AU25" s="321" t="n"/>
-      <c r="AV25" s="321" t="n"/>
-      <c r="AW25" s="321" t="n"/>
-      <c r="AX25" s="321" t="n"/>
-      <c r="AY25" s="321" t="n"/>
-      <c r="AZ25" s="321" t="n"/>
-      <c r="BA25" s="321" t="n"/>
-      <c r="BB25" s="321" t="n"/>
-      <c r="BC25" s="321" t="n"/>
-      <c r="BD25" s="323" t="n"/>
+      <c r="AD25" s="403" t="n"/>
+      <c r="AE25" s="403" t="n"/>
+      <c r="AF25" s="403" t="n"/>
+      <c r="AG25" s="403" t="n"/>
+      <c r="AH25" s="403" t="n"/>
+      <c r="AI25" s="403" t="n"/>
+      <c r="AJ25" s="403" t="n"/>
+      <c r="AK25" s="403" t="n"/>
+      <c r="AL25" s="404" t="n"/>
+      <c r="AM25" s="356" t="n"/>
+      <c r="AN25" s="405" t="n"/>
+      <c r="AO25" s="405" t="n"/>
+      <c r="AP25" s="405" t="n"/>
+      <c r="AQ25" s="405" t="n"/>
+      <c r="AR25" s="405" t="n"/>
+      <c r="AS25" s="405" t="n"/>
+      <c r="AT25" s="405" t="n"/>
+      <c r="AU25" s="405" t="n"/>
+      <c r="AV25" s="405" t="n"/>
+      <c r="AW25" s="405" t="n"/>
+      <c r="AX25" s="405" t="n"/>
+      <c r="AY25" s="405" t="n"/>
+      <c r="AZ25" s="405" t="n"/>
+      <c r="BA25" s="405" t="n"/>
+      <c r="BB25" s="405" t="n"/>
+      <c r="BC25" s="405" t="n"/>
+      <c r="BD25" s="406" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="287" t="inlineStr">
+      <c r="A26" s="353" t="inlineStr">
         <is>
           <t>Cleanliness / Packaging Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="271" t="n"/>
-      <c r="C26" s="271" t="n"/>
-      <c r="D26" s="271" t="n"/>
-      <c r="E26" s="271" t="n"/>
-      <c r="F26" s="271" t="n"/>
-      <c r="G26" s="271" t="n"/>
-      <c r="H26" s="271" t="n"/>
-      <c r="I26" s="271" t="n"/>
-      <c r="J26" s="272" t="n"/>
-      <c r="K26" s="288" t="n"/>
-      <c r="L26" s="321" t="n"/>
-      <c r="M26" s="321" t="n"/>
-      <c r="N26" s="321" t="n"/>
-      <c r="O26" s="321" t="n"/>
-      <c r="P26" s="321" t="n"/>
-      <c r="Q26" s="321" t="n"/>
-      <c r="R26" s="321" t="n"/>
-      <c r="S26" s="321" t="n"/>
-      <c r="T26" s="321" t="n"/>
-      <c r="U26" s="321" t="n"/>
-      <c r="V26" s="321" t="n"/>
-      <c r="W26" s="321" t="n"/>
-      <c r="X26" s="321" t="n"/>
-      <c r="Y26" s="321" t="n"/>
-      <c r="Z26" s="321" t="n"/>
-      <c r="AA26" s="321" t="n"/>
-      <c r="AB26" s="322" t="n"/>
-      <c r="AC26" s="289" t="inlineStr">
+      <c r="B26" s="403" t="n"/>
+      <c r="C26" s="403" t="n"/>
+      <c r="D26" s="403" t="n"/>
+      <c r="E26" s="403" t="n"/>
+      <c r="F26" s="403" t="n"/>
+      <c r="G26" s="403" t="n"/>
+      <c r="H26" s="403" t="n"/>
+      <c r="I26" s="403" t="n"/>
+      <c r="J26" s="404" t="n"/>
+      <c r="K26" s="356" t="n"/>
+      <c r="L26" s="405" t="n"/>
+      <c r="M26" s="405" t="n"/>
+      <c r="N26" s="405" t="n"/>
+      <c r="O26" s="405" t="n"/>
+      <c r="P26" s="405" t="n"/>
+      <c r="Q26" s="405" t="n"/>
+      <c r="R26" s="405" t="n"/>
+      <c r="S26" s="405" t="n"/>
+      <c r="T26" s="405" t="n"/>
+      <c r="U26" s="405" t="n"/>
+      <c r="V26" s="405" t="n"/>
+      <c r="W26" s="405" t="n"/>
+      <c r="X26" s="405" t="n"/>
+      <c r="Y26" s="405" t="n"/>
+      <c r="Z26" s="405" t="n"/>
+      <c r="AA26" s="405" t="n"/>
+      <c r="AB26" s="406" t="n"/>
+      <c r="AC26" s="359" t="inlineStr">
         <is>
           <t>Label / Doc Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="AD26" s="271" t="n"/>
-      <c r="AE26" s="271" t="n"/>
-      <c r="AF26" s="271" t="n"/>
-      <c r="AG26" s="271" t="n"/>
-      <c r="AH26" s="271" t="n"/>
-      <c r="AI26" s="271" t="n"/>
-      <c r="AJ26" s="271" t="n"/>
-      <c r="AK26" s="271" t="n"/>
-      <c r="AL26" s="272" t="n"/>
-      <c r="AM26" s="290" t="n"/>
-      <c r="AN26" s="321" t="n"/>
-      <c r="AO26" s="321" t="n"/>
-      <c r="AP26" s="321" t="n"/>
-      <c r="AQ26" s="321" t="n"/>
-      <c r="AR26" s="321" t="n"/>
-      <c r="AS26" s="321" t="n"/>
-      <c r="AT26" s="321" t="n"/>
-      <c r="AU26" s="321" t="n"/>
-      <c r="AV26" s="321" t="n"/>
-      <c r="AW26" s="321" t="n"/>
-      <c r="AX26" s="321" t="n"/>
-      <c r="AY26" s="321" t="n"/>
-      <c r="AZ26" s="321" t="n"/>
-      <c r="BA26" s="321" t="n"/>
-      <c r="BB26" s="321" t="n"/>
-      <c r="BC26" s="321" t="n"/>
-      <c r="BD26" s="323" t="n"/>
+      <c r="AD26" s="403" t="n"/>
+      <c r="AE26" s="403" t="n"/>
+      <c r="AF26" s="403" t="n"/>
+      <c r="AG26" s="403" t="n"/>
+      <c r="AH26" s="403" t="n"/>
+      <c r="AI26" s="403" t="n"/>
+      <c r="AJ26" s="403" t="n"/>
+      <c r="AK26" s="403" t="n"/>
+      <c r="AL26" s="404" t="n"/>
+      <c r="AM26" s="356" t="n"/>
+      <c r="AN26" s="405" t="n"/>
+      <c r="AO26" s="405" t="n"/>
+      <c r="AP26" s="405" t="n"/>
+      <c r="AQ26" s="405" t="n"/>
+      <c r="AR26" s="405" t="n"/>
+      <c r="AS26" s="405" t="n"/>
+      <c r="AT26" s="405" t="n"/>
+      <c r="AU26" s="405" t="n"/>
+      <c r="AV26" s="405" t="n"/>
+      <c r="AW26" s="405" t="n"/>
+      <c r="AX26" s="405" t="n"/>
+      <c r="AY26" s="405" t="n"/>
+      <c r="AZ26" s="405" t="n"/>
+      <c r="BA26" s="405" t="n"/>
+      <c r="BB26" s="405" t="n"/>
+      <c r="BC26" s="405" t="n"/>
+      <c r="BD26" s="406" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="287" t="inlineStr">
+      <c r="A27" s="353" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="B27" s="271" t="n"/>
-      <c r="C27" s="271" t="n"/>
-      <c r="D27" s="271" t="n"/>
-      <c r="E27" s="271" t="n"/>
-      <c r="F27" s="271" t="n"/>
-      <c r="G27" s="271" t="n"/>
-      <c r="H27" s="271" t="n"/>
-      <c r="I27" s="271" t="n"/>
-      <c r="J27" s="272" t="n"/>
-      <c r="K27" s="288" t="n"/>
-      <c r="L27" s="321" t="n"/>
-      <c r="M27" s="321" t="n"/>
-      <c r="N27" s="321" t="n"/>
-      <c r="O27" s="321" t="n"/>
-      <c r="P27" s="321" t="n"/>
-      <c r="Q27" s="321" t="n"/>
-      <c r="R27" s="321" t="n"/>
-      <c r="S27" s="321" t="n"/>
-      <c r="T27" s="321" t="n"/>
-      <c r="U27" s="321" t="n"/>
-      <c r="V27" s="321" t="n"/>
-      <c r="W27" s="321" t="n"/>
-      <c r="X27" s="321" t="n"/>
-      <c r="Y27" s="321" t="n"/>
-      <c r="Z27" s="321" t="n"/>
-      <c r="AA27" s="321" t="n"/>
-      <c r="AB27" s="322" t="n"/>
-      <c r="AC27" s="289" t="inlineStr">
+      <c r="B27" s="403" t="n"/>
+      <c r="C27" s="403" t="n"/>
+      <c r="D27" s="403" t="n"/>
+      <c r="E27" s="403" t="n"/>
+      <c r="F27" s="403" t="n"/>
+      <c r="G27" s="403" t="n"/>
+      <c r="H27" s="403" t="n"/>
+      <c r="I27" s="403" t="n"/>
+      <c r="J27" s="404" t="n"/>
+      <c r="K27" s="356" t="n"/>
+      <c r="L27" s="405" t="n"/>
+      <c r="M27" s="405" t="n"/>
+      <c r="N27" s="405" t="n"/>
+      <c r="O27" s="405" t="n"/>
+      <c r="P27" s="405" t="n"/>
+      <c r="Q27" s="405" t="n"/>
+      <c r="R27" s="405" t="n"/>
+      <c r="S27" s="405" t="n"/>
+      <c r="T27" s="405" t="n"/>
+      <c r="U27" s="405" t="n"/>
+      <c r="V27" s="405" t="n"/>
+      <c r="W27" s="405" t="n"/>
+      <c r="X27" s="405" t="n"/>
+      <c r="Y27" s="405" t="n"/>
+      <c r="Z27" s="405" t="n"/>
+      <c r="AA27" s="405" t="n"/>
+      <c r="AB27" s="406" t="n"/>
+      <c r="AC27" s="359" t="inlineStr">
         <is>
           <t>Closeout Status</t>
         </is>
       </c>
-      <c r="AD27" s="271" t="n"/>
-      <c r="AE27" s="271" t="n"/>
-      <c r="AF27" s="271" t="n"/>
-      <c r="AG27" s="271" t="n"/>
-      <c r="AH27" s="271" t="n"/>
-      <c r="AI27" s="271" t="n"/>
-      <c r="AJ27" s="271" t="n"/>
-      <c r="AK27" s="271" t="n"/>
-      <c r="AL27" s="272" t="n"/>
-      <c r="AM27" s="290" t="n"/>
-      <c r="AN27" s="321" t="n"/>
-      <c r="AO27" s="321" t="n"/>
-      <c r="AP27" s="321" t="n"/>
-      <c r="AQ27" s="321" t="n"/>
-      <c r="AR27" s="321" t="n"/>
-      <c r="AS27" s="321" t="n"/>
-      <c r="AT27" s="321" t="n"/>
-      <c r="AU27" s="321" t="n"/>
-      <c r="AV27" s="321" t="n"/>
-      <c r="AW27" s="321" t="n"/>
-      <c r="AX27" s="321" t="n"/>
-      <c r="AY27" s="321" t="n"/>
-      <c r="AZ27" s="321" t="n"/>
-      <c r="BA27" s="321" t="n"/>
-      <c r="BB27" s="321" t="n"/>
-      <c r="BC27" s="321" t="n"/>
-      <c r="BD27" s="323" t="n"/>
+      <c r="AD27" s="403" t="n"/>
+      <c r="AE27" s="403" t="n"/>
+      <c r="AF27" s="403" t="n"/>
+      <c r="AG27" s="403" t="n"/>
+      <c r="AH27" s="403" t="n"/>
+      <c r="AI27" s="403" t="n"/>
+      <c r="AJ27" s="403" t="n"/>
+      <c r="AK27" s="403" t="n"/>
+      <c r="AL27" s="404" t="n"/>
+      <c r="AM27" s="356" t="n"/>
+      <c r="AN27" s="405" t="n"/>
+      <c r="AO27" s="405" t="n"/>
+      <c r="AP27" s="405" t="n"/>
+      <c r="AQ27" s="405" t="n"/>
+      <c r="AR27" s="405" t="n"/>
+      <c r="AS27" s="405" t="n"/>
+      <c r="AT27" s="405" t="n"/>
+      <c r="AU27" s="405" t="n"/>
+      <c r="AV27" s="405" t="n"/>
+      <c r="AW27" s="405" t="n"/>
+      <c r="AX27" s="405" t="n"/>
+      <c r="AY27" s="405" t="n"/>
+      <c r="AZ27" s="405" t="n"/>
+      <c r="BA27" s="405" t="n"/>
+      <c r="BB27" s="405" t="n"/>
+      <c r="BC27" s="405" t="n"/>
+      <c r="BD27" s="406" t="n"/>
     </row>
     <row r="28" ht="4" customHeight="1">
-      <c r="A28" s="294" t="n"/>
-      <c r="D28" s="299" t="n"/>
-      <c r="H28" s="304" t="n"/>
-      <c r="AA28" s="301" t="n"/>
-      <c r="AR28" s="302" t="n"/>
-      <c r="AX28" s="302" t="n"/>
-      <c r="BB28" s="303" t="n"/>
+      <c r="A28" s="373" t="n"/>
+      <c r="B28" s="351" t="n"/>
+      <c r="C28" s="351" t="n"/>
+      <c r="D28" s="374" t="n"/>
+      <c r="E28" s="351" t="n"/>
+      <c r="F28" s="351" t="n"/>
+      <c r="G28" s="351" t="n"/>
+      <c r="H28" s="375" t="n"/>
+      <c r="I28" s="351" t="n"/>
+      <c r="J28" s="351" t="n"/>
+      <c r="K28" s="351" t="n"/>
+      <c r="L28" s="351" t="n"/>
+      <c r="M28" s="351" t="n"/>
+      <c r="N28" s="351" t="n"/>
+      <c r="O28" s="351" t="n"/>
+      <c r="P28" s="351" t="n"/>
+      <c r="Q28" s="351" t="n"/>
+      <c r="R28" s="351" t="n"/>
+      <c r="S28" s="351" t="n"/>
+      <c r="T28" s="351" t="n"/>
+      <c r="U28" s="351" t="n"/>
+      <c r="V28" s="351" t="n"/>
+      <c r="W28" s="351" t="n"/>
+      <c r="X28" s="351" t="n"/>
+      <c r="Y28" s="351" t="n"/>
+      <c r="Z28" s="351" t="n"/>
+      <c r="AA28" s="376" t="n"/>
+      <c r="AB28" s="351" t="n"/>
+      <c r="AC28" s="351" t="n"/>
+      <c r="AD28" s="351" t="n"/>
+      <c r="AE28" s="351" t="n"/>
+      <c r="AF28" s="351" t="n"/>
+      <c r="AG28" s="351" t="n"/>
+      <c r="AH28" s="351" t="n"/>
+      <c r="AI28" s="351" t="n"/>
+      <c r="AJ28" s="351" t="n"/>
+      <c r="AK28" s="351" t="n"/>
+      <c r="AL28" s="351" t="n"/>
+      <c r="AM28" s="351" t="n"/>
+      <c r="AN28" s="351" t="n"/>
+      <c r="AO28" s="351" t="n"/>
+      <c r="AP28" s="351" t="n"/>
+      <c r="AQ28" s="351" t="n"/>
+      <c r="AR28" s="377" t="n"/>
+      <c r="AS28" s="351" t="n"/>
+      <c r="AT28" s="351" t="n"/>
+      <c r="AU28" s="351" t="n"/>
+      <c r="AV28" s="351" t="n"/>
+      <c r="AW28" s="351" t="n"/>
+      <c r="AX28" s="377" t="n"/>
+      <c r="AY28" s="351" t="n"/>
+      <c r="AZ28" s="351" t="n"/>
+      <c r="BA28" s="351" t="n"/>
+      <c r="BB28" s="378" t="n"/>
+      <c r="BC28" s="351" t="n"/>
+      <c r="BD28" s="351" t="n"/>
     </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="284" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="352" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="285" t="n"/>
-      <c r="C29" s="285" t="n"/>
-      <c r="D29" s="285" t="n"/>
-      <c r="E29" s="285" t="n"/>
-      <c r="F29" s="285" t="n"/>
-      <c r="G29" s="285" t="n"/>
-      <c r="H29" s="285" t="n"/>
-      <c r="I29" s="285" t="n"/>
-      <c r="J29" s="285" t="n"/>
-      <c r="K29" s="285" t="n"/>
-      <c r="L29" s="285" t="n"/>
-      <c r="M29" s="285" t="n"/>
-      <c r="N29" s="285" t="n"/>
-      <c r="O29" s="285" t="n"/>
-      <c r="P29" s="285" t="n"/>
-      <c r="Q29" s="285" t="n"/>
-      <c r="R29" s="285" t="n"/>
-      <c r="S29" s="285" t="n"/>
-      <c r="T29" s="285" t="n"/>
-      <c r="U29" s="285" t="n"/>
-      <c r="V29" s="285" t="n"/>
-      <c r="W29" s="285" t="n"/>
-      <c r="X29" s="285" t="n"/>
-      <c r="Y29" s="285" t="n"/>
-      <c r="Z29" s="285" t="n"/>
-      <c r="AA29" s="285" t="n"/>
-      <c r="AB29" s="285" t="n"/>
-      <c r="AC29" s="285" t="n"/>
-      <c r="AD29" s="285" t="n"/>
-      <c r="AE29" s="285" t="n"/>
-      <c r="AF29" s="285" t="n"/>
-      <c r="AG29" s="285" t="n"/>
-      <c r="AH29" s="285" t="n"/>
-      <c r="AI29" s="285" t="n"/>
-      <c r="AJ29" s="285" t="n"/>
-      <c r="AK29" s="285" t="n"/>
-      <c r="AL29" s="285" t="n"/>
-      <c r="AM29" s="285" t="n"/>
-      <c r="AN29" s="285" t="n"/>
-      <c r="AO29" s="285" t="n"/>
-      <c r="AP29" s="285" t="n"/>
-      <c r="AQ29" s="285" t="n"/>
-      <c r="AR29" s="285" t="n"/>
-      <c r="AS29" s="285" t="n"/>
-      <c r="AT29" s="285" t="n"/>
-      <c r="AU29" s="285" t="n"/>
-      <c r="AV29" s="285" t="n"/>
-      <c r="AW29" s="285" t="n"/>
-      <c r="AX29" s="285" t="n"/>
-      <c r="AY29" s="285" t="n"/>
-      <c r="AZ29" s="285" t="n"/>
-      <c r="BA29" s="285" t="n"/>
-      <c r="BB29" s="285" t="n"/>
-      <c r="BC29" s="285" t="n"/>
-      <c r="BD29" s="286" t="n"/>
+      <c r="B29" s="403" t="n"/>
+      <c r="C29" s="403" t="n"/>
+      <c r="D29" s="403" t="n"/>
+      <c r="E29" s="403" t="n"/>
+      <c r="F29" s="403" t="n"/>
+      <c r="G29" s="403" t="n"/>
+      <c r="H29" s="403" t="n"/>
+      <c r="I29" s="403" t="n"/>
+      <c r="J29" s="403" t="n"/>
+      <c r="K29" s="403" t="n"/>
+      <c r="L29" s="403" t="n"/>
+      <c r="M29" s="403" t="n"/>
+      <c r="N29" s="403" t="n"/>
+      <c r="O29" s="403" t="n"/>
+      <c r="P29" s="403" t="n"/>
+      <c r="Q29" s="403" t="n"/>
+      <c r="R29" s="403" t="n"/>
+      <c r="S29" s="403" t="n"/>
+      <c r="T29" s="403" t="n"/>
+      <c r="U29" s="403" t="n"/>
+      <c r="V29" s="403" t="n"/>
+      <c r="W29" s="403" t="n"/>
+      <c r="X29" s="403" t="n"/>
+      <c r="Y29" s="403" t="n"/>
+      <c r="Z29" s="403" t="n"/>
+      <c r="AA29" s="403" t="n"/>
+      <c r="AB29" s="403" t="n"/>
+      <c r="AC29" s="403" t="n"/>
+      <c r="AD29" s="403" t="n"/>
+      <c r="AE29" s="403" t="n"/>
+      <c r="AF29" s="403" t="n"/>
+      <c r="AG29" s="403" t="n"/>
+      <c r="AH29" s="403" t="n"/>
+      <c r="AI29" s="403" t="n"/>
+      <c r="AJ29" s="403" t="n"/>
+      <c r="AK29" s="403" t="n"/>
+      <c r="AL29" s="403" t="n"/>
+      <c r="AM29" s="403" t="n"/>
+      <c r="AN29" s="403" t="n"/>
+      <c r="AO29" s="403" t="n"/>
+      <c r="AP29" s="403" t="n"/>
+      <c r="AQ29" s="403" t="n"/>
+      <c r="AR29" s="403" t="n"/>
+      <c r="AS29" s="403" t="n"/>
+      <c r="AT29" s="403" t="n"/>
+      <c r="AU29" s="403" t="n"/>
+      <c r="AV29" s="403" t="n"/>
+      <c r="AW29" s="403" t="n"/>
+      <c r="AX29" s="403" t="n"/>
+      <c r="AY29" s="403" t="n"/>
+      <c r="AZ29" s="403" t="n"/>
+      <c r="BA29" s="403" t="n"/>
+      <c r="BB29" s="403" t="n"/>
+      <c r="BC29" s="403" t="n"/>
+      <c r="BD29" s="404" t="n"/>
     </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="327" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="379" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="285" t="n"/>
-      <c r="C30" s="285" t="n"/>
-      <c r="D30" s="285" t="n"/>
-      <c r="E30" s="285" t="n"/>
-      <c r="F30" s="285" t="n"/>
-      <c r="G30" s="285" t="n"/>
-      <c r="H30" s="285" t="n"/>
-      <c r="I30" s="285" t="n"/>
-      <c r="J30" s="285" t="n"/>
-      <c r="K30" s="285" t="n"/>
-      <c r="L30" s="285" t="n"/>
-      <c r="M30" s="285" t="n"/>
-      <c r="N30" s="285" t="n"/>
-      <c r="O30" s="285" t="n"/>
-      <c r="P30" s="285" t="n"/>
-      <c r="Q30" s="285" t="n"/>
-      <c r="R30" s="328" t="n"/>
-      <c r="S30" s="51" t="inlineStr">
+      <c r="B30" s="398" t="n"/>
+      <c r="C30" s="398" t="n"/>
+      <c r="D30" s="398" t="n"/>
+      <c r="E30" s="398" t="n"/>
+      <c r="F30" s="398" t="n"/>
+      <c r="G30" s="398" t="n"/>
+      <c r="H30" s="398" t="n"/>
+      <c r="I30" s="398" t="n"/>
+      <c r="J30" s="398" t="n"/>
+      <c r="K30" s="398" t="n"/>
+      <c r="L30" s="398" t="n"/>
+      <c r="M30" s="398" t="n"/>
+      <c r="N30" s="398" t="n"/>
+      <c r="O30" s="398" t="n"/>
+      <c r="P30" s="398" t="n"/>
+      <c r="Q30" s="398" t="n"/>
+      <c r="R30" s="399" t="n"/>
+      <c r="S30" s="380" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="285" t="n"/>
-      <c r="U30" s="285" t="n"/>
-      <c r="V30" s="285" t="n"/>
-      <c r="W30" s="285" t="n"/>
-      <c r="X30" s="285" t="n"/>
-      <c r="Y30" s="285" t="n"/>
-      <c r="Z30" s="285" t="n"/>
-      <c r="AA30" s="285" t="n"/>
-      <c r="AB30" s="285" t="n"/>
-      <c r="AC30" s="285" t="n"/>
-      <c r="AD30" s="285" t="n"/>
-      <c r="AE30" s="285" t="n"/>
-      <c r="AF30" s="285" t="n"/>
-      <c r="AG30" s="285" t="n"/>
-      <c r="AH30" s="285" t="n"/>
-      <c r="AI30" s="285" t="n"/>
-      <c r="AJ30" s="285" t="n"/>
-      <c r="AK30" s="305" t="inlineStr">
+      <c r="T30" s="398" t="n"/>
+      <c r="U30" s="398" t="n"/>
+      <c r="V30" s="398" t="n"/>
+      <c r="W30" s="398" t="n"/>
+      <c r="X30" s="398" t="n"/>
+      <c r="Y30" s="398" t="n"/>
+      <c r="Z30" s="398" t="n"/>
+      <c r="AA30" s="398" t="n"/>
+      <c r="AB30" s="398" t="n"/>
+      <c r="AC30" s="398" t="n"/>
+      <c r="AD30" s="398" t="n"/>
+      <c r="AE30" s="398" t="n"/>
+      <c r="AF30" s="398" t="n"/>
+      <c r="AG30" s="398" t="n"/>
+      <c r="AH30" s="398" t="n"/>
+      <c r="AI30" s="398" t="n"/>
+      <c r="AJ30" s="398" t="n"/>
+      <c r="AK30" s="381" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="285" t="n"/>
-      <c r="AM30" s="285" t="n"/>
-      <c r="AN30" s="285" t="n"/>
-      <c r="AO30" s="285" t="n"/>
-      <c r="AP30" s="285" t="n"/>
-      <c r="AQ30" s="285" t="n"/>
-      <c r="AR30" s="285" t="n"/>
-      <c r="AS30" s="285" t="n"/>
-      <c r="AT30" s="285" t="n"/>
-      <c r="AU30" s="285" t="n"/>
-      <c r="AV30" s="285" t="n"/>
-      <c r="AW30" s="285" t="n"/>
-      <c r="AX30" s="285" t="n"/>
-      <c r="AY30" s="285" t="n"/>
-      <c r="AZ30" s="285" t="n"/>
-      <c r="BA30" s="285" t="n"/>
-      <c r="BB30" s="285" t="n"/>
-      <c r="BC30" s="285" t="n"/>
-      <c r="BD30" s="286" t="n"/>
+      <c r="AL30" s="398" t="n"/>
+      <c r="AM30" s="398" t="n"/>
+      <c r="AN30" s="398" t="n"/>
+      <c r="AO30" s="398" t="n"/>
+      <c r="AP30" s="398" t="n"/>
+      <c r="AQ30" s="398" t="n"/>
+      <c r="AR30" s="398" t="n"/>
+      <c r="AS30" s="398" t="n"/>
+      <c r="AT30" s="398" t="n"/>
+      <c r="AU30" s="398" t="n"/>
+      <c r="AV30" s="398" t="n"/>
+      <c r="AW30" s="398" t="n"/>
+      <c r="AX30" s="398" t="n"/>
+      <c r="AY30" s="398" t="n"/>
+      <c r="AZ30" s="398" t="n"/>
+      <c r="BA30" s="398" t="n"/>
+      <c r="BB30" s="398" t="n"/>
+      <c r="BC30" s="398" t="n"/>
+      <c r="BD30" s="399" t="n"/>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="306" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="382" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="329" t="n"/>
-      <c r="C31" s="329" t="n"/>
-      <c r="D31" s="329" t="n"/>
-      <c r="E31" s="329" t="n"/>
-      <c r="F31" s="329" t="n"/>
-      <c r="G31" s="329" t="n"/>
-      <c r="H31" s="329" t="n"/>
-      <c r="I31" s="329" t="n"/>
-      <c r="J31" s="329" t="n"/>
-      <c r="K31" s="329" t="n"/>
-      <c r="L31" s="329" t="n"/>
-      <c r="M31" s="329" t="n"/>
-      <c r="N31" s="329" t="n"/>
-      <c r="O31" s="329" t="n"/>
-      <c r="P31" s="329" t="n"/>
-      <c r="Q31" s="329" t="n"/>
-      <c r="R31" s="330" t="n"/>
-      <c r="S31" s="306" t="inlineStr">
+      <c r="B31" s="413" t="n"/>
+      <c r="C31" s="413" t="n"/>
+      <c r="D31" s="413" t="n"/>
+      <c r="E31" s="413" t="n"/>
+      <c r="F31" s="413" t="n"/>
+      <c r="G31" s="413" t="n"/>
+      <c r="H31" s="413" t="n"/>
+      <c r="I31" s="413" t="n"/>
+      <c r="J31" s="413" t="n"/>
+      <c r="K31" s="413" t="n"/>
+      <c r="L31" s="413" t="n"/>
+      <c r="M31" s="413" t="n"/>
+      <c r="N31" s="413" t="n"/>
+      <c r="O31" s="413" t="n"/>
+      <c r="P31" s="413" t="n"/>
+      <c r="Q31" s="413" t="n"/>
+      <c r="R31" s="414" t="n"/>
+      <c r="S31" s="382" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="329" t="n"/>
-      <c r="U31" s="329" t="n"/>
-      <c r="V31" s="329" t="n"/>
-      <c r="W31" s="329" t="n"/>
-      <c r="X31" s="329" t="n"/>
-      <c r="Y31" s="329" t="n"/>
-      <c r="Z31" s="329" t="n"/>
-      <c r="AA31" s="329" t="n"/>
-      <c r="AB31" s="329" t="n"/>
-      <c r="AC31" s="329" t="n"/>
-      <c r="AD31" s="329" t="n"/>
-      <c r="AE31" s="329" t="n"/>
-      <c r="AF31" s="329" t="n"/>
-      <c r="AG31" s="329" t="n"/>
-      <c r="AH31" s="329" t="n"/>
-      <c r="AI31" s="329" t="n"/>
-      <c r="AJ31" s="330" t="n"/>
-      <c r="AK31" s="306" t="inlineStr">
+      <c r="T31" s="413" t="n"/>
+      <c r="U31" s="413" t="n"/>
+      <c r="V31" s="413" t="n"/>
+      <c r="W31" s="413" t="n"/>
+      <c r="X31" s="413" t="n"/>
+      <c r="Y31" s="413" t="n"/>
+      <c r="Z31" s="413" t="n"/>
+      <c r="AA31" s="413" t="n"/>
+      <c r="AB31" s="413" t="n"/>
+      <c r="AC31" s="413" t="n"/>
+      <c r="AD31" s="413" t="n"/>
+      <c r="AE31" s="413" t="n"/>
+      <c r="AF31" s="413" t="n"/>
+      <c r="AG31" s="413" t="n"/>
+      <c r="AH31" s="413" t="n"/>
+      <c r="AI31" s="413" t="n"/>
+      <c r="AJ31" s="414" t="n"/>
+      <c r="AK31" s="382" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="329" t="n"/>
-      <c r="AM31" s="329" t="n"/>
-      <c r="AN31" s="329" t="n"/>
-      <c r="AO31" s="329" t="n"/>
-      <c r="AP31" s="329" t="n"/>
-      <c r="AQ31" s="329" t="n"/>
-      <c r="AR31" s="329" t="n"/>
-      <c r="AS31" s="329" t="n"/>
-      <c r="AT31" s="329" t="n"/>
-      <c r="AU31" s="329" t="n"/>
-      <c r="AV31" s="329" t="n"/>
-      <c r="AW31" s="329" t="n"/>
-      <c r="AX31" s="329" t="n"/>
-      <c r="AY31" s="329" t="n"/>
-      <c r="AZ31" s="329" t="n"/>
-      <c r="BA31" s="329" t="n"/>
-      <c r="BB31" s="329" t="n"/>
-      <c r="BC31" s="329" t="n"/>
-      <c r="BD31" s="330" t="n"/>
+      <c r="AL31" s="413" t="n"/>
+      <c r="AM31" s="413" t="n"/>
+      <c r="AN31" s="413" t="n"/>
+      <c r="AO31" s="413" t="n"/>
+      <c r="AP31" s="413" t="n"/>
+      <c r="AQ31" s="413" t="n"/>
+      <c r="AR31" s="413" t="n"/>
+      <c r="AS31" s="413" t="n"/>
+      <c r="AT31" s="413" t="n"/>
+      <c r="AU31" s="413" t="n"/>
+      <c r="AV31" s="413" t="n"/>
+      <c r="AW31" s="413" t="n"/>
+      <c r="AX31" s="413" t="n"/>
+      <c r="AY31" s="413" t="n"/>
+      <c r="AZ31" s="413" t="n"/>
+      <c r="BA31" s="413" t="n"/>
+      <c r="BB31" s="413" t="n"/>
+      <c r="BC31" s="413" t="n"/>
+      <c r="BD31" s="414" t="n"/>
     </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="331" t="n"/>
-      <c r="B32" s="332" t="n"/>
-      <c r="C32" s="332" t="n"/>
-      <c r="D32" s="332" t="n"/>
-      <c r="E32" s="332" t="n"/>
-      <c r="F32" s="332" t="n"/>
-      <c r="G32" s="332" t="n"/>
-      <c r="H32" s="332" t="n"/>
-      <c r="I32" s="332" t="n"/>
-      <c r="J32" s="332" t="n"/>
-      <c r="K32" s="332" t="n"/>
-      <c r="L32" s="332" t="n"/>
-      <c r="M32" s="332" t="n"/>
-      <c r="N32" s="332" t="n"/>
-      <c r="O32" s="332" t="n"/>
-      <c r="P32" s="332" t="n"/>
-      <c r="Q32" s="332" t="n"/>
-      <c r="R32" s="333" t="n"/>
-      <c r="S32" s="331" t="n"/>
-      <c r="T32" s="332" t="n"/>
-      <c r="U32" s="332" t="n"/>
-      <c r="V32" s="332" t="n"/>
-      <c r="W32" s="332" t="n"/>
-      <c r="X32" s="332" t="n"/>
-      <c r="Y32" s="332" t="n"/>
-      <c r="Z32" s="332" t="n"/>
-      <c r="AA32" s="332" t="n"/>
-      <c r="AB32" s="332" t="n"/>
-      <c r="AC32" s="332" t="n"/>
-      <c r="AD32" s="332" t="n"/>
-      <c r="AE32" s="332" t="n"/>
-      <c r="AF32" s="332" t="n"/>
-      <c r="AG32" s="332" t="n"/>
-      <c r="AH32" s="332" t="n"/>
-      <c r="AI32" s="332" t="n"/>
-      <c r="AJ32" s="333" t="n"/>
-      <c r="AK32" s="331" t="n"/>
-      <c r="AL32" s="332" t="n"/>
-      <c r="AM32" s="332" t="n"/>
-      <c r="AN32" s="332" t="n"/>
-      <c r="AO32" s="332" t="n"/>
-      <c r="AP32" s="332" t="n"/>
-      <c r="AQ32" s="332" t="n"/>
-      <c r="AR32" s="332" t="n"/>
-      <c r="AS32" s="332" t="n"/>
-      <c r="AT32" s="332" t="n"/>
-      <c r="AU32" s="332" t="n"/>
-      <c r="AV32" s="332" t="n"/>
-      <c r="AW32" s="332" t="n"/>
-      <c r="AX32" s="332" t="n"/>
-      <c r="AY32" s="332" t="n"/>
-      <c r="AZ32" s="332" t="n"/>
-      <c r="BA32" s="332" t="n"/>
-      <c r="BB32" s="332" t="n"/>
-      <c r="BC32" s="332" t="n"/>
-      <c r="BD32" s="333" t="n"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="415" t="n"/>
+      <c r="B32" s="386" t="n"/>
+      <c r="C32" s="386" t="n"/>
+      <c r="D32" s="386" t="n"/>
+      <c r="E32" s="386" t="n"/>
+      <c r="F32" s="386" t="n"/>
+      <c r="G32" s="386" t="n"/>
+      <c r="H32" s="386" t="n"/>
+      <c r="I32" s="386" t="n"/>
+      <c r="J32" s="386" t="n"/>
+      <c r="K32" s="386" t="n"/>
+      <c r="L32" s="386" t="n"/>
+      <c r="M32" s="386" t="n"/>
+      <c r="N32" s="386" t="n"/>
+      <c r="O32" s="386" t="n"/>
+      <c r="P32" s="386" t="n"/>
+      <c r="Q32" s="386" t="n"/>
+      <c r="R32" s="416" t="n"/>
+      <c r="S32" s="415" t="n"/>
+      <c r="T32" s="386" t="n"/>
+      <c r="U32" s="386" t="n"/>
+      <c r="V32" s="386" t="n"/>
+      <c r="W32" s="386" t="n"/>
+      <c r="X32" s="386" t="n"/>
+      <c r="Y32" s="386" t="n"/>
+      <c r="Z32" s="386" t="n"/>
+      <c r="AA32" s="386" t="n"/>
+      <c r="AB32" s="386" t="n"/>
+      <c r="AC32" s="386" t="n"/>
+      <c r="AD32" s="386" t="n"/>
+      <c r="AE32" s="386" t="n"/>
+      <c r="AF32" s="386" t="n"/>
+      <c r="AG32" s="386" t="n"/>
+      <c r="AH32" s="386" t="n"/>
+      <c r="AI32" s="386" t="n"/>
+      <c r="AJ32" s="416" t="n"/>
+      <c r="AK32" s="415" t="n"/>
+      <c r="AL32" s="386" t="n"/>
+      <c r="AM32" s="386" t="n"/>
+      <c r="AN32" s="386" t="n"/>
+      <c r="AO32" s="386" t="n"/>
+      <c r="AP32" s="386" t="n"/>
+      <c r="AQ32" s="386" t="n"/>
+      <c r="AR32" s="386" t="n"/>
+      <c r="AS32" s="386" t="n"/>
+      <c r="AT32" s="386" t="n"/>
+      <c r="AU32" s="386" t="n"/>
+      <c r="AV32" s="386" t="n"/>
+      <c r="AW32" s="386" t="n"/>
+      <c r="AX32" s="386" t="n"/>
+      <c r="AY32" s="386" t="n"/>
+      <c r="AZ32" s="386" t="n"/>
+      <c r="BA32" s="386" t="n"/>
+      <c r="BB32" s="386" t="n"/>
+      <c r="BC32" s="386" t="n"/>
+      <c r="BD32" s="416" t="n"/>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="334" t="n"/>
-      <c r="B33" s="335" t="n"/>
-      <c r="C33" s="335" t="n"/>
-      <c r="D33" s="335" t="n"/>
-      <c r="E33" s="335" t="n"/>
-      <c r="F33" s="335" t="n"/>
-      <c r="G33" s="335" t="n"/>
-      <c r="H33" s="335" t="n"/>
-      <c r="I33" s="335" t="n"/>
-      <c r="J33" s="335" t="n"/>
-      <c r="K33" s="335" t="n"/>
-      <c r="L33" s="335" t="n"/>
-      <c r="M33" s="335" t="n"/>
-      <c r="N33" s="335" t="n"/>
-      <c r="O33" s="335" t="n"/>
-      <c r="P33" s="335" t="n"/>
-      <c r="Q33" s="335" t="n"/>
-      <c r="R33" s="336" t="n"/>
-      <c r="S33" s="334" t="n"/>
-      <c r="T33" s="335" t="n"/>
-      <c r="U33" s="335" t="n"/>
-      <c r="V33" s="335" t="n"/>
-      <c r="W33" s="335" t="n"/>
-      <c r="X33" s="335" t="n"/>
-      <c r="Y33" s="335" t="n"/>
-      <c r="Z33" s="335" t="n"/>
-      <c r="AA33" s="335" t="n"/>
-      <c r="AB33" s="335" t="n"/>
-      <c r="AC33" s="335" t="n"/>
-      <c r="AD33" s="335" t="n"/>
-      <c r="AE33" s="335" t="n"/>
-      <c r="AF33" s="335" t="n"/>
-      <c r="AG33" s="335" t="n"/>
-      <c r="AH33" s="335" t="n"/>
-      <c r="AI33" s="335" t="n"/>
-      <c r="AJ33" s="336" t="n"/>
-      <c r="AK33" s="334" t="n"/>
-      <c r="AL33" s="335" t="n"/>
-      <c r="AM33" s="335" t="n"/>
-      <c r="AN33" s="335" t="n"/>
-      <c r="AO33" s="335" t="n"/>
-      <c r="AP33" s="335" t="n"/>
-      <c r="AQ33" s="335" t="n"/>
-      <c r="AR33" s="335" t="n"/>
-      <c r="AS33" s="335" t="n"/>
-      <c r="AT33" s="335" t="n"/>
-      <c r="AU33" s="335" t="n"/>
-      <c r="AV33" s="335" t="n"/>
-      <c r="AW33" s="335" t="n"/>
-      <c r="AX33" s="335" t="n"/>
-      <c r="AY33" s="335" t="n"/>
-      <c r="AZ33" s="335" t="n"/>
-      <c r="BA33" s="335" t="n"/>
-      <c r="BB33" s="335" t="n"/>
-      <c r="BC33" s="335" t="n"/>
-      <c r="BD33" s="336" t="n"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="417" t="n"/>
+      <c r="B33" s="411" t="n"/>
+      <c r="C33" s="411" t="n"/>
+      <c r="D33" s="411" t="n"/>
+      <c r="E33" s="411" t="n"/>
+      <c r="F33" s="411" t="n"/>
+      <c r="G33" s="411" t="n"/>
+      <c r="H33" s="411" t="n"/>
+      <c r="I33" s="411" t="n"/>
+      <c r="J33" s="411" t="n"/>
+      <c r="K33" s="411" t="n"/>
+      <c r="L33" s="411" t="n"/>
+      <c r="M33" s="411" t="n"/>
+      <c r="N33" s="411" t="n"/>
+      <c r="O33" s="411" t="n"/>
+      <c r="P33" s="411" t="n"/>
+      <c r="Q33" s="411" t="n"/>
+      <c r="R33" s="412" t="n"/>
+      <c r="S33" s="417" t="n"/>
+      <c r="T33" s="411" t="n"/>
+      <c r="U33" s="411" t="n"/>
+      <c r="V33" s="411" t="n"/>
+      <c r="W33" s="411" t="n"/>
+      <c r="X33" s="411" t="n"/>
+      <c r="Y33" s="411" t="n"/>
+      <c r="Z33" s="411" t="n"/>
+      <c r="AA33" s="411" t="n"/>
+      <c r="AB33" s="411" t="n"/>
+      <c r="AC33" s="411" t="n"/>
+      <c r="AD33" s="411" t="n"/>
+      <c r="AE33" s="411" t="n"/>
+      <c r="AF33" s="411" t="n"/>
+      <c r="AG33" s="411" t="n"/>
+      <c r="AH33" s="411" t="n"/>
+      <c r="AI33" s="411" t="n"/>
+      <c r="AJ33" s="412" t="n"/>
+      <c r="AK33" s="417" t="n"/>
+      <c r="AL33" s="411" t="n"/>
+      <c r="AM33" s="411" t="n"/>
+      <c r="AN33" s="411" t="n"/>
+      <c r="AO33" s="411" t="n"/>
+      <c r="AP33" s="411" t="n"/>
+      <c r="AQ33" s="411" t="n"/>
+      <c r="AR33" s="411" t="n"/>
+      <c r="AS33" s="411" t="n"/>
+      <c r="AT33" s="411" t="n"/>
+      <c r="AU33" s="411" t="n"/>
+      <c r="AV33" s="411" t="n"/>
+      <c r="AW33" s="411" t="n"/>
+      <c r="AX33" s="411" t="n"/>
+      <c r="AY33" s="411" t="n"/>
+      <c r="AZ33" s="411" t="n"/>
+      <c r="BA33" s="411" t="n"/>
+      <c r="BB33" s="411" t="n"/>
+      <c r="BC33" s="411" t="n"/>
+      <c r="BD33" s="412" t="n"/>
     </row>
     <row r="34" ht="4" customHeight="1">
-      <c r="A34" s="291" t="n"/>
-      <c r="D34" s="292" t="n"/>
-      <c r="R34" s="292" t="n"/>
-      <c r="AI34" s="292" t="n"/>
-      <c r="AP34" s="292" t="n"/>
-      <c r="AW34" s="292" t="n"/>
-      <c r="BA34" s="293" t="n"/>
+      <c r="A34" s="389" t="n"/>
+      <c r="B34" s="351" t="n"/>
+      <c r="C34" s="351" t="n"/>
+      <c r="D34" s="389" t="n"/>
+      <c r="E34" s="351" t="n"/>
+      <c r="F34" s="351" t="n"/>
+      <c r="G34" s="351" t="n"/>
+      <c r="H34" s="351" t="n"/>
+      <c r="I34" s="351" t="n"/>
+      <c r="J34" s="351" t="n"/>
+      <c r="K34" s="351" t="n"/>
+      <c r="L34" s="351" t="n"/>
+      <c r="M34" s="351" t="n"/>
+      <c r="N34" s="351" t="n"/>
+      <c r="O34" s="351" t="n"/>
+      <c r="P34" s="351" t="n"/>
+      <c r="Q34" s="351" t="n"/>
+      <c r="R34" s="389" t="n"/>
+      <c r="S34" s="351" t="n"/>
+      <c r="T34" s="351" t="n"/>
+      <c r="U34" s="351" t="n"/>
+      <c r="V34" s="351" t="n"/>
+      <c r="W34" s="351" t="n"/>
+      <c r="X34" s="351" t="n"/>
+      <c r="Y34" s="351" t="n"/>
+      <c r="Z34" s="351" t="n"/>
+      <c r="AA34" s="351" t="n"/>
+      <c r="AB34" s="351" t="n"/>
+      <c r="AC34" s="351" t="n"/>
+      <c r="AD34" s="351" t="n"/>
+      <c r="AE34" s="351" t="n"/>
+      <c r="AF34" s="351" t="n"/>
+      <c r="AG34" s="351" t="n"/>
+      <c r="AH34" s="351" t="n"/>
+      <c r="AI34" s="389" t="n"/>
+      <c r="AJ34" s="351" t="n"/>
+      <c r="AK34" s="351" t="n"/>
+      <c r="AL34" s="351" t="n"/>
+      <c r="AM34" s="351" t="n"/>
+      <c r="AN34" s="351" t="n"/>
+      <c r="AO34" s="351" t="n"/>
+      <c r="AP34" s="389" t="n"/>
+      <c r="AQ34" s="351" t="n"/>
+      <c r="AR34" s="351" t="n"/>
+      <c r="AS34" s="351" t="n"/>
+      <c r="AT34" s="351" t="n"/>
+      <c r="AU34" s="351" t="n"/>
+      <c r="AV34" s="351" t="n"/>
+      <c r="AW34" s="389" t="n"/>
+      <c r="AX34" s="351" t="n"/>
+      <c r="AY34" s="351" t="n"/>
+      <c r="AZ34" s="351" t="n"/>
+      <c r="BA34" s="389" t="n"/>
+      <c r="BB34" s="351" t="n"/>
+      <c r="BC34" s="351" t="n"/>
+      <c r="BD34" s="351" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="337" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="390" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B35" s="276" t="n"/>
-      <c r="C35" s="276" t="n"/>
-      <c r="D35" s="276" t="n"/>
-      <c r="E35" s="276" t="n"/>
-      <c r="F35" s="276" t="n"/>
-      <c r="G35" s="276" t="n"/>
-      <c r="H35" s="276" t="n"/>
-      <c r="I35" s="276" t="n"/>
-      <c r="J35" s="276" t="n"/>
-      <c r="K35" s="276" t="n"/>
-      <c r="L35" s="276" t="n"/>
-      <c r="M35" s="276" t="n"/>
-      <c r="N35" s="276" t="n"/>
-      <c r="O35" s="276" t="n"/>
-      <c r="P35" s="276" t="n"/>
-      <c r="Q35" s="276" t="n"/>
-      <c r="R35" s="276" t="n"/>
-      <c r="S35" s="276" t="n"/>
-      <c r="T35" s="276" t="n"/>
-      <c r="U35" s="276" t="n"/>
-      <c r="V35" s="276" t="n"/>
-      <c r="W35" s="276" t="n"/>
-      <c r="X35" s="276" t="n"/>
-      <c r="Y35" s="276" t="n"/>
-      <c r="Z35" s="276" t="n"/>
-      <c r="AA35" s="276" t="n"/>
-      <c r="AB35" s="276" t="n"/>
-      <c r="AC35" s="276" t="n"/>
-      <c r="AD35" s="276" t="n"/>
-      <c r="AE35" s="276" t="n"/>
-      <c r="AF35" s="276" t="n"/>
-      <c r="AG35" s="276" t="n"/>
-      <c r="AH35" s="276" t="n"/>
-      <c r="AI35" s="276" t="n"/>
-      <c r="AJ35" s="276" t="n"/>
-      <c r="AK35" s="276" t="n"/>
-      <c r="AL35" s="276" t="n"/>
-      <c r="AM35" s="276" t="n"/>
-      <c r="AN35" s="276" t="n"/>
-      <c r="AO35" s="276" t="n"/>
-      <c r="AP35" s="276" t="n"/>
-      <c r="AQ35" s="276" t="n"/>
-      <c r="AR35" s="276" t="n"/>
-      <c r="AS35" s="276" t="n"/>
-      <c r="AT35" s="276" t="n"/>
-      <c r="AU35" s="276" t="n"/>
-      <c r="AV35" s="276" t="n"/>
-      <c r="AW35" s="276" t="n"/>
-      <c r="AX35" s="276" t="n"/>
-      <c r="AY35" s="276" t="n"/>
-      <c r="AZ35" s="276" t="n"/>
-      <c r="BA35" s="276" t="n"/>
-      <c r="BB35" s="276" t="n"/>
-      <c r="BC35" s="276" t="n"/>
-      <c r="BD35" s="277" t="n"/>
+      <c r="B35" s="409" t="n"/>
+      <c r="C35" s="409" t="n"/>
+      <c r="D35" s="409" t="n"/>
+      <c r="E35" s="409" t="n"/>
+      <c r="F35" s="409" t="n"/>
+      <c r="G35" s="409" t="n"/>
+      <c r="H35" s="409" t="n"/>
+      <c r="I35" s="409" t="n"/>
+      <c r="J35" s="409" t="n"/>
+      <c r="K35" s="409" t="n"/>
+      <c r="L35" s="409" t="n"/>
+      <c r="M35" s="409" t="n"/>
+      <c r="N35" s="409" t="n"/>
+      <c r="O35" s="409" t="n"/>
+      <c r="P35" s="409" t="n"/>
+      <c r="Q35" s="409" t="n"/>
+      <c r="R35" s="409" t="n"/>
+      <c r="S35" s="409" t="n"/>
+      <c r="T35" s="409" t="n"/>
+      <c r="U35" s="409" t="n"/>
+      <c r="V35" s="409" t="n"/>
+      <c r="W35" s="409" t="n"/>
+      <c r="X35" s="409" t="n"/>
+      <c r="Y35" s="409" t="n"/>
+      <c r="Z35" s="409" t="n"/>
+      <c r="AA35" s="409" t="n"/>
+      <c r="AB35" s="409" t="n"/>
+      <c r="AC35" s="409" t="n"/>
+      <c r="AD35" s="409" t="n"/>
+      <c r="AE35" s="409" t="n"/>
+      <c r="AF35" s="409" t="n"/>
+      <c r="AG35" s="409" t="n"/>
+      <c r="AH35" s="409" t="n"/>
+      <c r="AI35" s="409" t="n"/>
+      <c r="AJ35" s="409" t="n"/>
+      <c r="AK35" s="409" t="n"/>
+      <c r="AL35" s="409" t="n"/>
+      <c r="AM35" s="409" t="n"/>
+      <c r="AN35" s="409" t="n"/>
+      <c r="AO35" s="409" t="n"/>
+      <c r="AP35" s="409" t="n"/>
+      <c r="AQ35" s="409" t="n"/>
+      <c r="AR35" s="409" t="n"/>
+      <c r="AS35" s="409" t="n"/>
+      <c r="AT35" s="409" t="n"/>
+      <c r="AU35" s="409" t="n"/>
+      <c r="AV35" s="409" t="n"/>
+      <c r="AW35" s="409" t="n"/>
+      <c r="AX35" s="409" t="n"/>
+      <c r="AY35" s="409" t="n"/>
+      <c r="AZ35" s="409" t="n"/>
+      <c r="BA35" s="409" t="n"/>
+      <c r="BB35" s="409" t="n"/>
+      <c r="BC35" s="409" t="n"/>
+      <c r="BD35" s="410" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -6956,7 +7646,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7191,30 +7880,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="316" t="inlineStr">
+      <c r="A1" s="391" t="inlineStr">
         <is>
           <t>Result Detail</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="420" t="n"/>
+      <c r="C1" s="420" t="n"/>
+      <c r="D1" s="420" t="n"/>
+      <c r="E1" s="420" t="n"/>
+      <c r="F1" s="420" t="n"/>
+      <c r="G1" s="421" t="n"/>
+      <c r="H1" s="346" t="n"/>
+      <c r="I1" s="346" t="n"/>
+      <c r="J1" s="346" t="n"/>
+      <c r="K1" s="346" t="n"/>
+      <c r="L1" s="346" t="n"/>
+      <c r="M1" s="346" t="n"/>
+      <c r="N1" s="346" t="n"/>
+      <c r="O1" s="346" t="n"/>
+      <c r="P1" s="346" t="n"/>
+      <c r="Q1" s="346" t="n"/>
+      <c r="R1" s="346" t="n"/>
+      <c r="S1" s="346" t="n"/>
+      <c r="T1" s="346" t="n"/>
+      <c r="U1" s="346" t="n"/>
+      <c r="V1" s="346" t="n"/>
+      <c r="W1" s="346" t="n"/>
+      <c r="X1" s="346" t="n"/>
+      <c r="Y1" s="346" t="n"/>
+      <c r="Z1" s="346" t="n"/>
+      <c r="AA1" s="346" t="n"/>
+      <c r="AB1" s="346" t="n"/>
+      <c r="AC1" s="346" t="n"/>
+      <c r="AD1" s="346" t="n"/>
+      <c r="AE1" s="346" t="n"/>
+      <c r="AF1" s="346" t="n"/>
+      <c r="AG1" s="346" t="n"/>
+      <c r="AH1" s="346" t="n"/>
+      <c r="AI1" s="346" t="n"/>
+      <c r="AJ1" s="346" t="n"/>
+      <c r="AK1" s="346" t="n"/>
+      <c r="AL1" s="346" t="n"/>
+      <c r="AM1" s="346" t="n"/>
+      <c r="AN1" s="346" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="317" t="inlineStr">
@@ -7222,224 +7977,826 @@
           <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
         </is>
       </c>
+      <c r="H2" s="346" t="n"/>
+      <c r="I2" s="346" t="n"/>
+      <c r="J2" s="346" t="n"/>
+      <c r="K2" s="346" t="n"/>
+      <c r="L2" s="346" t="n"/>
+      <c r="M2" s="346" t="n"/>
+      <c r="N2" s="346" t="n"/>
+      <c r="O2" s="346" t="n"/>
+      <c r="P2" s="346" t="n"/>
+      <c r="Q2" s="346" t="n"/>
+      <c r="R2" s="346" t="n"/>
+      <c r="S2" s="346" t="n"/>
+      <c r="T2" s="346" t="n"/>
+      <c r="U2" s="346" t="n"/>
+      <c r="V2" s="346" t="n"/>
+      <c r="W2" s="346" t="n"/>
+      <c r="X2" s="346" t="n"/>
+      <c r="Y2" s="346" t="n"/>
+      <c r="Z2" s="346" t="n"/>
+      <c r="AA2" s="346" t="n"/>
+      <c r="AB2" s="346" t="n"/>
+      <c r="AC2" s="346" t="n"/>
+      <c r="AD2" s="346" t="n"/>
+      <c r="AE2" s="346" t="n"/>
+      <c r="AF2" s="346" t="n"/>
+      <c r="AG2" s="346" t="n"/>
+      <c r="AH2" s="346" t="n"/>
+      <c r="AI2" s="346" t="n"/>
+      <c r="AJ2" s="346" t="n"/>
+      <c r="AK2" s="346" t="n"/>
+      <c r="AL2" s="346" t="n"/>
+      <c r="AM2" s="346" t="n"/>
+      <c r="AN2" s="346" t="n"/>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="346" t="n"/>
+      <c r="B3" s="346" t="n"/>
+      <c r="C3" s="346" t="n"/>
+      <c r="D3" s="346" t="n"/>
+      <c r="E3" s="346" t="n"/>
+      <c r="F3" s="346" t="n"/>
+      <c r="G3" s="346" t="n"/>
+      <c r="H3" s="346" t="n"/>
+      <c r="I3" s="346" t="n"/>
+      <c r="J3" s="346" t="n"/>
+      <c r="K3" s="346" t="n"/>
+      <c r="L3" s="346" t="n"/>
+      <c r="M3" s="346" t="n"/>
+      <c r="N3" s="346" t="n"/>
+      <c r="O3" s="346" t="n"/>
+      <c r="P3" s="346" t="n"/>
+      <c r="Q3" s="346" t="n"/>
+      <c r="R3" s="346" t="n"/>
+      <c r="S3" s="346" t="n"/>
+      <c r="T3" s="346" t="n"/>
+      <c r="U3" s="346" t="n"/>
+      <c r="V3" s="346" t="n"/>
+      <c r="W3" s="346" t="n"/>
+      <c r="X3" s="346" t="n"/>
+      <c r="Y3" s="346" t="n"/>
+      <c r="Z3" s="346" t="n"/>
+      <c r="AA3" s="346" t="n"/>
+      <c r="AB3" s="346" t="n"/>
+      <c r="AC3" s="346" t="n"/>
+      <c r="AD3" s="346" t="n"/>
+      <c r="AE3" s="346" t="n"/>
+      <c r="AF3" s="346" t="n"/>
+      <c r="AG3" s="346" t="n"/>
+      <c r="AH3" s="346" t="n"/>
+      <c r="AI3" s="346" t="n"/>
+      <c r="AJ3" s="346" t="n"/>
+      <c r="AK3" s="346" t="n"/>
+      <c r="AL3" s="346" t="n"/>
+      <c r="AM3" s="346" t="n"/>
+      <c r="AN3" s="346" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="318" t="inlineStr">
+      <c r="A4" s="362" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="318" t="inlineStr">
+      <c r="B4" s="362" t="inlineStr">
         <is>
           <t>Requirement / Characteristic</t>
         </is>
       </c>
-      <c r="C4" s="318" t="inlineStr">
+      <c r="C4" s="362" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="318" t="inlineStr">
+      <c r="D4" s="362" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E4" s="318" t="inlineStr">
+      <c r="E4" s="362" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="F4" s="318" t="inlineStr">
+      <c r="F4" s="362" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="G4" s="318" t="inlineStr">
+      <c r="G4" s="362" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
+      <c r="H4" s="346" t="n"/>
+      <c r="I4" s="346" t="n"/>
+      <c r="J4" s="346" t="n"/>
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="346" t="n"/>
+      <c r="M4" s="346" t="n"/>
+      <c r="N4" s="346" t="n"/>
+      <c r="O4" s="346" t="n"/>
+      <c r="P4" s="346" t="n"/>
+      <c r="Q4" s="346" t="n"/>
+      <c r="R4" s="346" t="n"/>
+      <c r="S4" s="346" t="n"/>
+      <c r="T4" s="346" t="n"/>
+      <c r="U4" s="346" t="n"/>
+      <c r="V4" s="346" t="n"/>
+      <c r="W4" s="346" t="n"/>
+      <c r="X4" s="346" t="n"/>
+      <c r="Y4" s="346" t="n"/>
+      <c r="Z4" s="346" t="n"/>
+      <c r="AA4" s="346" t="n"/>
+      <c r="AB4" s="346" t="n"/>
+      <c r="AC4" s="346" t="n"/>
+      <c r="AD4" s="346" t="n"/>
+      <c r="AE4" s="346" t="n"/>
+      <c r="AF4" s="346" t="n"/>
+      <c r="AG4" s="346" t="n"/>
+      <c r="AH4" s="346" t="n"/>
+      <c r="AI4" s="346" t="n"/>
+      <c r="AJ4" s="346" t="n"/>
+      <c r="AK4" s="346" t="n"/>
+      <c r="AL4" s="346" t="n"/>
+      <c r="AM4" s="346" t="n"/>
+      <c r="AN4" s="346" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="319">
+      <c r="A5" s="392">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="320" t="n"/>
-      <c r="C5" s="320" t="n"/>
-      <c r="D5" s="320" t="n"/>
-      <c r="E5" s="320" t="n"/>
-      <c r="F5" s="320" t="n"/>
-      <c r="G5" s="320" t="n"/>
+      <c r="B5" s="393" t="n"/>
+      <c r="C5" s="393" t="n"/>
+      <c r="D5" s="393" t="n"/>
+      <c r="E5" s="393" t="n"/>
+      <c r="F5" s="393" t="n"/>
+      <c r="G5" s="393" t="n"/>
+      <c r="H5" s="346" t="n"/>
+      <c r="I5" s="346" t="n"/>
+      <c r="J5" s="346" t="n"/>
+      <c r="K5" s="346" t="n"/>
+      <c r="L5" s="346" t="n"/>
+      <c r="M5" s="346" t="n"/>
+      <c r="N5" s="346" t="n"/>
+      <c r="O5" s="346" t="n"/>
+      <c r="P5" s="346" t="n"/>
+      <c r="Q5" s="346" t="n"/>
+      <c r="R5" s="346" t="n"/>
+      <c r="S5" s="346" t="n"/>
+      <c r="T5" s="346" t="n"/>
+      <c r="U5" s="346" t="n"/>
+      <c r="V5" s="346" t="n"/>
+      <c r="W5" s="346" t="n"/>
+      <c r="X5" s="346" t="n"/>
+      <c r="Y5" s="346" t="n"/>
+      <c r="Z5" s="346" t="n"/>
+      <c r="AA5" s="346" t="n"/>
+      <c r="AB5" s="346" t="n"/>
+      <c r="AC5" s="346" t="n"/>
+      <c r="AD5" s="346" t="n"/>
+      <c r="AE5" s="346" t="n"/>
+      <c r="AF5" s="346" t="n"/>
+      <c r="AG5" s="346" t="n"/>
+      <c r="AH5" s="346" t="n"/>
+      <c r="AI5" s="346" t="n"/>
+      <c r="AJ5" s="346" t="n"/>
+      <c r="AK5" s="346" t="n"/>
+      <c r="AL5" s="346" t="n"/>
+      <c r="AM5" s="346" t="n"/>
+      <c r="AN5" s="346" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="319">
+      <c r="A6" s="392">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="320" t="n"/>
-      <c r="C6" s="320" t="n"/>
-      <c r="D6" s="320" t="n"/>
-      <c r="E6" s="320" t="n"/>
-      <c r="F6" s="320" t="n"/>
-      <c r="G6" s="320" t="n"/>
+      <c r="B6" s="393" t="n"/>
+      <c r="C6" s="393" t="n"/>
+      <c r="D6" s="393" t="n"/>
+      <c r="E6" s="393" t="n"/>
+      <c r="F6" s="393" t="n"/>
+      <c r="G6" s="393" t="n"/>
+      <c r="H6" s="346" t="n"/>
+      <c r="I6" s="346" t="n"/>
+      <c r="J6" s="346" t="n"/>
+      <c r="K6" s="346" t="n"/>
+      <c r="L6" s="346" t="n"/>
+      <c r="M6" s="346" t="n"/>
+      <c r="N6" s="346" t="n"/>
+      <c r="O6" s="346" t="n"/>
+      <c r="P6" s="346" t="n"/>
+      <c r="Q6" s="346" t="n"/>
+      <c r="R6" s="346" t="n"/>
+      <c r="S6" s="346" t="n"/>
+      <c r="T6" s="346" t="n"/>
+      <c r="U6" s="346" t="n"/>
+      <c r="V6" s="346" t="n"/>
+      <c r="W6" s="346" t="n"/>
+      <c r="X6" s="346" t="n"/>
+      <c r="Y6" s="346" t="n"/>
+      <c r="Z6" s="346" t="n"/>
+      <c r="AA6" s="346" t="n"/>
+      <c r="AB6" s="346" t="n"/>
+      <c r="AC6" s="346" t="n"/>
+      <c r="AD6" s="346" t="n"/>
+      <c r="AE6" s="346" t="n"/>
+      <c r="AF6" s="346" t="n"/>
+      <c r="AG6" s="346" t="n"/>
+      <c r="AH6" s="346" t="n"/>
+      <c r="AI6" s="346" t="n"/>
+      <c r="AJ6" s="346" t="n"/>
+      <c r="AK6" s="346" t="n"/>
+      <c r="AL6" s="346" t="n"/>
+      <c r="AM6" s="346" t="n"/>
+      <c r="AN6" s="346" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="319">
+      <c r="A7" s="392">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="320" t="n"/>
-      <c r="C7" s="320" t="n"/>
-      <c r="D7" s="320" t="n"/>
-      <c r="E7" s="320" t="n"/>
-      <c r="F7" s="320" t="n"/>
-      <c r="G7" s="320" t="n"/>
+      <c r="B7" s="393" t="n"/>
+      <c r="C7" s="393" t="n"/>
+      <c r="D7" s="393" t="n"/>
+      <c r="E7" s="393" t="n"/>
+      <c r="F7" s="393" t="n"/>
+      <c r="G7" s="393" t="n"/>
+      <c r="H7" s="346" t="n"/>
+      <c r="I7" s="346" t="n"/>
+      <c r="J7" s="346" t="n"/>
+      <c r="K7" s="346" t="n"/>
+      <c r="L7" s="346" t="n"/>
+      <c r="M7" s="346" t="n"/>
+      <c r="N7" s="346" t="n"/>
+      <c r="O7" s="346" t="n"/>
+      <c r="P7" s="346" t="n"/>
+      <c r="Q7" s="346" t="n"/>
+      <c r="R7" s="346" t="n"/>
+      <c r="S7" s="346" t="n"/>
+      <c r="T7" s="346" t="n"/>
+      <c r="U7" s="346" t="n"/>
+      <c r="V7" s="346" t="n"/>
+      <c r="W7" s="346" t="n"/>
+      <c r="X7" s="346" t="n"/>
+      <c r="Y7" s="346" t="n"/>
+      <c r="Z7" s="346" t="n"/>
+      <c r="AA7" s="346" t="n"/>
+      <c r="AB7" s="346" t="n"/>
+      <c r="AC7" s="346" t="n"/>
+      <c r="AD7" s="346" t="n"/>
+      <c r="AE7" s="346" t="n"/>
+      <c r="AF7" s="346" t="n"/>
+      <c r="AG7" s="346" t="n"/>
+      <c r="AH7" s="346" t="n"/>
+      <c r="AI7" s="346" t="n"/>
+      <c r="AJ7" s="346" t="n"/>
+      <c r="AK7" s="346" t="n"/>
+      <c r="AL7" s="346" t="n"/>
+      <c r="AM7" s="346" t="n"/>
+      <c r="AN7" s="346" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="319">
+      <c r="A8" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="320" t="n"/>
-      <c r="C8" s="320" t="n"/>
-      <c r="D8" s="320" t="n"/>
-      <c r="E8" s="320" t="n"/>
-      <c r="F8" s="320" t="n"/>
-      <c r="G8" s="320" t="n"/>
+      <c r="B8" s="395" t="n"/>
+      <c r="C8" s="395" t="n"/>
+      <c r="D8" s="395" t="n"/>
+      <c r="E8" s="395" t="n"/>
+      <c r="F8" s="395" t="n"/>
+      <c r="G8" s="395" t="n"/>
+      <c r="H8" s="396" t="n"/>
+      <c r="I8" s="396" t="n"/>
+      <c r="J8" s="396" t="n"/>
+      <c r="K8" s="396" t="n"/>
+      <c r="L8" s="396" t="n"/>
+      <c r="M8" s="396" t="n"/>
+      <c r="N8" s="396" t="n"/>
+      <c r="O8" s="396" t="n"/>
+      <c r="P8" s="396" t="n"/>
+      <c r="Q8" s="396" t="n"/>
+      <c r="R8" s="396" t="n"/>
+      <c r="S8" s="396" t="n"/>
+      <c r="T8" s="396" t="n"/>
+      <c r="U8" s="396" t="n"/>
+      <c r="V8" s="396" t="n"/>
+      <c r="W8" s="396" t="n"/>
+      <c r="X8" s="396" t="n"/>
+      <c r="Y8" s="396" t="n"/>
+      <c r="Z8" s="396" t="n"/>
+      <c r="AA8" s="396" t="n"/>
+      <c r="AB8" s="396" t="n"/>
+      <c r="AC8" s="396" t="n"/>
+      <c r="AD8" s="396" t="n"/>
+      <c r="AE8" s="396" t="n"/>
+      <c r="AF8" s="396" t="n"/>
+      <c r="AG8" s="396" t="n"/>
+      <c r="AH8" s="396" t="n"/>
+      <c r="AI8" s="396" t="n"/>
+      <c r="AJ8" s="396" t="n"/>
+      <c r="AK8" s="396" t="n"/>
+      <c r="AL8" s="396" t="n"/>
+      <c r="AM8" s="396" t="n"/>
+      <c r="AN8" s="396" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="319">
+      <c r="A9" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="320" t="n"/>
-      <c r="C9" s="320" t="n"/>
-      <c r="D9" s="320" t="n"/>
-      <c r="E9" s="320" t="n"/>
-      <c r="F9" s="320" t="n"/>
-      <c r="G9" s="320" t="n"/>
+      <c r="B9" s="395" t="n"/>
+      <c r="C9" s="395" t="n"/>
+      <c r="D9" s="395" t="n"/>
+      <c r="E9" s="395" t="n"/>
+      <c r="F9" s="395" t="n"/>
+      <c r="G9" s="395" t="n"/>
+      <c r="H9" s="396" t="n"/>
+      <c r="I9" s="396" t="n"/>
+      <c r="J9" s="396" t="n"/>
+      <c r="K9" s="396" t="n"/>
+      <c r="L9" s="396" t="n"/>
+      <c r="M9" s="396" t="n"/>
+      <c r="N9" s="396" t="n"/>
+      <c r="O9" s="396" t="n"/>
+      <c r="P9" s="396" t="n"/>
+      <c r="Q9" s="396" t="n"/>
+      <c r="R9" s="396" t="n"/>
+      <c r="S9" s="396" t="n"/>
+      <c r="T9" s="396" t="n"/>
+      <c r="U9" s="396" t="n"/>
+      <c r="V9" s="396" t="n"/>
+      <c r="W9" s="396" t="n"/>
+      <c r="X9" s="396" t="n"/>
+      <c r="Y9" s="396" t="n"/>
+      <c r="Z9" s="396" t="n"/>
+      <c r="AA9" s="396" t="n"/>
+      <c r="AB9" s="396" t="n"/>
+      <c r="AC9" s="396" t="n"/>
+      <c r="AD9" s="396" t="n"/>
+      <c r="AE9" s="396" t="n"/>
+      <c r="AF9" s="396" t="n"/>
+      <c r="AG9" s="396" t="n"/>
+      <c r="AH9" s="396" t="n"/>
+      <c r="AI9" s="396" t="n"/>
+      <c r="AJ9" s="396" t="n"/>
+      <c r="AK9" s="396" t="n"/>
+      <c r="AL9" s="396" t="n"/>
+      <c r="AM9" s="396" t="n"/>
+      <c r="AN9" s="396" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="319">
+      <c r="A10" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="320" t="n"/>
-      <c r="C10" s="320" t="n"/>
-      <c r="D10" s="320" t="n"/>
-      <c r="E10" s="320" t="n"/>
-      <c r="F10" s="320" t="n"/>
-      <c r="G10" s="320" t="n"/>
+      <c r="B10" s="395" t="n"/>
+      <c r="C10" s="395" t="n"/>
+      <c r="D10" s="395" t="n"/>
+      <c r="E10" s="395" t="n"/>
+      <c r="F10" s="395" t="n"/>
+      <c r="G10" s="395" t="n"/>
+      <c r="H10" s="396" t="n"/>
+      <c r="I10" s="396" t="n"/>
+      <c r="J10" s="396" t="n"/>
+      <c r="K10" s="396" t="n"/>
+      <c r="L10" s="396" t="n"/>
+      <c r="M10" s="396" t="n"/>
+      <c r="N10" s="396" t="n"/>
+      <c r="O10" s="396" t="n"/>
+      <c r="P10" s="396" t="n"/>
+      <c r="Q10" s="396" t="n"/>
+      <c r="R10" s="396" t="n"/>
+      <c r="S10" s="396" t="n"/>
+      <c r="T10" s="396" t="n"/>
+      <c r="U10" s="396" t="n"/>
+      <c r="V10" s="396" t="n"/>
+      <c r="W10" s="396" t="n"/>
+      <c r="X10" s="396" t="n"/>
+      <c r="Y10" s="396" t="n"/>
+      <c r="Z10" s="396" t="n"/>
+      <c r="AA10" s="396" t="n"/>
+      <c r="AB10" s="396" t="n"/>
+      <c r="AC10" s="396" t="n"/>
+      <c r="AD10" s="396" t="n"/>
+      <c r="AE10" s="396" t="n"/>
+      <c r="AF10" s="396" t="n"/>
+      <c r="AG10" s="396" t="n"/>
+      <c r="AH10" s="396" t="n"/>
+      <c r="AI10" s="396" t="n"/>
+      <c r="AJ10" s="396" t="n"/>
+      <c r="AK10" s="396" t="n"/>
+      <c r="AL10" s="396" t="n"/>
+      <c r="AM10" s="396" t="n"/>
+      <c r="AN10" s="396" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="319">
+      <c r="A11" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="320" t="n"/>
-      <c r="C11" s="320" t="n"/>
-      <c r="D11" s="320" t="n"/>
-      <c r="E11" s="320" t="n"/>
-      <c r="F11" s="320" t="n"/>
-      <c r="G11" s="320" t="n"/>
+      <c r="B11" s="395" t="n"/>
+      <c r="C11" s="395" t="n"/>
+      <c r="D11" s="395" t="n"/>
+      <c r="E11" s="395" t="n"/>
+      <c r="F11" s="395" t="n"/>
+      <c r="G11" s="395" t="n"/>
+      <c r="H11" s="396" t="n"/>
+      <c r="I11" s="396" t="n"/>
+      <c r="J11" s="396" t="n"/>
+      <c r="K11" s="396" t="n"/>
+      <c r="L11" s="396" t="n"/>
+      <c r="M11" s="396" t="n"/>
+      <c r="N11" s="396" t="n"/>
+      <c r="O11" s="396" t="n"/>
+      <c r="P11" s="396" t="n"/>
+      <c r="Q11" s="396" t="n"/>
+      <c r="R11" s="396" t="n"/>
+      <c r="S11" s="396" t="n"/>
+      <c r="T11" s="396" t="n"/>
+      <c r="U11" s="396" t="n"/>
+      <c r="V11" s="396" t="n"/>
+      <c r="W11" s="396" t="n"/>
+      <c r="X11" s="396" t="n"/>
+      <c r="Y11" s="396" t="n"/>
+      <c r="Z11" s="396" t="n"/>
+      <c r="AA11" s="396" t="n"/>
+      <c r="AB11" s="396" t="n"/>
+      <c r="AC11" s="396" t="n"/>
+      <c r="AD11" s="396" t="n"/>
+      <c r="AE11" s="396" t="n"/>
+      <c r="AF11" s="396" t="n"/>
+      <c r="AG11" s="396" t="n"/>
+      <c r="AH11" s="396" t="n"/>
+      <c r="AI11" s="396" t="n"/>
+      <c r="AJ11" s="396" t="n"/>
+      <c r="AK11" s="396" t="n"/>
+      <c r="AL11" s="396" t="n"/>
+      <c r="AM11" s="396" t="n"/>
+      <c r="AN11" s="396" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="319">
+      <c r="A12" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="320" t="n"/>
-      <c r="C12" s="320" t="n"/>
-      <c r="D12" s="320" t="n"/>
-      <c r="E12" s="320" t="n"/>
-      <c r="F12" s="320" t="n"/>
-      <c r="G12" s="320" t="n"/>
+      <c r="B12" s="395" t="n"/>
+      <c r="C12" s="395" t="n"/>
+      <c r="D12" s="395" t="n"/>
+      <c r="E12" s="395" t="n"/>
+      <c r="F12" s="395" t="n"/>
+      <c r="G12" s="395" t="n"/>
+      <c r="H12" s="396" t="n"/>
+      <c r="I12" s="396" t="n"/>
+      <c r="J12" s="396" t="n"/>
+      <c r="K12" s="396" t="n"/>
+      <c r="L12" s="396" t="n"/>
+      <c r="M12" s="396" t="n"/>
+      <c r="N12" s="396" t="n"/>
+      <c r="O12" s="396" t="n"/>
+      <c r="P12" s="396" t="n"/>
+      <c r="Q12" s="396" t="n"/>
+      <c r="R12" s="396" t="n"/>
+      <c r="S12" s="396" t="n"/>
+      <c r="T12" s="396" t="n"/>
+      <c r="U12" s="396" t="n"/>
+      <c r="V12" s="396" t="n"/>
+      <c r="W12" s="396" t="n"/>
+      <c r="X12" s="396" t="n"/>
+      <c r="Y12" s="396" t="n"/>
+      <c r="Z12" s="396" t="n"/>
+      <c r="AA12" s="396" t="n"/>
+      <c r="AB12" s="396" t="n"/>
+      <c r="AC12" s="396" t="n"/>
+      <c r="AD12" s="396" t="n"/>
+      <c r="AE12" s="396" t="n"/>
+      <c r="AF12" s="396" t="n"/>
+      <c r="AG12" s="396" t="n"/>
+      <c r="AH12" s="396" t="n"/>
+      <c r="AI12" s="396" t="n"/>
+      <c r="AJ12" s="396" t="n"/>
+      <c r="AK12" s="396" t="n"/>
+      <c r="AL12" s="396" t="n"/>
+      <c r="AM12" s="396" t="n"/>
+      <c r="AN12" s="396" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="319">
+      <c r="A13" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="320" t="n"/>
-      <c r="C13" s="320" t="n"/>
-      <c r="D13" s="320" t="n"/>
-      <c r="E13" s="320" t="n"/>
-      <c r="F13" s="320" t="n"/>
-      <c r="G13" s="320" t="n"/>
+      <c r="B13" s="395" t="n"/>
+      <c r="C13" s="395" t="n"/>
+      <c r="D13" s="395" t="n"/>
+      <c r="E13" s="395" t="n"/>
+      <c r="F13" s="395" t="n"/>
+      <c r="G13" s="395" t="n"/>
+      <c r="H13" s="396" t="n"/>
+      <c r="I13" s="396" t="n"/>
+      <c r="J13" s="396" t="n"/>
+      <c r="K13" s="396" t="n"/>
+      <c r="L13" s="396" t="n"/>
+      <c r="M13" s="396" t="n"/>
+      <c r="N13" s="396" t="n"/>
+      <c r="O13" s="396" t="n"/>
+      <c r="P13" s="396" t="n"/>
+      <c r="Q13" s="396" t="n"/>
+      <c r="R13" s="396" t="n"/>
+      <c r="S13" s="396" t="n"/>
+      <c r="T13" s="396" t="n"/>
+      <c r="U13" s="396" t="n"/>
+      <c r="V13" s="396" t="n"/>
+      <c r="W13" s="396" t="n"/>
+      <c r="X13" s="396" t="n"/>
+      <c r="Y13" s="396" t="n"/>
+      <c r="Z13" s="396" t="n"/>
+      <c r="AA13" s="396" t="n"/>
+      <c r="AB13" s="396" t="n"/>
+      <c r="AC13" s="396" t="n"/>
+      <c r="AD13" s="396" t="n"/>
+      <c r="AE13" s="396" t="n"/>
+      <c r="AF13" s="396" t="n"/>
+      <c r="AG13" s="396" t="n"/>
+      <c r="AH13" s="396" t="n"/>
+      <c r="AI13" s="396" t="n"/>
+      <c r="AJ13" s="396" t="n"/>
+      <c r="AK13" s="396" t="n"/>
+      <c r="AL13" s="396" t="n"/>
+      <c r="AM13" s="396" t="n"/>
+      <c r="AN13" s="396" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="319">
+      <c r="A14" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="320" t="n"/>
-      <c r="C14" s="320" t="n"/>
-      <c r="D14" s="320" t="n"/>
-      <c r="E14" s="320" t="n"/>
-      <c r="F14" s="320" t="n"/>
-      <c r="G14" s="320" t="n"/>
+      <c r="B14" s="395" t="n"/>
+      <c r="C14" s="395" t="n"/>
+      <c r="D14" s="395" t="n"/>
+      <c r="E14" s="395" t="n"/>
+      <c r="F14" s="395" t="n"/>
+      <c r="G14" s="395" t="n"/>
+      <c r="H14" s="396" t="n"/>
+      <c r="I14" s="396" t="n"/>
+      <c r="J14" s="396" t="n"/>
+      <c r="K14" s="396" t="n"/>
+      <c r="L14" s="396" t="n"/>
+      <c r="M14" s="396" t="n"/>
+      <c r="N14" s="396" t="n"/>
+      <c r="O14" s="396" t="n"/>
+      <c r="P14" s="396" t="n"/>
+      <c r="Q14" s="396" t="n"/>
+      <c r="R14" s="396" t="n"/>
+      <c r="S14" s="396" t="n"/>
+      <c r="T14" s="396" t="n"/>
+      <c r="U14" s="396" t="n"/>
+      <c r="V14" s="396" t="n"/>
+      <c r="W14" s="396" t="n"/>
+      <c r="X14" s="396" t="n"/>
+      <c r="Y14" s="396" t="n"/>
+      <c r="Z14" s="396" t="n"/>
+      <c r="AA14" s="396" t="n"/>
+      <c r="AB14" s="396" t="n"/>
+      <c r="AC14" s="396" t="n"/>
+      <c r="AD14" s="396" t="n"/>
+      <c r="AE14" s="396" t="n"/>
+      <c r="AF14" s="396" t="n"/>
+      <c r="AG14" s="396" t="n"/>
+      <c r="AH14" s="396" t="n"/>
+      <c r="AI14" s="396" t="n"/>
+      <c r="AJ14" s="396" t="n"/>
+      <c r="AK14" s="396" t="n"/>
+      <c r="AL14" s="396" t="n"/>
+      <c r="AM14" s="396" t="n"/>
+      <c r="AN14" s="396" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="319">
+      <c r="A15" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B15" s="320" t="n"/>
-      <c r="C15" s="320" t="n"/>
-      <c r="D15" s="320" t="n"/>
-      <c r="E15" s="320" t="n"/>
-      <c r="F15" s="320" t="n"/>
-      <c r="G15" s="320" t="n"/>
+      <c r="B15" s="395" t="n"/>
+      <c r="C15" s="395" t="n"/>
+      <c r="D15" s="395" t="n"/>
+      <c r="E15" s="395" t="n"/>
+      <c r="F15" s="395" t="n"/>
+      <c r="G15" s="395" t="n"/>
+      <c r="H15" s="396" t="n"/>
+      <c r="I15" s="396" t="n"/>
+      <c r="J15" s="396" t="n"/>
+      <c r="K15" s="396" t="n"/>
+      <c r="L15" s="396" t="n"/>
+      <c r="M15" s="396" t="n"/>
+      <c r="N15" s="396" t="n"/>
+      <c r="O15" s="396" t="n"/>
+      <c r="P15" s="396" t="n"/>
+      <c r="Q15" s="396" t="n"/>
+      <c r="R15" s="396" t="n"/>
+      <c r="S15" s="396" t="n"/>
+      <c r="T15" s="396" t="n"/>
+      <c r="U15" s="396" t="n"/>
+      <c r="V15" s="396" t="n"/>
+      <c r="W15" s="396" t="n"/>
+      <c r="X15" s="396" t="n"/>
+      <c r="Y15" s="396" t="n"/>
+      <c r="Z15" s="396" t="n"/>
+      <c r="AA15" s="396" t="n"/>
+      <c r="AB15" s="396" t="n"/>
+      <c r="AC15" s="396" t="n"/>
+      <c r="AD15" s="396" t="n"/>
+      <c r="AE15" s="396" t="n"/>
+      <c r="AF15" s="396" t="n"/>
+      <c r="AG15" s="396" t="n"/>
+      <c r="AH15" s="396" t="n"/>
+      <c r="AI15" s="396" t="n"/>
+      <c r="AJ15" s="396" t="n"/>
+      <c r="AK15" s="396" t="n"/>
+      <c r="AL15" s="396" t="n"/>
+      <c r="AM15" s="396" t="n"/>
+      <c r="AN15" s="396" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="319">
+      <c r="A16" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B16" s="320" t="n"/>
-      <c r="C16" s="320" t="n"/>
-      <c r="D16" s="320" t="n"/>
-      <c r="E16" s="320" t="n"/>
-      <c r="F16" s="320" t="n"/>
-      <c r="G16" s="320" t="n"/>
+      <c r="B16" s="395" t="n"/>
+      <c r="C16" s="395" t="n"/>
+      <c r="D16" s="395" t="n"/>
+      <c r="E16" s="395" t="n"/>
+      <c r="F16" s="395" t="n"/>
+      <c r="G16" s="395" t="n"/>
+      <c r="H16" s="396" t="n"/>
+      <c r="I16" s="396" t="n"/>
+      <c r="J16" s="396" t="n"/>
+      <c r="K16" s="396" t="n"/>
+      <c r="L16" s="396" t="n"/>
+      <c r="M16" s="396" t="n"/>
+      <c r="N16" s="396" t="n"/>
+      <c r="O16" s="396" t="n"/>
+      <c r="P16" s="396" t="n"/>
+      <c r="Q16" s="396" t="n"/>
+      <c r="R16" s="396" t="n"/>
+      <c r="S16" s="396" t="n"/>
+      <c r="T16" s="396" t="n"/>
+      <c r="U16" s="396" t="n"/>
+      <c r="V16" s="396" t="n"/>
+      <c r="W16" s="396" t="n"/>
+      <c r="X16" s="396" t="n"/>
+      <c r="Y16" s="396" t="n"/>
+      <c r="Z16" s="396" t="n"/>
+      <c r="AA16" s="396" t="n"/>
+      <c r="AB16" s="396" t="n"/>
+      <c r="AC16" s="396" t="n"/>
+      <c r="AD16" s="396" t="n"/>
+      <c r="AE16" s="396" t="n"/>
+      <c r="AF16" s="396" t="n"/>
+      <c r="AG16" s="396" t="n"/>
+      <c r="AH16" s="396" t="n"/>
+      <c r="AI16" s="396" t="n"/>
+      <c r="AJ16" s="396" t="n"/>
+      <c r="AK16" s="396" t="n"/>
+      <c r="AL16" s="396" t="n"/>
+      <c r="AM16" s="396" t="n"/>
+      <c r="AN16" s="396" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="319">
+      <c r="A17" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B17" s="320" t="n"/>
-      <c r="C17" s="320" t="n"/>
-      <c r="D17" s="320" t="n"/>
-      <c r="E17" s="320" t="n"/>
-      <c r="F17" s="320" t="n"/>
-      <c r="G17" s="320" t="n"/>
+      <c r="B17" s="395" t="n"/>
+      <c r="C17" s="395" t="n"/>
+      <c r="D17" s="395" t="n"/>
+      <c r="E17" s="395" t="n"/>
+      <c r="F17" s="395" t="n"/>
+      <c r="G17" s="395" t="n"/>
+      <c r="H17" s="396" t="n"/>
+      <c r="I17" s="396" t="n"/>
+      <c r="J17" s="396" t="n"/>
+      <c r="K17" s="396" t="n"/>
+      <c r="L17" s="396" t="n"/>
+      <c r="M17" s="396" t="n"/>
+      <c r="N17" s="396" t="n"/>
+      <c r="O17" s="396" t="n"/>
+      <c r="P17" s="396" t="n"/>
+      <c r="Q17" s="396" t="n"/>
+      <c r="R17" s="396" t="n"/>
+      <c r="S17" s="396" t="n"/>
+      <c r="T17" s="396" t="n"/>
+      <c r="U17" s="396" t="n"/>
+      <c r="V17" s="396" t="n"/>
+      <c r="W17" s="396" t="n"/>
+      <c r="X17" s="396" t="n"/>
+      <c r="Y17" s="396" t="n"/>
+      <c r="Z17" s="396" t="n"/>
+      <c r="AA17" s="396" t="n"/>
+      <c r="AB17" s="396" t="n"/>
+      <c r="AC17" s="396" t="n"/>
+      <c r="AD17" s="396" t="n"/>
+      <c r="AE17" s="396" t="n"/>
+      <c r="AF17" s="396" t="n"/>
+      <c r="AG17" s="396" t="n"/>
+      <c r="AH17" s="396" t="n"/>
+      <c r="AI17" s="396" t="n"/>
+      <c r="AJ17" s="396" t="n"/>
+      <c r="AK17" s="396" t="n"/>
+      <c r="AL17" s="396" t="n"/>
+      <c r="AM17" s="396" t="n"/>
+      <c r="AN17" s="396" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="319">
+      <c r="A18" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B18" s="320" t="n"/>
-      <c r="C18" s="320" t="n"/>
-      <c r="D18" s="320" t="n"/>
-      <c r="E18" s="320" t="n"/>
-      <c r="F18" s="320" t="n"/>
-      <c r="G18" s="320" t="n"/>
+      <c r="B18" s="395" t="n"/>
+      <c r="C18" s="395" t="n"/>
+      <c r="D18" s="395" t="n"/>
+      <c r="E18" s="395" t="n"/>
+      <c r="F18" s="395" t="n"/>
+      <c r="G18" s="395" t="n"/>
+      <c r="H18" s="396" t="n"/>
+      <c r="I18" s="396" t="n"/>
+      <c r="J18" s="396" t="n"/>
+      <c r="K18" s="396" t="n"/>
+      <c r="L18" s="396" t="n"/>
+      <c r="M18" s="396" t="n"/>
+      <c r="N18" s="396" t="n"/>
+      <c r="O18" s="396" t="n"/>
+      <c r="P18" s="396" t="n"/>
+      <c r="Q18" s="396" t="n"/>
+      <c r="R18" s="396" t="n"/>
+      <c r="S18" s="396" t="n"/>
+      <c r="T18" s="396" t="n"/>
+      <c r="U18" s="396" t="n"/>
+      <c r="V18" s="396" t="n"/>
+      <c r="W18" s="396" t="n"/>
+      <c r="X18" s="396" t="n"/>
+      <c r="Y18" s="396" t="n"/>
+      <c r="Z18" s="396" t="n"/>
+      <c r="AA18" s="396" t="n"/>
+      <c r="AB18" s="396" t="n"/>
+      <c r="AC18" s="396" t="n"/>
+      <c r="AD18" s="396" t="n"/>
+      <c r="AE18" s="396" t="n"/>
+      <c r="AF18" s="396" t="n"/>
+      <c r="AG18" s="396" t="n"/>
+      <c r="AH18" s="396" t="n"/>
+      <c r="AI18" s="396" t="n"/>
+      <c r="AJ18" s="396" t="n"/>
+      <c r="AK18" s="396" t="n"/>
+      <c r="AL18" s="396" t="n"/>
+      <c r="AM18" s="396" t="n"/>
+      <c r="AN18" s="396" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="319">
+      <c r="A19" s="394">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B19" s="320" t="n"/>
-      <c r="C19" s="320" t="n"/>
-      <c r="D19" s="320" t="n"/>
-      <c r="E19" s="320" t="n"/>
-      <c r="F19" s="320" t="n"/>
-      <c r="G19" s="320" t="n"/>
+      <c r="B19" s="395" t="n"/>
+      <c r="C19" s="395" t="n"/>
+      <c r="D19" s="395" t="n"/>
+      <c r="E19" s="395" t="n"/>
+      <c r="F19" s="395" t="n"/>
+      <c r="G19" s="395" t="n"/>
+      <c r="H19" s="396" t="n"/>
+      <c r="I19" s="396" t="n"/>
+      <c r="J19" s="396" t="n"/>
+      <c r="K19" s="396" t="n"/>
+      <c r="L19" s="396" t="n"/>
+      <c r="M19" s="396" t="n"/>
+      <c r="N19" s="396" t="n"/>
+      <c r="O19" s="396" t="n"/>
+      <c r="P19" s="396" t="n"/>
+      <c r="Q19" s="396" t="n"/>
+      <c r="R19" s="396" t="n"/>
+      <c r="S19" s="396" t="n"/>
+      <c r="T19" s="396" t="n"/>
+      <c r="U19" s="396" t="n"/>
+      <c r="V19" s="396" t="n"/>
+      <c r="W19" s="396" t="n"/>
+      <c r="X19" s="396" t="n"/>
+      <c r="Y19" s="396" t="n"/>
+      <c r="Z19" s="396" t="n"/>
+      <c r="AA19" s="396" t="n"/>
+      <c r="AB19" s="396" t="n"/>
+      <c r="AC19" s="396" t="n"/>
+      <c r="AD19" s="396" t="n"/>
+      <c r="AE19" s="396" t="n"/>
+      <c r="AF19" s="396" t="n"/>
+      <c r="AG19" s="396" t="n"/>
+      <c r="AH19" s="396" t="n"/>
+      <c r="AI19" s="396" t="n"/>
+      <c r="AJ19" s="396" t="n"/>
+      <c r="AK19" s="396" t="n"/>
+      <c r="AL19" s="396" t="n"/>
+      <c r="AM19" s="396" t="n"/>
+      <c r="AN19" s="396" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -7452,7 +8809,8 @@
       <formula1>'LISTS'!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
@@ -7465,30 +8823,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="316" t="inlineStr">
+      <c r="A1" s="391" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="420" t="n"/>
+      <c r="C1" s="420" t="n"/>
+      <c r="D1" s="420" t="n"/>
+      <c r="E1" s="420" t="n"/>
+      <c r="F1" s="420" t="n"/>
+      <c r="G1" s="421" t="n"/>
+      <c r="H1" s="346" t="n"/>
+      <c r="I1" s="346" t="n"/>
+      <c r="J1" s="346" t="n"/>
+      <c r="K1" s="346" t="n"/>
+      <c r="L1" s="346" t="n"/>
+      <c r="M1" s="346" t="n"/>
+      <c r="N1" s="346" t="n"/>
+      <c r="O1" s="346" t="n"/>
+      <c r="P1" s="346" t="n"/>
+      <c r="Q1" s="346" t="n"/>
+      <c r="R1" s="346" t="n"/>
+      <c r="S1" s="346" t="n"/>
+      <c r="T1" s="346" t="n"/>
+      <c r="U1" s="346" t="n"/>
+      <c r="V1" s="346" t="n"/>
+      <c r="W1" s="346" t="n"/>
+      <c r="X1" s="346" t="n"/>
+      <c r="Y1" s="346" t="n"/>
+      <c r="Z1" s="346" t="n"/>
+      <c r="AA1" s="346" t="n"/>
+      <c r="AB1" s="346" t="n"/>
+      <c r="AC1" s="346" t="n"/>
+      <c r="AD1" s="346" t="n"/>
+      <c r="AE1" s="346" t="n"/>
+      <c r="AF1" s="346" t="n"/>
+      <c r="AG1" s="346" t="n"/>
+      <c r="AH1" s="346" t="n"/>
+      <c r="AI1" s="346" t="n"/>
+      <c r="AJ1" s="346" t="n"/>
+      <c r="AK1" s="346" t="n"/>
+      <c r="AL1" s="346" t="n"/>
+      <c r="AM1" s="346" t="n"/>
+      <c r="AN1" s="346" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="317" t="inlineStr">
@@ -7496,54 +8920,202 @@
           <t>Reference plan / lot / method / release documents from their owning source.</t>
         </is>
       </c>
+      <c r="H2" s="346" t="n"/>
+      <c r="I2" s="346" t="n"/>
+      <c r="J2" s="346" t="n"/>
+      <c r="K2" s="346" t="n"/>
+      <c r="L2" s="346" t="n"/>
+      <c r="M2" s="346" t="n"/>
+      <c r="N2" s="346" t="n"/>
+      <c r="O2" s="346" t="n"/>
+      <c r="P2" s="346" t="n"/>
+      <c r="Q2" s="346" t="n"/>
+      <c r="R2" s="346" t="n"/>
+      <c r="S2" s="346" t="n"/>
+      <c r="T2" s="346" t="n"/>
+      <c r="U2" s="346" t="n"/>
+      <c r="V2" s="346" t="n"/>
+      <c r="W2" s="346" t="n"/>
+      <c r="X2" s="346" t="n"/>
+      <c r="Y2" s="346" t="n"/>
+      <c r="Z2" s="346" t="n"/>
+      <c r="AA2" s="346" t="n"/>
+      <c r="AB2" s="346" t="n"/>
+      <c r="AC2" s="346" t="n"/>
+      <c r="AD2" s="346" t="n"/>
+      <c r="AE2" s="346" t="n"/>
+      <c r="AF2" s="346" t="n"/>
+      <c r="AG2" s="346" t="n"/>
+      <c r="AH2" s="346" t="n"/>
+      <c r="AI2" s="346" t="n"/>
+      <c r="AJ2" s="346" t="n"/>
+      <c r="AK2" s="346" t="n"/>
+      <c r="AL2" s="346" t="n"/>
+      <c r="AM2" s="346" t="n"/>
+      <c r="AN2" s="346" t="n"/>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="346" t="n"/>
+      <c r="B3" s="346" t="n"/>
+      <c r="C3" s="346" t="n"/>
+      <c r="D3" s="346" t="n"/>
+      <c r="E3" s="346" t="n"/>
+      <c r="F3" s="346" t="n"/>
+      <c r="G3" s="346" t="n"/>
+      <c r="H3" s="346" t="n"/>
+      <c r="I3" s="346" t="n"/>
+      <c r="J3" s="346" t="n"/>
+      <c r="K3" s="346" t="n"/>
+      <c r="L3" s="346" t="n"/>
+      <c r="M3" s="346" t="n"/>
+      <c r="N3" s="346" t="n"/>
+      <c r="O3" s="346" t="n"/>
+      <c r="P3" s="346" t="n"/>
+      <c r="Q3" s="346" t="n"/>
+      <c r="R3" s="346" t="n"/>
+      <c r="S3" s="346" t="n"/>
+      <c r="T3" s="346" t="n"/>
+      <c r="U3" s="346" t="n"/>
+      <c r="V3" s="346" t="n"/>
+      <c r="W3" s="346" t="n"/>
+      <c r="X3" s="346" t="n"/>
+      <c r="Y3" s="346" t="n"/>
+      <c r="Z3" s="346" t="n"/>
+      <c r="AA3" s="346" t="n"/>
+      <c r="AB3" s="346" t="n"/>
+      <c r="AC3" s="346" t="n"/>
+      <c r="AD3" s="346" t="n"/>
+      <c r="AE3" s="346" t="n"/>
+      <c r="AF3" s="346" t="n"/>
+      <c r="AG3" s="346" t="n"/>
+      <c r="AH3" s="346" t="n"/>
+      <c r="AI3" s="346" t="n"/>
+      <c r="AJ3" s="346" t="n"/>
+      <c r="AK3" s="346" t="n"/>
+      <c r="AL3" s="346" t="n"/>
+      <c r="AM3" s="346" t="n"/>
+      <c r="AN3" s="346" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="318" t="inlineStr">
+      <c r="A4" s="362" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="318" t="inlineStr">
+      <c r="B4" s="362" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="318" t="inlineStr">
+      <c r="C4" s="362" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="346" t="n"/>
+      <c r="E4" s="346" t="n"/>
+      <c r="F4" s="346" t="n"/>
+      <c r="G4" s="346" t="n"/>
+      <c r="H4" s="346" t="n"/>
+      <c r="I4" s="346" t="n"/>
+      <c r="J4" s="346" t="n"/>
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="346" t="n"/>
+      <c r="M4" s="346" t="n"/>
+      <c r="N4" s="346" t="n"/>
+      <c r="O4" s="346" t="n"/>
+      <c r="P4" s="346" t="n"/>
+      <c r="Q4" s="346" t="n"/>
+      <c r="R4" s="346" t="n"/>
+      <c r="S4" s="346" t="n"/>
+      <c r="T4" s="346" t="n"/>
+      <c r="U4" s="346" t="n"/>
+      <c r="V4" s="346" t="n"/>
+      <c r="W4" s="346" t="n"/>
+      <c r="X4" s="346" t="n"/>
+      <c r="Y4" s="346" t="n"/>
+      <c r="Z4" s="346" t="n"/>
+      <c r="AA4" s="346" t="n"/>
+      <c r="AB4" s="346" t="n"/>
+      <c r="AC4" s="346" t="n"/>
+      <c r="AD4" s="346" t="n"/>
+      <c r="AE4" s="346" t="n"/>
+      <c r="AF4" s="346" t="n"/>
+      <c r="AG4" s="346" t="n"/>
+      <c r="AH4" s="346" t="n"/>
+      <c r="AI4" s="346" t="n"/>
+      <c r="AJ4" s="346" t="n"/>
+      <c r="AK4" s="346" t="n"/>
+      <c r="AL4" s="346" t="n"/>
+      <c r="AM4" s="346" t="n"/>
+      <c r="AN4" s="346" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="319" t="inlineStr">
+      <c r="A5" s="392" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="320" t="inlineStr">
+      <c r="B5" s="393" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="320" t="inlineStr">
+      <c r="C5" s="393" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="346" t="n"/>
+      <c r="E5" s="346" t="n"/>
+      <c r="F5" s="346" t="n"/>
+      <c r="G5" s="346" t="n"/>
+      <c r="H5" s="346" t="n"/>
+      <c r="I5" s="346" t="n"/>
+      <c r="J5" s="346" t="n"/>
+      <c r="K5" s="346" t="n"/>
+      <c r="L5" s="346" t="n"/>
+      <c r="M5" s="346" t="n"/>
+      <c r="N5" s="346" t="n"/>
+      <c r="O5" s="346" t="n"/>
+      <c r="P5" s="346" t="n"/>
+      <c r="Q5" s="346" t="n"/>
+      <c r="R5" s="346" t="n"/>
+      <c r="S5" s="346" t="n"/>
+      <c r="T5" s="346" t="n"/>
+      <c r="U5" s="346" t="n"/>
+      <c r="V5" s="346" t="n"/>
+      <c r="W5" s="346" t="n"/>
+      <c r="X5" s="346" t="n"/>
+      <c r="Y5" s="346" t="n"/>
+      <c r="Z5" s="346" t="n"/>
+      <c r="AA5" s="346" t="n"/>
+      <c r="AB5" s="346" t="n"/>
+      <c r="AC5" s="346" t="n"/>
+      <c r="AD5" s="346" t="n"/>
+      <c r="AE5" s="346" t="n"/>
+      <c r="AF5" s="346" t="n"/>
+      <c r="AG5" s="346" t="n"/>
+      <c r="AH5" s="346" t="n"/>
+      <c r="AI5" s="346" t="n"/>
+      <c r="AJ5" s="346" t="n"/>
+      <c r="AK5" s="346" t="n"/>
+      <c r="AL5" s="346" t="n"/>
+      <c r="AM5" s="346" t="n"/>
+      <c r="AN5" s="346" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="319" t="inlineStr">
+      <c r="A6" s="392" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="320" t="inlineStr">
+      <c r="B6" s="393" t="inlineStr">
         <is>
           <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
         </is>
       </c>
-      <c r="C6" s="320" t="inlineStr">
+      <c r="C6" s="393" t="inlineStr">
         <is>
           <t>This form does not replace SOP-605; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-605; this form captures results, checks, decisions or exceptions only.
@@ -7551,159 +9123,529 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="346" t="n"/>
+      <c r="E6" s="346" t="n"/>
+      <c r="F6" s="346" t="n"/>
+      <c r="G6" s="346" t="n"/>
+      <c r="H6" s="346" t="n"/>
+      <c r="I6" s="346" t="n"/>
+      <c r="J6" s="346" t="n"/>
+      <c r="K6" s="346" t="n"/>
+      <c r="L6" s="346" t="n"/>
+      <c r="M6" s="346" t="n"/>
+      <c r="N6" s="346" t="n"/>
+      <c r="O6" s="346" t="n"/>
+      <c r="P6" s="346" t="n"/>
+      <c r="Q6" s="346" t="n"/>
+      <c r="R6" s="346" t="n"/>
+      <c r="S6" s="346" t="n"/>
+      <c r="T6" s="346" t="n"/>
+      <c r="U6" s="346" t="n"/>
+      <c r="V6" s="346" t="n"/>
+      <c r="W6" s="346" t="n"/>
+      <c r="X6" s="346" t="n"/>
+      <c r="Y6" s="346" t="n"/>
+      <c r="Z6" s="346" t="n"/>
+      <c r="AA6" s="346" t="n"/>
+      <c r="AB6" s="346" t="n"/>
+      <c r="AC6" s="346" t="n"/>
+      <c r="AD6" s="346" t="n"/>
+      <c r="AE6" s="346" t="n"/>
+      <c r="AF6" s="346" t="n"/>
+      <c r="AG6" s="346" t="n"/>
+      <c r="AH6" s="346" t="n"/>
+      <c r="AI6" s="346" t="n"/>
+      <c r="AJ6" s="346" t="n"/>
+      <c r="AK6" s="346" t="n"/>
+      <c r="AL6" s="346" t="n"/>
+      <c r="AM6" s="346" t="n"/>
+      <c r="AN6" s="346" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="319" t="inlineStr">
+      <c r="A7" s="392" t="inlineStr">
         <is>
           <t>SOP SOP-605</t>
         </is>
       </c>
-      <c r="B7" s="320" t="inlineStr">
+      <c r="B7" s="393" t="inlineStr">
         <is>
           <t>SOP-605 — Kiểm tra cuối, CoC và phê duyệt giao hàng | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="320" t="inlineStr">
+      <c r="C7" s="393" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-605-final-inspection-coc-and-shipment-release.html</t>
         </is>
       </c>
+      <c r="D7" s="346" t="n"/>
+      <c r="E7" s="346" t="n"/>
+      <c r="F7" s="346" t="n"/>
+      <c r="G7" s="346" t="n"/>
+      <c r="H7" s="346" t="n"/>
+      <c r="I7" s="346" t="n"/>
+      <c r="J7" s="346" t="n"/>
+      <c r="K7" s="346" t="n"/>
+      <c r="L7" s="346" t="n"/>
+      <c r="M7" s="346" t="n"/>
+      <c r="N7" s="346" t="n"/>
+      <c r="O7" s="346" t="n"/>
+      <c r="P7" s="346" t="n"/>
+      <c r="Q7" s="346" t="n"/>
+      <c r="R7" s="346" t="n"/>
+      <c r="S7" s="346" t="n"/>
+      <c r="T7" s="346" t="n"/>
+      <c r="U7" s="346" t="n"/>
+      <c r="V7" s="346" t="n"/>
+      <c r="W7" s="346" t="n"/>
+      <c r="X7" s="346" t="n"/>
+      <c r="Y7" s="346" t="n"/>
+      <c r="Z7" s="346" t="n"/>
+      <c r="AA7" s="346" t="n"/>
+      <c r="AB7" s="346" t="n"/>
+      <c r="AC7" s="346" t="n"/>
+      <c r="AD7" s="346" t="n"/>
+      <c r="AE7" s="346" t="n"/>
+      <c r="AF7" s="346" t="n"/>
+      <c r="AG7" s="346" t="n"/>
+      <c r="AH7" s="346" t="n"/>
+      <c r="AI7" s="346" t="n"/>
+      <c r="AJ7" s="346" t="n"/>
+      <c r="AK7" s="346" t="n"/>
+      <c r="AL7" s="346" t="n"/>
+      <c r="AM7" s="346" t="n"/>
+      <c r="AN7" s="346" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="319" t="inlineStr">
+      <c r="A8" s="394" t="inlineStr">
         <is>
           <t>WI WI-605</t>
         </is>
       </c>
-      <c r="B8" s="320" t="inlineStr">
+      <c r="B8" s="395" t="inlineStr">
         <is>
           <t>WI-605 — Kiểm cuối, CoC/CofC, bàn giao phát hành giao hàng</t>
         </is>
       </c>
-      <c r="C8" s="320" t="inlineStr">
+      <c r="C8" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-605-final-inspection-coc-and-shipment-release-handoff.html</t>
         </is>
       </c>
+      <c r="D8" s="396" t="n"/>
+      <c r="E8" s="396" t="n"/>
+      <c r="F8" s="396" t="n"/>
+      <c r="G8" s="396" t="n"/>
+      <c r="H8" s="396" t="n"/>
+      <c r="I8" s="396" t="n"/>
+      <c r="J8" s="396" t="n"/>
+      <c r="K8" s="396" t="n"/>
+      <c r="L8" s="396" t="n"/>
+      <c r="M8" s="396" t="n"/>
+      <c r="N8" s="396" t="n"/>
+      <c r="O8" s="396" t="n"/>
+      <c r="P8" s="396" t="n"/>
+      <c r="Q8" s="396" t="n"/>
+      <c r="R8" s="396" t="n"/>
+      <c r="S8" s="396" t="n"/>
+      <c r="T8" s="396" t="n"/>
+      <c r="U8" s="396" t="n"/>
+      <c r="V8" s="396" t="n"/>
+      <c r="W8" s="396" t="n"/>
+      <c r="X8" s="396" t="n"/>
+      <c r="Y8" s="396" t="n"/>
+      <c r="Z8" s="396" t="n"/>
+      <c r="AA8" s="396" t="n"/>
+      <c r="AB8" s="396" t="n"/>
+      <c r="AC8" s="396" t="n"/>
+      <c r="AD8" s="396" t="n"/>
+      <c r="AE8" s="396" t="n"/>
+      <c r="AF8" s="396" t="n"/>
+      <c r="AG8" s="396" t="n"/>
+      <c r="AH8" s="396" t="n"/>
+      <c r="AI8" s="396" t="n"/>
+      <c r="AJ8" s="396" t="n"/>
+      <c r="AK8" s="396" t="n"/>
+      <c r="AL8" s="396" t="n"/>
+      <c r="AM8" s="396" t="n"/>
+      <c r="AN8" s="396" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="319" t="inlineStr">
+      <c r="A9" s="394" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-001</t>
         </is>
       </c>
-      <c r="B9" s="320" t="inlineStr">
+      <c r="B9" s="395" t="inlineStr">
         <is>
           <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
         </is>
       </c>
-      <c r="C9" s="320" t="inlineStr">
+      <c r="C9" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
         </is>
       </c>
+      <c r="D9" s="396" t="n"/>
+      <c r="E9" s="396" t="n"/>
+      <c r="F9" s="396" t="n"/>
+      <c r="G9" s="396" t="n"/>
+      <c r="H9" s="396" t="n"/>
+      <c r="I9" s="396" t="n"/>
+      <c r="J9" s="396" t="n"/>
+      <c r="K9" s="396" t="n"/>
+      <c r="L9" s="396" t="n"/>
+      <c r="M9" s="396" t="n"/>
+      <c r="N9" s="396" t="n"/>
+      <c r="O9" s="396" t="n"/>
+      <c r="P9" s="396" t="n"/>
+      <c r="Q9" s="396" t="n"/>
+      <c r="R9" s="396" t="n"/>
+      <c r="S9" s="396" t="n"/>
+      <c r="T9" s="396" t="n"/>
+      <c r="U9" s="396" t="n"/>
+      <c r="V9" s="396" t="n"/>
+      <c r="W9" s="396" t="n"/>
+      <c r="X9" s="396" t="n"/>
+      <c r="Y9" s="396" t="n"/>
+      <c r="Z9" s="396" t="n"/>
+      <c r="AA9" s="396" t="n"/>
+      <c r="AB9" s="396" t="n"/>
+      <c r="AC9" s="396" t="n"/>
+      <c r="AD9" s="396" t="n"/>
+      <c r="AE9" s="396" t="n"/>
+      <c r="AF9" s="396" t="n"/>
+      <c r="AG9" s="396" t="n"/>
+      <c r="AH9" s="396" t="n"/>
+      <c r="AI9" s="396" t="n"/>
+      <c r="AJ9" s="396" t="n"/>
+      <c r="AK9" s="396" t="n"/>
+      <c r="AL9" s="396" t="n"/>
+      <c r="AM9" s="396" t="n"/>
+      <c r="AN9" s="396" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="319" t="inlineStr">
+      <c r="A10" s="394" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-002</t>
         </is>
       </c>
-      <c r="B10" s="320" t="inlineStr">
+      <c r="B10" s="395" t="inlineStr">
         <is>
           <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
         </is>
       </c>
-      <c r="C10" s="320" t="inlineStr">
+      <c r="C10" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
         </is>
       </c>
+      <c r="D10" s="396" t="n"/>
+      <c r="E10" s="396" t="n"/>
+      <c r="F10" s="396" t="n"/>
+      <c r="G10" s="396" t="n"/>
+      <c r="H10" s="396" t="n"/>
+      <c r="I10" s="396" t="n"/>
+      <c r="J10" s="396" t="n"/>
+      <c r="K10" s="396" t="n"/>
+      <c r="L10" s="396" t="n"/>
+      <c r="M10" s="396" t="n"/>
+      <c r="N10" s="396" t="n"/>
+      <c r="O10" s="396" t="n"/>
+      <c r="P10" s="396" t="n"/>
+      <c r="Q10" s="396" t="n"/>
+      <c r="R10" s="396" t="n"/>
+      <c r="S10" s="396" t="n"/>
+      <c r="T10" s="396" t="n"/>
+      <c r="U10" s="396" t="n"/>
+      <c r="V10" s="396" t="n"/>
+      <c r="W10" s="396" t="n"/>
+      <c r="X10" s="396" t="n"/>
+      <c r="Y10" s="396" t="n"/>
+      <c r="Z10" s="396" t="n"/>
+      <c r="AA10" s="396" t="n"/>
+      <c r="AB10" s="396" t="n"/>
+      <c r="AC10" s="396" t="n"/>
+      <c r="AD10" s="396" t="n"/>
+      <c r="AE10" s="396" t="n"/>
+      <c r="AF10" s="396" t="n"/>
+      <c r="AG10" s="396" t="n"/>
+      <c r="AH10" s="396" t="n"/>
+      <c r="AI10" s="396" t="n"/>
+      <c r="AJ10" s="396" t="n"/>
+      <c r="AK10" s="396" t="n"/>
+      <c r="AL10" s="396" t="n"/>
+      <c r="AM10" s="396" t="n"/>
+      <c r="AN10" s="396" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="319" t="inlineStr">
+      <c r="A11" s="394" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-003</t>
         </is>
       </c>
-      <c r="B11" s="320" t="inlineStr">
+      <c r="B11" s="395" t="inlineStr">
         <is>
           <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
         </is>
       </c>
-      <c r="C11" s="320" t="inlineStr">
+      <c r="C11" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
         </is>
       </c>
+      <c r="D11" s="396" t="n"/>
+      <c r="E11" s="396" t="n"/>
+      <c r="F11" s="396" t="n"/>
+      <c r="G11" s="396" t="n"/>
+      <c r="H11" s="396" t="n"/>
+      <c r="I11" s="396" t="n"/>
+      <c r="J11" s="396" t="n"/>
+      <c r="K11" s="396" t="n"/>
+      <c r="L11" s="396" t="n"/>
+      <c r="M11" s="396" t="n"/>
+      <c r="N11" s="396" t="n"/>
+      <c r="O11" s="396" t="n"/>
+      <c r="P11" s="396" t="n"/>
+      <c r="Q11" s="396" t="n"/>
+      <c r="R11" s="396" t="n"/>
+      <c r="S11" s="396" t="n"/>
+      <c r="T11" s="396" t="n"/>
+      <c r="U11" s="396" t="n"/>
+      <c r="V11" s="396" t="n"/>
+      <c r="W11" s="396" t="n"/>
+      <c r="X11" s="396" t="n"/>
+      <c r="Y11" s="396" t="n"/>
+      <c r="Z11" s="396" t="n"/>
+      <c r="AA11" s="396" t="n"/>
+      <c r="AB11" s="396" t="n"/>
+      <c r="AC11" s="396" t="n"/>
+      <c r="AD11" s="396" t="n"/>
+      <c r="AE11" s="396" t="n"/>
+      <c r="AF11" s="396" t="n"/>
+      <c r="AG11" s="396" t="n"/>
+      <c r="AH11" s="396" t="n"/>
+      <c r="AI11" s="396" t="n"/>
+      <c r="AJ11" s="396" t="n"/>
+      <c r="AK11" s="396" t="n"/>
+      <c r="AL11" s="396" t="n"/>
+      <c r="AM11" s="396" t="n"/>
+      <c r="AN11" s="396" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="319" t="inlineStr">
+      <c r="A12" s="394" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-004</t>
         </is>
       </c>
-      <c r="B12" s="320" t="inlineStr">
+      <c r="B12" s="395" t="inlineStr">
         <is>
           <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
         </is>
       </c>
-      <c r="C12" s="320" t="inlineStr">
+      <c r="C12" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
         </is>
       </c>
+      <c r="D12" s="396" t="n"/>
+      <c r="E12" s="396" t="n"/>
+      <c r="F12" s="396" t="n"/>
+      <c r="G12" s="396" t="n"/>
+      <c r="H12" s="396" t="n"/>
+      <c r="I12" s="396" t="n"/>
+      <c r="J12" s="396" t="n"/>
+      <c r="K12" s="396" t="n"/>
+      <c r="L12" s="396" t="n"/>
+      <c r="M12" s="396" t="n"/>
+      <c r="N12" s="396" t="n"/>
+      <c r="O12" s="396" t="n"/>
+      <c r="P12" s="396" t="n"/>
+      <c r="Q12" s="396" t="n"/>
+      <c r="R12" s="396" t="n"/>
+      <c r="S12" s="396" t="n"/>
+      <c r="T12" s="396" t="n"/>
+      <c r="U12" s="396" t="n"/>
+      <c r="V12" s="396" t="n"/>
+      <c r="W12" s="396" t="n"/>
+      <c r="X12" s="396" t="n"/>
+      <c r="Y12" s="396" t="n"/>
+      <c r="Z12" s="396" t="n"/>
+      <c r="AA12" s="396" t="n"/>
+      <c r="AB12" s="396" t="n"/>
+      <c r="AC12" s="396" t="n"/>
+      <c r="AD12" s="396" t="n"/>
+      <c r="AE12" s="396" t="n"/>
+      <c r="AF12" s="396" t="n"/>
+      <c r="AG12" s="396" t="n"/>
+      <c r="AH12" s="396" t="n"/>
+      <c r="AI12" s="396" t="n"/>
+      <c r="AJ12" s="396" t="n"/>
+      <c r="AK12" s="396" t="n"/>
+      <c r="AL12" s="396" t="n"/>
+      <c r="AM12" s="396" t="n"/>
+      <c r="AN12" s="396" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="319" t="inlineStr">
+      <c r="A13" s="394" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-006</t>
         </is>
       </c>
-      <c r="B13" s="320" t="inlineStr">
+      <c r="B13" s="395" t="inlineStr">
         <is>
           <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
         </is>
       </c>
-      <c r="C13" s="320" t="inlineStr">
+      <c r="C13" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
         </is>
       </c>
+      <c r="D13" s="396" t="n"/>
+      <c r="E13" s="396" t="n"/>
+      <c r="F13" s="396" t="n"/>
+      <c r="G13" s="396" t="n"/>
+      <c r="H13" s="396" t="n"/>
+      <c r="I13" s="396" t="n"/>
+      <c r="J13" s="396" t="n"/>
+      <c r="K13" s="396" t="n"/>
+      <c r="L13" s="396" t="n"/>
+      <c r="M13" s="396" t="n"/>
+      <c r="N13" s="396" t="n"/>
+      <c r="O13" s="396" t="n"/>
+      <c r="P13" s="396" t="n"/>
+      <c r="Q13" s="396" t="n"/>
+      <c r="R13" s="396" t="n"/>
+      <c r="S13" s="396" t="n"/>
+      <c r="T13" s="396" t="n"/>
+      <c r="U13" s="396" t="n"/>
+      <c r="V13" s="396" t="n"/>
+      <c r="W13" s="396" t="n"/>
+      <c r="X13" s="396" t="n"/>
+      <c r="Y13" s="396" t="n"/>
+      <c r="Z13" s="396" t="n"/>
+      <c r="AA13" s="396" t="n"/>
+      <c r="AB13" s="396" t="n"/>
+      <c r="AC13" s="396" t="n"/>
+      <c r="AD13" s="396" t="n"/>
+      <c r="AE13" s="396" t="n"/>
+      <c r="AF13" s="396" t="n"/>
+      <c r="AG13" s="396" t="n"/>
+      <c r="AH13" s="396" t="n"/>
+      <c r="AI13" s="396" t="n"/>
+      <c r="AJ13" s="396" t="n"/>
+      <c r="AK13" s="396" t="n"/>
+      <c r="AL13" s="396" t="n"/>
+      <c r="AM13" s="396" t="n"/>
+      <c r="AN13" s="396" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="319" t="inlineStr">
+      <c r="A14" s="394" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B14" s="320" t="inlineStr">
+      <c r="B14" s="395" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C14" s="320" t="inlineStr">
+      <c r="C14" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
+      <c r="D14" s="396" t="n"/>
+      <c r="E14" s="396" t="n"/>
+      <c r="F14" s="396" t="n"/>
+      <c r="G14" s="396" t="n"/>
+      <c r="H14" s="396" t="n"/>
+      <c r="I14" s="396" t="n"/>
+      <c r="J14" s="396" t="n"/>
+      <c r="K14" s="396" t="n"/>
+      <c r="L14" s="396" t="n"/>
+      <c r="M14" s="396" t="n"/>
+      <c r="N14" s="396" t="n"/>
+      <c r="O14" s="396" t="n"/>
+      <c r="P14" s="396" t="n"/>
+      <c r="Q14" s="396" t="n"/>
+      <c r="R14" s="396" t="n"/>
+      <c r="S14" s="396" t="n"/>
+      <c r="T14" s="396" t="n"/>
+      <c r="U14" s="396" t="n"/>
+      <c r="V14" s="396" t="n"/>
+      <c r="W14" s="396" t="n"/>
+      <c r="X14" s="396" t="n"/>
+      <c r="Y14" s="396" t="n"/>
+      <c r="Z14" s="396" t="n"/>
+      <c r="AA14" s="396" t="n"/>
+      <c r="AB14" s="396" t="n"/>
+      <c r="AC14" s="396" t="n"/>
+      <c r="AD14" s="396" t="n"/>
+      <c r="AE14" s="396" t="n"/>
+      <c r="AF14" s="396" t="n"/>
+      <c r="AG14" s="396" t="n"/>
+      <c r="AH14" s="396" t="n"/>
+      <c r="AI14" s="396" t="n"/>
+      <c r="AJ14" s="396" t="n"/>
+      <c r="AK14" s="396" t="n"/>
+      <c r="AL14" s="396" t="n"/>
+      <c r="AM14" s="396" t="n"/>
+      <c r="AN14" s="396" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="319" t="inlineStr">
+      <c r="A15" s="394" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QMS-020</t>
         </is>
       </c>
-      <c r="B15" s="320" t="inlineStr">
+      <c r="B15" s="395" t="inlineStr">
         <is>
           <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
         </is>
       </c>
-      <c r="C15" s="320" t="inlineStr">
+      <c r="C15" s="395" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
         </is>
       </c>
+      <c r="D15" s="396" t="n"/>
+      <c r="E15" s="396" t="n"/>
+      <c r="F15" s="396" t="n"/>
+      <c r="G15" s="396" t="n"/>
+      <c r="H15" s="396" t="n"/>
+      <c r="I15" s="396" t="n"/>
+      <c r="J15" s="396" t="n"/>
+      <c r="K15" s="396" t="n"/>
+      <c r="L15" s="396" t="n"/>
+      <c r="M15" s="396" t="n"/>
+      <c r="N15" s="396" t="n"/>
+      <c r="O15" s="396" t="n"/>
+      <c r="P15" s="396" t="n"/>
+      <c r="Q15" s="396" t="n"/>
+      <c r="R15" s="396" t="n"/>
+      <c r="S15" s="396" t="n"/>
+      <c r="T15" s="396" t="n"/>
+      <c r="U15" s="396" t="n"/>
+      <c r="V15" s="396" t="n"/>
+      <c r="W15" s="396" t="n"/>
+      <c r="X15" s="396" t="n"/>
+      <c r="Y15" s="396" t="n"/>
+      <c r="Z15" s="396" t="n"/>
+      <c r="AA15" s="396" t="n"/>
+      <c r="AB15" s="396" t="n"/>
+      <c r="AC15" s="396" t="n"/>
+      <c r="AD15" s="396" t="n"/>
+      <c r="AE15" s="396" t="n"/>
+      <c r="AF15" s="396" t="n"/>
+      <c r="AG15" s="396" t="n"/>
+      <c r="AH15" s="396" t="n"/>
+      <c r="AI15" s="396" t="n"/>
+      <c r="AJ15" s="396" t="n"/>
+      <c r="AK15" s="396" t="n"/>
+      <c r="AL15" s="396" t="n"/>
+      <c r="AM15" s="396" t="n"/>
+      <c r="AN15" s="396" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -7712,7 +9654,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7722,30 +9665,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="316" t="inlineStr">
+      <c r="A1" s="391" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="420" t="n"/>
+      <c r="C1" s="420" t="n"/>
+      <c r="D1" s="420" t="n"/>
+      <c r="E1" s="420" t="n"/>
+      <c r="F1" s="420" t="n"/>
+      <c r="G1" s="421" t="n"/>
+      <c r="H1" s="346" t="n"/>
+      <c r="I1" s="346" t="n"/>
+      <c r="J1" s="346" t="n"/>
+      <c r="K1" s="346" t="n"/>
+      <c r="L1" s="346" t="n"/>
+      <c r="M1" s="346" t="n"/>
+      <c r="N1" s="346" t="n"/>
+      <c r="O1" s="346" t="n"/>
+      <c r="P1" s="346" t="n"/>
+      <c r="Q1" s="346" t="n"/>
+      <c r="R1" s="346" t="n"/>
+      <c r="S1" s="346" t="n"/>
+      <c r="T1" s="346" t="n"/>
+      <c r="U1" s="346" t="n"/>
+      <c r="V1" s="346" t="n"/>
+      <c r="W1" s="346" t="n"/>
+      <c r="X1" s="346" t="n"/>
+      <c r="Y1" s="346" t="n"/>
+      <c r="Z1" s="346" t="n"/>
+      <c r="AA1" s="346" t="n"/>
+      <c r="AB1" s="346" t="n"/>
+      <c r="AC1" s="346" t="n"/>
+      <c r="AD1" s="346" t="n"/>
+      <c r="AE1" s="346" t="n"/>
+      <c r="AF1" s="346" t="n"/>
+      <c r="AG1" s="346" t="n"/>
+      <c r="AH1" s="346" t="n"/>
+      <c r="AI1" s="346" t="n"/>
+      <c r="AJ1" s="346" t="n"/>
+      <c r="AK1" s="346" t="n"/>
+      <c r="AL1" s="346" t="n"/>
+      <c r="AM1" s="346" t="n"/>
+      <c r="AN1" s="346" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="317" t="inlineStr">
@@ -7753,92 +9762,351 @@
           <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
         </is>
       </c>
+      <c r="H2" s="346" t="n"/>
+      <c r="I2" s="346" t="n"/>
+      <c r="J2" s="346" t="n"/>
+      <c r="K2" s="346" t="n"/>
+      <c r="L2" s="346" t="n"/>
+      <c r="M2" s="346" t="n"/>
+      <c r="N2" s="346" t="n"/>
+      <c r="O2" s="346" t="n"/>
+      <c r="P2" s="346" t="n"/>
+      <c r="Q2" s="346" t="n"/>
+      <c r="R2" s="346" t="n"/>
+      <c r="S2" s="346" t="n"/>
+      <c r="T2" s="346" t="n"/>
+      <c r="U2" s="346" t="n"/>
+      <c r="V2" s="346" t="n"/>
+      <c r="W2" s="346" t="n"/>
+      <c r="X2" s="346" t="n"/>
+      <c r="Y2" s="346" t="n"/>
+      <c r="Z2" s="346" t="n"/>
+      <c r="AA2" s="346" t="n"/>
+      <c r="AB2" s="346" t="n"/>
+      <c r="AC2" s="346" t="n"/>
+      <c r="AD2" s="346" t="n"/>
+      <c r="AE2" s="346" t="n"/>
+      <c r="AF2" s="346" t="n"/>
+      <c r="AG2" s="346" t="n"/>
+      <c r="AH2" s="346" t="n"/>
+      <c r="AI2" s="346" t="n"/>
+      <c r="AJ2" s="346" t="n"/>
+      <c r="AK2" s="346" t="n"/>
+      <c r="AL2" s="346" t="n"/>
+      <c r="AM2" s="346" t="n"/>
+      <c r="AN2" s="346" t="n"/>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="346" t="n"/>
+      <c r="B3" s="346" t="n"/>
+      <c r="C3" s="346" t="n"/>
+      <c r="D3" s="346" t="n"/>
+      <c r="E3" s="346" t="n"/>
+      <c r="F3" s="346" t="n"/>
+      <c r="G3" s="346" t="n"/>
+      <c r="H3" s="346" t="n"/>
+      <c r="I3" s="346" t="n"/>
+      <c r="J3" s="346" t="n"/>
+      <c r="K3" s="346" t="n"/>
+      <c r="L3" s="346" t="n"/>
+      <c r="M3" s="346" t="n"/>
+      <c r="N3" s="346" t="n"/>
+      <c r="O3" s="346" t="n"/>
+      <c r="P3" s="346" t="n"/>
+      <c r="Q3" s="346" t="n"/>
+      <c r="R3" s="346" t="n"/>
+      <c r="S3" s="346" t="n"/>
+      <c r="T3" s="346" t="n"/>
+      <c r="U3" s="346" t="n"/>
+      <c r="V3" s="346" t="n"/>
+      <c r="W3" s="346" t="n"/>
+      <c r="X3" s="346" t="n"/>
+      <c r="Y3" s="346" t="n"/>
+      <c r="Z3" s="346" t="n"/>
+      <c r="AA3" s="346" t="n"/>
+      <c r="AB3" s="346" t="n"/>
+      <c r="AC3" s="346" t="n"/>
+      <c r="AD3" s="346" t="n"/>
+      <c r="AE3" s="346" t="n"/>
+      <c r="AF3" s="346" t="n"/>
+      <c r="AG3" s="346" t="n"/>
+      <c r="AH3" s="346" t="n"/>
+      <c r="AI3" s="346" t="n"/>
+      <c r="AJ3" s="346" t="n"/>
+      <c r="AK3" s="346" t="n"/>
+      <c r="AL3" s="346" t="n"/>
+      <c r="AM3" s="346" t="n"/>
+      <c r="AN3" s="346" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="318" t="inlineStr">
+      <c r="A4" s="362" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="318" t="inlineStr">
+      <c r="B4" s="362" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="318" t="inlineStr">
+      <c r="C4" s="362" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="346" t="n"/>
+      <c r="E4" s="346" t="n"/>
+      <c r="F4" s="346" t="n"/>
+      <c r="G4" s="346" t="n"/>
+      <c r="H4" s="346" t="n"/>
+      <c r="I4" s="346" t="n"/>
+      <c r="J4" s="346" t="n"/>
+      <c r="K4" s="346" t="n"/>
+      <c r="L4" s="346" t="n"/>
+      <c r="M4" s="346" t="n"/>
+      <c r="N4" s="346" t="n"/>
+      <c r="O4" s="346" t="n"/>
+      <c r="P4" s="346" t="n"/>
+      <c r="Q4" s="346" t="n"/>
+      <c r="R4" s="346" t="n"/>
+      <c r="S4" s="346" t="n"/>
+      <c r="T4" s="346" t="n"/>
+      <c r="U4" s="346" t="n"/>
+      <c r="V4" s="346" t="n"/>
+      <c r="W4" s="346" t="n"/>
+      <c r="X4" s="346" t="n"/>
+      <c r="Y4" s="346" t="n"/>
+      <c r="Z4" s="346" t="n"/>
+      <c r="AA4" s="346" t="n"/>
+      <c r="AB4" s="346" t="n"/>
+      <c r="AC4" s="346" t="n"/>
+      <c r="AD4" s="346" t="n"/>
+      <c r="AE4" s="346" t="n"/>
+      <c r="AF4" s="346" t="n"/>
+      <c r="AG4" s="346" t="n"/>
+      <c r="AH4" s="346" t="n"/>
+      <c r="AI4" s="346" t="n"/>
+      <c r="AJ4" s="346" t="n"/>
+      <c r="AK4" s="346" t="n"/>
+      <c r="AL4" s="346" t="n"/>
+      <c r="AM4" s="346" t="n"/>
+      <c r="AN4" s="346" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="319" t="inlineStr">
+      <c r="A5" s="392" t="inlineStr">
         <is>
           <t>Evidence item 1</t>
         </is>
       </c>
-      <c r="B5" s="320" t="inlineStr">
+      <c r="B5" s="393" t="inlineStr">
         <is>
           <t>Reference to the correct evidence folder, shared location or dossier package.</t>
         </is>
       </c>
-      <c r="C5" s="320" t="inlineStr">
+      <c r="C5" s="393" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
+      <c r="D5" s="346" t="n"/>
+      <c r="E5" s="346" t="n"/>
+      <c r="F5" s="346" t="n"/>
+      <c r="G5" s="346" t="n"/>
+      <c r="H5" s="346" t="n"/>
+      <c r="I5" s="346" t="n"/>
+      <c r="J5" s="346" t="n"/>
+      <c r="K5" s="346" t="n"/>
+      <c r="L5" s="346" t="n"/>
+      <c r="M5" s="346" t="n"/>
+      <c r="N5" s="346" t="n"/>
+      <c r="O5" s="346" t="n"/>
+      <c r="P5" s="346" t="n"/>
+      <c r="Q5" s="346" t="n"/>
+      <c r="R5" s="346" t="n"/>
+      <c r="S5" s="346" t="n"/>
+      <c r="T5" s="346" t="n"/>
+      <c r="U5" s="346" t="n"/>
+      <c r="V5" s="346" t="n"/>
+      <c r="W5" s="346" t="n"/>
+      <c r="X5" s="346" t="n"/>
+      <c r="Y5" s="346" t="n"/>
+      <c r="Z5" s="346" t="n"/>
+      <c r="AA5" s="346" t="n"/>
+      <c r="AB5" s="346" t="n"/>
+      <c r="AC5" s="346" t="n"/>
+      <c r="AD5" s="346" t="n"/>
+      <c r="AE5" s="346" t="n"/>
+      <c r="AF5" s="346" t="n"/>
+      <c r="AG5" s="346" t="n"/>
+      <c r="AH5" s="346" t="n"/>
+      <c r="AI5" s="346" t="n"/>
+      <c r="AJ5" s="346" t="n"/>
+      <c r="AK5" s="346" t="n"/>
+      <c r="AL5" s="346" t="n"/>
+      <c r="AM5" s="346" t="n"/>
+      <c r="AN5" s="346" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="319" t="inlineStr">
+      <c r="A6" s="392" t="inlineStr">
         <is>
           <t>Evidence item 2</t>
         </is>
       </c>
-      <c r="B6" s="320" t="inlineStr">
+      <c r="B6" s="393" t="inlineStr">
         <is>
           <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
         </is>
       </c>
-      <c r="C6" s="320" t="inlineStr">
+      <c r="C6" s="393" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
+      <c r="D6" s="346" t="n"/>
+      <c r="E6" s="346" t="n"/>
+      <c r="F6" s="346" t="n"/>
+      <c r="G6" s="346" t="n"/>
+      <c r="H6" s="346" t="n"/>
+      <c r="I6" s="346" t="n"/>
+      <c r="J6" s="346" t="n"/>
+      <c r="K6" s="346" t="n"/>
+      <c r="L6" s="346" t="n"/>
+      <c r="M6" s="346" t="n"/>
+      <c r="N6" s="346" t="n"/>
+      <c r="O6" s="346" t="n"/>
+      <c r="P6" s="346" t="n"/>
+      <c r="Q6" s="346" t="n"/>
+      <c r="R6" s="346" t="n"/>
+      <c r="S6" s="346" t="n"/>
+      <c r="T6" s="346" t="n"/>
+      <c r="U6" s="346" t="n"/>
+      <c r="V6" s="346" t="n"/>
+      <c r="W6" s="346" t="n"/>
+      <c r="X6" s="346" t="n"/>
+      <c r="Y6" s="346" t="n"/>
+      <c r="Z6" s="346" t="n"/>
+      <c r="AA6" s="346" t="n"/>
+      <c r="AB6" s="346" t="n"/>
+      <c r="AC6" s="346" t="n"/>
+      <c r="AD6" s="346" t="n"/>
+      <c r="AE6" s="346" t="n"/>
+      <c r="AF6" s="346" t="n"/>
+      <c r="AG6" s="346" t="n"/>
+      <c r="AH6" s="346" t="n"/>
+      <c r="AI6" s="346" t="n"/>
+      <c r="AJ6" s="346" t="n"/>
+      <c r="AK6" s="346" t="n"/>
+      <c r="AL6" s="346" t="n"/>
+      <c r="AM6" s="346" t="n"/>
+      <c r="AN6" s="346" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="319" t="inlineStr">
+      <c r="A7" s="392" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B7" s="320" t="inlineStr">
+      <c r="B7" s="393" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C7" s="320" t="inlineStr">
+      <c r="C7" s="393" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D7" s="346" t="n"/>
+      <c r="E7" s="346" t="n"/>
+      <c r="F7" s="346" t="n"/>
+      <c r="G7" s="346" t="n"/>
+      <c r="H7" s="346" t="n"/>
+      <c r="I7" s="346" t="n"/>
+      <c r="J7" s="346" t="n"/>
+      <c r="K7" s="346" t="n"/>
+      <c r="L7" s="346" t="n"/>
+      <c r="M7" s="346" t="n"/>
+      <c r="N7" s="346" t="n"/>
+      <c r="O7" s="346" t="n"/>
+      <c r="P7" s="346" t="n"/>
+      <c r="Q7" s="346" t="n"/>
+      <c r="R7" s="346" t="n"/>
+      <c r="S7" s="346" t="n"/>
+      <c r="T7" s="346" t="n"/>
+      <c r="U7" s="346" t="n"/>
+      <c r="V7" s="346" t="n"/>
+      <c r="W7" s="346" t="n"/>
+      <c r="X7" s="346" t="n"/>
+      <c r="Y7" s="346" t="n"/>
+      <c r="Z7" s="346" t="n"/>
+      <c r="AA7" s="346" t="n"/>
+      <c r="AB7" s="346" t="n"/>
+      <c r="AC7" s="346" t="n"/>
+      <c r="AD7" s="346" t="n"/>
+      <c r="AE7" s="346" t="n"/>
+      <c r="AF7" s="346" t="n"/>
+      <c r="AG7" s="346" t="n"/>
+      <c r="AH7" s="346" t="n"/>
+      <c r="AI7" s="346" t="n"/>
+      <c r="AJ7" s="346" t="n"/>
+      <c r="AK7" s="346" t="n"/>
+      <c r="AL7" s="346" t="n"/>
+      <c r="AM7" s="346" t="n"/>
+      <c r="AN7" s="346" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="319" t="inlineStr">
+      <c r="A8" s="394" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B8" s="320" t="inlineStr">
+      <c r="B8" s="395" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C8" s="320" t="inlineStr">
+      <c r="C8" s="395" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D8" s="396" t="n"/>
+      <c r="E8" s="396" t="n"/>
+      <c r="F8" s="396" t="n"/>
+      <c r="G8" s="396" t="n"/>
+      <c r="H8" s="396" t="n"/>
+      <c r="I8" s="396" t="n"/>
+      <c r="J8" s="396" t="n"/>
+      <c r="K8" s="396" t="n"/>
+      <c r="L8" s="396" t="n"/>
+      <c r="M8" s="396" t="n"/>
+      <c r="N8" s="396" t="n"/>
+      <c r="O8" s="396" t="n"/>
+      <c r="P8" s="396" t="n"/>
+      <c r="Q8" s="396" t="n"/>
+      <c r="R8" s="396" t="n"/>
+      <c r="S8" s="396" t="n"/>
+      <c r="T8" s="396" t="n"/>
+      <c r="U8" s="396" t="n"/>
+      <c r="V8" s="396" t="n"/>
+      <c r="W8" s="396" t="n"/>
+      <c r="X8" s="396" t="n"/>
+      <c r="Y8" s="396" t="n"/>
+      <c r="Z8" s="396" t="n"/>
+      <c r="AA8" s="396" t="n"/>
+      <c r="AB8" s="396" t="n"/>
+      <c r="AC8" s="396" t="n"/>
+      <c r="AD8" s="396" t="n"/>
+      <c r="AE8" s="396" t="n"/>
+      <c r="AF8" s="396" t="n"/>
+      <c r="AG8" s="396" t="n"/>
+      <c r="AH8" s="396" t="n"/>
+      <c r="AI8" s="396" t="n"/>
+      <c r="AJ8" s="396" t="n"/>
+      <c r="AK8" s="396" t="n"/>
+      <c r="AL8" s="396" t="n"/>
+      <c r="AM8" s="396" t="n"/>
+      <c r="AN8" s="396" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -7847,6 +10115,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="79">
+  <fonts count="84">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -474,8 +474,35 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00BBCCCC"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -707,8 +734,33 @@
         <fgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="293">
+  <borders count="321">
     <border>
       <left/>
       <right/>
@@ -3842,12 +3894,308 @@
         <color rgb="00C5D9E8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="425">
+  <cellXfs count="538">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4864,6 +5212,326 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="315" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="317" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="319" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="307" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="310" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="318" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="318" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="272" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="306" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="309" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="304" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="315" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4938,6 +5606,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5307,708 +6095,798 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="338" t="inlineStr"/>
-      <c r="B1" s="419" t="n"/>
-      <c r="C1" s="419" t="n"/>
-      <c r="D1" s="419" t="n"/>
-      <c r="E1" s="419" t="n"/>
-      <c r="F1" s="419" t="n"/>
-      <c r="G1" s="419" t="n"/>
-      <c r="H1" s="419" t="n"/>
-      <c r="I1" s="419" t="n"/>
-      <c r="J1" s="419" t="n"/>
-      <c r="K1" s="419" t="n"/>
-      <c r="L1" s="340" t="inlineStr">
+      <c r="A1" s="425" t="inlineStr"/>
+      <c r="B1" s="426" t="n"/>
+      <c r="C1" s="426" t="n"/>
+      <c r="D1" s="426" t="n"/>
+      <c r="E1" s="426" t="n"/>
+      <c r="F1" s="426" t="n"/>
+      <c r="G1" s="426" t="n"/>
+      <c r="H1" s="426" t="n"/>
+      <c r="I1" s="426" t="n"/>
+      <c r="J1" s="426" t="n"/>
+      <c r="K1" s="427" t="n"/>
+      <c r="L1" s="428" t="inlineStr">
         <is>
           <t>Final Inspection Report</t>
         </is>
       </c>
-      <c r="M1" s="419" t="n"/>
-      <c r="N1" s="419" t="n"/>
-      <c r="O1" s="419" t="n"/>
-      <c r="P1" s="419" t="n"/>
-      <c r="Q1" s="419" t="n"/>
-      <c r="R1" s="419" t="n"/>
-      <c r="S1" s="419" t="n"/>
-      <c r="T1" s="419" t="n"/>
-      <c r="U1" s="419" t="n"/>
-      <c r="V1" s="419" t="n"/>
-      <c r="W1" s="419" t="n"/>
-      <c r="X1" s="419" t="n"/>
-      <c r="Y1" s="419" t="n"/>
-      <c r="Z1" s="419" t="n"/>
-      <c r="AA1" s="419" t="n"/>
-      <c r="AB1" s="419" t="n"/>
-      <c r="AC1" s="419" t="n"/>
-      <c r="AD1" s="419" t="n"/>
-      <c r="AE1" s="419" t="n"/>
-      <c r="AF1" s="419" t="n"/>
-      <c r="AG1" s="419" t="n"/>
-      <c r="AH1" s="419" t="n"/>
-      <c r="AI1" s="419" t="n"/>
-      <c r="AJ1" s="419" t="n"/>
-      <c r="AK1" s="419" t="n"/>
-      <c r="AL1" s="419" t="n"/>
-      <c r="AM1" s="419" t="n"/>
-      <c r="AN1" s="419" t="n"/>
-      <c r="AO1" s="419" t="n"/>
-      <c r="AP1" s="419" t="n"/>
-      <c r="AQ1" s="341" t="inlineStr">
+      <c r="M1" s="429" t="n"/>
+      <c r="N1" s="429" t="n"/>
+      <c r="O1" s="429" t="n"/>
+      <c r="P1" s="429" t="n"/>
+      <c r="Q1" s="429" t="n"/>
+      <c r="R1" s="429" t="n"/>
+      <c r="S1" s="429" t="n"/>
+      <c r="T1" s="429" t="n"/>
+      <c r="U1" s="429" t="n"/>
+      <c r="V1" s="429" t="n"/>
+      <c r="W1" s="429" t="n"/>
+      <c r="X1" s="429" t="n"/>
+      <c r="Y1" s="429" t="n"/>
+      <c r="Z1" s="429" t="n"/>
+      <c r="AA1" s="429" t="n"/>
+      <c r="AB1" s="429" t="n"/>
+      <c r="AC1" s="429" t="n"/>
+      <c r="AD1" s="429" t="n"/>
+      <c r="AE1" s="429" t="n"/>
+      <c r="AF1" s="429" t="n"/>
+      <c r="AG1" s="429" t="n"/>
+      <c r="AH1" s="429" t="n"/>
+      <c r="AI1" s="429" t="n"/>
+      <c r="AJ1" s="429" t="n"/>
+      <c r="AK1" s="429" t="n"/>
+      <c r="AL1" s="429" t="n"/>
+      <c r="AM1" s="429" t="n"/>
+      <c r="AN1" s="429" t="n"/>
+      <c r="AO1" s="429" t="n"/>
+      <c r="AP1" s="430" t="n"/>
+      <c r="AQ1" s="431" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="420" t="n"/>
-      <c r="AS1" s="420" t="n"/>
-      <c r="AT1" s="420" t="n"/>
-      <c r="AU1" s="420" t="n"/>
-      <c r="AV1" s="421" t="n"/>
-      <c r="AW1" s="344" t="inlineStr">
+      <c r="AR1" s="432" t="n"/>
+      <c r="AS1" s="432" t="n"/>
+      <c r="AT1" s="432" t="n"/>
+      <c r="AU1" s="432" t="n"/>
+      <c r="AV1" s="433" t="n"/>
+      <c r="AW1" s="434" t="inlineStr">
         <is>
           <t>FRM-641</t>
         </is>
       </c>
-      <c r="AX1" s="420" t="n"/>
-      <c r="AY1" s="420" t="n"/>
-      <c r="AZ1" s="420" t="n"/>
-      <c r="BA1" s="420" t="n"/>
-      <c r="BB1" s="420" t="n"/>
-      <c r="BC1" s="420" t="n"/>
-      <c r="BD1" s="421" t="n"/>
+      <c r="AX1" s="435" t="n"/>
+      <c r="AY1" s="435" t="n"/>
+      <c r="AZ1" s="435" t="n"/>
+      <c r="BA1" s="435" t="n"/>
+      <c r="BB1" s="435" t="n"/>
+      <c r="BC1" s="435" t="n"/>
+      <c r="BD1" s="436" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="422" t="n"/>
-      <c r="L2" s="422" t="n"/>
-      <c r="AQ2" s="341" t="inlineStr">
+      <c r="A2" s="437" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="25" t="n"/>
+      <c r="I2" s="25" t="n"/>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="438" t="n"/>
+      <c r="L2" s="439" t="n"/>
+      <c r="M2" s="440" t="n"/>
+      <c r="N2" s="440" t="n"/>
+      <c r="O2" s="440" t="n"/>
+      <c r="P2" s="440" t="n"/>
+      <c r="Q2" s="440" t="n"/>
+      <c r="R2" s="440" t="n"/>
+      <c r="S2" s="440" t="n"/>
+      <c r="T2" s="440" t="n"/>
+      <c r="U2" s="440" t="n"/>
+      <c r="V2" s="440" t="n"/>
+      <c r="W2" s="440" t="n"/>
+      <c r="X2" s="440" t="n"/>
+      <c r="Y2" s="440" t="n"/>
+      <c r="Z2" s="440" t="n"/>
+      <c r="AA2" s="440" t="n"/>
+      <c r="AB2" s="440" t="n"/>
+      <c r="AC2" s="440" t="n"/>
+      <c r="AD2" s="440" t="n"/>
+      <c r="AE2" s="440" t="n"/>
+      <c r="AF2" s="440" t="n"/>
+      <c r="AG2" s="440" t="n"/>
+      <c r="AH2" s="440" t="n"/>
+      <c r="AI2" s="440" t="n"/>
+      <c r="AJ2" s="440" t="n"/>
+      <c r="AK2" s="440" t="n"/>
+      <c r="AL2" s="440" t="n"/>
+      <c r="AM2" s="440" t="n"/>
+      <c r="AN2" s="440" t="n"/>
+      <c r="AO2" s="440" t="n"/>
+      <c r="AP2" s="441" t="n"/>
+      <c r="AQ2" s="442" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="420" t="n"/>
-      <c r="AS2" s="420" t="n"/>
-      <c r="AT2" s="420" t="n"/>
-      <c r="AU2" s="420" t="n"/>
-      <c r="AV2" s="421" t="n"/>
-      <c r="AW2" s="344" t="inlineStr">
+      <c r="AR2" s="443" t="n"/>
+      <c r="AS2" s="443" t="n"/>
+      <c r="AT2" s="443" t="n"/>
+      <c r="AU2" s="443" t="n"/>
+      <c r="AV2" s="444" t="n"/>
+      <c r="AW2" s="445" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="420" t="n"/>
-      <c r="AY2" s="420" t="n"/>
-      <c r="AZ2" s="420" t="n"/>
-      <c r="BA2" s="420" t="n"/>
-      <c r="BB2" s="420" t="n"/>
-      <c r="BC2" s="420" t="n"/>
-      <c r="BD2" s="421" t="n"/>
+      <c r="AX2" s="446" t="n"/>
+      <c r="AY2" s="446" t="n"/>
+      <c r="AZ2" s="446" t="n"/>
+      <c r="BA2" s="446" t="n"/>
+      <c r="BB2" s="446" t="n"/>
+      <c r="BC2" s="446" t="n"/>
+      <c r="BD2" s="447" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="422" t="n"/>
-      <c r="L3" s="423" t="n"/>
-      <c r="M3" s="424" t="n"/>
-      <c r="N3" s="424" t="n"/>
-      <c r="O3" s="424" t="n"/>
-      <c r="P3" s="424" t="n"/>
-      <c r="Q3" s="424" t="n"/>
-      <c r="R3" s="424" t="n"/>
-      <c r="S3" s="424" t="n"/>
-      <c r="T3" s="424" t="n"/>
-      <c r="U3" s="424" t="n"/>
-      <c r="V3" s="424" t="n"/>
-      <c r="W3" s="424" t="n"/>
-      <c r="X3" s="424" t="n"/>
-      <c r="Y3" s="424" t="n"/>
-      <c r="Z3" s="424" t="n"/>
-      <c r="AA3" s="424" t="n"/>
-      <c r="AB3" s="424" t="n"/>
-      <c r="AC3" s="424" t="n"/>
-      <c r="AD3" s="424" t="n"/>
-      <c r="AE3" s="424" t="n"/>
-      <c r="AF3" s="424" t="n"/>
-      <c r="AG3" s="424" t="n"/>
-      <c r="AH3" s="424" t="n"/>
-      <c r="AI3" s="424" t="n"/>
-      <c r="AJ3" s="424" t="n"/>
-      <c r="AK3" s="424" t="n"/>
-      <c r="AL3" s="424" t="n"/>
-      <c r="AM3" s="424" t="n"/>
-      <c r="AN3" s="424" t="n"/>
-      <c r="AO3" s="424" t="n"/>
-      <c r="AP3" s="424" t="n"/>
-      <c r="AQ3" s="341" t="inlineStr">
+      <c r="A3" s="437" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="438" t="n"/>
+      <c r="L3" s="439" t="n"/>
+      <c r="M3" s="440" t="n"/>
+      <c r="N3" s="440" t="n"/>
+      <c r="O3" s="440" t="n"/>
+      <c r="P3" s="440" t="n"/>
+      <c r="Q3" s="440" t="n"/>
+      <c r="R3" s="440" t="n"/>
+      <c r="S3" s="440" t="n"/>
+      <c r="T3" s="440" t="n"/>
+      <c r="U3" s="440" t="n"/>
+      <c r="V3" s="440" t="n"/>
+      <c r="W3" s="440" t="n"/>
+      <c r="X3" s="440" t="n"/>
+      <c r="Y3" s="440" t="n"/>
+      <c r="Z3" s="440" t="n"/>
+      <c r="AA3" s="440" t="n"/>
+      <c r="AB3" s="440" t="n"/>
+      <c r="AC3" s="440" t="n"/>
+      <c r="AD3" s="440" t="n"/>
+      <c r="AE3" s="440" t="n"/>
+      <c r="AF3" s="440" t="n"/>
+      <c r="AG3" s="440" t="n"/>
+      <c r="AH3" s="440" t="n"/>
+      <c r="AI3" s="440" t="n"/>
+      <c r="AJ3" s="440" t="n"/>
+      <c r="AK3" s="440" t="n"/>
+      <c r="AL3" s="440" t="n"/>
+      <c r="AM3" s="440" t="n"/>
+      <c r="AN3" s="440" t="n"/>
+      <c r="AO3" s="440" t="n"/>
+      <c r="AP3" s="441" t="n"/>
+      <c r="AQ3" s="442" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="420" t="n"/>
-      <c r="AS3" s="420" t="n"/>
-      <c r="AT3" s="420" t="n"/>
-      <c r="AU3" s="420" t="n"/>
-      <c r="AV3" s="421" t="n"/>
-      <c r="AW3" s="344" t="inlineStr">
+      <c r="AR3" s="443" t="n"/>
+      <c r="AS3" s="443" t="n"/>
+      <c r="AT3" s="443" t="n"/>
+      <c r="AU3" s="443" t="n"/>
+      <c r="AV3" s="444" t="n"/>
+      <c r="AW3" s="445" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="420" t="n"/>
-      <c r="AY3" s="420" t="n"/>
-      <c r="AZ3" s="420" t="n"/>
-      <c r="BA3" s="420" t="n"/>
-      <c r="BB3" s="420" t="n"/>
-      <c r="BC3" s="420" t="n"/>
-      <c r="BD3" s="421" t="n"/>
+      <c r="AX3" s="446" t="n"/>
+      <c r="AY3" s="446" t="n"/>
+      <c r="AZ3" s="446" t="n"/>
+      <c r="BA3" s="446" t="n"/>
+      <c r="BB3" s="446" t="n"/>
+      <c r="BC3" s="446" t="n"/>
+      <c r="BD3" s="447" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="422" t="n"/>
-      <c r="L4" s="349" t="inlineStr">
+      <c r="A4" s="437" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="438" t="n"/>
+      <c r="L4" s="448" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="341" t="inlineStr">
+      <c r="M4" s="449" t="n"/>
+      <c r="N4" s="449" t="n"/>
+      <c r="O4" s="449" t="n"/>
+      <c r="P4" s="449" t="n"/>
+      <c r="Q4" s="449" t="n"/>
+      <c r="R4" s="449" t="n"/>
+      <c r="S4" s="449" t="n"/>
+      <c r="T4" s="449" t="n"/>
+      <c r="U4" s="449" t="n"/>
+      <c r="V4" s="449" t="n"/>
+      <c r="W4" s="449" t="n"/>
+      <c r="X4" s="449" t="n"/>
+      <c r="Y4" s="449" t="n"/>
+      <c r="Z4" s="449" t="n"/>
+      <c r="AA4" s="449" t="n"/>
+      <c r="AB4" s="449" t="n"/>
+      <c r="AC4" s="449" t="n"/>
+      <c r="AD4" s="449" t="n"/>
+      <c r="AE4" s="449" t="n"/>
+      <c r="AF4" s="449" t="n"/>
+      <c r="AG4" s="449" t="n"/>
+      <c r="AH4" s="449" t="n"/>
+      <c r="AI4" s="449" t="n"/>
+      <c r="AJ4" s="449" t="n"/>
+      <c r="AK4" s="449" t="n"/>
+      <c r="AL4" s="449" t="n"/>
+      <c r="AM4" s="449" t="n"/>
+      <c r="AN4" s="449" t="n"/>
+      <c r="AO4" s="449" t="n"/>
+      <c r="AP4" s="450" t="n"/>
+      <c r="AQ4" s="442" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="420" t="n"/>
-      <c r="AS4" s="420" t="n"/>
-      <c r="AT4" s="420" t="n"/>
-      <c r="AU4" s="420" t="n"/>
-      <c r="AV4" s="421" t="n"/>
-      <c r="AW4" s="344" t="inlineStr">
+      <c r="AR4" s="443" t="n"/>
+      <c r="AS4" s="443" t="n"/>
+      <c r="AT4" s="443" t="n"/>
+      <c r="AU4" s="443" t="n"/>
+      <c r="AV4" s="444" t="n"/>
+      <c r="AW4" s="445" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="420" t="n"/>
-      <c r="AY4" s="420" t="n"/>
-      <c r="AZ4" s="420" t="n"/>
-      <c r="BA4" s="420" t="n"/>
-      <c r="BB4" s="420" t="n"/>
-      <c r="BC4" s="420" t="n"/>
-      <c r="BD4" s="421" t="n"/>
+      <c r="AX4" s="446" t="n"/>
+      <c r="AY4" s="446" t="n"/>
+      <c r="AZ4" s="446" t="n"/>
+      <c r="BA4" s="446" t="n"/>
+      <c r="BB4" s="446" t="n"/>
+      <c r="BC4" s="446" t="n"/>
+      <c r="BD4" s="447" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="423" t="n"/>
-      <c r="B5" s="424" t="n"/>
-      <c r="C5" s="424" t="n"/>
-      <c r="D5" s="424" t="n"/>
-      <c r="E5" s="424" t="n"/>
-      <c r="F5" s="424" t="n"/>
-      <c r="G5" s="424" t="n"/>
-      <c r="H5" s="424" t="n"/>
-      <c r="I5" s="424" t="n"/>
-      <c r="J5" s="424" t="n"/>
-      <c r="K5" s="424" t="n"/>
-      <c r="L5" s="350" t="inlineStr">
+      <c r="A5" s="451" t="n"/>
+      <c r="B5" s="452" t="n"/>
+      <c r="C5" s="452" t="n"/>
+      <c r="D5" s="452" t="n"/>
+      <c r="E5" s="452" t="n"/>
+      <c r="F5" s="452" t="n"/>
+      <c r="G5" s="452" t="n"/>
+      <c r="H5" s="452" t="n"/>
+      <c r="I5" s="452" t="n"/>
+      <c r="J5" s="452" t="n"/>
+      <c r="K5" s="453" t="n"/>
+      <c r="L5" s="454" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="424" t="n"/>
-      <c r="N5" s="424" t="n"/>
-      <c r="O5" s="424" t="n"/>
-      <c r="P5" s="424" t="n"/>
-      <c r="Q5" s="424" t="n"/>
-      <c r="R5" s="424" t="n"/>
-      <c r="S5" s="424" t="n"/>
-      <c r="T5" s="424" t="n"/>
-      <c r="U5" s="424" t="n"/>
-      <c r="V5" s="424" t="n"/>
-      <c r="W5" s="424" t="n"/>
-      <c r="X5" s="424" t="n"/>
-      <c r="Y5" s="424" t="n"/>
-      <c r="Z5" s="424" t="n"/>
-      <c r="AA5" s="424" t="n"/>
-      <c r="AB5" s="424" t="n"/>
-      <c r="AC5" s="424" t="n"/>
-      <c r="AD5" s="424" t="n"/>
-      <c r="AE5" s="424" t="n"/>
-      <c r="AF5" s="424" t="n"/>
-      <c r="AG5" s="424" t="n"/>
-      <c r="AH5" s="424" t="n"/>
-      <c r="AI5" s="424" t="n"/>
-      <c r="AJ5" s="424" t="n"/>
-      <c r="AK5" s="424" t="n"/>
-      <c r="AL5" s="424" t="n"/>
-      <c r="AM5" s="424" t="n"/>
-      <c r="AN5" s="424" t="n"/>
-      <c r="AO5" s="424" t="n"/>
-      <c r="AP5" s="424" t="n"/>
-      <c r="AQ5" s="341" t="inlineStr">
+      <c r="M5" s="455" t="n"/>
+      <c r="N5" s="455" t="n"/>
+      <c r="O5" s="455" t="n"/>
+      <c r="P5" s="455" t="n"/>
+      <c r="Q5" s="455" t="n"/>
+      <c r="R5" s="455" t="n"/>
+      <c r="S5" s="455" t="n"/>
+      <c r="T5" s="455" t="n"/>
+      <c r="U5" s="455" t="n"/>
+      <c r="V5" s="455" t="n"/>
+      <c r="W5" s="455" t="n"/>
+      <c r="X5" s="455" t="n"/>
+      <c r="Y5" s="455" t="n"/>
+      <c r="Z5" s="455" t="n"/>
+      <c r="AA5" s="455" t="n"/>
+      <c r="AB5" s="455" t="n"/>
+      <c r="AC5" s="455" t="n"/>
+      <c r="AD5" s="455" t="n"/>
+      <c r="AE5" s="455" t="n"/>
+      <c r="AF5" s="455" t="n"/>
+      <c r="AG5" s="455" t="n"/>
+      <c r="AH5" s="455" t="n"/>
+      <c r="AI5" s="455" t="n"/>
+      <c r="AJ5" s="455" t="n"/>
+      <c r="AK5" s="455" t="n"/>
+      <c r="AL5" s="455" t="n"/>
+      <c r="AM5" s="455" t="n"/>
+      <c r="AN5" s="455" t="n"/>
+      <c r="AO5" s="455" t="n"/>
+      <c r="AP5" s="456" t="n"/>
+      <c r="AQ5" s="457" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="420" t="n"/>
-      <c r="AS5" s="420" t="n"/>
-      <c r="AT5" s="420" t="n"/>
-      <c r="AU5" s="420" t="n"/>
-      <c r="AV5" s="421" t="n"/>
-      <c r="AW5" s="344" t="inlineStr">
+      <c r="AR5" s="458" t="n"/>
+      <c r="AS5" s="458" t="n"/>
+      <c r="AT5" s="458" t="n"/>
+      <c r="AU5" s="458" t="n"/>
+      <c r="AV5" s="459" t="n"/>
+      <c r="AW5" s="460" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="420" t="n"/>
-      <c r="AY5" s="420" t="n"/>
-      <c r="AZ5" s="420" t="n"/>
-      <c r="BA5" s="420" t="n"/>
-      <c r="BB5" s="420" t="n"/>
-      <c r="BC5" s="420" t="n"/>
-      <c r="BD5" s="421" t="n"/>
+      <c r="AX5" s="461" t="n"/>
+      <c r="AY5" s="461" t="n"/>
+      <c r="AZ5" s="461" t="n"/>
+      <c r="BA5" s="461" t="n"/>
+      <c r="BB5" s="461" t="n"/>
+      <c r="BC5" s="461" t="n"/>
+      <c r="BD5" s="462" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="351" t="inlineStr"/>
-      <c r="B6" s="418" t="n"/>
-      <c r="C6" s="418" t="n"/>
-      <c r="D6" s="418" t="n"/>
-      <c r="E6" s="418" t="n"/>
-      <c r="F6" s="418" t="n"/>
-      <c r="G6" s="418" t="n"/>
-      <c r="H6" s="418" t="n"/>
-      <c r="I6" s="418" t="n"/>
-      <c r="J6" s="418" t="n"/>
-      <c r="K6" s="418" t="n"/>
-      <c r="L6" s="418" t="n"/>
-      <c r="M6" s="418" t="n"/>
-      <c r="N6" s="418" t="n"/>
-      <c r="O6" s="418" t="n"/>
-      <c r="P6" s="418" t="n"/>
-      <c r="Q6" s="418" t="n"/>
-      <c r="R6" s="418" t="n"/>
-      <c r="S6" s="418" t="n"/>
-      <c r="T6" s="418" t="n"/>
-      <c r="U6" s="418" t="n"/>
-      <c r="V6" s="418" t="n"/>
-      <c r="W6" s="418" t="n"/>
-      <c r="X6" s="418" t="n"/>
-      <c r="Y6" s="418" t="n"/>
-      <c r="Z6" s="418" t="n"/>
-      <c r="AA6" s="418" t="n"/>
-      <c r="AB6" s="418" t="n"/>
-      <c r="AC6" s="418" t="n"/>
-      <c r="AD6" s="418" t="n"/>
-      <c r="AE6" s="418" t="n"/>
-      <c r="AF6" s="418" t="n"/>
-      <c r="AG6" s="418" t="n"/>
-      <c r="AH6" s="418" t="n"/>
-      <c r="AI6" s="418" t="n"/>
-      <c r="AJ6" s="418" t="n"/>
-      <c r="AK6" s="418" t="n"/>
-      <c r="AL6" s="418" t="n"/>
-      <c r="AM6" s="418" t="n"/>
-      <c r="AN6" s="418" t="n"/>
-      <c r="AO6" s="418" t="n"/>
-      <c r="AP6" s="418" t="n"/>
-      <c r="AQ6" s="418" t="n"/>
-      <c r="AR6" s="418" t="n"/>
-      <c r="AS6" s="418" t="n"/>
-      <c r="AT6" s="418" t="n"/>
-      <c r="AU6" s="418" t="n"/>
-      <c r="AV6" s="418" t="n"/>
-      <c r="AW6" s="418" t="n"/>
-      <c r="AX6" s="418" t="n"/>
-      <c r="AY6" s="418" t="n"/>
-      <c r="AZ6" s="418" t="n"/>
-      <c r="BA6" s="418" t="n"/>
-      <c r="BB6" s="418" t="n"/>
-      <c r="BC6" s="418" t="n"/>
-      <c r="BD6" s="418" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="463" t="n"/>
+      <c r="B6" s="463" t="n"/>
+      <c r="C6" s="463" t="n"/>
+      <c r="D6" s="463" t="n"/>
+      <c r="E6" s="463" t="n"/>
+      <c r="F6" s="463" t="n"/>
+      <c r="G6" s="463" t="n"/>
+      <c r="H6" s="463" t="n"/>
+      <c r="I6" s="463" t="n"/>
+      <c r="J6" s="463" t="n"/>
+      <c r="K6" s="463" t="n"/>
+      <c r="L6" s="463" t="n"/>
+      <c r="M6" s="463" t="n"/>
+      <c r="N6" s="463" t="n"/>
+      <c r="O6" s="463" t="n"/>
+      <c r="P6" s="463" t="n"/>
+      <c r="Q6" s="463" t="n"/>
+      <c r="R6" s="463" t="n"/>
+      <c r="S6" s="463" t="n"/>
+      <c r="T6" s="463" t="n"/>
+      <c r="U6" s="463" t="n"/>
+      <c r="V6" s="463" t="n"/>
+      <c r="W6" s="463" t="n"/>
+      <c r="X6" s="463" t="n"/>
+      <c r="Y6" s="463" t="n"/>
+      <c r="Z6" s="463" t="n"/>
+      <c r="AA6" s="463" t="n"/>
+      <c r="AB6" s="463" t="n"/>
+      <c r="AC6" s="463" t="n"/>
+      <c r="AD6" s="463" t="n"/>
+      <c r="AE6" s="463" t="n"/>
+      <c r="AF6" s="463" t="n"/>
+      <c r="AG6" s="463" t="n"/>
+      <c r="AH6" s="463" t="n"/>
+      <c r="AI6" s="463" t="n"/>
+      <c r="AJ6" s="463" t="n"/>
+      <c r="AK6" s="463" t="n"/>
+      <c r="AL6" s="463" t="n"/>
+      <c r="AM6" s="463" t="n"/>
+      <c r="AN6" s="463" t="n"/>
+      <c r="AO6" s="463" t="n"/>
+      <c r="AP6" s="463" t="n"/>
+      <c r="AQ6" s="463" t="n"/>
+      <c r="AR6" s="463" t="n"/>
+      <c r="AS6" s="463" t="n"/>
+      <c r="AT6" s="463" t="n"/>
+      <c r="AU6" s="463" t="n"/>
+      <c r="AV6" s="463" t="n"/>
+      <c r="AW6" s="463" t="n"/>
+      <c r="AX6" s="463" t="n"/>
+      <c r="AY6" s="463" t="n"/>
+      <c r="AZ6" s="463" t="n"/>
+      <c r="BA6" s="463" t="n"/>
+      <c r="BB6" s="463" t="n"/>
+      <c r="BC6" s="463" t="n"/>
+      <c r="BD6" s="463" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="352" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="464" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="420" t="n"/>
-      <c r="C7" s="420" t="n"/>
-      <c r="D7" s="420" t="n"/>
-      <c r="E7" s="420" t="n"/>
-      <c r="F7" s="420" t="n"/>
-      <c r="G7" s="420" t="n"/>
-      <c r="H7" s="420" t="n"/>
-      <c r="I7" s="420" t="n"/>
-      <c r="J7" s="420" t="n"/>
-      <c r="K7" s="420" t="n"/>
-      <c r="L7" s="420" t="n"/>
-      <c r="M7" s="420" t="n"/>
-      <c r="N7" s="420" t="n"/>
-      <c r="O7" s="420" t="n"/>
-      <c r="P7" s="420" t="n"/>
-      <c r="Q7" s="420" t="n"/>
-      <c r="R7" s="420" t="n"/>
-      <c r="S7" s="420" t="n"/>
-      <c r="T7" s="420" t="n"/>
-      <c r="U7" s="420" t="n"/>
-      <c r="V7" s="420" t="n"/>
-      <c r="W7" s="420" t="n"/>
-      <c r="X7" s="420" t="n"/>
-      <c r="Y7" s="420" t="n"/>
-      <c r="Z7" s="420" t="n"/>
-      <c r="AA7" s="420" t="n"/>
-      <c r="AB7" s="420" t="n"/>
-      <c r="AC7" s="420" t="n"/>
-      <c r="AD7" s="420" t="n"/>
-      <c r="AE7" s="420" t="n"/>
-      <c r="AF7" s="420" t="n"/>
-      <c r="AG7" s="420" t="n"/>
-      <c r="AH7" s="420" t="n"/>
-      <c r="AI7" s="420" t="n"/>
-      <c r="AJ7" s="420" t="n"/>
-      <c r="AK7" s="420" t="n"/>
-      <c r="AL7" s="420" t="n"/>
-      <c r="AM7" s="420" t="n"/>
-      <c r="AN7" s="420" t="n"/>
-      <c r="AO7" s="420" t="n"/>
-      <c r="AP7" s="420" t="n"/>
-      <c r="AQ7" s="420" t="n"/>
-      <c r="AR7" s="420" t="n"/>
-      <c r="AS7" s="420" t="n"/>
-      <c r="AT7" s="420" t="n"/>
-      <c r="AU7" s="420" t="n"/>
-      <c r="AV7" s="420" t="n"/>
-      <c r="AW7" s="420" t="n"/>
-      <c r="AX7" s="420" t="n"/>
-      <c r="AY7" s="420" t="n"/>
-      <c r="AZ7" s="420" t="n"/>
-      <c r="BA7" s="420" t="n"/>
-      <c r="BB7" s="420" t="n"/>
-      <c r="BC7" s="420" t="n"/>
-      <c r="BD7" s="421" t="n"/>
+      <c r="B7" s="465" t="n"/>
+      <c r="C7" s="465" t="n"/>
+      <c r="D7" s="465" t="n"/>
+      <c r="E7" s="465" t="n"/>
+      <c r="F7" s="465" t="n"/>
+      <c r="G7" s="465" t="n"/>
+      <c r="H7" s="465" t="n"/>
+      <c r="I7" s="465" t="n"/>
+      <c r="J7" s="465" t="n"/>
+      <c r="K7" s="465" t="n"/>
+      <c r="L7" s="465" t="n"/>
+      <c r="M7" s="465" t="n"/>
+      <c r="N7" s="465" t="n"/>
+      <c r="O7" s="465" t="n"/>
+      <c r="P7" s="465" t="n"/>
+      <c r="Q7" s="465" t="n"/>
+      <c r="R7" s="465" t="n"/>
+      <c r="S7" s="465" t="n"/>
+      <c r="T7" s="465" t="n"/>
+      <c r="U7" s="465" t="n"/>
+      <c r="V7" s="465" t="n"/>
+      <c r="W7" s="465" t="n"/>
+      <c r="X7" s="465" t="n"/>
+      <c r="Y7" s="465" t="n"/>
+      <c r="Z7" s="465" t="n"/>
+      <c r="AA7" s="465" t="n"/>
+      <c r="AB7" s="465" t="n"/>
+      <c r="AC7" s="465" t="n"/>
+      <c r="AD7" s="465" t="n"/>
+      <c r="AE7" s="465" t="n"/>
+      <c r="AF7" s="465" t="n"/>
+      <c r="AG7" s="465" t="n"/>
+      <c r="AH7" s="465" t="n"/>
+      <c r="AI7" s="465" t="n"/>
+      <c r="AJ7" s="465" t="n"/>
+      <c r="AK7" s="465" t="n"/>
+      <c r="AL7" s="465" t="n"/>
+      <c r="AM7" s="465" t="n"/>
+      <c r="AN7" s="465" t="n"/>
+      <c r="AO7" s="465" t="n"/>
+      <c r="AP7" s="465" t="n"/>
+      <c r="AQ7" s="465" t="n"/>
+      <c r="AR7" s="465" t="n"/>
+      <c r="AS7" s="465" t="n"/>
+      <c r="AT7" s="465" t="n"/>
+      <c r="AU7" s="465" t="n"/>
+      <c r="AV7" s="465" t="n"/>
+      <c r="AW7" s="465" t="n"/>
+      <c r="AX7" s="465" t="n"/>
+      <c r="AY7" s="465" t="n"/>
+      <c r="AZ7" s="465" t="n"/>
+      <c r="BA7" s="465" t="n"/>
+      <c r="BB7" s="465" t="n"/>
+      <c r="BC7" s="465" t="n"/>
+      <c r="BD7" s="466" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="353" t="inlineStr">
+      <c r="A8" s="467" t="inlineStr">
         <is>
           <t>Final Inspection Report ID</t>
         </is>
       </c>
-      <c r="B8" s="403" t="n"/>
-      <c r="C8" s="403" t="n"/>
-      <c r="D8" s="403" t="n"/>
-      <c r="E8" s="403" t="n"/>
-      <c r="F8" s="403" t="n"/>
-      <c r="G8" s="403" t="n"/>
-      <c r="H8" s="403" t="n"/>
-      <c r="I8" s="403" t="n"/>
-      <c r="J8" s="404" t="n"/>
-      <c r="K8" s="356" t="n"/>
-      <c r="L8" s="405" t="n"/>
-      <c r="M8" s="405" t="n"/>
-      <c r="N8" s="405" t="n"/>
-      <c r="O8" s="405" t="n"/>
-      <c r="P8" s="405" t="n"/>
-      <c r="Q8" s="405" t="n"/>
-      <c r="R8" s="405" t="n"/>
-      <c r="S8" s="405" t="n"/>
-      <c r="T8" s="405" t="n"/>
-      <c r="U8" s="405" t="n"/>
-      <c r="V8" s="405" t="n"/>
-      <c r="W8" s="405" t="n"/>
-      <c r="X8" s="405" t="n"/>
-      <c r="Y8" s="405" t="n"/>
-      <c r="Z8" s="405" t="n"/>
-      <c r="AA8" s="405" t="n"/>
-      <c r="AB8" s="406" t="n"/>
-      <c r="AC8" s="359" t="inlineStr">
+      <c r="B8" s="468" t="n"/>
+      <c r="C8" s="468" t="n"/>
+      <c r="D8" s="468" t="n"/>
+      <c r="E8" s="468" t="n"/>
+      <c r="F8" s="468" t="n"/>
+      <c r="G8" s="468" t="n"/>
+      <c r="H8" s="468" t="n"/>
+      <c r="I8" s="468" t="n"/>
+      <c r="J8" s="468" t="n"/>
+      <c r="K8" s="469" t="n"/>
+      <c r="L8" s="470" t="n"/>
+      <c r="M8" s="470" t="n"/>
+      <c r="N8" s="470" t="n"/>
+      <c r="O8" s="470" t="n"/>
+      <c r="P8" s="470" t="n"/>
+      <c r="Q8" s="470" t="n"/>
+      <c r="R8" s="470" t="n"/>
+      <c r="S8" s="470" t="n"/>
+      <c r="T8" s="470" t="n"/>
+      <c r="U8" s="470" t="n"/>
+      <c r="V8" s="470" t="n"/>
+      <c r="W8" s="470" t="n"/>
+      <c r="X8" s="470" t="n"/>
+      <c r="Y8" s="470" t="n"/>
+      <c r="Z8" s="470" t="n"/>
+      <c r="AA8" s="470" t="n"/>
+      <c r="AB8" s="470" t="n"/>
+      <c r="AC8" s="471" t="inlineStr">
         <is>
           <t>Final Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="403" t="n"/>
-      <c r="AE8" s="403" t="n"/>
-      <c r="AF8" s="403" t="n"/>
-      <c r="AG8" s="403" t="n"/>
-      <c r="AH8" s="403" t="n"/>
-      <c r="AI8" s="403" t="n"/>
-      <c r="AJ8" s="403" t="n"/>
-      <c r="AK8" s="403" t="n"/>
-      <c r="AL8" s="404" t="n"/>
-      <c r="AM8" s="356" t="n"/>
-      <c r="AN8" s="405" t="n"/>
-      <c r="AO8" s="405" t="n"/>
-      <c r="AP8" s="405" t="n"/>
-      <c r="AQ8" s="405" t="n"/>
-      <c r="AR8" s="405" t="n"/>
-      <c r="AS8" s="405" t="n"/>
-      <c r="AT8" s="405" t="n"/>
-      <c r="AU8" s="405" t="n"/>
-      <c r="AV8" s="405" t="n"/>
-      <c r="AW8" s="405" t="n"/>
-      <c r="AX8" s="405" t="n"/>
-      <c r="AY8" s="405" t="n"/>
-      <c r="AZ8" s="405" t="n"/>
-      <c r="BA8" s="405" t="n"/>
-      <c r="BB8" s="405" t="n"/>
-      <c r="BC8" s="405" t="n"/>
-      <c r="BD8" s="406" t="n"/>
+      <c r="AD8" s="468" t="n"/>
+      <c r="AE8" s="468" t="n"/>
+      <c r="AF8" s="468" t="n"/>
+      <c r="AG8" s="468" t="n"/>
+      <c r="AH8" s="468" t="n"/>
+      <c r="AI8" s="468" t="n"/>
+      <c r="AJ8" s="468" t="n"/>
+      <c r="AK8" s="468" t="n"/>
+      <c r="AL8" s="468" t="n"/>
+      <c r="AM8" s="469" t="n"/>
+      <c r="AN8" s="470" t="n"/>
+      <c r="AO8" s="470" t="n"/>
+      <c r="AP8" s="470" t="n"/>
+      <c r="AQ8" s="470" t="n"/>
+      <c r="AR8" s="470" t="n"/>
+      <c r="AS8" s="470" t="n"/>
+      <c r="AT8" s="470" t="n"/>
+      <c r="AU8" s="470" t="n"/>
+      <c r="AV8" s="470" t="n"/>
+      <c r="AW8" s="470" t="n"/>
+      <c r="AX8" s="470" t="n"/>
+      <c r="AY8" s="470" t="n"/>
+      <c r="AZ8" s="470" t="n"/>
+      <c r="BA8" s="470" t="n"/>
+      <c r="BB8" s="470" t="n"/>
+      <c r="BC8" s="470" t="n"/>
+      <c r="BD8" s="472" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="353" t="inlineStr">
+      <c r="A9" s="473" t="inlineStr">
         <is>
           <t>Job / Shipment</t>
         </is>
       </c>
-      <c r="B9" s="403" t="n"/>
-      <c r="C9" s="403" t="n"/>
-      <c r="D9" s="403" t="n"/>
-      <c r="E9" s="403" t="n"/>
-      <c r="F9" s="403" t="n"/>
-      <c r="G9" s="403" t="n"/>
-      <c r="H9" s="403" t="n"/>
-      <c r="I9" s="403" t="n"/>
-      <c r="J9" s="404" t="n"/>
-      <c r="K9" s="356" t="n"/>
-      <c r="L9" s="405" t="n"/>
-      <c r="M9" s="405" t="n"/>
-      <c r="N9" s="405" t="n"/>
-      <c r="O9" s="405" t="n"/>
-      <c r="P9" s="405" t="n"/>
-      <c r="Q9" s="405" t="n"/>
-      <c r="R9" s="405" t="n"/>
-      <c r="S9" s="405" t="n"/>
-      <c r="T9" s="405" t="n"/>
-      <c r="U9" s="405" t="n"/>
-      <c r="V9" s="405" t="n"/>
-      <c r="W9" s="405" t="n"/>
-      <c r="X9" s="405" t="n"/>
-      <c r="Y9" s="405" t="n"/>
-      <c r="Z9" s="405" t="n"/>
-      <c r="AA9" s="405" t="n"/>
-      <c r="AB9" s="406" t="n"/>
-      <c r="AC9" s="359" t="inlineStr">
+      <c r="B9" s="342" t="n"/>
+      <c r="C9" s="342" t="n"/>
+      <c r="D9" s="342" t="n"/>
+      <c r="E9" s="342" t="n"/>
+      <c r="F9" s="342" t="n"/>
+      <c r="G9" s="342" t="n"/>
+      <c r="H9" s="342" t="n"/>
+      <c r="I9" s="342" t="n"/>
+      <c r="J9" s="342" t="n"/>
+      <c r="K9" s="474" t="n"/>
+      <c r="L9" s="360" t="n"/>
+      <c r="M9" s="360" t="n"/>
+      <c r="N9" s="360" t="n"/>
+      <c r="O9" s="360" t="n"/>
+      <c r="P9" s="360" t="n"/>
+      <c r="Q9" s="360" t="n"/>
+      <c r="R9" s="360" t="n"/>
+      <c r="S9" s="360" t="n"/>
+      <c r="T9" s="360" t="n"/>
+      <c r="U9" s="360" t="n"/>
+      <c r="V9" s="360" t="n"/>
+      <c r="W9" s="360" t="n"/>
+      <c r="X9" s="360" t="n"/>
+      <c r="Y9" s="360" t="n"/>
+      <c r="Z9" s="360" t="n"/>
+      <c r="AA9" s="360" t="n"/>
+      <c r="AB9" s="360" t="n"/>
+      <c r="AC9" s="475" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="AD9" s="403" t="n"/>
-      <c r="AE9" s="403" t="n"/>
-      <c r="AF9" s="403" t="n"/>
-      <c r="AG9" s="403" t="n"/>
-      <c r="AH9" s="403" t="n"/>
-      <c r="AI9" s="403" t="n"/>
-      <c r="AJ9" s="403" t="n"/>
-      <c r="AK9" s="403" t="n"/>
-      <c r="AL9" s="404" t="n"/>
-      <c r="AM9" s="356" t="n"/>
-      <c r="AN9" s="405" t="n"/>
-      <c r="AO9" s="405" t="n"/>
-      <c r="AP9" s="405" t="n"/>
-      <c r="AQ9" s="405" t="n"/>
-      <c r="AR9" s="405" t="n"/>
-      <c r="AS9" s="405" t="n"/>
-      <c r="AT9" s="405" t="n"/>
-      <c r="AU9" s="405" t="n"/>
-      <c r="AV9" s="405" t="n"/>
-      <c r="AW9" s="405" t="n"/>
-      <c r="AX9" s="405" t="n"/>
-      <c r="AY9" s="405" t="n"/>
-      <c r="AZ9" s="405" t="n"/>
-      <c r="BA9" s="405" t="n"/>
-      <c r="BB9" s="405" t="n"/>
-      <c r="BC9" s="405" t="n"/>
-      <c r="BD9" s="406" t="n"/>
+      <c r="AD9" s="342" t="n"/>
+      <c r="AE9" s="342" t="n"/>
+      <c r="AF9" s="342" t="n"/>
+      <c r="AG9" s="342" t="n"/>
+      <c r="AH9" s="342" t="n"/>
+      <c r="AI9" s="342" t="n"/>
+      <c r="AJ9" s="342" t="n"/>
+      <c r="AK9" s="342" t="n"/>
+      <c r="AL9" s="342" t="n"/>
+      <c r="AM9" s="474" t="n"/>
+      <c r="AN9" s="360" t="n"/>
+      <c r="AO9" s="360" t="n"/>
+      <c r="AP9" s="360" t="n"/>
+      <c r="AQ9" s="360" t="n"/>
+      <c r="AR9" s="360" t="n"/>
+      <c r="AS9" s="360" t="n"/>
+      <c r="AT9" s="360" t="n"/>
+      <c r="AU9" s="360" t="n"/>
+      <c r="AV9" s="360" t="n"/>
+      <c r="AW9" s="360" t="n"/>
+      <c r="AX9" s="360" t="n"/>
+      <c r="AY9" s="360" t="n"/>
+      <c r="AZ9" s="360" t="n"/>
+      <c r="BA9" s="360" t="n"/>
+      <c r="BB9" s="360" t="n"/>
+      <c r="BC9" s="360" t="n"/>
+      <c r="BD9" s="476" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="353" t="inlineStr">
+      <c r="A10" s="473" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="B10" s="403" t="n"/>
-      <c r="C10" s="403" t="n"/>
-      <c r="D10" s="403" t="n"/>
-      <c r="E10" s="403" t="n"/>
-      <c r="F10" s="403" t="n"/>
-      <c r="G10" s="403" t="n"/>
-      <c r="H10" s="403" t="n"/>
-      <c r="I10" s="403" t="n"/>
-      <c r="J10" s="404" t="n"/>
-      <c r="K10" s="356" t="n"/>
-      <c r="L10" s="405" t="n"/>
-      <c r="M10" s="405" t="n"/>
-      <c r="N10" s="405" t="n"/>
-      <c r="O10" s="405" t="n"/>
-      <c r="P10" s="405" t="n"/>
-      <c r="Q10" s="405" t="n"/>
-      <c r="R10" s="405" t="n"/>
-      <c r="S10" s="405" t="n"/>
-      <c r="T10" s="405" t="n"/>
-      <c r="U10" s="405" t="n"/>
-      <c r="V10" s="405" t="n"/>
-      <c r="W10" s="405" t="n"/>
-      <c r="X10" s="405" t="n"/>
-      <c r="Y10" s="405" t="n"/>
-      <c r="Z10" s="405" t="n"/>
-      <c r="AA10" s="405" t="n"/>
-      <c r="AB10" s="406" t="n"/>
-      <c r="AC10" s="359" t="inlineStr">
+      <c r="B10" s="342" t="n"/>
+      <c r="C10" s="342" t="n"/>
+      <c r="D10" s="342" t="n"/>
+      <c r="E10" s="342" t="n"/>
+      <c r="F10" s="342" t="n"/>
+      <c r="G10" s="342" t="n"/>
+      <c r="H10" s="342" t="n"/>
+      <c r="I10" s="342" t="n"/>
+      <c r="J10" s="342" t="n"/>
+      <c r="K10" s="474" t="n"/>
+      <c r="L10" s="360" t="n"/>
+      <c r="M10" s="360" t="n"/>
+      <c r="N10" s="360" t="n"/>
+      <c r="O10" s="360" t="n"/>
+      <c r="P10" s="360" t="n"/>
+      <c r="Q10" s="360" t="n"/>
+      <c r="R10" s="360" t="n"/>
+      <c r="S10" s="360" t="n"/>
+      <c r="T10" s="360" t="n"/>
+      <c r="U10" s="360" t="n"/>
+      <c r="V10" s="360" t="n"/>
+      <c r="W10" s="360" t="n"/>
+      <c r="X10" s="360" t="n"/>
+      <c r="Y10" s="360" t="n"/>
+      <c r="Z10" s="360" t="n"/>
+      <c r="AA10" s="360" t="n"/>
+      <c r="AB10" s="360" t="n"/>
+      <c r="AC10" s="475" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="AD10" s="403" t="n"/>
-      <c r="AE10" s="403" t="n"/>
-      <c r="AF10" s="403" t="n"/>
-      <c r="AG10" s="403" t="n"/>
-      <c r="AH10" s="403" t="n"/>
-      <c r="AI10" s="403" t="n"/>
-      <c r="AJ10" s="403" t="n"/>
-      <c r="AK10" s="403" t="n"/>
-      <c r="AL10" s="404" t="n"/>
-      <c r="AM10" s="356" t="n"/>
-      <c r="AN10" s="405" t="n"/>
-      <c r="AO10" s="405" t="n"/>
-      <c r="AP10" s="405" t="n"/>
-      <c r="AQ10" s="405" t="n"/>
-      <c r="AR10" s="405" t="n"/>
-      <c r="AS10" s="405" t="n"/>
-      <c r="AT10" s="405" t="n"/>
-      <c r="AU10" s="405" t="n"/>
-      <c r="AV10" s="405" t="n"/>
-      <c r="AW10" s="405" t="n"/>
-      <c r="AX10" s="405" t="n"/>
-      <c r="AY10" s="405" t="n"/>
-      <c r="AZ10" s="405" t="n"/>
-      <c r="BA10" s="405" t="n"/>
-      <c r="BB10" s="405" t="n"/>
-      <c r="BC10" s="405" t="n"/>
-      <c r="BD10" s="406" t="n"/>
+      <c r="AD10" s="342" t="n"/>
+      <c r="AE10" s="342" t="n"/>
+      <c r="AF10" s="342" t="n"/>
+      <c r="AG10" s="342" t="n"/>
+      <c r="AH10" s="342" t="n"/>
+      <c r="AI10" s="342" t="n"/>
+      <c r="AJ10" s="342" t="n"/>
+      <c r="AK10" s="342" t="n"/>
+      <c r="AL10" s="342" t="n"/>
+      <c r="AM10" s="474" t="n"/>
+      <c r="AN10" s="360" t="n"/>
+      <c r="AO10" s="360" t="n"/>
+      <c r="AP10" s="360" t="n"/>
+      <c r="AQ10" s="360" t="n"/>
+      <c r="AR10" s="360" t="n"/>
+      <c r="AS10" s="360" t="n"/>
+      <c r="AT10" s="360" t="n"/>
+      <c r="AU10" s="360" t="n"/>
+      <c r="AV10" s="360" t="n"/>
+      <c r="AW10" s="360" t="n"/>
+      <c r="AX10" s="360" t="n"/>
+      <c r="AY10" s="360" t="n"/>
+      <c r="AZ10" s="360" t="n"/>
+      <c r="BA10" s="360" t="n"/>
+      <c r="BB10" s="360" t="n"/>
+      <c r="BC10" s="360" t="n"/>
+      <c r="BD10" s="476" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="353" t="inlineStr">
+      <c r="A11" s="473" t="inlineStr">
         <is>
           <t>Inspection Basis</t>
         </is>
       </c>
-      <c r="B11" s="403" t="n"/>
-      <c r="C11" s="403" t="n"/>
-      <c r="D11" s="403" t="n"/>
-      <c r="E11" s="403" t="n"/>
-      <c r="F11" s="403" t="n"/>
-      <c r="G11" s="403" t="n"/>
-      <c r="H11" s="403" t="n"/>
-      <c r="I11" s="403" t="n"/>
-      <c r="J11" s="404" t="n"/>
-      <c r="K11" s="356" t="n"/>
-      <c r="L11" s="405" t="n"/>
-      <c r="M11" s="405" t="n"/>
-      <c r="N11" s="405" t="n"/>
-      <c r="O11" s="405" t="n"/>
-      <c r="P11" s="405" t="n"/>
-      <c r="Q11" s="405" t="n"/>
-      <c r="R11" s="405" t="n"/>
-      <c r="S11" s="405" t="n"/>
-      <c r="T11" s="405" t="n"/>
-      <c r="U11" s="405" t="n"/>
-      <c r="V11" s="405" t="n"/>
-      <c r="W11" s="405" t="n"/>
-      <c r="X11" s="405" t="n"/>
-      <c r="Y11" s="405" t="n"/>
-      <c r="Z11" s="405" t="n"/>
-      <c r="AA11" s="405" t="n"/>
-      <c r="AB11" s="406" t="n"/>
-      <c r="AC11" s="359" t="inlineStr">
+      <c r="B11" s="342" t="n"/>
+      <c r="C11" s="342" t="n"/>
+      <c r="D11" s="342" t="n"/>
+      <c r="E11" s="342" t="n"/>
+      <c r="F11" s="342" t="n"/>
+      <c r="G11" s="342" t="n"/>
+      <c r="H11" s="342" t="n"/>
+      <c r="I11" s="342" t="n"/>
+      <c r="J11" s="342" t="n"/>
+      <c r="K11" s="474" t="n"/>
+      <c r="L11" s="360" t="n"/>
+      <c r="M11" s="360" t="n"/>
+      <c r="N11" s="360" t="n"/>
+      <c r="O11" s="360" t="n"/>
+      <c r="P11" s="360" t="n"/>
+      <c r="Q11" s="360" t="n"/>
+      <c r="R11" s="360" t="n"/>
+      <c r="S11" s="360" t="n"/>
+      <c r="T11" s="360" t="n"/>
+      <c r="U11" s="360" t="n"/>
+      <c r="V11" s="360" t="n"/>
+      <c r="W11" s="360" t="n"/>
+      <c r="X11" s="360" t="n"/>
+      <c r="Y11" s="360" t="n"/>
+      <c r="Z11" s="360" t="n"/>
+      <c r="AA11" s="360" t="n"/>
+      <c r="AB11" s="360" t="n"/>
+      <c r="AC11" s="475" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="AD11" s="403" t="n"/>
-      <c r="AE11" s="403" t="n"/>
-      <c r="AF11" s="403" t="n"/>
-      <c r="AG11" s="403" t="n"/>
-      <c r="AH11" s="403" t="n"/>
-      <c r="AI11" s="403" t="n"/>
-      <c r="AJ11" s="403" t="n"/>
-      <c r="AK11" s="403" t="n"/>
-      <c r="AL11" s="404" t="n"/>
-      <c r="AM11" s="356" t="n"/>
-      <c r="AN11" s="405" t="n"/>
-      <c r="AO11" s="405" t="n"/>
-      <c r="AP11" s="405" t="n"/>
-      <c r="AQ11" s="405" t="n"/>
-      <c r="AR11" s="405" t="n"/>
-      <c r="AS11" s="405" t="n"/>
-      <c r="AT11" s="405" t="n"/>
-      <c r="AU11" s="405" t="n"/>
-      <c r="AV11" s="405" t="n"/>
-      <c r="AW11" s="405" t="n"/>
-      <c r="AX11" s="405" t="n"/>
-      <c r="AY11" s="405" t="n"/>
-      <c r="AZ11" s="405" t="n"/>
-      <c r="BA11" s="405" t="n"/>
-      <c r="BB11" s="405" t="n"/>
-      <c r="BC11" s="405" t="n"/>
-      <c r="BD11" s="406" t="n"/>
+      <c r="AD11" s="342" t="n"/>
+      <c r="AE11" s="342" t="n"/>
+      <c r="AF11" s="342" t="n"/>
+      <c r="AG11" s="342" t="n"/>
+      <c r="AH11" s="342" t="n"/>
+      <c r="AI11" s="342" t="n"/>
+      <c r="AJ11" s="342" t="n"/>
+      <c r="AK11" s="342" t="n"/>
+      <c r="AL11" s="342" t="n"/>
+      <c r="AM11" s="474" t="n"/>
+      <c r="AN11" s="360" t="n"/>
+      <c r="AO11" s="360" t="n"/>
+      <c r="AP11" s="360" t="n"/>
+      <c r="AQ11" s="360" t="n"/>
+      <c r="AR11" s="360" t="n"/>
+      <c r="AS11" s="360" t="n"/>
+      <c r="AT11" s="360" t="n"/>
+      <c r="AU11" s="360" t="n"/>
+      <c r="AV11" s="360" t="n"/>
+      <c r="AW11" s="360" t="n"/>
+      <c r="AX11" s="360" t="n"/>
+      <c r="AY11" s="360" t="n"/>
+      <c r="AZ11" s="360" t="n"/>
+      <c r="BA11" s="360" t="n"/>
+      <c r="BB11" s="360" t="n"/>
+      <c r="BC11" s="360" t="n"/>
+      <c r="BD11" s="476" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="353" t="inlineStr">
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="477" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B12" s="398" t="n"/>
-      <c r="C12" s="398" t="n"/>
-      <c r="D12" s="398" t="n"/>
-      <c r="E12" s="398" t="n"/>
-      <c r="F12" s="398" t="n"/>
-      <c r="G12" s="398" t="n"/>
-      <c r="H12" s="398" t="n"/>
-      <c r="I12" s="398" t="n"/>
-      <c r="J12" s="399" t="n"/>
-      <c r="K12" s="356" t="n"/>
-      <c r="L12" s="407" t="n"/>
-      <c r="M12" s="407" t="n"/>
-      <c r="N12" s="407" t="n"/>
-      <c r="O12" s="407" t="n"/>
-      <c r="P12" s="407" t="n"/>
-      <c r="Q12" s="407" t="n"/>
-      <c r="R12" s="407" t="n"/>
-      <c r="S12" s="407" t="n"/>
-      <c r="T12" s="407" t="n"/>
-      <c r="U12" s="407" t="n"/>
-      <c r="V12" s="407" t="n"/>
-      <c r="W12" s="407" t="n"/>
-      <c r="X12" s="407" t="n"/>
-      <c r="Y12" s="407" t="n"/>
-      <c r="Z12" s="407" t="n"/>
-      <c r="AA12" s="407" t="n"/>
-      <c r="AB12" s="408" t="n"/>
-      <c r="AC12" s="359" t="inlineStr">
+      <c r="B12" s="478" t="n"/>
+      <c r="C12" s="478" t="n"/>
+      <c r="D12" s="478" t="n"/>
+      <c r="E12" s="478" t="n"/>
+      <c r="F12" s="478" t="n"/>
+      <c r="G12" s="478" t="n"/>
+      <c r="H12" s="478" t="n"/>
+      <c r="I12" s="478" t="n"/>
+      <c r="J12" s="478" t="n"/>
+      <c r="K12" s="479" t="n"/>
+      <c r="L12" s="480" t="n"/>
+      <c r="M12" s="480" t="n"/>
+      <c r="N12" s="480" t="n"/>
+      <c r="O12" s="480" t="n"/>
+      <c r="P12" s="480" t="n"/>
+      <c r="Q12" s="480" t="n"/>
+      <c r="R12" s="480" t="n"/>
+      <c r="S12" s="480" t="n"/>
+      <c r="T12" s="480" t="n"/>
+      <c r="U12" s="480" t="n"/>
+      <c r="V12" s="480" t="n"/>
+      <c r="W12" s="480" t="n"/>
+      <c r="X12" s="480" t="n"/>
+      <c r="Y12" s="480" t="n"/>
+      <c r="Z12" s="480" t="n"/>
+      <c r="AA12" s="480" t="n"/>
+      <c r="AB12" s="480" t="n"/>
+      <c r="AC12" s="481" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="398" t="n"/>
-      <c r="AE12" s="398" t="n"/>
-      <c r="AF12" s="398" t="n"/>
-      <c r="AG12" s="398" t="n"/>
-      <c r="AH12" s="398" t="n"/>
-      <c r="AI12" s="398" t="n"/>
-      <c r="AJ12" s="398" t="n"/>
-      <c r="AK12" s="398" t="n"/>
-      <c r="AL12" s="399" t="n"/>
-      <c r="AM12" s="356" t="n"/>
-      <c r="AN12" s="407" t="n"/>
-      <c r="AO12" s="407" t="n"/>
-      <c r="AP12" s="407" t="n"/>
-      <c r="AQ12" s="407" t="n"/>
-      <c r="AR12" s="407" t="n"/>
-      <c r="AS12" s="407" t="n"/>
-      <c r="AT12" s="407" t="n"/>
-      <c r="AU12" s="407" t="n"/>
-      <c r="AV12" s="407" t="n"/>
-      <c r="AW12" s="407" t="n"/>
-      <c r="AX12" s="407" t="n"/>
-      <c r="AY12" s="407" t="n"/>
-      <c r="AZ12" s="407" t="n"/>
-      <c r="BA12" s="407" t="n"/>
-      <c r="BB12" s="407" t="n"/>
-      <c r="BC12" s="407" t="n"/>
-      <c r="BD12" s="408" t="n"/>
+      <c r="AD12" s="478" t="n"/>
+      <c r="AE12" s="478" t="n"/>
+      <c r="AF12" s="478" t="n"/>
+      <c r="AG12" s="478" t="n"/>
+      <c r="AH12" s="478" t="n"/>
+      <c r="AI12" s="478" t="n"/>
+      <c r="AJ12" s="478" t="n"/>
+      <c r="AK12" s="478" t="n"/>
+      <c r="AL12" s="478" t="n"/>
+      <c r="AM12" s="479" t="n"/>
+      <c r="AN12" s="480" t="n"/>
+      <c r="AO12" s="480" t="n"/>
+      <c r="AP12" s="480" t="n"/>
+      <c r="AQ12" s="480" t="n"/>
+      <c r="AR12" s="480" t="n"/>
+      <c r="AS12" s="480" t="n"/>
+      <c r="AT12" s="480" t="n"/>
+      <c r="AU12" s="480" t="n"/>
+      <c r="AV12" s="480" t="n"/>
+      <c r="AW12" s="480" t="n"/>
+      <c r="AX12" s="480" t="n"/>
+      <c r="AY12" s="480" t="n"/>
+      <c r="AZ12" s="480" t="n"/>
+      <c r="BA12" s="480" t="n"/>
+      <c r="BB12" s="480" t="n"/>
+      <c r="BC12" s="480" t="n"/>
+      <c r="BD12" s="482" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1">
+    <row r="13" ht="3" customHeight="1">
       <c r="A13" s="351" t="n"/>
       <c r="B13" s="351" t="n"/>
       <c r="C13" s="351" t="n"/>
@@ -6066,610 +6944,610 @@
       <c r="BC13" s="351" t="n"/>
       <c r="BD13" s="351" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="352" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="464" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B14" s="403" t="n"/>
-      <c r="C14" s="403" t="n"/>
-      <c r="D14" s="403" t="n"/>
-      <c r="E14" s="403" t="n"/>
-      <c r="F14" s="403" t="n"/>
-      <c r="G14" s="403" t="n"/>
-      <c r="H14" s="403" t="n"/>
-      <c r="I14" s="403" t="n"/>
-      <c r="J14" s="403" t="n"/>
-      <c r="K14" s="403" t="n"/>
-      <c r="L14" s="403" t="n"/>
-      <c r="M14" s="403" t="n"/>
-      <c r="N14" s="403" t="n"/>
-      <c r="O14" s="403" t="n"/>
-      <c r="P14" s="403" t="n"/>
-      <c r="Q14" s="403" t="n"/>
-      <c r="R14" s="403" t="n"/>
-      <c r="S14" s="403" t="n"/>
-      <c r="T14" s="403" t="n"/>
-      <c r="U14" s="403" t="n"/>
-      <c r="V14" s="403" t="n"/>
-      <c r="W14" s="403" t="n"/>
-      <c r="X14" s="403" t="n"/>
-      <c r="Y14" s="403" t="n"/>
-      <c r="Z14" s="403" t="n"/>
-      <c r="AA14" s="403" t="n"/>
-      <c r="AB14" s="403" t="n"/>
-      <c r="AC14" s="403" t="n"/>
-      <c r="AD14" s="403" t="n"/>
-      <c r="AE14" s="403" t="n"/>
-      <c r="AF14" s="403" t="n"/>
-      <c r="AG14" s="403" t="n"/>
-      <c r="AH14" s="403" t="n"/>
-      <c r="AI14" s="403" t="n"/>
-      <c r="AJ14" s="403" t="n"/>
-      <c r="AK14" s="403" t="n"/>
-      <c r="AL14" s="403" t="n"/>
-      <c r="AM14" s="403" t="n"/>
-      <c r="AN14" s="403" t="n"/>
-      <c r="AO14" s="403" t="n"/>
-      <c r="AP14" s="403" t="n"/>
-      <c r="AQ14" s="403" t="n"/>
-      <c r="AR14" s="403" t="n"/>
-      <c r="AS14" s="403" t="n"/>
-      <c r="AT14" s="403" t="n"/>
-      <c r="AU14" s="403" t="n"/>
-      <c r="AV14" s="403" t="n"/>
-      <c r="AW14" s="403" t="n"/>
-      <c r="AX14" s="403" t="n"/>
-      <c r="AY14" s="403" t="n"/>
-      <c r="AZ14" s="403" t="n"/>
-      <c r="BA14" s="403" t="n"/>
-      <c r="BB14" s="403" t="n"/>
-      <c r="BC14" s="403" t="n"/>
-      <c r="BD14" s="404" t="n"/>
+      <c r="B14" s="465" t="n"/>
+      <c r="C14" s="465" t="n"/>
+      <c r="D14" s="465" t="n"/>
+      <c r="E14" s="465" t="n"/>
+      <c r="F14" s="465" t="n"/>
+      <c r="G14" s="465" t="n"/>
+      <c r="H14" s="465" t="n"/>
+      <c r="I14" s="465" t="n"/>
+      <c r="J14" s="465" t="n"/>
+      <c r="K14" s="465" t="n"/>
+      <c r="L14" s="465" t="n"/>
+      <c r="M14" s="465" t="n"/>
+      <c r="N14" s="465" t="n"/>
+      <c r="O14" s="465" t="n"/>
+      <c r="P14" s="465" t="n"/>
+      <c r="Q14" s="465" t="n"/>
+      <c r="R14" s="465" t="n"/>
+      <c r="S14" s="465" t="n"/>
+      <c r="T14" s="465" t="n"/>
+      <c r="U14" s="465" t="n"/>
+      <c r="V14" s="465" t="n"/>
+      <c r="W14" s="465" t="n"/>
+      <c r="X14" s="465" t="n"/>
+      <c r="Y14" s="465" t="n"/>
+      <c r="Z14" s="465" t="n"/>
+      <c r="AA14" s="465" t="n"/>
+      <c r="AB14" s="465" t="n"/>
+      <c r="AC14" s="465" t="n"/>
+      <c r="AD14" s="465" t="n"/>
+      <c r="AE14" s="465" t="n"/>
+      <c r="AF14" s="465" t="n"/>
+      <c r="AG14" s="465" t="n"/>
+      <c r="AH14" s="465" t="n"/>
+      <c r="AI14" s="465" t="n"/>
+      <c r="AJ14" s="465" t="n"/>
+      <c r="AK14" s="465" t="n"/>
+      <c r="AL14" s="465" t="n"/>
+      <c r="AM14" s="465" t="n"/>
+      <c r="AN14" s="465" t="n"/>
+      <c r="AO14" s="465" t="n"/>
+      <c r="AP14" s="465" t="n"/>
+      <c r="AQ14" s="465" t="n"/>
+      <c r="AR14" s="465" t="n"/>
+      <c r="AS14" s="465" t="n"/>
+      <c r="AT14" s="465" t="n"/>
+      <c r="AU14" s="465" t="n"/>
+      <c r="AV14" s="465" t="n"/>
+      <c r="AW14" s="465" t="n"/>
+      <c r="AX14" s="465" t="n"/>
+      <c r="AY14" s="465" t="n"/>
+      <c r="AZ14" s="465" t="n"/>
+      <c r="BA14" s="465" t="n"/>
+      <c r="BB14" s="465" t="n"/>
+      <c r="BC14" s="465" t="n"/>
+      <c r="BD14" s="466" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="362" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="483" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="403" t="n"/>
-      <c r="C15" s="404" t="n"/>
-      <c r="D15" s="363" t="inlineStr">
+      <c r="B15" s="484" t="n"/>
+      <c r="C15" s="484" t="n"/>
+      <c r="D15" s="485" t="inlineStr">
         <is>
           <t>Check Group</t>
         </is>
       </c>
-      <c r="E15" s="403" t="n"/>
-      <c r="F15" s="403" t="n"/>
-      <c r="G15" s="404" t="n"/>
-      <c r="H15" s="363" t="inlineStr">
+      <c r="E15" s="484" t="n"/>
+      <c r="F15" s="484" t="n"/>
+      <c r="G15" s="484" t="n"/>
+      <c r="H15" s="485" t="inlineStr">
         <is>
           <t>Characteristic / Requirement</t>
         </is>
       </c>
-      <c r="I15" s="403" t="n"/>
-      <c r="J15" s="403" t="n"/>
-      <c r="K15" s="403" t="n"/>
-      <c r="L15" s="403" t="n"/>
-      <c r="M15" s="403" t="n"/>
-      <c r="N15" s="403" t="n"/>
-      <c r="O15" s="403" t="n"/>
-      <c r="P15" s="403" t="n"/>
-      <c r="Q15" s="403" t="n"/>
-      <c r="R15" s="403" t="n"/>
-      <c r="S15" s="403" t="n"/>
-      <c r="T15" s="403" t="n"/>
-      <c r="U15" s="403" t="n"/>
-      <c r="V15" s="403" t="n"/>
-      <c r="W15" s="403" t="n"/>
-      <c r="X15" s="403" t="n"/>
-      <c r="Y15" s="403" t="n"/>
-      <c r="Z15" s="404" t="n"/>
-      <c r="AA15" s="363" t="inlineStr">
+      <c r="I15" s="484" t="n"/>
+      <c r="J15" s="484" t="n"/>
+      <c r="K15" s="484" t="n"/>
+      <c r="L15" s="484" t="n"/>
+      <c r="M15" s="484" t="n"/>
+      <c r="N15" s="484" t="n"/>
+      <c r="O15" s="484" t="n"/>
+      <c r="P15" s="484" t="n"/>
+      <c r="Q15" s="484" t="n"/>
+      <c r="R15" s="484" t="n"/>
+      <c r="S15" s="484" t="n"/>
+      <c r="T15" s="484" t="n"/>
+      <c r="U15" s="484" t="n"/>
+      <c r="V15" s="484" t="n"/>
+      <c r="W15" s="484" t="n"/>
+      <c r="X15" s="484" t="n"/>
+      <c r="Y15" s="484" t="n"/>
+      <c r="Z15" s="484" t="n"/>
+      <c r="AA15" s="485" t="inlineStr">
         <is>
           <t>Method / Inspection Basis</t>
         </is>
       </c>
-      <c r="AB15" s="403" t="n"/>
-      <c r="AC15" s="403" t="n"/>
-      <c r="AD15" s="403" t="n"/>
-      <c r="AE15" s="403" t="n"/>
-      <c r="AF15" s="403" t="n"/>
-      <c r="AG15" s="403" t="n"/>
-      <c r="AH15" s="403" t="n"/>
-      <c r="AI15" s="403" t="n"/>
-      <c r="AJ15" s="403" t="n"/>
-      <c r="AK15" s="403" t="n"/>
-      <c r="AL15" s="403" t="n"/>
-      <c r="AM15" s="403" t="n"/>
-      <c r="AN15" s="403" t="n"/>
-      <c r="AO15" s="403" t="n"/>
-      <c r="AP15" s="403" t="n"/>
-      <c r="AQ15" s="404" t="n"/>
-      <c r="AR15" s="363" t="inlineStr">
+      <c r="AB15" s="484" t="n"/>
+      <c r="AC15" s="484" t="n"/>
+      <c r="AD15" s="484" t="n"/>
+      <c r="AE15" s="484" t="n"/>
+      <c r="AF15" s="484" t="n"/>
+      <c r="AG15" s="484" t="n"/>
+      <c r="AH15" s="484" t="n"/>
+      <c r="AI15" s="484" t="n"/>
+      <c r="AJ15" s="484" t="n"/>
+      <c r="AK15" s="484" t="n"/>
+      <c r="AL15" s="484" t="n"/>
+      <c r="AM15" s="484" t="n"/>
+      <c r="AN15" s="484" t="n"/>
+      <c r="AO15" s="484" t="n"/>
+      <c r="AP15" s="484" t="n"/>
+      <c r="AQ15" s="484" t="n"/>
+      <c r="AR15" s="485" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="403" t="n"/>
-      <c r="AT15" s="403" t="n"/>
-      <c r="AU15" s="403" t="n"/>
-      <c r="AV15" s="403" t="n"/>
-      <c r="AW15" s="404" t="n"/>
-      <c r="AX15" s="363" t="inlineStr">
+      <c r="AS15" s="484" t="n"/>
+      <c r="AT15" s="484" t="n"/>
+      <c r="AU15" s="484" t="n"/>
+      <c r="AV15" s="484" t="n"/>
+      <c r="AW15" s="484" t="n"/>
+      <c r="AX15" s="485" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY15" s="403" t="n"/>
-      <c r="AZ15" s="403" t="n"/>
-      <c r="BA15" s="404" t="n"/>
-      <c r="BB15" s="363" t="inlineStr">
+      <c r="AY15" s="484" t="n"/>
+      <c r="AZ15" s="484" t="n"/>
+      <c r="BA15" s="484" t="n"/>
+      <c r="BB15" s="485" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="403" t="n"/>
-      <c r="BD15" s="404" t="n"/>
+      <c r="BC15" s="484" t="n"/>
+      <c r="BD15" s="486" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="364">
+      <c r="A16" s="487">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="409" t="n"/>
-      <c r="C16" s="410" t="n"/>
-      <c r="D16" s="367" t="inlineStr">
+      <c r="B16" s="468" t="n"/>
+      <c r="C16" s="468" t="n"/>
+      <c r="D16" s="488" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="411" t="n"/>
-      <c r="F16" s="411" t="n"/>
-      <c r="G16" s="412" t="n"/>
-      <c r="H16" s="370" t="n"/>
-      <c r="I16" s="411" t="n"/>
-      <c r="J16" s="411" t="n"/>
-      <c r="K16" s="411" t="n"/>
-      <c r="L16" s="411" t="n"/>
-      <c r="M16" s="411" t="n"/>
-      <c r="N16" s="411" t="n"/>
-      <c r="O16" s="411" t="n"/>
-      <c r="P16" s="411" t="n"/>
-      <c r="Q16" s="411" t="n"/>
-      <c r="R16" s="411" t="n"/>
-      <c r="S16" s="411" t="n"/>
-      <c r="T16" s="411" t="n"/>
-      <c r="U16" s="411" t="n"/>
-      <c r="V16" s="411" t="n"/>
-      <c r="W16" s="411" t="n"/>
-      <c r="X16" s="411" t="n"/>
-      <c r="Y16" s="411" t="n"/>
-      <c r="Z16" s="412" t="n"/>
-      <c r="AA16" s="371" t="n"/>
-      <c r="AB16" s="411" t="n"/>
-      <c r="AC16" s="411" t="n"/>
-      <c r="AD16" s="411" t="n"/>
-      <c r="AE16" s="411" t="n"/>
-      <c r="AF16" s="411" t="n"/>
-      <c r="AG16" s="411" t="n"/>
-      <c r="AH16" s="411" t="n"/>
-      <c r="AI16" s="411" t="n"/>
-      <c r="AJ16" s="411" t="n"/>
-      <c r="AK16" s="411" t="n"/>
-      <c r="AL16" s="411" t="n"/>
-      <c r="AM16" s="411" t="n"/>
-      <c r="AN16" s="411" t="n"/>
-      <c r="AO16" s="411" t="n"/>
-      <c r="AP16" s="411" t="n"/>
-      <c r="AQ16" s="412" t="n"/>
-      <c r="AR16" s="370" t="n"/>
-      <c r="AS16" s="411" t="n"/>
-      <c r="AT16" s="411" t="n"/>
-      <c r="AU16" s="411" t="n"/>
-      <c r="AV16" s="411" t="n"/>
-      <c r="AW16" s="412" t="n"/>
-      <c r="AX16" s="370" t="n"/>
-      <c r="AY16" s="411" t="n"/>
-      <c r="AZ16" s="411" t="n"/>
-      <c r="BA16" s="412" t="n"/>
-      <c r="BB16" s="372" t="n"/>
-      <c r="BC16" s="411" t="n"/>
-      <c r="BD16" s="412" t="n"/>
+      <c r="E16" s="470" t="n"/>
+      <c r="F16" s="470" t="n"/>
+      <c r="G16" s="470" t="n"/>
+      <c r="H16" s="469" t="n"/>
+      <c r="I16" s="470" t="n"/>
+      <c r="J16" s="470" t="n"/>
+      <c r="K16" s="470" t="n"/>
+      <c r="L16" s="470" t="n"/>
+      <c r="M16" s="470" t="n"/>
+      <c r="N16" s="470" t="n"/>
+      <c r="O16" s="470" t="n"/>
+      <c r="P16" s="470" t="n"/>
+      <c r="Q16" s="470" t="n"/>
+      <c r="R16" s="470" t="n"/>
+      <c r="S16" s="470" t="n"/>
+      <c r="T16" s="470" t="n"/>
+      <c r="U16" s="470" t="n"/>
+      <c r="V16" s="470" t="n"/>
+      <c r="W16" s="470" t="n"/>
+      <c r="X16" s="470" t="n"/>
+      <c r="Y16" s="470" t="n"/>
+      <c r="Z16" s="470" t="n"/>
+      <c r="AA16" s="489" t="n"/>
+      <c r="AB16" s="470" t="n"/>
+      <c r="AC16" s="470" t="n"/>
+      <c r="AD16" s="470" t="n"/>
+      <c r="AE16" s="470" t="n"/>
+      <c r="AF16" s="470" t="n"/>
+      <c r="AG16" s="470" t="n"/>
+      <c r="AH16" s="470" t="n"/>
+      <c r="AI16" s="470" t="n"/>
+      <c r="AJ16" s="470" t="n"/>
+      <c r="AK16" s="470" t="n"/>
+      <c r="AL16" s="470" t="n"/>
+      <c r="AM16" s="470" t="n"/>
+      <c r="AN16" s="470" t="n"/>
+      <c r="AO16" s="470" t="n"/>
+      <c r="AP16" s="470" t="n"/>
+      <c r="AQ16" s="470" t="n"/>
+      <c r="AR16" s="469" t="n"/>
+      <c r="AS16" s="470" t="n"/>
+      <c r="AT16" s="470" t="n"/>
+      <c r="AU16" s="470" t="n"/>
+      <c r="AV16" s="470" t="n"/>
+      <c r="AW16" s="470" t="n"/>
+      <c r="AX16" s="469" t="n"/>
+      <c r="AY16" s="470" t="n"/>
+      <c r="AZ16" s="470" t="n"/>
+      <c r="BA16" s="470" t="n"/>
+      <c r="BB16" s="490" t="n"/>
+      <c r="BC16" s="470" t="n"/>
+      <c r="BD16" s="472" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="364">
+      <c r="A17" s="491">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="409" t="n"/>
-      <c r="C17" s="410" t="n"/>
-      <c r="D17" s="367" t="inlineStr">
+      <c r="B17" s="342" t="n"/>
+      <c r="C17" s="342" t="n"/>
+      <c r="D17" s="492" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="411" t="n"/>
-      <c r="F17" s="411" t="n"/>
-      <c r="G17" s="412" t="n"/>
-      <c r="H17" s="370" t="n"/>
-      <c r="I17" s="411" t="n"/>
-      <c r="J17" s="411" t="n"/>
-      <c r="K17" s="411" t="n"/>
-      <c r="L17" s="411" t="n"/>
-      <c r="M17" s="411" t="n"/>
-      <c r="N17" s="411" t="n"/>
-      <c r="O17" s="411" t="n"/>
-      <c r="P17" s="411" t="n"/>
-      <c r="Q17" s="411" t="n"/>
-      <c r="R17" s="411" t="n"/>
-      <c r="S17" s="411" t="n"/>
-      <c r="T17" s="411" t="n"/>
-      <c r="U17" s="411" t="n"/>
-      <c r="V17" s="411" t="n"/>
-      <c r="W17" s="411" t="n"/>
-      <c r="X17" s="411" t="n"/>
-      <c r="Y17" s="411" t="n"/>
-      <c r="Z17" s="412" t="n"/>
-      <c r="AA17" s="371" t="n"/>
-      <c r="AB17" s="411" t="n"/>
-      <c r="AC17" s="411" t="n"/>
-      <c r="AD17" s="411" t="n"/>
-      <c r="AE17" s="411" t="n"/>
-      <c r="AF17" s="411" t="n"/>
-      <c r="AG17" s="411" t="n"/>
-      <c r="AH17" s="411" t="n"/>
-      <c r="AI17" s="411" t="n"/>
-      <c r="AJ17" s="411" t="n"/>
-      <c r="AK17" s="411" t="n"/>
-      <c r="AL17" s="411" t="n"/>
-      <c r="AM17" s="411" t="n"/>
-      <c r="AN17" s="411" t="n"/>
-      <c r="AO17" s="411" t="n"/>
-      <c r="AP17" s="411" t="n"/>
-      <c r="AQ17" s="412" t="n"/>
-      <c r="AR17" s="370" t="n"/>
-      <c r="AS17" s="411" t="n"/>
-      <c r="AT17" s="411" t="n"/>
-      <c r="AU17" s="411" t="n"/>
-      <c r="AV17" s="411" t="n"/>
-      <c r="AW17" s="412" t="n"/>
-      <c r="AX17" s="370" t="n"/>
-      <c r="AY17" s="411" t="n"/>
-      <c r="AZ17" s="411" t="n"/>
-      <c r="BA17" s="412" t="n"/>
-      <c r="BB17" s="372" t="n"/>
-      <c r="BC17" s="411" t="n"/>
-      <c r="BD17" s="412" t="n"/>
+      <c r="E17" s="360" t="n"/>
+      <c r="F17" s="360" t="n"/>
+      <c r="G17" s="360" t="n"/>
+      <c r="H17" s="474" t="n"/>
+      <c r="I17" s="360" t="n"/>
+      <c r="J17" s="360" t="n"/>
+      <c r="K17" s="360" t="n"/>
+      <c r="L17" s="360" t="n"/>
+      <c r="M17" s="360" t="n"/>
+      <c r="N17" s="360" t="n"/>
+      <c r="O17" s="360" t="n"/>
+      <c r="P17" s="360" t="n"/>
+      <c r="Q17" s="360" t="n"/>
+      <c r="R17" s="360" t="n"/>
+      <c r="S17" s="360" t="n"/>
+      <c r="T17" s="360" t="n"/>
+      <c r="U17" s="360" t="n"/>
+      <c r="V17" s="360" t="n"/>
+      <c r="W17" s="360" t="n"/>
+      <c r="X17" s="360" t="n"/>
+      <c r="Y17" s="360" t="n"/>
+      <c r="Z17" s="360" t="n"/>
+      <c r="AA17" s="493" t="n"/>
+      <c r="AB17" s="360" t="n"/>
+      <c r="AC17" s="360" t="n"/>
+      <c r="AD17" s="360" t="n"/>
+      <c r="AE17" s="360" t="n"/>
+      <c r="AF17" s="360" t="n"/>
+      <c r="AG17" s="360" t="n"/>
+      <c r="AH17" s="360" t="n"/>
+      <c r="AI17" s="360" t="n"/>
+      <c r="AJ17" s="360" t="n"/>
+      <c r="AK17" s="360" t="n"/>
+      <c r="AL17" s="360" t="n"/>
+      <c r="AM17" s="360" t="n"/>
+      <c r="AN17" s="360" t="n"/>
+      <c r="AO17" s="360" t="n"/>
+      <c r="AP17" s="360" t="n"/>
+      <c r="AQ17" s="360" t="n"/>
+      <c r="AR17" s="474" t="n"/>
+      <c r="AS17" s="360" t="n"/>
+      <c r="AT17" s="360" t="n"/>
+      <c r="AU17" s="360" t="n"/>
+      <c r="AV17" s="360" t="n"/>
+      <c r="AW17" s="360" t="n"/>
+      <c r="AX17" s="474" t="n"/>
+      <c r="AY17" s="360" t="n"/>
+      <c r="AZ17" s="360" t="n"/>
+      <c r="BA17" s="360" t="n"/>
+      <c r="BB17" s="494" t="n"/>
+      <c r="BC17" s="360" t="n"/>
+      <c r="BD17" s="476" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="364">
+      <c r="A18" s="491">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="409" t="n"/>
-      <c r="C18" s="410" t="n"/>
-      <c r="D18" s="367" t="inlineStr">
+      <c r="B18" s="342" t="n"/>
+      <c r="C18" s="342" t="n"/>
+      <c r="D18" s="492" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="411" t="n"/>
-      <c r="F18" s="411" t="n"/>
-      <c r="G18" s="412" t="n"/>
-      <c r="H18" s="370" t="n"/>
-      <c r="I18" s="411" t="n"/>
-      <c r="J18" s="411" t="n"/>
-      <c r="K18" s="411" t="n"/>
-      <c r="L18" s="411" t="n"/>
-      <c r="M18" s="411" t="n"/>
-      <c r="N18" s="411" t="n"/>
-      <c r="O18" s="411" t="n"/>
-      <c r="P18" s="411" t="n"/>
-      <c r="Q18" s="411" t="n"/>
-      <c r="R18" s="411" t="n"/>
-      <c r="S18" s="411" t="n"/>
-      <c r="T18" s="411" t="n"/>
-      <c r="U18" s="411" t="n"/>
-      <c r="V18" s="411" t="n"/>
-      <c r="W18" s="411" t="n"/>
-      <c r="X18" s="411" t="n"/>
-      <c r="Y18" s="411" t="n"/>
-      <c r="Z18" s="412" t="n"/>
-      <c r="AA18" s="371" t="n"/>
-      <c r="AB18" s="411" t="n"/>
-      <c r="AC18" s="411" t="n"/>
-      <c r="AD18" s="411" t="n"/>
-      <c r="AE18" s="411" t="n"/>
-      <c r="AF18" s="411" t="n"/>
-      <c r="AG18" s="411" t="n"/>
-      <c r="AH18" s="411" t="n"/>
-      <c r="AI18" s="411" t="n"/>
-      <c r="AJ18" s="411" t="n"/>
-      <c r="AK18" s="411" t="n"/>
-      <c r="AL18" s="411" t="n"/>
-      <c r="AM18" s="411" t="n"/>
-      <c r="AN18" s="411" t="n"/>
-      <c r="AO18" s="411" t="n"/>
-      <c r="AP18" s="411" t="n"/>
-      <c r="AQ18" s="412" t="n"/>
-      <c r="AR18" s="370" t="n"/>
-      <c r="AS18" s="411" t="n"/>
-      <c r="AT18" s="411" t="n"/>
-      <c r="AU18" s="411" t="n"/>
-      <c r="AV18" s="411" t="n"/>
-      <c r="AW18" s="412" t="n"/>
-      <c r="AX18" s="370" t="n"/>
-      <c r="AY18" s="411" t="n"/>
-      <c r="AZ18" s="411" t="n"/>
-      <c r="BA18" s="412" t="n"/>
-      <c r="BB18" s="372" t="n"/>
-      <c r="BC18" s="411" t="n"/>
-      <c r="BD18" s="412" t="n"/>
+      <c r="E18" s="360" t="n"/>
+      <c r="F18" s="360" t="n"/>
+      <c r="G18" s="360" t="n"/>
+      <c r="H18" s="474" t="n"/>
+      <c r="I18" s="360" t="n"/>
+      <c r="J18" s="360" t="n"/>
+      <c r="K18" s="360" t="n"/>
+      <c r="L18" s="360" t="n"/>
+      <c r="M18" s="360" t="n"/>
+      <c r="N18" s="360" t="n"/>
+      <c r="O18" s="360" t="n"/>
+      <c r="P18" s="360" t="n"/>
+      <c r="Q18" s="360" t="n"/>
+      <c r="R18" s="360" t="n"/>
+      <c r="S18" s="360" t="n"/>
+      <c r="T18" s="360" t="n"/>
+      <c r="U18" s="360" t="n"/>
+      <c r="V18" s="360" t="n"/>
+      <c r="W18" s="360" t="n"/>
+      <c r="X18" s="360" t="n"/>
+      <c r="Y18" s="360" t="n"/>
+      <c r="Z18" s="360" t="n"/>
+      <c r="AA18" s="493" t="n"/>
+      <c r="AB18" s="360" t="n"/>
+      <c r="AC18" s="360" t="n"/>
+      <c r="AD18" s="360" t="n"/>
+      <c r="AE18" s="360" t="n"/>
+      <c r="AF18" s="360" t="n"/>
+      <c r="AG18" s="360" t="n"/>
+      <c r="AH18" s="360" t="n"/>
+      <c r="AI18" s="360" t="n"/>
+      <c r="AJ18" s="360" t="n"/>
+      <c r="AK18" s="360" t="n"/>
+      <c r="AL18" s="360" t="n"/>
+      <c r="AM18" s="360" t="n"/>
+      <c r="AN18" s="360" t="n"/>
+      <c r="AO18" s="360" t="n"/>
+      <c r="AP18" s="360" t="n"/>
+      <c r="AQ18" s="360" t="n"/>
+      <c r="AR18" s="474" t="n"/>
+      <c r="AS18" s="360" t="n"/>
+      <c r="AT18" s="360" t="n"/>
+      <c r="AU18" s="360" t="n"/>
+      <c r="AV18" s="360" t="n"/>
+      <c r="AW18" s="360" t="n"/>
+      <c r="AX18" s="474" t="n"/>
+      <c r="AY18" s="360" t="n"/>
+      <c r="AZ18" s="360" t="n"/>
+      <c r="BA18" s="360" t="n"/>
+      <c r="BB18" s="494" t="n"/>
+      <c r="BC18" s="360" t="n"/>
+      <c r="BD18" s="476" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="364">
+      <c r="A19" s="491">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="409" t="n"/>
-      <c r="C19" s="410" t="n"/>
-      <c r="D19" s="367" t="inlineStr">
+      <c r="B19" s="342" t="n"/>
+      <c r="C19" s="342" t="n"/>
+      <c r="D19" s="492" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="411" t="n"/>
-      <c r="F19" s="411" t="n"/>
-      <c r="G19" s="412" t="n"/>
-      <c r="H19" s="370" t="n"/>
-      <c r="I19" s="411" t="n"/>
-      <c r="J19" s="411" t="n"/>
-      <c r="K19" s="411" t="n"/>
-      <c r="L19" s="411" t="n"/>
-      <c r="M19" s="411" t="n"/>
-      <c r="N19" s="411" t="n"/>
-      <c r="O19" s="411" t="n"/>
-      <c r="P19" s="411" t="n"/>
-      <c r="Q19" s="411" t="n"/>
-      <c r="R19" s="411" t="n"/>
-      <c r="S19" s="411" t="n"/>
-      <c r="T19" s="411" t="n"/>
-      <c r="U19" s="411" t="n"/>
-      <c r="V19" s="411" t="n"/>
-      <c r="W19" s="411" t="n"/>
-      <c r="X19" s="411" t="n"/>
-      <c r="Y19" s="411" t="n"/>
-      <c r="Z19" s="412" t="n"/>
-      <c r="AA19" s="371" t="n"/>
-      <c r="AB19" s="411" t="n"/>
-      <c r="AC19" s="411" t="n"/>
-      <c r="AD19" s="411" t="n"/>
-      <c r="AE19" s="411" t="n"/>
-      <c r="AF19" s="411" t="n"/>
-      <c r="AG19" s="411" t="n"/>
-      <c r="AH19" s="411" t="n"/>
-      <c r="AI19" s="411" t="n"/>
-      <c r="AJ19" s="411" t="n"/>
-      <c r="AK19" s="411" t="n"/>
-      <c r="AL19" s="411" t="n"/>
-      <c r="AM19" s="411" t="n"/>
-      <c r="AN19" s="411" t="n"/>
-      <c r="AO19" s="411" t="n"/>
-      <c r="AP19" s="411" t="n"/>
-      <c r="AQ19" s="412" t="n"/>
-      <c r="AR19" s="370" t="n"/>
-      <c r="AS19" s="411" t="n"/>
-      <c r="AT19" s="411" t="n"/>
-      <c r="AU19" s="411" t="n"/>
-      <c r="AV19" s="411" t="n"/>
-      <c r="AW19" s="412" t="n"/>
-      <c r="AX19" s="370" t="n"/>
-      <c r="AY19" s="411" t="n"/>
-      <c r="AZ19" s="411" t="n"/>
-      <c r="BA19" s="412" t="n"/>
-      <c r="BB19" s="372" t="n"/>
-      <c r="BC19" s="411" t="n"/>
-      <c r="BD19" s="412" t="n"/>
+      <c r="E19" s="360" t="n"/>
+      <c r="F19" s="360" t="n"/>
+      <c r="G19" s="360" t="n"/>
+      <c r="H19" s="474" t="n"/>
+      <c r="I19" s="360" t="n"/>
+      <c r="J19" s="360" t="n"/>
+      <c r="K19" s="360" t="n"/>
+      <c r="L19" s="360" t="n"/>
+      <c r="M19" s="360" t="n"/>
+      <c r="N19" s="360" t="n"/>
+      <c r="O19" s="360" t="n"/>
+      <c r="P19" s="360" t="n"/>
+      <c r="Q19" s="360" t="n"/>
+      <c r="R19" s="360" t="n"/>
+      <c r="S19" s="360" t="n"/>
+      <c r="T19" s="360" t="n"/>
+      <c r="U19" s="360" t="n"/>
+      <c r="V19" s="360" t="n"/>
+      <c r="W19" s="360" t="n"/>
+      <c r="X19" s="360" t="n"/>
+      <c r="Y19" s="360" t="n"/>
+      <c r="Z19" s="360" t="n"/>
+      <c r="AA19" s="493" t="n"/>
+      <c r="AB19" s="360" t="n"/>
+      <c r="AC19" s="360" t="n"/>
+      <c r="AD19" s="360" t="n"/>
+      <c r="AE19" s="360" t="n"/>
+      <c r="AF19" s="360" t="n"/>
+      <c r="AG19" s="360" t="n"/>
+      <c r="AH19" s="360" t="n"/>
+      <c r="AI19" s="360" t="n"/>
+      <c r="AJ19" s="360" t="n"/>
+      <c r="AK19" s="360" t="n"/>
+      <c r="AL19" s="360" t="n"/>
+      <c r="AM19" s="360" t="n"/>
+      <c r="AN19" s="360" t="n"/>
+      <c r="AO19" s="360" t="n"/>
+      <c r="AP19" s="360" t="n"/>
+      <c r="AQ19" s="360" t="n"/>
+      <c r="AR19" s="474" t="n"/>
+      <c r="AS19" s="360" t="n"/>
+      <c r="AT19" s="360" t="n"/>
+      <c r="AU19" s="360" t="n"/>
+      <c r="AV19" s="360" t="n"/>
+      <c r="AW19" s="360" t="n"/>
+      <c r="AX19" s="474" t="n"/>
+      <c r="AY19" s="360" t="n"/>
+      <c r="AZ19" s="360" t="n"/>
+      <c r="BA19" s="360" t="n"/>
+      <c r="BB19" s="494" t="n"/>
+      <c r="BC19" s="360" t="n"/>
+      <c r="BD19" s="476" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="364">
+      <c r="A20" s="491">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="409" t="n"/>
-      <c r="C20" s="410" t="n"/>
-      <c r="D20" s="367" t="inlineStr">
+      <c r="B20" s="342" t="n"/>
+      <c r="C20" s="342" t="n"/>
+      <c r="D20" s="492" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="411" t="n"/>
-      <c r="F20" s="411" t="n"/>
-      <c r="G20" s="412" t="n"/>
-      <c r="H20" s="370" t="n"/>
-      <c r="I20" s="411" t="n"/>
-      <c r="J20" s="411" t="n"/>
-      <c r="K20" s="411" t="n"/>
-      <c r="L20" s="411" t="n"/>
-      <c r="M20" s="411" t="n"/>
-      <c r="N20" s="411" t="n"/>
-      <c r="O20" s="411" t="n"/>
-      <c r="P20" s="411" t="n"/>
-      <c r="Q20" s="411" t="n"/>
-      <c r="R20" s="411" t="n"/>
-      <c r="S20" s="411" t="n"/>
-      <c r="T20" s="411" t="n"/>
-      <c r="U20" s="411" t="n"/>
-      <c r="V20" s="411" t="n"/>
-      <c r="W20" s="411" t="n"/>
-      <c r="X20" s="411" t="n"/>
-      <c r="Y20" s="411" t="n"/>
-      <c r="Z20" s="412" t="n"/>
-      <c r="AA20" s="371" t="n"/>
-      <c r="AB20" s="411" t="n"/>
-      <c r="AC20" s="411" t="n"/>
-      <c r="AD20" s="411" t="n"/>
-      <c r="AE20" s="411" t="n"/>
-      <c r="AF20" s="411" t="n"/>
-      <c r="AG20" s="411" t="n"/>
-      <c r="AH20" s="411" t="n"/>
-      <c r="AI20" s="411" t="n"/>
-      <c r="AJ20" s="411" t="n"/>
-      <c r="AK20" s="411" t="n"/>
-      <c r="AL20" s="411" t="n"/>
-      <c r="AM20" s="411" t="n"/>
-      <c r="AN20" s="411" t="n"/>
-      <c r="AO20" s="411" t="n"/>
-      <c r="AP20" s="411" t="n"/>
-      <c r="AQ20" s="412" t="n"/>
-      <c r="AR20" s="370" t="n"/>
-      <c r="AS20" s="411" t="n"/>
-      <c r="AT20" s="411" t="n"/>
-      <c r="AU20" s="411" t="n"/>
-      <c r="AV20" s="411" t="n"/>
-      <c r="AW20" s="412" t="n"/>
-      <c r="AX20" s="370" t="n"/>
-      <c r="AY20" s="411" t="n"/>
-      <c r="AZ20" s="411" t="n"/>
-      <c r="BA20" s="412" t="n"/>
-      <c r="BB20" s="372" t="n"/>
-      <c r="BC20" s="411" t="n"/>
-      <c r="BD20" s="412" t="n"/>
+      <c r="E20" s="360" t="n"/>
+      <c r="F20" s="360" t="n"/>
+      <c r="G20" s="360" t="n"/>
+      <c r="H20" s="474" t="n"/>
+      <c r="I20" s="360" t="n"/>
+      <c r="J20" s="360" t="n"/>
+      <c r="K20" s="360" t="n"/>
+      <c r="L20" s="360" t="n"/>
+      <c r="M20" s="360" t="n"/>
+      <c r="N20" s="360" t="n"/>
+      <c r="O20" s="360" t="n"/>
+      <c r="P20" s="360" t="n"/>
+      <c r="Q20" s="360" t="n"/>
+      <c r="R20" s="360" t="n"/>
+      <c r="S20" s="360" t="n"/>
+      <c r="T20" s="360" t="n"/>
+      <c r="U20" s="360" t="n"/>
+      <c r="V20" s="360" t="n"/>
+      <c r="W20" s="360" t="n"/>
+      <c r="X20" s="360" t="n"/>
+      <c r="Y20" s="360" t="n"/>
+      <c r="Z20" s="360" t="n"/>
+      <c r="AA20" s="493" t="n"/>
+      <c r="AB20" s="360" t="n"/>
+      <c r="AC20" s="360" t="n"/>
+      <c r="AD20" s="360" t="n"/>
+      <c r="AE20" s="360" t="n"/>
+      <c r="AF20" s="360" t="n"/>
+      <c r="AG20" s="360" t="n"/>
+      <c r="AH20" s="360" t="n"/>
+      <c r="AI20" s="360" t="n"/>
+      <c r="AJ20" s="360" t="n"/>
+      <c r="AK20" s="360" t="n"/>
+      <c r="AL20" s="360" t="n"/>
+      <c r="AM20" s="360" t="n"/>
+      <c r="AN20" s="360" t="n"/>
+      <c r="AO20" s="360" t="n"/>
+      <c r="AP20" s="360" t="n"/>
+      <c r="AQ20" s="360" t="n"/>
+      <c r="AR20" s="474" t="n"/>
+      <c r="AS20" s="360" t="n"/>
+      <c r="AT20" s="360" t="n"/>
+      <c r="AU20" s="360" t="n"/>
+      <c r="AV20" s="360" t="n"/>
+      <c r="AW20" s="360" t="n"/>
+      <c r="AX20" s="474" t="n"/>
+      <c r="AY20" s="360" t="n"/>
+      <c r="AZ20" s="360" t="n"/>
+      <c r="BA20" s="360" t="n"/>
+      <c r="BB20" s="494" t="n"/>
+      <c r="BC20" s="360" t="n"/>
+      <c r="BD20" s="476" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="364">
+      <c r="A21" s="491">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="409" t="n"/>
-      <c r="C21" s="410" t="n"/>
-      <c r="D21" s="367" t="inlineStr">
+      <c r="B21" s="342" t="n"/>
+      <c r="C21" s="342" t="n"/>
+      <c r="D21" s="492" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="411" t="n"/>
-      <c r="F21" s="411" t="n"/>
-      <c r="G21" s="412" t="n"/>
-      <c r="H21" s="370" t="n"/>
-      <c r="I21" s="411" t="n"/>
-      <c r="J21" s="411" t="n"/>
-      <c r="K21" s="411" t="n"/>
-      <c r="L21" s="411" t="n"/>
-      <c r="M21" s="411" t="n"/>
-      <c r="N21" s="411" t="n"/>
-      <c r="O21" s="411" t="n"/>
-      <c r="P21" s="411" t="n"/>
-      <c r="Q21" s="411" t="n"/>
-      <c r="R21" s="411" t="n"/>
-      <c r="S21" s="411" t="n"/>
-      <c r="T21" s="411" t="n"/>
-      <c r="U21" s="411" t="n"/>
-      <c r="V21" s="411" t="n"/>
-      <c r="W21" s="411" t="n"/>
-      <c r="X21" s="411" t="n"/>
-      <c r="Y21" s="411" t="n"/>
-      <c r="Z21" s="412" t="n"/>
-      <c r="AA21" s="371" t="n"/>
-      <c r="AB21" s="411" t="n"/>
-      <c r="AC21" s="411" t="n"/>
-      <c r="AD21" s="411" t="n"/>
-      <c r="AE21" s="411" t="n"/>
-      <c r="AF21" s="411" t="n"/>
-      <c r="AG21" s="411" t="n"/>
-      <c r="AH21" s="411" t="n"/>
-      <c r="AI21" s="411" t="n"/>
-      <c r="AJ21" s="411" t="n"/>
-      <c r="AK21" s="411" t="n"/>
-      <c r="AL21" s="411" t="n"/>
-      <c r="AM21" s="411" t="n"/>
-      <c r="AN21" s="411" t="n"/>
-      <c r="AO21" s="411" t="n"/>
-      <c r="AP21" s="411" t="n"/>
-      <c r="AQ21" s="412" t="n"/>
-      <c r="AR21" s="370" t="n"/>
-      <c r="AS21" s="411" t="n"/>
-      <c r="AT21" s="411" t="n"/>
-      <c r="AU21" s="411" t="n"/>
-      <c r="AV21" s="411" t="n"/>
-      <c r="AW21" s="412" t="n"/>
-      <c r="AX21" s="370" t="n"/>
-      <c r="AY21" s="411" t="n"/>
-      <c r="AZ21" s="411" t="n"/>
-      <c r="BA21" s="412" t="n"/>
-      <c r="BB21" s="372" t="n"/>
-      <c r="BC21" s="411" t="n"/>
-      <c r="BD21" s="412" t="n"/>
+      <c r="E21" s="360" t="n"/>
+      <c r="F21" s="360" t="n"/>
+      <c r="G21" s="360" t="n"/>
+      <c r="H21" s="474" t="n"/>
+      <c r="I21" s="360" t="n"/>
+      <c r="J21" s="360" t="n"/>
+      <c r="K21" s="360" t="n"/>
+      <c r="L21" s="360" t="n"/>
+      <c r="M21" s="360" t="n"/>
+      <c r="N21" s="360" t="n"/>
+      <c r="O21" s="360" t="n"/>
+      <c r="P21" s="360" t="n"/>
+      <c r="Q21" s="360" t="n"/>
+      <c r="R21" s="360" t="n"/>
+      <c r="S21" s="360" t="n"/>
+      <c r="T21" s="360" t="n"/>
+      <c r="U21" s="360" t="n"/>
+      <c r="V21" s="360" t="n"/>
+      <c r="W21" s="360" t="n"/>
+      <c r="X21" s="360" t="n"/>
+      <c r="Y21" s="360" t="n"/>
+      <c r="Z21" s="360" t="n"/>
+      <c r="AA21" s="493" t="n"/>
+      <c r="AB21" s="360" t="n"/>
+      <c r="AC21" s="360" t="n"/>
+      <c r="AD21" s="360" t="n"/>
+      <c r="AE21" s="360" t="n"/>
+      <c r="AF21" s="360" t="n"/>
+      <c r="AG21" s="360" t="n"/>
+      <c r="AH21" s="360" t="n"/>
+      <c r="AI21" s="360" t="n"/>
+      <c r="AJ21" s="360" t="n"/>
+      <c r="AK21" s="360" t="n"/>
+      <c r="AL21" s="360" t="n"/>
+      <c r="AM21" s="360" t="n"/>
+      <c r="AN21" s="360" t="n"/>
+      <c r="AO21" s="360" t="n"/>
+      <c r="AP21" s="360" t="n"/>
+      <c r="AQ21" s="360" t="n"/>
+      <c r="AR21" s="474" t="n"/>
+      <c r="AS21" s="360" t="n"/>
+      <c r="AT21" s="360" t="n"/>
+      <c r="AU21" s="360" t="n"/>
+      <c r="AV21" s="360" t="n"/>
+      <c r="AW21" s="360" t="n"/>
+      <c r="AX21" s="474" t="n"/>
+      <c r="AY21" s="360" t="n"/>
+      <c r="AZ21" s="360" t="n"/>
+      <c r="BA21" s="360" t="n"/>
+      <c r="BB21" s="494" t="n"/>
+      <c r="BC21" s="360" t="n"/>
+      <c r="BD21" s="476" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="364">
+      <c r="A22" s="495">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="409" t="n"/>
-      <c r="C22" s="410" t="n"/>
-      <c r="D22" s="367" t="inlineStr">
+      <c r="B22" s="478" t="n"/>
+      <c r="C22" s="478" t="n"/>
+      <c r="D22" s="496" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="411" t="n"/>
-      <c r="F22" s="411" t="n"/>
-      <c r="G22" s="412" t="n"/>
-      <c r="H22" s="370" t="n"/>
-      <c r="I22" s="411" t="n"/>
-      <c r="J22" s="411" t="n"/>
-      <c r="K22" s="411" t="n"/>
-      <c r="L22" s="411" t="n"/>
-      <c r="M22" s="411" t="n"/>
-      <c r="N22" s="411" t="n"/>
-      <c r="O22" s="411" t="n"/>
-      <c r="P22" s="411" t="n"/>
-      <c r="Q22" s="411" t="n"/>
-      <c r="R22" s="411" t="n"/>
-      <c r="S22" s="411" t="n"/>
-      <c r="T22" s="411" t="n"/>
-      <c r="U22" s="411" t="n"/>
-      <c r="V22" s="411" t="n"/>
-      <c r="W22" s="411" t="n"/>
-      <c r="X22" s="411" t="n"/>
-      <c r="Y22" s="411" t="n"/>
-      <c r="Z22" s="412" t="n"/>
-      <c r="AA22" s="371" t="n"/>
-      <c r="AB22" s="411" t="n"/>
-      <c r="AC22" s="411" t="n"/>
-      <c r="AD22" s="411" t="n"/>
-      <c r="AE22" s="411" t="n"/>
-      <c r="AF22" s="411" t="n"/>
-      <c r="AG22" s="411" t="n"/>
-      <c r="AH22" s="411" t="n"/>
-      <c r="AI22" s="411" t="n"/>
-      <c r="AJ22" s="411" t="n"/>
-      <c r="AK22" s="411" t="n"/>
-      <c r="AL22" s="411" t="n"/>
-      <c r="AM22" s="411" t="n"/>
-      <c r="AN22" s="411" t="n"/>
-      <c r="AO22" s="411" t="n"/>
-      <c r="AP22" s="411" t="n"/>
-      <c r="AQ22" s="412" t="n"/>
-      <c r="AR22" s="370" t="n"/>
-      <c r="AS22" s="411" t="n"/>
-      <c r="AT22" s="411" t="n"/>
-      <c r="AU22" s="411" t="n"/>
-      <c r="AV22" s="411" t="n"/>
-      <c r="AW22" s="412" t="n"/>
-      <c r="AX22" s="370" t="n"/>
-      <c r="AY22" s="411" t="n"/>
-      <c r="AZ22" s="411" t="n"/>
-      <c r="BA22" s="412" t="n"/>
-      <c r="BB22" s="372" t="n"/>
-      <c r="BC22" s="411" t="n"/>
-      <c r="BD22" s="412" t="n"/>
+      <c r="E22" s="480" t="n"/>
+      <c r="F22" s="480" t="n"/>
+      <c r="G22" s="480" t="n"/>
+      <c r="H22" s="479" t="n"/>
+      <c r="I22" s="480" t="n"/>
+      <c r="J22" s="480" t="n"/>
+      <c r="K22" s="480" t="n"/>
+      <c r="L22" s="480" t="n"/>
+      <c r="M22" s="480" t="n"/>
+      <c r="N22" s="480" t="n"/>
+      <c r="O22" s="480" t="n"/>
+      <c r="P22" s="480" t="n"/>
+      <c r="Q22" s="480" t="n"/>
+      <c r="R22" s="480" t="n"/>
+      <c r="S22" s="480" t="n"/>
+      <c r="T22" s="480" t="n"/>
+      <c r="U22" s="480" t="n"/>
+      <c r="V22" s="480" t="n"/>
+      <c r="W22" s="480" t="n"/>
+      <c r="X22" s="480" t="n"/>
+      <c r="Y22" s="480" t="n"/>
+      <c r="Z22" s="480" t="n"/>
+      <c r="AA22" s="497" t="n"/>
+      <c r="AB22" s="480" t="n"/>
+      <c r="AC22" s="480" t="n"/>
+      <c r="AD22" s="480" t="n"/>
+      <c r="AE22" s="480" t="n"/>
+      <c r="AF22" s="480" t="n"/>
+      <c r="AG22" s="480" t="n"/>
+      <c r="AH22" s="480" t="n"/>
+      <c r="AI22" s="480" t="n"/>
+      <c r="AJ22" s="480" t="n"/>
+      <c r="AK22" s="480" t="n"/>
+      <c r="AL22" s="480" t="n"/>
+      <c r="AM22" s="480" t="n"/>
+      <c r="AN22" s="480" t="n"/>
+      <c r="AO22" s="480" t="n"/>
+      <c r="AP22" s="480" t="n"/>
+      <c r="AQ22" s="480" t="n"/>
+      <c r="AR22" s="479" t="n"/>
+      <c r="AS22" s="480" t="n"/>
+      <c r="AT22" s="480" t="n"/>
+      <c r="AU22" s="480" t="n"/>
+      <c r="AV22" s="480" t="n"/>
+      <c r="AW22" s="480" t="n"/>
+      <c r="AX22" s="479" t="n"/>
+      <c r="AY22" s="480" t="n"/>
+      <c r="AZ22" s="480" t="n"/>
+      <c r="BA22" s="480" t="n"/>
+      <c r="BB22" s="498" t="n"/>
+      <c r="BC22" s="480" t="n"/>
+      <c r="BD22" s="482" t="n"/>
     </row>
-    <row r="23" ht="4" customHeight="1">
+    <row r="23" ht="3" customHeight="1">
       <c r="A23" s="373" t="n"/>
       <c r="B23" s="351" t="n"/>
       <c r="C23" s="351" t="n"/>
@@ -6727,267 +7605,267 @@
       <c r="BC23" s="351" t="n"/>
       <c r="BD23" s="351" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="352" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="464" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B24" s="403" t="n"/>
-      <c r="C24" s="403" t="n"/>
-      <c r="D24" s="403" t="n"/>
-      <c r="E24" s="403" t="n"/>
-      <c r="F24" s="403" t="n"/>
-      <c r="G24" s="403" t="n"/>
-      <c r="H24" s="403" t="n"/>
-      <c r="I24" s="403" t="n"/>
-      <c r="J24" s="403" t="n"/>
-      <c r="K24" s="403" t="n"/>
-      <c r="L24" s="403" t="n"/>
-      <c r="M24" s="403" t="n"/>
-      <c r="N24" s="403" t="n"/>
-      <c r="O24" s="403" t="n"/>
-      <c r="P24" s="403" t="n"/>
-      <c r="Q24" s="403" t="n"/>
-      <c r="R24" s="403" t="n"/>
-      <c r="S24" s="403" t="n"/>
-      <c r="T24" s="403" t="n"/>
-      <c r="U24" s="403" t="n"/>
-      <c r="V24" s="403" t="n"/>
-      <c r="W24" s="403" t="n"/>
-      <c r="X24" s="403" t="n"/>
-      <c r="Y24" s="403" t="n"/>
-      <c r="Z24" s="403" t="n"/>
-      <c r="AA24" s="403" t="n"/>
-      <c r="AB24" s="403" t="n"/>
-      <c r="AC24" s="403" t="n"/>
-      <c r="AD24" s="403" t="n"/>
-      <c r="AE24" s="403" t="n"/>
-      <c r="AF24" s="403" t="n"/>
-      <c r="AG24" s="403" t="n"/>
-      <c r="AH24" s="403" t="n"/>
-      <c r="AI24" s="403" t="n"/>
-      <c r="AJ24" s="403" t="n"/>
-      <c r="AK24" s="403" t="n"/>
-      <c r="AL24" s="403" t="n"/>
-      <c r="AM24" s="403" t="n"/>
-      <c r="AN24" s="403" t="n"/>
-      <c r="AO24" s="403" t="n"/>
-      <c r="AP24" s="403" t="n"/>
-      <c r="AQ24" s="403" t="n"/>
-      <c r="AR24" s="403" t="n"/>
-      <c r="AS24" s="403" t="n"/>
-      <c r="AT24" s="403" t="n"/>
-      <c r="AU24" s="403" t="n"/>
-      <c r="AV24" s="403" t="n"/>
-      <c r="AW24" s="403" t="n"/>
-      <c r="AX24" s="403" t="n"/>
-      <c r="AY24" s="403" t="n"/>
-      <c r="AZ24" s="403" t="n"/>
-      <c r="BA24" s="403" t="n"/>
-      <c r="BB24" s="403" t="n"/>
-      <c r="BC24" s="403" t="n"/>
-      <c r="BD24" s="404" t="n"/>
+      <c r="B24" s="465" t="n"/>
+      <c r="C24" s="465" t="n"/>
+      <c r="D24" s="465" t="n"/>
+      <c r="E24" s="465" t="n"/>
+      <c r="F24" s="465" t="n"/>
+      <c r="G24" s="465" t="n"/>
+      <c r="H24" s="465" t="n"/>
+      <c r="I24" s="465" t="n"/>
+      <c r="J24" s="465" t="n"/>
+      <c r="K24" s="465" t="n"/>
+      <c r="L24" s="465" t="n"/>
+      <c r="M24" s="465" t="n"/>
+      <c r="N24" s="465" t="n"/>
+      <c r="O24" s="465" t="n"/>
+      <c r="P24" s="465" t="n"/>
+      <c r="Q24" s="465" t="n"/>
+      <c r="R24" s="465" t="n"/>
+      <c r="S24" s="465" t="n"/>
+      <c r="T24" s="465" t="n"/>
+      <c r="U24" s="465" t="n"/>
+      <c r="V24" s="465" t="n"/>
+      <c r="W24" s="465" t="n"/>
+      <c r="X24" s="465" t="n"/>
+      <c r="Y24" s="465" t="n"/>
+      <c r="Z24" s="465" t="n"/>
+      <c r="AA24" s="465" t="n"/>
+      <c r="AB24" s="465" t="n"/>
+      <c r="AC24" s="465" t="n"/>
+      <c r="AD24" s="465" t="n"/>
+      <c r="AE24" s="465" t="n"/>
+      <c r="AF24" s="465" t="n"/>
+      <c r="AG24" s="465" t="n"/>
+      <c r="AH24" s="465" t="n"/>
+      <c r="AI24" s="465" t="n"/>
+      <c r="AJ24" s="465" t="n"/>
+      <c r="AK24" s="465" t="n"/>
+      <c r="AL24" s="465" t="n"/>
+      <c r="AM24" s="465" t="n"/>
+      <c r="AN24" s="465" t="n"/>
+      <c r="AO24" s="465" t="n"/>
+      <c r="AP24" s="465" t="n"/>
+      <c r="AQ24" s="465" t="n"/>
+      <c r="AR24" s="465" t="n"/>
+      <c r="AS24" s="465" t="n"/>
+      <c r="AT24" s="465" t="n"/>
+      <c r="AU24" s="465" t="n"/>
+      <c r="AV24" s="465" t="n"/>
+      <c r="AW24" s="465" t="n"/>
+      <c r="AX24" s="465" t="n"/>
+      <c r="AY24" s="465" t="n"/>
+      <c r="AZ24" s="465" t="n"/>
+      <c r="BA24" s="465" t="n"/>
+      <c r="BB24" s="465" t="n"/>
+      <c r="BC24" s="465" t="n"/>
+      <c r="BD24" s="466" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="353" t="inlineStr">
+      <c r="A25" s="467" t="inlineStr">
         <is>
           <t>Disposition / Release Decision</t>
         </is>
       </c>
-      <c r="B25" s="403" t="n"/>
-      <c r="C25" s="403" t="n"/>
-      <c r="D25" s="403" t="n"/>
-      <c r="E25" s="403" t="n"/>
-      <c r="F25" s="403" t="n"/>
-      <c r="G25" s="403" t="n"/>
-      <c r="H25" s="403" t="n"/>
-      <c r="I25" s="403" t="n"/>
-      <c r="J25" s="404" t="n"/>
-      <c r="K25" s="356" t="n"/>
-      <c r="L25" s="405" t="n"/>
-      <c r="M25" s="405" t="n"/>
-      <c r="N25" s="405" t="n"/>
-      <c r="O25" s="405" t="n"/>
-      <c r="P25" s="405" t="n"/>
-      <c r="Q25" s="405" t="n"/>
-      <c r="R25" s="405" t="n"/>
-      <c r="S25" s="405" t="n"/>
-      <c r="T25" s="405" t="n"/>
-      <c r="U25" s="405" t="n"/>
-      <c r="V25" s="405" t="n"/>
-      <c r="W25" s="405" t="n"/>
-      <c r="X25" s="405" t="n"/>
-      <c r="Y25" s="405" t="n"/>
-      <c r="Z25" s="405" t="n"/>
-      <c r="AA25" s="405" t="n"/>
-      <c r="AB25" s="406" t="n"/>
-      <c r="AC25" s="359" t="inlineStr">
+      <c r="B25" s="468" t="n"/>
+      <c r="C25" s="468" t="n"/>
+      <c r="D25" s="468" t="n"/>
+      <c r="E25" s="468" t="n"/>
+      <c r="F25" s="468" t="n"/>
+      <c r="G25" s="468" t="n"/>
+      <c r="H25" s="468" t="n"/>
+      <c r="I25" s="468" t="n"/>
+      <c r="J25" s="468" t="n"/>
+      <c r="K25" s="469" t="n"/>
+      <c r="L25" s="470" t="n"/>
+      <c r="M25" s="470" t="n"/>
+      <c r="N25" s="470" t="n"/>
+      <c r="O25" s="470" t="n"/>
+      <c r="P25" s="470" t="n"/>
+      <c r="Q25" s="470" t="n"/>
+      <c r="R25" s="470" t="n"/>
+      <c r="S25" s="470" t="n"/>
+      <c r="T25" s="470" t="n"/>
+      <c r="U25" s="470" t="n"/>
+      <c r="V25" s="470" t="n"/>
+      <c r="W25" s="470" t="n"/>
+      <c r="X25" s="470" t="n"/>
+      <c r="Y25" s="470" t="n"/>
+      <c r="Z25" s="470" t="n"/>
+      <c r="AA25" s="470" t="n"/>
+      <c r="AB25" s="470" t="n"/>
+      <c r="AC25" s="471" t="inlineStr">
         <is>
           <t>Linked NCR / Concession</t>
         </is>
       </c>
-      <c r="AD25" s="403" t="n"/>
-      <c r="AE25" s="403" t="n"/>
-      <c r="AF25" s="403" t="n"/>
-      <c r="AG25" s="403" t="n"/>
-      <c r="AH25" s="403" t="n"/>
-      <c r="AI25" s="403" t="n"/>
-      <c r="AJ25" s="403" t="n"/>
-      <c r="AK25" s="403" t="n"/>
-      <c r="AL25" s="404" t="n"/>
-      <c r="AM25" s="356" t="n"/>
-      <c r="AN25" s="405" t="n"/>
-      <c r="AO25" s="405" t="n"/>
-      <c r="AP25" s="405" t="n"/>
-      <c r="AQ25" s="405" t="n"/>
-      <c r="AR25" s="405" t="n"/>
-      <c r="AS25" s="405" t="n"/>
-      <c r="AT25" s="405" t="n"/>
-      <c r="AU25" s="405" t="n"/>
-      <c r="AV25" s="405" t="n"/>
-      <c r="AW25" s="405" t="n"/>
-      <c r="AX25" s="405" t="n"/>
-      <c r="AY25" s="405" t="n"/>
-      <c r="AZ25" s="405" t="n"/>
-      <c r="BA25" s="405" t="n"/>
-      <c r="BB25" s="405" t="n"/>
-      <c r="BC25" s="405" t="n"/>
-      <c r="BD25" s="406" t="n"/>
+      <c r="AD25" s="468" t="n"/>
+      <c r="AE25" s="468" t="n"/>
+      <c r="AF25" s="468" t="n"/>
+      <c r="AG25" s="468" t="n"/>
+      <c r="AH25" s="468" t="n"/>
+      <c r="AI25" s="468" t="n"/>
+      <c r="AJ25" s="468" t="n"/>
+      <c r="AK25" s="468" t="n"/>
+      <c r="AL25" s="468" t="n"/>
+      <c r="AM25" s="469" t="n"/>
+      <c r="AN25" s="470" t="n"/>
+      <c r="AO25" s="470" t="n"/>
+      <c r="AP25" s="470" t="n"/>
+      <c r="AQ25" s="470" t="n"/>
+      <c r="AR25" s="470" t="n"/>
+      <c r="AS25" s="470" t="n"/>
+      <c r="AT25" s="470" t="n"/>
+      <c r="AU25" s="470" t="n"/>
+      <c r="AV25" s="470" t="n"/>
+      <c r="AW25" s="470" t="n"/>
+      <c r="AX25" s="470" t="n"/>
+      <c r="AY25" s="470" t="n"/>
+      <c r="AZ25" s="470" t="n"/>
+      <c r="BA25" s="470" t="n"/>
+      <c r="BB25" s="470" t="n"/>
+      <c r="BC25" s="470" t="n"/>
+      <c r="BD25" s="472" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="353" t="inlineStr">
+      <c r="A26" s="473" t="inlineStr">
         <is>
           <t>Cleanliness / Packaging Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="403" t="n"/>
-      <c r="C26" s="403" t="n"/>
-      <c r="D26" s="403" t="n"/>
-      <c r="E26" s="403" t="n"/>
-      <c r="F26" s="403" t="n"/>
-      <c r="G26" s="403" t="n"/>
-      <c r="H26" s="403" t="n"/>
-      <c r="I26" s="403" t="n"/>
-      <c r="J26" s="404" t="n"/>
-      <c r="K26" s="356" t="n"/>
-      <c r="L26" s="405" t="n"/>
-      <c r="M26" s="405" t="n"/>
-      <c r="N26" s="405" t="n"/>
-      <c r="O26" s="405" t="n"/>
-      <c r="P26" s="405" t="n"/>
-      <c r="Q26" s="405" t="n"/>
-      <c r="R26" s="405" t="n"/>
-      <c r="S26" s="405" t="n"/>
-      <c r="T26" s="405" t="n"/>
-      <c r="U26" s="405" t="n"/>
-      <c r="V26" s="405" t="n"/>
-      <c r="W26" s="405" t="n"/>
-      <c r="X26" s="405" t="n"/>
-      <c r="Y26" s="405" t="n"/>
-      <c r="Z26" s="405" t="n"/>
-      <c r="AA26" s="405" t="n"/>
-      <c r="AB26" s="406" t="n"/>
-      <c r="AC26" s="359" t="inlineStr">
+      <c r="B26" s="342" t="n"/>
+      <c r="C26" s="342" t="n"/>
+      <c r="D26" s="342" t="n"/>
+      <c r="E26" s="342" t="n"/>
+      <c r="F26" s="342" t="n"/>
+      <c r="G26" s="342" t="n"/>
+      <c r="H26" s="342" t="n"/>
+      <c r="I26" s="342" t="n"/>
+      <c r="J26" s="342" t="n"/>
+      <c r="K26" s="474" t="n"/>
+      <c r="L26" s="360" t="n"/>
+      <c r="M26" s="360" t="n"/>
+      <c r="N26" s="360" t="n"/>
+      <c r="O26" s="360" t="n"/>
+      <c r="P26" s="360" t="n"/>
+      <c r="Q26" s="360" t="n"/>
+      <c r="R26" s="360" t="n"/>
+      <c r="S26" s="360" t="n"/>
+      <c r="T26" s="360" t="n"/>
+      <c r="U26" s="360" t="n"/>
+      <c r="V26" s="360" t="n"/>
+      <c r="W26" s="360" t="n"/>
+      <c r="X26" s="360" t="n"/>
+      <c r="Y26" s="360" t="n"/>
+      <c r="Z26" s="360" t="n"/>
+      <c r="AA26" s="360" t="n"/>
+      <c r="AB26" s="360" t="n"/>
+      <c r="AC26" s="475" t="inlineStr">
         <is>
           <t>Label / Doc Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="AD26" s="403" t="n"/>
-      <c r="AE26" s="403" t="n"/>
-      <c r="AF26" s="403" t="n"/>
-      <c r="AG26" s="403" t="n"/>
-      <c r="AH26" s="403" t="n"/>
-      <c r="AI26" s="403" t="n"/>
-      <c r="AJ26" s="403" t="n"/>
-      <c r="AK26" s="403" t="n"/>
-      <c r="AL26" s="404" t="n"/>
-      <c r="AM26" s="356" t="n"/>
-      <c r="AN26" s="405" t="n"/>
-      <c r="AO26" s="405" t="n"/>
-      <c r="AP26" s="405" t="n"/>
-      <c r="AQ26" s="405" t="n"/>
-      <c r="AR26" s="405" t="n"/>
-      <c r="AS26" s="405" t="n"/>
-      <c r="AT26" s="405" t="n"/>
-      <c r="AU26" s="405" t="n"/>
-      <c r="AV26" s="405" t="n"/>
-      <c r="AW26" s="405" t="n"/>
-      <c r="AX26" s="405" t="n"/>
-      <c r="AY26" s="405" t="n"/>
-      <c r="AZ26" s="405" t="n"/>
-      <c r="BA26" s="405" t="n"/>
-      <c r="BB26" s="405" t="n"/>
-      <c r="BC26" s="405" t="n"/>
-      <c r="BD26" s="406" t="n"/>
+      <c r="AD26" s="342" t="n"/>
+      <c r="AE26" s="342" t="n"/>
+      <c r="AF26" s="342" t="n"/>
+      <c r="AG26" s="342" t="n"/>
+      <c r="AH26" s="342" t="n"/>
+      <c r="AI26" s="342" t="n"/>
+      <c r="AJ26" s="342" t="n"/>
+      <c r="AK26" s="342" t="n"/>
+      <c r="AL26" s="342" t="n"/>
+      <c r="AM26" s="474" t="n"/>
+      <c r="AN26" s="360" t="n"/>
+      <c r="AO26" s="360" t="n"/>
+      <c r="AP26" s="360" t="n"/>
+      <c r="AQ26" s="360" t="n"/>
+      <c r="AR26" s="360" t="n"/>
+      <c r="AS26" s="360" t="n"/>
+      <c r="AT26" s="360" t="n"/>
+      <c r="AU26" s="360" t="n"/>
+      <c r="AV26" s="360" t="n"/>
+      <c r="AW26" s="360" t="n"/>
+      <c r="AX26" s="360" t="n"/>
+      <c r="AY26" s="360" t="n"/>
+      <c r="AZ26" s="360" t="n"/>
+      <c r="BA26" s="360" t="n"/>
+      <c r="BB26" s="360" t="n"/>
+      <c r="BC26" s="360" t="n"/>
+      <c r="BD26" s="476" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="353" t="inlineStr">
+      <c r="A27" s="477" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="B27" s="403" t="n"/>
-      <c r="C27" s="403" t="n"/>
-      <c r="D27" s="403" t="n"/>
-      <c r="E27" s="403" t="n"/>
-      <c r="F27" s="403" t="n"/>
-      <c r="G27" s="403" t="n"/>
-      <c r="H27" s="403" t="n"/>
-      <c r="I27" s="403" t="n"/>
-      <c r="J27" s="404" t="n"/>
-      <c r="K27" s="356" t="n"/>
-      <c r="L27" s="405" t="n"/>
-      <c r="M27" s="405" t="n"/>
-      <c r="N27" s="405" t="n"/>
-      <c r="O27" s="405" t="n"/>
-      <c r="P27" s="405" t="n"/>
-      <c r="Q27" s="405" t="n"/>
-      <c r="R27" s="405" t="n"/>
-      <c r="S27" s="405" t="n"/>
-      <c r="T27" s="405" t="n"/>
-      <c r="U27" s="405" t="n"/>
-      <c r="V27" s="405" t="n"/>
-      <c r="W27" s="405" t="n"/>
-      <c r="X27" s="405" t="n"/>
-      <c r="Y27" s="405" t="n"/>
-      <c r="Z27" s="405" t="n"/>
-      <c r="AA27" s="405" t="n"/>
-      <c r="AB27" s="406" t="n"/>
-      <c r="AC27" s="359" t="inlineStr">
+      <c r="B27" s="478" t="n"/>
+      <c r="C27" s="478" t="n"/>
+      <c r="D27" s="478" t="n"/>
+      <c r="E27" s="478" t="n"/>
+      <c r="F27" s="478" t="n"/>
+      <c r="G27" s="478" t="n"/>
+      <c r="H27" s="478" t="n"/>
+      <c r="I27" s="478" t="n"/>
+      <c r="J27" s="478" t="n"/>
+      <c r="K27" s="479" t="n"/>
+      <c r="L27" s="480" t="n"/>
+      <c r="M27" s="480" t="n"/>
+      <c r="N27" s="480" t="n"/>
+      <c r="O27" s="480" t="n"/>
+      <c r="P27" s="480" t="n"/>
+      <c r="Q27" s="480" t="n"/>
+      <c r="R27" s="480" t="n"/>
+      <c r="S27" s="480" t="n"/>
+      <c r="T27" s="480" t="n"/>
+      <c r="U27" s="480" t="n"/>
+      <c r="V27" s="480" t="n"/>
+      <c r="W27" s="480" t="n"/>
+      <c r="X27" s="480" t="n"/>
+      <c r="Y27" s="480" t="n"/>
+      <c r="Z27" s="480" t="n"/>
+      <c r="AA27" s="480" t="n"/>
+      <c r="AB27" s="480" t="n"/>
+      <c r="AC27" s="481" t="inlineStr">
         <is>
           <t>Closeout Status</t>
         </is>
       </c>
-      <c r="AD27" s="403" t="n"/>
-      <c r="AE27" s="403" t="n"/>
-      <c r="AF27" s="403" t="n"/>
-      <c r="AG27" s="403" t="n"/>
-      <c r="AH27" s="403" t="n"/>
-      <c r="AI27" s="403" t="n"/>
-      <c r="AJ27" s="403" t="n"/>
-      <c r="AK27" s="403" t="n"/>
-      <c r="AL27" s="404" t="n"/>
-      <c r="AM27" s="356" t="n"/>
-      <c r="AN27" s="405" t="n"/>
-      <c r="AO27" s="405" t="n"/>
-      <c r="AP27" s="405" t="n"/>
-      <c r="AQ27" s="405" t="n"/>
-      <c r="AR27" s="405" t="n"/>
-      <c r="AS27" s="405" t="n"/>
-      <c r="AT27" s="405" t="n"/>
-      <c r="AU27" s="405" t="n"/>
-      <c r="AV27" s="405" t="n"/>
-      <c r="AW27" s="405" t="n"/>
-      <c r="AX27" s="405" t="n"/>
-      <c r="AY27" s="405" t="n"/>
-      <c r="AZ27" s="405" t="n"/>
-      <c r="BA27" s="405" t="n"/>
-      <c r="BB27" s="405" t="n"/>
-      <c r="BC27" s="405" t="n"/>
-      <c r="BD27" s="406" t="n"/>
+      <c r="AD27" s="478" t="n"/>
+      <c r="AE27" s="478" t="n"/>
+      <c r="AF27" s="478" t="n"/>
+      <c r="AG27" s="478" t="n"/>
+      <c r="AH27" s="478" t="n"/>
+      <c r="AI27" s="478" t="n"/>
+      <c r="AJ27" s="478" t="n"/>
+      <c r="AK27" s="478" t="n"/>
+      <c r="AL27" s="478" t="n"/>
+      <c r="AM27" s="479" t="n"/>
+      <c r="AN27" s="480" t="n"/>
+      <c r="AO27" s="480" t="n"/>
+      <c r="AP27" s="480" t="n"/>
+      <c r="AQ27" s="480" t="n"/>
+      <c r="AR27" s="480" t="n"/>
+      <c r="AS27" s="480" t="n"/>
+      <c r="AT27" s="480" t="n"/>
+      <c r="AU27" s="480" t="n"/>
+      <c r="AV27" s="480" t="n"/>
+      <c r="AW27" s="480" t="n"/>
+      <c r="AX27" s="480" t="n"/>
+      <c r="AY27" s="480" t="n"/>
+      <c r="AZ27" s="480" t="n"/>
+      <c r="BA27" s="480" t="n"/>
+      <c r="BB27" s="480" t="n"/>
+      <c r="BC27" s="480" t="n"/>
+      <c r="BD27" s="482" t="n"/>
     </row>
-    <row r="28" ht="4" customHeight="1">
+    <row r="28" ht="3" customHeight="1">
       <c r="A28" s="373" t="n"/>
       <c r="B28" s="351" t="n"/>
       <c r="C28" s="351" t="n"/>
@@ -7045,325 +7923,325 @@
       <c r="BC28" s="351" t="n"/>
       <c r="BD28" s="351" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="352" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="464" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="403" t="n"/>
-      <c r="C29" s="403" t="n"/>
-      <c r="D29" s="403" t="n"/>
-      <c r="E29" s="403" t="n"/>
-      <c r="F29" s="403" t="n"/>
-      <c r="G29" s="403" t="n"/>
-      <c r="H29" s="403" t="n"/>
-      <c r="I29" s="403" t="n"/>
-      <c r="J29" s="403" t="n"/>
-      <c r="K29" s="403" t="n"/>
-      <c r="L29" s="403" t="n"/>
-      <c r="M29" s="403" t="n"/>
-      <c r="N29" s="403" t="n"/>
-      <c r="O29" s="403" t="n"/>
-      <c r="P29" s="403" t="n"/>
-      <c r="Q29" s="403" t="n"/>
-      <c r="R29" s="403" t="n"/>
-      <c r="S29" s="403" t="n"/>
-      <c r="T29" s="403" t="n"/>
-      <c r="U29" s="403" t="n"/>
-      <c r="V29" s="403" t="n"/>
-      <c r="W29" s="403" t="n"/>
-      <c r="X29" s="403" t="n"/>
-      <c r="Y29" s="403" t="n"/>
-      <c r="Z29" s="403" t="n"/>
-      <c r="AA29" s="403" t="n"/>
-      <c r="AB29" s="403" t="n"/>
-      <c r="AC29" s="403" t="n"/>
-      <c r="AD29" s="403" t="n"/>
-      <c r="AE29" s="403" t="n"/>
-      <c r="AF29" s="403" t="n"/>
-      <c r="AG29" s="403" t="n"/>
-      <c r="AH29" s="403" t="n"/>
-      <c r="AI29" s="403" t="n"/>
-      <c r="AJ29" s="403" t="n"/>
-      <c r="AK29" s="403" t="n"/>
-      <c r="AL29" s="403" t="n"/>
-      <c r="AM29" s="403" t="n"/>
-      <c r="AN29" s="403" t="n"/>
-      <c r="AO29" s="403" t="n"/>
-      <c r="AP29" s="403" t="n"/>
-      <c r="AQ29" s="403" t="n"/>
-      <c r="AR29" s="403" t="n"/>
-      <c r="AS29" s="403" t="n"/>
-      <c r="AT29" s="403" t="n"/>
-      <c r="AU29" s="403" t="n"/>
-      <c r="AV29" s="403" t="n"/>
-      <c r="AW29" s="403" t="n"/>
-      <c r="AX29" s="403" t="n"/>
-      <c r="AY29" s="403" t="n"/>
-      <c r="AZ29" s="403" t="n"/>
-      <c r="BA29" s="403" t="n"/>
-      <c r="BB29" s="403" t="n"/>
-      <c r="BC29" s="403" t="n"/>
-      <c r="BD29" s="404" t="n"/>
+      <c r="B29" s="465" t="n"/>
+      <c r="C29" s="465" t="n"/>
+      <c r="D29" s="465" t="n"/>
+      <c r="E29" s="465" t="n"/>
+      <c r="F29" s="465" t="n"/>
+      <c r="G29" s="465" t="n"/>
+      <c r="H29" s="465" t="n"/>
+      <c r="I29" s="465" t="n"/>
+      <c r="J29" s="465" t="n"/>
+      <c r="K29" s="465" t="n"/>
+      <c r="L29" s="465" t="n"/>
+      <c r="M29" s="465" t="n"/>
+      <c r="N29" s="465" t="n"/>
+      <c r="O29" s="465" t="n"/>
+      <c r="P29" s="465" t="n"/>
+      <c r="Q29" s="465" t="n"/>
+      <c r="R29" s="465" t="n"/>
+      <c r="S29" s="465" t="n"/>
+      <c r="T29" s="465" t="n"/>
+      <c r="U29" s="465" t="n"/>
+      <c r="V29" s="465" t="n"/>
+      <c r="W29" s="465" t="n"/>
+      <c r="X29" s="465" t="n"/>
+      <c r="Y29" s="465" t="n"/>
+      <c r="Z29" s="465" t="n"/>
+      <c r="AA29" s="465" t="n"/>
+      <c r="AB29" s="465" t="n"/>
+      <c r="AC29" s="465" t="n"/>
+      <c r="AD29" s="465" t="n"/>
+      <c r="AE29" s="465" t="n"/>
+      <c r="AF29" s="465" t="n"/>
+      <c r="AG29" s="465" t="n"/>
+      <c r="AH29" s="465" t="n"/>
+      <c r="AI29" s="465" t="n"/>
+      <c r="AJ29" s="465" t="n"/>
+      <c r="AK29" s="465" t="n"/>
+      <c r="AL29" s="465" t="n"/>
+      <c r="AM29" s="465" t="n"/>
+      <c r="AN29" s="465" t="n"/>
+      <c r="AO29" s="465" t="n"/>
+      <c r="AP29" s="465" t="n"/>
+      <c r="AQ29" s="465" t="n"/>
+      <c r="AR29" s="465" t="n"/>
+      <c r="AS29" s="465" t="n"/>
+      <c r="AT29" s="465" t="n"/>
+      <c r="AU29" s="465" t="n"/>
+      <c r="AV29" s="465" t="n"/>
+      <c r="AW29" s="465" t="n"/>
+      <c r="AX29" s="465" t="n"/>
+      <c r="AY29" s="465" t="n"/>
+      <c r="AZ29" s="465" t="n"/>
+      <c r="BA29" s="465" t="n"/>
+      <c r="BB29" s="465" t="n"/>
+      <c r="BC29" s="465" t="n"/>
+      <c r="BD29" s="466" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="379" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="487" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="398" t="n"/>
-      <c r="C30" s="398" t="n"/>
-      <c r="D30" s="398" t="n"/>
-      <c r="E30" s="398" t="n"/>
-      <c r="F30" s="398" t="n"/>
-      <c r="G30" s="398" t="n"/>
-      <c r="H30" s="398" t="n"/>
-      <c r="I30" s="398" t="n"/>
-      <c r="J30" s="398" t="n"/>
-      <c r="K30" s="398" t="n"/>
-      <c r="L30" s="398" t="n"/>
-      <c r="M30" s="398" t="n"/>
-      <c r="N30" s="398" t="n"/>
-      <c r="O30" s="398" t="n"/>
-      <c r="P30" s="398" t="n"/>
-      <c r="Q30" s="398" t="n"/>
-      <c r="R30" s="399" t="n"/>
-      <c r="S30" s="380" t="inlineStr">
+      <c r="B30" s="468" t="n"/>
+      <c r="C30" s="468" t="n"/>
+      <c r="D30" s="468" t="n"/>
+      <c r="E30" s="468" t="n"/>
+      <c r="F30" s="468" t="n"/>
+      <c r="G30" s="468" t="n"/>
+      <c r="H30" s="468" t="n"/>
+      <c r="I30" s="468" t="n"/>
+      <c r="J30" s="468" t="n"/>
+      <c r="K30" s="468" t="n"/>
+      <c r="L30" s="468" t="n"/>
+      <c r="M30" s="468" t="n"/>
+      <c r="N30" s="468" t="n"/>
+      <c r="O30" s="468" t="n"/>
+      <c r="P30" s="468" t="n"/>
+      <c r="Q30" s="468" t="n"/>
+      <c r="R30" s="468" t="n"/>
+      <c r="S30" s="499" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="398" t="n"/>
-      <c r="U30" s="398" t="n"/>
-      <c r="V30" s="398" t="n"/>
-      <c r="W30" s="398" t="n"/>
-      <c r="X30" s="398" t="n"/>
-      <c r="Y30" s="398" t="n"/>
-      <c r="Z30" s="398" t="n"/>
-      <c r="AA30" s="398" t="n"/>
-      <c r="AB30" s="398" t="n"/>
-      <c r="AC30" s="398" t="n"/>
-      <c r="AD30" s="398" t="n"/>
-      <c r="AE30" s="398" t="n"/>
-      <c r="AF30" s="398" t="n"/>
-      <c r="AG30" s="398" t="n"/>
-      <c r="AH30" s="398" t="n"/>
-      <c r="AI30" s="398" t="n"/>
-      <c r="AJ30" s="398" t="n"/>
-      <c r="AK30" s="381" t="inlineStr">
+      <c r="T30" s="468" t="n"/>
+      <c r="U30" s="468" t="n"/>
+      <c r="V30" s="468" t="n"/>
+      <c r="W30" s="468" t="n"/>
+      <c r="X30" s="468" t="n"/>
+      <c r="Y30" s="468" t="n"/>
+      <c r="Z30" s="468" t="n"/>
+      <c r="AA30" s="468" t="n"/>
+      <c r="AB30" s="468" t="n"/>
+      <c r="AC30" s="468" t="n"/>
+      <c r="AD30" s="468" t="n"/>
+      <c r="AE30" s="468" t="n"/>
+      <c r="AF30" s="468" t="n"/>
+      <c r="AG30" s="468" t="n"/>
+      <c r="AH30" s="468" t="n"/>
+      <c r="AI30" s="468" t="n"/>
+      <c r="AJ30" s="468" t="n"/>
+      <c r="AK30" s="499" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="398" t="n"/>
-      <c r="AM30" s="398" t="n"/>
-      <c r="AN30" s="398" t="n"/>
-      <c r="AO30" s="398" t="n"/>
-      <c r="AP30" s="398" t="n"/>
-      <c r="AQ30" s="398" t="n"/>
-      <c r="AR30" s="398" t="n"/>
-      <c r="AS30" s="398" t="n"/>
-      <c r="AT30" s="398" t="n"/>
-      <c r="AU30" s="398" t="n"/>
-      <c r="AV30" s="398" t="n"/>
-      <c r="AW30" s="398" t="n"/>
-      <c r="AX30" s="398" t="n"/>
-      <c r="AY30" s="398" t="n"/>
-      <c r="AZ30" s="398" t="n"/>
-      <c r="BA30" s="398" t="n"/>
-      <c r="BB30" s="398" t="n"/>
-      <c r="BC30" s="398" t="n"/>
-      <c r="BD30" s="399" t="n"/>
+      <c r="AL30" s="468" t="n"/>
+      <c r="AM30" s="468" t="n"/>
+      <c r="AN30" s="468" t="n"/>
+      <c r="AO30" s="468" t="n"/>
+      <c r="AP30" s="468" t="n"/>
+      <c r="AQ30" s="468" t="n"/>
+      <c r="AR30" s="468" t="n"/>
+      <c r="AS30" s="468" t="n"/>
+      <c r="AT30" s="468" t="n"/>
+      <c r="AU30" s="468" t="n"/>
+      <c r="AV30" s="468" t="n"/>
+      <c r="AW30" s="468" t="n"/>
+      <c r="AX30" s="468" t="n"/>
+      <c r="AY30" s="468" t="n"/>
+      <c r="AZ30" s="468" t="n"/>
+      <c r="BA30" s="468" t="n"/>
+      <c r="BB30" s="468" t="n"/>
+      <c r="BC30" s="468" t="n"/>
+      <c r="BD30" s="500" t="n"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="382" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="501" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="413" t="n"/>
-      <c r="C31" s="413" t="n"/>
-      <c r="D31" s="413" t="n"/>
-      <c r="E31" s="413" t="n"/>
-      <c r="F31" s="413" t="n"/>
-      <c r="G31" s="413" t="n"/>
-      <c r="H31" s="413" t="n"/>
-      <c r="I31" s="413" t="n"/>
-      <c r="J31" s="413" t="n"/>
-      <c r="K31" s="413" t="n"/>
-      <c r="L31" s="413" t="n"/>
-      <c r="M31" s="413" t="n"/>
-      <c r="N31" s="413" t="n"/>
-      <c r="O31" s="413" t="n"/>
-      <c r="P31" s="413" t="n"/>
-      <c r="Q31" s="413" t="n"/>
-      <c r="R31" s="414" t="n"/>
-      <c r="S31" s="382" t="inlineStr">
+      <c r="B31" s="360" t="n"/>
+      <c r="C31" s="360" t="n"/>
+      <c r="D31" s="360" t="n"/>
+      <c r="E31" s="360" t="n"/>
+      <c r="F31" s="360" t="n"/>
+      <c r="G31" s="360" t="n"/>
+      <c r="H31" s="360" t="n"/>
+      <c r="I31" s="360" t="n"/>
+      <c r="J31" s="360" t="n"/>
+      <c r="K31" s="360" t="n"/>
+      <c r="L31" s="360" t="n"/>
+      <c r="M31" s="360" t="n"/>
+      <c r="N31" s="360" t="n"/>
+      <c r="O31" s="360" t="n"/>
+      <c r="P31" s="360" t="n"/>
+      <c r="Q31" s="360" t="n"/>
+      <c r="R31" s="360" t="n"/>
+      <c r="S31" s="502" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="413" t="n"/>
-      <c r="U31" s="413" t="n"/>
-      <c r="V31" s="413" t="n"/>
-      <c r="W31" s="413" t="n"/>
-      <c r="X31" s="413" t="n"/>
-      <c r="Y31" s="413" t="n"/>
-      <c r="Z31" s="413" t="n"/>
-      <c r="AA31" s="413" t="n"/>
-      <c r="AB31" s="413" t="n"/>
-      <c r="AC31" s="413" t="n"/>
-      <c r="AD31" s="413" t="n"/>
-      <c r="AE31" s="413" t="n"/>
-      <c r="AF31" s="413" t="n"/>
-      <c r="AG31" s="413" t="n"/>
-      <c r="AH31" s="413" t="n"/>
-      <c r="AI31" s="413" t="n"/>
-      <c r="AJ31" s="414" t="n"/>
-      <c r="AK31" s="382" t="inlineStr">
+      <c r="T31" s="360" t="n"/>
+      <c r="U31" s="360" t="n"/>
+      <c r="V31" s="360" t="n"/>
+      <c r="W31" s="360" t="n"/>
+      <c r="X31" s="360" t="n"/>
+      <c r="Y31" s="360" t="n"/>
+      <c r="Z31" s="360" t="n"/>
+      <c r="AA31" s="360" t="n"/>
+      <c r="AB31" s="360" t="n"/>
+      <c r="AC31" s="360" t="n"/>
+      <c r="AD31" s="360" t="n"/>
+      <c r="AE31" s="360" t="n"/>
+      <c r="AF31" s="360" t="n"/>
+      <c r="AG31" s="360" t="n"/>
+      <c r="AH31" s="360" t="n"/>
+      <c r="AI31" s="360" t="n"/>
+      <c r="AJ31" s="360" t="n"/>
+      <c r="AK31" s="502" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="413" t="n"/>
-      <c r="AM31" s="413" t="n"/>
-      <c r="AN31" s="413" t="n"/>
-      <c r="AO31" s="413" t="n"/>
-      <c r="AP31" s="413" t="n"/>
-      <c r="AQ31" s="413" t="n"/>
-      <c r="AR31" s="413" t="n"/>
-      <c r="AS31" s="413" t="n"/>
-      <c r="AT31" s="413" t="n"/>
-      <c r="AU31" s="413" t="n"/>
-      <c r="AV31" s="413" t="n"/>
-      <c r="AW31" s="413" t="n"/>
-      <c r="AX31" s="413" t="n"/>
-      <c r="AY31" s="413" t="n"/>
-      <c r="AZ31" s="413" t="n"/>
-      <c r="BA31" s="413" t="n"/>
-      <c r="BB31" s="413" t="n"/>
-      <c r="BC31" s="413" t="n"/>
-      <c r="BD31" s="414" t="n"/>
+      <c r="AL31" s="360" t="n"/>
+      <c r="AM31" s="360" t="n"/>
+      <c r="AN31" s="360" t="n"/>
+      <c r="AO31" s="360" t="n"/>
+      <c r="AP31" s="360" t="n"/>
+      <c r="AQ31" s="360" t="n"/>
+      <c r="AR31" s="360" t="n"/>
+      <c r="AS31" s="360" t="n"/>
+      <c r="AT31" s="360" t="n"/>
+      <c r="AU31" s="360" t="n"/>
+      <c r="AV31" s="360" t="n"/>
+      <c r="AW31" s="360" t="n"/>
+      <c r="AX31" s="360" t="n"/>
+      <c r="AY31" s="360" t="n"/>
+      <c r="AZ31" s="360" t="n"/>
+      <c r="BA31" s="360" t="n"/>
+      <c r="BB31" s="360" t="n"/>
+      <c r="BC31" s="360" t="n"/>
+      <c r="BD31" s="476" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="415" t="n"/>
-      <c r="B32" s="386" t="n"/>
-      <c r="C32" s="386" t="n"/>
-      <c r="D32" s="386" t="n"/>
-      <c r="E32" s="386" t="n"/>
-      <c r="F32" s="386" t="n"/>
-      <c r="G32" s="386" t="n"/>
-      <c r="H32" s="386" t="n"/>
-      <c r="I32" s="386" t="n"/>
-      <c r="J32" s="386" t="n"/>
-      <c r="K32" s="386" t="n"/>
-      <c r="L32" s="386" t="n"/>
-      <c r="M32" s="386" t="n"/>
-      <c r="N32" s="386" t="n"/>
-      <c r="O32" s="386" t="n"/>
-      <c r="P32" s="386" t="n"/>
-      <c r="Q32" s="386" t="n"/>
-      <c r="R32" s="416" t="n"/>
-      <c r="S32" s="415" t="n"/>
-      <c r="T32" s="386" t="n"/>
-      <c r="U32" s="386" t="n"/>
-      <c r="V32" s="386" t="n"/>
-      <c r="W32" s="386" t="n"/>
-      <c r="X32" s="386" t="n"/>
-      <c r="Y32" s="386" t="n"/>
-      <c r="Z32" s="386" t="n"/>
-      <c r="AA32" s="386" t="n"/>
-      <c r="AB32" s="386" t="n"/>
-      <c r="AC32" s="386" t="n"/>
-      <c r="AD32" s="386" t="n"/>
-      <c r="AE32" s="386" t="n"/>
-      <c r="AF32" s="386" t="n"/>
-      <c r="AG32" s="386" t="n"/>
-      <c r="AH32" s="386" t="n"/>
-      <c r="AI32" s="386" t="n"/>
-      <c r="AJ32" s="416" t="n"/>
-      <c r="AK32" s="415" t="n"/>
-      <c r="AL32" s="386" t="n"/>
-      <c r="AM32" s="386" t="n"/>
-      <c r="AN32" s="386" t="n"/>
-      <c r="AO32" s="386" t="n"/>
-      <c r="AP32" s="386" t="n"/>
-      <c r="AQ32" s="386" t="n"/>
-      <c r="AR32" s="386" t="n"/>
-      <c r="AS32" s="386" t="n"/>
-      <c r="AT32" s="386" t="n"/>
-      <c r="AU32" s="386" t="n"/>
-      <c r="AV32" s="386" t="n"/>
-      <c r="AW32" s="386" t="n"/>
-      <c r="AX32" s="386" t="n"/>
-      <c r="AY32" s="386" t="n"/>
-      <c r="AZ32" s="386" t="n"/>
-      <c r="BA32" s="386" t="n"/>
-      <c r="BB32" s="386" t="n"/>
-      <c r="BC32" s="386" t="n"/>
-      <c r="BD32" s="416" t="n"/>
+      <c r="A32" s="503" t="n"/>
+      <c r="B32" s="360" t="n"/>
+      <c r="C32" s="360" t="n"/>
+      <c r="D32" s="360" t="n"/>
+      <c r="E32" s="360" t="n"/>
+      <c r="F32" s="360" t="n"/>
+      <c r="G32" s="360" t="n"/>
+      <c r="H32" s="360" t="n"/>
+      <c r="I32" s="360" t="n"/>
+      <c r="J32" s="360" t="n"/>
+      <c r="K32" s="360" t="n"/>
+      <c r="L32" s="360" t="n"/>
+      <c r="M32" s="360" t="n"/>
+      <c r="N32" s="360" t="n"/>
+      <c r="O32" s="360" t="n"/>
+      <c r="P32" s="360" t="n"/>
+      <c r="Q32" s="360" t="n"/>
+      <c r="R32" s="360" t="n"/>
+      <c r="S32" s="504" t="n"/>
+      <c r="T32" s="360" t="n"/>
+      <c r="U32" s="360" t="n"/>
+      <c r="V32" s="360" t="n"/>
+      <c r="W32" s="360" t="n"/>
+      <c r="X32" s="360" t="n"/>
+      <c r="Y32" s="360" t="n"/>
+      <c r="Z32" s="360" t="n"/>
+      <c r="AA32" s="360" t="n"/>
+      <c r="AB32" s="360" t="n"/>
+      <c r="AC32" s="360" t="n"/>
+      <c r="AD32" s="360" t="n"/>
+      <c r="AE32" s="360" t="n"/>
+      <c r="AF32" s="360" t="n"/>
+      <c r="AG32" s="360" t="n"/>
+      <c r="AH32" s="360" t="n"/>
+      <c r="AI32" s="360" t="n"/>
+      <c r="AJ32" s="360" t="n"/>
+      <c r="AK32" s="504" t="n"/>
+      <c r="AL32" s="360" t="n"/>
+      <c r="AM32" s="360" t="n"/>
+      <c r="AN32" s="360" t="n"/>
+      <c r="AO32" s="360" t="n"/>
+      <c r="AP32" s="360" t="n"/>
+      <c r="AQ32" s="360" t="n"/>
+      <c r="AR32" s="360" t="n"/>
+      <c r="AS32" s="360" t="n"/>
+      <c r="AT32" s="360" t="n"/>
+      <c r="AU32" s="360" t="n"/>
+      <c r="AV32" s="360" t="n"/>
+      <c r="AW32" s="360" t="n"/>
+      <c r="AX32" s="360" t="n"/>
+      <c r="AY32" s="360" t="n"/>
+      <c r="AZ32" s="360" t="n"/>
+      <c r="BA32" s="360" t="n"/>
+      <c r="BB32" s="360" t="n"/>
+      <c r="BC32" s="360" t="n"/>
+      <c r="BD32" s="476" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="417" t="n"/>
-      <c r="B33" s="411" t="n"/>
-      <c r="C33" s="411" t="n"/>
-      <c r="D33" s="411" t="n"/>
-      <c r="E33" s="411" t="n"/>
-      <c r="F33" s="411" t="n"/>
-      <c r="G33" s="411" t="n"/>
-      <c r="H33" s="411" t="n"/>
-      <c r="I33" s="411" t="n"/>
-      <c r="J33" s="411" t="n"/>
-      <c r="K33" s="411" t="n"/>
-      <c r="L33" s="411" t="n"/>
-      <c r="M33" s="411" t="n"/>
-      <c r="N33" s="411" t="n"/>
-      <c r="O33" s="411" t="n"/>
-      <c r="P33" s="411" t="n"/>
-      <c r="Q33" s="411" t="n"/>
-      <c r="R33" s="412" t="n"/>
-      <c r="S33" s="417" t="n"/>
-      <c r="T33" s="411" t="n"/>
-      <c r="U33" s="411" t="n"/>
-      <c r="V33" s="411" t="n"/>
-      <c r="W33" s="411" t="n"/>
-      <c r="X33" s="411" t="n"/>
-      <c r="Y33" s="411" t="n"/>
-      <c r="Z33" s="411" t="n"/>
-      <c r="AA33" s="411" t="n"/>
-      <c r="AB33" s="411" t="n"/>
-      <c r="AC33" s="411" t="n"/>
-      <c r="AD33" s="411" t="n"/>
-      <c r="AE33" s="411" t="n"/>
-      <c r="AF33" s="411" t="n"/>
-      <c r="AG33" s="411" t="n"/>
-      <c r="AH33" s="411" t="n"/>
-      <c r="AI33" s="411" t="n"/>
-      <c r="AJ33" s="412" t="n"/>
-      <c r="AK33" s="417" t="n"/>
-      <c r="AL33" s="411" t="n"/>
-      <c r="AM33" s="411" t="n"/>
-      <c r="AN33" s="411" t="n"/>
-      <c r="AO33" s="411" t="n"/>
-      <c r="AP33" s="411" t="n"/>
-      <c r="AQ33" s="411" t="n"/>
-      <c r="AR33" s="411" t="n"/>
-      <c r="AS33" s="411" t="n"/>
-      <c r="AT33" s="411" t="n"/>
-      <c r="AU33" s="411" t="n"/>
-      <c r="AV33" s="411" t="n"/>
-      <c r="AW33" s="411" t="n"/>
-      <c r="AX33" s="411" t="n"/>
-      <c r="AY33" s="411" t="n"/>
-      <c r="AZ33" s="411" t="n"/>
-      <c r="BA33" s="411" t="n"/>
-      <c r="BB33" s="411" t="n"/>
-      <c r="BC33" s="411" t="n"/>
-      <c r="BD33" s="412" t="n"/>
+      <c r="A33" s="505" t="n"/>
+      <c r="B33" s="480" t="n"/>
+      <c r="C33" s="480" t="n"/>
+      <c r="D33" s="480" t="n"/>
+      <c r="E33" s="480" t="n"/>
+      <c r="F33" s="480" t="n"/>
+      <c r="G33" s="480" t="n"/>
+      <c r="H33" s="480" t="n"/>
+      <c r="I33" s="480" t="n"/>
+      <c r="J33" s="480" t="n"/>
+      <c r="K33" s="480" t="n"/>
+      <c r="L33" s="480" t="n"/>
+      <c r="M33" s="480" t="n"/>
+      <c r="N33" s="480" t="n"/>
+      <c r="O33" s="480" t="n"/>
+      <c r="P33" s="480" t="n"/>
+      <c r="Q33" s="480" t="n"/>
+      <c r="R33" s="480" t="n"/>
+      <c r="S33" s="506" t="n"/>
+      <c r="T33" s="480" t="n"/>
+      <c r="U33" s="480" t="n"/>
+      <c r="V33" s="480" t="n"/>
+      <c r="W33" s="480" t="n"/>
+      <c r="X33" s="480" t="n"/>
+      <c r="Y33" s="480" t="n"/>
+      <c r="Z33" s="480" t="n"/>
+      <c r="AA33" s="480" t="n"/>
+      <c r="AB33" s="480" t="n"/>
+      <c r="AC33" s="480" t="n"/>
+      <c r="AD33" s="480" t="n"/>
+      <c r="AE33" s="480" t="n"/>
+      <c r="AF33" s="480" t="n"/>
+      <c r="AG33" s="480" t="n"/>
+      <c r="AH33" s="480" t="n"/>
+      <c r="AI33" s="480" t="n"/>
+      <c r="AJ33" s="480" t="n"/>
+      <c r="AK33" s="506" t="n"/>
+      <c r="AL33" s="480" t="n"/>
+      <c r="AM33" s="480" t="n"/>
+      <c r="AN33" s="480" t="n"/>
+      <c r="AO33" s="480" t="n"/>
+      <c r="AP33" s="480" t="n"/>
+      <c r="AQ33" s="480" t="n"/>
+      <c r="AR33" s="480" t="n"/>
+      <c r="AS33" s="480" t="n"/>
+      <c r="AT33" s="480" t="n"/>
+      <c r="AU33" s="480" t="n"/>
+      <c r="AV33" s="480" t="n"/>
+      <c r="AW33" s="480" t="n"/>
+      <c r="AX33" s="480" t="n"/>
+      <c r="AY33" s="480" t="n"/>
+      <c r="AZ33" s="480" t="n"/>
+      <c r="BA33" s="480" t="n"/>
+      <c r="BB33" s="480" t="n"/>
+      <c r="BC33" s="480" t="n"/>
+      <c r="BD33" s="482" t="n"/>
     </row>
-    <row r="34" ht="4" customHeight="1">
+    <row r="34" ht="3" customHeight="1">
       <c r="A34" s="389" t="n"/>
       <c r="B34" s="351" t="n"/>
       <c r="C34" s="351" t="n"/>
@@ -7422,66 +8300,66 @@
       <c r="BD34" s="351" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="390" t="inlineStr">
+      <c r="A35" s="507" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B35" s="409" t="n"/>
-      <c r="C35" s="409" t="n"/>
-      <c r="D35" s="409" t="n"/>
-      <c r="E35" s="409" t="n"/>
-      <c r="F35" s="409" t="n"/>
-      <c r="G35" s="409" t="n"/>
-      <c r="H35" s="409" t="n"/>
-      <c r="I35" s="409" t="n"/>
-      <c r="J35" s="409" t="n"/>
-      <c r="K35" s="409" t="n"/>
-      <c r="L35" s="409" t="n"/>
-      <c r="M35" s="409" t="n"/>
-      <c r="N35" s="409" t="n"/>
-      <c r="O35" s="409" t="n"/>
-      <c r="P35" s="409" t="n"/>
-      <c r="Q35" s="409" t="n"/>
-      <c r="R35" s="409" t="n"/>
-      <c r="S35" s="409" t="n"/>
-      <c r="T35" s="409" t="n"/>
-      <c r="U35" s="409" t="n"/>
-      <c r="V35" s="409" t="n"/>
-      <c r="W35" s="409" t="n"/>
-      <c r="X35" s="409" t="n"/>
-      <c r="Y35" s="409" t="n"/>
-      <c r="Z35" s="409" t="n"/>
-      <c r="AA35" s="409" t="n"/>
-      <c r="AB35" s="409" t="n"/>
-      <c r="AC35" s="409" t="n"/>
-      <c r="AD35" s="409" t="n"/>
-      <c r="AE35" s="409" t="n"/>
-      <c r="AF35" s="409" t="n"/>
-      <c r="AG35" s="409" t="n"/>
-      <c r="AH35" s="409" t="n"/>
-      <c r="AI35" s="409" t="n"/>
-      <c r="AJ35" s="409" t="n"/>
-      <c r="AK35" s="409" t="n"/>
-      <c r="AL35" s="409" t="n"/>
-      <c r="AM35" s="409" t="n"/>
-      <c r="AN35" s="409" t="n"/>
-      <c r="AO35" s="409" t="n"/>
-      <c r="AP35" s="409" t="n"/>
-      <c r="AQ35" s="409" t="n"/>
-      <c r="AR35" s="409" t="n"/>
-      <c r="AS35" s="409" t="n"/>
-      <c r="AT35" s="409" t="n"/>
-      <c r="AU35" s="409" t="n"/>
-      <c r="AV35" s="409" t="n"/>
-      <c r="AW35" s="409" t="n"/>
-      <c r="AX35" s="409" t="n"/>
-      <c r="AY35" s="409" t="n"/>
-      <c r="AZ35" s="409" t="n"/>
-      <c r="BA35" s="409" t="n"/>
-      <c r="BB35" s="409" t="n"/>
-      <c r="BC35" s="409" t="n"/>
-      <c r="BD35" s="410" t="n"/>
+      <c r="B35" s="508" t="n"/>
+      <c r="C35" s="508" t="n"/>
+      <c r="D35" s="508" t="n"/>
+      <c r="E35" s="508" t="n"/>
+      <c r="F35" s="508" t="n"/>
+      <c r="G35" s="508" t="n"/>
+      <c r="H35" s="508" t="n"/>
+      <c r="I35" s="508" t="n"/>
+      <c r="J35" s="508" t="n"/>
+      <c r="K35" s="508" t="n"/>
+      <c r="L35" s="508" t="n"/>
+      <c r="M35" s="508" t="n"/>
+      <c r="N35" s="508" t="n"/>
+      <c r="O35" s="508" t="n"/>
+      <c r="P35" s="508" t="n"/>
+      <c r="Q35" s="508" t="n"/>
+      <c r="R35" s="508" t="n"/>
+      <c r="S35" s="508" t="n"/>
+      <c r="T35" s="508" t="n"/>
+      <c r="U35" s="508" t="n"/>
+      <c r="V35" s="508" t="n"/>
+      <c r="W35" s="508" t="n"/>
+      <c r="X35" s="508" t="n"/>
+      <c r="Y35" s="508" t="n"/>
+      <c r="Z35" s="508" t="n"/>
+      <c r="AA35" s="508" t="n"/>
+      <c r="AB35" s="508" t="n"/>
+      <c r="AC35" s="508" t="n"/>
+      <c r="AD35" s="508" t="n"/>
+      <c r="AE35" s="508" t="n"/>
+      <c r="AF35" s="508" t="n"/>
+      <c r="AG35" s="508" t="n"/>
+      <c r="AH35" s="508" t="n"/>
+      <c r="AI35" s="508" t="n"/>
+      <c r="AJ35" s="508" t="n"/>
+      <c r="AK35" s="508" t="n"/>
+      <c r="AL35" s="508" t="n"/>
+      <c r="AM35" s="508" t="n"/>
+      <c r="AN35" s="508" t="n"/>
+      <c r="AO35" s="508" t="n"/>
+      <c r="AP35" s="508" t="n"/>
+      <c r="AQ35" s="508" t="n"/>
+      <c r="AR35" s="508" t="n"/>
+      <c r="AS35" s="508" t="n"/>
+      <c r="AT35" s="508" t="n"/>
+      <c r="AU35" s="508" t="n"/>
+      <c r="AV35" s="508" t="n"/>
+      <c r="AW35" s="508" t="n"/>
+      <c r="AX35" s="508" t="n"/>
+      <c r="AY35" s="508" t="n"/>
+      <c r="AZ35" s="508" t="n"/>
+      <c r="BA35" s="508" t="n"/>
+      <c r="BB35" s="508" t="n"/>
+      <c r="BC35" s="508" t="n"/>
+      <c r="BD35" s="509" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -7497,7 +8375,7 @@
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="114">
+  <mergeCells count="113">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AX18:BA18"/>
     <mergeCell ref="H19:Z19"/>
@@ -7509,7 +8387,6 @@
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="AQ4:AV4"/>
     <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="S30:AJ30"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AA20:AQ20"/>
@@ -7646,6 +8523,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7812,7 +8690,7 @@
         </is>
       </c>
       <c r="D5" s="266" t="n"/>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="346" t="inlineStr">
         <is>
           <t>MONITORING</t>
         </is>
@@ -7821,7 +8699,7 @@
       <c r="G5" s="266" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="346" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
@@ -7830,7 +8708,7 @@
       <c r="G6" s="266" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="346" t="inlineStr">
         <is>
           <t>PUR</t>
         </is>
@@ -7838,7 +8716,7 @@
       <c r="F7" s="266" t="n"/>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="346" t="inlineStr">
         <is>
           <t>WHS</t>
         </is>
@@ -7846,7 +8724,7 @@
       <c r="F8" s="266" t="n"/>
     </row>
     <row r="9">
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="346" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
@@ -7854,7 +8732,7 @@
       <c r="F9" s="266" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="346" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -7862,7 +8740,7 @@
       <c r="F10" s="266" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="346" t="inlineStr">
         <is>
           <t>MGT</t>
         </is>
@@ -7925,878 +8803,884 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="391" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="510" t="inlineStr">
         <is>
           <t>Result Detail</t>
         </is>
       </c>
-      <c r="B1" s="420" t="n"/>
-      <c r="C1" s="420" t="n"/>
-      <c r="D1" s="420" t="n"/>
-      <c r="E1" s="420" t="n"/>
-      <c r="F1" s="420" t="n"/>
-      <c r="G1" s="421" t="n"/>
-      <c r="H1" s="346" t="n"/>
-      <c r="I1" s="346" t="n"/>
-      <c r="J1" s="346" t="n"/>
-      <c r="K1" s="346" t="n"/>
-      <c r="L1" s="346" t="n"/>
-      <c r="M1" s="346" t="n"/>
-      <c r="N1" s="346" t="n"/>
-      <c r="O1" s="346" t="n"/>
-      <c r="P1" s="346" t="n"/>
-      <c r="Q1" s="346" t="n"/>
-      <c r="R1" s="346" t="n"/>
-      <c r="S1" s="346" t="n"/>
-      <c r="T1" s="346" t="n"/>
-      <c r="U1" s="346" t="n"/>
-      <c r="V1" s="346" t="n"/>
-      <c r="W1" s="346" t="n"/>
-      <c r="X1" s="346" t="n"/>
-      <c r="Y1" s="346" t="n"/>
-      <c r="Z1" s="346" t="n"/>
-      <c r="AA1" s="346" t="n"/>
-      <c r="AB1" s="346" t="n"/>
-      <c r="AC1" s="346" t="n"/>
-      <c r="AD1" s="346" t="n"/>
-      <c r="AE1" s="346" t="n"/>
-      <c r="AF1" s="346" t="n"/>
-      <c r="AG1" s="346" t="n"/>
-      <c r="AH1" s="346" t="n"/>
-      <c r="AI1" s="346" t="n"/>
-      <c r="AJ1" s="346" t="n"/>
-      <c r="AK1" s="346" t="n"/>
-      <c r="AL1" s="346" t="n"/>
-      <c r="AM1" s="346" t="n"/>
-      <c r="AN1" s="346" t="n"/>
+      <c r="B1" s="426" t="n"/>
+      <c r="C1" s="426" t="n"/>
+      <c r="D1" s="426" t="n"/>
+      <c r="E1" s="426" t="n"/>
+      <c r="F1" s="426" t="n"/>
+      <c r="G1" s="426" t="n"/>
+      <c r="H1" s="511" t="n"/>
+      <c r="I1" s="428" t="n"/>
+      <c r="J1" s="429" t="n"/>
+      <c r="K1" s="429" t="n"/>
+      <c r="L1" s="429" t="n"/>
+      <c r="M1" s="429" t="n"/>
+      <c r="N1" s="429" t="n"/>
+      <c r="O1" s="429" t="n"/>
+      <c r="P1" s="429" t="n"/>
+      <c r="Q1" s="429" t="n"/>
+      <c r="R1" s="429" t="n"/>
+      <c r="S1" s="429" t="n"/>
+      <c r="T1" s="429" t="n"/>
+      <c r="U1" s="429" t="n"/>
+      <c r="V1" s="429" t="n"/>
+      <c r="W1" s="429" t="n"/>
+      <c r="X1" s="429" t="n"/>
+      <c r="Y1" s="429" t="n"/>
+      <c r="Z1" s="429" t="n"/>
+      <c r="AA1" s="429" t="n"/>
+      <c r="AB1" s="429" t="n"/>
+      <c r="AC1" s="429" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="431" t="n"/>
+      <c r="AF1" s="432" t="n"/>
+      <c r="AG1" s="432" t="n"/>
+      <c r="AH1" s="433" t="n"/>
+      <c r="AI1" s="434" t="n"/>
+      <c r="AJ1" s="435" t="n"/>
+      <c r="AK1" s="435" t="n"/>
+      <c r="AL1" s="435" t="n"/>
+      <c r="AM1" s="435" t="n"/>
+      <c r="AN1" s="436" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="317" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="512" t="inlineStr">
         <is>
           <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
         </is>
       </c>
-      <c r="H2" s="346" t="n"/>
-      <c r="I2" s="346" t="n"/>
-      <c r="J2" s="346" t="n"/>
-      <c r="K2" s="346" t="n"/>
-      <c r="L2" s="346" t="n"/>
-      <c r="M2" s="346" t="n"/>
-      <c r="N2" s="346" t="n"/>
-      <c r="O2" s="346" t="n"/>
-      <c r="P2" s="346" t="n"/>
-      <c r="Q2" s="346" t="n"/>
-      <c r="R2" s="346" t="n"/>
-      <c r="S2" s="346" t="n"/>
-      <c r="T2" s="346" t="n"/>
-      <c r="U2" s="346" t="n"/>
-      <c r="V2" s="346" t="n"/>
-      <c r="W2" s="346" t="n"/>
-      <c r="X2" s="346" t="n"/>
-      <c r="Y2" s="346" t="n"/>
-      <c r="Z2" s="346" t="n"/>
-      <c r="AA2" s="346" t="n"/>
-      <c r="AB2" s="346" t="n"/>
-      <c r="AC2" s="346" t="n"/>
-      <c r="AD2" s="346" t="n"/>
-      <c r="AE2" s="346" t="n"/>
-      <c r="AF2" s="346" t="n"/>
-      <c r="AG2" s="346" t="n"/>
-      <c r="AH2" s="346" t="n"/>
-      <c r="AI2" s="346" t="n"/>
-      <c r="AJ2" s="346" t="n"/>
-      <c r="AK2" s="346" t="n"/>
-      <c r="AL2" s="346" t="n"/>
-      <c r="AM2" s="346" t="n"/>
-      <c r="AN2" s="346" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="513" t="n"/>
+      <c r="I2" s="439" t="n"/>
+      <c r="J2" s="440" t="n"/>
+      <c r="K2" s="440" t="n"/>
+      <c r="L2" s="440" t="n"/>
+      <c r="M2" s="440" t="n"/>
+      <c r="N2" s="440" t="n"/>
+      <c r="O2" s="440" t="n"/>
+      <c r="P2" s="440" t="n"/>
+      <c r="Q2" s="440" t="n"/>
+      <c r="R2" s="440" t="n"/>
+      <c r="S2" s="440" t="n"/>
+      <c r="T2" s="440" t="n"/>
+      <c r="U2" s="440" t="n"/>
+      <c r="V2" s="440" t="n"/>
+      <c r="W2" s="440" t="n"/>
+      <c r="X2" s="440" t="n"/>
+      <c r="Y2" s="440" t="n"/>
+      <c r="Z2" s="440" t="n"/>
+      <c r="AA2" s="440" t="n"/>
+      <c r="AB2" s="440" t="n"/>
+      <c r="AC2" s="440" t="n"/>
+      <c r="AD2" s="441" t="n"/>
+      <c r="AE2" s="442" t="n"/>
+      <c r="AF2" s="443" t="n"/>
+      <c r="AG2" s="443" t="n"/>
+      <c r="AH2" s="444" t="n"/>
+      <c r="AI2" s="445" t="n"/>
+      <c r="AJ2" s="446" t="n"/>
+      <c r="AK2" s="446" t="n"/>
+      <c r="AL2" s="446" t="n"/>
+      <c r="AM2" s="446" t="n"/>
+      <c r="AN2" s="447" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="346" t="n"/>
-      <c r="B3" s="346" t="n"/>
-      <c r="C3" s="346" t="n"/>
-      <c r="D3" s="346" t="n"/>
-      <c r="E3" s="346" t="n"/>
-      <c r="F3" s="346" t="n"/>
-      <c r="G3" s="346" t="n"/>
-      <c r="H3" s="346" t="n"/>
-      <c r="I3" s="346" t="n"/>
-      <c r="J3" s="346" t="n"/>
-      <c r="K3" s="346" t="n"/>
-      <c r="L3" s="346" t="n"/>
-      <c r="M3" s="346" t="n"/>
-      <c r="N3" s="346" t="n"/>
-      <c r="O3" s="346" t="n"/>
-      <c r="P3" s="346" t="n"/>
-      <c r="Q3" s="346" t="n"/>
-      <c r="R3" s="346" t="n"/>
-      <c r="S3" s="346" t="n"/>
-      <c r="T3" s="346" t="n"/>
-      <c r="U3" s="346" t="n"/>
-      <c r="V3" s="346" t="n"/>
-      <c r="W3" s="346" t="n"/>
-      <c r="X3" s="346" t="n"/>
-      <c r="Y3" s="346" t="n"/>
-      <c r="Z3" s="346" t="n"/>
-      <c r="AA3" s="346" t="n"/>
-      <c r="AB3" s="346" t="n"/>
-      <c r="AC3" s="346" t="n"/>
-      <c r="AD3" s="346" t="n"/>
-      <c r="AE3" s="346" t="n"/>
-      <c r="AF3" s="346" t="n"/>
-      <c r="AG3" s="346" t="n"/>
-      <c r="AH3" s="346" t="n"/>
-      <c r="AI3" s="346" t="n"/>
-      <c r="AJ3" s="346" t="n"/>
-      <c r="AK3" s="346" t="n"/>
-      <c r="AL3" s="346" t="n"/>
-      <c r="AM3" s="346" t="n"/>
-      <c r="AN3" s="346" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="514" t="n"/>
+      <c r="B3" s="515" t="n"/>
+      <c r="C3" s="515" t="n"/>
+      <c r="D3" s="515" t="n"/>
+      <c r="E3" s="515" t="n"/>
+      <c r="F3" s="515" t="n"/>
+      <c r="G3" s="515" t="n"/>
+      <c r="H3" s="513" t="n"/>
+      <c r="I3" s="439" t="n"/>
+      <c r="J3" s="440" t="n"/>
+      <c r="K3" s="440" t="n"/>
+      <c r="L3" s="440" t="n"/>
+      <c r="M3" s="440" t="n"/>
+      <c r="N3" s="440" t="n"/>
+      <c r="O3" s="440" t="n"/>
+      <c r="P3" s="440" t="n"/>
+      <c r="Q3" s="440" t="n"/>
+      <c r="R3" s="440" t="n"/>
+      <c r="S3" s="440" t="n"/>
+      <c r="T3" s="440" t="n"/>
+      <c r="U3" s="440" t="n"/>
+      <c r="V3" s="440" t="n"/>
+      <c r="W3" s="440" t="n"/>
+      <c r="X3" s="440" t="n"/>
+      <c r="Y3" s="440" t="n"/>
+      <c r="Z3" s="440" t="n"/>
+      <c r="AA3" s="440" t="n"/>
+      <c r="AB3" s="440" t="n"/>
+      <c r="AC3" s="440" t="n"/>
+      <c r="AD3" s="441" t="n"/>
+      <c r="AE3" s="442" t="n"/>
+      <c r="AF3" s="443" t="n"/>
+      <c r="AG3" s="443" t="n"/>
+      <c r="AH3" s="444" t="n"/>
+      <c r="AI3" s="445" t="n"/>
+      <c r="AJ3" s="446" t="n"/>
+      <c r="AK3" s="446" t="n"/>
+      <c r="AL3" s="446" t="n"/>
+      <c r="AM3" s="446" t="n"/>
+      <c r="AN3" s="447" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="362" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="516" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="362" t="inlineStr">
+      <c r="B4" s="517" t="inlineStr">
         <is>
           <t>Requirement / Characteristic</t>
         </is>
       </c>
-      <c r="C4" s="362" t="inlineStr">
+      <c r="C4" s="517" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="D4" s="362" t="inlineStr">
+      <c r="D4" s="517" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="E4" s="362" t="inlineStr">
+      <c r="E4" s="517" t="inlineStr">
         <is>
           <t>Evaluation</t>
         </is>
       </c>
-      <c r="F4" s="362" t="inlineStr">
+      <c r="F4" s="517" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="G4" s="362" t="inlineStr">
+      <c r="G4" s="517" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="346" t="n"/>
-      <c r="I4" s="346" t="n"/>
-      <c r="J4" s="346" t="n"/>
-      <c r="K4" s="346" t="n"/>
-      <c r="L4" s="346" t="n"/>
-      <c r="M4" s="346" t="n"/>
-      <c r="N4" s="346" t="n"/>
-      <c r="O4" s="346" t="n"/>
-      <c r="P4" s="346" t="n"/>
-      <c r="Q4" s="346" t="n"/>
-      <c r="R4" s="346" t="n"/>
-      <c r="S4" s="346" t="n"/>
-      <c r="T4" s="346" t="n"/>
-      <c r="U4" s="346" t="n"/>
-      <c r="V4" s="346" t="n"/>
-      <c r="W4" s="346" t="n"/>
-      <c r="X4" s="346" t="n"/>
-      <c r="Y4" s="346" t="n"/>
-      <c r="Z4" s="346" t="n"/>
-      <c r="AA4" s="346" t="n"/>
-      <c r="AB4" s="346" t="n"/>
-      <c r="AC4" s="346" t="n"/>
-      <c r="AD4" s="346" t="n"/>
-      <c r="AE4" s="346" t="n"/>
-      <c r="AF4" s="346" t="n"/>
-      <c r="AG4" s="346" t="n"/>
-      <c r="AH4" s="346" t="n"/>
-      <c r="AI4" s="346" t="n"/>
-      <c r="AJ4" s="346" t="n"/>
-      <c r="AK4" s="346" t="n"/>
-      <c r="AL4" s="346" t="n"/>
-      <c r="AM4" s="346" t="n"/>
-      <c r="AN4" s="346" t="n"/>
+      <c r="H4" s="513" t="n"/>
+      <c r="I4" s="448" t="n"/>
+      <c r="J4" s="449" t="n"/>
+      <c r="K4" s="449" t="n"/>
+      <c r="L4" s="449" t="n"/>
+      <c r="M4" s="449" t="n"/>
+      <c r="N4" s="449" t="n"/>
+      <c r="O4" s="449" t="n"/>
+      <c r="P4" s="449" t="n"/>
+      <c r="Q4" s="449" t="n"/>
+      <c r="R4" s="449" t="n"/>
+      <c r="S4" s="449" t="n"/>
+      <c r="T4" s="449" t="n"/>
+      <c r="U4" s="449" t="n"/>
+      <c r="V4" s="449" t="n"/>
+      <c r="W4" s="449" t="n"/>
+      <c r="X4" s="449" t="n"/>
+      <c r="Y4" s="449" t="n"/>
+      <c r="Z4" s="449" t="n"/>
+      <c r="AA4" s="449" t="n"/>
+      <c r="AB4" s="449" t="n"/>
+      <c r="AC4" s="449" t="n"/>
+      <c r="AD4" s="450" t="n"/>
+      <c r="AE4" s="442" t="n"/>
+      <c r="AF4" s="443" t="n"/>
+      <c r="AG4" s="443" t="n"/>
+      <c r="AH4" s="444" t="n"/>
+      <c r="AI4" s="445" t="n"/>
+      <c r="AJ4" s="446" t="n"/>
+      <c r="AK4" s="446" t="n"/>
+      <c r="AL4" s="446" t="n"/>
+      <c r="AM4" s="446" t="n"/>
+      <c r="AN4" s="447" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="392">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="518">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="393" t="n"/>
-      <c r="C5" s="393" t="n"/>
-      <c r="D5" s="393" t="n"/>
-      <c r="E5" s="393" t="n"/>
-      <c r="F5" s="393" t="n"/>
-      <c r="G5" s="393" t="n"/>
-      <c r="H5" s="346" t="n"/>
-      <c r="I5" s="346" t="n"/>
-      <c r="J5" s="346" t="n"/>
-      <c r="K5" s="346" t="n"/>
-      <c r="L5" s="346" t="n"/>
-      <c r="M5" s="346" t="n"/>
-      <c r="N5" s="346" t="n"/>
-      <c r="O5" s="346" t="n"/>
-      <c r="P5" s="346" t="n"/>
-      <c r="Q5" s="346" t="n"/>
-      <c r="R5" s="346" t="n"/>
-      <c r="S5" s="346" t="n"/>
-      <c r="T5" s="346" t="n"/>
-      <c r="U5" s="346" t="n"/>
-      <c r="V5" s="346" t="n"/>
-      <c r="W5" s="346" t="n"/>
-      <c r="X5" s="346" t="n"/>
-      <c r="Y5" s="346" t="n"/>
-      <c r="Z5" s="346" t="n"/>
-      <c r="AA5" s="346" t="n"/>
-      <c r="AB5" s="346" t="n"/>
-      <c r="AC5" s="346" t="n"/>
-      <c r="AD5" s="346" t="n"/>
-      <c r="AE5" s="346" t="n"/>
-      <c r="AF5" s="346" t="n"/>
-      <c r="AG5" s="346" t="n"/>
-      <c r="AH5" s="346" t="n"/>
-      <c r="AI5" s="346" t="n"/>
-      <c r="AJ5" s="346" t="n"/>
-      <c r="AK5" s="346" t="n"/>
-      <c r="AL5" s="346" t="n"/>
-      <c r="AM5" s="346" t="n"/>
-      <c r="AN5" s="346" t="n"/>
+      <c r="B5" s="519" t="n"/>
+      <c r="C5" s="519" t="n"/>
+      <c r="D5" s="519" t="n"/>
+      <c r="E5" s="519" t="n"/>
+      <c r="F5" s="519" t="n"/>
+      <c r="G5" s="519" t="n"/>
+      <c r="H5" s="520" t="n"/>
+      <c r="I5" s="454" t="n"/>
+      <c r="J5" s="455" t="n"/>
+      <c r="K5" s="455" t="n"/>
+      <c r="L5" s="455" t="n"/>
+      <c r="M5" s="455" t="n"/>
+      <c r="N5" s="455" t="n"/>
+      <c r="O5" s="455" t="n"/>
+      <c r="P5" s="455" t="n"/>
+      <c r="Q5" s="455" t="n"/>
+      <c r="R5" s="455" t="n"/>
+      <c r="S5" s="455" t="n"/>
+      <c r="T5" s="455" t="n"/>
+      <c r="U5" s="455" t="n"/>
+      <c r="V5" s="455" t="n"/>
+      <c r="W5" s="455" t="n"/>
+      <c r="X5" s="455" t="n"/>
+      <c r="Y5" s="455" t="n"/>
+      <c r="Z5" s="455" t="n"/>
+      <c r="AA5" s="455" t="n"/>
+      <c r="AB5" s="455" t="n"/>
+      <c r="AC5" s="455" t="n"/>
+      <c r="AD5" s="456" t="n"/>
+      <c r="AE5" s="457" t="n"/>
+      <c r="AF5" s="458" t="n"/>
+      <c r="AG5" s="458" t="n"/>
+      <c r="AH5" s="459" t="n"/>
+      <c r="AI5" s="460" t="n"/>
+      <c r="AJ5" s="461" t="n"/>
+      <c r="AK5" s="461" t="n"/>
+      <c r="AL5" s="461" t="n"/>
+      <c r="AM5" s="461" t="n"/>
+      <c r="AN5" s="462" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="392">
+      <c r="A6" s="521">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="393" t="n"/>
-      <c r="C6" s="393" t="n"/>
-      <c r="D6" s="393" t="n"/>
-      <c r="E6" s="393" t="n"/>
-      <c r="F6" s="393" t="n"/>
-      <c r="G6" s="393" t="n"/>
-      <c r="H6" s="346" t="n"/>
-      <c r="I6" s="346" t="n"/>
-      <c r="J6" s="346" t="n"/>
-      <c r="K6" s="346" t="n"/>
-      <c r="L6" s="346" t="n"/>
-      <c r="M6" s="346" t="n"/>
-      <c r="N6" s="346" t="n"/>
-      <c r="O6" s="346" t="n"/>
-      <c r="P6" s="346" t="n"/>
-      <c r="Q6" s="346" t="n"/>
-      <c r="R6" s="346" t="n"/>
-      <c r="S6" s="346" t="n"/>
-      <c r="T6" s="346" t="n"/>
-      <c r="U6" s="346" t="n"/>
-      <c r="V6" s="346" t="n"/>
-      <c r="W6" s="346" t="n"/>
-      <c r="X6" s="346" t="n"/>
-      <c r="Y6" s="346" t="n"/>
-      <c r="Z6" s="346" t="n"/>
-      <c r="AA6" s="346" t="n"/>
-      <c r="AB6" s="346" t="n"/>
-      <c r="AC6" s="346" t="n"/>
-      <c r="AD6" s="346" t="n"/>
-      <c r="AE6" s="346" t="n"/>
-      <c r="AF6" s="346" t="n"/>
-      <c r="AG6" s="346" t="n"/>
-      <c r="AH6" s="346" t="n"/>
-      <c r="AI6" s="346" t="n"/>
-      <c r="AJ6" s="346" t="n"/>
-      <c r="AK6" s="346" t="n"/>
-      <c r="AL6" s="346" t="n"/>
-      <c r="AM6" s="346" t="n"/>
-      <c r="AN6" s="346" t="n"/>
+      <c r="B6" s="522" t="n"/>
+      <c r="C6" s="523" t="n"/>
+      <c r="D6" s="523" t="n"/>
+      <c r="E6" s="523" t="n"/>
+      <c r="F6" s="523" t="n"/>
+      <c r="G6" s="523" t="n"/>
+      <c r="H6" s="468" t="n"/>
+      <c r="I6" s="468" t="n"/>
+      <c r="J6" s="468" t="n"/>
+      <c r="K6" s="468" t="n"/>
+      <c r="L6" s="468" t="n"/>
+      <c r="M6" s="468" t="n"/>
+      <c r="N6" s="468" t="n"/>
+      <c r="O6" s="468" t="n"/>
+      <c r="P6" s="468" t="n"/>
+      <c r="Q6" s="468" t="n"/>
+      <c r="R6" s="468" t="n"/>
+      <c r="S6" s="468" t="n"/>
+      <c r="T6" s="468" t="n"/>
+      <c r="U6" s="468" t="n"/>
+      <c r="V6" s="468" t="n"/>
+      <c r="W6" s="468" t="n"/>
+      <c r="X6" s="468" t="n"/>
+      <c r="Y6" s="468" t="n"/>
+      <c r="Z6" s="468" t="n"/>
+      <c r="AA6" s="468" t="n"/>
+      <c r="AB6" s="468" t="n"/>
+      <c r="AC6" s="468" t="n"/>
+      <c r="AD6" s="468" t="n"/>
+      <c r="AE6" s="468" t="n"/>
+      <c r="AF6" s="468" t="n"/>
+      <c r="AG6" s="468" t="n"/>
+      <c r="AH6" s="468" t="n"/>
+      <c r="AI6" s="468" t="n"/>
+      <c r="AJ6" s="468" t="n"/>
+      <c r="AK6" s="468" t="n"/>
+      <c r="AL6" s="468" t="n"/>
+      <c r="AM6" s="468" t="n"/>
+      <c r="AN6" s="500" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="392">
+      <c r="A7" s="524">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="393" t="n"/>
-      <c r="C7" s="393" t="n"/>
-      <c r="D7" s="393" t="n"/>
-      <c r="E7" s="393" t="n"/>
-      <c r="F7" s="393" t="n"/>
-      <c r="G7" s="393" t="n"/>
-      <c r="H7" s="346" t="n"/>
-      <c r="I7" s="346" t="n"/>
-      <c r="J7" s="346" t="n"/>
-      <c r="K7" s="346" t="n"/>
-      <c r="L7" s="346" t="n"/>
-      <c r="M7" s="346" t="n"/>
-      <c r="N7" s="346" t="n"/>
-      <c r="O7" s="346" t="n"/>
-      <c r="P7" s="346" t="n"/>
-      <c r="Q7" s="346" t="n"/>
-      <c r="R7" s="346" t="n"/>
-      <c r="S7" s="346" t="n"/>
-      <c r="T7" s="346" t="n"/>
-      <c r="U7" s="346" t="n"/>
-      <c r="V7" s="346" t="n"/>
-      <c r="W7" s="346" t="n"/>
-      <c r="X7" s="346" t="n"/>
-      <c r="Y7" s="346" t="n"/>
-      <c r="Z7" s="346" t="n"/>
-      <c r="AA7" s="346" t="n"/>
-      <c r="AB7" s="346" t="n"/>
-      <c r="AC7" s="346" t="n"/>
-      <c r="AD7" s="346" t="n"/>
-      <c r="AE7" s="346" t="n"/>
-      <c r="AF7" s="346" t="n"/>
-      <c r="AG7" s="346" t="n"/>
-      <c r="AH7" s="346" t="n"/>
-      <c r="AI7" s="346" t="n"/>
-      <c r="AJ7" s="346" t="n"/>
-      <c r="AK7" s="346" t="n"/>
-      <c r="AL7" s="346" t="n"/>
-      <c r="AM7" s="346" t="n"/>
-      <c r="AN7" s="346" t="n"/>
+      <c r="B7" s="525" t="n"/>
+      <c r="C7" s="526" t="n"/>
+      <c r="D7" s="526" t="n"/>
+      <c r="E7" s="526" t="n"/>
+      <c r="F7" s="526" t="n"/>
+      <c r="G7" s="526" t="n"/>
+      <c r="H7" s="342" t="n"/>
+      <c r="I7" s="342" t="n"/>
+      <c r="J7" s="342" t="n"/>
+      <c r="K7" s="342" t="n"/>
+      <c r="L7" s="342" t="n"/>
+      <c r="M7" s="342" t="n"/>
+      <c r="N7" s="342" t="n"/>
+      <c r="O7" s="342" t="n"/>
+      <c r="P7" s="342" t="n"/>
+      <c r="Q7" s="342" t="n"/>
+      <c r="R7" s="342" t="n"/>
+      <c r="S7" s="342" t="n"/>
+      <c r="T7" s="342" t="n"/>
+      <c r="U7" s="342" t="n"/>
+      <c r="V7" s="342" t="n"/>
+      <c r="W7" s="342" t="n"/>
+      <c r="X7" s="342" t="n"/>
+      <c r="Y7" s="342" t="n"/>
+      <c r="Z7" s="342" t="n"/>
+      <c r="AA7" s="342" t="n"/>
+      <c r="AB7" s="342" t="n"/>
+      <c r="AC7" s="342" t="n"/>
+      <c r="AD7" s="342" t="n"/>
+      <c r="AE7" s="342" t="n"/>
+      <c r="AF7" s="342" t="n"/>
+      <c r="AG7" s="342" t="n"/>
+      <c r="AH7" s="342" t="n"/>
+      <c r="AI7" s="342" t="n"/>
+      <c r="AJ7" s="342" t="n"/>
+      <c r="AK7" s="342" t="n"/>
+      <c r="AL7" s="342" t="n"/>
+      <c r="AM7" s="342" t="n"/>
+      <c r="AN7" s="527" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="394">
+      <c r="A8" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="395" t="n"/>
-      <c r="C8" s="395" t="n"/>
-      <c r="D8" s="395" t="n"/>
-      <c r="E8" s="395" t="n"/>
-      <c r="F8" s="395" t="n"/>
-      <c r="G8" s="395" t="n"/>
-      <c r="H8" s="396" t="n"/>
-      <c r="I8" s="396" t="n"/>
-      <c r="J8" s="396" t="n"/>
-      <c r="K8" s="396" t="n"/>
-      <c r="L8" s="396" t="n"/>
-      <c r="M8" s="396" t="n"/>
-      <c r="N8" s="396" t="n"/>
-      <c r="O8" s="396" t="n"/>
-      <c r="P8" s="396" t="n"/>
-      <c r="Q8" s="396" t="n"/>
-      <c r="R8" s="396" t="n"/>
-      <c r="S8" s="396" t="n"/>
-      <c r="T8" s="396" t="n"/>
-      <c r="U8" s="396" t="n"/>
-      <c r="V8" s="396" t="n"/>
-      <c r="W8" s="396" t="n"/>
-      <c r="X8" s="396" t="n"/>
-      <c r="Y8" s="396" t="n"/>
-      <c r="Z8" s="396" t="n"/>
-      <c r="AA8" s="396" t="n"/>
-      <c r="AB8" s="396" t="n"/>
-      <c r="AC8" s="396" t="n"/>
-      <c r="AD8" s="396" t="n"/>
-      <c r="AE8" s="396" t="n"/>
-      <c r="AF8" s="396" t="n"/>
-      <c r="AG8" s="396" t="n"/>
-      <c r="AH8" s="396" t="n"/>
-      <c r="AI8" s="396" t="n"/>
-      <c r="AJ8" s="396" t="n"/>
-      <c r="AK8" s="396" t="n"/>
-      <c r="AL8" s="396" t="n"/>
-      <c r="AM8" s="396" t="n"/>
-      <c r="AN8" s="396" t="n"/>
+      <c r="B8" s="529" t="n"/>
+      <c r="C8" s="530" t="n"/>
+      <c r="D8" s="530" t="n"/>
+      <c r="E8" s="530" t="n"/>
+      <c r="F8" s="530" t="n"/>
+      <c r="G8" s="530" t="n"/>
+      <c r="H8" s="354" t="n"/>
+      <c r="I8" s="354" t="n"/>
+      <c r="J8" s="354" t="n"/>
+      <c r="K8" s="354" t="n"/>
+      <c r="L8" s="354" t="n"/>
+      <c r="M8" s="354" t="n"/>
+      <c r="N8" s="354" t="n"/>
+      <c r="O8" s="354" t="n"/>
+      <c r="P8" s="354" t="n"/>
+      <c r="Q8" s="354" t="n"/>
+      <c r="R8" s="354" t="n"/>
+      <c r="S8" s="354" t="n"/>
+      <c r="T8" s="354" t="n"/>
+      <c r="U8" s="354" t="n"/>
+      <c r="V8" s="354" t="n"/>
+      <c r="W8" s="354" t="n"/>
+      <c r="X8" s="354" t="n"/>
+      <c r="Y8" s="354" t="n"/>
+      <c r="Z8" s="354" t="n"/>
+      <c r="AA8" s="354" t="n"/>
+      <c r="AB8" s="354" t="n"/>
+      <c r="AC8" s="354" t="n"/>
+      <c r="AD8" s="354" t="n"/>
+      <c r="AE8" s="354" t="n"/>
+      <c r="AF8" s="354" t="n"/>
+      <c r="AG8" s="354" t="n"/>
+      <c r="AH8" s="354" t="n"/>
+      <c r="AI8" s="354" t="n"/>
+      <c r="AJ8" s="354" t="n"/>
+      <c r="AK8" s="354" t="n"/>
+      <c r="AL8" s="354" t="n"/>
+      <c r="AM8" s="354" t="n"/>
+      <c r="AN8" s="531" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="394">
+      <c r="A9" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="395" t="n"/>
-      <c r="C9" s="395" t="n"/>
-      <c r="D9" s="395" t="n"/>
-      <c r="E9" s="395" t="n"/>
-      <c r="F9" s="395" t="n"/>
-      <c r="G9" s="395" t="n"/>
-      <c r="H9" s="396" t="n"/>
-      <c r="I9" s="396" t="n"/>
-      <c r="J9" s="396" t="n"/>
-      <c r="K9" s="396" t="n"/>
-      <c r="L9" s="396" t="n"/>
-      <c r="M9" s="396" t="n"/>
-      <c r="N9" s="396" t="n"/>
-      <c r="O9" s="396" t="n"/>
-      <c r="P9" s="396" t="n"/>
-      <c r="Q9" s="396" t="n"/>
-      <c r="R9" s="396" t="n"/>
-      <c r="S9" s="396" t="n"/>
-      <c r="T9" s="396" t="n"/>
-      <c r="U9" s="396" t="n"/>
-      <c r="V9" s="396" t="n"/>
-      <c r="W9" s="396" t="n"/>
-      <c r="X9" s="396" t="n"/>
-      <c r="Y9" s="396" t="n"/>
-      <c r="Z9" s="396" t="n"/>
-      <c r="AA9" s="396" t="n"/>
-      <c r="AB9" s="396" t="n"/>
-      <c r="AC9" s="396" t="n"/>
-      <c r="AD9" s="396" t="n"/>
-      <c r="AE9" s="396" t="n"/>
-      <c r="AF9" s="396" t="n"/>
-      <c r="AG9" s="396" t="n"/>
-      <c r="AH9" s="396" t="n"/>
-      <c r="AI9" s="396" t="n"/>
-      <c r="AJ9" s="396" t="n"/>
-      <c r="AK9" s="396" t="n"/>
-      <c r="AL9" s="396" t="n"/>
-      <c r="AM9" s="396" t="n"/>
-      <c r="AN9" s="396" t="n"/>
+      <c r="B9" s="529" t="n"/>
+      <c r="C9" s="530" t="n"/>
+      <c r="D9" s="530" t="n"/>
+      <c r="E9" s="530" t="n"/>
+      <c r="F9" s="530" t="n"/>
+      <c r="G9" s="530" t="n"/>
+      <c r="H9" s="354" t="n"/>
+      <c r="I9" s="354" t="n"/>
+      <c r="J9" s="354" t="n"/>
+      <c r="K9" s="354" t="n"/>
+      <c r="L9" s="354" t="n"/>
+      <c r="M9" s="354" t="n"/>
+      <c r="N9" s="354" t="n"/>
+      <c r="O9" s="354" t="n"/>
+      <c r="P9" s="354" t="n"/>
+      <c r="Q9" s="354" t="n"/>
+      <c r="R9" s="354" t="n"/>
+      <c r="S9" s="354" t="n"/>
+      <c r="T9" s="354" t="n"/>
+      <c r="U9" s="354" t="n"/>
+      <c r="V9" s="354" t="n"/>
+      <c r="W9" s="354" t="n"/>
+      <c r="X9" s="354" t="n"/>
+      <c r="Y9" s="354" t="n"/>
+      <c r="Z9" s="354" t="n"/>
+      <c r="AA9" s="354" t="n"/>
+      <c r="AB9" s="354" t="n"/>
+      <c r="AC9" s="354" t="n"/>
+      <c r="AD9" s="354" t="n"/>
+      <c r="AE9" s="354" t="n"/>
+      <c r="AF9" s="354" t="n"/>
+      <c r="AG9" s="354" t="n"/>
+      <c r="AH9" s="354" t="n"/>
+      <c r="AI9" s="354" t="n"/>
+      <c r="AJ9" s="354" t="n"/>
+      <c r="AK9" s="354" t="n"/>
+      <c r="AL9" s="354" t="n"/>
+      <c r="AM9" s="354" t="n"/>
+      <c r="AN9" s="531" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="394">
+      <c r="A10" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="395" t="n"/>
-      <c r="C10" s="395" t="n"/>
-      <c r="D10" s="395" t="n"/>
-      <c r="E10" s="395" t="n"/>
-      <c r="F10" s="395" t="n"/>
-      <c r="G10" s="395" t="n"/>
-      <c r="H10" s="396" t="n"/>
-      <c r="I10" s="396" t="n"/>
-      <c r="J10" s="396" t="n"/>
-      <c r="K10" s="396" t="n"/>
-      <c r="L10" s="396" t="n"/>
-      <c r="M10" s="396" t="n"/>
-      <c r="N10" s="396" t="n"/>
-      <c r="O10" s="396" t="n"/>
-      <c r="P10" s="396" t="n"/>
-      <c r="Q10" s="396" t="n"/>
-      <c r="R10" s="396" t="n"/>
-      <c r="S10" s="396" t="n"/>
-      <c r="T10" s="396" t="n"/>
-      <c r="U10" s="396" t="n"/>
-      <c r="V10" s="396" t="n"/>
-      <c r="W10" s="396" t="n"/>
-      <c r="X10" s="396" t="n"/>
-      <c r="Y10" s="396" t="n"/>
-      <c r="Z10" s="396" t="n"/>
-      <c r="AA10" s="396" t="n"/>
-      <c r="AB10" s="396" t="n"/>
-      <c r="AC10" s="396" t="n"/>
-      <c r="AD10" s="396" t="n"/>
-      <c r="AE10" s="396" t="n"/>
-      <c r="AF10" s="396" t="n"/>
-      <c r="AG10" s="396" t="n"/>
-      <c r="AH10" s="396" t="n"/>
-      <c r="AI10" s="396" t="n"/>
-      <c r="AJ10" s="396" t="n"/>
-      <c r="AK10" s="396" t="n"/>
-      <c r="AL10" s="396" t="n"/>
-      <c r="AM10" s="396" t="n"/>
-      <c r="AN10" s="396" t="n"/>
+      <c r="B10" s="529" t="n"/>
+      <c r="C10" s="530" t="n"/>
+      <c r="D10" s="530" t="n"/>
+      <c r="E10" s="530" t="n"/>
+      <c r="F10" s="530" t="n"/>
+      <c r="G10" s="530" t="n"/>
+      <c r="H10" s="354" t="n"/>
+      <c r="I10" s="354" t="n"/>
+      <c r="J10" s="354" t="n"/>
+      <c r="K10" s="354" t="n"/>
+      <c r="L10" s="354" t="n"/>
+      <c r="M10" s="354" t="n"/>
+      <c r="N10" s="354" t="n"/>
+      <c r="O10" s="354" t="n"/>
+      <c r="P10" s="354" t="n"/>
+      <c r="Q10" s="354" t="n"/>
+      <c r="R10" s="354" t="n"/>
+      <c r="S10" s="354" t="n"/>
+      <c r="T10" s="354" t="n"/>
+      <c r="U10" s="354" t="n"/>
+      <c r="V10" s="354" t="n"/>
+      <c r="W10" s="354" t="n"/>
+      <c r="X10" s="354" t="n"/>
+      <c r="Y10" s="354" t="n"/>
+      <c r="Z10" s="354" t="n"/>
+      <c r="AA10" s="354" t="n"/>
+      <c r="AB10" s="354" t="n"/>
+      <c r="AC10" s="354" t="n"/>
+      <c r="AD10" s="354" t="n"/>
+      <c r="AE10" s="354" t="n"/>
+      <c r="AF10" s="354" t="n"/>
+      <c r="AG10" s="354" t="n"/>
+      <c r="AH10" s="354" t="n"/>
+      <c r="AI10" s="354" t="n"/>
+      <c r="AJ10" s="354" t="n"/>
+      <c r="AK10" s="354" t="n"/>
+      <c r="AL10" s="354" t="n"/>
+      <c r="AM10" s="354" t="n"/>
+      <c r="AN10" s="531" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="394">
+      <c r="A11" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="395" t="n"/>
-      <c r="C11" s="395" t="n"/>
-      <c r="D11" s="395" t="n"/>
-      <c r="E11" s="395" t="n"/>
-      <c r="F11" s="395" t="n"/>
-      <c r="G11" s="395" t="n"/>
-      <c r="H11" s="396" t="n"/>
-      <c r="I11" s="396" t="n"/>
-      <c r="J11" s="396" t="n"/>
-      <c r="K11" s="396" t="n"/>
-      <c r="L11" s="396" t="n"/>
-      <c r="M11" s="396" t="n"/>
-      <c r="N11" s="396" t="n"/>
-      <c r="O11" s="396" t="n"/>
-      <c r="P11" s="396" t="n"/>
-      <c r="Q11" s="396" t="n"/>
-      <c r="R11" s="396" t="n"/>
-      <c r="S11" s="396" t="n"/>
-      <c r="T11" s="396" t="n"/>
-      <c r="U11" s="396" t="n"/>
-      <c r="V11" s="396" t="n"/>
-      <c r="W11" s="396" t="n"/>
-      <c r="X11" s="396" t="n"/>
-      <c r="Y11" s="396" t="n"/>
-      <c r="Z11" s="396" t="n"/>
-      <c r="AA11" s="396" t="n"/>
-      <c r="AB11" s="396" t="n"/>
-      <c r="AC11" s="396" t="n"/>
-      <c r="AD11" s="396" t="n"/>
-      <c r="AE11" s="396" t="n"/>
-      <c r="AF11" s="396" t="n"/>
-      <c r="AG11" s="396" t="n"/>
-      <c r="AH11" s="396" t="n"/>
-      <c r="AI11" s="396" t="n"/>
-      <c r="AJ11" s="396" t="n"/>
-      <c r="AK11" s="396" t="n"/>
-      <c r="AL11" s="396" t="n"/>
-      <c r="AM11" s="396" t="n"/>
-      <c r="AN11" s="396" t="n"/>
+      <c r="B11" s="529" t="n"/>
+      <c r="C11" s="530" t="n"/>
+      <c r="D11" s="530" t="n"/>
+      <c r="E11" s="530" t="n"/>
+      <c r="F11" s="530" t="n"/>
+      <c r="G11" s="530" t="n"/>
+      <c r="H11" s="354" t="n"/>
+      <c r="I11" s="354" t="n"/>
+      <c r="J11" s="354" t="n"/>
+      <c r="K11" s="354" t="n"/>
+      <c r="L11" s="354" t="n"/>
+      <c r="M11" s="354" t="n"/>
+      <c r="N11" s="354" t="n"/>
+      <c r="O11" s="354" t="n"/>
+      <c r="P11" s="354" t="n"/>
+      <c r="Q11" s="354" t="n"/>
+      <c r="R11" s="354" t="n"/>
+      <c r="S11" s="354" t="n"/>
+      <c r="T11" s="354" t="n"/>
+      <c r="U11" s="354" t="n"/>
+      <c r="V11" s="354" t="n"/>
+      <c r="W11" s="354" t="n"/>
+      <c r="X11" s="354" t="n"/>
+      <c r="Y11" s="354" t="n"/>
+      <c r="Z11" s="354" t="n"/>
+      <c r="AA11" s="354" t="n"/>
+      <c r="AB11" s="354" t="n"/>
+      <c r="AC11" s="354" t="n"/>
+      <c r="AD11" s="354" t="n"/>
+      <c r="AE11" s="354" t="n"/>
+      <c r="AF11" s="354" t="n"/>
+      <c r="AG11" s="354" t="n"/>
+      <c r="AH11" s="354" t="n"/>
+      <c r="AI11" s="354" t="n"/>
+      <c r="AJ11" s="354" t="n"/>
+      <c r="AK11" s="354" t="n"/>
+      <c r="AL11" s="354" t="n"/>
+      <c r="AM11" s="354" t="n"/>
+      <c r="AN11" s="531" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="394">
+      <c r="A12" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="395" t="n"/>
-      <c r="C12" s="395" t="n"/>
-      <c r="D12" s="395" t="n"/>
-      <c r="E12" s="395" t="n"/>
-      <c r="F12" s="395" t="n"/>
-      <c r="G12" s="395" t="n"/>
-      <c r="H12" s="396" t="n"/>
-      <c r="I12" s="396" t="n"/>
-      <c r="J12" s="396" t="n"/>
-      <c r="K12" s="396" t="n"/>
-      <c r="L12" s="396" t="n"/>
-      <c r="M12" s="396" t="n"/>
-      <c r="N12" s="396" t="n"/>
-      <c r="O12" s="396" t="n"/>
-      <c r="P12" s="396" t="n"/>
-      <c r="Q12" s="396" t="n"/>
-      <c r="R12" s="396" t="n"/>
-      <c r="S12" s="396" t="n"/>
-      <c r="T12" s="396" t="n"/>
-      <c r="U12" s="396" t="n"/>
-      <c r="V12" s="396" t="n"/>
-      <c r="W12" s="396" t="n"/>
-      <c r="X12" s="396" t="n"/>
-      <c r="Y12" s="396" t="n"/>
-      <c r="Z12" s="396" t="n"/>
-      <c r="AA12" s="396" t="n"/>
-      <c r="AB12" s="396" t="n"/>
-      <c r="AC12" s="396" t="n"/>
-      <c r="AD12" s="396" t="n"/>
-      <c r="AE12" s="396" t="n"/>
-      <c r="AF12" s="396" t="n"/>
-      <c r="AG12" s="396" t="n"/>
-      <c r="AH12" s="396" t="n"/>
-      <c r="AI12" s="396" t="n"/>
-      <c r="AJ12" s="396" t="n"/>
-      <c r="AK12" s="396" t="n"/>
-      <c r="AL12" s="396" t="n"/>
-      <c r="AM12" s="396" t="n"/>
-      <c r="AN12" s="396" t="n"/>
+      <c r="B12" s="529" t="n"/>
+      <c r="C12" s="530" t="n"/>
+      <c r="D12" s="530" t="n"/>
+      <c r="E12" s="530" t="n"/>
+      <c r="F12" s="530" t="n"/>
+      <c r="G12" s="530" t="n"/>
+      <c r="H12" s="354" t="n"/>
+      <c r="I12" s="354" t="n"/>
+      <c r="J12" s="354" t="n"/>
+      <c r="K12" s="354" t="n"/>
+      <c r="L12" s="354" t="n"/>
+      <c r="M12" s="354" t="n"/>
+      <c r="N12" s="354" t="n"/>
+      <c r="O12" s="354" t="n"/>
+      <c r="P12" s="354" t="n"/>
+      <c r="Q12" s="354" t="n"/>
+      <c r="R12" s="354" t="n"/>
+      <c r="S12" s="354" t="n"/>
+      <c r="T12" s="354" t="n"/>
+      <c r="U12" s="354" t="n"/>
+      <c r="V12" s="354" t="n"/>
+      <c r="W12" s="354" t="n"/>
+      <c r="X12" s="354" t="n"/>
+      <c r="Y12" s="354" t="n"/>
+      <c r="Z12" s="354" t="n"/>
+      <c r="AA12" s="354" t="n"/>
+      <c r="AB12" s="354" t="n"/>
+      <c r="AC12" s="354" t="n"/>
+      <c r="AD12" s="354" t="n"/>
+      <c r="AE12" s="354" t="n"/>
+      <c r="AF12" s="354" t="n"/>
+      <c r="AG12" s="354" t="n"/>
+      <c r="AH12" s="354" t="n"/>
+      <c r="AI12" s="354" t="n"/>
+      <c r="AJ12" s="354" t="n"/>
+      <c r="AK12" s="354" t="n"/>
+      <c r="AL12" s="354" t="n"/>
+      <c r="AM12" s="354" t="n"/>
+      <c r="AN12" s="531" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="394">
+      <c r="A13" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="395" t="n"/>
-      <c r="C13" s="395" t="n"/>
-      <c r="D13" s="395" t="n"/>
-      <c r="E13" s="395" t="n"/>
-      <c r="F13" s="395" t="n"/>
-      <c r="G13" s="395" t="n"/>
-      <c r="H13" s="396" t="n"/>
-      <c r="I13" s="396" t="n"/>
-      <c r="J13" s="396" t="n"/>
-      <c r="K13" s="396" t="n"/>
-      <c r="L13" s="396" t="n"/>
-      <c r="M13" s="396" t="n"/>
-      <c r="N13" s="396" t="n"/>
-      <c r="O13" s="396" t="n"/>
-      <c r="P13" s="396" t="n"/>
-      <c r="Q13" s="396" t="n"/>
-      <c r="R13" s="396" t="n"/>
-      <c r="S13" s="396" t="n"/>
-      <c r="T13" s="396" t="n"/>
-      <c r="U13" s="396" t="n"/>
-      <c r="V13" s="396" t="n"/>
-      <c r="W13" s="396" t="n"/>
-      <c r="X13" s="396" t="n"/>
-      <c r="Y13" s="396" t="n"/>
-      <c r="Z13" s="396" t="n"/>
-      <c r="AA13" s="396" t="n"/>
-      <c r="AB13" s="396" t="n"/>
-      <c r="AC13" s="396" t="n"/>
-      <c r="AD13" s="396" t="n"/>
-      <c r="AE13" s="396" t="n"/>
-      <c r="AF13" s="396" t="n"/>
-      <c r="AG13" s="396" t="n"/>
-      <c r="AH13" s="396" t="n"/>
-      <c r="AI13" s="396" t="n"/>
-      <c r="AJ13" s="396" t="n"/>
-      <c r="AK13" s="396" t="n"/>
-      <c r="AL13" s="396" t="n"/>
-      <c r="AM13" s="396" t="n"/>
-      <c r="AN13" s="396" t="n"/>
+      <c r="B13" s="529" t="n"/>
+      <c r="C13" s="530" t="n"/>
+      <c r="D13" s="530" t="n"/>
+      <c r="E13" s="530" t="n"/>
+      <c r="F13" s="530" t="n"/>
+      <c r="G13" s="530" t="n"/>
+      <c r="H13" s="354" t="n"/>
+      <c r="I13" s="354" t="n"/>
+      <c r="J13" s="354" t="n"/>
+      <c r="K13" s="354" t="n"/>
+      <c r="L13" s="354" t="n"/>
+      <c r="M13" s="354" t="n"/>
+      <c r="N13" s="354" t="n"/>
+      <c r="O13" s="354" t="n"/>
+      <c r="P13" s="354" t="n"/>
+      <c r="Q13" s="354" t="n"/>
+      <c r="R13" s="354" t="n"/>
+      <c r="S13" s="354" t="n"/>
+      <c r="T13" s="354" t="n"/>
+      <c r="U13" s="354" t="n"/>
+      <c r="V13" s="354" t="n"/>
+      <c r="W13" s="354" t="n"/>
+      <c r="X13" s="354" t="n"/>
+      <c r="Y13" s="354" t="n"/>
+      <c r="Z13" s="354" t="n"/>
+      <c r="AA13" s="354" t="n"/>
+      <c r="AB13" s="354" t="n"/>
+      <c r="AC13" s="354" t="n"/>
+      <c r="AD13" s="354" t="n"/>
+      <c r="AE13" s="354" t="n"/>
+      <c r="AF13" s="354" t="n"/>
+      <c r="AG13" s="354" t="n"/>
+      <c r="AH13" s="354" t="n"/>
+      <c r="AI13" s="354" t="n"/>
+      <c r="AJ13" s="354" t="n"/>
+      <c r="AK13" s="354" t="n"/>
+      <c r="AL13" s="354" t="n"/>
+      <c r="AM13" s="354" t="n"/>
+      <c r="AN13" s="531" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="394">
+      <c r="A14" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="395" t="n"/>
-      <c r="C14" s="395" t="n"/>
-      <c r="D14" s="395" t="n"/>
-      <c r="E14" s="395" t="n"/>
-      <c r="F14" s="395" t="n"/>
-      <c r="G14" s="395" t="n"/>
-      <c r="H14" s="396" t="n"/>
-      <c r="I14" s="396" t="n"/>
-      <c r="J14" s="396" t="n"/>
-      <c r="K14" s="396" t="n"/>
-      <c r="L14" s="396" t="n"/>
-      <c r="M14" s="396" t="n"/>
-      <c r="N14" s="396" t="n"/>
-      <c r="O14" s="396" t="n"/>
-      <c r="P14" s="396" t="n"/>
-      <c r="Q14" s="396" t="n"/>
-      <c r="R14" s="396" t="n"/>
-      <c r="S14" s="396" t="n"/>
-      <c r="T14" s="396" t="n"/>
-      <c r="U14" s="396" t="n"/>
-      <c r="V14" s="396" t="n"/>
-      <c r="W14" s="396" t="n"/>
-      <c r="X14" s="396" t="n"/>
-      <c r="Y14" s="396" t="n"/>
-      <c r="Z14" s="396" t="n"/>
-      <c r="AA14" s="396" t="n"/>
-      <c r="AB14" s="396" t="n"/>
-      <c r="AC14" s="396" t="n"/>
-      <c r="AD14" s="396" t="n"/>
-      <c r="AE14" s="396" t="n"/>
-      <c r="AF14" s="396" t="n"/>
-      <c r="AG14" s="396" t="n"/>
-      <c r="AH14" s="396" t="n"/>
-      <c r="AI14" s="396" t="n"/>
-      <c r="AJ14" s="396" t="n"/>
-      <c r="AK14" s="396" t="n"/>
-      <c r="AL14" s="396" t="n"/>
-      <c r="AM14" s="396" t="n"/>
-      <c r="AN14" s="396" t="n"/>
+      <c r="B14" s="529" t="n"/>
+      <c r="C14" s="530" t="n"/>
+      <c r="D14" s="530" t="n"/>
+      <c r="E14" s="530" t="n"/>
+      <c r="F14" s="530" t="n"/>
+      <c r="G14" s="530" t="n"/>
+      <c r="H14" s="354" t="n"/>
+      <c r="I14" s="354" t="n"/>
+      <c r="J14" s="354" t="n"/>
+      <c r="K14" s="354" t="n"/>
+      <c r="L14" s="354" t="n"/>
+      <c r="M14" s="354" t="n"/>
+      <c r="N14" s="354" t="n"/>
+      <c r="O14" s="354" t="n"/>
+      <c r="P14" s="354" t="n"/>
+      <c r="Q14" s="354" t="n"/>
+      <c r="R14" s="354" t="n"/>
+      <c r="S14" s="354" t="n"/>
+      <c r="T14" s="354" t="n"/>
+      <c r="U14" s="354" t="n"/>
+      <c r="V14" s="354" t="n"/>
+      <c r="W14" s="354" t="n"/>
+      <c r="X14" s="354" t="n"/>
+      <c r="Y14" s="354" t="n"/>
+      <c r="Z14" s="354" t="n"/>
+      <c r="AA14" s="354" t="n"/>
+      <c r="AB14" s="354" t="n"/>
+      <c r="AC14" s="354" t="n"/>
+      <c r="AD14" s="354" t="n"/>
+      <c r="AE14" s="354" t="n"/>
+      <c r="AF14" s="354" t="n"/>
+      <c r="AG14" s="354" t="n"/>
+      <c r="AH14" s="354" t="n"/>
+      <c r="AI14" s="354" t="n"/>
+      <c r="AJ14" s="354" t="n"/>
+      <c r="AK14" s="354" t="n"/>
+      <c r="AL14" s="354" t="n"/>
+      <c r="AM14" s="354" t="n"/>
+      <c r="AN14" s="531" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="394">
+      <c r="A15" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B15" s="395" t="n"/>
-      <c r="C15" s="395" t="n"/>
-      <c r="D15" s="395" t="n"/>
-      <c r="E15" s="395" t="n"/>
-      <c r="F15" s="395" t="n"/>
-      <c r="G15" s="395" t="n"/>
-      <c r="H15" s="396" t="n"/>
-      <c r="I15" s="396" t="n"/>
-      <c r="J15" s="396" t="n"/>
-      <c r="K15" s="396" t="n"/>
-      <c r="L15" s="396" t="n"/>
-      <c r="M15" s="396" t="n"/>
-      <c r="N15" s="396" t="n"/>
-      <c r="O15" s="396" t="n"/>
-      <c r="P15" s="396" t="n"/>
-      <c r="Q15" s="396" t="n"/>
-      <c r="R15" s="396" t="n"/>
-      <c r="S15" s="396" t="n"/>
-      <c r="T15" s="396" t="n"/>
-      <c r="U15" s="396" t="n"/>
-      <c r="V15" s="396" t="n"/>
-      <c r="W15" s="396" t="n"/>
-      <c r="X15" s="396" t="n"/>
-      <c r="Y15" s="396" t="n"/>
-      <c r="Z15" s="396" t="n"/>
-      <c r="AA15" s="396" t="n"/>
-      <c r="AB15" s="396" t="n"/>
-      <c r="AC15" s="396" t="n"/>
-      <c r="AD15" s="396" t="n"/>
-      <c r="AE15" s="396" t="n"/>
-      <c r="AF15" s="396" t="n"/>
-      <c r="AG15" s="396" t="n"/>
-      <c r="AH15" s="396" t="n"/>
-      <c r="AI15" s="396" t="n"/>
-      <c r="AJ15" s="396" t="n"/>
-      <c r="AK15" s="396" t="n"/>
-      <c r="AL15" s="396" t="n"/>
-      <c r="AM15" s="396" t="n"/>
-      <c r="AN15" s="396" t="n"/>
+      <c r="B15" s="529" t="n"/>
+      <c r="C15" s="530" t="n"/>
+      <c r="D15" s="530" t="n"/>
+      <c r="E15" s="530" t="n"/>
+      <c r="F15" s="530" t="n"/>
+      <c r="G15" s="530" t="n"/>
+      <c r="H15" s="354" t="n"/>
+      <c r="I15" s="354" t="n"/>
+      <c r="J15" s="354" t="n"/>
+      <c r="K15" s="354" t="n"/>
+      <c r="L15" s="354" t="n"/>
+      <c r="M15" s="354" t="n"/>
+      <c r="N15" s="354" t="n"/>
+      <c r="O15" s="354" t="n"/>
+      <c r="P15" s="354" t="n"/>
+      <c r="Q15" s="354" t="n"/>
+      <c r="R15" s="354" t="n"/>
+      <c r="S15" s="354" t="n"/>
+      <c r="T15" s="354" t="n"/>
+      <c r="U15" s="354" t="n"/>
+      <c r="V15" s="354" t="n"/>
+      <c r="W15" s="354" t="n"/>
+      <c r="X15" s="354" t="n"/>
+      <c r="Y15" s="354" t="n"/>
+      <c r="Z15" s="354" t="n"/>
+      <c r="AA15" s="354" t="n"/>
+      <c r="AB15" s="354" t="n"/>
+      <c r="AC15" s="354" t="n"/>
+      <c r="AD15" s="354" t="n"/>
+      <c r="AE15" s="354" t="n"/>
+      <c r="AF15" s="354" t="n"/>
+      <c r="AG15" s="354" t="n"/>
+      <c r="AH15" s="354" t="n"/>
+      <c r="AI15" s="354" t="n"/>
+      <c r="AJ15" s="354" t="n"/>
+      <c r="AK15" s="354" t="n"/>
+      <c r="AL15" s="354" t="n"/>
+      <c r="AM15" s="354" t="n"/>
+      <c r="AN15" s="531" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="394">
+      <c r="A16" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B16" s="395" t="n"/>
-      <c r="C16" s="395" t="n"/>
-      <c r="D16" s="395" t="n"/>
-      <c r="E16" s="395" t="n"/>
-      <c r="F16" s="395" t="n"/>
-      <c r="G16" s="395" t="n"/>
-      <c r="H16" s="396" t="n"/>
-      <c r="I16" s="396" t="n"/>
-      <c r="J16" s="396" t="n"/>
-      <c r="K16" s="396" t="n"/>
-      <c r="L16" s="396" t="n"/>
-      <c r="M16" s="396" t="n"/>
-      <c r="N16" s="396" t="n"/>
-      <c r="O16" s="396" t="n"/>
-      <c r="P16" s="396" t="n"/>
-      <c r="Q16" s="396" t="n"/>
-      <c r="R16" s="396" t="n"/>
-      <c r="S16" s="396" t="n"/>
-      <c r="T16" s="396" t="n"/>
-      <c r="U16" s="396" t="n"/>
-      <c r="V16" s="396" t="n"/>
-      <c r="W16" s="396" t="n"/>
-      <c r="X16" s="396" t="n"/>
-      <c r="Y16" s="396" t="n"/>
-      <c r="Z16" s="396" t="n"/>
-      <c r="AA16" s="396" t="n"/>
-      <c r="AB16" s="396" t="n"/>
-      <c r="AC16" s="396" t="n"/>
-      <c r="AD16" s="396" t="n"/>
-      <c r="AE16" s="396" t="n"/>
-      <c r="AF16" s="396" t="n"/>
-      <c r="AG16" s="396" t="n"/>
-      <c r="AH16" s="396" t="n"/>
-      <c r="AI16" s="396" t="n"/>
-      <c r="AJ16" s="396" t="n"/>
-      <c r="AK16" s="396" t="n"/>
-      <c r="AL16" s="396" t="n"/>
-      <c r="AM16" s="396" t="n"/>
-      <c r="AN16" s="396" t="n"/>
+      <c r="B16" s="529" t="n"/>
+      <c r="C16" s="530" t="n"/>
+      <c r="D16" s="530" t="n"/>
+      <c r="E16" s="530" t="n"/>
+      <c r="F16" s="530" t="n"/>
+      <c r="G16" s="530" t="n"/>
+      <c r="H16" s="354" t="n"/>
+      <c r="I16" s="354" t="n"/>
+      <c r="J16" s="354" t="n"/>
+      <c r="K16" s="354" t="n"/>
+      <c r="L16" s="354" t="n"/>
+      <c r="M16" s="354" t="n"/>
+      <c r="N16" s="354" t="n"/>
+      <c r="O16" s="354" t="n"/>
+      <c r="P16" s="354" t="n"/>
+      <c r="Q16" s="354" t="n"/>
+      <c r="R16" s="354" t="n"/>
+      <c r="S16" s="354" t="n"/>
+      <c r="T16" s="354" t="n"/>
+      <c r="U16" s="354" t="n"/>
+      <c r="V16" s="354" t="n"/>
+      <c r="W16" s="354" t="n"/>
+      <c r="X16" s="354" t="n"/>
+      <c r="Y16" s="354" t="n"/>
+      <c r="Z16" s="354" t="n"/>
+      <c r="AA16" s="354" t="n"/>
+      <c r="AB16" s="354" t="n"/>
+      <c r="AC16" s="354" t="n"/>
+      <c r="AD16" s="354" t="n"/>
+      <c r="AE16" s="354" t="n"/>
+      <c r="AF16" s="354" t="n"/>
+      <c r="AG16" s="354" t="n"/>
+      <c r="AH16" s="354" t="n"/>
+      <c r="AI16" s="354" t="n"/>
+      <c r="AJ16" s="354" t="n"/>
+      <c r="AK16" s="354" t="n"/>
+      <c r="AL16" s="354" t="n"/>
+      <c r="AM16" s="354" t="n"/>
+      <c r="AN16" s="531" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="394">
+      <c r="A17" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B17" s="395" t="n"/>
-      <c r="C17" s="395" t="n"/>
-      <c r="D17" s="395" t="n"/>
-      <c r="E17" s="395" t="n"/>
-      <c r="F17" s="395" t="n"/>
-      <c r="G17" s="395" t="n"/>
-      <c r="H17" s="396" t="n"/>
-      <c r="I17" s="396" t="n"/>
-      <c r="J17" s="396" t="n"/>
-      <c r="K17" s="396" t="n"/>
-      <c r="L17" s="396" t="n"/>
-      <c r="M17" s="396" t="n"/>
-      <c r="N17" s="396" t="n"/>
-      <c r="O17" s="396" t="n"/>
-      <c r="P17" s="396" t="n"/>
-      <c r="Q17" s="396" t="n"/>
-      <c r="R17" s="396" t="n"/>
-      <c r="S17" s="396" t="n"/>
-      <c r="T17" s="396" t="n"/>
-      <c r="U17" s="396" t="n"/>
-      <c r="V17" s="396" t="n"/>
-      <c r="W17" s="396" t="n"/>
-      <c r="X17" s="396" t="n"/>
-      <c r="Y17" s="396" t="n"/>
-      <c r="Z17" s="396" t="n"/>
-      <c r="AA17" s="396" t="n"/>
-      <c r="AB17" s="396" t="n"/>
-      <c r="AC17" s="396" t="n"/>
-      <c r="AD17" s="396" t="n"/>
-      <c r="AE17" s="396" t="n"/>
-      <c r="AF17" s="396" t="n"/>
-      <c r="AG17" s="396" t="n"/>
-      <c r="AH17" s="396" t="n"/>
-      <c r="AI17" s="396" t="n"/>
-      <c r="AJ17" s="396" t="n"/>
-      <c r="AK17" s="396" t="n"/>
-      <c r="AL17" s="396" t="n"/>
-      <c r="AM17" s="396" t="n"/>
-      <c r="AN17" s="396" t="n"/>
+      <c r="B17" s="529" t="n"/>
+      <c r="C17" s="530" t="n"/>
+      <c r="D17" s="530" t="n"/>
+      <c r="E17" s="530" t="n"/>
+      <c r="F17" s="530" t="n"/>
+      <c r="G17" s="530" t="n"/>
+      <c r="H17" s="354" t="n"/>
+      <c r="I17" s="354" t="n"/>
+      <c r="J17" s="354" t="n"/>
+      <c r="K17" s="354" t="n"/>
+      <c r="L17" s="354" t="n"/>
+      <c r="M17" s="354" t="n"/>
+      <c r="N17" s="354" t="n"/>
+      <c r="O17" s="354" t="n"/>
+      <c r="P17" s="354" t="n"/>
+      <c r="Q17" s="354" t="n"/>
+      <c r="R17" s="354" t="n"/>
+      <c r="S17" s="354" t="n"/>
+      <c r="T17" s="354" t="n"/>
+      <c r="U17" s="354" t="n"/>
+      <c r="V17" s="354" t="n"/>
+      <c r="W17" s="354" t="n"/>
+      <c r="X17" s="354" t="n"/>
+      <c r="Y17" s="354" t="n"/>
+      <c r="Z17" s="354" t="n"/>
+      <c r="AA17" s="354" t="n"/>
+      <c r="AB17" s="354" t="n"/>
+      <c r="AC17" s="354" t="n"/>
+      <c r="AD17" s="354" t="n"/>
+      <c r="AE17" s="354" t="n"/>
+      <c r="AF17" s="354" t="n"/>
+      <c r="AG17" s="354" t="n"/>
+      <c r="AH17" s="354" t="n"/>
+      <c r="AI17" s="354" t="n"/>
+      <c r="AJ17" s="354" t="n"/>
+      <c r="AK17" s="354" t="n"/>
+      <c r="AL17" s="354" t="n"/>
+      <c r="AM17" s="354" t="n"/>
+      <c r="AN17" s="531" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="394">
+      <c r="A18" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B18" s="395" t="n"/>
-      <c r="C18" s="395" t="n"/>
-      <c r="D18" s="395" t="n"/>
-      <c r="E18" s="395" t="n"/>
-      <c r="F18" s="395" t="n"/>
-      <c r="G18" s="395" t="n"/>
-      <c r="H18" s="396" t="n"/>
-      <c r="I18" s="396" t="n"/>
-      <c r="J18" s="396" t="n"/>
-      <c r="K18" s="396" t="n"/>
-      <c r="L18" s="396" t="n"/>
-      <c r="M18" s="396" t="n"/>
-      <c r="N18" s="396" t="n"/>
-      <c r="O18" s="396" t="n"/>
-      <c r="P18" s="396" t="n"/>
-      <c r="Q18" s="396" t="n"/>
-      <c r="R18" s="396" t="n"/>
-      <c r="S18" s="396" t="n"/>
-      <c r="T18" s="396" t="n"/>
-      <c r="U18" s="396" t="n"/>
-      <c r="V18" s="396" t="n"/>
-      <c r="W18" s="396" t="n"/>
-      <c r="X18" s="396" t="n"/>
-      <c r="Y18" s="396" t="n"/>
-      <c r="Z18" s="396" t="n"/>
-      <c r="AA18" s="396" t="n"/>
-      <c r="AB18" s="396" t="n"/>
-      <c r="AC18" s="396" t="n"/>
-      <c r="AD18" s="396" t="n"/>
-      <c r="AE18" s="396" t="n"/>
-      <c r="AF18" s="396" t="n"/>
-      <c r="AG18" s="396" t="n"/>
-      <c r="AH18" s="396" t="n"/>
-      <c r="AI18" s="396" t="n"/>
-      <c r="AJ18" s="396" t="n"/>
-      <c r="AK18" s="396" t="n"/>
-      <c r="AL18" s="396" t="n"/>
-      <c r="AM18" s="396" t="n"/>
-      <c r="AN18" s="396" t="n"/>
+      <c r="B18" s="529" t="n"/>
+      <c r="C18" s="530" t="n"/>
+      <c r="D18" s="530" t="n"/>
+      <c r="E18" s="530" t="n"/>
+      <c r="F18" s="530" t="n"/>
+      <c r="G18" s="530" t="n"/>
+      <c r="H18" s="354" t="n"/>
+      <c r="I18" s="354" t="n"/>
+      <c r="J18" s="354" t="n"/>
+      <c r="K18" s="354" t="n"/>
+      <c r="L18" s="354" t="n"/>
+      <c r="M18" s="354" t="n"/>
+      <c r="N18" s="354" t="n"/>
+      <c r="O18" s="354" t="n"/>
+      <c r="P18" s="354" t="n"/>
+      <c r="Q18" s="354" t="n"/>
+      <c r="R18" s="354" t="n"/>
+      <c r="S18" s="354" t="n"/>
+      <c r="T18" s="354" t="n"/>
+      <c r="U18" s="354" t="n"/>
+      <c r="V18" s="354" t="n"/>
+      <c r="W18" s="354" t="n"/>
+      <c r="X18" s="354" t="n"/>
+      <c r="Y18" s="354" t="n"/>
+      <c r="Z18" s="354" t="n"/>
+      <c r="AA18" s="354" t="n"/>
+      <c r="AB18" s="354" t="n"/>
+      <c r="AC18" s="354" t="n"/>
+      <c r="AD18" s="354" t="n"/>
+      <c r="AE18" s="354" t="n"/>
+      <c r="AF18" s="354" t="n"/>
+      <c r="AG18" s="354" t="n"/>
+      <c r="AH18" s="354" t="n"/>
+      <c r="AI18" s="354" t="n"/>
+      <c r="AJ18" s="354" t="n"/>
+      <c r="AK18" s="354" t="n"/>
+      <c r="AL18" s="354" t="n"/>
+      <c r="AM18" s="354" t="n"/>
+      <c r="AN18" s="531" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="394">
+      <c r="A19" s="532">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B19" s="395" t="n"/>
-      <c r="C19" s="395" t="n"/>
-      <c r="D19" s="395" t="n"/>
-      <c r="E19" s="395" t="n"/>
-      <c r="F19" s="395" t="n"/>
-      <c r="G19" s="395" t="n"/>
-      <c r="H19" s="396" t="n"/>
-      <c r="I19" s="396" t="n"/>
-      <c r="J19" s="396" t="n"/>
-      <c r="K19" s="396" t="n"/>
-      <c r="L19" s="396" t="n"/>
-      <c r="M19" s="396" t="n"/>
-      <c r="N19" s="396" t="n"/>
-      <c r="O19" s="396" t="n"/>
-      <c r="P19" s="396" t="n"/>
-      <c r="Q19" s="396" t="n"/>
-      <c r="R19" s="396" t="n"/>
-      <c r="S19" s="396" t="n"/>
-      <c r="T19" s="396" t="n"/>
-      <c r="U19" s="396" t="n"/>
-      <c r="V19" s="396" t="n"/>
-      <c r="W19" s="396" t="n"/>
-      <c r="X19" s="396" t="n"/>
-      <c r="Y19" s="396" t="n"/>
-      <c r="Z19" s="396" t="n"/>
-      <c r="AA19" s="396" t="n"/>
-      <c r="AB19" s="396" t="n"/>
-      <c r="AC19" s="396" t="n"/>
-      <c r="AD19" s="396" t="n"/>
-      <c r="AE19" s="396" t="n"/>
-      <c r="AF19" s="396" t="n"/>
-      <c r="AG19" s="396" t="n"/>
-      <c r="AH19" s="396" t="n"/>
-      <c r="AI19" s="396" t="n"/>
-      <c r="AJ19" s="396" t="n"/>
-      <c r="AK19" s="396" t="n"/>
-      <c r="AL19" s="396" t="n"/>
-      <c r="AM19" s="396" t="n"/>
-      <c r="AN19" s="396" t="n"/>
+      <c r="B19" s="533" t="n"/>
+      <c r="C19" s="534" t="n"/>
+      <c r="D19" s="534" t="n"/>
+      <c r="E19" s="534" t="n"/>
+      <c r="F19" s="534" t="n"/>
+      <c r="G19" s="534" t="n"/>
+      <c r="H19" s="535" t="n"/>
+      <c r="I19" s="535" t="n"/>
+      <c r="J19" s="535" t="n"/>
+      <c r="K19" s="535" t="n"/>
+      <c r="L19" s="535" t="n"/>
+      <c r="M19" s="535" t="n"/>
+      <c r="N19" s="535" t="n"/>
+      <c r="O19" s="535" t="n"/>
+      <c r="P19" s="535" t="n"/>
+      <c r="Q19" s="535" t="n"/>
+      <c r="R19" s="535" t="n"/>
+      <c r="S19" s="535" t="n"/>
+      <c r="T19" s="535" t="n"/>
+      <c r="U19" s="535" t="n"/>
+      <c r="V19" s="535" t="n"/>
+      <c r="W19" s="535" t="n"/>
+      <c r="X19" s="535" t="n"/>
+      <c r="Y19" s="535" t="n"/>
+      <c r="Z19" s="535" t="n"/>
+      <c r="AA19" s="535" t="n"/>
+      <c r="AB19" s="535" t="n"/>
+      <c r="AC19" s="535" t="n"/>
+      <c r="AD19" s="535" t="n"/>
+      <c r="AE19" s="535" t="n"/>
+      <c r="AF19" s="535" t="n"/>
+      <c r="AG19" s="535" t="n"/>
+      <c r="AH19" s="535" t="n"/>
+      <c r="AI19" s="535" t="n"/>
+      <c r="AJ19" s="535" t="n"/>
+      <c r="AK19" s="535" t="n"/>
+      <c r="AL19" s="535" t="n"/>
+      <c r="AM19" s="535" t="n"/>
+      <c r="AN19" s="536" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -8811,8 +9695,9 @@
   </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8868,254 +9753,260 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="391" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="510" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="420" t="n"/>
-      <c r="C1" s="420" t="n"/>
-      <c r="D1" s="420" t="n"/>
-      <c r="E1" s="420" t="n"/>
-      <c r="F1" s="420" t="n"/>
-      <c r="G1" s="421" t="n"/>
-      <c r="H1" s="346" t="n"/>
-      <c r="I1" s="346" t="n"/>
-      <c r="J1" s="346" t="n"/>
-      <c r="K1" s="346" t="n"/>
-      <c r="L1" s="346" t="n"/>
-      <c r="M1" s="346" t="n"/>
-      <c r="N1" s="346" t="n"/>
-      <c r="O1" s="346" t="n"/>
-      <c r="P1" s="346" t="n"/>
-      <c r="Q1" s="346" t="n"/>
-      <c r="R1" s="346" t="n"/>
-      <c r="S1" s="346" t="n"/>
-      <c r="T1" s="346" t="n"/>
-      <c r="U1" s="346" t="n"/>
-      <c r="V1" s="346" t="n"/>
-      <c r="W1" s="346" t="n"/>
-      <c r="X1" s="346" t="n"/>
-      <c r="Y1" s="346" t="n"/>
-      <c r="Z1" s="346" t="n"/>
-      <c r="AA1" s="346" t="n"/>
-      <c r="AB1" s="346" t="n"/>
-      <c r="AC1" s="346" t="n"/>
-      <c r="AD1" s="346" t="n"/>
-      <c r="AE1" s="346" t="n"/>
-      <c r="AF1" s="346" t="n"/>
-      <c r="AG1" s="346" t="n"/>
-      <c r="AH1" s="346" t="n"/>
-      <c r="AI1" s="346" t="n"/>
-      <c r="AJ1" s="346" t="n"/>
-      <c r="AK1" s="346" t="n"/>
-      <c r="AL1" s="346" t="n"/>
-      <c r="AM1" s="346" t="n"/>
-      <c r="AN1" s="346" t="n"/>
+      <c r="B1" s="426" t="n"/>
+      <c r="C1" s="426" t="n"/>
+      <c r="D1" s="426" t="n"/>
+      <c r="E1" s="426" t="n"/>
+      <c r="F1" s="426" t="n"/>
+      <c r="G1" s="426" t="n"/>
+      <c r="H1" s="511" t="n"/>
+      <c r="I1" s="428" t="n"/>
+      <c r="J1" s="429" t="n"/>
+      <c r="K1" s="429" t="n"/>
+      <c r="L1" s="429" t="n"/>
+      <c r="M1" s="429" t="n"/>
+      <c r="N1" s="429" t="n"/>
+      <c r="O1" s="429" t="n"/>
+      <c r="P1" s="429" t="n"/>
+      <c r="Q1" s="429" t="n"/>
+      <c r="R1" s="429" t="n"/>
+      <c r="S1" s="429" t="n"/>
+      <c r="T1" s="429" t="n"/>
+      <c r="U1" s="429" t="n"/>
+      <c r="V1" s="429" t="n"/>
+      <c r="W1" s="429" t="n"/>
+      <c r="X1" s="429" t="n"/>
+      <c r="Y1" s="429" t="n"/>
+      <c r="Z1" s="429" t="n"/>
+      <c r="AA1" s="429" t="n"/>
+      <c r="AB1" s="429" t="n"/>
+      <c r="AC1" s="429" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="431" t="n"/>
+      <c r="AF1" s="432" t="n"/>
+      <c r="AG1" s="432" t="n"/>
+      <c r="AH1" s="433" t="n"/>
+      <c r="AI1" s="434" t="n"/>
+      <c r="AJ1" s="435" t="n"/>
+      <c r="AK1" s="435" t="n"/>
+      <c r="AL1" s="435" t="n"/>
+      <c r="AM1" s="435" t="n"/>
+      <c r="AN1" s="436" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="317" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="512" t="inlineStr">
         <is>
           <t>Reference plan / lot / method / release documents from their owning source.</t>
         </is>
       </c>
-      <c r="H2" s="346" t="n"/>
-      <c r="I2" s="346" t="n"/>
-      <c r="J2" s="346" t="n"/>
-      <c r="K2" s="346" t="n"/>
-      <c r="L2" s="346" t="n"/>
-      <c r="M2" s="346" t="n"/>
-      <c r="N2" s="346" t="n"/>
-      <c r="O2" s="346" t="n"/>
-      <c r="P2" s="346" t="n"/>
-      <c r="Q2" s="346" t="n"/>
-      <c r="R2" s="346" t="n"/>
-      <c r="S2" s="346" t="n"/>
-      <c r="T2" s="346" t="n"/>
-      <c r="U2" s="346" t="n"/>
-      <c r="V2" s="346" t="n"/>
-      <c r="W2" s="346" t="n"/>
-      <c r="X2" s="346" t="n"/>
-      <c r="Y2" s="346" t="n"/>
-      <c r="Z2" s="346" t="n"/>
-      <c r="AA2" s="346" t="n"/>
-      <c r="AB2" s="346" t="n"/>
-      <c r="AC2" s="346" t="n"/>
-      <c r="AD2" s="346" t="n"/>
-      <c r="AE2" s="346" t="n"/>
-      <c r="AF2" s="346" t="n"/>
-      <c r="AG2" s="346" t="n"/>
-      <c r="AH2" s="346" t="n"/>
-      <c r="AI2" s="346" t="n"/>
-      <c r="AJ2" s="346" t="n"/>
-      <c r="AK2" s="346" t="n"/>
-      <c r="AL2" s="346" t="n"/>
-      <c r="AM2" s="346" t="n"/>
-      <c r="AN2" s="346" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="513" t="n"/>
+      <c r="I2" s="439" t="n"/>
+      <c r="J2" s="440" t="n"/>
+      <c r="K2" s="440" t="n"/>
+      <c r="L2" s="440" t="n"/>
+      <c r="M2" s="440" t="n"/>
+      <c r="N2" s="440" t="n"/>
+      <c r="O2" s="440" t="n"/>
+      <c r="P2" s="440" t="n"/>
+      <c r="Q2" s="440" t="n"/>
+      <c r="R2" s="440" t="n"/>
+      <c r="S2" s="440" t="n"/>
+      <c r="T2" s="440" t="n"/>
+      <c r="U2" s="440" t="n"/>
+      <c r="V2" s="440" t="n"/>
+      <c r="W2" s="440" t="n"/>
+      <c r="X2" s="440" t="n"/>
+      <c r="Y2" s="440" t="n"/>
+      <c r="Z2" s="440" t="n"/>
+      <c r="AA2" s="440" t="n"/>
+      <c r="AB2" s="440" t="n"/>
+      <c r="AC2" s="440" t="n"/>
+      <c r="AD2" s="441" t="n"/>
+      <c r="AE2" s="442" t="n"/>
+      <c r="AF2" s="443" t="n"/>
+      <c r="AG2" s="443" t="n"/>
+      <c r="AH2" s="444" t="n"/>
+      <c r="AI2" s="445" t="n"/>
+      <c r="AJ2" s="446" t="n"/>
+      <c r="AK2" s="446" t="n"/>
+      <c r="AL2" s="446" t="n"/>
+      <c r="AM2" s="446" t="n"/>
+      <c r="AN2" s="447" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="346" t="n"/>
-      <c r="B3" s="346" t="n"/>
-      <c r="C3" s="346" t="n"/>
-      <c r="D3" s="346" t="n"/>
-      <c r="E3" s="346" t="n"/>
-      <c r="F3" s="346" t="n"/>
-      <c r="G3" s="346" t="n"/>
-      <c r="H3" s="346" t="n"/>
-      <c r="I3" s="346" t="n"/>
-      <c r="J3" s="346" t="n"/>
-      <c r="K3" s="346" t="n"/>
-      <c r="L3" s="346" t="n"/>
-      <c r="M3" s="346" t="n"/>
-      <c r="N3" s="346" t="n"/>
-      <c r="O3" s="346" t="n"/>
-      <c r="P3" s="346" t="n"/>
-      <c r="Q3" s="346" t="n"/>
-      <c r="R3" s="346" t="n"/>
-      <c r="S3" s="346" t="n"/>
-      <c r="T3" s="346" t="n"/>
-      <c r="U3" s="346" t="n"/>
-      <c r="V3" s="346" t="n"/>
-      <c r="W3" s="346" t="n"/>
-      <c r="X3" s="346" t="n"/>
-      <c r="Y3" s="346" t="n"/>
-      <c r="Z3" s="346" t="n"/>
-      <c r="AA3" s="346" t="n"/>
-      <c r="AB3" s="346" t="n"/>
-      <c r="AC3" s="346" t="n"/>
-      <c r="AD3" s="346" t="n"/>
-      <c r="AE3" s="346" t="n"/>
-      <c r="AF3" s="346" t="n"/>
-      <c r="AG3" s="346" t="n"/>
-      <c r="AH3" s="346" t="n"/>
-      <c r="AI3" s="346" t="n"/>
-      <c r="AJ3" s="346" t="n"/>
-      <c r="AK3" s="346" t="n"/>
-      <c r="AL3" s="346" t="n"/>
-      <c r="AM3" s="346" t="n"/>
-      <c r="AN3" s="346" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="514" t="n"/>
+      <c r="B3" s="515" t="n"/>
+      <c r="C3" s="515" t="n"/>
+      <c r="D3" s="515" t="n"/>
+      <c r="E3" s="515" t="n"/>
+      <c r="F3" s="515" t="n"/>
+      <c r="G3" s="515" t="n"/>
+      <c r="H3" s="513" t="n"/>
+      <c r="I3" s="439" t="n"/>
+      <c r="J3" s="440" t="n"/>
+      <c r="K3" s="440" t="n"/>
+      <c r="L3" s="440" t="n"/>
+      <c r="M3" s="440" t="n"/>
+      <c r="N3" s="440" t="n"/>
+      <c r="O3" s="440" t="n"/>
+      <c r="P3" s="440" t="n"/>
+      <c r="Q3" s="440" t="n"/>
+      <c r="R3" s="440" t="n"/>
+      <c r="S3" s="440" t="n"/>
+      <c r="T3" s="440" t="n"/>
+      <c r="U3" s="440" t="n"/>
+      <c r="V3" s="440" t="n"/>
+      <c r="W3" s="440" t="n"/>
+      <c r="X3" s="440" t="n"/>
+      <c r="Y3" s="440" t="n"/>
+      <c r="Z3" s="440" t="n"/>
+      <c r="AA3" s="440" t="n"/>
+      <c r="AB3" s="440" t="n"/>
+      <c r="AC3" s="440" t="n"/>
+      <c r="AD3" s="441" t="n"/>
+      <c r="AE3" s="442" t="n"/>
+      <c r="AF3" s="443" t="n"/>
+      <c r="AG3" s="443" t="n"/>
+      <c r="AH3" s="444" t="n"/>
+      <c r="AI3" s="445" t="n"/>
+      <c r="AJ3" s="446" t="n"/>
+      <c r="AK3" s="446" t="n"/>
+      <c r="AL3" s="446" t="n"/>
+      <c r="AM3" s="446" t="n"/>
+      <c r="AN3" s="447" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="362" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="516" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="362" t="inlineStr">
+      <c r="B4" s="517" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="362" t="inlineStr">
+      <c r="C4" s="517" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="346" t="n"/>
-      <c r="E4" s="346" t="n"/>
-      <c r="F4" s="346" t="n"/>
-      <c r="G4" s="346" t="n"/>
-      <c r="H4" s="346" t="n"/>
-      <c r="I4" s="346" t="n"/>
-      <c r="J4" s="346" t="n"/>
-      <c r="K4" s="346" t="n"/>
-      <c r="L4" s="346" t="n"/>
-      <c r="M4" s="346" t="n"/>
-      <c r="N4" s="346" t="n"/>
-      <c r="O4" s="346" t="n"/>
-      <c r="P4" s="346" t="n"/>
-      <c r="Q4" s="346" t="n"/>
-      <c r="R4" s="346" t="n"/>
-      <c r="S4" s="346" t="n"/>
-      <c r="T4" s="346" t="n"/>
-      <c r="U4" s="346" t="n"/>
-      <c r="V4" s="346" t="n"/>
-      <c r="W4" s="346" t="n"/>
-      <c r="X4" s="346" t="n"/>
-      <c r="Y4" s="346" t="n"/>
-      <c r="Z4" s="346" t="n"/>
-      <c r="AA4" s="346" t="n"/>
-      <c r="AB4" s="346" t="n"/>
-      <c r="AC4" s="346" t="n"/>
-      <c r="AD4" s="346" t="n"/>
-      <c r="AE4" s="346" t="n"/>
-      <c r="AF4" s="346" t="n"/>
-      <c r="AG4" s="346" t="n"/>
-      <c r="AH4" s="346" t="n"/>
-      <c r="AI4" s="346" t="n"/>
-      <c r="AJ4" s="346" t="n"/>
-      <c r="AK4" s="346" t="n"/>
-      <c r="AL4" s="346" t="n"/>
-      <c r="AM4" s="346" t="n"/>
-      <c r="AN4" s="346" t="n"/>
+      <c r="D4" s="515" t="n"/>
+      <c r="E4" s="515" t="n"/>
+      <c r="F4" s="515" t="n"/>
+      <c r="G4" s="515" t="n"/>
+      <c r="H4" s="513" t="n"/>
+      <c r="I4" s="448" t="n"/>
+      <c r="J4" s="449" t="n"/>
+      <c r="K4" s="449" t="n"/>
+      <c r="L4" s="449" t="n"/>
+      <c r="M4" s="449" t="n"/>
+      <c r="N4" s="449" t="n"/>
+      <c r="O4" s="449" t="n"/>
+      <c r="P4" s="449" t="n"/>
+      <c r="Q4" s="449" t="n"/>
+      <c r="R4" s="449" t="n"/>
+      <c r="S4" s="449" t="n"/>
+      <c r="T4" s="449" t="n"/>
+      <c r="U4" s="449" t="n"/>
+      <c r="V4" s="449" t="n"/>
+      <c r="W4" s="449" t="n"/>
+      <c r="X4" s="449" t="n"/>
+      <c r="Y4" s="449" t="n"/>
+      <c r="Z4" s="449" t="n"/>
+      <c r="AA4" s="449" t="n"/>
+      <c r="AB4" s="449" t="n"/>
+      <c r="AC4" s="449" t="n"/>
+      <c r="AD4" s="450" t="n"/>
+      <c r="AE4" s="442" t="n"/>
+      <c r="AF4" s="443" t="n"/>
+      <c r="AG4" s="443" t="n"/>
+      <c r="AH4" s="444" t="n"/>
+      <c r="AI4" s="445" t="n"/>
+      <c r="AJ4" s="446" t="n"/>
+      <c r="AK4" s="446" t="n"/>
+      <c r="AL4" s="446" t="n"/>
+      <c r="AM4" s="446" t="n"/>
+      <c r="AN4" s="447" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="392" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="518" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="393" t="inlineStr">
+      <c r="B5" s="519" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="393" t="inlineStr">
+      <c r="C5" s="519" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="346" t="n"/>
-      <c r="E5" s="346" t="n"/>
-      <c r="F5" s="346" t="n"/>
-      <c r="G5" s="346" t="n"/>
-      <c r="H5" s="346" t="n"/>
-      <c r="I5" s="346" t="n"/>
-      <c r="J5" s="346" t="n"/>
-      <c r="K5" s="346" t="n"/>
-      <c r="L5" s="346" t="n"/>
-      <c r="M5" s="346" t="n"/>
-      <c r="N5" s="346" t="n"/>
-      <c r="O5" s="346" t="n"/>
-      <c r="P5" s="346" t="n"/>
-      <c r="Q5" s="346" t="n"/>
-      <c r="R5" s="346" t="n"/>
-      <c r="S5" s="346" t="n"/>
-      <c r="T5" s="346" t="n"/>
-      <c r="U5" s="346" t="n"/>
-      <c r="V5" s="346" t="n"/>
-      <c r="W5" s="346" t="n"/>
-      <c r="X5" s="346" t="n"/>
-      <c r="Y5" s="346" t="n"/>
-      <c r="Z5" s="346" t="n"/>
-      <c r="AA5" s="346" t="n"/>
-      <c r="AB5" s="346" t="n"/>
-      <c r="AC5" s="346" t="n"/>
-      <c r="AD5" s="346" t="n"/>
-      <c r="AE5" s="346" t="n"/>
-      <c r="AF5" s="346" t="n"/>
-      <c r="AG5" s="346" t="n"/>
-      <c r="AH5" s="346" t="n"/>
-      <c r="AI5" s="346" t="n"/>
-      <c r="AJ5" s="346" t="n"/>
-      <c r="AK5" s="346" t="n"/>
-      <c r="AL5" s="346" t="n"/>
-      <c r="AM5" s="346" t="n"/>
-      <c r="AN5" s="346" t="n"/>
+      <c r="D5" s="537" t="n"/>
+      <c r="E5" s="537" t="n"/>
+      <c r="F5" s="537" t="n"/>
+      <c r="G5" s="537" t="n"/>
+      <c r="H5" s="520" t="n"/>
+      <c r="I5" s="454" t="n"/>
+      <c r="J5" s="455" t="n"/>
+      <c r="K5" s="455" t="n"/>
+      <c r="L5" s="455" t="n"/>
+      <c r="M5" s="455" t="n"/>
+      <c r="N5" s="455" t="n"/>
+      <c r="O5" s="455" t="n"/>
+      <c r="P5" s="455" t="n"/>
+      <c r="Q5" s="455" t="n"/>
+      <c r="R5" s="455" t="n"/>
+      <c r="S5" s="455" t="n"/>
+      <c r="T5" s="455" t="n"/>
+      <c r="U5" s="455" t="n"/>
+      <c r="V5" s="455" t="n"/>
+      <c r="W5" s="455" t="n"/>
+      <c r="X5" s="455" t="n"/>
+      <c r="Y5" s="455" t="n"/>
+      <c r="Z5" s="455" t="n"/>
+      <c r="AA5" s="455" t="n"/>
+      <c r="AB5" s="455" t="n"/>
+      <c r="AC5" s="455" t="n"/>
+      <c r="AD5" s="456" t="n"/>
+      <c r="AE5" s="457" t="n"/>
+      <c r="AF5" s="458" t="n"/>
+      <c r="AG5" s="458" t="n"/>
+      <c r="AH5" s="459" t="n"/>
+      <c r="AI5" s="460" t="n"/>
+      <c r="AJ5" s="461" t="n"/>
+      <c r="AK5" s="461" t="n"/>
+      <c r="AL5" s="461" t="n"/>
+      <c r="AM5" s="461" t="n"/>
+      <c r="AN5" s="462" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="392" t="inlineStr">
+      <c r="A6" s="521" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="393" t="inlineStr">
+      <c r="B6" s="522" t="inlineStr">
         <is>
           <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
         </is>
       </c>
-      <c r="C6" s="393" t="inlineStr">
+      <c r="C6" s="523" t="inlineStr">
         <is>
           <t>This form does not replace SOP-605; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-605; this form captures results, checks, decisions or exceptions only.
@@ -9123,529 +10014,529 @@
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="346" t="n"/>
-      <c r="E6" s="346" t="n"/>
-      <c r="F6" s="346" t="n"/>
-      <c r="G6" s="346" t="n"/>
-      <c r="H6" s="346" t="n"/>
-      <c r="I6" s="346" t="n"/>
-      <c r="J6" s="346" t="n"/>
-      <c r="K6" s="346" t="n"/>
-      <c r="L6" s="346" t="n"/>
-      <c r="M6" s="346" t="n"/>
-      <c r="N6" s="346" t="n"/>
-      <c r="O6" s="346" t="n"/>
-      <c r="P6" s="346" t="n"/>
-      <c r="Q6" s="346" t="n"/>
-      <c r="R6" s="346" t="n"/>
-      <c r="S6" s="346" t="n"/>
-      <c r="T6" s="346" t="n"/>
-      <c r="U6" s="346" t="n"/>
-      <c r="V6" s="346" t="n"/>
-      <c r="W6" s="346" t="n"/>
-      <c r="X6" s="346" t="n"/>
-      <c r="Y6" s="346" t="n"/>
-      <c r="Z6" s="346" t="n"/>
-      <c r="AA6" s="346" t="n"/>
-      <c r="AB6" s="346" t="n"/>
-      <c r="AC6" s="346" t="n"/>
-      <c r="AD6" s="346" t="n"/>
-      <c r="AE6" s="346" t="n"/>
-      <c r="AF6" s="346" t="n"/>
-      <c r="AG6" s="346" t="n"/>
-      <c r="AH6" s="346" t="n"/>
-      <c r="AI6" s="346" t="n"/>
-      <c r="AJ6" s="346" t="n"/>
-      <c r="AK6" s="346" t="n"/>
-      <c r="AL6" s="346" t="n"/>
-      <c r="AM6" s="346" t="n"/>
-      <c r="AN6" s="346" t="n"/>
+      <c r="D6" s="468" t="n"/>
+      <c r="E6" s="468" t="n"/>
+      <c r="F6" s="468" t="n"/>
+      <c r="G6" s="468" t="n"/>
+      <c r="H6" s="468" t="n"/>
+      <c r="I6" s="468" t="n"/>
+      <c r="J6" s="468" t="n"/>
+      <c r="K6" s="468" t="n"/>
+      <c r="L6" s="468" t="n"/>
+      <c r="M6" s="468" t="n"/>
+      <c r="N6" s="468" t="n"/>
+      <c r="O6" s="468" t="n"/>
+      <c r="P6" s="468" t="n"/>
+      <c r="Q6" s="468" t="n"/>
+      <c r="R6" s="468" t="n"/>
+      <c r="S6" s="468" t="n"/>
+      <c r="T6" s="468" t="n"/>
+      <c r="U6" s="468" t="n"/>
+      <c r="V6" s="468" t="n"/>
+      <c r="W6" s="468" t="n"/>
+      <c r="X6" s="468" t="n"/>
+      <c r="Y6" s="468" t="n"/>
+      <c r="Z6" s="468" t="n"/>
+      <c r="AA6" s="468" t="n"/>
+      <c r="AB6" s="468" t="n"/>
+      <c r="AC6" s="468" t="n"/>
+      <c r="AD6" s="468" t="n"/>
+      <c r="AE6" s="468" t="n"/>
+      <c r="AF6" s="468" t="n"/>
+      <c r="AG6" s="468" t="n"/>
+      <c r="AH6" s="468" t="n"/>
+      <c r="AI6" s="468" t="n"/>
+      <c r="AJ6" s="468" t="n"/>
+      <c r="AK6" s="468" t="n"/>
+      <c r="AL6" s="468" t="n"/>
+      <c r="AM6" s="468" t="n"/>
+      <c r="AN6" s="500" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="392" t="inlineStr">
+      <c r="A7" s="524" t="inlineStr">
         <is>
           <t>SOP SOP-605</t>
         </is>
       </c>
-      <c r="B7" s="393" t="inlineStr">
+      <c r="B7" s="525" t="inlineStr">
         <is>
           <t>SOP-605 — Kiểm tra cuối, CoC và phê duyệt giao hàng | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="393" t="inlineStr">
+      <c r="C7" s="526" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-605-final-inspection-coc-and-shipment-release.html</t>
         </is>
       </c>
-      <c r="D7" s="346" t="n"/>
-      <c r="E7" s="346" t="n"/>
-      <c r="F7" s="346" t="n"/>
-      <c r="G7" s="346" t="n"/>
-      <c r="H7" s="346" t="n"/>
-      <c r="I7" s="346" t="n"/>
-      <c r="J7" s="346" t="n"/>
-      <c r="K7" s="346" t="n"/>
-      <c r="L7" s="346" t="n"/>
-      <c r="M7" s="346" t="n"/>
-      <c r="N7" s="346" t="n"/>
-      <c r="O7" s="346" t="n"/>
-      <c r="P7" s="346" t="n"/>
-      <c r="Q7" s="346" t="n"/>
-      <c r="R7" s="346" t="n"/>
-      <c r="S7" s="346" t="n"/>
-      <c r="T7" s="346" t="n"/>
-      <c r="U7" s="346" t="n"/>
-      <c r="V7" s="346" t="n"/>
-      <c r="W7" s="346" t="n"/>
-      <c r="X7" s="346" t="n"/>
-      <c r="Y7" s="346" t="n"/>
-      <c r="Z7" s="346" t="n"/>
-      <c r="AA7" s="346" t="n"/>
-      <c r="AB7" s="346" t="n"/>
-      <c r="AC7" s="346" t="n"/>
-      <c r="AD7" s="346" t="n"/>
-      <c r="AE7" s="346" t="n"/>
-      <c r="AF7" s="346" t="n"/>
-      <c r="AG7" s="346" t="n"/>
-      <c r="AH7" s="346" t="n"/>
-      <c r="AI7" s="346" t="n"/>
-      <c r="AJ7" s="346" t="n"/>
-      <c r="AK7" s="346" t="n"/>
-      <c r="AL7" s="346" t="n"/>
-      <c r="AM7" s="346" t="n"/>
-      <c r="AN7" s="346" t="n"/>
+      <c r="D7" s="342" t="n"/>
+      <c r="E7" s="342" t="n"/>
+      <c r="F7" s="342" t="n"/>
+      <c r="G7" s="342" t="n"/>
+      <c r="H7" s="342" t="n"/>
+      <c r="I7" s="342" t="n"/>
+      <c r="J7" s="342" t="n"/>
+      <c r="K7" s="342" t="n"/>
+      <c r="L7" s="342" t="n"/>
+      <c r="M7" s="342" t="n"/>
+      <c r="N7" s="342" t="n"/>
+      <c r="O7" s="342" t="n"/>
+      <c r="P7" s="342" t="n"/>
+      <c r="Q7" s="342" t="n"/>
+      <c r="R7" s="342" t="n"/>
+      <c r="S7" s="342" t="n"/>
+      <c r="T7" s="342" t="n"/>
+      <c r="U7" s="342" t="n"/>
+      <c r="V7" s="342" t="n"/>
+      <c r="W7" s="342" t="n"/>
+      <c r="X7" s="342" t="n"/>
+      <c r="Y7" s="342" t="n"/>
+      <c r="Z7" s="342" t="n"/>
+      <c r="AA7" s="342" t="n"/>
+      <c r="AB7" s="342" t="n"/>
+      <c r="AC7" s="342" t="n"/>
+      <c r="AD7" s="342" t="n"/>
+      <c r="AE7" s="342" t="n"/>
+      <c r="AF7" s="342" t="n"/>
+      <c r="AG7" s="342" t="n"/>
+      <c r="AH7" s="342" t="n"/>
+      <c r="AI7" s="342" t="n"/>
+      <c r="AJ7" s="342" t="n"/>
+      <c r="AK7" s="342" t="n"/>
+      <c r="AL7" s="342" t="n"/>
+      <c r="AM7" s="342" t="n"/>
+      <c r="AN7" s="527" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="394" t="inlineStr">
+      <c r="A8" s="528" t="inlineStr">
         <is>
           <t>WI WI-605</t>
         </is>
       </c>
-      <c r="B8" s="395" t="inlineStr">
+      <c r="B8" s="529" t="inlineStr">
         <is>
           <t>WI-605 — Kiểm cuối, CoC/CofC, bàn giao phát hành giao hàng</t>
         </is>
       </c>
-      <c r="C8" s="395" t="inlineStr">
+      <c r="C8" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-605-final-inspection-coc-and-shipment-release-handoff.html</t>
         </is>
       </c>
-      <c r="D8" s="396" t="n"/>
-      <c r="E8" s="396" t="n"/>
-      <c r="F8" s="396" t="n"/>
-      <c r="G8" s="396" t="n"/>
-      <c r="H8" s="396" t="n"/>
-      <c r="I8" s="396" t="n"/>
-      <c r="J8" s="396" t="n"/>
-      <c r="K8" s="396" t="n"/>
-      <c r="L8" s="396" t="n"/>
-      <c r="M8" s="396" t="n"/>
-      <c r="N8" s="396" t="n"/>
-      <c r="O8" s="396" t="n"/>
-      <c r="P8" s="396" t="n"/>
-      <c r="Q8" s="396" t="n"/>
-      <c r="R8" s="396" t="n"/>
-      <c r="S8" s="396" t="n"/>
-      <c r="T8" s="396" t="n"/>
-      <c r="U8" s="396" t="n"/>
-      <c r="V8" s="396" t="n"/>
-      <c r="W8" s="396" t="n"/>
-      <c r="X8" s="396" t="n"/>
-      <c r="Y8" s="396" t="n"/>
-      <c r="Z8" s="396" t="n"/>
-      <c r="AA8" s="396" t="n"/>
-      <c r="AB8" s="396" t="n"/>
-      <c r="AC8" s="396" t="n"/>
-      <c r="AD8" s="396" t="n"/>
-      <c r="AE8" s="396" t="n"/>
-      <c r="AF8" s="396" t="n"/>
-      <c r="AG8" s="396" t="n"/>
-      <c r="AH8" s="396" t="n"/>
-      <c r="AI8" s="396" t="n"/>
-      <c r="AJ8" s="396" t="n"/>
-      <c r="AK8" s="396" t="n"/>
-      <c r="AL8" s="396" t="n"/>
-      <c r="AM8" s="396" t="n"/>
-      <c r="AN8" s="396" t="n"/>
+      <c r="D8" s="354" t="n"/>
+      <c r="E8" s="354" t="n"/>
+      <c r="F8" s="354" t="n"/>
+      <c r="G8" s="354" t="n"/>
+      <c r="H8" s="354" t="n"/>
+      <c r="I8" s="354" t="n"/>
+      <c r="J8" s="354" t="n"/>
+      <c r="K8" s="354" t="n"/>
+      <c r="L8" s="354" t="n"/>
+      <c r="M8" s="354" t="n"/>
+      <c r="N8" s="354" t="n"/>
+      <c r="O8" s="354" t="n"/>
+      <c r="P8" s="354" t="n"/>
+      <c r="Q8" s="354" t="n"/>
+      <c r="R8" s="354" t="n"/>
+      <c r="S8" s="354" t="n"/>
+      <c r="T8" s="354" t="n"/>
+      <c r="U8" s="354" t="n"/>
+      <c r="V8" s="354" t="n"/>
+      <c r="W8" s="354" t="n"/>
+      <c r="X8" s="354" t="n"/>
+      <c r="Y8" s="354" t="n"/>
+      <c r="Z8" s="354" t="n"/>
+      <c r="AA8" s="354" t="n"/>
+      <c r="AB8" s="354" t="n"/>
+      <c r="AC8" s="354" t="n"/>
+      <c r="AD8" s="354" t="n"/>
+      <c r="AE8" s="354" t="n"/>
+      <c r="AF8" s="354" t="n"/>
+      <c r="AG8" s="354" t="n"/>
+      <c r="AH8" s="354" t="n"/>
+      <c r="AI8" s="354" t="n"/>
+      <c r="AJ8" s="354" t="n"/>
+      <c r="AK8" s="354" t="n"/>
+      <c r="AL8" s="354" t="n"/>
+      <c r="AM8" s="354" t="n"/>
+      <c r="AN8" s="531" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="394" t="inlineStr">
+      <c r="A9" s="528" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-001</t>
         </is>
       </c>
-      <c r="B9" s="395" t="inlineStr">
+      <c r="B9" s="529" t="inlineStr">
         <is>
           <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
         </is>
       </c>
-      <c r="C9" s="395" t="inlineStr">
+      <c r="C9" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
         </is>
       </c>
-      <c r="D9" s="396" t="n"/>
-      <c r="E9" s="396" t="n"/>
-      <c r="F9" s="396" t="n"/>
-      <c r="G9" s="396" t="n"/>
-      <c r="H9" s="396" t="n"/>
-      <c r="I9" s="396" t="n"/>
-      <c r="J9" s="396" t="n"/>
-      <c r="K9" s="396" t="n"/>
-      <c r="L9" s="396" t="n"/>
-      <c r="M9" s="396" t="n"/>
-      <c r="N9" s="396" t="n"/>
-      <c r="O9" s="396" t="n"/>
-      <c r="P9" s="396" t="n"/>
-      <c r="Q9" s="396" t="n"/>
-      <c r="R9" s="396" t="n"/>
-      <c r="S9" s="396" t="n"/>
-      <c r="T9" s="396" t="n"/>
-      <c r="U9" s="396" t="n"/>
-      <c r="V9" s="396" t="n"/>
-      <c r="W9" s="396" t="n"/>
-      <c r="X9" s="396" t="n"/>
-      <c r="Y9" s="396" t="n"/>
-      <c r="Z9" s="396" t="n"/>
-      <c r="AA9" s="396" t="n"/>
-      <c r="AB9" s="396" t="n"/>
-      <c r="AC9" s="396" t="n"/>
-      <c r="AD9" s="396" t="n"/>
-      <c r="AE9" s="396" t="n"/>
-      <c r="AF9" s="396" t="n"/>
-      <c r="AG9" s="396" t="n"/>
-      <c r="AH9" s="396" t="n"/>
-      <c r="AI9" s="396" t="n"/>
-      <c r="AJ9" s="396" t="n"/>
-      <c r="AK9" s="396" t="n"/>
-      <c r="AL9" s="396" t="n"/>
-      <c r="AM9" s="396" t="n"/>
-      <c r="AN9" s="396" t="n"/>
+      <c r="D9" s="354" t="n"/>
+      <c r="E9" s="354" t="n"/>
+      <c r="F9" s="354" t="n"/>
+      <c r="G9" s="354" t="n"/>
+      <c r="H9" s="354" t="n"/>
+      <c r="I9" s="354" t="n"/>
+      <c r="J9" s="354" t="n"/>
+      <c r="K9" s="354" t="n"/>
+      <c r="L9" s="354" t="n"/>
+      <c r="M9" s="354" t="n"/>
+      <c r="N9" s="354" t="n"/>
+      <c r="O9" s="354" t="n"/>
+      <c r="P9" s="354" t="n"/>
+      <c r="Q9" s="354" t="n"/>
+      <c r="R9" s="354" t="n"/>
+      <c r="S9" s="354" t="n"/>
+      <c r="T9" s="354" t="n"/>
+      <c r="U9" s="354" t="n"/>
+      <c r="V9" s="354" t="n"/>
+      <c r="W9" s="354" t="n"/>
+      <c r="X9" s="354" t="n"/>
+      <c r="Y9" s="354" t="n"/>
+      <c r="Z9" s="354" t="n"/>
+      <c r="AA9" s="354" t="n"/>
+      <c r="AB9" s="354" t="n"/>
+      <c r="AC9" s="354" t="n"/>
+      <c r="AD9" s="354" t="n"/>
+      <c r="AE9" s="354" t="n"/>
+      <c r="AF9" s="354" t="n"/>
+      <c r="AG9" s="354" t="n"/>
+      <c r="AH9" s="354" t="n"/>
+      <c r="AI9" s="354" t="n"/>
+      <c r="AJ9" s="354" t="n"/>
+      <c r="AK9" s="354" t="n"/>
+      <c r="AL9" s="354" t="n"/>
+      <c r="AM9" s="354" t="n"/>
+      <c r="AN9" s="531" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="394" t="inlineStr">
+      <c r="A10" s="528" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-002</t>
         </is>
       </c>
-      <c r="B10" s="395" t="inlineStr">
+      <c r="B10" s="529" t="inlineStr">
         <is>
           <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
         </is>
       </c>
-      <c r="C10" s="395" t="inlineStr">
+      <c r="C10" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
         </is>
       </c>
-      <c r="D10" s="396" t="n"/>
-      <c r="E10" s="396" t="n"/>
-      <c r="F10" s="396" t="n"/>
-      <c r="G10" s="396" t="n"/>
-      <c r="H10" s="396" t="n"/>
-      <c r="I10" s="396" t="n"/>
-      <c r="J10" s="396" t="n"/>
-      <c r="K10" s="396" t="n"/>
-      <c r="L10" s="396" t="n"/>
-      <c r="M10" s="396" t="n"/>
-      <c r="N10" s="396" t="n"/>
-      <c r="O10" s="396" t="n"/>
-      <c r="P10" s="396" t="n"/>
-      <c r="Q10" s="396" t="n"/>
-      <c r="R10" s="396" t="n"/>
-      <c r="S10" s="396" t="n"/>
-      <c r="T10" s="396" t="n"/>
-      <c r="U10" s="396" t="n"/>
-      <c r="V10" s="396" t="n"/>
-      <c r="W10" s="396" t="n"/>
-      <c r="X10" s="396" t="n"/>
-      <c r="Y10" s="396" t="n"/>
-      <c r="Z10" s="396" t="n"/>
-      <c r="AA10" s="396" t="n"/>
-      <c r="AB10" s="396" t="n"/>
-      <c r="AC10" s="396" t="n"/>
-      <c r="AD10" s="396" t="n"/>
-      <c r="AE10" s="396" t="n"/>
-      <c r="AF10" s="396" t="n"/>
-      <c r="AG10" s="396" t="n"/>
-      <c r="AH10" s="396" t="n"/>
-      <c r="AI10" s="396" t="n"/>
-      <c r="AJ10" s="396" t="n"/>
-      <c r="AK10" s="396" t="n"/>
-      <c r="AL10" s="396" t="n"/>
-      <c r="AM10" s="396" t="n"/>
-      <c r="AN10" s="396" t="n"/>
+      <c r="D10" s="354" t="n"/>
+      <c r="E10" s="354" t="n"/>
+      <c r="F10" s="354" t="n"/>
+      <c r="G10" s="354" t="n"/>
+      <c r="H10" s="354" t="n"/>
+      <c r="I10" s="354" t="n"/>
+      <c r="J10" s="354" t="n"/>
+      <c r="K10" s="354" t="n"/>
+      <c r="L10" s="354" t="n"/>
+      <c r="M10" s="354" t="n"/>
+      <c r="N10" s="354" t="n"/>
+      <c r="O10" s="354" t="n"/>
+      <c r="P10" s="354" t="n"/>
+      <c r="Q10" s="354" t="n"/>
+      <c r="R10" s="354" t="n"/>
+      <c r="S10" s="354" t="n"/>
+      <c r="T10" s="354" t="n"/>
+      <c r="U10" s="354" t="n"/>
+      <c r="V10" s="354" t="n"/>
+      <c r="W10" s="354" t="n"/>
+      <c r="X10" s="354" t="n"/>
+      <c r="Y10" s="354" t="n"/>
+      <c r="Z10" s="354" t="n"/>
+      <c r="AA10" s="354" t="n"/>
+      <c r="AB10" s="354" t="n"/>
+      <c r="AC10" s="354" t="n"/>
+      <c r="AD10" s="354" t="n"/>
+      <c r="AE10" s="354" t="n"/>
+      <c r="AF10" s="354" t="n"/>
+      <c r="AG10" s="354" t="n"/>
+      <c r="AH10" s="354" t="n"/>
+      <c r="AI10" s="354" t="n"/>
+      <c r="AJ10" s="354" t="n"/>
+      <c r="AK10" s="354" t="n"/>
+      <c r="AL10" s="354" t="n"/>
+      <c r="AM10" s="354" t="n"/>
+      <c r="AN10" s="531" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="394" t="inlineStr">
+      <c r="A11" s="528" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-003</t>
         </is>
       </c>
-      <c r="B11" s="395" t="inlineStr">
+      <c r="B11" s="529" t="inlineStr">
         <is>
           <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
         </is>
       </c>
-      <c r="C11" s="395" t="inlineStr">
+      <c r="C11" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
         </is>
       </c>
-      <c r="D11" s="396" t="n"/>
-      <c r="E11" s="396" t="n"/>
-      <c r="F11" s="396" t="n"/>
-      <c r="G11" s="396" t="n"/>
-      <c r="H11" s="396" t="n"/>
-      <c r="I11" s="396" t="n"/>
-      <c r="J11" s="396" t="n"/>
-      <c r="K11" s="396" t="n"/>
-      <c r="L11" s="396" t="n"/>
-      <c r="M11" s="396" t="n"/>
-      <c r="N11" s="396" t="n"/>
-      <c r="O11" s="396" t="n"/>
-      <c r="P11" s="396" t="n"/>
-      <c r="Q11" s="396" t="n"/>
-      <c r="R11" s="396" t="n"/>
-      <c r="S11" s="396" t="n"/>
-      <c r="T11" s="396" t="n"/>
-      <c r="U11" s="396" t="n"/>
-      <c r="V11" s="396" t="n"/>
-      <c r="W11" s="396" t="n"/>
-      <c r="X11" s="396" t="n"/>
-      <c r="Y11" s="396" t="n"/>
-      <c r="Z11" s="396" t="n"/>
-      <c r="AA11" s="396" t="n"/>
-      <c r="AB11" s="396" t="n"/>
-      <c r="AC11" s="396" t="n"/>
-      <c r="AD11" s="396" t="n"/>
-      <c r="AE11" s="396" t="n"/>
-      <c r="AF11" s="396" t="n"/>
-      <c r="AG11" s="396" t="n"/>
-      <c r="AH11" s="396" t="n"/>
-      <c r="AI11" s="396" t="n"/>
-      <c r="AJ11" s="396" t="n"/>
-      <c r="AK11" s="396" t="n"/>
-      <c r="AL11" s="396" t="n"/>
-      <c r="AM11" s="396" t="n"/>
-      <c r="AN11" s="396" t="n"/>
+      <c r="D11" s="354" t="n"/>
+      <c r="E11" s="354" t="n"/>
+      <c r="F11" s="354" t="n"/>
+      <c r="G11" s="354" t="n"/>
+      <c r="H11" s="354" t="n"/>
+      <c r="I11" s="354" t="n"/>
+      <c r="J11" s="354" t="n"/>
+      <c r="K11" s="354" t="n"/>
+      <c r="L11" s="354" t="n"/>
+      <c r="M11" s="354" t="n"/>
+      <c r="N11" s="354" t="n"/>
+      <c r="O11" s="354" t="n"/>
+      <c r="P11" s="354" t="n"/>
+      <c r="Q11" s="354" t="n"/>
+      <c r="R11" s="354" t="n"/>
+      <c r="S11" s="354" t="n"/>
+      <c r="T11" s="354" t="n"/>
+      <c r="U11" s="354" t="n"/>
+      <c r="V11" s="354" t="n"/>
+      <c r="W11" s="354" t="n"/>
+      <c r="X11" s="354" t="n"/>
+      <c r="Y11" s="354" t="n"/>
+      <c r="Z11" s="354" t="n"/>
+      <c r="AA11" s="354" t="n"/>
+      <c r="AB11" s="354" t="n"/>
+      <c r="AC11" s="354" t="n"/>
+      <c r="AD11" s="354" t="n"/>
+      <c r="AE11" s="354" t="n"/>
+      <c r="AF11" s="354" t="n"/>
+      <c r="AG11" s="354" t="n"/>
+      <c r="AH11" s="354" t="n"/>
+      <c r="AI11" s="354" t="n"/>
+      <c r="AJ11" s="354" t="n"/>
+      <c r="AK11" s="354" t="n"/>
+      <c r="AL11" s="354" t="n"/>
+      <c r="AM11" s="354" t="n"/>
+      <c r="AN11" s="531" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="394" t="inlineStr">
+      <c r="A12" s="528" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-004</t>
         </is>
       </c>
-      <c r="B12" s="395" t="inlineStr">
+      <c r="B12" s="529" t="inlineStr">
         <is>
           <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
         </is>
       </c>
-      <c r="C12" s="395" t="inlineStr">
+      <c r="C12" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
         </is>
       </c>
-      <c r="D12" s="396" t="n"/>
-      <c r="E12" s="396" t="n"/>
-      <c r="F12" s="396" t="n"/>
-      <c r="G12" s="396" t="n"/>
-      <c r="H12" s="396" t="n"/>
-      <c r="I12" s="396" t="n"/>
-      <c r="J12" s="396" t="n"/>
-      <c r="K12" s="396" t="n"/>
-      <c r="L12" s="396" t="n"/>
-      <c r="M12" s="396" t="n"/>
-      <c r="N12" s="396" t="n"/>
-      <c r="O12" s="396" t="n"/>
-      <c r="P12" s="396" t="n"/>
-      <c r="Q12" s="396" t="n"/>
-      <c r="R12" s="396" t="n"/>
-      <c r="S12" s="396" t="n"/>
-      <c r="T12" s="396" t="n"/>
-      <c r="U12" s="396" t="n"/>
-      <c r="V12" s="396" t="n"/>
-      <c r="W12" s="396" t="n"/>
-      <c r="X12" s="396" t="n"/>
-      <c r="Y12" s="396" t="n"/>
-      <c r="Z12" s="396" t="n"/>
-      <c r="AA12" s="396" t="n"/>
-      <c r="AB12" s="396" t="n"/>
-      <c r="AC12" s="396" t="n"/>
-      <c r="AD12" s="396" t="n"/>
-      <c r="AE12" s="396" t="n"/>
-      <c r="AF12" s="396" t="n"/>
-      <c r="AG12" s="396" t="n"/>
-      <c r="AH12" s="396" t="n"/>
-      <c r="AI12" s="396" t="n"/>
-      <c r="AJ12" s="396" t="n"/>
-      <c r="AK12" s="396" t="n"/>
-      <c r="AL12" s="396" t="n"/>
-      <c r="AM12" s="396" t="n"/>
-      <c r="AN12" s="396" t="n"/>
+      <c r="D12" s="354" t="n"/>
+      <c r="E12" s="354" t="n"/>
+      <c r="F12" s="354" t="n"/>
+      <c r="G12" s="354" t="n"/>
+      <c r="H12" s="354" t="n"/>
+      <c r="I12" s="354" t="n"/>
+      <c r="J12" s="354" t="n"/>
+      <c r="K12" s="354" t="n"/>
+      <c r="L12" s="354" t="n"/>
+      <c r="M12" s="354" t="n"/>
+      <c r="N12" s="354" t="n"/>
+      <c r="O12" s="354" t="n"/>
+      <c r="P12" s="354" t="n"/>
+      <c r="Q12" s="354" t="n"/>
+      <c r="R12" s="354" t="n"/>
+      <c r="S12" s="354" t="n"/>
+      <c r="T12" s="354" t="n"/>
+      <c r="U12" s="354" t="n"/>
+      <c r="V12" s="354" t="n"/>
+      <c r="W12" s="354" t="n"/>
+      <c r="X12" s="354" t="n"/>
+      <c r="Y12" s="354" t="n"/>
+      <c r="Z12" s="354" t="n"/>
+      <c r="AA12" s="354" t="n"/>
+      <c r="AB12" s="354" t="n"/>
+      <c r="AC12" s="354" t="n"/>
+      <c r="AD12" s="354" t="n"/>
+      <c r="AE12" s="354" t="n"/>
+      <c r="AF12" s="354" t="n"/>
+      <c r="AG12" s="354" t="n"/>
+      <c r="AH12" s="354" t="n"/>
+      <c r="AI12" s="354" t="n"/>
+      <c r="AJ12" s="354" t="n"/>
+      <c r="AK12" s="354" t="n"/>
+      <c r="AL12" s="354" t="n"/>
+      <c r="AM12" s="354" t="n"/>
+      <c r="AN12" s="531" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="394" t="inlineStr">
+      <c r="A13" s="528" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-006</t>
         </is>
       </c>
-      <c r="B13" s="395" t="inlineStr">
+      <c r="B13" s="529" t="inlineStr">
         <is>
           <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
         </is>
       </c>
-      <c r="C13" s="395" t="inlineStr">
+      <c r="C13" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
         </is>
       </c>
-      <c r="D13" s="396" t="n"/>
-      <c r="E13" s="396" t="n"/>
-      <c r="F13" s="396" t="n"/>
-      <c r="G13" s="396" t="n"/>
-      <c r="H13" s="396" t="n"/>
-      <c r="I13" s="396" t="n"/>
-      <c r="J13" s="396" t="n"/>
-      <c r="K13" s="396" t="n"/>
-      <c r="L13" s="396" t="n"/>
-      <c r="M13" s="396" t="n"/>
-      <c r="N13" s="396" t="n"/>
-      <c r="O13" s="396" t="n"/>
-      <c r="P13" s="396" t="n"/>
-      <c r="Q13" s="396" t="n"/>
-      <c r="R13" s="396" t="n"/>
-      <c r="S13" s="396" t="n"/>
-      <c r="T13" s="396" t="n"/>
-      <c r="U13" s="396" t="n"/>
-      <c r="V13" s="396" t="n"/>
-      <c r="W13" s="396" t="n"/>
-      <c r="X13" s="396" t="n"/>
-      <c r="Y13" s="396" t="n"/>
-      <c r="Z13" s="396" t="n"/>
-      <c r="AA13" s="396" t="n"/>
-      <c r="AB13" s="396" t="n"/>
-      <c r="AC13" s="396" t="n"/>
-      <c r="AD13" s="396" t="n"/>
-      <c r="AE13" s="396" t="n"/>
-      <c r="AF13" s="396" t="n"/>
-      <c r="AG13" s="396" t="n"/>
-      <c r="AH13" s="396" t="n"/>
-      <c r="AI13" s="396" t="n"/>
-      <c r="AJ13" s="396" t="n"/>
-      <c r="AK13" s="396" t="n"/>
-      <c r="AL13" s="396" t="n"/>
-      <c r="AM13" s="396" t="n"/>
-      <c r="AN13" s="396" t="n"/>
+      <c r="D13" s="354" t="n"/>
+      <c r="E13" s="354" t="n"/>
+      <c r="F13" s="354" t="n"/>
+      <c r="G13" s="354" t="n"/>
+      <c r="H13" s="354" t="n"/>
+      <c r="I13" s="354" t="n"/>
+      <c r="J13" s="354" t="n"/>
+      <c r="K13" s="354" t="n"/>
+      <c r="L13" s="354" t="n"/>
+      <c r="M13" s="354" t="n"/>
+      <c r="N13" s="354" t="n"/>
+      <c r="O13" s="354" t="n"/>
+      <c r="P13" s="354" t="n"/>
+      <c r="Q13" s="354" t="n"/>
+      <c r="R13" s="354" t="n"/>
+      <c r="S13" s="354" t="n"/>
+      <c r="T13" s="354" t="n"/>
+      <c r="U13" s="354" t="n"/>
+      <c r="V13" s="354" t="n"/>
+      <c r="W13" s="354" t="n"/>
+      <c r="X13" s="354" t="n"/>
+      <c r="Y13" s="354" t="n"/>
+      <c r="Z13" s="354" t="n"/>
+      <c r="AA13" s="354" t="n"/>
+      <c r="AB13" s="354" t="n"/>
+      <c r="AC13" s="354" t="n"/>
+      <c r="AD13" s="354" t="n"/>
+      <c r="AE13" s="354" t="n"/>
+      <c r="AF13" s="354" t="n"/>
+      <c r="AG13" s="354" t="n"/>
+      <c r="AH13" s="354" t="n"/>
+      <c r="AI13" s="354" t="n"/>
+      <c r="AJ13" s="354" t="n"/>
+      <c r="AK13" s="354" t="n"/>
+      <c r="AL13" s="354" t="n"/>
+      <c r="AM13" s="354" t="n"/>
+      <c r="AN13" s="531" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="394" t="inlineStr">
+      <c r="A14" s="528" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B14" s="395" t="inlineStr">
+      <c r="B14" s="529" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C14" s="395" t="inlineStr">
+      <c r="C14" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
-      <c r="D14" s="396" t="n"/>
-      <c r="E14" s="396" t="n"/>
-      <c r="F14" s="396" t="n"/>
-      <c r="G14" s="396" t="n"/>
-      <c r="H14" s="396" t="n"/>
-      <c r="I14" s="396" t="n"/>
-      <c r="J14" s="396" t="n"/>
-      <c r="K14" s="396" t="n"/>
-      <c r="L14" s="396" t="n"/>
-      <c r="M14" s="396" t="n"/>
-      <c r="N14" s="396" t="n"/>
-      <c r="O14" s="396" t="n"/>
-      <c r="P14" s="396" t="n"/>
-      <c r="Q14" s="396" t="n"/>
-      <c r="R14" s="396" t="n"/>
-      <c r="S14" s="396" t="n"/>
-      <c r="T14" s="396" t="n"/>
-      <c r="U14" s="396" t="n"/>
-      <c r="V14" s="396" t="n"/>
-      <c r="W14" s="396" t="n"/>
-      <c r="X14" s="396" t="n"/>
-      <c r="Y14" s="396" t="n"/>
-      <c r="Z14" s="396" t="n"/>
-      <c r="AA14" s="396" t="n"/>
-      <c r="AB14" s="396" t="n"/>
-      <c r="AC14" s="396" t="n"/>
-      <c r="AD14" s="396" t="n"/>
-      <c r="AE14" s="396" t="n"/>
-      <c r="AF14" s="396" t="n"/>
-      <c r="AG14" s="396" t="n"/>
-      <c r="AH14" s="396" t="n"/>
-      <c r="AI14" s="396" t="n"/>
-      <c r="AJ14" s="396" t="n"/>
-      <c r="AK14" s="396" t="n"/>
-      <c r="AL14" s="396" t="n"/>
-      <c r="AM14" s="396" t="n"/>
-      <c r="AN14" s="396" t="n"/>
+      <c r="D14" s="354" t="n"/>
+      <c r="E14" s="354" t="n"/>
+      <c r="F14" s="354" t="n"/>
+      <c r="G14" s="354" t="n"/>
+      <c r="H14" s="354" t="n"/>
+      <c r="I14" s="354" t="n"/>
+      <c r="J14" s="354" t="n"/>
+      <c r="K14" s="354" t="n"/>
+      <c r="L14" s="354" t="n"/>
+      <c r="M14" s="354" t="n"/>
+      <c r="N14" s="354" t="n"/>
+      <c r="O14" s="354" t="n"/>
+      <c r="P14" s="354" t="n"/>
+      <c r="Q14" s="354" t="n"/>
+      <c r="R14" s="354" t="n"/>
+      <c r="S14" s="354" t="n"/>
+      <c r="T14" s="354" t="n"/>
+      <c r="U14" s="354" t="n"/>
+      <c r="V14" s="354" t="n"/>
+      <c r="W14" s="354" t="n"/>
+      <c r="X14" s="354" t="n"/>
+      <c r="Y14" s="354" t="n"/>
+      <c r="Z14" s="354" t="n"/>
+      <c r="AA14" s="354" t="n"/>
+      <c r="AB14" s="354" t="n"/>
+      <c r="AC14" s="354" t="n"/>
+      <c r="AD14" s="354" t="n"/>
+      <c r="AE14" s="354" t="n"/>
+      <c r="AF14" s="354" t="n"/>
+      <c r="AG14" s="354" t="n"/>
+      <c r="AH14" s="354" t="n"/>
+      <c r="AI14" s="354" t="n"/>
+      <c r="AJ14" s="354" t="n"/>
+      <c r="AK14" s="354" t="n"/>
+      <c r="AL14" s="354" t="n"/>
+      <c r="AM14" s="354" t="n"/>
+      <c r="AN14" s="531" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="394" t="inlineStr">
+      <c r="A15" s="532" t="inlineStr">
         <is>
           <t>ANNEX ANNEX-QMS-020</t>
         </is>
       </c>
-      <c r="B15" s="395" t="inlineStr">
+      <c r="B15" s="533" t="inlineStr">
         <is>
           <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
         </is>
       </c>
-      <c r="C15" s="395" t="inlineStr">
+      <c r="C15" s="534" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
         </is>
       </c>
-      <c r="D15" s="396" t="n"/>
-      <c r="E15" s="396" t="n"/>
-      <c r="F15" s="396" t="n"/>
-      <c r="G15" s="396" t="n"/>
-      <c r="H15" s="396" t="n"/>
-      <c r="I15" s="396" t="n"/>
-      <c r="J15" s="396" t="n"/>
-      <c r="K15" s="396" t="n"/>
-      <c r="L15" s="396" t="n"/>
-      <c r="M15" s="396" t="n"/>
-      <c r="N15" s="396" t="n"/>
-      <c r="O15" s="396" t="n"/>
-      <c r="P15" s="396" t="n"/>
-      <c r="Q15" s="396" t="n"/>
-      <c r="R15" s="396" t="n"/>
-      <c r="S15" s="396" t="n"/>
-      <c r="T15" s="396" t="n"/>
-      <c r="U15" s="396" t="n"/>
-      <c r="V15" s="396" t="n"/>
-      <c r="W15" s="396" t="n"/>
-      <c r="X15" s="396" t="n"/>
-      <c r="Y15" s="396" t="n"/>
-      <c r="Z15" s="396" t="n"/>
-      <c r="AA15" s="396" t="n"/>
-      <c r="AB15" s="396" t="n"/>
-      <c r="AC15" s="396" t="n"/>
-      <c r="AD15" s="396" t="n"/>
-      <c r="AE15" s="396" t="n"/>
-      <c r="AF15" s="396" t="n"/>
-      <c r="AG15" s="396" t="n"/>
-      <c r="AH15" s="396" t="n"/>
-      <c r="AI15" s="396" t="n"/>
-      <c r="AJ15" s="396" t="n"/>
-      <c r="AK15" s="396" t="n"/>
-      <c r="AL15" s="396" t="n"/>
-      <c r="AM15" s="396" t="n"/>
-      <c r="AN15" s="396" t="n"/>
+      <c r="D15" s="535" t="n"/>
+      <c r="E15" s="535" t="n"/>
+      <c r="F15" s="535" t="n"/>
+      <c r="G15" s="535" t="n"/>
+      <c r="H15" s="535" t="n"/>
+      <c r="I15" s="535" t="n"/>
+      <c r="J15" s="535" t="n"/>
+      <c r="K15" s="535" t="n"/>
+      <c r="L15" s="535" t="n"/>
+      <c r="M15" s="535" t="n"/>
+      <c r="N15" s="535" t="n"/>
+      <c r="O15" s="535" t="n"/>
+      <c r="P15" s="535" t="n"/>
+      <c r="Q15" s="535" t="n"/>
+      <c r="R15" s="535" t="n"/>
+      <c r="S15" s="535" t="n"/>
+      <c r="T15" s="535" t="n"/>
+      <c r="U15" s="535" t="n"/>
+      <c r="V15" s="535" t="n"/>
+      <c r="W15" s="535" t="n"/>
+      <c r="X15" s="535" t="n"/>
+      <c r="Y15" s="535" t="n"/>
+      <c r="Z15" s="535" t="n"/>
+      <c r="AA15" s="535" t="n"/>
+      <c r="AB15" s="535" t="n"/>
+      <c r="AC15" s="535" t="n"/>
+      <c r="AD15" s="535" t="n"/>
+      <c r="AE15" s="535" t="n"/>
+      <c r="AF15" s="535" t="n"/>
+      <c r="AG15" s="535" t="n"/>
+      <c r="AH15" s="535" t="n"/>
+      <c r="AI15" s="535" t="n"/>
+      <c r="AJ15" s="535" t="n"/>
+      <c r="AK15" s="535" t="n"/>
+      <c r="AL15" s="535" t="n"/>
+      <c r="AM15" s="535" t="n"/>
+      <c r="AN15" s="536" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -9656,6 +10547,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9710,403 +10602,409 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="391" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="510" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="420" t="n"/>
-      <c r="C1" s="420" t="n"/>
-      <c r="D1" s="420" t="n"/>
-      <c r="E1" s="420" t="n"/>
-      <c r="F1" s="420" t="n"/>
-      <c r="G1" s="421" t="n"/>
-      <c r="H1" s="346" t="n"/>
-      <c r="I1" s="346" t="n"/>
-      <c r="J1" s="346" t="n"/>
-      <c r="K1" s="346" t="n"/>
-      <c r="L1" s="346" t="n"/>
-      <c r="M1" s="346" t="n"/>
-      <c r="N1" s="346" t="n"/>
-      <c r="O1" s="346" t="n"/>
-      <c r="P1" s="346" t="n"/>
-      <c r="Q1" s="346" t="n"/>
-      <c r="R1" s="346" t="n"/>
-      <c r="S1" s="346" t="n"/>
-      <c r="T1" s="346" t="n"/>
-      <c r="U1" s="346" t="n"/>
-      <c r="V1" s="346" t="n"/>
-      <c r="W1" s="346" t="n"/>
-      <c r="X1" s="346" t="n"/>
-      <c r="Y1" s="346" t="n"/>
-      <c r="Z1" s="346" t="n"/>
-      <c r="AA1" s="346" t="n"/>
-      <c r="AB1" s="346" t="n"/>
-      <c r="AC1" s="346" t="n"/>
-      <c r="AD1" s="346" t="n"/>
-      <c r="AE1" s="346" t="n"/>
-      <c r="AF1" s="346" t="n"/>
-      <c r="AG1" s="346" t="n"/>
-      <c r="AH1" s="346" t="n"/>
-      <c r="AI1" s="346" t="n"/>
-      <c r="AJ1" s="346" t="n"/>
-      <c r="AK1" s="346" t="n"/>
-      <c r="AL1" s="346" t="n"/>
-      <c r="AM1" s="346" t="n"/>
-      <c r="AN1" s="346" t="n"/>
+      <c r="B1" s="426" t="n"/>
+      <c r="C1" s="426" t="n"/>
+      <c r="D1" s="426" t="n"/>
+      <c r="E1" s="426" t="n"/>
+      <c r="F1" s="426" t="n"/>
+      <c r="G1" s="426" t="n"/>
+      <c r="H1" s="511" t="n"/>
+      <c r="I1" s="428" t="n"/>
+      <c r="J1" s="429" t="n"/>
+      <c r="K1" s="429" t="n"/>
+      <c r="L1" s="429" t="n"/>
+      <c r="M1" s="429" t="n"/>
+      <c r="N1" s="429" t="n"/>
+      <c r="O1" s="429" t="n"/>
+      <c r="P1" s="429" t="n"/>
+      <c r="Q1" s="429" t="n"/>
+      <c r="R1" s="429" t="n"/>
+      <c r="S1" s="429" t="n"/>
+      <c r="T1" s="429" t="n"/>
+      <c r="U1" s="429" t="n"/>
+      <c r="V1" s="429" t="n"/>
+      <c r="W1" s="429" t="n"/>
+      <c r="X1" s="429" t="n"/>
+      <c r="Y1" s="429" t="n"/>
+      <c r="Z1" s="429" t="n"/>
+      <c r="AA1" s="429" t="n"/>
+      <c r="AB1" s="429" t="n"/>
+      <c r="AC1" s="429" t="n"/>
+      <c r="AD1" s="430" t="n"/>
+      <c r="AE1" s="431" t="n"/>
+      <c r="AF1" s="432" t="n"/>
+      <c r="AG1" s="432" t="n"/>
+      <c r="AH1" s="433" t="n"/>
+      <c r="AI1" s="434" t="n"/>
+      <c r="AJ1" s="435" t="n"/>
+      <c r="AK1" s="435" t="n"/>
+      <c r="AL1" s="435" t="n"/>
+      <c r="AM1" s="435" t="n"/>
+      <c r="AN1" s="436" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="317" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="512" t="inlineStr">
         <is>
           <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
         </is>
       </c>
-      <c r="H2" s="346" t="n"/>
-      <c r="I2" s="346" t="n"/>
-      <c r="J2" s="346" t="n"/>
-      <c r="K2" s="346" t="n"/>
-      <c r="L2" s="346" t="n"/>
-      <c r="M2" s="346" t="n"/>
-      <c r="N2" s="346" t="n"/>
-      <c r="O2" s="346" t="n"/>
-      <c r="P2" s="346" t="n"/>
-      <c r="Q2" s="346" t="n"/>
-      <c r="R2" s="346" t="n"/>
-      <c r="S2" s="346" t="n"/>
-      <c r="T2" s="346" t="n"/>
-      <c r="U2" s="346" t="n"/>
-      <c r="V2" s="346" t="n"/>
-      <c r="W2" s="346" t="n"/>
-      <c r="X2" s="346" t="n"/>
-      <c r="Y2" s="346" t="n"/>
-      <c r="Z2" s="346" t="n"/>
-      <c r="AA2" s="346" t="n"/>
-      <c r="AB2" s="346" t="n"/>
-      <c r="AC2" s="346" t="n"/>
-      <c r="AD2" s="346" t="n"/>
-      <c r="AE2" s="346" t="n"/>
-      <c r="AF2" s="346" t="n"/>
-      <c r="AG2" s="346" t="n"/>
-      <c r="AH2" s="346" t="n"/>
-      <c r="AI2" s="346" t="n"/>
-      <c r="AJ2" s="346" t="n"/>
-      <c r="AK2" s="346" t="n"/>
-      <c r="AL2" s="346" t="n"/>
-      <c r="AM2" s="346" t="n"/>
-      <c r="AN2" s="346" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="513" t="n"/>
+      <c r="I2" s="439" t="n"/>
+      <c r="J2" s="440" t="n"/>
+      <c r="K2" s="440" t="n"/>
+      <c r="L2" s="440" t="n"/>
+      <c r="M2" s="440" t="n"/>
+      <c r="N2" s="440" t="n"/>
+      <c r="O2" s="440" t="n"/>
+      <c r="P2" s="440" t="n"/>
+      <c r="Q2" s="440" t="n"/>
+      <c r="R2" s="440" t="n"/>
+      <c r="S2" s="440" t="n"/>
+      <c r="T2" s="440" t="n"/>
+      <c r="U2" s="440" t="n"/>
+      <c r="V2" s="440" t="n"/>
+      <c r="W2" s="440" t="n"/>
+      <c r="X2" s="440" t="n"/>
+      <c r="Y2" s="440" t="n"/>
+      <c r="Z2" s="440" t="n"/>
+      <c r="AA2" s="440" t="n"/>
+      <c r="AB2" s="440" t="n"/>
+      <c r="AC2" s="440" t="n"/>
+      <c r="AD2" s="441" t="n"/>
+      <c r="AE2" s="442" t="n"/>
+      <c r="AF2" s="443" t="n"/>
+      <c r="AG2" s="443" t="n"/>
+      <c r="AH2" s="444" t="n"/>
+      <c r="AI2" s="445" t="n"/>
+      <c r="AJ2" s="446" t="n"/>
+      <c r="AK2" s="446" t="n"/>
+      <c r="AL2" s="446" t="n"/>
+      <c r="AM2" s="446" t="n"/>
+      <c r="AN2" s="447" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="346" t="n"/>
-      <c r="B3" s="346" t="n"/>
-      <c r="C3" s="346" t="n"/>
-      <c r="D3" s="346" t="n"/>
-      <c r="E3" s="346" t="n"/>
-      <c r="F3" s="346" t="n"/>
-      <c r="G3" s="346" t="n"/>
-      <c r="H3" s="346" t="n"/>
-      <c r="I3" s="346" t="n"/>
-      <c r="J3" s="346" t="n"/>
-      <c r="K3" s="346" t="n"/>
-      <c r="L3" s="346" t="n"/>
-      <c r="M3" s="346" t="n"/>
-      <c r="N3" s="346" t="n"/>
-      <c r="O3" s="346" t="n"/>
-      <c r="P3" s="346" t="n"/>
-      <c r="Q3" s="346" t="n"/>
-      <c r="R3" s="346" t="n"/>
-      <c r="S3" s="346" t="n"/>
-      <c r="T3" s="346" t="n"/>
-      <c r="U3" s="346" t="n"/>
-      <c r="V3" s="346" t="n"/>
-      <c r="W3" s="346" t="n"/>
-      <c r="X3" s="346" t="n"/>
-      <c r="Y3" s="346" t="n"/>
-      <c r="Z3" s="346" t="n"/>
-      <c r="AA3" s="346" t="n"/>
-      <c r="AB3" s="346" t="n"/>
-      <c r="AC3" s="346" t="n"/>
-      <c r="AD3" s="346" t="n"/>
-      <c r="AE3" s="346" t="n"/>
-      <c r="AF3" s="346" t="n"/>
-      <c r="AG3" s="346" t="n"/>
-      <c r="AH3" s="346" t="n"/>
-      <c r="AI3" s="346" t="n"/>
-      <c r="AJ3" s="346" t="n"/>
-      <c r="AK3" s="346" t="n"/>
-      <c r="AL3" s="346" t="n"/>
-      <c r="AM3" s="346" t="n"/>
-      <c r="AN3" s="346" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="514" t="n"/>
+      <c r="B3" s="515" t="n"/>
+      <c r="C3" s="515" t="n"/>
+      <c r="D3" s="515" t="n"/>
+      <c r="E3" s="515" t="n"/>
+      <c r="F3" s="515" t="n"/>
+      <c r="G3" s="515" t="n"/>
+      <c r="H3" s="513" t="n"/>
+      <c r="I3" s="439" t="n"/>
+      <c r="J3" s="440" t="n"/>
+      <c r="K3" s="440" t="n"/>
+      <c r="L3" s="440" t="n"/>
+      <c r="M3" s="440" t="n"/>
+      <c r="N3" s="440" t="n"/>
+      <c r="O3" s="440" t="n"/>
+      <c r="P3" s="440" t="n"/>
+      <c r="Q3" s="440" t="n"/>
+      <c r="R3" s="440" t="n"/>
+      <c r="S3" s="440" t="n"/>
+      <c r="T3" s="440" t="n"/>
+      <c r="U3" s="440" t="n"/>
+      <c r="V3" s="440" t="n"/>
+      <c r="W3" s="440" t="n"/>
+      <c r="X3" s="440" t="n"/>
+      <c r="Y3" s="440" t="n"/>
+      <c r="Z3" s="440" t="n"/>
+      <c r="AA3" s="440" t="n"/>
+      <c r="AB3" s="440" t="n"/>
+      <c r="AC3" s="440" t="n"/>
+      <c r="AD3" s="441" t="n"/>
+      <c r="AE3" s="442" t="n"/>
+      <c r="AF3" s="443" t="n"/>
+      <c r="AG3" s="443" t="n"/>
+      <c r="AH3" s="444" t="n"/>
+      <c r="AI3" s="445" t="n"/>
+      <c r="AJ3" s="446" t="n"/>
+      <c r="AK3" s="446" t="n"/>
+      <c r="AL3" s="446" t="n"/>
+      <c r="AM3" s="446" t="n"/>
+      <c r="AN3" s="447" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="362" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="516" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="362" t="inlineStr">
+      <c r="B4" s="517" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="362" t="inlineStr">
+      <c r="C4" s="517" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="346" t="n"/>
-      <c r="E4" s="346" t="n"/>
-      <c r="F4" s="346" t="n"/>
-      <c r="G4" s="346" t="n"/>
-      <c r="H4" s="346" t="n"/>
-      <c r="I4" s="346" t="n"/>
-      <c r="J4" s="346" t="n"/>
-      <c r="K4" s="346" t="n"/>
-      <c r="L4" s="346" t="n"/>
-      <c r="M4" s="346" t="n"/>
-      <c r="N4" s="346" t="n"/>
-      <c r="O4" s="346" t="n"/>
-      <c r="P4" s="346" t="n"/>
-      <c r="Q4" s="346" t="n"/>
-      <c r="R4" s="346" t="n"/>
-      <c r="S4" s="346" t="n"/>
-      <c r="T4" s="346" t="n"/>
-      <c r="U4" s="346" t="n"/>
-      <c r="V4" s="346" t="n"/>
-      <c r="W4" s="346" t="n"/>
-      <c r="X4" s="346" t="n"/>
-      <c r="Y4" s="346" t="n"/>
-      <c r="Z4" s="346" t="n"/>
-      <c r="AA4" s="346" t="n"/>
-      <c r="AB4" s="346" t="n"/>
-      <c r="AC4" s="346" t="n"/>
-      <c r="AD4" s="346" t="n"/>
-      <c r="AE4" s="346" t="n"/>
-      <c r="AF4" s="346" t="n"/>
-      <c r="AG4" s="346" t="n"/>
-      <c r="AH4" s="346" t="n"/>
-      <c r="AI4" s="346" t="n"/>
-      <c r="AJ4" s="346" t="n"/>
-      <c r="AK4" s="346" t="n"/>
-      <c r="AL4" s="346" t="n"/>
-      <c r="AM4" s="346" t="n"/>
-      <c r="AN4" s="346" t="n"/>
+      <c r="D4" s="515" t="n"/>
+      <c r="E4" s="515" t="n"/>
+      <c r="F4" s="515" t="n"/>
+      <c r="G4" s="515" t="n"/>
+      <c r="H4" s="513" t="n"/>
+      <c r="I4" s="448" t="n"/>
+      <c r="J4" s="449" t="n"/>
+      <c r="K4" s="449" t="n"/>
+      <c r="L4" s="449" t="n"/>
+      <c r="M4" s="449" t="n"/>
+      <c r="N4" s="449" t="n"/>
+      <c r="O4" s="449" t="n"/>
+      <c r="P4" s="449" t="n"/>
+      <c r="Q4" s="449" t="n"/>
+      <c r="R4" s="449" t="n"/>
+      <c r="S4" s="449" t="n"/>
+      <c r="T4" s="449" t="n"/>
+      <c r="U4" s="449" t="n"/>
+      <c r="V4" s="449" t="n"/>
+      <c r="W4" s="449" t="n"/>
+      <c r="X4" s="449" t="n"/>
+      <c r="Y4" s="449" t="n"/>
+      <c r="Z4" s="449" t="n"/>
+      <c r="AA4" s="449" t="n"/>
+      <c r="AB4" s="449" t="n"/>
+      <c r="AC4" s="449" t="n"/>
+      <c r="AD4" s="450" t="n"/>
+      <c r="AE4" s="442" t="n"/>
+      <c r="AF4" s="443" t="n"/>
+      <c r="AG4" s="443" t="n"/>
+      <c r="AH4" s="444" t="n"/>
+      <c r="AI4" s="445" t="n"/>
+      <c r="AJ4" s="446" t="n"/>
+      <c r="AK4" s="446" t="n"/>
+      <c r="AL4" s="446" t="n"/>
+      <c r="AM4" s="446" t="n"/>
+      <c r="AN4" s="447" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="392" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="518" t="inlineStr">
         <is>
           <t>Evidence item 1</t>
         </is>
       </c>
-      <c r="B5" s="393" t="inlineStr">
+      <c r="B5" s="519" t="inlineStr">
         <is>
           <t>Reference to the correct evidence folder, shared location or dossier package.</t>
         </is>
       </c>
-      <c r="C5" s="393" t="inlineStr">
+      <c r="C5" s="519" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
-      <c r="D5" s="346" t="n"/>
-      <c r="E5" s="346" t="n"/>
-      <c r="F5" s="346" t="n"/>
-      <c r="G5" s="346" t="n"/>
-      <c r="H5" s="346" t="n"/>
-      <c r="I5" s="346" t="n"/>
-      <c r="J5" s="346" t="n"/>
-      <c r="K5" s="346" t="n"/>
-      <c r="L5" s="346" t="n"/>
-      <c r="M5" s="346" t="n"/>
-      <c r="N5" s="346" t="n"/>
-      <c r="O5" s="346" t="n"/>
-      <c r="P5" s="346" t="n"/>
-      <c r="Q5" s="346" t="n"/>
-      <c r="R5" s="346" t="n"/>
-      <c r="S5" s="346" t="n"/>
-      <c r="T5" s="346" t="n"/>
-      <c r="U5" s="346" t="n"/>
-      <c r="V5" s="346" t="n"/>
-      <c r="W5" s="346" t="n"/>
-      <c r="X5" s="346" t="n"/>
-      <c r="Y5" s="346" t="n"/>
-      <c r="Z5" s="346" t="n"/>
-      <c r="AA5" s="346" t="n"/>
-      <c r="AB5" s="346" t="n"/>
-      <c r="AC5" s="346" t="n"/>
-      <c r="AD5" s="346" t="n"/>
-      <c r="AE5" s="346" t="n"/>
-      <c r="AF5" s="346" t="n"/>
-      <c r="AG5" s="346" t="n"/>
-      <c r="AH5" s="346" t="n"/>
-      <c r="AI5" s="346" t="n"/>
-      <c r="AJ5" s="346" t="n"/>
-      <c r="AK5" s="346" t="n"/>
-      <c r="AL5" s="346" t="n"/>
-      <c r="AM5" s="346" t="n"/>
-      <c r="AN5" s="346" t="n"/>
+      <c r="D5" s="537" t="n"/>
+      <c r="E5" s="537" t="n"/>
+      <c r="F5" s="537" t="n"/>
+      <c r="G5" s="537" t="n"/>
+      <c r="H5" s="520" t="n"/>
+      <c r="I5" s="454" t="n"/>
+      <c r="J5" s="455" t="n"/>
+      <c r="K5" s="455" t="n"/>
+      <c r="L5" s="455" t="n"/>
+      <c r="M5" s="455" t="n"/>
+      <c r="N5" s="455" t="n"/>
+      <c r="O5" s="455" t="n"/>
+      <c r="P5" s="455" t="n"/>
+      <c r="Q5" s="455" t="n"/>
+      <c r="R5" s="455" t="n"/>
+      <c r="S5" s="455" t="n"/>
+      <c r="T5" s="455" t="n"/>
+      <c r="U5" s="455" t="n"/>
+      <c r="V5" s="455" t="n"/>
+      <c r="W5" s="455" t="n"/>
+      <c r="X5" s="455" t="n"/>
+      <c r="Y5" s="455" t="n"/>
+      <c r="Z5" s="455" t="n"/>
+      <c r="AA5" s="455" t="n"/>
+      <c r="AB5" s="455" t="n"/>
+      <c r="AC5" s="455" t="n"/>
+      <c r="AD5" s="456" t="n"/>
+      <c r="AE5" s="457" t="n"/>
+      <c r="AF5" s="458" t="n"/>
+      <c r="AG5" s="458" t="n"/>
+      <c r="AH5" s="459" t="n"/>
+      <c r="AI5" s="460" t="n"/>
+      <c r="AJ5" s="461" t="n"/>
+      <c r="AK5" s="461" t="n"/>
+      <c r="AL5" s="461" t="n"/>
+      <c r="AM5" s="461" t="n"/>
+      <c r="AN5" s="462" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="392" t="inlineStr">
+      <c r="A6" s="521" t="inlineStr">
         <is>
           <t>Evidence item 2</t>
         </is>
       </c>
-      <c r="B6" s="393" t="inlineStr">
+      <c r="B6" s="522" t="inlineStr">
         <is>
           <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
         </is>
       </c>
-      <c r="C6" s="393" t="inlineStr">
+      <c r="C6" s="523" t="inlineStr">
         <is>
           <t>Link or reference ID</t>
         </is>
       </c>
-      <c r="D6" s="346" t="n"/>
-      <c r="E6" s="346" t="n"/>
-      <c r="F6" s="346" t="n"/>
-      <c r="G6" s="346" t="n"/>
-      <c r="H6" s="346" t="n"/>
-      <c r="I6" s="346" t="n"/>
-      <c r="J6" s="346" t="n"/>
-      <c r="K6" s="346" t="n"/>
-      <c r="L6" s="346" t="n"/>
-      <c r="M6" s="346" t="n"/>
-      <c r="N6" s="346" t="n"/>
-      <c r="O6" s="346" t="n"/>
-      <c r="P6" s="346" t="n"/>
-      <c r="Q6" s="346" t="n"/>
-      <c r="R6" s="346" t="n"/>
-      <c r="S6" s="346" t="n"/>
-      <c r="T6" s="346" t="n"/>
-      <c r="U6" s="346" t="n"/>
-      <c r="V6" s="346" t="n"/>
-      <c r="W6" s="346" t="n"/>
-      <c r="X6" s="346" t="n"/>
-      <c r="Y6" s="346" t="n"/>
-      <c r="Z6" s="346" t="n"/>
-      <c r="AA6" s="346" t="n"/>
-      <c r="AB6" s="346" t="n"/>
-      <c r="AC6" s="346" t="n"/>
-      <c r="AD6" s="346" t="n"/>
-      <c r="AE6" s="346" t="n"/>
-      <c r="AF6" s="346" t="n"/>
-      <c r="AG6" s="346" t="n"/>
-      <c r="AH6" s="346" t="n"/>
-      <c r="AI6" s="346" t="n"/>
-      <c r="AJ6" s="346" t="n"/>
-      <c r="AK6" s="346" t="n"/>
-      <c r="AL6" s="346" t="n"/>
-      <c r="AM6" s="346" t="n"/>
-      <c r="AN6" s="346" t="n"/>
+      <c r="D6" s="468" t="n"/>
+      <c r="E6" s="468" t="n"/>
+      <c r="F6" s="468" t="n"/>
+      <c r="G6" s="468" t="n"/>
+      <c r="H6" s="468" t="n"/>
+      <c r="I6" s="468" t="n"/>
+      <c r="J6" s="468" t="n"/>
+      <c r="K6" s="468" t="n"/>
+      <c r="L6" s="468" t="n"/>
+      <c r="M6" s="468" t="n"/>
+      <c r="N6" s="468" t="n"/>
+      <c r="O6" s="468" t="n"/>
+      <c r="P6" s="468" t="n"/>
+      <c r="Q6" s="468" t="n"/>
+      <c r="R6" s="468" t="n"/>
+      <c r="S6" s="468" t="n"/>
+      <c r="T6" s="468" t="n"/>
+      <c r="U6" s="468" t="n"/>
+      <c r="V6" s="468" t="n"/>
+      <c r="W6" s="468" t="n"/>
+      <c r="X6" s="468" t="n"/>
+      <c r="Y6" s="468" t="n"/>
+      <c r="Z6" s="468" t="n"/>
+      <c r="AA6" s="468" t="n"/>
+      <c r="AB6" s="468" t="n"/>
+      <c r="AC6" s="468" t="n"/>
+      <c r="AD6" s="468" t="n"/>
+      <c r="AE6" s="468" t="n"/>
+      <c r="AF6" s="468" t="n"/>
+      <c r="AG6" s="468" t="n"/>
+      <c r="AH6" s="468" t="n"/>
+      <c r="AI6" s="468" t="n"/>
+      <c r="AJ6" s="468" t="n"/>
+      <c r="AK6" s="468" t="n"/>
+      <c r="AL6" s="468" t="n"/>
+      <c r="AM6" s="468" t="n"/>
+      <c r="AN6" s="500" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="392" t="inlineStr">
+      <c r="A7" s="524" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B7" s="393" t="inlineStr">
+      <c r="B7" s="525" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C7" s="393" t="inlineStr">
+      <c r="C7" s="526" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D7" s="346" t="n"/>
-      <c r="E7" s="346" t="n"/>
-      <c r="F7" s="346" t="n"/>
-      <c r="G7" s="346" t="n"/>
-      <c r="H7" s="346" t="n"/>
-      <c r="I7" s="346" t="n"/>
-      <c r="J7" s="346" t="n"/>
-      <c r="K7" s="346" t="n"/>
-      <c r="L7" s="346" t="n"/>
-      <c r="M7" s="346" t="n"/>
-      <c r="N7" s="346" t="n"/>
-      <c r="O7" s="346" t="n"/>
-      <c r="P7" s="346" t="n"/>
-      <c r="Q7" s="346" t="n"/>
-      <c r="R7" s="346" t="n"/>
-      <c r="S7" s="346" t="n"/>
-      <c r="T7" s="346" t="n"/>
-      <c r="U7" s="346" t="n"/>
-      <c r="V7" s="346" t="n"/>
-      <c r="W7" s="346" t="n"/>
-      <c r="X7" s="346" t="n"/>
-      <c r="Y7" s="346" t="n"/>
-      <c r="Z7" s="346" t="n"/>
-      <c r="AA7" s="346" t="n"/>
-      <c r="AB7" s="346" t="n"/>
-      <c r="AC7" s="346" t="n"/>
-      <c r="AD7" s="346" t="n"/>
-      <c r="AE7" s="346" t="n"/>
-      <c r="AF7" s="346" t="n"/>
-      <c r="AG7" s="346" t="n"/>
-      <c r="AH7" s="346" t="n"/>
-      <c r="AI7" s="346" t="n"/>
-      <c r="AJ7" s="346" t="n"/>
-      <c r="AK7" s="346" t="n"/>
-      <c r="AL7" s="346" t="n"/>
-      <c r="AM7" s="346" t="n"/>
-      <c r="AN7" s="346" t="n"/>
+      <c r="D7" s="342" t="n"/>
+      <c r="E7" s="342" t="n"/>
+      <c r="F7" s="342" t="n"/>
+      <c r="G7" s="342" t="n"/>
+      <c r="H7" s="342" t="n"/>
+      <c r="I7" s="342" t="n"/>
+      <c r="J7" s="342" t="n"/>
+      <c r="K7" s="342" t="n"/>
+      <c r="L7" s="342" t="n"/>
+      <c r="M7" s="342" t="n"/>
+      <c r="N7" s="342" t="n"/>
+      <c r="O7" s="342" t="n"/>
+      <c r="P7" s="342" t="n"/>
+      <c r="Q7" s="342" t="n"/>
+      <c r="R7" s="342" t="n"/>
+      <c r="S7" s="342" t="n"/>
+      <c r="T7" s="342" t="n"/>
+      <c r="U7" s="342" t="n"/>
+      <c r="V7" s="342" t="n"/>
+      <c r="W7" s="342" t="n"/>
+      <c r="X7" s="342" t="n"/>
+      <c r="Y7" s="342" t="n"/>
+      <c r="Z7" s="342" t="n"/>
+      <c r="AA7" s="342" t="n"/>
+      <c r="AB7" s="342" t="n"/>
+      <c r="AC7" s="342" t="n"/>
+      <c r="AD7" s="342" t="n"/>
+      <c r="AE7" s="342" t="n"/>
+      <c r="AF7" s="342" t="n"/>
+      <c r="AG7" s="342" t="n"/>
+      <c r="AH7" s="342" t="n"/>
+      <c r="AI7" s="342" t="n"/>
+      <c r="AJ7" s="342" t="n"/>
+      <c r="AK7" s="342" t="n"/>
+      <c r="AL7" s="342" t="n"/>
+      <c r="AM7" s="342" t="n"/>
+      <c r="AN7" s="527" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="394" t="inlineStr">
+      <c r="A8" s="532" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B8" s="395" t="inlineStr">
+      <c r="B8" s="533" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C8" s="395" t="inlineStr">
+      <c r="C8" s="534" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D8" s="396" t="n"/>
-      <c r="E8" s="396" t="n"/>
-      <c r="F8" s="396" t="n"/>
-      <c r="G8" s="396" t="n"/>
-      <c r="H8" s="396" t="n"/>
-      <c r="I8" s="396" t="n"/>
-      <c r="J8" s="396" t="n"/>
-      <c r="K8" s="396" t="n"/>
-      <c r="L8" s="396" t="n"/>
-      <c r="M8" s="396" t="n"/>
-      <c r="N8" s="396" t="n"/>
-      <c r="O8" s="396" t="n"/>
-      <c r="P8" s="396" t="n"/>
-      <c r="Q8" s="396" t="n"/>
-      <c r="R8" s="396" t="n"/>
-      <c r="S8" s="396" t="n"/>
-      <c r="T8" s="396" t="n"/>
-      <c r="U8" s="396" t="n"/>
-      <c r="V8" s="396" t="n"/>
-      <c r="W8" s="396" t="n"/>
-      <c r="X8" s="396" t="n"/>
-      <c r="Y8" s="396" t="n"/>
-      <c r="Z8" s="396" t="n"/>
-      <c r="AA8" s="396" t="n"/>
-      <c r="AB8" s="396" t="n"/>
-      <c r="AC8" s="396" t="n"/>
-      <c r="AD8" s="396" t="n"/>
-      <c r="AE8" s="396" t="n"/>
-      <c r="AF8" s="396" t="n"/>
-      <c r="AG8" s="396" t="n"/>
-      <c r="AH8" s="396" t="n"/>
-      <c r="AI8" s="396" t="n"/>
-      <c r="AJ8" s="396" t="n"/>
-      <c r="AK8" s="396" t="n"/>
-      <c r="AL8" s="396" t="n"/>
-      <c r="AM8" s="396" t="n"/>
-      <c r="AN8" s="396" t="n"/>
+      <c r="D8" s="535" t="n"/>
+      <c r="E8" s="535" t="n"/>
+      <c r="F8" s="535" t="n"/>
+      <c r="G8" s="535" t="n"/>
+      <c r="H8" s="535" t="n"/>
+      <c r="I8" s="535" t="n"/>
+      <c r="J8" s="535" t="n"/>
+      <c r="K8" s="535" t="n"/>
+      <c r="L8" s="535" t="n"/>
+      <c r="M8" s="535" t="n"/>
+      <c r="N8" s="535" t="n"/>
+      <c r="O8" s="535" t="n"/>
+      <c r="P8" s="535" t="n"/>
+      <c r="Q8" s="535" t="n"/>
+      <c r="R8" s="535" t="n"/>
+      <c r="S8" s="535" t="n"/>
+      <c r="T8" s="535" t="n"/>
+      <c r="U8" s="535" t="n"/>
+      <c r="V8" s="535" t="n"/>
+      <c r="W8" s="535" t="n"/>
+      <c r="X8" s="535" t="n"/>
+      <c r="Y8" s="535" t="n"/>
+      <c r="Z8" s="535" t="n"/>
+      <c r="AA8" s="535" t="n"/>
+      <c r="AB8" s="535" t="n"/>
+      <c r="AC8" s="535" t="n"/>
+      <c r="AD8" s="535" t="n"/>
+      <c r="AE8" s="535" t="n"/>
+      <c r="AF8" s="535" t="n"/>
+      <c r="AG8" s="535" t="n"/>
+      <c r="AH8" s="535" t="n"/>
+      <c r="AI8" s="535" t="n"/>
+      <c r="AJ8" s="535" t="n"/>
+      <c r="AK8" s="535" t="n"/>
+      <c r="AL8" s="535" t="n"/>
+      <c r="AM8" s="535" t="n"/>
+      <c r="AN8" s="536" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
@@ -10117,5 +11015,6 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="84">
+  <fonts count="85">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -501,6 +501,12 @@
       <color rgb="00BBCCCC"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="52">
     <fill>
@@ -760,7 +766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="321">
+  <borders count="362">
     <border>
       <left/>
       <right/>
@@ -4189,13 +4195,484 @@
       </top>
       <bottom style="medium">
         <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="538">
+  <cellXfs count="600">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5532,6 +6009,186 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="359" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5613,11 +6270,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
+      <colOff>298782</colOff>
+      <row>0</row>
+      <rowOff>275446</rowOff>
     </from>
-    <ext cx="1792692" cy="517122"/>
+    <ext cx="1394316" cy="402206"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5661,6 +6318,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5691,6 +6351,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5721,6 +6384,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6095,2271 +6761,2271 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="425" t="inlineStr"/>
-      <c r="B1" s="426" t="n"/>
-      <c r="C1" s="426" t="n"/>
-      <c r="D1" s="426" t="n"/>
-      <c r="E1" s="426" t="n"/>
-      <c r="F1" s="426" t="n"/>
-      <c r="G1" s="426" t="n"/>
-      <c r="H1" s="426" t="n"/>
-      <c r="I1" s="426" t="n"/>
-      <c r="J1" s="426" t="n"/>
-      <c r="K1" s="427" t="n"/>
-      <c r="L1" s="428" t="inlineStr">
+      <c r="A1" s="538" t="inlineStr"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="53" t="n"/>
+      <c r="L1" s="539" t="inlineStr">
         <is>
           <t>Final Inspection Report</t>
         </is>
       </c>
-      <c r="M1" s="429" t="n"/>
-      <c r="N1" s="429" t="n"/>
-      <c r="O1" s="429" t="n"/>
-      <c r="P1" s="429" t="n"/>
-      <c r="Q1" s="429" t="n"/>
-      <c r="R1" s="429" t="n"/>
-      <c r="S1" s="429" t="n"/>
-      <c r="T1" s="429" t="n"/>
-      <c r="U1" s="429" t="n"/>
-      <c r="V1" s="429" t="n"/>
-      <c r="W1" s="429" t="n"/>
-      <c r="X1" s="429" t="n"/>
-      <c r="Y1" s="429" t="n"/>
-      <c r="Z1" s="429" t="n"/>
-      <c r="AA1" s="429" t="n"/>
-      <c r="AB1" s="429" t="n"/>
-      <c r="AC1" s="429" t="n"/>
-      <c r="AD1" s="429" t="n"/>
-      <c r="AE1" s="429" t="n"/>
-      <c r="AF1" s="429" t="n"/>
-      <c r="AG1" s="429" t="n"/>
-      <c r="AH1" s="429" t="n"/>
-      <c r="AI1" s="429" t="n"/>
-      <c r="AJ1" s="429" t="n"/>
-      <c r="AK1" s="429" t="n"/>
-      <c r="AL1" s="429" t="n"/>
-      <c r="AM1" s="429" t="n"/>
-      <c r="AN1" s="429" t="n"/>
-      <c r="AO1" s="429" t="n"/>
-      <c r="AP1" s="430" t="n"/>
-      <c r="AQ1" s="431" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="540" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="432" t="n"/>
-      <c r="AS1" s="432" t="n"/>
-      <c r="AT1" s="432" t="n"/>
-      <c r="AU1" s="432" t="n"/>
-      <c r="AV1" s="433" t="n"/>
-      <c r="AW1" s="434" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="541" t="n"/>
+      <c r="AW1" s="542" t="inlineStr">
         <is>
           <t>FRM-641</t>
         </is>
       </c>
-      <c r="AX1" s="435" t="n"/>
-      <c r="AY1" s="435" t="n"/>
-      <c r="AZ1" s="435" t="n"/>
-      <c r="BA1" s="435" t="n"/>
-      <c r="BB1" s="435" t="n"/>
-      <c r="BC1" s="435" t="n"/>
-      <c r="BD1" s="436" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="53" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="437" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="25" t="n"/>
-      <c r="I2" s="25" t="n"/>
-      <c r="J2" s="25" t="n"/>
-      <c r="K2" s="438" t="n"/>
-      <c r="L2" s="439" t="n"/>
-      <c r="M2" s="440" t="n"/>
-      <c r="N2" s="440" t="n"/>
-      <c r="O2" s="440" t="n"/>
-      <c r="P2" s="440" t="n"/>
-      <c r="Q2" s="440" t="n"/>
-      <c r="R2" s="440" t="n"/>
-      <c r="S2" s="440" t="n"/>
-      <c r="T2" s="440" t="n"/>
-      <c r="U2" s="440" t="n"/>
-      <c r="V2" s="440" t="n"/>
-      <c r="W2" s="440" t="n"/>
-      <c r="X2" s="440" t="n"/>
-      <c r="Y2" s="440" t="n"/>
-      <c r="Z2" s="440" t="n"/>
-      <c r="AA2" s="440" t="n"/>
-      <c r="AB2" s="440" t="n"/>
-      <c r="AC2" s="440" t="n"/>
-      <c r="AD2" s="440" t="n"/>
-      <c r="AE2" s="440" t="n"/>
-      <c r="AF2" s="440" t="n"/>
-      <c r="AG2" s="440" t="n"/>
-      <c r="AH2" s="440" t="n"/>
-      <c r="AI2" s="440" t="n"/>
-      <c r="AJ2" s="440" t="n"/>
-      <c r="AK2" s="440" t="n"/>
-      <c r="AL2" s="440" t="n"/>
-      <c r="AM2" s="440" t="n"/>
-      <c r="AN2" s="440" t="n"/>
-      <c r="AO2" s="440" t="n"/>
-      <c r="AP2" s="441" t="n"/>
-      <c r="AQ2" s="442" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="10" t="n"/>
+      <c r="AE2" s="10" t="n"/>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="10" t="n"/>
+      <c r="AI2" s="10" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="10" t="n"/>
+      <c r="AO2" s="10" t="n"/>
+      <c r="AP2" s="10" t="n"/>
+      <c r="AQ2" s="543" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="443" t="n"/>
-      <c r="AS2" s="443" t="n"/>
-      <c r="AT2" s="443" t="n"/>
-      <c r="AU2" s="443" t="n"/>
-      <c r="AV2" s="444" t="n"/>
-      <c r="AW2" s="445" t="inlineStr">
+      <c r="AR2" s="544" t="n"/>
+      <c r="AS2" s="544" t="n"/>
+      <c r="AT2" s="544" t="n"/>
+      <c r="AU2" s="544" t="n"/>
+      <c r="AV2" s="545" t="n"/>
+      <c r="AW2" s="546" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="446" t="n"/>
-      <c r="AY2" s="446" t="n"/>
-      <c r="AZ2" s="446" t="n"/>
-      <c r="BA2" s="446" t="n"/>
-      <c r="BB2" s="446" t="n"/>
-      <c r="BC2" s="446" t="n"/>
-      <c r="BD2" s="447" t="n"/>
+      <c r="AX2" s="544" t="n"/>
+      <c r="AY2" s="544" t="n"/>
+      <c r="AZ2" s="544" t="n"/>
+      <c r="BA2" s="544" t="n"/>
+      <c r="BB2" s="544" t="n"/>
+      <c r="BC2" s="544" t="n"/>
+      <c r="BD2" s="547" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="437" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="438" t="n"/>
-      <c r="L3" s="439" t="n"/>
-      <c r="M3" s="440" t="n"/>
-      <c r="N3" s="440" t="n"/>
-      <c r="O3" s="440" t="n"/>
-      <c r="P3" s="440" t="n"/>
-      <c r="Q3" s="440" t="n"/>
-      <c r="R3" s="440" t="n"/>
-      <c r="S3" s="440" t="n"/>
-      <c r="T3" s="440" t="n"/>
-      <c r="U3" s="440" t="n"/>
-      <c r="V3" s="440" t="n"/>
-      <c r="W3" s="440" t="n"/>
-      <c r="X3" s="440" t="n"/>
-      <c r="Y3" s="440" t="n"/>
-      <c r="Z3" s="440" t="n"/>
-      <c r="AA3" s="440" t="n"/>
-      <c r="AB3" s="440" t="n"/>
-      <c r="AC3" s="440" t="n"/>
-      <c r="AD3" s="440" t="n"/>
-      <c r="AE3" s="440" t="n"/>
-      <c r="AF3" s="440" t="n"/>
-      <c r="AG3" s="440" t="n"/>
-      <c r="AH3" s="440" t="n"/>
-      <c r="AI3" s="440" t="n"/>
-      <c r="AJ3" s="440" t="n"/>
-      <c r="AK3" s="440" t="n"/>
-      <c r="AL3" s="440" t="n"/>
-      <c r="AM3" s="440" t="n"/>
-      <c r="AN3" s="440" t="n"/>
-      <c r="AO3" s="440" t="n"/>
-      <c r="AP3" s="441" t="n"/>
-      <c r="AQ3" s="442" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="10" t="n"/>
+      <c r="AI3" s="10" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="10" t="n"/>
+      <c r="AO3" s="10" t="n"/>
+      <c r="AP3" s="10" t="n"/>
+      <c r="AQ3" s="543" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="443" t="n"/>
-      <c r="AS3" s="443" t="n"/>
-      <c r="AT3" s="443" t="n"/>
-      <c r="AU3" s="443" t="n"/>
-      <c r="AV3" s="444" t="n"/>
-      <c r="AW3" s="445" t="inlineStr">
+      <c r="AR3" s="544" t="n"/>
+      <c r="AS3" s="544" t="n"/>
+      <c r="AT3" s="544" t="n"/>
+      <c r="AU3" s="544" t="n"/>
+      <c r="AV3" s="545" t="n"/>
+      <c r="AW3" s="546" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="446" t="n"/>
-      <c r="AY3" s="446" t="n"/>
-      <c r="AZ3" s="446" t="n"/>
-      <c r="BA3" s="446" t="n"/>
-      <c r="BB3" s="446" t="n"/>
-      <c r="BC3" s="446" t="n"/>
-      <c r="BD3" s="447" t="n"/>
+      <c r="AX3" s="544" t="n"/>
+      <c r="AY3" s="544" t="n"/>
+      <c r="AZ3" s="544" t="n"/>
+      <c r="BA3" s="544" t="n"/>
+      <c r="BB3" s="544" t="n"/>
+      <c r="BC3" s="544" t="n"/>
+      <c r="BD3" s="547" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="437" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="438" t="n"/>
-      <c r="L4" s="448" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="548" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="449" t="n"/>
-      <c r="N4" s="449" t="n"/>
-      <c r="O4" s="449" t="n"/>
-      <c r="P4" s="449" t="n"/>
-      <c r="Q4" s="449" t="n"/>
-      <c r="R4" s="449" t="n"/>
-      <c r="S4" s="449" t="n"/>
-      <c r="T4" s="449" t="n"/>
-      <c r="U4" s="449" t="n"/>
-      <c r="V4" s="449" t="n"/>
-      <c r="W4" s="449" t="n"/>
-      <c r="X4" s="449" t="n"/>
-      <c r="Y4" s="449" t="n"/>
-      <c r="Z4" s="449" t="n"/>
-      <c r="AA4" s="449" t="n"/>
-      <c r="AB4" s="449" t="n"/>
-      <c r="AC4" s="449" t="n"/>
-      <c r="AD4" s="449" t="n"/>
-      <c r="AE4" s="449" t="n"/>
-      <c r="AF4" s="449" t="n"/>
-      <c r="AG4" s="449" t="n"/>
-      <c r="AH4" s="449" t="n"/>
-      <c r="AI4" s="449" t="n"/>
-      <c r="AJ4" s="449" t="n"/>
-      <c r="AK4" s="449" t="n"/>
-      <c r="AL4" s="449" t="n"/>
-      <c r="AM4" s="449" t="n"/>
-      <c r="AN4" s="449" t="n"/>
-      <c r="AO4" s="449" t="n"/>
-      <c r="AP4" s="450" t="n"/>
-      <c r="AQ4" s="442" t="inlineStr">
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="10" t="n"/>
+      <c r="AI4" s="10" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="10" t="n"/>
+      <c r="AO4" s="10" t="n"/>
+      <c r="AP4" s="10" t="n"/>
+      <c r="AQ4" s="543" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="443" t="n"/>
-      <c r="AS4" s="443" t="n"/>
-      <c r="AT4" s="443" t="n"/>
-      <c r="AU4" s="443" t="n"/>
-      <c r="AV4" s="444" t="n"/>
-      <c r="AW4" s="445" t="inlineStr">
+      <c r="AR4" s="544" t="n"/>
+      <c r="AS4" s="544" t="n"/>
+      <c r="AT4" s="544" t="n"/>
+      <c r="AU4" s="544" t="n"/>
+      <c r="AV4" s="545" t="n"/>
+      <c r="AW4" s="546" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="446" t="n"/>
-      <c r="AY4" s="446" t="n"/>
-      <c r="AZ4" s="446" t="n"/>
-      <c r="BA4" s="446" t="n"/>
-      <c r="BB4" s="446" t="n"/>
-      <c r="BC4" s="446" t="n"/>
-      <c r="BD4" s="447" t="n"/>
+      <c r="AX4" s="544" t="n"/>
+      <c r="AY4" s="544" t="n"/>
+      <c r="AZ4" s="544" t="n"/>
+      <c r="BA4" s="544" t="n"/>
+      <c r="BB4" s="544" t="n"/>
+      <c r="BC4" s="544" t="n"/>
+      <c r="BD4" s="547" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="451" t="n"/>
-      <c r="B5" s="452" t="n"/>
-      <c r="C5" s="452" t="n"/>
-      <c r="D5" s="452" t="n"/>
-      <c r="E5" s="452" t="n"/>
-      <c r="F5" s="452" t="n"/>
-      <c r="G5" s="452" t="n"/>
-      <c r="H5" s="452" t="n"/>
-      <c r="I5" s="452" t="n"/>
-      <c r="J5" s="452" t="n"/>
-      <c r="K5" s="453" t="n"/>
-      <c r="L5" s="454" t="inlineStr">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="455" t="n"/>
-      <c r="N5" s="455" t="n"/>
-      <c r="O5" s="455" t="n"/>
-      <c r="P5" s="455" t="n"/>
-      <c r="Q5" s="455" t="n"/>
-      <c r="R5" s="455" t="n"/>
-      <c r="S5" s="455" t="n"/>
-      <c r="T5" s="455" t="n"/>
-      <c r="U5" s="455" t="n"/>
-      <c r="V5" s="455" t="n"/>
-      <c r="W5" s="455" t="n"/>
-      <c r="X5" s="455" t="n"/>
-      <c r="Y5" s="455" t="n"/>
-      <c r="Z5" s="455" t="n"/>
-      <c r="AA5" s="455" t="n"/>
-      <c r="AB5" s="455" t="n"/>
-      <c r="AC5" s="455" t="n"/>
-      <c r="AD5" s="455" t="n"/>
-      <c r="AE5" s="455" t="n"/>
-      <c r="AF5" s="455" t="n"/>
-      <c r="AG5" s="455" t="n"/>
-      <c r="AH5" s="455" t="n"/>
-      <c r="AI5" s="455" t="n"/>
-      <c r="AJ5" s="455" t="n"/>
-      <c r="AK5" s="455" t="n"/>
-      <c r="AL5" s="455" t="n"/>
-      <c r="AM5" s="455" t="n"/>
-      <c r="AN5" s="455" t="n"/>
-      <c r="AO5" s="455" t="n"/>
-      <c r="AP5" s="456" t="n"/>
-      <c r="AQ5" s="457" t="inlineStr">
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="19" t="n"/>
+      <c r="V5" s="19" t="n"/>
+      <c r="W5" s="19" t="n"/>
+      <c r="X5" s="19" t="n"/>
+      <c r="Y5" s="19" t="n"/>
+      <c r="Z5" s="19" t="n"/>
+      <c r="AA5" s="19" t="n"/>
+      <c r="AB5" s="19" t="n"/>
+      <c r="AC5" s="19" t="n"/>
+      <c r="AD5" s="19" t="n"/>
+      <c r="AE5" s="19" t="n"/>
+      <c r="AF5" s="19" t="n"/>
+      <c r="AG5" s="19" t="n"/>
+      <c r="AH5" s="19" t="n"/>
+      <c r="AI5" s="19" t="n"/>
+      <c r="AJ5" s="19" t="n"/>
+      <c r="AK5" s="19" t="n"/>
+      <c r="AL5" s="19" t="n"/>
+      <c r="AM5" s="19" t="n"/>
+      <c r="AN5" s="19" t="n"/>
+      <c r="AO5" s="19" t="n"/>
+      <c r="AP5" s="19" t="n"/>
+      <c r="AQ5" s="549" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="458" t="n"/>
-      <c r="AS5" s="458" t="n"/>
-      <c r="AT5" s="458" t="n"/>
-      <c r="AU5" s="458" t="n"/>
-      <c r="AV5" s="459" t="n"/>
-      <c r="AW5" s="460" t="inlineStr">
+      <c r="AR5" s="550" t="n"/>
+      <c r="AS5" s="550" t="n"/>
+      <c r="AT5" s="550" t="n"/>
+      <c r="AU5" s="550" t="n"/>
+      <c r="AV5" s="551" t="n"/>
+      <c r="AW5" s="552" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="461" t="n"/>
-      <c r="AY5" s="461" t="n"/>
-      <c r="AZ5" s="461" t="n"/>
-      <c r="BA5" s="461" t="n"/>
-      <c r="BB5" s="461" t="n"/>
-      <c r="BC5" s="461" t="n"/>
-      <c r="BD5" s="462" t="n"/>
+      <c r="AX5" s="550" t="n"/>
+      <c r="AY5" s="550" t="n"/>
+      <c r="AZ5" s="550" t="n"/>
+      <c r="BA5" s="550" t="n"/>
+      <c r="BB5" s="550" t="n"/>
+      <c r="BC5" s="550" t="n"/>
+      <c r="BD5" s="553" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="463" t="n"/>
-      <c r="B6" s="463" t="n"/>
-      <c r="C6" s="463" t="n"/>
-      <c r="D6" s="463" t="n"/>
-      <c r="E6" s="463" t="n"/>
-      <c r="F6" s="463" t="n"/>
-      <c r="G6" s="463" t="n"/>
-      <c r="H6" s="463" t="n"/>
-      <c r="I6" s="463" t="n"/>
-      <c r="J6" s="463" t="n"/>
-      <c r="K6" s="463" t="n"/>
-      <c r="L6" s="463" t="n"/>
-      <c r="M6" s="463" t="n"/>
-      <c r="N6" s="463" t="n"/>
-      <c r="O6" s="463" t="n"/>
-      <c r="P6" s="463" t="n"/>
-      <c r="Q6" s="463" t="n"/>
-      <c r="R6" s="463" t="n"/>
-      <c r="S6" s="463" t="n"/>
-      <c r="T6" s="463" t="n"/>
-      <c r="U6" s="463" t="n"/>
-      <c r="V6" s="463" t="n"/>
-      <c r="W6" s="463" t="n"/>
-      <c r="X6" s="463" t="n"/>
-      <c r="Y6" s="463" t="n"/>
-      <c r="Z6" s="463" t="n"/>
-      <c r="AA6" s="463" t="n"/>
-      <c r="AB6" s="463" t="n"/>
-      <c r="AC6" s="463" t="n"/>
-      <c r="AD6" s="463" t="n"/>
-      <c r="AE6" s="463" t="n"/>
-      <c r="AF6" s="463" t="n"/>
-      <c r="AG6" s="463" t="n"/>
-      <c r="AH6" s="463" t="n"/>
-      <c r="AI6" s="463" t="n"/>
-      <c r="AJ6" s="463" t="n"/>
-      <c r="AK6" s="463" t="n"/>
-      <c r="AL6" s="463" t="n"/>
-      <c r="AM6" s="463" t="n"/>
-      <c r="AN6" s="463" t="n"/>
-      <c r="AO6" s="463" t="n"/>
-      <c r="AP6" s="463" t="n"/>
-      <c r="AQ6" s="463" t="n"/>
-      <c r="AR6" s="463" t="n"/>
-      <c r="AS6" s="463" t="n"/>
-      <c r="AT6" s="463" t="n"/>
-      <c r="AU6" s="463" t="n"/>
-      <c r="AV6" s="463" t="n"/>
-      <c r="AW6" s="463" t="n"/>
-      <c r="AX6" s="463" t="n"/>
-      <c r="AY6" s="463" t="n"/>
-      <c r="AZ6" s="463" t="n"/>
-      <c r="BA6" s="463" t="n"/>
-      <c r="BB6" s="463" t="n"/>
-      <c r="BC6" s="463" t="n"/>
-      <c r="BD6" s="463" t="n"/>
+      <c r="A6" s="515" t="n"/>
+      <c r="B6" s="515" t="n"/>
+      <c r="C6" s="515" t="n"/>
+      <c r="D6" s="515" t="n"/>
+      <c r="E6" s="515" t="n"/>
+      <c r="F6" s="515" t="n"/>
+      <c r="G6" s="515" t="n"/>
+      <c r="H6" s="515" t="n"/>
+      <c r="I6" s="515" t="n"/>
+      <c r="J6" s="515" t="n"/>
+      <c r="K6" s="515" t="n"/>
+      <c r="L6" s="515" t="n"/>
+      <c r="M6" s="515" t="n"/>
+      <c r="N6" s="515" t="n"/>
+      <c r="O6" s="515" t="n"/>
+      <c r="P6" s="515" t="n"/>
+      <c r="Q6" s="515" t="n"/>
+      <c r="R6" s="515" t="n"/>
+      <c r="S6" s="515" t="n"/>
+      <c r="T6" s="515" t="n"/>
+      <c r="U6" s="515" t="n"/>
+      <c r="V6" s="515" t="n"/>
+      <c r="W6" s="515" t="n"/>
+      <c r="X6" s="515" t="n"/>
+      <c r="Y6" s="515" t="n"/>
+      <c r="Z6" s="515" t="n"/>
+      <c r="AA6" s="515" t="n"/>
+      <c r="AB6" s="515" t="n"/>
+      <c r="AC6" s="515" t="n"/>
+      <c r="AD6" s="515" t="n"/>
+      <c r="AE6" s="515" t="n"/>
+      <c r="AF6" s="515" t="n"/>
+      <c r="AG6" s="515" t="n"/>
+      <c r="AH6" s="515" t="n"/>
+      <c r="AI6" s="515" t="n"/>
+      <c r="AJ6" s="515" t="n"/>
+      <c r="AK6" s="515" t="n"/>
+      <c r="AL6" s="515" t="n"/>
+      <c r="AM6" s="515" t="n"/>
+      <c r="AN6" s="515" t="n"/>
+      <c r="AO6" s="515" t="n"/>
+      <c r="AP6" s="515" t="n"/>
+      <c r="AQ6" s="515" t="n"/>
+      <c r="AR6" s="515" t="n"/>
+      <c r="AS6" s="515" t="n"/>
+      <c r="AT6" s="515" t="n"/>
+      <c r="AU6" s="515" t="n"/>
+      <c r="AV6" s="515" t="n"/>
+      <c r="AW6" s="515" t="n"/>
+      <c r="AX6" s="515" t="n"/>
+      <c r="AY6" s="515" t="n"/>
+      <c r="AZ6" s="515" t="n"/>
+      <c r="BA6" s="515" t="n"/>
+      <c r="BB6" s="515" t="n"/>
+      <c r="BC6" s="515" t="n"/>
+      <c r="BD6" s="515" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="464" t="inlineStr">
+      <c r="A7" s="554" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="465" t="n"/>
-      <c r="C7" s="465" t="n"/>
-      <c r="D7" s="465" t="n"/>
-      <c r="E7" s="465" t="n"/>
-      <c r="F7" s="465" t="n"/>
-      <c r="G7" s="465" t="n"/>
-      <c r="H7" s="465" t="n"/>
-      <c r="I7" s="465" t="n"/>
-      <c r="J7" s="465" t="n"/>
-      <c r="K7" s="465" t="n"/>
-      <c r="L7" s="465" t="n"/>
-      <c r="M7" s="465" t="n"/>
-      <c r="N7" s="465" t="n"/>
-      <c r="O7" s="465" t="n"/>
-      <c r="P7" s="465" t="n"/>
-      <c r="Q7" s="465" t="n"/>
-      <c r="R7" s="465" t="n"/>
-      <c r="S7" s="465" t="n"/>
-      <c r="T7" s="465" t="n"/>
-      <c r="U7" s="465" t="n"/>
-      <c r="V7" s="465" t="n"/>
-      <c r="W7" s="465" t="n"/>
-      <c r="X7" s="465" t="n"/>
-      <c r="Y7" s="465" t="n"/>
-      <c r="Z7" s="465" t="n"/>
-      <c r="AA7" s="465" t="n"/>
-      <c r="AB7" s="465" t="n"/>
-      <c r="AC7" s="465" t="n"/>
-      <c r="AD7" s="465" t="n"/>
-      <c r="AE7" s="465" t="n"/>
-      <c r="AF7" s="465" t="n"/>
-      <c r="AG7" s="465" t="n"/>
-      <c r="AH7" s="465" t="n"/>
-      <c r="AI7" s="465" t="n"/>
-      <c r="AJ7" s="465" t="n"/>
-      <c r="AK7" s="465" t="n"/>
-      <c r="AL7" s="465" t="n"/>
-      <c r="AM7" s="465" t="n"/>
-      <c r="AN7" s="465" t="n"/>
-      <c r="AO7" s="465" t="n"/>
-      <c r="AP7" s="465" t="n"/>
-      <c r="AQ7" s="465" t="n"/>
-      <c r="AR7" s="465" t="n"/>
-      <c r="AS7" s="465" t="n"/>
-      <c r="AT7" s="465" t="n"/>
-      <c r="AU7" s="465" t="n"/>
-      <c r="AV7" s="465" t="n"/>
-      <c r="AW7" s="465" t="n"/>
-      <c r="AX7" s="465" t="n"/>
-      <c r="AY7" s="465" t="n"/>
-      <c r="AZ7" s="465" t="n"/>
-      <c r="BA7" s="465" t="n"/>
-      <c r="BB7" s="465" t="n"/>
-      <c r="BC7" s="465" t="n"/>
-      <c r="BD7" s="466" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n"/>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="27" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="27" t="n"/>
+      <c r="AE7" s="27" t="n"/>
+      <c r="AF7" s="27" t="n"/>
+      <c r="AG7" s="27" t="n"/>
+      <c r="AH7" s="27" t="n"/>
+      <c r="AI7" s="27" t="n"/>
+      <c r="AJ7" s="27" t="n"/>
+      <c r="AK7" s="27" t="n"/>
+      <c r="AL7" s="27" t="n"/>
+      <c r="AM7" s="27" t="n"/>
+      <c r="AN7" s="27" t="n"/>
+      <c r="AO7" s="27" t="n"/>
+      <c r="AP7" s="27" t="n"/>
+      <c r="AQ7" s="27" t="n"/>
+      <c r="AR7" s="27" t="n"/>
+      <c r="AS7" s="27" t="n"/>
+      <c r="AT7" s="27" t="n"/>
+      <c r="AU7" s="27" t="n"/>
+      <c r="AV7" s="27" t="n"/>
+      <c r="AW7" s="27" t="n"/>
+      <c r="AX7" s="27" t="n"/>
+      <c r="AY7" s="27" t="n"/>
+      <c r="AZ7" s="27" t="n"/>
+      <c r="BA7" s="27" t="n"/>
+      <c r="BB7" s="27" t="n"/>
+      <c r="BC7" s="27" t="n"/>
+      <c r="BD7" s="28" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="467" t="inlineStr">
+      <c r="A8" s="555" t="inlineStr">
         <is>
           <t>Final Inspection Report ID</t>
         </is>
       </c>
-      <c r="B8" s="468" t="n"/>
-      <c r="C8" s="468" t="n"/>
-      <c r="D8" s="468" t="n"/>
-      <c r="E8" s="468" t="n"/>
-      <c r="F8" s="468" t="n"/>
-      <c r="G8" s="468" t="n"/>
-      <c r="H8" s="468" t="n"/>
-      <c r="I8" s="468" t="n"/>
-      <c r="J8" s="468" t="n"/>
-      <c r="K8" s="469" t="n"/>
-      <c r="L8" s="470" t="n"/>
-      <c r="M8" s="470" t="n"/>
-      <c r="N8" s="470" t="n"/>
-      <c r="O8" s="470" t="n"/>
-      <c r="P8" s="470" t="n"/>
-      <c r="Q8" s="470" t="n"/>
-      <c r="R8" s="470" t="n"/>
-      <c r="S8" s="470" t="n"/>
-      <c r="T8" s="470" t="n"/>
-      <c r="U8" s="470" t="n"/>
-      <c r="V8" s="470" t="n"/>
-      <c r="W8" s="470" t="n"/>
-      <c r="X8" s="470" t="n"/>
-      <c r="Y8" s="470" t="n"/>
-      <c r="Z8" s="470" t="n"/>
-      <c r="AA8" s="470" t="n"/>
-      <c r="AB8" s="470" t="n"/>
-      <c r="AC8" s="471" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="556" t="n"/>
+      <c r="L8" s="557" t="n"/>
+      <c r="M8" s="557" t="n"/>
+      <c r="N8" s="557" t="n"/>
+      <c r="O8" s="557" t="n"/>
+      <c r="P8" s="557" t="n"/>
+      <c r="Q8" s="557" t="n"/>
+      <c r="R8" s="557" t="n"/>
+      <c r="S8" s="557" t="n"/>
+      <c r="T8" s="557" t="n"/>
+      <c r="U8" s="557" t="n"/>
+      <c r="V8" s="557" t="n"/>
+      <c r="W8" s="557" t="n"/>
+      <c r="X8" s="557" t="n"/>
+      <c r="Y8" s="557" t="n"/>
+      <c r="Z8" s="557" t="n"/>
+      <c r="AA8" s="557" t="n"/>
+      <c r="AB8" s="558" t="n"/>
+      <c r="AC8" s="559" t="inlineStr">
         <is>
           <t>Final Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="468" t="n"/>
-      <c r="AE8" s="468" t="n"/>
-      <c r="AF8" s="468" t="n"/>
-      <c r="AG8" s="468" t="n"/>
-      <c r="AH8" s="468" t="n"/>
-      <c r="AI8" s="468" t="n"/>
-      <c r="AJ8" s="468" t="n"/>
-      <c r="AK8" s="468" t="n"/>
-      <c r="AL8" s="468" t="n"/>
-      <c r="AM8" s="469" t="n"/>
-      <c r="AN8" s="470" t="n"/>
-      <c r="AO8" s="470" t="n"/>
-      <c r="AP8" s="470" t="n"/>
-      <c r="AQ8" s="470" t="n"/>
-      <c r="AR8" s="470" t="n"/>
-      <c r="AS8" s="470" t="n"/>
-      <c r="AT8" s="470" t="n"/>
-      <c r="AU8" s="470" t="n"/>
-      <c r="AV8" s="470" t="n"/>
-      <c r="AW8" s="470" t="n"/>
-      <c r="AX8" s="470" t="n"/>
-      <c r="AY8" s="470" t="n"/>
-      <c r="AZ8" s="470" t="n"/>
-      <c r="BA8" s="470" t="n"/>
-      <c r="BB8" s="470" t="n"/>
-      <c r="BC8" s="470" t="n"/>
-      <c r="BD8" s="472" t="n"/>
+      <c r="AD8" s="5" t="n"/>
+      <c r="AE8" s="5" t="n"/>
+      <c r="AF8" s="5" t="n"/>
+      <c r="AG8" s="5" t="n"/>
+      <c r="AH8" s="5" t="n"/>
+      <c r="AI8" s="5" t="n"/>
+      <c r="AJ8" s="5" t="n"/>
+      <c r="AK8" s="5" t="n"/>
+      <c r="AL8" s="6" t="n"/>
+      <c r="AM8" s="556" t="n"/>
+      <c r="AN8" s="557" t="n"/>
+      <c r="AO8" s="557" t="n"/>
+      <c r="AP8" s="557" t="n"/>
+      <c r="AQ8" s="557" t="n"/>
+      <c r="AR8" s="557" t="n"/>
+      <c r="AS8" s="557" t="n"/>
+      <c r="AT8" s="557" t="n"/>
+      <c r="AU8" s="557" t="n"/>
+      <c r="AV8" s="557" t="n"/>
+      <c r="AW8" s="557" t="n"/>
+      <c r="AX8" s="557" t="n"/>
+      <c r="AY8" s="557" t="n"/>
+      <c r="AZ8" s="557" t="n"/>
+      <c r="BA8" s="557" t="n"/>
+      <c r="BB8" s="557" t="n"/>
+      <c r="BC8" s="557" t="n"/>
+      <c r="BD8" s="560" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="473" t="inlineStr">
+      <c r="A9" s="561" t="inlineStr">
         <is>
           <t>Job / Shipment</t>
         </is>
       </c>
-      <c r="B9" s="342" t="n"/>
-      <c r="C9" s="342" t="n"/>
-      <c r="D9" s="342" t="n"/>
-      <c r="E9" s="342" t="n"/>
-      <c r="F9" s="342" t="n"/>
-      <c r="G9" s="342" t="n"/>
-      <c r="H9" s="342" t="n"/>
-      <c r="I9" s="342" t="n"/>
-      <c r="J9" s="342" t="n"/>
-      <c r="K9" s="474" t="n"/>
-      <c r="L9" s="360" t="n"/>
-      <c r="M9" s="360" t="n"/>
-      <c r="N9" s="360" t="n"/>
-      <c r="O9" s="360" t="n"/>
-      <c r="P9" s="360" t="n"/>
-      <c r="Q9" s="360" t="n"/>
-      <c r="R9" s="360" t="n"/>
-      <c r="S9" s="360" t="n"/>
-      <c r="T9" s="360" t="n"/>
-      <c r="U9" s="360" t="n"/>
-      <c r="V9" s="360" t="n"/>
-      <c r="W9" s="360" t="n"/>
-      <c r="X9" s="360" t="n"/>
-      <c r="Y9" s="360" t="n"/>
-      <c r="Z9" s="360" t="n"/>
-      <c r="AA9" s="360" t="n"/>
-      <c r="AB9" s="360" t="n"/>
-      <c r="AC9" s="475" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="562" t="n"/>
+      <c r="L9" s="563" t="n"/>
+      <c r="M9" s="563" t="n"/>
+      <c r="N9" s="563" t="n"/>
+      <c r="O9" s="563" t="n"/>
+      <c r="P9" s="563" t="n"/>
+      <c r="Q9" s="563" t="n"/>
+      <c r="R9" s="563" t="n"/>
+      <c r="S9" s="563" t="n"/>
+      <c r="T9" s="563" t="n"/>
+      <c r="U9" s="563" t="n"/>
+      <c r="V9" s="563" t="n"/>
+      <c r="W9" s="563" t="n"/>
+      <c r="X9" s="563" t="n"/>
+      <c r="Y9" s="563" t="n"/>
+      <c r="Z9" s="563" t="n"/>
+      <c r="AA9" s="563" t="n"/>
+      <c r="AB9" s="564" t="n"/>
+      <c r="AC9" s="565" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="AD9" s="342" t="n"/>
-      <c r="AE9" s="342" t="n"/>
-      <c r="AF9" s="342" t="n"/>
-      <c r="AG9" s="342" t="n"/>
-      <c r="AH9" s="342" t="n"/>
-      <c r="AI9" s="342" t="n"/>
-      <c r="AJ9" s="342" t="n"/>
-      <c r="AK9" s="342" t="n"/>
-      <c r="AL9" s="342" t="n"/>
-      <c r="AM9" s="474" t="n"/>
-      <c r="AN9" s="360" t="n"/>
-      <c r="AO9" s="360" t="n"/>
-      <c r="AP9" s="360" t="n"/>
-      <c r="AQ9" s="360" t="n"/>
-      <c r="AR9" s="360" t="n"/>
-      <c r="AS9" s="360" t="n"/>
-      <c r="AT9" s="360" t="n"/>
-      <c r="AU9" s="360" t="n"/>
-      <c r="AV9" s="360" t="n"/>
-      <c r="AW9" s="360" t="n"/>
-      <c r="AX9" s="360" t="n"/>
-      <c r="AY9" s="360" t="n"/>
-      <c r="AZ9" s="360" t="n"/>
-      <c r="BA9" s="360" t="n"/>
-      <c r="BB9" s="360" t="n"/>
-      <c r="BC9" s="360" t="n"/>
-      <c r="BD9" s="476" t="n"/>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="n"/>
+      <c r="AF9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n"/>
+      <c r="AH9" s="12" t="n"/>
+      <c r="AI9" s="12" t="n"/>
+      <c r="AJ9" s="12" t="n"/>
+      <c r="AK9" s="12" t="n"/>
+      <c r="AL9" s="13" t="n"/>
+      <c r="AM9" s="562" t="n"/>
+      <c r="AN9" s="563" t="n"/>
+      <c r="AO9" s="563" t="n"/>
+      <c r="AP9" s="563" t="n"/>
+      <c r="AQ9" s="563" t="n"/>
+      <c r="AR9" s="563" t="n"/>
+      <c r="AS9" s="563" t="n"/>
+      <c r="AT9" s="563" t="n"/>
+      <c r="AU9" s="563" t="n"/>
+      <c r="AV9" s="563" t="n"/>
+      <c r="AW9" s="563" t="n"/>
+      <c r="AX9" s="563" t="n"/>
+      <c r="AY9" s="563" t="n"/>
+      <c r="AZ9" s="563" t="n"/>
+      <c r="BA9" s="563" t="n"/>
+      <c r="BB9" s="563" t="n"/>
+      <c r="BC9" s="563" t="n"/>
+      <c r="BD9" s="566" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="473" t="inlineStr">
+      <c r="A10" s="561" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="B10" s="342" t="n"/>
-      <c r="C10" s="342" t="n"/>
-      <c r="D10" s="342" t="n"/>
-      <c r="E10" s="342" t="n"/>
-      <c r="F10" s="342" t="n"/>
-      <c r="G10" s="342" t="n"/>
-      <c r="H10" s="342" t="n"/>
-      <c r="I10" s="342" t="n"/>
-      <c r="J10" s="342" t="n"/>
-      <c r="K10" s="474" t="n"/>
-      <c r="L10" s="360" t="n"/>
-      <c r="M10" s="360" t="n"/>
-      <c r="N10" s="360" t="n"/>
-      <c r="O10" s="360" t="n"/>
-      <c r="P10" s="360" t="n"/>
-      <c r="Q10" s="360" t="n"/>
-      <c r="R10" s="360" t="n"/>
-      <c r="S10" s="360" t="n"/>
-      <c r="T10" s="360" t="n"/>
-      <c r="U10" s="360" t="n"/>
-      <c r="V10" s="360" t="n"/>
-      <c r="W10" s="360" t="n"/>
-      <c r="X10" s="360" t="n"/>
-      <c r="Y10" s="360" t="n"/>
-      <c r="Z10" s="360" t="n"/>
-      <c r="AA10" s="360" t="n"/>
-      <c r="AB10" s="360" t="n"/>
-      <c r="AC10" s="475" t="inlineStr">
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="562" t="n"/>
+      <c r="L10" s="563" t="n"/>
+      <c r="M10" s="563" t="n"/>
+      <c r="N10" s="563" t="n"/>
+      <c r="O10" s="563" t="n"/>
+      <c r="P10" s="563" t="n"/>
+      <c r="Q10" s="563" t="n"/>
+      <c r="R10" s="563" t="n"/>
+      <c r="S10" s="563" t="n"/>
+      <c r="T10" s="563" t="n"/>
+      <c r="U10" s="563" t="n"/>
+      <c r="V10" s="563" t="n"/>
+      <c r="W10" s="563" t="n"/>
+      <c r="X10" s="563" t="n"/>
+      <c r="Y10" s="563" t="n"/>
+      <c r="Z10" s="563" t="n"/>
+      <c r="AA10" s="563" t="n"/>
+      <c r="AB10" s="564" t="n"/>
+      <c r="AC10" s="565" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="AD10" s="342" t="n"/>
-      <c r="AE10" s="342" t="n"/>
-      <c r="AF10" s="342" t="n"/>
-      <c r="AG10" s="342" t="n"/>
-      <c r="AH10" s="342" t="n"/>
-      <c r="AI10" s="342" t="n"/>
-      <c r="AJ10" s="342" t="n"/>
-      <c r="AK10" s="342" t="n"/>
-      <c r="AL10" s="342" t="n"/>
-      <c r="AM10" s="474" t="n"/>
-      <c r="AN10" s="360" t="n"/>
-      <c r="AO10" s="360" t="n"/>
-      <c r="AP10" s="360" t="n"/>
-      <c r="AQ10" s="360" t="n"/>
-      <c r="AR10" s="360" t="n"/>
-      <c r="AS10" s="360" t="n"/>
-      <c r="AT10" s="360" t="n"/>
-      <c r="AU10" s="360" t="n"/>
-      <c r="AV10" s="360" t="n"/>
-      <c r="AW10" s="360" t="n"/>
-      <c r="AX10" s="360" t="n"/>
-      <c r="AY10" s="360" t="n"/>
-      <c r="AZ10" s="360" t="n"/>
-      <c r="BA10" s="360" t="n"/>
-      <c r="BB10" s="360" t="n"/>
-      <c r="BC10" s="360" t="n"/>
-      <c r="BD10" s="476" t="n"/>
+      <c r="AD10" s="12" t="n"/>
+      <c r="AE10" s="12" t="n"/>
+      <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="12" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="12" t="n"/>
+      <c r="AK10" s="12" t="n"/>
+      <c r="AL10" s="13" t="n"/>
+      <c r="AM10" s="562" t="n"/>
+      <c r="AN10" s="563" t="n"/>
+      <c r="AO10" s="563" t="n"/>
+      <c r="AP10" s="563" t="n"/>
+      <c r="AQ10" s="563" t="n"/>
+      <c r="AR10" s="563" t="n"/>
+      <c r="AS10" s="563" t="n"/>
+      <c r="AT10" s="563" t="n"/>
+      <c r="AU10" s="563" t="n"/>
+      <c r="AV10" s="563" t="n"/>
+      <c r="AW10" s="563" t="n"/>
+      <c r="AX10" s="563" t="n"/>
+      <c r="AY10" s="563" t="n"/>
+      <c r="AZ10" s="563" t="n"/>
+      <c r="BA10" s="563" t="n"/>
+      <c r="BB10" s="563" t="n"/>
+      <c r="BC10" s="563" t="n"/>
+      <c r="BD10" s="566" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="473" t="inlineStr">
+      <c r="A11" s="561" t="inlineStr">
         <is>
           <t>Inspection Basis</t>
         </is>
       </c>
-      <c r="B11" s="342" t="n"/>
-      <c r="C11" s="342" t="n"/>
-      <c r="D11" s="342" t="n"/>
-      <c r="E11" s="342" t="n"/>
-      <c r="F11" s="342" t="n"/>
-      <c r="G11" s="342" t="n"/>
-      <c r="H11" s="342" t="n"/>
-      <c r="I11" s="342" t="n"/>
-      <c r="J11" s="342" t="n"/>
-      <c r="K11" s="474" t="n"/>
-      <c r="L11" s="360" t="n"/>
-      <c r="M11" s="360" t="n"/>
-      <c r="N11" s="360" t="n"/>
-      <c r="O11" s="360" t="n"/>
-      <c r="P11" s="360" t="n"/>
-      <c r="Q11" s="360" t="n"/>
-      <c r="R11" s="360" t="n"/>
-      <c r="S11" s="360" t="n"/>
-      <c r="T11" s="360" t="n"/>
-      <c r="U11" s="360" t="n"/>
-      <c r="V11" s="360" t="n"/>
-      <c r="W11" s="360" t="n"/>
-      <c r="X11" s="360" t="n"/>
-      <c r="Y11" s="360" t="n"/>
-      <c r="Z11" s="360" t="n"/>
-      <c r="AA11" s="360" t="n"/>
-      <c r="AB11" s="360" t="n"/>
-      <c r="AC11" s="475" t="inlineStr">
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="562" t="n"/>
+      <c r="L11" s="563" t="n"/>
+      <c r="M11" s="563" t="n"/>
+      <c r="N11" s="563" t="n"/>
+      <c r="O11" s="563" t="n"/>
+      <c r="P11" s="563" t="n"/>
+      <c r="Q11" s="563" t="n"/>
+      <c r="R11" s="563" t="n"/>
+      <c r="S11" s="563" t="n"/>
+      <c r="T11" s="563" t="n"/>
+      <c r="U11" s="563" t="n"/>
+      <c r="V11" s="563" t="n"/>
+      <c r="W11" s="563" t="n"/>
+      <c r="X11" s="563" t="n"/>
+      <c r="Y11" s="563" t="n"/>
+      <c r="Z11" s="563" t="n"/>
+      <c r="AA11" s="563" t="n"/>
+      <c r="AB11" s="564" t="n"/>
+      <c r="AC11" s="565" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="AD11" s="342" t="n"/>
-      <c r="AE11" s="342" t="n"/>
-      <c r="AF11" s="342" t="n"/>
-      <c r="AG11" s="342" t="n"/>
-      <c r="AH11" s="342" t="n"/>
-      <c r="AI11" s="342" t="n"/>
-      <c r="AJ11" s="342" t="n"/>
-      <c r="AK11" s="342" t="n"/>
-      <c r="AL11" s="342" t="n"/>
-      <c r="AM11" s="474" t="n"/>
-      <c r="AN11" s="360" t="n"/>
-      <c r="AO11" s="360" t="n"/>
-      <c r="AP11" s="360" t="n"/>
-      <c r="AQ11" s="360" t="n"/>
-      <c r="AR11" s="360" t="n"/>
-      <c r="AS11" s="360" t="n"/>
-      <c r="AT11" s="360" t="n"/>
-      <c r="AU11" s="360" t="n"/>
-      <c r="AV11" s="360" t="n"/>
-      <c r="AW11" s="360" t="n"/>
-      <c r="AX11" s="360" t="n"/>
-      <c r="AY11" s="360" t="n"/>
-      <c r="AZ11" s="360" t="n"/>
-      <c r="BA11" s="360" t="n"/>
-      <c r="BB11" s="360" t="n"/>
-      <c r="BC11" s="360" t="n"/>
-      <c r="BD11" s="476" t="n"/>
+      <c r="AD11" s="12" t="n"/>
+      <c r="AE11" s="12" t="n"/>
+      <c r="AF11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n"/>
+      <c r="AH11" s="12" t="n"/>
+      <c r="AI11" s="12" t="n"/>
+      <c r="AJ11" s="12" t="n"/>
+      <c r="AK11" s="12" t="n"/>
+      <c r="AL11" s="13" t="n"/>
+      <c r="AM11" s="562" t="n"/>
+      <c r="AN11" s="563" t="n"/>
+      <c r="AO11" s="563" t="n"/>
+      <c r="AP11" s="563" t="n"/>
+      <c r="AQ11" s="563" t="n"/>
+      <c r="AR11" s="563" t="n"/>
+      <c r="AS11" s="563" t="n"/>
+      <c r="AT11" s="563" t="n"/>
+      <c r="AU11" s="563" t="n"/>
+      <c r="AV11" s="563" t="n"/>
+      <c r="AW11" s="563" t="n"/>
+      <c r="AX11" s="563" t="n"/>
+      <c r="AY11" s="563" t="n"/>
+      <c r="AZ11" s="563" t="n"/>
+      <c r="BA11" s="563" t="n"/>
+      <c r="BB11" s="563" t="n"/>
+      <c r="BC11" s="563" t="n"/>
+      <c r="BD11" s="566" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="477" t="inlineStr">
+      <c r="A12" s="567" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B12" s="478" t="n"/>
-      <c r="C12" s="478" t="n"/>
-      <c r="D12" s="478" t="n"/>
-      <c r="E12" s="478" t="n"/>
-      <c r="F12" s="478" t="n"/>
-      <c r="G12" s="478" t="n"/>
-      <c r="H12" s="478" t="n"/>
-      <c r="I12" s="478" t="n"/>
-      <c r="J12" s="478" t="n"/>
-      <c r="K12" s="479" t="n"/>
-      <c r="L12" s="480" t="n"/>
-      <c r="M12" s="480" t="n"/>
-      <c r="N12" s="480" t="n"/>
-      <c r="O12" s="480" t="n"/>
-      <c r="P12" s="480" t="n"/>
-      <c r="Q12" s="480" t="n"/>
-      <c r="R12" s="480" t="n"/>
-      <c r="S12" s="480" t="n"/>
-      <c r="T12" s="480" t="n"/>
-      <c r="U12" s="480" t="n"/>
-      <c r="V12" s="480" t="n"/>
-      <c r="W12" s="480" t="n"/>
-      <c r="X12" s="480" t="n"/>
-      <c r="Y12" s="480" t="n"/>
-      <c r="Z12" s="480" t="n"/>
-      <c r="AA12" s="480" t="n"/>
-      <c r="AB12" s="480" t="n"/>
-      <c r="AC12" s="481" t="inlineStr">
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="568" t="n"/>
+      <c r="L12" s="569" t="n"/>
+      <c r="M12" s="569" t="n"/>
+      <c r="N12" s="569" t="n"/>
+      <c r="O12" s="569" t="n"/>
+      <c r="P12" s="569" t="n"/>
+      <c r="Q12" s="569" t="n"/>
+      <c r="R12" s="569" t="n"/>
+      <c r="S12" s="569" t="n"/>
+      <c r="T12" s="569" t="n"/>
+      <c r="U12" s="569" t="n"/>
+      <c r="V12" s="569" t="n"/>
+      <c r="W12" s="569" t="n"/>
+      <c r="X12" s="569" t="n"/>
+      <c r="Y12" s="569" t="n"/>
+      <c r="Z12" s="569" t="n"/>
+      <c r="AA12" s="569" t="n"/>
+      <c r="AB12" s="570" t="n"/>
+      <c r="AC12" s="571" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="478" t="n"/>
-      <c r="AE12" s="478" t="n"/>
-      <c r="AF12" s="478" t="n"/>
-      <c r="AG12" s="478" t="n"/>
-      <c r="AH12" s="478" t="n"/>
-      <c r="AI12" s="478" t="n"/>
-      <c r="AJ12" s="478" t="n"/>
-      <c r="AK12" s="478" t="n"/>
-      <c r="AL12" s="478" t="n"/>
-      <c r="AM12" s="479" t="n"/>
-      <c r="AN12" s="480" t="n"/>
-      <c r="AO12" s="480" t="n"/>
-      <c r="AP12" s="480" t="n"/>
-      <c r="AQ12" s="480" t="n"/>
-      <c r="AR12" s="480" t="n"/>
-      <c r="AS12" s="480" t="n"/>
-      <c r="AT12" s="480" t="n"/>
-      <c r="AU12" s="480" t="n"/>
-      <c r="AV12" s="480" t="n"/>
-      <c r="AW12" s="480" t="n"/>
-      <c r="AX12" s="480" t="n"/>
-      <c r="AY12" s="480" t="n"/>
-      <c r="AZ12" s="480" t="n"/>
-      <c r="BA12" s="480" t="n"/>
-      <c r="BB12" s="480" t="n"/>
-      <c r="BC12" s="480" t="n"/>
-      <c r="BD12" s="482" t="n"/>
+      <c r="AD12" s="19" t="n"/>
+      <c r="AE12" s="19" t="n"/>
+      <c r="AF12" s="19" t="n"/>
+      <c r="AG12" s="19" t="n"/>
+      <c r="AH12" s="19" t="n"/>
+      <c r="AI12" s="19" t="n"/>
+      <c r="AJ12" s="19" t="n"/>
+      <c r="AK12" s="19" t="n"/>
+      <c r="AL12" s="22" t="n"/>
+      <c r="AM12" s="568" t="n"/>
+      <c r="AN12" s="569" t="n"/>
+      <c r="AO12" s="569" t="n"/>
+      <c r="AP12" s="569" t="n"/>
+      <c r="AQ12" s="569" t="n"/>
+      <c r="AR12" s="569" t="n"/>
+      <c r="AS12" s="569" t="n"/>
+      <c r="AT12" s="569" t="n"/>
+      <c r="AU12" s="569" t="n"/>
+      <c r="AV12" s="569" t="n"/>
+      <c r="AW12" s="569" t="n"/>
+      <c r="AX12" s="569" t="n"/>
+      <c r="AY12" s="569" t="n"/>
+      <c r="AZ12" s="569" t="n"/>
+      <c r="BA12" s="569" t="n"/>
+      <c r="BB12" s="569" t="n"/>
+      <c r="BC12" s="569" t="n"/>
+      <c r="BD12" s="572" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
-      <c r="A13" s="351" t="n"/>
-      <c r="B13" s="351" t="n"/>
-      <c r="C13" s="351" t="n"/>
-      <c r="D13" s="351" t="n"/>
-      <c r="E13" s="351" t="n"/>
-      <c r="F13" s="351" t="n"/>
-      <c r="G13" s="351" t="n"/>
-      <c r="H13" s="351" t="n"/>
-      <c r="I13" s="351" t="n"/>
-      <c r="J13" s="351" t="n"/>
-      <c r="K13" s="351" t="n"/>
-      <c r="L13" s="351" t="n"/>
-      <c r="M13" s="351" t="n"/>
-      <c r="N13" s="351" t="n"/>
-      <c r="O13" s="351" t="n"/>
-      <c r="P13" s="351" t="n"/>
-      <c r="Q13" s="351" t="n"/>
-      <c r="R13" s="351" t="n"/>
-      <c r="S13" s="351" t="n"/>
-      <c r="T13" s="351" t="n"/>
-      <c r="U13" s="351" t="n"/>
-      <c r="V13" s="351" t="n"/>
-      <c r="W13" s="351" t="n"/>
-      <c r="X13" s="351" t="n"/>
-      <c r="Y13" s="351" t="n"/>
-      <c r="Z13" s="351" t="n"/>
-      <c r="AA13" s="351" t="n"/>
-      <c r="AB13" s="351" t="n"/>
-      <c r="AC13" s="351" t="n"/>
-      <c r="AD13" s="351" t="n"/>
-      <c r="AE13" s="351" t="n"/>
-      <c r="AF13" s="351" t="n"/>
-      <c r="AG13" s="351" t="n"/>
-      <c r="AH13" s="351" t="n"/>
-      <c r="AI13" s="351" t="n"/>
-      <c r="AJ13" s="351" t="n"/>
-      <c r="AK13" s="351" t="n"/>
-      <c r="AL13" s="351" t="n"/>
-      <c r="AM13" s="351" t="n"/>
-      <c r="AN13" s="351" t="n"/>
-      <c r="AO13" s="351" t="n"/>
-      <c r="AP13" s="351" t="n"/>
-      <c r="AQ13" s="351" t="n"/>
-      <c r="AR13" s="351" t="n"/>
-      <c r="AS13" s="351" t="n"/>
-      <c r="AT13" s="351" t="n"/>
-      <c r="AU13" s="351" t="n"/>
-      <c r="AV13" s="351" t="n"/>
-      <c r="AW13" s="351" t="n"/>
-      <c r="AX13" s="351" t="n"/>
-      <c r="AY13" s="351" t="n"/>
-      <c r="AZ13" s="351" t="n"/>
-      <c r="BA13" s="351" t="n"/>
-      <c r="BB13" s="351" t="n"/>
-      <c r="BC13" s="351" t="n"/>
-      <c r="BD13" s="351" t="n"/>
+      <c r="A13" s="573" t="n"/>
+      <c r="B13" s="573" t="n"/>
+      <c r="C13" s="573" t="n"/>
+      <c r="D13" s="573" t="n"/>
+      <c r="E13" s="573" t="n"/>
+      <c r="F13" s="573" t="n"/>
+      <c r="G13" s="573" t="n"/>
+      <c r="H13" s="573" t="n"/>
+      <c r="I13" s="573" t="n"/>
+      <c r="J13" s="573" t="n"/>
+      <c r="K13" s="573" t="n"/>
+      <c r="L13" s="573" t="n"/>
+      <c r="M13" s="573" t="n"/>
+      <c r="N13" s="573" t="n"/>
+      <c r="O13" s="573" t="n"/>
+      <c r="P13" s="573" t="n"/>
+      <c r="Q13" s="573" t="n"/>
+      <c r="R13" s="573" t="n"/>
+      <c r="S13" s="573" t="n"/>
+      <c r="T13" s="573" t="n"/>
+      <c r="U13" s="573" t="n"/>
+      <c r="V13" s="573" t="n"/>
+      <c r="W13" s="573" t="n"/>
+      <c r="X13" s="573" t="n"/>
+      <c r="Y13" s="573" t="n"/>
+      <c r="Z13" s="573" t="n"/>
+      <c r="AA13" s="573" t="n"/>
+      <c r="AB13" s="573" t="n"/>
+      <c r="AC13" s="573" t="n"/>
+      <c r="AD13" s="573" t="n"/>
+      <c r="AE13" s="573" t="n"/>
+      <c r="AF13" s="573" t="n"/>
+      <c r="AG13" s="573" t="n"/>
+      <c r="AH13" s="573" t="n"/>
+      <c r="AI13" s="573" t="n"/>
+      <c r="AJ13" s="573" t="n"/>
+      <c r="AK13" s="573" t="n"/>
+      <c r="AL13" s="573" t="n"/>
+      <c r="AM13" s="573" t="n"/>
+      <c r="AN13" s="573" t="n"/>
+      <c r="AO13" s="573" t="n"/>
+      <c r="AP13" s="573" t="n"/>
+      <c r="AQ13" s="573" t="n"/>
+      <c r="AR13" s="573" t="n"/>
+      <c r="AS13" s="573" t="n"/>
+      <c r="AT13" s="573" t="n"/>
+      <c r="AU13" s="573" t="n"/>
+      <c r="AV13" s="573" t="n"/>
+      <c r="AW13" s="573" t="n"/>
+      <c r="AX13" s="573" t="n"/>
+      <c r="AY13" s="573" t="n"/>
+      <c r="AZ13" s="573" t="n"/>
+      <c r="BA13" s="573" t="n"/>
+      <c r="BB13" s="573" t="n"/>
+      <c r="BC13" s="573" t="n"/>
+      <c r="BD13" s="573" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="464" t="inlineStr">
+      <c r="A14" s="554" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B14" s="465" t="n"/>
-      <c r="C14" s="465" t="n"/>
-      <c r="D14" s="465" t="n"/>
-      <c r="E14" s="465" t="n"/>
-      <c r="F14" s="465" t="n"/>
-      <c r="G14" s="465" t="n"/>
-      <c r="H14" s="465" t="n"/>
-      <c r="I14" s="465" t="n"/>
-      <c r="J14" s="465" t="n"/>
-      <c r="K14" s="465" t="n"/>
-      <c r="L14" s="465" t="n"/>
-      <c r="M14" s="465" t="n"/>
-      <c r="N14" s="465" t="n"/>
-      <c r="O14" s="465" t="n"/>
-      <c r="P14" s="465" t="n"/>
-      <c r="Q14" s="465" t="n"/>
-      <c r="R14" s="465" t="n"/>
-      <c r="S14" s="465" t="n"/>
-      <c r="T14" s="465" t="n"/>
-      <c r="U14" s="465" t="n"/>
-      <c r="V14" s="465" t="n"/>
-      <c r="W14" s="465" t="n"/>
-      <c r="X14" s="465" t="n"/>
-      <c r="Y14" s="465" t="n"/>
-      <c r="Z14" s="465" t="n"/>
-      <c r="AA14" s="465" t="n"/>
-      <c r="AB14" s="465" t="n"/>
-      <c r="AC14" s="465" t="n"/>
-      <c r="AD14" s="465" t="n"/>
-      <c r="AE14" s="465" t="n"/>
-      <c r="AF14" s="465" t="n"/>
-      <c r="AG14" s="465" t="n"/>
-      <c r="AH14" s="465" t="n"/>
-      <c r="AI14" s="465" t="n"/>
-      <c r="AJ14" s="465" t="n"/>
-      <c r="AK14" s="465" t="n"/>
-      <c r="AL14" s="465" t="n"/>
-      <c r="AM14" s="465" t="n"/>
-      <c r="AN14" s="465" t="n"/>
-      <c r="AO14" s="465" t="n"/>
-      <c r="AP14" s="465" t="n"/>
-      <c r="AQ14" s="465" t="n"/>
-      <c r="AR14" s="465" t="n"/>
-      <c r="AS14" s="465" t="n"/>
-      <c r="AT14" s="465" t="n"/>
-      <c r="AU14" s="465" t="n"/>
-      <c r="AV14" s="465" t="n"/>
-      <c r="AW14" s="465" t="n"/>
-      <c r="AX14" s="465" t="n"/>
-      <c r="AY14" s="465" t="n"/>
-      <c r="AZ14" s="465" t="n"/>
-      <c r="BA14" s="465" t="n"/>
-      <c r="BB14" s="465" t="n"/>
-      <c r="BC14" s="465" t="n"/>
-      <c r="BD14" s="466" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="27" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="27" t="n"/>
+      <c r="R14" s="27" t="n"/>
+      <c r="S14" s="27" t="n"/>
+      <c r="T14" s="27" t="n"/>
+      <c r="U14" s="27" t="n"/>
+      <c r="V14" s="27" t="n"/>
+      <c r="W14" s="27" t="n"/>
+      <c r="X14" s="27" t="n"/>
+      <c r="Y14" s="27" t="n"/>
+      <c r="Z14" s="27" t="n"/>
+      <c r="AA14" s="27" t="n"/>
+      <c r="AB14" s="27" t="n"/>
+      <c r="AC14" s="27" t="n"/>
+      <c r="AD14" s="27" t="n"/>
+      <c r="AE14" s="27" t="n"/>
+      <c r="AF14" s="27" t="n"/>
+      <c r="AG14" s="27" t="n"/>
+      <c r="AH14" s="27" t="n"/>
+      <c r="AI14" s="27" t="n"/>
+      <c r="AJ14" s="27" t="n"/>
+      <c r="AK14" s="27" t="n"/>
+      <c r="AL14" s="27" t="n"/>
+      <c r="AM14" s="27" t="n"/>
+      <c r="AN14" s="27" t="n"/>
+      <c r="AO14" s="27" t="n"/>
+      <c r="AP14" s="27" t="n"/>
+      <c r="AQ14" s="27" t="n"/>
+      <c r="AR14" s="27" t="n"/>
+      <c r="AS14" s="27" t="n"/>
+      <c r="AT14" s="27" t="n"/>
+      <c r="AU14" s="27" t="n"/>
+      <c r="AV14" s="27" t="n"/>
+      <c r="AW14" s="27" t="n"/>
+      <c r="AX14" s="27" t="n"/>
+      <c r="AY14" s="27" t="n"/>
+      <c r="AZ14" s="27" t="n"/>
+      <c r="BA14" s="27" t="n"/>
+      <c r="BB14" s="27" t="n"/>
+      <c r="BC14" s="27" t="n"/>
+      <c r="BD14" s="28" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="483" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="484" t="n"/>
-      <c r="C15" s="484" t="n"/>
-      <c r="D15" s="485" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Check Group</t>
         </is>
       </c>
-      <c r="E15" s="484" t="n"/>
-      <c r="F15" s="484" t="n"/>
-      <c r="G15" s="484" t="n"/>
-      <c r="H15" s="485" t="inlineStr">
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>Characteristic / Requirement</t>
         </is>
       </c>
-      <c r="I15" s="484" t="n"/>
-      <c r="J15" s="484" t="n"/>
-      <c r="K15" s="484" t="n"/>
-      <c r="L15" s="484" t="n"/>
-      <c r="M15" s="484" t="n"/>
-      <c r="N15" s="484" t="n"/>
-      <c r="O15" s="484" t="n"/>
-      <c r="P15" s="484" t="n"/>
-      <c r="Q15" s="484" t="n"/>
-      <c r="R15" s="484" t="n"/>
-      <c r="S15" s="484" t="n"/>
-      <c r="T15" s="484" t="n"/>
-      <c r="U15" s="484" t="n"/>
-      <c r="V15" s="484" t="n"/>
-      <c r="W15" s="484" t="n"/>
-      <c r="X15" s="484" t="n"/>
-      <c r="Y15" s="484" t="n"/>
-      <c r="Z15" s="484" t="n"/>
-      <c r="AA15" s="485" t="inlineStr">
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+      <c r="Y15" s="5" t="n"/>
+      <c r="Z15" s="6" t="n"/>
+      <c r="AA15" s="37" t="inlineStr">
         <is>
           <t>Method / Inspection Basis</t>
         </is>
       </c>
-      <c r="AB15" s="484" t="n"/>
-      <c r="AC15" s="484" t="n"/>
-      <c r="AD15" s="484" t="n"/>
-      <c r="AE15" s="484" t="n"/>
-      <c r="AF15" s="484" t="n"/>
-      <c r="AG15" s="484" t="n"/>
-      <c r="AH15" s="484" t="n"/>
-      <c r="AI15" s="484" t="n"/>
-      <c r="AJ15" s="484" t="n"/>
-      <c r="AK15" s="484" t="n"/>
-      <c r="AL15" s="484" t="n"/>
-      <c r="AM15" s="484" t="n"/>
-      <c r="AN15" s="484" t="n"/>
-      <c r="AO15" s="484" t="n"/>
-      <c r="AP15" s="484" t="n"/>
-      <c r="AQ15" s="484" t="n"/>
-      <c r="AR15" s="485" t="inlineStr">
+      <c r="AB15" s="5" t="n"/>
+      <c r="AC15" s="5" t="n"/>
+      <c r="AD15" s="5" t="n"/>
+      <c r="AE15" s="5" t="n"/>
+      <c r="AF15" s="5" t="n"/>
+      <c r="AG15" s="5" t="n"/>
+      <c r="AH15" s="5" t="n"/>
+      <c r="AI15" s="5" t="n"/>
+      <c r="AJ15" s="5" t="n"/>
+      <c r="AK15" s="5" t="n"/>
+      <c r="AL15" s="5" t="n"/>
+      <c r="AM15" s="5" t="n"/>
+      <c r="AN15" s="5" t="n"/>
+      <c r="AO15" s="5" t="n"/>
+      <c r="AP15" s="5" t="n"/>
+      <c r="AQ15" s="6" t="n"/>
+      <c r="AR15" s="37" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="484" t="n"/>
-      <c r="AT15" s="484" t="n"/>
-      <c r="AU15" s="484" t="n"/>
-      <c r="AV15" s="484" t="n"/>
-      <c r="AW15" s="484" t="n"/>
-      <c r="AX15" s="485" t="inlineStr">
+      <c r="AS15" s="5" t="n"/>
+      <c r="AT15" s="5" t="n"/>
+      <c r="AU15" s="5" t="n"/>
+      <c r="AV15" s="5" t="n"/>
+      <c r="AW15" s="6" t="n"/>
+      <c r="AX15" s="37" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY15" s="484" t="n"/>
-      <c r="AZ15" s="484" t="n"/>
-      <c r="BA15" s="484" t="n"/>
-      <c r="BB15" s="485" t="inlineStr">
+      <c r="AY15" s="5" t="n"/>
+      <c r="AZ15" s="5" t="n"/>
+      <c r="BA15" s="6" t="n"/>
+      <c r="BB15" s="37" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="484" t="n"/>
-      <c r="BD15" s="486" t="n"/>
+      <c r="BC15" s="5" t="n"/>
+      <c r="BD15" s="8" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="487">
+      <c r="A16" s="574">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="468" t="n"/>
-      <c r="C16" s="468" t="n"/>
-      <c r="D16" s="488" t="inlineStr">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="575" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="470" t="n"/>
-      <c r="F16" s="470" t="n"/>
-      <c r="G16" s="470" t="n"/>
-      <c r="H16" s="469" t="n"/>
-      <c r="I16" s="470" t="n"/>
-      <c r="J16" s="470" t="n"/>
-      <c r="K16" s="470" t="n"/>
-      <c r="L16" s="470" t="n"/>
-      <c r="M16" s="470" t="n"/>
-      <c r="N16" s="470" t="n"/>
-      <c r="O16" s="470" t="n"/>
-      <c r="P16" s="470" t="n"/>
-      <c r="Q16" s="470" t="n"/>
-      <c r="R16" s="470" t="n"/>
-      <c r="S16" s="470" t="n"/>
-      <c r="T16" s="470" t="n"/>
-      <c r="U16" s="470" t="n"/>
-      <c r="V16" s="470" t="n"/>
-      <c r="W16" s="470" t="n"/>
-      <c r="X16" s="470" t="n"/>
-      <c r="Y16" s="470" t="n"/>
-      <c r="Z16" s="470" t="n"/>
-      <c r="AA16" s="489" t="n"/>
-      <c r="AB16" s="470" t="n"/>
-      <c r="AC16" s="470" t="n"/>
-      <c r="AD16" s="470" t="n"/>
-      <c r="AE16" s="470" t="n"/>
-      <c r="AF16" s="470" t="n"/>
-      <c r="AG16" s="470" t="n"/>
-      <c r="AH16" s="470" t="n"/>
-      <c r="AI16" s="470" t="n"/>
-      <c r="AJ16" s="470" t="n"/>
-      <c r="AK16" s="470" t="n"/>
-      <c r="AL16" s="470" t="n"/>
-      <c r="AM16" s="470" t="n"/>
-      <c r="AN16" s="470" t="n"/>
-      <c r="AO16" s="470" t="n"/>
-      <c r="AP16" s="470" t="n"/>
-      <c r="AQ16" s="470" t="n"/>
-      <c r="AR16" s="469" t="n"/>
-      <c r="AS16" s="470" t="n"/>
-      <c r="AT16" s="470" t="n"/>
-      <c r="AU16" s="470" t="n"/>
-      <c r="AV16" s="470" t="n"/>
-      <c r="AW16" s="470" t="n"/>
-      <c r="AX16" s="469" t="n"/>
-      <c r="AY16" s="470" t="n"/>
-      <c r="AZ16" s="470" t="n"/>
-      <c r="BA16" s="470" t="n"/>
-      <c r="BB16" s="490" t="n"/>
-      <c r="BC16" s="470" t="n"/>
-      <c r="BD16" s="472" t="n"/>
+      <c r="E16" s="557" t="n"/>
+      <c r="F16" s="557" t="n"/>
+      <c r="G16" s="558" t="n"/>
+      <c r="H16" s="556" t="n"/>
+      <c r="I16" s="557" t="n"/>
+      <c r="J16" s="557" t="n"/>
+      <c r="K16" s="557" t="n"/>
+      <c r="L16" s="557" t="n"/>
+      <c r="M16" s="557" t="n"/>
+      <c r="N16" s="557" t="n"/>
+      <c r="O16" s="557" t="n"/>
+      <c r="P16" s="557" t="n"/>
+      <c r="Q16" s="557" t="n"/>
+      <c r="R16" s="557" t="n"/>
+      <c r="S16" s="557" t="n"/>
+      <c r="T16" s="557" t="n"/>
+      <c r="U16" s="557" t="n"/>
+      <c r="V16" s="557" t="n"/>
+      <c r="W16" s="557" t="n"/>
+      <c r="X16" s="557" t="n"/>
+      <c r="Y16" s="557" t="n"/>
+      <c r="Z16" s="558" t="n"/>
+      <c r="AA16" s="576" t="n"/>
+      <c r="AB16" s="557" t="n"/>
+      <c r="AC16" s="557" t="n"/>
+      <c r="AD16" s="557" t="n"/>
+      <c r="AE16" s="557" t="n"/>
+      <c r="AF16" s="557" t="n"/>
+      <c r="AG16" s="557" t="n"/>
+      <c r="AH16" s="557" t="n"/>
+      <c r="AI16" s="557" t="n"/>
+      <c r="AJ16" s="557" t="n"/>
+      <c r="AK16" s="557" t="n"/>
+      <c r="AL16" s="557" t="n"/>
+      <c r="AM16" s="557" t="n"/>
+      <c r="AN16" s="557" t="n"/>
+      <c r="AO16" s="557" t="n"/>
+      <c r="AP16" s="557" t="n"/>
+      <c r="AQ16" s="558" t="n"/>
+      <c r="AR16" s="556" t="n"/>
+      <c r="AS16" s="557" t="n"/>
+      <c r="AT16" s="557" t="n"/>
+      <c r="AU16" s="557" t="n"/>
+      <c r="AV16" s="557" t="n"/>
+      <c r="AW16" s="558" t="n"/>
+      <c r="AX16" s="556" t="n"/>
+      <c r="AY16" s="557" t="n"/>
+      <c r="AZ16" s="557" t="n"/>
+      <c r="BA16" s="558" t="n"/>
+      <c r="BB16" s="577" t="n"/>
+      <c r="BC16" s="557" t="n"/>
+      <c r="BD16" s="560" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="491">
+      <c r="A17" s="578">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="342" t="n"/>
-      <c r="C17" s="342" t="n"/>
-      <c r="D17" s="492" t="inlineStr">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="579" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="360" t="n"/>
-      <c r="F17" s="360" t="n"/>
-      <c r="G17" s="360" t="n"/>
-      <c r="H17" s="474" t="n"/>
-      <c r="I17" s="360" t="n"/>
-      <c r="J17" s="360" t="n"/>
-      <c r="K17" s="360" t="n"/>
-      <c r="L17" s="360" t="n"/>
-      <c r="M17" s="360" t="n"/>
-      <c r="N17" s="360" t="n"/>
-      <c r="O17" s="360" t="n"/>
-      <c r="P17" s="360" t="n"/>
-      <c r="Q17" s="360" t="n"/>
-      <c r="R17" s="360" t="n"/>
-      <c r="S17" s="360" t="n"/>
-      <c r="T17" s="360" t="n"/>
-      <c r="U17" s="360" t="n"/>
-      <c r="V17" s="360" t="n"/>
-      <c r="W17" s="360" t="n"/>
-      <c r="X17" s="360" t="n"/>
-      <c r="Y17" s="360" t="n"/>
-      <c r="Z17" s="360" t="n"/>
-      <c r="AA17" s="493" t="n"/>
-      <c r="AB17" s="360" t="n"/>
-      <c r="AC17" s="360" t="n"/>
-      <c r="AD17" s="360" t="n"/>
-      <c r="AE17" s="360" t="n"/>
-      <c r="AF17" s="360" t="n"/>
-      <c r="AG17" s="360" t="n"/>
-      <c r="AH17" s="360" t="n"/>
-      <c r="AI17" s="360" t="n"/>
-      <c r="AJ17" s="360" t="n"/>
-      <c r="AK17" s="360" t="n"/>
-      <c r="AL17" s="360" t="n"/>
-      <c r="AM17" s="360" t="n"/>
-      <c r="AN17" s="360" t="n"/>
-      <c r="AO17" s="360" t="n"/>
-      <c r="AP17" s="360" t="n"/>
-      <c r="AQ17" s="360" t="n"/>
-      <c r="AR17" s="474" t="n"/>
-      <c r="AS17" s="360" t="n"/>
-      <c r="AT17" s="360" t="n"/>
-      <c r="AU17" s="360" t="n"/>
-      <c r="AV17" s="360" t="n"/>
-      <c r="AW17" s="360" t="n"/>
-      <c r="AX17" s="474" t="n"/>
-      <c r="AY17" s="360" t="n"/>
-      <c r="AZ17" s="360" t="n"/>
-      <c r="BA17" s="360" t="n"/>
-      <c r="BB17" s="494" t="n"/>
-      <c r="BC17" s="360" t="n"/>
-      <c r="BD17" s="476" t="n"/>
+      <c r="E17" s="563" t="n"/>
+      <c r="F17" s="563" t="n"/>
+      <c r="G17" s="564" t="n"/>
+      <c r="H17" s="562" t="n"/>
+      <c r="I17" s="563" t="n"/>
+      <c r="J17" s="563" t="n"/>
+      <c r="K17" s="563" t="n"/>
+      <c r="L17" s="563" t="n"/>
+      <c r="M17" s="563" t="n"/>
+      <c r="N17" s="563" t="n"/>
+      <c r="O17" s="563" t="n"/>
+      <c r="P17" s="563" t="n"/>
+      <c r="Q17" s="563" t="n"/>
+      <c r="R17" s="563" t="n"/>
+      <c r="S17" s="563" t="n"/>
+      <c r="T17" s="563" t="n"/>
+      <c r="U17" s="563" t="n"/>
+      <c r="V17" s="563" t="n"/>
+      <c r="W17" s="563" t="n"/>
+      <c r="X17" s="563" t="n"/>
+      <c r="Y17" s="563" t="n"/>
+      <c r="Z17" s="564" t="n"/>
+      <c r="AA17" s="580" t="n"/>
+      <c r="AB17" s="563" t="n"/>
+      <c r="AC17" s="563" t="n"/>
+      <c r="AD17" s="563" t="n"/>
+      <c r="AE17" s="563" t="n"/>
+      <c r="AF17" s="563" t="n"/>
+      <c r="AG17" s="563" t="n"/>
+      <c r="AH17" s="563" t="n"/>
+      <c r="AI17" s="563" t="n"/>
+      <c r="AJ17" s="563" t="n"/>
+      <c r="AK17" s="563" t="n"/>
+      <c r="AL17" s="563" t="n"/>
+      <c r="AM17" s="563" t="n"/>
+      <c r="AN17" s="563" t="n"/>
+      <c r="AO17" s="563" t="n"/>
+      <c r="AP17" s="563" t="n"/>
+      <c r="AQ17" s="564" t="n"/>
+      <c r="AR17" s="562" t="n"/>
+      <c r="AS17" s="563" t="n"/>
+      <c r="AT17" s="563" t="n"/>
+      <c r="AU17" s="563" t="n"/>
+      <c r="AV17" s="563" t="n"/>
+      <c r="AW17" s="564" t="n"/>
+      <c r="AX17" s="562" t="n"/>
+      <c r="AY17" s="563" t="n"/>
+      <c r="AZ17" s="563" t="n"/>
+      <c r="BA17" s="564" t="n"/>
+      <c r="BB17" s="581" t="n"/>
+      <c r="BC17" s="563" t="n"/>
+      <c r="BD17" s="566" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="491">
+      <c r="A18" s="578">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="342" t="n"/>
-      <c r="C18" s="342" t="n"/>
-      <c r="D18" s="492" t="inlineStr">
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="579" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="360" t="n"/>
-      <c r="F18" s="360" t="n"/>
-      <c r="G18" s="360" t="n"/>
-      <c r="H18" s="474" t="n"/>
-      <c r="I18" s="360" t="n"/>
-      <c r="J18" s="360" t="n"/>
-      <c r="K18" s="360" t="n"/>
-      <c r="L18" s="360" t="n"/>
-      <c r="M18" s="360" t="n"/>
-      <c r="N18" s="360" t="n"/>
-      <c r="O18" s="360" t="n"/>
-      <c r="P18" s="360" t="n"/>
-      <c r="Q18" s="360" t="n"/>
-      <c r="R18" s="360" t="n"/>
-      <c r="S18" s="360" t="n"/>
-      <c r="T18" s="360" t="n"/>
-      <c r="U18" s="360" t="n"/>
-      <c r="V18" s="360" t="n"/>
-      <c r="W18" s="360" t="n"/>
-      <c r="X18" s="360" t="n"/>
-      <c r="Y18" s="360" t="n"/>
-      <c r="Z18" s="360" t="n"/>
-      <c r="AA18" s="493" t="n"/>
-      <c r="AB18" s="360" t="n"/>
-      <c r="AC18" s="360" t="n"/>
-      <c r="AD18" s="360" t="n"/>
-      <c r="AE18" s="360" t="n"/>
-      <c r="AF18" s="360" t="n"/>
-      <c r="AG18" s="360" t="n"/>
-      <c r="AH18" s="360" t="n"/>
-      <c r="AI18" s="360" t="n"/>
-      <c r="AJ18" s="360" t="n"/>
-      <c r="AK18" s="360" t="n"/>
-      <c r="AL18" s="360" t="n"/>
-      <c r="AM18" s="360" t="n"/>
-      <c r="AN18" s="360" t="n"/>
-      <c r="AO18" s="360" t="n"/>
-      <c r="AP18" s="360" t="n"/>
-      <c r="AQ18" s="360" t="n"/>
-      <c r="AR18" s="474" t="n"/>
-      <c r="AS18" s="360" t="n"/>
-      <c r="AT18" s="360" t="n"/>
-      <c r="AU18" s="360" t="n"/>
-      <c r="AV18" s="360" t="n"/>
-      <c r="AW18" s="360" t="n"/>
-      <c r="AX18" s="474" t="n"/>
-      <c r="AY18" s="360" t="n"/>
-      <c r="AZ18" s="360" t="n"/>
-      <c r="BA18" s="360" t="n"/>
-      <c r="BB18" s="494" t="n"/>
-      <c r="BC18" s="360" t="n"/>
-      <c r="BD18" s="476" t="n"/>
+      <c r="E18" s="563" t="n"/>
+      <c r="F18" s="563" t="n"/>
+      <c r="G18" s="564" t="n"/>
+      <c r="H18" s="562" t="n"/>
+      <c r="I18" s="563" t="n"/>
+      <c r="J18" s="563" t="n"/>
+      <c r="K18" s="563" t="n"/>
+      <c r="L18" s="563" t="n"/>
+      <c r="M18" s="563" t="n"/>
+      <c r="N18" s="563" t="n"/>
+      <c r="O18" s="563" t="n"/>
+      <c r="P18" s="563" t="n"/>
+      <c r="Q18" s="563" t="n"/>
+      <c r="R18" s="563" t="n"/>
+      <c r="S18" s="563" t="n"/>
+      <c r="T18" s="563" t="n"/>
+      <c r="U18" s="563" t="n"/>
+      <c r="V18" s="563" t="n"/>
+      <c r="W18" s="563" t="n"/>
+      <c r="X18" s="563" t="n"/>
+      <c r="Y18" s="563" t="n"/>
+      <c r="Z18" s="564" t="n"/>
+      <c r="AA18" s="580" t="n"/>
+      <c r="AB18" s="563" t="n"/>
+      <c r="AC18" s="563" t="n"/>
+      <c r="AD18" s="563" t="n"/>
+      <c r="AE18" s="563" t="n"/>
+      <c r="AF18" s="563" t="n"/>
+      <c r="AG18" s="563" t="n"/>
+      <c r="AH18" s="563" t="n"/>
+      <c r="AI18" s="563" t="n"/>
+      <c r="AJ18" s="563" t="n"/>
+      <c r="AK18" s="563" t="n"/>
+      <c r="AL18" s="563" t="n"/>
+      <c r="AM18" s="563" t="n"/>
+      <c r="AN18" s="563" t="n"/>
+      <c r="AO18" s="563" t="n"/>
+      <c r="AP18" s="563" t="n"/>
+      <c r="AQ18" s="564" t="n"/>
+      <c r="AR18" s="562" t="n"/>
+      <c r="AS18" s="563" t="n"/>
+      <c r="AT18" s="563" t="n"/>
+      <c r="AU18" s="563" t="n"/>
+      <c r="AV18" s="563" t="n"/>
+      <c r="AW18" s="564" t="n"/>
+      <c r="AX18" s="562" t="n"/>
+      <c r="AY18" s="563" t="n"/>
+      <c r="AZ18" s="563" t="n"/>
+      <c r="BA18" s="564" t="n"/>
+      <c r="BB18" s="581" t="n"/>
+      <c r="BC18" s="563" t="n"/>
+      <c r="BD18" s="566" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="491">
+      <c r="A19" s="578">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="342" t="n"/>
-      <c r="C19" s="342" t="n"/>
-      <c r="D19" s="492" t="inlineStr">
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="579" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="360" t="n"/>
-      <c r="F19" s="360" t="n"/>
-      <c r="G19" s="360" t="n"/>
-      <c r="H19" s="474" t="n"/>
-      <c r="I19" s="360" t="n"/>
-      <c r="J19" s="360" t="n"/>
-      <c r="K19" s="360" t="n"/>
-      <c r="L19" s="360" t="n"/>
-      <c r="M19" s="360" t="n"/>
-      <c r="N19" s="360" t="n"/>
-      <c r="O19" s="360" t="n"/>
-      <c r="P19" s="360" t="n"/>
-      <c r="Q19" s="360" t="n"/>
-      <c r="R19" s="360" t="n"/>
-      <c r="S19" s="360" t="n"/>
-      <c r="T19" s="360" t="n"/>
-      <c r="U19" s="360" t="n"/>
-      <c r="V19" s="360" t="n"/>
-      <c r="W19" s="360" t="n"/>
-      <c r="X19" s="360" t="n"/>
-      <c r="Y19" s="360" t="n"/>
-      <c r="Z19" s="360" t="n"/>
-      <c r="AA19" s="493" t="n"/>
-      <c r="AB19" s="360" t="n"/>
-      <c r="AC19" s="360" t="n"/>
-      <c r="AD19" s="360" t="n"/>
-      <c r="AE19" s="360" t="n"/>
-      <c r="AF19" s="360" t="n"/>
-      <c r="AG19" s="360" t="n"/>
-      <c r="AH19" s="360" t="n"/>
-      <c r="AI19" s="360" t="n"/>
-      <c r="AJ19" s="360" t="n"/>
-      <c r="AK19" s="360" t="n"/>
-      <c r="AL19" s="360" t="n"/>
-      <c r="AM19" s="360" t="n"/>
-      <c r="AN19" s="360" t="n"/>
-      <c r="AO19" s="360" t="n"/>
-      <c r="AP19" s="360" t="n"/>
-      <c r="AQ19" s="360" t="n"/>
-      <c r="AR19" s="474" t="n"/>
-      <c r="AS19" s="360" t="n"/>
-      <c r="AT19" s="360" t="n"/>
-      <c r="AU19" s="360" t="n"/>
-      <c r="AV19" s="360" t="n"/>
-      <c r="AW19" s="360" t="n"/>
-      <c r="AX19" s="474" t="n"/>
-      <c r="AY19" s="360" t="n"/>
-      <c r="AZ19" s="360" t="n"/>
-      <c r="BA19" s="360" t="n"/>
-      <c r="BB19" s="494" t="n"/>
-      <c r="BC19" s="360" t="n"/>
-      <c r="BD19" s="476" t="n"/>
+      <c r="E19" s="563" t="n"/>
+      <c r="F19" s="563" t="n"/>
+      <c r="G19" s="564" t="n"/>
+      <c r="H19" s="562" t="n"/>
+      <c r="I19" s="563" t="n"/>
+      <c r="J19" s="563" t="n"/>
+      <c r="K19" s="563" t="n"/>
+      <c r="L19" s="563" t="n"/>
+      <c r="M19" s="563" t="n"/>
+      <c r="N19" s="563" t="n"/>
+      <c r="O19" s="563" t="n"/>
+      <c r="P19" s="563" t="n"/>
+      <c r="Q19" s="563" t="n"/>
+      <c r="R19" s="563" t="n"/>
+      <c r="S19" s="563" t="n"/>
+      <c r="T19" s="563" t="n"/>
+      <c r="U19" s="563" t="n"/>
+      <c r="V19" s="563" t="n"/>
+      <c r="W19" s="563" t="n"/>
+      <c r="X19" s="563" t="n"/>
+      <c r="Y19" s="563" t="n"/>
+      <c r="Z19" s="564" t="n"/>
+      <c r="AA19" s="580" t="n"/>
+      <c r="AB19" s="563" t="n"/>
+      <c r="AC19" s="563" t="n"/>
+      <c r="AD19" s="563" t="n"/>
+      <c r="AE19" s="563" t="n"/>
+      <c r="AF19" s="563" t="n"/>
+      <c r="AG19" s="563" t="n"/>
+      <c r="AH19" s="563" t="n"/>
+      <c r="AI19" s="563" t="n"/>
+      <c r="AJ19" s="563" t="n"/>
+      <c r="AK19" s="563" t="n"/>
+      <c r="AL19" s="563" t="n"/>
+      <c r="AM19" s="563" t="n"/>
+      <c r="AN19" s="563" t="n"/>
+      <c r="AO19" s="563" t="n"/>
+      <c r="AP19" s="563" t="n"/>
+      <c r="AQ19" s="564" t="n"/>
+      <c r="AR19" s="562" t="n"/>
+      <c r="AS19" s="563" t="n"/>
+      <c r="AT19" s="563" t="n"/>
+      <c r="AU19" s="563" t="n"/>
+      <c r="AV19" s="563" t="n"/>
+      <c r="AW19" s="564" t="n"/>
+      <c r="AX19" s="562" t="n"/>
+      <c r="AY19" s="563" t="n"/>
+      <c r="AZ19" s="563" t="n"/>
+      <c r="BA19" s="564" t="n"/>
+      <c r="BB19" s="581" t="n"/>
+      <c r="BC19" s="563" t="n"/>
+      <c r="BD19" s="566" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="491">
+      <c r="A20" s="578">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="342" t="n"/>
-      <c r="C20" s="342" t="n"/>
-      <c r="D20" s="492" t="inlineStr">
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="579" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="360" t="n"/>
-      <c r="F20" s="360" t="n"/>
-      <c r="G20" s="360" t="n"/>
-      <c r="H20" s="474" t="n"/>
-      <c r="I20" s="360" t="n"/>
-      <c r="J20" s="360" t="n"/>
-      <c r="K20" s="360" t="n"/>
-      <c r="L20" s="360" t="n"/>
-      <c r="M20" s="360" t="n"/>
-      <c r="N20" s="360" t="n"/>
-      <c r="O20" s="360" t="n"/>
-      <c r="P20" s="360" t="n"/>
-      <c r="Q20" s="360" t="n"/>
-      <c r="R20" s="360" t="n"/>
-      <c r="S20" s="360" t="n"/>
-      <c r="T20" s="360" t="n"/>
-      <c r="U20" s="360" t="n"/>
-      <c r="V20" s="360" t="n"/>
-      <c r="W20" s="360" t="n"/>
-      <c r="X20" s="360" t="n"/>
-      <c r="Y20" s="360" t="n"/>
-      <c r="Z20" s="360" t="n"/>
-      <c r="AA20" s="493" t="n"/>
-      <c r="AB20" s="360" t="n"/>
-      <c r="AC20" s="360" t="n"/>
-      <c r="AD20" s="360" t="n"/>
-      <c r="AE20" s="360" t="n"/>
-      <c r="AF20" s="360" t="n"/>
-      <c r="AG20" s="360" t="n"/>
-      <c r="AH20" s="360" t="n"/>
-      <c r="AI20" s="360" t="n"/>
-      <c r="AJ20" s="360" t="n"/>
-      <c r="AK20" s="360" t="n"/>
-      <c r="AL20" s="360" t="n"/>
-      <c r="AM20" s="360" t="n"/>
-      <c r="AN20" s="360" t="n"/>
-      <c r="AO20" s="360" t="n"/>
-      <c r="AP20" s="360" t="n"/>
-      <c r="AQ20" s="360" t="n"/>
-      <c r="AR20" s="474" t="n"/>
-      <c r="AS20" s="360" t="n"/>
-      <c r="AT20" s="360" t="n"/>
-      <c r="AU20" s="360" t="n"/>
-      <c r="AV20" s="360" t="n"/>
-      <c r="AW20" s="360" t="n"/>
-      <c r="AX20" s="474" t="n"/>
-      <c r="AY20" s="360" t="n"/>
-      <c r="AZ20" s="360" t="n"/>
-      <c r="BA20" s="360" t="n"/>
-      <c r="BB20" s="494" t="n"/>
-      <c r="BC20" s="360" t="n"/>
-      <c r="BD20" s="476" t="n"/>
+      <c r="E20" s="563" t="n"/>
+      <c r="F20" s="563" t="n"/>
+      <c r="G20" s="564" t="n"/>
+      <c r="H20" s="562" t="n"/>
+      <c r="I20" s="563" t="n"/>
+      <c r="J20" s="563" t="n"/>
+      <c r="K20" s="563" t="n"/>
+      <c r="L20" s="563" t="n"/>
+      <c r="M20" s="563" t="n"/>
+      <c r="N20" s="563" t="n"/>
+      <c r="O20" s="563" t="n"/>
+      <c r="P20" s="563" t="n"/>
+      <c r="Q20" s="563" t="n"/>
+      <c r="R20" s="563" t="n"/>
+      <c r="S20" s="563" t="n"/>
+      <c r="T20" s="563" t="n"/>
+      <c r="U20" s="563" t="n"/>
+      <c r="V20" s="563" t="n"/>
+      <c r="W20" s="563" t="n"/>
+      <c r="X20" s="563" t="n"/>
+      <c r="Y20" s="563" t="n"/>
+      <c r="Z20" s="564" t="n"/>
+      <c r="AA20" s="580" t="n"/>
+      <c r="AB20" s="563" t="n"/>
+      <c r="AC20" s="563" t="n"/>
+      <c r="AD20" s="563" t="n"/>
+      <c r="AE20" s="563" t="n"/>
+      <c r="AF20" s="563" t="n"/>
+      <c r="AG20" s="563" t="n"/>
+      <c r="AH20" s="563" t="n"/>
+      <c r="AI20" s="563" t="n"/>
+      <c r="AJ20" s="563" t="n"/>
+      <c r="AK20" s="563" t="n"/>
+      <c r="AL20" s="563" t="n"/>
+      <c r="AM20" s="563" t="n"/>
+      <c r="AN20" s="563" t="n"/>
+      <c r="AO20" s="563" t="n"/>
+      <c r="AP20" s="563" t="n"/>
+      <c r="AQ20" s="564" t="n"/>
+      <c r="AR20" s="562" t="n"/>
+      <c r="AS20" s="563" t="n"/>
+      <c r="AT20" s="563" t="n"/>
+      <c r="AU20" s="563" t="n"/>
+      <c r="AV20" s="563" t="n"/>
+      <c r="AW20" s="564" t="n"/>
+      <c r="AX20" s="562" t="n"/>
+      <c r="AY20" s="563" t="n"/>
+      <c r="AZ20" s="563" t="n"/>
+      <c r="BA20" s="564" t="n"/>
+      <c r="BB20" s="581" t="n"/>
+      <c r="BC20" s="563" t="n"/>
+      <c r="BD20" s="566" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="491">
+      <c r="A21" s="578">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="342" t="n"/>
-      <c r="C21" s="342" t="n"/>
-      <c r="D21" s="492" t="inlineStr">
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="579" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="360" t="n"/>
-      <c r="F21" s="360" t="n"/>
-      <c r="G21" s="360" t="n"/>
-      <c r="H21" s="474" t="n"/>
-      <c r="I21" s="360" t="n"/>
-      <c r="J21" s="360" t="n"/>
-      <c r="K21" s="360" t="n"/>
-      <c r="L21" s="360" t="n"/>
-      <c r="M21" s="360" t="n"/>
-      <c r="N21" s="360" t="n"/>
-      <c r="O21" s="360" t="n"/>
-      <c r="P21" s="360" t="n"/>
-      <c r="Q21" s="360" t="n"/>
-      <c r="R21" s="360" t="n"/>
-      <c r="S21" s="360" t="n"/>
-      <c r="T21" s="360" t="n"/>
-      <c r="U21" s="360" t="n"/>
-      <c r="V21" s="360" t="n"/>
-      <c r="W21" s="360" t="n"/>
-      <c r="X21" s="360" t="n"/>
-      <c r="Y21" s="360" t="n"/>
-      <c r="Z21" s="360" t="n"/>
-      <c r="AA21" s="493" t="n"/>
-      <c r="AB21" s="360" t="n"/>
-      <c r="AC21" s="360" t="n"/>
-      <c r="AD21" s="360" t="n"/>
-      <c r="AE21" s="360" t="n"/>
-      <c r="AF21" s="360" t="n"/>
-      <c r="AG21" s="360" t="n"/>
-      <c r="AH21" s="360" t="n"/>
-      <c r="AI21" s="360" t="n"/>
-      <c r="AJ21" s="360" t="n"/>
-      <c r="AK21" s="360" t="n"/>
-      <c r="AL21" s="360" t="n"/>
-      <c r="AM21" s="360" t="n"/>
-      <c r="AN21" s="360" t="n"/>
-      <c r="AO21" s="360" t="n"/>
-      <c r="AP21" s="360" t="n"/>
-      <c r="AQ21" s="360" t="n"/>
-      <c r="AR21" s="474" t="n"/>
-      <c r="AS21" s="360" t="n"/>
-      <c r="AT21" s="360" t="n"/>
-      <c r="AU21" s="360" t="n"/>
-      <c r="AV21" s="360" t="n"/>
-      <c r="AW21" s="360" t="n"/>
-      <c r="AX21" s="474" t="n"/>
-      <c r="AY21" s="360" t="n"/>
-      <c r="AZ21" s="360" t="n"/>
-      <c r="BA21" s="360" t="n"/>
-      <c r="BB21" s="494" t="n"/>
-      <c r="BC21" s="360" t="n"/>
-      <c r="BD21" s="476" t="n"/>
+      <c r="E21" s="563" t="n"/>
+      <c r="F21" s="563" t="n"/>
+      <c r="G21" s="564" t="n"/>
+      <c r="H21" s="562" t="n"/>
+      <c r="I21" s="563" t="n"/>
+      <c r="J21" s="563" t="n"/>
+      <c r="K21" s="563" t="n"/>
+      <c r="L21" s="563" t="n"/>
+      <c r="M21" s="563" t="n"/>
+      <c r="N21" s="563" t="n"/>
+      <c r="O21" s="563" t="n"/>
+      <c r="P21" s="563" t="n"/>
+      <c r="Q21" s="563" t="n"/>
+      <c r="R21" s="563" t="n"/>
+      <c r="S21" s="563" t="n"/>
+      <c r="T21" s="563" t="n"/>
+      <c r="U21" s="563" t="n"/>
+      <c r="V21" s="563" t="n"/>
+      <c r="W21" s="563" t="n"/>
+      <c r="X21" s="563" t="n"/>
+      <c r="Y21" s="563" t="n"/>
+      <c r="Z21" s="564" t="n"/>
+      <c r="AA21" s="580" t="n"/>
+      <c r="AB21" s="563" t="n"/>
+      <c r="AC21" s="563" t="n"/>
+      <c r="AD21" s="563" t="n"/>
+      <c r="AE21" s="563" t="n"/>
+      <c r="AF21" s="563" t="n"/>
+      <c r="AG21" s="563" t="n"/>
+      <c r="AH21" s="563" t="n"/>
+      <c r="AI21" s="563" t="n"/>
+      <c r="AJ21" s="563" t="n"/>
+      <c r="AK21" s="563" t="n"/>
+      <c r="AL21" s="563" t="n"/>
+      <c r="AM21" s="563" t="n"/>
+      <c r="AN21" s="563" t="n"/>
+      <c r="AO21" s="563" t="n"/>
+      <c r="AP21" s="563" t="n"/>
+      <c r="AQ21" s="564" t="n"/>
+      <c r="AR21" s="562" t="n"/>
+      <c r="AS21" s="563" t="n"/>
+      <c r="AT21" s="563" t="n"/>
+      <c r="AU21" s="563" t="n"/>
+      <c r="AV21" s="563" t="n"/>
+      <c r="AW21" s="564" t="n"/>
+      <c r="AX21" s="562" t="n"/>
+      <c r="AY21" s="563" t="n"/>
+      <c r="AZ21" s="563" t="n"/>
+      <c r="BA21" s="564" t="n"/>
+      <c r="BB21" s="581" t="n"/>
+      <c r="BC21" s="563" t="n"/>
+      <c r="BD21" s="566" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="495">
+      <c r="A22" s="582">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="478" t="n"/>
-      <c r="C22" s="478" t="n"/>
-      <c r="D22" s="496" t="inlineStr">
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="583" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="480" t="n"/>
-      <c r="F22" s="480" t="n"/>
-      <c r="G22" s="480" t="n"/>
-      <c r="H22" s="479" t="n"/>
-      <c r="I22" s="480" t="n"/>
-      <c r="J22" s="480" t="n"/>
-      <c r="K22" s="480" t="n"/>
-      <c r="L22" s="480" t="n"/>
-      <c r="M22" s="480" t="n"/>
-      <c r="N22" s="480" t="n"/>
-      <c r="O22" s="480" t="n"/>
-      <c r="P22" s="480" t="n"/>
-      <c r="Q22" s="480" t="n"/>
-      <c r="R22" s="480" t="n"/>
-      <c r="S22" s="480" t="n"/>
-      <c r="T22" s="480" t="n"/>
-      <c r="U22" s="480" t="n"/>
-      <c r="V22" s="480" t="n"/>
-      <c r="W22" s="480" t="n"/>
-      <c r="X22" s="480" t="n"/>
-      <c r="Y22" s="480" t="n"/>
-      <c r="Z22" s="480" t="n"/>
-      <c r="AA22" s="497" t="n"/>
-      <c r="AB22" s="480" t="n"/>
-      <c r="AC22" s="480" t="n"/>
-      <c r="AD22" s="480" t="n"/>
-      <c r="AE22" s="480" t="n"/>
-      <c r="AF22" s="480" t="n"/>
-      <c r="AG22" s="480" t="n"/>
-      <c r="AH22" s="480" t="n"/>
-      <c r="AI22" s="480" t="n"/>
-      <c r="AJ22" s="480" t="n"/>
-      <c r="AK22" s="480" t="n"/>
-      <c r="AL22" s="480" t="n"/>
-      <c r="AM22" s="480" t="n"/>
-      <c r="AN22" s="480" t="n"/>
-      <c r="AO22" s="480" t="n"/>
-      <c r="AP22" s="480" t="n"/>
-      <c r="AQ22" s="480" t="n"/>
-      <c r="AR22" s="479" t="n"/>
-      <c r="AS22" s="480" t="n"/>
-      <c r="AT22" s="480" t="n"/>
-      <c r="AU22" s="480" t="n"/>
-      <c r="AV22" s="480" t="n"/>
-      <c r="AW22" s="480" t="n"/>
-      <c r="AX22" s="479" t="n"/>
-      <c r="AY22" s="480" t="n"/>
-      <c r="AZ22" s="480" t="n"/>
-      <c r="BA22" s="480" t="n"/>
-      <c r="BB22" s="498" t="n"/>
-      <c r="BC22" s="480" t="n"/>
-      <c r="BD22" s="482" t="n"/>
+      <c r="E22" s="569" t="n"/>
+      <c r="F22" s="569" t="n"/>
+      <c r="G22" s="570" t="n"/>
+      <c r="H22" s="568" t="n"/>
+      <c r="I22" s="569" t="n"/>
+      <c r="J22" s="569" t="n"/>
+      <c r="K22" s="569" t="n"/>
+      <c r="L22" s="569" t="n"/>
+      <c r="M22" s="569" t="n"/>
+      <c r="N22" s="569" t="n"/>
+      <c r="O22" s="569" t="n"/>
+      <c r="P22" s="569" t="n"/>
+      <c r="Q22" s="569" t="n"/>
+      <c r="R22" s="569" t="n"/>
+      <c r="S22" s="569" t="n"/>
+      <c r="T22" s="569" t="n"/>
+      <c r="U22" s="569" t="n"/>
+      <c r="V22" s="569" t="n"/>
+      <c r="W22" s="569" t="n"/>
+      <c r="X22" s="569" t="n"/>
+      <c r="Y22" s="569" t="n"/>
+      <c r="Z22" s="570" t="n"/>
+      <c r="AA22" s="584" t="n"/>
+      <c r="AB22" s="569" t="n"/>
+      <c r="AC22" s="569" t="n"/>
+      <c r="AD22" s="569" t="n"/>
+      <c r="AE22" s="569" t="n"/>
+      <c r="AF22" s="569" t="n"/>
+      <c r="AG22" s="569" t="n"/>
+      <c r="AH22" s="569" t="n"/>
+      <c r="AI22" s="569" t="n"/>
+      <c r="AJ22" s="569" t="n"/>
+      <c r="AK22" s="569" t="n"/>
+      <c r="AL22" s="569" t="n"/>
+      <c r="AM22" s="569" t="n"/>
+      <c r="AN22" s="569" t="n"/>
+      <c r="AO22" s="569" t="n"/>
+      <c r="AP22" s="569" t="n"/>
+      <c r="AQ22" s="570" t="n"/>
+      <c r="AR22" s="568" t="n"/>
+      <c r="AS22" s="569" t="n"/>
+      <c r="AT22" s="569" t="n"/>
+      <c r="AU22" s="569" t="n"/>
+      <c r="AV22" s="569" t="n"/>
+      <c r="AW22" s="570" t="n"/>
+      <c r="AX22" s="568" t="n"/>
+      <c r="AY22" s="569" t="n"/>
+      <c r="AZ22" s="569" t="n"/>
+      <c r="BA22" s="570" t="n"/>
+      <c r="BB22" s="585" t="n"/>
+      <c r="BC22" s="569" t="n"/>
+      <c r="BD22" s="572" t="n"/>
     </row>
     <row r="23" ht="3" customHeight="1">
-      <c r="A23" s="373" t="n"/>
-      <c r="B23" s="351" t="n"/>
-      <c r="C23" s="351" t="n"/>
-      <c r="D23" s="374" t="n"/>
-      <c r="E23" s="351" t="n"/>
-      <c r="F23" s="351" t="n"/>
-      <c r="G23" s="351" t="n"/>
-      <c r="H23" s="375" t="n"/>
-      <c r="I23" s="351" t="n"/>
-      <c r="J23" s="351" t="n"/>
-      <c r="K23" s="351" t="n"/>
-      <c r="L23" s="351" t="n"/>
-      <c r="M23" s="351" t="n"/>
-      <c r="N23" s="351" t="n"/>
-      <c r="O23" s="351" t="n"/>
-      <c r="P23" s="351" t="n"/>
-      <c r="Q23" s="351" t="n"/>
-      <c r="R23" s="351" t="n"/>
-      <c r="S23" s="351" t="n"/>
-      <c r="T23" s="351" t="n"/>
-      <c r="U23" s="351" t="n"/>
-      <c r="V23" s="351" t="n"/>
-      <c r="W23" s="351" t="n"/>
-      <c r="X23" s="351" t="n"/>
-      <c r="Y23" s="351" t="n"/>
-      <c r="Z23" s="351" t="n"/>
-      <c r="AA23" s="376" t="n"/>
-      <c r="AB23" s="351" t="n"/>
-      <c r="AC23" s="351" t="n"/>
-      <c r="AD23" s="351" t="n"/>
-      <c r="AE23" s="351" t="n"/>
-      <c r="AF23" s="351" t="n"/>
-      <c r="AG23" s="351" t="n"/>
-      <c r="AH23" s="351" t="n"/>
-      <c r="AI23" s="351" t="n"/>
-      <c r="AJ23" s="351" t="n"/>
-      <c r="AK23" s="351" t="n"/>
-      <c r="AL23" s="351" t="n"/>
-      <c r="AM23" s="351" t="n"/>
-      <c r="AN23" s="351" t="n"/>
-      <c r="AO23" s="351" t="n"/>
-      <c r="AP23" s="351" t="n"/>
-      <c r="AQ23" s="351" t="n"/>
-      <c r="AR23" s="377" t="n"/>
-      <c r="AS23" s="351" t="n"/>
-      <c r="AT23" s="351" t="n"/>
-      <c r="AU23" s="351" t="n"/>
-      <c r="AV23" s="351" t="n"/>
-      <c r="AW23" s="351" t="n"/>
-      <c r="AX23" s="377" t="n"/>
-      <c r="AY23" s="351" t="n"/>
-      <c r="AZ23" s="351" t="n"/>
-      <c r="BA23" s="351" t="n"/>
-      <c r="BB23" s="378" t="n"/>
-      <c r="BC23" s="351" t="n"/>
-      <c r="BD23" s="351" t="n"/>
+      <c r="A23" s="586" t="n"/>
+      <c r="B23" s="573" t="n"/>
+      <c r="C23" s="573" t="n"/>
+      <c r="D23" s="587" t="n"/>
+      <c r="E23" s="573" t="n"/>
+      <c r="F23" s="573" t="n"/>
+      <c r="G23" s="573" t="n"/>
+      <c r="H23" s="588" t="n"/>
+      <c r="I23" s="573" t="n"/>
+      <c r="J23" s="573" t="n"/>
+      <c r="K23" s="573" t="n"/>
+      <c r="L23" s="573" t="n"/>
+      <c r="M23" s="573" t="n"/>
+      <c r="N23" s="573" t="n"/>
+      <c r="O23" s="573" t="n"/>
+      <c r="P23" s="573" t="n"/>
+      <c r="Q23" s="573" t="n"/>
+      <c r="R23" s="573" t="n"/>
+      <c r="S23" s="573" t="n"/>
+      <c r="T23" s="573" t="n"/>
+      <c r="U23" s="573" t="n"/>
+      <c r="V23" s="573" t="n"/>
+      <c r="W23" s="573" t="n"/>
+      <c r="X23" s="573" t="n"/>
+      <c r="Y23" s="573" t="n"/>
+      <c r="Z23" s="573" t="n"/>
+      <c r="AA23" s="589" t="n"/>
+      <c r="AB23" s="573" t="n"/>
+      <c r="AC23" s="573" t="n"/>
+      <c r="AD23" s="573" t="n"/>
+      <c r="AE23" s="573" t="n"/>
+      <c r="AF23" s="573" t="n"/>
+      <c r="AG23" s="573" t="n"/>
+      <c r="AH23" s="573" t="n"/>
+      <c r="AI23" s="573" t="n"/>
+      <c r="AJ23" s="573" t="n"/>
+      <c r="AK23" s="573" t="n"/>
+      <c r="AL23" s="573" t="n"/>
+      <c r="AM23" s="573" t="n"/>
+      <c r="AN23" s="573" t="n"/>
+      <c r="AO23" s="573" t="n"/>
+      <c r="AP23" s="573" t="n"/>
+      <c r="AQ23" s="573" t="n"/>
+      <c r="AR23" s="590" t="n"/>
+      <c r="AS23" s="573" t="n"/>
+      <c r="AT23" s="573" t="n"/>
+      <c r="AU23" s="573" t="n"/>
+      <c r="AV23" s="573" t="n"/>
+      <c r="AW23" s="573" t="n"/>
+      <c r="AX23" s="590" t="n"/>
+      <c r="AY23" s="573" t="n"/>
+      <c r="AZ23" s="573" t="n"/>
+      <c r="BA23" s="573" t="n"/>
+      <c r="BB23" s="591" t="n"/>
+      <c r="BC23" s="573" t="n"/>
+      <c r="BD23" s="573" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="464" t="inlineStr">
+      <c r="A24" s="554" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B24" s="465" t="n"/>
-      <c r="C24" s="465" t="n"/>
-      <c r="D24" s="465" t="n"/>
-      <c r="E24" s="465" t="n"/>
-      <c r="F24" s="465" t="n"/>
-      <c r="G24" s="465" t="n"/>
-      <c r="H24" s="465" t="n"/>
-      <c r="I24" s="465" t="n"/>
-      <c r="J24" s="465" t="n"/>
-      <c r="K24" s="465" t="n"/>
-      <c r="L24" s="465" t="n"/>
-      <c r="M24" s="465" t="n"/>
-      <c r="N24" s="465" t="n"/>
-      <c r="O24" s="465" t="n"/>
-      <c r="P24" s="465" t="n"/>
-      <c r="Q24" s="465" t="n"/>
-      <c r="R24" s="465" t="n"/>
-      <c r="S24" s="465" t="n"/>
-      <c r="T24" s="465" t="n"/>
-      <c r="U24" s="465" t="n"/>
-      <c r="V24" s="465" t="n"/>
-      <c r="W24" s="465" t="n"/>
-      <c r="X24" s="465" t="n"/>
-      <c r="Y24" s="465" t="n"/>
-      <c r="Z24" s="465" t="n"/>
-      <c r="AA24" s="465" t="n"/>
-      <c r="AB24" s="465" t="n"/>
-      <c r="AC24" s="465" t="n"/>
-      <c r="AD24" s="465" t="n"/>
-      <c r="AE24" s="465" t="n"/>
-      <c r="AF24" s="465" t="n"/>
-      <c r="AG24" s="465" t="n"/>
-      <c r="AH24" s="465" t="n"/>
-      <c r="AI24" s="465" t="n"/>
-      <c r="AJ24" s="465" t="n"/>
-      <c r="AK24" s="465" t="n"/>
-      <c r="AL24" s="465" t="n"/>
-      <c r="AM24" s="465" t="n"/>
-      <c r="AN24" s="465" t="n"/>
-      <c r="AO24" s="465" t="n"/>
-      <c r="AP24" s="465" t="n"/>
-      <c r="AQ24" s="465" t="n"/>
-      <c r="AR24" s="465" t="n"/>
-      <c r="AS24" s="465" t="n"/>
-      <c r="AT24" s="465" t="n"/>
-      <c r="AU24" s="465" t="n"/>
-      <c r="AV24" s="465" t="n"/>
-      <c r="AW24" s="465" t="n"/>
-      <c r="AX24" s="465" t="n"/>
-      <c r="AY24" s="465" t="n"/>
-      <c r="AZ24" s="465" t="n"/>
-      <c r="BA24" s="465" t="n"/>
-      <c r="BB24" s="465" t="n"/>
-      <c r="BC24" s="465" t="n"/>
-      <c r="BD24" s="466" t="n"/>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="n"/>
+      <c r="H24" s="27" t="n"/>
+      <c r="I24" s="27" t="n"/>
+      <c r="J24" s="27" t="n"/>
+      <c r="K24" s="27" t="n"/>
+      <c r="L24" s="27" t="n"/>
+      <c r="M24" s="27" t="n"/>
+      <c r="N24" s="27" t="n"/>
+      <c r="O24" s="27" t="n"/>
+      <c r="P24" s="27" t="n"/>
+      <c r="Q24" s="27" t="n"/>
+      <c r="R24" s="27" t="n"/>
+      <c r="S24" s="27" t="n"/>
+      <c r="T24" s="27" t="n"/>
+      <c r="U24" s="27" t="n"/>
+      <c r="V24" s="27" t="n"/>
+      <c r="W24" s="27" t="n"/>
+      <c r="X24" s="27" t="n"/>
+      <c r="Y24" s="27" t="n"/>
+      <c r="Z24" s="27" t="n"/>
+      <c r="AA24" s="27" t="n"/>
+      <c r="AB24" s="27" t="n"/>
+      <c r="AC24" s="27" t="n"/>
+      <c r="AD24" s="27" t="n"/>
+      <c r="AE24" s="27" t="n"/>
+      <c r="AF24" s="27" t="n"/>
+      <c r="AG24" s="27" t="n"/>
+      <c r="AH24" s="27" t="n"/>
+      <c r="AI24" s="27" t="n"/>
+      <c r="AJ24" s="27" t="n"/>
+      <c r="AK24" s="27" t="n"/>
+      <c r="AL24" s="27" t="n"/>
+      <c r="AM24" s="27" t="n"/>
+      <c r="AN24" s="27" t="n"/>
+      <c r="AO24" s="27" t="n"/>
+      <c r="AP24" s="27" t="n"/>
+      <c r="AQ24" s="27" t="n"/>
+      <c r="AR24" s="27" t="n"/>
+      <c r="AS24" s="27" t="n"/>
+      <c r="AT24" s="27" t="n"/>
+      <c r="AU24" s="27" t="n"/>
+      <c r="AV24" s="27" t="n"/>
+      <c r="AW24" s="27" t="n"/>
+      <c r="AX24" s="27" t="n"/>
+      <c r="AY24" s="27" t="n"/>
+      <c r="AZ24" s="27" t="n"/>
+      <c r="BA24" s="27" t="n"/>
+      <c r="BB24" s="27" t="n"/>
+      <c r="BC24" s="27" t="n"/>
+      <c r="BD24" s="28" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="467" t="inlineStr">
+      <c r="A25" s="555" t="inlineStr">
         <is>
           <t>Disposition / Release Decision</t>
         </is>
       </c>
-      <c r="B25" s="468" t="n"/>
-      <c r="C25" s="468" t="n"/>
-      <c r="D25" s="468" t="n"/>
-      <c r="E25" s="468" t="n"/>
-      <c r="F25" s="468" t="n"/>
-      <c r="G25" s="468" t="n"/>
-      <c r="H25" s="468" t="n"/>
-      <c r="I25" s="468" t="n"/>
-      <c r="J25" s="468" t="n"/>
-      <c r="K25" s="469" t="n"/>
-      <c r="L25" s="470" t="n"/>
-      <c r="M25" s="470" t="n"/>
-      <c r="N25" s="470" t="n"/>
-      <c r="O25" s="470" t="n"/>
-      <c r="P25" s="470" t="n"/>
-      <c r="Q25" s="470" t="n"/>
-      <c r="R25" s="470" t="n"/>
-      <c r="S25" s="470" t="n"/>
-      <c r="T25" s="470" t="n"/>
-      <c r="U25" s="470" t="n"/>
-      <c r="V25" s="470" t="n"/>
-      <c r="W25" s="470" t="n"/>
-      <c r="X25" s="470" t="n"/>
-      <c r="Y25" s="470" t="n"/>
-      <c r="Z25" s="470" t="n"/>
-      <c r="AA25" s="470" t="n"/>
-      <c r="AB25" s="470" t="n"/>
-      <c r="AC25" s="471" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="556" t="n"/>
+      <c r="L25" s="557" t="n"/>
+      <c r="M25" s="557" t="n"/>
+      <c r="N25" s="557" t="n"/>
+      <c r="O25" s="557" t="n"/>
+      <c r="P25" s="557" t="n"/>
+      <c r="Q25" s="557" t="n"/>
+      <c r="R25" s="557" t="n"/>
+      <c r="S25" s="557" t="n"/>
+      <c r="T25" s="557" t="n"/>
+      <c r="U25" s="557" t="n"/>
+      <c r="V25" s="557" t="n"/>
+      <c r="W25" s="557" t="n"/>
+      <c r="X25" s="557" t="n"/>
+      <c r="Y25" s="557" t="n"/>
+      <c r="Z25" s="557" t="n"/>
+      <c r="AA25" s="557" t="n"/>
+      <c r="AB25" s="558" t="n"/>
+      <c r="AC25" s="559" t="inlineStr">
         <is>
           <t>Linked NCR / Concession</t>
         </is>
       </c>
-      <c r="AD25" s="468" t="n"/>
-      <c r="AE25" s="468" t="n"/>
-      <c r="AF25" s="468" t="n"/>
-      <c r="AG25" s="468" t="n"/>
-      <c r="AH25" s="468" t="n"/>
-      <c r="AI25" s="468" t="n"/>
-      <c r="AJ25" s="468" t="n"/>
-      <c r="AK25" s="468" t="n"/>
-      <c r="AL25" s="468" t="n"/>
-      <c r="AM25" s="469" t="n"/>
-      <c r="AN25" s="470" t="n"/>
-      <c r="AO25" s="470" t="n"/>
-      <c r="AP25" s="470" t="n"/>
-      <c r="AQ25" s="470" t="n"/>
-      <c r="AR25" s="470" t="n"/>
-      <c r="AS25" s="470" t="n"/>
-      <c r="AT25" s="470" t="n"/>
-      <c r="AU25" s="470" t="n"/>
-      <c r="AV25" s="470" t="n"/>
-      <c r="AW25" s="470" t="n"/>
-      <c r="AX25" s="470" t="n"/>
-      <c r="AY25" s="470" t="n"/>
-      <c r="AZ25" s="470" t="n"/>
-      <c r="BA25" s="470" t="n"/>
-      <c r="BB25" s="470" t="n"/>
-      <c r="BC25" s="470" t="n"/>
-      <c r="BD25" s="472" t="n"/>
+      <c r="AD25" s="5" t="n"/>
+      <c r="AE25" s="5" t="n"/>
+      <c r="AF25" s="5" t="n"/>
+      <c r="AG25" s="5" t="n"/>
+      <c r="AH25" s="5" t="n"/>
+      <c r="AI25" s="5" t="n"/>
+      <c r="AJ25" s="5" t="n"/>
+      <c r="AK25" s="5" t="n"/>
+      <c r="AL25" s="6" t="n"/>
+      <c r="AM25" s="556" t="n"/>
+      <c r="AN25" s="557" t="n"/>
+      <c r="AO25" s="557" t="n"/>
+      <c r="AP25" s="557" t="n"/>
+      <c r="AQ25" s="557" t="n"/>
+      <c r="AR25" s="557" t="n"/>
+      <c r="AS25" s="557" t="n"/>
+      <c r="AT25" s="557" t="n"/>
+      <c r="AU25" s="557" t="n"/>
+      <c r="AV25" s="557" t="n"/>
+      <c r="AW25" s="557" t="n"/>
+      <c r="AX25" s="557" t="n"/>
+      <c r="AY25" s="557" t="n"/>
+      <c r="AZ25" s="557" t="n"/>
+      <c r="BA25" s="557" t="n"/>
+      <c r="BB25" s="557" t="n"/>
+      <c r="BC25" s="557" t="n"/>
+      <c r="BD25" s="560" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="473" t="inlineStr">
+      <c r="A26" s="561" t="inlineStr">
         <is>
           <t>Cleanliness / Packaging Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="342" t="n"/>
-      <c r="C26" s="342" t="n"/>
-      <c r="D26" s="342" t="n"/>
-      <c r="E26" s="342" t="n"/>
-      <c r="F26" s="342" t="n"/>
-      <c r="G26" s="342" t="n"/>
-      <c r="H26" s="342" t="n"/>
-      <c r="I26" s="342" t="n"/>
-      <c r="J26" s="342" t="n"/>
-      <c r="K26" s="474" t="n"/>
-      <c r="L26" s="360" t="n"/>
-      <c r="M26" s="360" t="n"/>
-      <c r="N26" s="360" t="n"/>
-      <c r="O26" s="360" t="n"/>
-      <c r="P26" s="360" t="n"/>
-      <c r="Q26" s="360" t="n"/>
-      <c r="R26" s="360" t="n"/>
-      <c r="S26" s="360" t="n"/>
-      <c r="T26" s="360" t="n"/>
-      <c r="U26" s="360" t="n"/>
-      <c r="V26" s="360" t="n"/>
-      <c r="W26" s="360" t="n"/>
-      <c r="X26" s="360" t="n"/>
-      <c r="Y26" s="360" t="n"/>
-      <c r="Z26" s="360" t="n"/>
-      <c r="AA26" s="360" t="n"/>
-      <c r="AB26" s="360" t="n"/>
-      <c r="AC26" s="475" t="inlineStr">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="562" t="n"/>
+      <c r="L26" s="563" t="n"/>
+      <c r="M26" s="563" t="n"/>
+      <c r="N26" s="563" t="n"/>
+      <c r="O26" s="563" t="n"/>
+      <c r="P26" s="563" t="n"/>
+      <c r="Q26" s="563" t="n"/>
+      <c r="R26" s="563" t="n"/>
+      <c r="S26" s="563" t="n"/>
+      <c r="T26" s="563" t="n"/>
+      <c r="U26" s="563" t="n"/>
+      <c r="V26" s="563" t="n"/>
+      <c r="W26" s="563" t="n"/>
+      <c r="X26" s="563" t="n"/>
+      <c r="Y26" s="563" t="n"/>
+      <c r="Z26" s="563" t="n"/>
+      <c r="AA26" s="563" t="n"/>
+      <c r="AB26" s="564" t="n"/>
+      <c r="AC26" s="565" t="inlineStr">
         <is>
           <t>Label / Doc Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="AD26" s="342" t="n"/>
-      <c r="AE26" s="342" t="n"/>
-      <c r="AF26" s="342" t="n"/>
-      <c r="AG26" s="342" t="n"/>
-      <c r="AH26" s="342" t="n"/>
-      <c r="AI26" s="342" t="n"/>
-      <c r="AJ26" s="342" t="n"/>
-      <c r="AK26" s="342" t="n"/>
-      <c r="AL26" s="342" t="n"/>
-      <c r="AM26" s="474" t="n"/>
-      <c r="AN26" s="360" t="n"/>
-      <c r="AO26" s="360" t="n"/>
-      <c r="AP26" s="360" t="n"/>
-      <c r="AQ26" s="360" t="n"/>
-      <c r="AR26" s="360" t="n"/>
-      <c r="AS26" s="360" t="n"/>
-      <c r="AT26" s="360" t="n"/>
-      <c r="AU26" s="360" t="n"/>
-      <c r="AV26" s="360" t="n"/>
-      <c r="AW26" s="360" t="n"/>
-      <c r="AX26" s="360" t="n"/>
-      <c r="AY26" s="360" t="n"/>
-      <c r="AZ26" s="360" t="n"/>
-      <c r="BA26" s="360" t="n"/>
-      <c r="BB26" s="360" t="n"/>
-      <c r="BC26" s="360" t="n"/>
-      <c r="BD26" s="476" t="n"/>
+      <c r="AD26" s="12" t="n"/>
+      <c r="AE26" s="12" t="n"/>
+      <c r="AF26" s="12" t="n"/>
+      <c r="AG26" s="12" t="n"/>
+      <c r="AH26" s="12" t="n"/>
+      <c r="AI26" s="12" t="n"/>
+      <c r="AJ26" s="12" t="n"/>
+      <c r="AK26" s="12" t="n"/>
+      <c r="AL26" s="13" t="n"/>
+      <c r="AM26" s="562" t="n"/>
+      <c r="AN26" s="563" t="n"/>
+      <c r="AO26" s="563" t="n"/>
+      <c r="AP26" s="563" t="n"/>
+      <c r="AQ26" s="563" t="n"/>
+      <c r="AR26" s="563" t="n"/>
+      <c r="AS26" s="563" t="n"/>
+      <c r="AT26" s="563" t="n"/>
+      <c r="AU26" s="563" t="n"/>
+      <c r="AV26" s="563" t="n"/>
+      <c r="AW26" s="563" t="n"/>
+      <c r="AX26" s="563" t="n"/>
+      <c r="AY26" s="563" t="n"/>
+      <c r="AZ26" s="563" t="n"/>
+      <c r="BA26" s="563" t="n"/>
+      <c r="BB26" s="563" t="n"/>
+      <c r="BC26" s="563" t="n"/>
+      <c r="BD26" s="566" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="477" t="inlineStr">
+      <c r="A27" s="567" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="B27" s="478" t="n"/>
-      <c r="C27" s="478" t="n"/>
-      <c r="D27" s="478" t="n"/>
-      <c r="E27" s="478" t="n"/>
-      <c r="F27" s="478" t="n"/>
-      <c r="G27" s="478" t="n"/>
-      <c r="H27" s="478" t="n"/>
-      <c r="I27" s="478" t="n"/>
-      <c r="J27" s="478" t="n"/>
-      <c r="K27" s="479" t="n"/>
-      <c r="L27" s="480" t="n"/>
-      <c r="M27" s="480" t="n"/>
-      <c r="N27" s="480" t="n"/>
-      <c r="O27" s="480" t="n"/>
-      <c r="P27" s="480" t="n"/>
-      <c r="Q27" s="480" t="n"/>
-      <c r="R27" s="480" t="n"/>
-      <c r="S27" s="480" t="n"/>
-      <c r="T27" s="480" t="n"/>
-      <c r="U27" s="480" t="n"/>
-      <c r="V27" s="480" t="n"/>
-      <c r="W27" s="480" t="n"/>
-      <c r="X27" s="480" t="n"/>
-      <c r="Y27" s="480" t="n"/>
-      <c r="Z27" s="480" t="n"/>
-      <c r="AA27" s="480" t="n"/>
-      <c r="AB27" s="480" t="n"/>
-      <c r="AC27" s="481" t="inlineStr">
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="568" t="n"/>
+      <c r="L27" s="569" t="n"/>
+      <c r="M27" s="569" t="n"/>
+      <c r="N27" s="569" t="n"/>
+      <c r="O27" s="569" t="n"/>
+      <c r="P27" s="569" t="n"/>
+      <c r="Q27" s="569" t="n"/>
+      <c r="R27" s="569" t="n"/>
+      <c r="S27" s="569" t="n"/>
+      <c r="T27" s="569" t="n"/>
+      <c r="U27" s="569" t="n"/>
+      <c r="V27" s="569" t="n"/>
+      <c r="W27" s="569" t="n"/>
+      <c r="X27" s="569" t="n"/>
+      <c r="Y27" s="569" t="n"/>
+      <c r="Z27" s="569" t="n"/>
+      <c r="AA27" s="569" t="n"/>
+      <c r="AB27" s="570" t="n"/>
+      <c r="AC27" s="571" t="inlineStr">
         <is>
           <t>Closeout Status</t>
         </is>
       </c>
-      <c r="AD27" s="478" t="n"/>
-      <c r="AE27" s="478" t="n"/>
-      <c r="AF27" s="478" t="n"/>
-      <c r="AG27" s="478" t="n"/>
-      <c r="AH27" s="478" t="n"/>
-      <c r="AI27" s="478" t="n"/>
-      <c r="AJ27" s="478" t="n"/>
-      <c r="AK27" s="478" t="n"/>
-      <c r="AL27" s="478" t="n"/>
-      <c r="AM27" s="479" t="n"/>
-      <c r="AN27" s="480" t="n"/>
-      <c r="AO27" s="480" t="n"/>
-      <c r="AP27" s="480" t="n"/>
-      <c r="AQ27" s="480" t="n"/>
-      <c r="AR27" s="480" t="n"/>
-      <c r="AS27" s="480" t="n"/>
-      <c r="AT27" s="480" t="n"/>
-      <c r="AU27" s="480" t="n"/>
-      <c r="AV27" s="480" t="n"/>
-      <c r="AW27" s="480" t="n"/>
-      <c r="AX27" s="480" t="n"/>
-      <c r="AY27" s="480" t="n"/>
-      <c r="AZ27" s="480" t="n"/>
-      <c r="BA27" s="480" t="n"/>
-      <c r="BB27" s="480" t="n"/>
-      <c r="BC27" s="480" t="n"/>
-      <c r="BD27" s="482" t="n"/>
+      <c r="AD27" s="19" t="n"/>
+      <c r="AE27" s="19" t="n"/>
+      <c r="AF27" s="19" t="n"/>
+      <c r="AG27" s="19" t="n"/>
+      <c r="AH27" s="19" t="n"/>
+      <c r="AI27" s="19" t="n"/>
+      <c r="AJ27" s="19" t="n"/>
+      <c r="AK27" s="19" t="n"/>
+      <c r="AL27" s="22" t="n"/>
+      <c r="AM27" s="568" t="n"/>
+      <c r="AN27" s="569" t="n"/>
+      <c r="AO27" s="569" t="n"/>
+      <c r="AP27" s="569" t="n"/>
+      <c r="AQ27" s="569" t="n"/>
+      <c r="AR27" s="569" t="n"/>
+      <c r="AS27" s="569" t="n"/>
+      <c r="AT27" s="569" t="n"/>
+      <c r="AU27" s="569" t="n"/>
+      <c r="AV27" s="569" t="n"/>
+      <c r="AW27" s="569" t="n"/>
+      <c r="AX27" s="569" t="n"/>
+      <c r="AY27" s="569" t="n"/>
+      <c r="AZ27" s="569" t="n"/>
+      <c r="BA27" s="569" t="n"/>
+      <c r="BB27" s="569" t="n"/>
+      <c r="BC27" s="569" t="n"/>
+      <c r="BD27" s="572" t="n"/>
     </row>
     <row r="28" ht="3" customHeight="1">
-      <c r="A28" s="373" t="n"/>
-      <c r="B28" s="351" t="n"/>
-      <c r="C28" s="351" t="n"/>
-      <c r="D28" s="374" t="n"/>
-      <c r="E28" s="351" t="n"/>
-      <c r="F28" s="351" t="n"/>
-      <c r="G28" s="351" t="n"/>
-      <c r="H28" s="375" t="n"/>
-      <c r="I28" s="351" t="n"/>
-      <c r="J28" s="351" t="n"/>
-      <c r="K28" s="351" t="n"/>
-      <c r="L28" s="351" t="n"/>
-      <c r="M28" s="351" t="n"/>
-      <c r="N28" s="351" t="n"/>
-      <c r="O28" s="351" t="n"/>
-      <c r="P28" s="351" t="n"/>
-      <c r="Q28" s="351" t="n"/>
-      <c r="R28" s="351" t="n"/>
-      <c r="S28" s="351" t="n"/>
-      <c r="T28" s="351" t="n"/>
-      <c r="U28" s="351" t="n"/>
-      <c r="V28" s="351" t="n"/>
-      <c r="W28" s="351" t="n"/>
-      <c r="X28" s="351" t="n"/>
-      <c r="Y28" s="351" t="n"/>
-      <c r="Z28" s="351" t="n"/>
-      <c r="AA28" s="376" t="n"/>
-      <c r="AB28" s="351" t="n"/>
-      <c r="AC28" s="351" t="n"/>
-      <c r="AD28" s="351" t="n"/>
-      <c r="AE28" s="351" t="n"/>
-      <c r="AF28" s="351" t="n"/>
-      <c r="AG28" s="351" t="n"/>
-      <c r="AH28" s="351" t="n"/>
-      <c r="AI28" s="351" t="n"/>
-      <c r="AJ28" s="351" t="n"/>
-      <c r="AK28" s="351" t="n"/>
-      <c r="AL28" s="351" t="n"/>
-      <c r="AM28" s="351" t="n"/>
-      <c r="AN28" s="351" t="n"/>
-      <c r="AO28" s="351" t="n"/>
-      <c r="AP28" s="351" t="n"/>
-      <c r="AQ28" s="351" t="n"/>
-      <c r="AR28" s="377" t="n"/>
-      <c r="AS28" s="351" t="n"/>
-      <c r="AT28" s="351" t="n"/>
-      <c r="AU28" s="351" t="n"/>
-      <c r="AV28" s="351" t="n"/>
-      <c r="AW28" s="351" t="n"/>
-      <c r="AX28" s="377" t="n"/>
-      <c r="AY28" s="351" t="n"/>
-      <c r="AZ28" s="351" t="n"/>
-      <c r="BA28" s="351" t="n"/>
-      <c r="BB28" s="378" t="n"/>
-      <c r="BC28" s="351" t="n"/>
-      <c r="BD28" s="351" t="n"/>
+      <c r="A28" s="586" t="n"/>
+      <c r="B28" s="573" t="n"/>
+      <c r="C28" s="573" t="n"/>
+      <c r="D28" s="587" t="n"/>
+      <c r="E28" s="573" t="n"/>
+      <c r="F28" s="573" t="n"/>
+      <c r="G28" s="573" t="n"/>
+      <c r="H28" s="588" t="n"/>
+      <c r="I28" s="573" t="n"/>
+      <c r="J28" s="573" t="n"/>
+      <c r="K28" s="573" t="n"/>
+      <c r="L28" s="573" t="n"/>
+      <c r="M28" s="573" t="n"/>
+      <c r="N28" s="573" t="n"/>
+      <c r="O28" s="573" t="n"/>
+      <c r="P28" s="573" t="n"/>
+      <c r="Q28" s="573" t="n"/>
+      <c r="R28" s="573" t="n"/>
+      <c r="S28" s="573" t="n"/>
+      <c r="T28" s="573" t="n"/>
+      <c r="U28" s="573" t="n"/>
+      <c r="V28" s="573" t="n"/>
+      <c r="W28" s="573" t="n"/>
+      <c r="X28" s="573" t="n"/>
+      <c r="Y28" s="573" t="n"/>
+      <c r="Z28" s="573" t="n"/>
+      <c r="AA28" s="589" t="n"/>
+      <c r="AB28" s="573" t="n"/>
+      <c r="AC28" s="573" t="n"/>
+      <c r="AD28" s="573" t="n"/>
+      <c r="AE28" s="573" t="n"/>
+      <c r="AF28" s="573" t="n"/>
+      <c r="AG28" s="573" t="n"/>
+      <c r="AH28" s="573" t="n"/>
+      <c r="AI28" s="573" t="n"/>
+      <c r="AJ28" s="573" t="n"/>
+      <c r="AK28" s="573" t="n"/>
+      <c r="AL28" s="573" t="n"/>
+      <c r="AM28" s="573" t="n"/>
+      <c r="AN28" s="573" t="n"/>
+      <c r="AO28" s="573" t="n"/>
+      <c r="AP28" s="573" t="n"/>
+      <c r="AQ28" s="573" t="n"/>
+      <c r="AR28" s="590" t="n"/>
+      <c r="AS28" s="573" t="n"/>
+      <c r="AT28" s="573" t="n"/>
+      <c r="AU28" s="573" t="n"/>
+      <c r="AV28" s="573" t="n"/>
+      <c r="AW28" s="573" t="n"/>
+      <c r="AX28" s="590" t="n"/>
+      <c r="AY28" s="573" t="n"/>
+      <c r="AZ28" s="573" t="n"/>
+      <c r="BA28" s="573" t="n"/>
+      <c r="BB28" s="591" t="n"/>
+      <c r="BC28" s="573" t="n"/>
+      <c r="BD28" s="573" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="464" t="inlineStr">
+      <c r="A29" s="554" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="465" t="n"/>
-      <c r="C29" s="465" t="n"/>
-      <c r="D29" s="465" t="n"/>
-      <c r="E29" s="465" t="n"/>
-      <c r="F29" s="465" t="n"/>
-      <c r="G29" s="465" t="n"/>
-      <c r="H29" s="465" t="n"/>
-      <c r="I29" s="465" t="n"/>
-      <c r="J29" s="465" t="n"/>
-      <c r="K29" s="465" t="n"/>
-      <c r="L29" s="465" t="n"/>
-      <c r="M29" s="465" t="n"/>
-      <c r="N29" s="465" t="n"/>
-      <c r="O29" s="465" t="n"/>
-      <c r="P29" s="465" t="n"/>
-      <c r="Q29" s="465" t="n"/>
-      <c r="R29" s="465" t="n"/>
-      <c r="S29" s="465" t="n"/>
-      <c r="T29" s="465" t="n"/>
-      <c r="U29" s="465" t="n"/>
-      <c r="V29" s="465" t="n"/>
-      <c r="W29" s="465" t="n"/>
-      <c r="X29" s="465" t="n"/>
-      <c r="Y29" s="465" t="n"/>
-      <c r="Z29" s="465" t="n"/>
-      <c r="AA29" s="465" t="n"/>
-      <c r="AB29" s="465" t="n"/>
-      <c r="AC29" s="465" t="n"/>
-      <c r="AD29" s="465" t="n"/>
-      <c r="AE29" s="465" t="n"/>
-      <c r="AF29" s="465" t="n"/>
-      <c r="AG29" s="465" t="n"/>
-      <c r="AH29" s="465" t="n"/>
-      <c r="AI29" s="465" t="n"/>
-      <c r="AJ29" s="465" t="n"/>
-      <c r="AK29" s="465" t="n"/>
-      <c r="AL29" s="465" t="n"/>
-      <c r="AM29" s="465" t="n"/>
-      <c r="AN29" s="465" t="n"/>
-      <c r="AO29" s="465" t="n"/>
-      <c r="AP29" s="465" t="n"/>
-      <c r="AQ29" s="465" t="n"/>
-      <c r="AR29" s="465" t="n"/>
-      <c r="AS29" s="465" t="n"/>
-      <c r="AT29" s="465" t="n"/>
-      <c r="AU29" s="465" t="n"/>
-      <c r="AV29" s="465" t="n"/>
-      <c r="AW29" s="465" t="n"/>
-      <c r="AX29" s="465" t="n"/>
-      <c r="AY29" s="465" t="n"/>
-      <c r="AZ29" s="465" t="n"/>
-      <c r="BA29" s="465" t="n"/>
-      <c r="BB29" s="465" t="n"/>
-      <c r="BC29" s="465" t="n"/>
-      <c r="BD29" s="466" t="n"/>
+      <c r="B29" s="27" t="n"/>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="27" t="n"/>
+      <c r="H29" s="27" t="n"/>
+      <c r="I29" s="27" t="n"/>
+      <c r="J29" s="27" t="n"/>
+      <c r="K29" s="27" t="n"/>
+      <c r="L29" s="27" t="n"/>
+      <c r="M29" s="27" t="n"/>
+      <c r="N29" s="27" t="n"/>
+      <c r="O29" s="27" t="n"/>
+      <c r="P29" s="27" t="n"/>
+      <c r="Q29" s="27" t="n"/>
+      <c r="R29" s="27" t="n"/>
+      <c r="S29" s="27" t="n"/>
+      <c r="T29" s="27" t="n"/>
+      <c r="U29" s="27" t="n"/>
+      <c r="V29" s="27" t="n"/>
+      <c r="W29" s="27" t="n"/>
+      <c r="X29" s="27" t="n"/>
+      <c r="Y29" s="27" t="n"/>
+      <c r="Z29" s="27" t="n"/>
+      <c r="AA29" s="27" t="n"/>
+      <c r="AB29" s="27" t="n"/>
+      <c r="AC29" s="27" t="n"/>
+      <c r="AD29" s="27" t="n"/>
+      <c r="AE29" s="27" t="n"/>
+      <c r="AF29" s="27" t="n"/>
+      <c r="AG29" s="27" t="n"/>
+      <c r="AH29" s="27" t="n"/>
+      <c r="AI29" s="27" t="n"/>
+      <c r="AJ29" s="27" t="n"/>
+      <c r="AK29" s="27" t="n"/>
+      <c r="AL29" s="27" t="n"/>
+      <c r="AM29" s="27" t="n"/>
+      <c r="AN29" s="27" t="n"/>
+      <c r="AO29" s="27" t="n"/>
+      <c r="AP29" s="27" t="n"/>
+      <c r="AQ29" s="27" t="n"/>
+      <c r="AR29" s="27" t="n"/>
+      <c r="AS29" s="27" t="n"/>
+      <c r="AT29" s="27" t="n"/>
+      <c r="AU29" s="27" t="n"/>
+      <c r="AV29" s="27" t="n"/>
+      <c r="AW29" s="27" t="n"/>
+      <c r="AX29" s="27" t="n"/>
+      <c r="AY29" s="27" t="n"/>
+      <c r="AZ29" s="27" t="n"/>
+      <c r="BA29" s="27" t="n"/>
+      <c r="BB29" s="27" t="n"/>
+      <c r="BC29" s="27" t="n"/>
+      <c r="BD29" s="28" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="487" t="inlineStr">
+      <c r="A30" s="574" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="468" t="n"/>
-      <c r="C30" s="468" t="n"/>
-      <c r="D30" s="468" t="n"/>
-      <c r="E30" s="468" t="n"/>
-      <c r="F30" s="468" t="n"/>
-      <c r="G30" s="468" t="n"/>
-      <c r="H30" s="468" t="n"/>
-      <c r="I30" s="468" t="n"/>
-      <c r="J30" s="468" t="n"/>
-      <c r="K30" s="468" t="n"/>
-      <c r="L30" s="468" t="n"/>
-      <c r="M30" s="468" t="n"/>
-      <c r="N30" s="468" t="n"/>
-      <c r="O30" s="468" t="n"/>
-      <c r="P30" s="468" t="n"/>
-      <c r="Q30" s="468" t="n"/>
-      <c r="R30" s="468" t="n"/>
-      <c r="S30" s="499" t="inlineStr">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="6" t="n"/>
+      <c r="S30" s="592" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="468" t="n"/>
-      <c r="U30" s="468" t="n"/>
-      <c r="V30" s="468" t="n"/>
-      <c r="W30" s="468" t="n"/>
-      <c r="X30" s="468" t="n"/>
-      <c r="Y30" s="468" t="n"/>
-      <c r="Z30" s="468" t="n"/>
-      <c r="AA30" s="468" t="n"/>
-      <c r="AB30" s="468" t="n"/>
-      <c r="AC30" s="468" t="n"/>
-      <c r="AD30" s="468" t="n"/>
-      <c r="AE30" s="468" t="n"/>
-      <c r="AF30" s="468" t="n"/>
-      <c r="AG30" s="468" t="n"/>
-      <c r="AH30" s="468" t="n"/>
-      <c r="AI30" s="468" t="n"/>
-      <c r="AJ30" s="468" t="n"/>
-      <c r="AK30" s="499" t="inlineStr">
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="5" t="n"/>
+      <c r="V30" s="5" t="n"/>
+      <c r="W30" s="5" t="n"/>
+      <c r="X30" s="5" t="n"/>
+      <c r="Y30" s="5" t="n"/>
+      <c r="Z30" s="5" t="n"/>
+      <c r="AA30" s="5" t="n"/>
+      <c r="AB30" s="5" t="n"/>
+      <c r="AC30" s="5" t="n"/>
+      <c r="AD30" s="5" t="n"/>
+      <c r="AE30" s="5" t="n"/>
+      <c r="AF30" s="5" t="n"/>
+      <c r="AG30" s="5" t="n"/>
+      <c r="AH30" s="5" t="n"/>
+      <c r="AI30" s="5" t="n"/>
+      <c r="AJ30" s="6" t="n"/>
+      <c r="AK30" s="592" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="468" t="n"/>
-      <c r="AM30" s="468" t="n"/>
-      <c r="AN30" s="468" t="n"/>
-      <c r="AO30" s="468" t="n"/>
-      <c r="AP30" s="468" t="n"/>
-      <c r="AQ30" s="468" t="n"/>
-      <c r="AR30" s="468" t="n"/>
-      <c r="AS30" s="468" t="n"/>
-      <c r="AT30" s="468" t="n"/>
-      <c r="AU30" s="468" t="n"/>
-      <c r="AV30" s="468" t="n"/>
-      <c r="AW30" s="468" t="n"/>
-      <c r="AX30" s="468" t="n"/>
-      <c r="AY30" s="468" t="n"/>
-      <c r="AZ30" s="468" t="n"/>
-      <c r="BA30" s="468" t="n"/>
-      <c r="BB30" s="468" t="n"/>
-      <c r="BC30" s="468" t="n"/>
-      <c r="BD30" s="500" t="n"/>
+      <c r="AL30" s="5" t="n"/>
+      <c r="AM30" s="5" t="n"/>
+      <c r="AN30" s="5" t="n"/>
+      <c r="AO30" s="5" t="n"/>
+      <c r="AP30" s="5" t="n"/>
+      <c r="AQ30" s="5" t="n"/>
+      <c r="AR30" s="5" t="n"/>
+      <c r="AS30" s="5" t="n"/>
+      <c r="AT30" s="5" t="n"/>
+      <c r="AU30" s="5" t="n"/>
+      <c r="AV30" s="5" t="n"/>
+      <c r="AW30" s="5" t="n"/>
+      <c r="AX30" s="5" t="n"/>
+      <c r="AY30" s="5" t="n"/>
+      <c r="AZ30" s="5" t="n"/>
+      <c r="BA30" s="5" t="n"/>
+      <c r="BB30" s="5" t="n"/>
+      <c r="BC30" s="5" t="n"/>
+      <c r="BD30" s="8" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="501" t="inlineStr">
+      <c r="A31" s="593" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="360" t="n"/>
-      <c r="C31" s="360" t="n"/>
-      <c r="D31" s="360" t="n"/>
-      <c r="E31" s="360" t="n"/>
-      <c r="F31" s="360" t="n"/>
-      <c r="G31" s="360" t="n"/>
-      <c r="H31" s="360" t="n"/>
-      <c r="I31" s="360" t="n"/>
-      <c r="J31" s="360" t="n"/>
-      <c r="K31" s="360" t="n"/>
-      <c r="L31" s="360" t="n"/>
-      <c r="M31" s="360" t="n"/>
-      <c r="N31" s="360" t="n"/>
-      <c r="O31" s="360" t="n"/>
-      <c r="P31" s="360" t="n"/>
-      <c r="Q31" s="360" t="n"/>
-      <c r="R31" s="360" t="n"/>
-      <c r="S31" s="502" t="inlineStr">
+      <c r="B31" s="563" t="n"/>
+      <c r="C31" s="563" t="n"/>
+      <c r="D31" s="563" t="n"/>
+      <c r="E31" s="563" t="n"/>
+      <c r="F31" s="563" t="n"/>
+      <c r="G31" s="563" t="n"/>
+      <c r="H31" s="563" t="n"/>
+      <c r="I31" s="563" t="n"/>
+      <c r="J31" s="563" t="n"/>
+      <c r="K31" s="563" t="n"/>
+      <c r="L31" s="563" t="n"/>
+      <c r="M31" s="563" t="n"/>
+      <c r="N31" s="563" t="n"/>
+      <c r="O31" s="563" t="n"/>
+      <c r="P31" s="563" t="n"/>
+      <c r="Q31" s="563" t="n"/>
+      <c r="R31" s="564" t="n"/>
+      <c r="S31" s="594" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="360" t="n"/>
-      <c r="U31" s="360" t="n"/>
-      <c r="V31" s="360" t="n"/>
-      <c r="W31" s="360" t="n"/>
-      <c r="X31" s="360" t="n"/>
-      <c r="Y31" s="360" t="n"/>
-      <c r="Z31" s="360" t="n"/>
-      <c r="AA31" s="360" t="n"/>
-      <c r="AB31" s="360" t="n"/>
-      <c r="AC31" s="360" t="n"/>
-      <c r="AD31" s="360" t="n"/>
-      <c r="AE31" s="360" t="n"/>
-      <c r="AF31" s="360" t="n"/>
-      <c r="AG31" s="360" t="n"/>
-      <c r="AH31" s="360" t="n"/>
-      <c r="AI31" s="360" t="n"/>
-      <c r="AJ31" s="360" t="n"/>
-      <c r="AK31" s="502" t="inlineStr">
+      <c r="T31" s="563" t="n"/>
+      <c r="U31" s="563" t="n"/>
+      <c r="V31" s="563" t="n"/>
+      <c r="W31" s="563" t="n"/>
+      <c r="X31" s="563" t="n"/>
+      <c r="Y31" s="563" t="n"/>
+      <c r="Z31" s="563" t="n"/>
+      <c r="AA31" s="563" t="n"/>
+      <c r="AB31" s="563" t="n"/>
+      <c r="AC31" s="563" t="n"/>
+      <c r="AD31" s="563" t="n"/>
+      <c r="AE31" s="563" t="n"/>
+      <c r="AF31" s="563" t="n"/>
+      <c r="AG31" s="563" t="n"/>
+      <c r="AH31" s="563" t="n"/>
+      <c r="AI31" s="563" t="n"/>
+      <c r="AJ31" s="564" t="n"/>
+      <c r="AK31" s="594" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="360" t="n"/>
-      <c r="AM31" s="360" t="n"/>
-      <c r="AN31" s="360" t="n"/>
-      <c r="AO31" s="360" t="n"/>
-      <c r="AP31" s="360" t="n"/>
-      <c r="AQ31" s="360" t="n"/>
-      <c r="AR31" s="360" t="n"/>
-      <c r="AS31" s="360" t="n"/>
-      <c r="AT31" s="360" t="n"/>
-      <c r="AU31" s="360" t="n"/>
-      <c r="AV31" s="360" t="n"/>
-      <c r="AW31" s="360" t="n"/>
-      <c r="AX31" s="360" t="n"/>
-      <c r="AY31" s="360" t="n"/>
-      <c r="AZ31" s="360" t="n"/>
-      <c r="BA31" s="360" t="n"/>
-      <c r="BB31" s="360" t="n"/>
-      <c r="BC31" s="360" t="n"/>
-      <c r="BD31" s="476" t="n"/>
+      <c r="AL31" s="563" t="n"/>
+      <c r="AM31" s="563" t="n"/>
+      <c r="AN31" s="563" t="n"/>
+      <c r="AO31" s="563" t="n"/>
+      <c r="AP31" s="563" t="n"/>
+      <c r="AQ31" s="563" t="n"/>
+      <c r="AR31" s="563" t="n"/>
+      <c r="AS31" s="563" t="n"/>
+      <c r="AT31" s="563" t="n"/>
+      <c r="AU31" s="563" t="n"/>
+      <c r="AV31" s="563" t="n"/>
+      <c r="AW31" s="563" t="n"/>
+      <c r="AX31" s="563" t="n"/>
+      <c r="AY31" s="563" t="n"/>
+      <c r="AZ31" s="563" t="n"/>
+      <c r="BA31" s="563" t="n"/>
+      <c r="BB31" s="563" t="n"/>
+      <c r="BC31" s="563" t="n"/>
+      <c r="BD31" s="566" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="503" t="n"/>
-      <c r="B32" s="360" t="n"/>
-      <c r="C32" s="360" t="n"/>
-      <c r="D32" s="360" t="n"/>
-      <c r="E32" s="360" t="n"/>
-      <c r="F32" s="360" t="n"/>
-      <c r="G32" s="360" t="n"/>
-      <c r="H32" s="360" t="n"/>
-      <c r="I32" s="360" t="n"/>
-      <c r="J32" s="360" t="n"/>
-      <c r="K32" s="360" t="n"/>
-      <c r="L32" s="360" t="n"/>
-      <c r="M32" s="360" t="n"/>
-      <c r="N32" s="360" t="n"/>
-      <c r="O32" s="360" t="n"/>
-      <c r="P32" s="360" t="n"/>
-      <c r="Q32" s="360" t="n"/>
-      <c r="R32" s="360" t="n"/>
-      <c r="S32" s="504" t="n"/>
-      <c r="T32" s="360" t="n"/>
-      <c r="U32" s="360" t="n"/>
-      <c r="V32" s="360" t="n"/>
-      <c r="W32" s="360" t="n"/>
-      <c r="X32" s="360" t="n"/>
-      <c r="Y32" s="360" t="n"/>
-      <c r="Z32" s="360" t="n"/>
-      <c r="AA32" s="360" t="n"/>
-      <c r="AB32" s="360" t="n"/>
-      <c r="AC32" s="360" t="n"/>
-      <c r="AD32" s="360" t="n"/>
-      <c r="AE32" s="360" t="n"/>
-      <c r="AF32" s="360" t="n"/>
-      <c r="AG32" s="360" t="n"/>
-      <c r="AH32" s="360" t="n"/>
-      <c r="AI32" s="360" t="n"/>
-      <c r="AJ32" s="360" t="n"/>
-      <c r="AK32" s="504" t="n"/>
-      <c r="AL32" s="360" t="n"/>
-      <c r="AM32" s="360" t="n"/>
-      <c r="AN32" s="360" t="n"/>
-      <c r="AO32" s="360" t="n"/>
-      <c r="AP32" s="360" t="n"/>
-      <c r="AQ32" s="360" t="n"/>
-      <c r="AR32" s="360" t="n"/>
-      <c r="AS32" s="360" t="n"/>
-      <c r="AT32" s="360" t="n"/>
-      <c r="AU32" s="360" t="n"/>
-      <c r="AV32" s="360" t="n"/>
-      <c r="AW32" s="360" t="n"/>
-      <c r="AX32" s="360" t="n"/>
-      <c r="AY32" s="360" t="n"/>
-      <c r="AZ32" s="360" t="n"/>
-      <c r="BA32" s="360" t="n"/>
-      <c r="BB32" s="360" t="n"/>
-      <c r="BC32" s="360" t="n"/>
-      <c r="BD32" s="476" t="n"/>
+      <c r="A32" s="595" t="n"/>
+      <c r="B32" s="563" t="n"/>
+      <c r="C32" s="563" t="n"/>
+      <c r="D32" s="563" t="n"/>
+      <c r="E32" s="563" t="n"/>
+      <c r="F32" s="563" t="n"/>
+      <c r="G32" s="563" t="n"/>
+      <c r="H32" s="563" t="n"/>
+      <c r="I32" s="563" t="n"/>
+      <c r="J32" s="563" t="n"/>
+      <c r="K32" s="563" t="n"/>
+      <c r="L32" s="563" t="n"/>
+      <c r="M32" s="563" t="n"/>
+      <c r="N32" s="563" t="n"/>
+      <c r="O32" s="563" t="n"/>
+      <c r="P32" s="563" t="n"/>
+      <c r="Q32" s="563" t="n"/>
+      <c r="R32" s="564" t="n"/>
+      <c r="S32" s="563" t="n"/>
+      <c r="T32" s="563" t="n"/>
+      <c r="U32" s="563" t="n"/>
+      <c r="V32" s="563" t="n"/>
+      <c r="W32" s="563" t="n"/>
+      <c r="X32" s="563" t="n"/>
+      <c r="Y32" s="563" t="n"/>
+      <c r="Z32" s="563" t="n"/>
+      <c r="AA32" s="563" t="n"/>
+      <c r="AB32" s="563" t="n"/>
+      <c r="AC32" s="563" t="n"/>
+      <c r="AD32" s="563" t="n"/>
+      <c r="AE32" s="563" t="n"/>
+      <c r="AF32" s="563" t="n"/>
+      <c r="AG32" s="563" t="n"/>
+      <c r="AH32" s="563" t="n"/>
+      <c r="AI32" s="563" t="n"/>
+      <c r="AJ32" s="564" t="n"/>
+      <c r="AK32" s="563" t="n"/>
+      <c r="AL32" s="563" t="n"/>
+      <c r="AM32" s="563" t="n"/>
+      <c r="AN32" s="563" t="n"/>
+      <c r="AO32" s="563" t="n"/>
+      <c r="AP32" s="563" t="n"/>
+      <c r="AQ32" s="563" t="n"/>
+      <c r="AR32" s="563" t="n"/>
+      <c r="AS32" s="563" t="n"/>
+      <c r="AT32" s="563" t="n"/>
+      <c r="AU32" s="563" t="n"/>
+      <c r="AV32" s="563" t="n"/>
+      <c r="AW32" s="563" t="n"/>
+      <c r="AX32" s="563" t="n"/>
+      <c r="AY32" s="563" t="n"/>
+      <c r="AZ32" s="563" t="n"/>
+      <c r="BA32" s="563" t="n"/>
+      <c r="BB32" s="563" t="n"/>
+      <c r="BC32" s="563" t="n"/>
+      <c r="BD32" s="566" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="505" t="n"/>
-      <c r="B33" s="480" t="n"/>
-      <c r="C33" s="480" t="n"/>
-      <c r="D33" s="480" t="n"/>
-      <c r="E33" s="480" t="n"/>
-      <c r="F33" s="480" t="n"/>
-      <c r="G33" s="480" t="n"/>
-      <c r="H33" s="480" t="n"/>
-      <c r="I33" s="480" t="n"/>
-      <c r="J33" s="480" t="n"/>
-      <c r="K33" s="480" t="n"/>
-      <c r="L33" s="480" t="n"/>
-      <c r="M33" s="480" t="n"/>
-      <c r="N33" s="480" t="n"/>
-      <c r="O33" s="480" t="n"/>
-      <c r="P33" s="480" t="n"/>
-      <c r="Q33" s="480" t="n"/>
-      <c r="R33" s="480" t="n"/>
-      <c r="S33" s="506" t="n"/>
-      <c r="T33" s="480" t="n"/>
-      <c r="U33" s="480" t="n"/>
-      <c r="V33" s="480" t="n"/>
-      <c r="W33" s="480" t="n"/>
-      <c r="X33" s="480" t="n"/>
-      <c r="Y33" s="480" t="n"/>
-      <c r="Z33" s="480" t="n"/>
-      <c r="AA33" s="480" t="n"/>
-      <c r="AB33" s="480" t="n"/>
-      <c r="AC33" s="480" t="n"/>
-      <c r="AD33" s="480" t="n"/>
-      <c r="AE33" s="480" t="n"/>
-      <c r="AF33" s="480" t="n"/>
-      <c r="AG33" s="480" t="n"/>
-      <c r="AH33" s="480" t="n"/>
-      <c r="AI33" s="480" t="n"/>
-      <c r="AJ33" s="480" t="n"/>
-      <c r="AK33" s="506" t="n"/>
-      <c r="AL33" s="480" t="n"/>
-      <c r="AM33" s="480" t="n"/>
-      <c r="AN33" s="480" t="n"/>
-      <c r="AO33" s="480" t="n"/>
-      <c r="AP33" s="480" t="n"/>
-      <c r="AQ33" s="480" t="n"/>
-      <c r="AR33" s="480" t="n"/>
-      <c r="AS33" s="480" t="n"/>
-      <c r="AT33" s="480" t="n"/>
-      <c r="AU33" s="480" t="n"/>
-      <c r="AV33" s="480" t="n"/>
-      <c r="AW33" s="480" t="n"/>
-      <c r="AX33" s="480" t="n"/>
-      <c r="AY33" s="480" t="n"/>
-      <c r="AZ33" s="480" t="n"/>
-      <c r="BA33" s="480" t="n"/>
-      <c r="BB33" s="480" t="n"/>
-      <c r="BC33" s="480" t="n"/>
-      <c r="BD33" s="482" t="n"/>
+      <c r="A33" s="596" t="n"/>
+      <c r="B33" s="569" t="n"/>
+      <c r="C33" s="569" t="n"/>
+      <c r="D33" s="569" t="n"/>
+      <c r="E33" s="569" t="n"/>
+      <c r="F33" s="569" t="n"/>
+      <c r="G33" s="569" t="n"/>
+      <c r="H33" s="569" t="n"/>
+      <c r="I33" s="569" t="n"/>
+      <c r="J33" s="569" t="n"/>
+      <c r="K33" s="569" t="n"/>
+      <c r="L33" s="569" t="n"/>
+      <c r="M33" s="569" t="n"/>
+      <c r="N33" s="569" t="n"/>
+      <c r="O33" s="569" t="n"/>
+      <c r="P33" s="569" t="n"/>
+      <c r="Q33" s="569" t="n"/>
+      <c r="R33" s="570" t="n"/>
+      <c r="S33" s="569" t="n"/>
+      <c r="T33" s="569" t="n"/>
+      <c r="U33" s="569" t="n"/>
+      <c r="V33" s="569" t="n"/>
+      <c r="W33" s="569" t="n"/>
+      <c r="X33" s="569" t="n"/>
+      <c r="Y33" s="569" t="n"/>
+      <c r="Z33" s="569" t="n"/>
+      <c r="AA33" s="569" t="n"/>
+      <c r="AB33" s="569" t="n"/>
+      <c r="AC33" s="569" t="n"/>
+      <c r="AD33" s="569" t="n"/>
+      <c r="AE33" s="569" t="n"/>
+      <c r="AF33" s="569" t="n"/>
+      <c r="AG33" s="569" t="n"/>
+      <c r="AH33" s="569" t="n"/>
+      <c r="AI33" s="569" t="n"/>
+      <c r="AJ33" s="570" t="n"/>
+      <c r="AK33" s="569" t="n"/>
+      <c r="AL33" s="569" t="n"/>
+      <c r="AM33" s="569" t="n"/>
+      <c r="AN33" s="569" t="n"/>
+      <c r="AO33" s="569" t="n"/>
+      <c r="AP33" s="569" t="n"/>
+      <c r="AQ33" s="569" t="n"/>
+      <c r="AR33" s="569" t="n"/>
+      <c r="AS33" s="569" t="n"/>
+      <c r="AT33" s="569" t="n"/>
+      <c r="AU33" s="569" t="n"/>
+      <c r="AV33" s="569" t="n"/>
+      <c r="AW33" s="569" t="n"/>
+      <c r="AX33" s="569" t="n"/>
+      <c r="AY33" s="569" t="n"/>
+      <c r="AZ33" s="569" t="n"/>
+      <c r="BA33" s="569" t="n"/>
+      <c r="BB33" s="569" t="n"/>
+      <c r="BC33" s="569" t="n"/>
+      <c r="BD33" s="572" t="n"/>
     </row>
     <row r="34" ht="3" customHeight="1">
-      <c r="A34" s="389" t="n"/>
-      <c r="B34" s="351" t="n"/>
-      <c r="C34" s="351" t="n"/>
-      <c r="D34" s="389" t="n"/>
-      <c r="E34" s="351" t="n"/>
-      <c r="F34" s="351" t="n"/>
-      <c r="G34" s="351" t="n"/>
-      <c r="H34" s="351" t="n"/>
-      <c r="I34" s="351" t="n"/>
-      <c r="J34" s="351" t="n"/>
-      <c r="K34" s="351" t="n"/>
-      <c r="L34" s="351" t="n"/>
-      <c r="M34" s="351" t="n"/>
-      <c r="N34" s="351" t="n"/>
-      <c r="O34" s="351" t="n"/>
-      <c r="P34" s="351" t="n"/>
-      <c r="Q34" s="351" t="n"/>
-      <c r="R34" s="389" t="n"/>
-      <c r="S34" s="351" t="n"/>
-      <c r="T34" s="351" t="n"/>
-      <c r="U34" s="351" t="n"/>
-      <c r="V34" s="351" t="n"/>
-      <c r="W34" s="351" t="n"/>
-      <c r="X34" s="351" t="n"/>
-      <c r="Y34" s="351" t="n"/>
-      <c r="Z34" s="351" t="n"/>
-      <c r="AA34" s="351" t="n"/>
-      <c r="AB34" s="351" t="n"/>
-      <c r="AC34" s="351" t="n"/>
-      <c r="AD34" s="351" t="n"/>
-      <c r="AE34" s="351" t="n"/>
-      <c r="AF34" s="351" t="n"/>
-      <c r="AG34" s="351" t="n"/>
-      <c r="AH34" s="351" t="n"/>
-      <c r="AI34" s="389" t="n"/>
-      <c r="AJ34" s="351" t="n"/>
-      <c r="AK34" s="351" t="n"/>
-      <c r="AL34" s="351" t="n"/>
-      <c r="AM34" s="351" t="n"/>
-      <c r="AN34" s="351" t="n"/>
-      <c r="AO34" s="351" t="n"/>
-      <c r="AP34" s="389" t="n"/>
-      <c r="AQ34" s="351" t="n"/>
-      <c r="AR34" s="351" t="n"/>
-      <c r="AS34" s="351" t="n"/>
-      <c r="AT34" s="351" t="n"/>
-      <c r="AU34" s="351" t="n"/>
-      <c r="AV34" s="351" t="n"/>
-      <c r="AW34" s="389" t="n"/>
-      <c r="AX34" s="351" t="n"/>
-      <c r="AY34" s="351" t="n"/>
-      <c r="AZ34" s="351" t="n"/>
-      <c r="BA34" s="389" t="n"/>
-      <c r="BB34" s="351" t="n"/>
-      <c r="BC34" s="351" t="n"/>
-      <c r="BD34" s="351" t="n"/>
+      <c r="A34" s="597" t="n"/>
+      <c r="B34" s="573" t="n"/>
+      <c r="C34" s="573" t="n"/>
+      <c r="D34" s="597" t="n"/>
+      <c r="E34" s="573" t="n"/>
+      <c r="F34" s="573" t="n"/>
+      <c r="G34" s="573" t="n"/>
+      <c r="H34" s="573" t="n"/>
+      <c r="I34" s="573" t="n"/>
+      <c r="J34" s="573" t="n"/>
+      <c r="K34" s="573" t="n"/>
+      <c r="L34" s="573" t="n"/>
+      <c r="M34" s="573" t="n"/>
+      <c r="N34" s="573" t="n"/>
+      <c r="O34" s="573" t="n"/>
+      <c r="P34" s="573" t="n"/>
+      <c r="Q34" s="573" t="n"/>
+      <c r="R34" s="597" t="n"/>
+      <c r="S34" s="573" t="n"/>
+      <c r="T34" s="573" t="n"/>
+      <c r="U34" s="573" t="n"/>
+      <c r="V34" s="573" t="n"/>
+      <c r="W34" s="573" t="n"/>
+      <c r="X34" s="573" t="n"/>
+      <c r="Y34" s="573" t="n"/>
+      <c r="Z34" s="573" t="n"/>
+      <c r="AA34" s="573" t="n"/>
+      <c r="AB34" s="573" t="n"/>
+      <c r="AC34" s="573" t="n"/>
+      <c r="AD34" s="573" t="n"/>
+      <c r="AE34" s="573" t="n"/>
+      <c r="AF34" s="573" t="n"/>
+      <c r="AG34" s="573" t="n"/>
+      <c r="AH34" s="573" t="n"/>
+      <c r="AI34" s="597" t="n"/>
+      <c r="AJ34" s="573" t="n"/>
+      <c r="AK34" s="573" t="n"/>
+      <c r="AL34" s="573" t="n"/>
+      <c r="AM34" s="573" t="n"/>
+      <c r="AN34" s="573" t="n"/>
+      <c r="AO34" s="573" t="n"/>
+      <c r="AP34" s="597" t="n"/>
+      <c r="AQ34" s="573" t="n"/>
+      <c r="AR34" s="573" t="n"/>
+      <c r="AS34" s="573" t="n"/>
+      <c r="AT34" s="573" t="n"/>
+      <c r="AU34" s="573" t="n"/>
+      <c r="AV34" s="573" t="n"/>
+      <c r="AW34" s="597" t="n"/>
+      <c r="AX34" s="573" t="n"/>
+      <c r="AY34" s="573" t="n"/>
+      <c r="AZ34" s="573" t="n"/>
+      <c r="BA34" s="597" t="n"/>
+      <c r="BB34" s="573" t="n"/>
+      <c r="BC34" s="573" t="n"/>
+      <c r="BD34" s="573" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="507" t="inlineStr">
+      <c r="A35" s="598" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B35" s="508" t="n"/>
-      <c r="C35" s="508" t="n"/>
-      <c r="D35" s="508" t="n"/>
-      <c r="E35" s="508" t="n"/>
-      <c r="F35" s="508" t="n"/>
-      <c r="G35" s="508" t="n"/>
-      <c r="H35" s="508" t="n"/>
-      <c r="I35" s="508" t="n"/>
-      <c r="J35" s="508" t="n"/>
-      <c r="K35" s="508" t="n"/>
-      <c r="L35" s="508" t="n"/>
-      <c r="M35" s="508" t="n"/>
-      <c r="N35" s="508" t="n"/>
-      <c r="O35" s="508" t="n"/>
-      <c r="P35" s="508" t="n"/>
-      <c r="Q35" s="508" t="n"/>
-      <c r="R35" s="508" t="n"/>
-      <c r="S35" s="508" t="n"/>
-      <c r="T35" s="508" t="n"/>
-      <c r="U35" s="508" t="n"/>
-      <c r="V35" s="508" t="n"/>
-      <c r="W35" s="508" t="n"/>
-      <c r="X35" s="508" t="n"/>
-      <c r="Y35" s="508" t="n"/>
-      <c r="Z35" s="508" t="n"/>
-      <c r="AA35" s="508" t="n"/>
-      <c r="AB35" s="508" t="n"/>
-      <c r="AC35" s="508" t="n"/>
-      <c r="AD35" s="508" t="n"/>
-      <c r="AE35" s="508" t="n"/>
-      <c r="AF35" s="508" t="n"/>
-      <c r="AG35" s="508" t="n"/>
-      <c r="AH35" s="508" t="n"/>
-      <c r="AI35" s="508" t="n"/>
-      <c r="AJ35" s="508" t="n"/>
-      <c r="AK35" s="508" t="n"/>
-      <c r="AL35" s="508" t="n"/>
-      <c r="AM35" s="508" t="n"/>
-      <c r="AN35" s="508" t="n"/>
-      <c r="AO35" s="508" t="n"/>
-      <c r="AP35" s="508" t="n"/>
-      <c r="AQ35" s="508" t="n"/>
-      <c r="AR35" s="508" t="n"/>
-      <c r="AS35" s="508" t="n"/>
-      <c r="AT35" s="508" t="n"/>
-      <c r="AU35" s="508" t="n"/>
-      <c r="AV35" s="508" t="n"/>
-      <c r="AW35" s="508" t="n"/>
-      <c r="AX35" s="508" t="n"/>
-      <c r="AY35" s="508" t="n"/>
-      <c r="AZ35" s="508" t="n"/>
-      <c r="BA35" s="508" t="n"/>
-      <c r="BB35" s="508" t="n"/>
-      <c r="BC35" s="508" t="n"/>
-      <c r="BD35" s="509" t="n"/>
+      <c r="B35" s="27" t="n"/>
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="27" t="n"/>
+      <c r="H35" s="27" t="n"/>
+      <c r="I35" s="27" t="n"/>
+      <c r="J35" s="27" t="n"/>
+      <c r="K35" s="27" t="n"/>
+      <c r="L35" s="27" t="n"/>
+      <c r="M35" s="27" t="n"/>
+      <c r="N35" s="27" t="n"/>
+      <c r="O35" s="27" t="n"/>
+      <c r="P35" s="27" t="n"/>
+      <c r="Q35" s="27" t="n"/>
+      <c r="R35" s="27" t="n"/>
+      <c r="S35" s="27" t="n"/>
+      <c r="T35" s="27" t="n"/>
+      <c r="U35" s="27" t="n"/>
+      <c r="V35" s="27" t="n"/>
+      <c r="W35" s="27" t="n"/>
+      <c r="X35" s="27" t="n"/>
+      <c r="Y35" s="27" t="n"/>
+      <c r="Z35" s="27" t="n"/>
+      <c r="AA35" s="27" t="n"/>
+      <c r="AB35" s="27" t="n"/>
+      <c r="AC35" s="27" t="n"/>
+      <c r="AD35" s="27" t="n"/>
+      <c r="AE35" s="27" t="n"/>
+      <c r="AF35" s="27" t="n"/>
+      <c r="AG35" s="27" t="n"/>
+      <c r="AH35" s="27" t="n"/>
+      <c r="AI35" s="27" t="n"/>
+      <c r="AJ35" s="27" t="n"/>
+      <c r="AK35" s="27" t="n"/>
+      <c r="AL35" s="27" t="n"/>
+      <c r="AM35" s="27" t="n"/>
+      <c r="AN35" s="27" t="n"/>
+      <c r="AO35" s="27" t="n"/>
+      <c r="AP35" s="27" t="n"/>
+      <c r="AQ35" s="27" t="n"/>
+      <c r="AR35" s="27" t="n"/>
+      <c r="AS35" s="27" t="n"/>
+      <c r="AT35" s="27" t="n"/>
+      <c r="AU35" s="27" t="n"/>
+      <c r="AV35" s="27" t="n"/>
+      <c r="AW35" s="27" t="n"/>
+      <c r="AX35" s="27" t="n"/>
+      <c r="AY35" s="27" t="n"/>
+      <c r="AZ35" s="27" t="n"/>
+      <c r="BA35" s="27" t="n"/>
+      <c r="BB35" s="27" t="n"/>
+      <c r="BC35" s="27" t="n"/>
+      <c r="BD35" s="28" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -8517,7 +9183,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;C&amp;"-,Regular"&amp;7 FRM-641  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-641  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8533,7 +9199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8758,7 +9424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:CU19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -8809,12 +9475,12 @@
           <t>Result Detail</t>
         </is>
       </c>
-      <c r="B1" s="426" t="n"/>
-      <c r="C1" s="426" t="n"/>
-      <c r="D1" s="426" t="n"/>
-      <c r="E1" s="426" t="n"/>
-      <c r="F1" s="426" t="n"/>
-      <c r="G1" s="426" t="n"/>
+      <c r="B1" s="599" t="n"/>
+      <c r="C1" s="599" t="n"/>
+      <c r="D1" s="599" t="n"/>
+      <c r="E1" s="599" t="n"/>
+      <c r="F1" s="599" t="n"/>
+      <c r="G1" s="599" t="n"/>
       <c r="H1" s="511" t="n"/>
       <c r="I1" s="428" t="n"/>
       <c r="J1" s="429" t="n"/>
@@ -8855,12 +9521,6 @@
           <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="513" t="n"/>
       <c r="I2" s="439" t="n"/>
       <c r="J2" s="440" t="n"/>
@@ -9708,7 +10368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:CU15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9759,12 +10419,12 @@
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="426" t="n"/>
-      <c r="C1" s="426" t="n"/>
-      <c r="D1" s="426" t="n"/>
-      <c r="E1" s="426" t="n"/>
-      <c r="F1" s="426" t="n"/>
-      <c r="G1" s="426" t="n"/>
+      <c r="B1" s="599" t="n"/>
+      <c r="C1" s="599" t="n"/>
+      <c r="D1" s="599" t="n"/>
+      <c r="E1" s="599" t="n"/>
+      <c r="F1" s="599" t="n"/>
+      <c r="G1" s="599" t="n"/>
       <c r="H1" s="511" t="n"/>
       <c r="I1" s="428" t="n"/>
       <c r="J1" s="429" t="n"/>
@@ -9805,12 +10465,6 @@
           <t>Reference plan / lot / method / release documents from their owning source.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="513" t="n"/>
       <c r="I2" s="439" t="n"/>
       <c r="J2" s="440" t="n"/>
@@ -10557,7 +11211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:CU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10608,12 +11262,12 @@
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="426" t="n"/>
-      <c r="C1" s="426" t="n"/>
-      <c r="D1" s="426" t="n"/>
-      <c r="E1" s="426" t="n"/>
-      <c r="F1" s="426" t="n"/>
-      <c r="G1" s="426" t="n"/>
+      <c r="B1" s="599" t="n"/>
+      <c r="C1" s="599" t="n"/>
+      <c r="D1" s="599" t="n"/>
+      <c r="E1" s="599" t="n"/>
+      <c r="F1" s="599" t="n"/>
+      <c r="G1" s="599" t="n"/>
       <c r="H1" s="511" t="n"/>
       <c r="I1" s="428" t="n"/>
       <c r="J1" s="429" t="n"/>
@@ -10654,12 +11308,6 @@
           <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="513" t="n"/>
       <c r="I2" s="439" t="n"/>
       <c r="J2" s="440" t="n"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINAL_INSP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FINAL_INSP'!$A$1:$BD$35</definedName>
@@ -766,7 +766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="362">
+  <borders count="371">
     <border>
       <left/>
       <right/>
@@ -4667,12 +4667,118 @@
       <bottom style="thin">
         <color rgb="000078D4"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="600">
+  <cellXfs count="644">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6189,6 +6295,130 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="120" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6288,6 +6518,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6761,346 +6994,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="538" t="inlineStr"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="53" t="n"/>
+      <c r="A1" s="600" t="inlineStr"/>
+      <c r="B1" s="268" t="n"/>
+      <c r="C1" s="268" t="n"/>
+      <c r="D1" s="268" t="n"/>
+      <c r="E1" s="268" t="n"/>
+      <c r="F1" s="268" t="n"/>
+      <c r="G1" s="268" t="n"/>
+      <c r="H1" s="268" t="n"/>
+      <c r="I1" s="268" t="n"/>
+      <c r="J1" s="268" t="n"/>
+      <c r="K1" s="601" t="n"/>
       <c r="L1" s="539" t="inlineStr">
         <is>
           <t>Final Inspection Report</t>
         </is>
       </c>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="2" t="n"/>
-      <c r="AI1" s="2" t="n"/>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="2" t="n"/>
-      <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
-      <c r="AQ1" s="540" t="inlineStr">
+      <c r="M1" s="268" t="n"/>
+      <c r="N1" s="268" t="n"/>
+      <c r="O1" s="268" t="n"/>
+      <c r="P1" s="268" t="n"/>
+      <c r="Q1" s="268" t="n"/>
+      <c r="R1" s="268" t="n"/>
+      <c r="S1" s="268" t="n"/>
+      <c r="T1" s="268" t="n"/>
+      <c r="U1" s="268" t="n"/>
+      <c r="V1" s="268" t="n"/>
+      <c r="W1" s="268" t="n"/>
+      <c r="X1" s="268" t="n"/>
+      <c r="Y1" s="268" t="n"/>
+      <c r="Z1" s="268" t="n"/>
+      <c r="AA1" s="268" t="n"/>
+      <c r="AB1" s="268" t="n"/>
+      <c r="AC1" s="268" t="n"/>
+      <c r="AD1" s="268" t="n"/>
+      <c r="AE1" s="268" t="n"/>
+      <c r="AF1" s="268" t="n"/>
+      <c r="AG1" s="268" t="n"/>
+      <c r="AH1" s="268" t="n"/>
+      <c r="AI1" s="268" t="n"/>
+      <c r="AJ1" s="268" t="n"/>
+      <c r="AK1" s="268" t="n"/>
+      <c r="AL1" s="268" t="n"/>
+      <c r="AM1" s="268" t="n"/>
+      <c r="AN1" s="268" t="n"/>
+      <c r="AO1" s="268" t="n"/>
+      <c r="AP1" s="268" t="n"/>
+      <c r="AQ1" s="602" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="2" t="n"/>
-      <c r="AS1" s="2" t="n"/>
-      <c r="AT1" s="2" t="n"/>
-      <c r="AU1" s="2" t="n"/>
-      <c r="AV1" s="541" t="n"/>
-      <c r="AW1" s="542" t="inlineStr">
+      <c r="AR1" s="268" t="n"/>
+      <c r="AS1" s="268" t="n"/>
+      <c r="AT1" s="268" t="n"/>
+      <c r="AU1" s="268" t="n"/>
+      <c r="AV1" s="603" t="n"/>
+      <c r="AW1" s="604" t="inlineStr">
         <is>
           <t>FRM-641</t>
         </is>
       </c>
-      <c r="AX1" s="2" t="n"/>
-      <c r="AY1" s="2" t="n"/>
-      <c r="AZ1" s="2" t="n"/>
-      <c r="BA1" s="2" t="n"/>
-      <c r="BB1" s="2" t="n"/>
-      <c r="BC1" s="2" t="n"/>
-      <c r="BD1" s="53" t="n"/>
+      <c r="AX1" s="268" t="n"/>
+      <c r="AY1" s="268" t="n"/>
+      <c r="AZ1" s="268" t="n"/>
+      <c r="BA1" s="268" t="n"/>
+      <c r="BB1" s="268" t="n"/>
+      <c r="BC1" s="268" t="n"/>
+      <c r="BD1" s="601" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="54" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="10" t="n"/>
-      <c r="AE2" s="10" t="n"/>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="10" t="n"/>
-      <c r="AI2" s="10" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="10" t="n"/>
-      <c r="AO2" s="10" t="n"/>
-      <c r="AP2" s="10" t="n"/>
-      <c r="AQ2" s="543" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="K2" s="605" t="n"/>
+      <c r="L2" s="275" t="n"/>
+      <c r="AQ2" s="606" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="544" t="n"/>
-      <c r="AS2" s="544" t="n"/>
-      <c r="AT2" s="544" t="n"/>
-      <c r="AU2" s="544" t="n"/>
-      <c r="AV2" s="545" t="n"/>
-      <c r="AW2" s="546" t="inlineStr">
+      <c r="AR2" s="607" t="n"/>
+      <c r="AS2" s="607" t="n"/>
+      <c r="AT2" s="607" t="n"/>
+      <c r="AU2" s="607" t="n"/>
+      <c r="AV2" s="608" t="n"/>
+      <c r="AW2" s="609" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="544" t="n"/>
-      <c r="AY2" s="544" t="n"/>
-      <c r="AZ2" s="544" t="n"/>
-      <c r="BA2" s="544" t="n"/>
-      <c r="BB2" s="544" t="n"/>
-      <c r="BC2" s="544" t="n"/>
-      <c r="BD2" s="547" t="n"/>
+      <c r="AX2" s="607" t="n"/>
+      <c r="AY2" s="607" t="n"/>
+      <c r="AZ2" s="607" t="n"/>
+      <c r="BA2" s="607" t="n"/>
+      <c r="BB2" s="607" t="n"/>
+      <c r="BC2" s="607" t="n"/>
+      <c r="BD2" s="610" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="54" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="10" t="n"/>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="10" t="n"/>
-      <c r="AI3" s="10" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="10" t="n"/>
-      <c r="AO3" s="10" t="n"/>
-      <c r="AP3" s="10" t="n"/>
-      <c r="AQ3" s="543" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="K3" s="605" t="n"/>
+      <c r="L3" s="275" t="n"/>
+      <c r="AQ3" s="606" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="544" t="n"/>
-      <c r="AS3" s="544" t="n"/>
-      <c r="AT3" s="544" t="n"/>
-      <c r="AU3" s="544" t="n"/>
-      <c r="AV3" s="545" t="n"/>
-      <c r="AW3" s="546" t="inlineStr">
+      <c r="AR3" s="607" t="n"/>
+      <c r="AS3" s="607" t="n"/>
+      <c r="AT3" s="607" t="n"/>
+      <c r="AU3" s="607" t="n"/>
+      <c r="AV3" s="608" t="n"/>
+      <c r="AW3" s="609" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="544" t="n"/>
-      <c r="AY3" s="544" t="n"/>
-      <c r="AZ3" s="544" t="n"/>
-      <c r="BA3" s="544" t="n"/>
-      <c r="BB3" s="544" t="n"/>
-      <c r="BC3" s="544" t="n"/>
-      <c r="BD3" s="547" t="n"/>
+      <c r="AX3" s="607" t="n"/>
+      <c r="AY3" s="607" t="n"/>
+      <c r="AZ3" s="607" t="n"/>
+      <c r="BA3" s="607" t="n"/>
+      <c r="BB3" s="607" t="n"/>
+      <c r="BC3" s="607" t="n"/>
+      <c r="BD3" s="610" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="10" t="n"/>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="54" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="K4" s="605" t="n"/>
       <c r="L4" s="548" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="10" t="n"/>
-      <c r="AE4" s="10" t="n"/>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="10" t="n"/>
-      <c r="AI4" s="10" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="10" t="n"/>
-      <c r="AO4" s="10" t="n"/>
-      <c r="AP4" s="10" t="n"/>
-      <c r="AQ4" s="543" t="inlineStr">
+      <c r="AQ4" s="606" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="544" t="n"/>
-      <c r="AS4" s="544" t="n"/>
-      <c r="AT4" s="544" t="n"/>
-      <c r="AU4" s="544" t="n"/>
-      <c r="AV4" s="545" t="n"/>
-      <c r="AW4" s="546" t="inlineStr">
+      <c r="AR4" s="607" t="n"/>
+      <c r="AS4" s="607" t="n"/>
+      <c r="AT4" s="607" t="n"/>
+      <c r="AU4" s="607" t="n"/>
+      <c r="AV4" s="608" t="n"/>
+      <c r="AW4" s="609" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="544" t="n"/>
-      <c r="AY4" s="544" t="n"/>
-      <c r="AZ4" s="544" t="n"/>
-      <c r="BA4" s="544" t="n"/>
-      <c r="BB4" s="544" t="n"/>
-      <c r="BC4" s="544" t="n"/>
-      <c r="BD4" s="547" t="n"/>
+      <c r="AX4" s="607" t="n"/>
+      <c r="AY4" s="607" t="n"/>
+      <c r="AZ4" s="607" t="n"/>
+      <c r="BA4" s="607" t="n"/>
+      <c r="BB4" s="607" t="n"/>
+      <c r="BC4" s="607" t="n"/>
+      <c r="BD4" s="610" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n"/>
-      <c r="E5" s="19" t="n"/>
-      <c r="F5" s="19" t="n"/>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
-      <c r="I5" s="19" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="24" t="n"/>
+      <c r="A5" s="280" t="n"/>
+      <c r="B5" s="281" t="n"/>
+      <c r="C5" s="281" t="n"/>
+      <c r="D5" s="281" t="n"/>
+      <c r="E5" s="281" t="n"/>
+      <c r="F5" s="281" t="n"/>
+      <c r="G5" s="281" t="n"/>
+      <c r="H5" s="281" t="n"/>
+      <c r="I5" s="281" t="n"/>
+      <c r="J5" s="281" t="n"/>
+      <c r="K5" s="283" t="n"/>
       <c r="L5" s="20" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="19" t="n"/>
-      <c r="N5" s="19" t="n"/>
-      <c r="O5" s="19" t="n"/>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="19" t="n"/>
-      <c r="R5" s="19" t="n"/>
-      <c r="S5" s="19" t="n"/>
-      <c r="T5" s="19" t="n"/>
-      <c r="U5" s="19" t="n"/>
-      <c r="V5" s="19" t="n"/>
-      <c r="W5" s="19" t="n"/>
-      <c r="X5" s="19" t="n"/>
-      <c r="Y5" s="19" t="n"/>
-      <c r="Z5" s="19" t="n"/>
-      <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="19" t="n"/>
-      <c r="AC5" s="19" t="n"/>
-      <c r="AD5" s="19" t="n"/>
-      <c r="AE5" s="19" t="n"/>
-      <c r="AF5" s="19" t="n"/>
-      <c r="AG5" s="19" t="n"/>
-      <c r="AH5" s="19" t="n"/>
-      <c r="AI5" s="19" t="n"/>
-      <c r="AJ5" s="19" t="n"/>
-      <c r="AK5" s="19" t="n"/>
-      <c r="AL5" s="19" t="n"/>
-      <c r="AM5" s="19" t="n"/>
-      <c r="AN5" s="19" t="n"/>
-      <c r="AO5" s="19" t="n"/>
-      <c r="AP5" s="19" t="n"/>
-      <c r="AQ5" s="549" t="inlineStr">
+      <c r="M5" s="281" t="n"/>
+      <c r="N5" s="281" t="n"/>
+      <c r="O5" s="281" t="n"/>
+      <c r="P5" s="281" t="n"/>
+      <c r="Q5" s="281" t="n"/>
+      <c r="R5" s="281" t="n"/>
+      <c r="S5" s="281" t="n"/>
+      <c r="T5" s="281" t="n"/>
+      <c r="U5" s="281" t="n"/>
+      <c r="V5" s="281" t="n"/>
+      <c r="W5" s="281" t="n"/>
+      <c r="X5" s="281" t="n"/>
+      <c r="Y5" s="281" t="n"/>
+      <c r="Z5" s="281" t="n"/>
+      <c r="AA5" s="281" t="n"/>
+      <c r="AB5" s="281" t="n"/>
+      <c r="AC5" s="281" t="n"/>
+      <c r="AD5" s="281" t="n"/>
+      <c r="AE5" s="281" t="n"/>
+      <c r="AF5" s="281" t="n"/>
+      <c r="AG5" s="281" t="n"/>
+      <c r="AH5" s="281" t="n"/>
+      <c r="AI5" s="281" t="n"/>
+      <c r="AJ5" s="281" t="n"/>
+      <c r="AK5" s="281" t="n"/>
+      <c r="AL5" s="281" t="n"/>
+      <c r="AM5" s="281" t="n"/>
+      <c r="AN5" s="281" t="n"/>
+      <c r="AO5" s="281" t="n"/>
+      <c r="AP5" s="281" t="n"/>
+      <c r="AQ5" s="611" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="550" t="n"/>
-      <c r="AS5" s="550" t="n"/>
-      <c r="AT5" s="550" t="n"/>
-      <c r="AU5" s="550" t="n"/>
-      <c r="AV5" s="551" t="n"/>
-      <c r="AW5" s="552" t="inlineStr">
+      <c r="AR5" s="612" t="n"/>
+      <c r="AS5" s="612" t="n"/>
+      <c r="AT5" s="612" t="n"/>
+      <c r="AU5" s="612" t="n"/>
+      <c r="AV5" s="613" t="n"/>
+      <c r="AW5" s="614" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="550" t="n"/>
-      <c r="AY5" s="550" t="n"/>
-      <c r="AZ5" s="550" t="n"/>
-      <c r="BA5" s="550" t="n"/>
-      <c r="BB5" s="550" t="n"/>
-      <c r="BC5" s="550" t="n"/>
-      <c r="BD5" s="553" t="n"/>
+      <c r="AX5" s="612" t="n"/>
+      <c r="AY5" s="612" t="n"/>
+      <c r="AZ5" s="612" t="n"/>
+      <c r="BA5" s="612" t="n"/>
+      <c r="BB5" s="612" t="n"/>
+      <c r="BC5" s="612" t="n"/>
+      <c r="BD5" s="615" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="515" t="n"/>
@@ -7161,396 +7277,396 @@
       <c r="BD6" s="515" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="554" t="inlineStr">
+      <c r="A7" s="616" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-      <c r="Q7" s="27" t="n"/>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n"/>
-      <c r="T7" s="27" t="n"/>
-      <c r="U7" s="27" t="n"/>
-      <c r="V7" s="27" t="n"/>
-      <c r="W7" s="27" t="n"/>
-      <c r="X7" s="27" t="n"/>
-      <c r="Y7" s="27" t="n"/>
-      <c r="Z7" s="27" t="n"/>
-      <c r="AA7" s="27" t="n"/>
-      <c r="AB7" s="27" t="n"/>
-      <c r="AC7" s="27" t="n"/>
-      <c r="AD7" s="27" t="n"/>
-      <c r="AE7" s="27" t="n"/>
-      <c r="AF7" s="27" t="n"/>
-      <c r="AG7" s="27" t="n"/>
-      <c r="AH7" s="27" t="n"/>
-      <c r="AI7" s="27" t="n"/>
-      <c r="AJ7" s="27" t="n"/>
-      <c r="AK7" s="27" t="n"/>
-      <c r="AL7" s="27" t="n"/>
-      <c r="AM7" s="27" t="n"/>
-      <c r="AN7" s="27" t="n"/>
-      <c r="AO7" s="27" t="n"/>
-      <c r="AP7" s="27" t="n"/>
-      <c r="AQ7" s="27" t="n"/>
-      <c r="AR7" s="27" t="n"/>
-      <c r="AS7" s="27" t="n"/>
-      <c r="AT7" s="27" t="n"/>
-      <c r="AU7" s="27" t="n"/>
-      <c r="AV7" s="27" t="n"/>
-      <c r="AW7" s="27" t="n"/>
-      <c r="AX7" s="27" t="n"/>
-      <c r="AY7" s="27" t="n"/>
-      <c r="AZ7" s="27" t="n"/>
-      <c r="BA7" s="27" t="n"/>
-      <c r="BB7" s="27" t="n"/>
-      <c r="BC7" s="27" t="n"/>
-      <c r="BD7" s="28" t="n"/>
+      <c r="B7" s="285" t="n"/>
+      <c r="C7" s="285" t="n"/>
+      <c r="D7" s="285" t="n"/>
+      <c r="E7" s="285" t="n"/>
+      <c r="F7" s="285" t="n"/>
+      <c r="G7" s="285" t="n"/>
+      <c r="H7" s="285" t="n"/>
+      <c r="I7" s="285" t="n"/>
+      <c r="J7" s="285" t="n"/>
+      <c r="K7" s="285" t="n"/>
+      <c r="L7" s="285" t="n"/>
+      <c r="M7" s="285" t="n"/>
+      <c r="N7" s="285" t="n"/>
+      <c r="O7" s="285" t="n"/>
+      <c r="P7" s="285" t="n"/>
+      <c r="Q7" s="285" t="n"/>
+      <c r="R7" s="285" t="n"/>
+      <c r="S7" s="285" t="n"/>
+      <c r="T7" s="285" t="n"/>
+      <c r="U7" s="285" t="n"/>
+      <c r="V7" s="285" t="n"/>
+      <c r="W7" s="285" t="n"/>
+      <c r="X7" s="285" t="n"/>
+      <c r="Y7" s="285" t="n"/>
+      <c r="Z7" s="285" t="n"/>
+      <c r="AA7" s="285" t="n"/>
+      <c r="AB7" s="285" t="n"/>
+      <c r="AC7" s="285" t="n"/>
+      <c r="AD7" s="285" t="n"/>
+      <c r="AE7" s="285" t="n"/>
+      <c r="AF7" s="285" t="n"/>
+      <c r="AG7" s="285" t="n"/>
+      <c r="AH7" s="285" t="n"/>
+      <c r="AI7" s="285" t="n"/>
+      <c r="AJ7" s="285" t="n"/>
+      <c r="AK7" s="285" t="n"/>
+      <c r="AL7" s="285" t="n"/>
+      <c r="AM7" s="285" t="n"/>
+      <c r="AN7" s="285" t="n"/>
+      <c r="AO7" s="285" t="n"/>
+      <c r="AP7" s="285" t="n"/>
+      <c r="AQ7" s="285" t="n"/>
+      <c r="AR7" s="285" t="n"/>
+      <c r="AS7" s="285" t="n"/>
+      <c r="AT7" s="285" t="n"/>
+      <c r="AU7" s="285" t="n"/>
+      <c r="AV7" s="285" t="n"/>
+      <c r="AW7" s="285" t="n"/>
+      <c r="AX7" s="285" t="n"/>
+      <c r="AY7" s="285" t="n"/>
+      <c r="AZ7" s="285" t="n"/>
+      <c r="BA7" s="285" t="n"/>
+      <c r="BB7" s="285" t="n"/>
+      <c r="BC7" s="285" t="n"/>
+      <c r="BD7" s="286" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="555" t="inlineStr">
+      <c r="A8" s="617" t="inlineStr">
         <is>
           <t>Final Inspection Report ID</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="556" t="n"/>
-      <c r="L8" s="557" t="n"/>
-      <c r="M8" s="557" t="n"/>
-      <c r="N8" s="557" t="n"/>
-      <c r="O8" s="557" t="n"/>
-      <c r="P8" s="557" t="n"/>
-      <c r="Q8" s="557" t="n"/>
-      <c r="R8" s="557" t="n"/>
-      <c r="S8" s="557" t="n"/>
-      <c r="T8" s="557" t="n"/>
-      <c r="U8" s="557" t="n"/>
-      <c r="V8" s="557" t="n"/>
-      <c r="W8" s="557" t="n"/>
-      <c r="X8" s="557" t="n"/>
-      <c r="Y8" s="557" t="n"/>
-      <c r="Z8" s="557" t="n"/>
-      <c r="AA8" s="557" t="n"/>
-      <c r="AB8" s="558" t="n"/>
-      <c r="AC8" s="559" t="inlineStr">
+      <c r="B8" s="271" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="271" t="n"/>
+      <c r="F8" s="271" t="n"/>
+      <c r="G8" s="271" t="n"/>
+      <c r="H8" s="271" t="n"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="272" t="n"/>
+      <c r="K8" s="288" t="n"/>
+      <c r="L8" s="321" t="n"/>
+      <c r="M8" s="321" t="n"/>
+      <c r="N8" s="321" t="n"/>
+      <c r="O8" s="321" t="n"/>
+      <c r="P8" s="321" t="n"/>
+      <c r="Q8" s="321" t="n"/>
+      <c r="R8" s="321" t="n"/>
+      <c r="S8" s="321" t="n"/>
+      <c r="T8" s="321" t="n"/>
+      <c r="U8" s="321" t="n"/>
+      <c r="V8" s="321" t="n"/>
+      <c r="W8" s="321" t="n"/>
+      <c r="X8" s="321" t="n"/>
+      <c r="Y8" s="321" t="n"/>
+      <c r="Z8" s="321" t="n"/>
+      <c r="AA8" s="321" t="n"/>
+      <c r="AB8" s="322" t="n"/>
+      <c r="AC8" s="618" t="inlineStr">
         <is>
           <t>Final Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="5" t="n"/>
-      <c r="AE8" s="5" t="n"/>
-      <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="5" t="n"/>
-      <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="5" t="n"/>
-      <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="6" t="n"/>
-      <c r="AM8" s="556" t="n"/>
-      <c r="AN8" s="557" t="n"/>
-      <c r="AO8" s="557" t="n"/>
-      <c r="AP8" s="557" t="n"/>
-      <c r="AQ8" s="557" t="n"/>
-      <c r="AR8" s="557" t="n"/>
-      <c r="AS8" s="557" t="n"/>
-      <c r="AT8" s="557" t="n"/>
-      <c r="AU8" s="557" t="n"/>
-      <c r="AV8" s="557" t="n"/>
-      <c r="AW8" s="557" t="n"/>
-      <c r="AX8" s="557" t="n"/>
-      <c r="AY8" s="557" t="n"/>
-      <c r="AZ8" s="557" t="n"/>
-      <c r="BA8" s="557" t="n"/>
-      <c r="BB8" s="557" t="n"/>
-      <c r="BC8" s="557" t="n"/>
-      <c r="BD8" s="560" t="n"/>
+      <c r="AD8" s="271" t="n"/>
+      <c r="AE8" s="271" t="n"/>
+      <c r="AF8" s="271" t="n"/>
+      <c r="AG8" s="271" t="n"/>
+      <c r="AH8" s="271" t="n"/>
+      <c r="AI8" s="271" t="n"/>
+      <c r="AJ8" s="271" t="n"/>
+      <c r="AK8" s="271" t="n"/>
+      <c r="AL8" s="272" t="n"/>
+      <c r="AM8" s="290" t="n"/>
+      <c r="AN8" s="321" t="n"/>
+      <c r="AO8" s="321" t="n"/>
+      <c r="AP8" s="321" t="n"/>
+      <c r="AQ8" s="321" t="n"/>
+      <c r="AR8" s="321" t="n"/>
+      <c r="AS8" s="321" t="n"/>
+      <c r="AT8" s="321" t="n"/>
+      <c r="AU8" s="321" t="n"/>
+      <c r="AV8" s="321" t="n"/>
+      <c r="AW8" s="321" t="n"/>
+      <c r="AX8" s="321" t="n"/>
+      <c r="AY8" s="321" t="n"/>
+      <c r="AZ8" s="321" t="n"/>
+      <c r="BA8" s="321" t="n"/>
+      <c r="BB8" s="321" t="n"/>
+      <c r="BC8" s="321" t="n"/>
+      <c r="BD8" s="323" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="561" t="inlineStr">
+      <c r="A9" s="619" t="inlineStr">
         <is>
           <t>Job / Shipment</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="562" t="n"/>
-      <c r="L9" s="563" t="n"/>
-      <c r="M9" s="563" t="n"/>
-      <c r="N9" s="563" t="n"/>
-      <c r="O9" s="563" t="n"/>
-      <c r="P9" s="563" t="n"/>
-      <c r="Q9" s="563" t="n"/>
-      <c r="R9" s="563" t="n"/>
-      <c r="S9" s="563" t="n"/>
-      <c r="T9" s="563" t="n"/>
-      <c r="U9" s="563" t="n"/>
-      <c r="V9" s="563" t="n"/>
-      <c r="W9" s="563" t="n"/>
-      <c r="X9" s="563" t="n"/>
-      <c r="Y9" s="563" t="n"/>
-      <c r="Z9" s="563" t="n"/>
-      <c r="AA9" s="563" t="n"/>
-      <c r="AB9" s="564" t="n"/>
-      <c r="AC9" s="565" t="inlineStr">
+      <c r="B9" s="276" t="n"/>
+      <c r="C9" s="276" t="n"/>
+      <c r="D9" s="276" t="n"/>
+      <c r="E9" s="276" t="n"/>
+      <c r="F9" s="276" t="n"/>
+      <c r="G9" s="276" t="n"/>
+      <c r="H9" s="276" t="n"/>
+      <c r="I9" s="276" t="n"/>
+      <c r="J9" s="277" t="n"/>
+      <c r="K9" s="296" t="n"/>
+      <c r="L9" s="324" t="n"/>
+      <c r="M9" s="324" t="n"/>
+      <c r="N9" s="324" t="n"/>
+      <c r="O9" s="324" t="n"/>
+      <c r="P9" s="324" t="n"/>
+      <c r="Q9" s="324" t="n"/>
+      <c r="R9" s="324" t="n"/>
+      <c r="S9" s="324" t="n"/>
+      <c r="T9" s="324" t="n"/>
+      <c r="U9" s="324" t="n"/>
+      <c r="V9" s="324" t="n"/>
+      <c r="W9" s="324" t="n"/>
+      <c r="X9" s="324" t="n"/>
+      <c r="Y9" s="324" t="n"/>
+      <c r="Z9" s="324" t="n"/>
+      <c r="AA9" s="324" t="n"/>
+      <c r="AB9" s="325" t="n"/>
+      <c r="AC9" s="620" t="inlineStr">
         <is>
           <t>Part No. / Revision</t>
         </is>
       </c>
-      <c r="AD9" s="12" t="n"/>
-      <c r="AE9" s="12" t="n"/>
-      <c r="AF9" s="12" t="n"/>
-      <c r="AG9" s="12" t="n"/>
-      <c r="AH9" s="12" t="n"/>
-      <c r="AI9" s="12" t="n"/>
-      <c r="AJ9" s="12" t="n"/>
-      <c r="AK9" s="12" t="n"/>
-      <c r="AL9" s="13" t="n"/>
-      <c r="AM9" s="562" t="n"/>
-      <c r="AN9" s="563" t="n"/>
-      <c r="AO9" s="563" t="n"/>
-      <c r="AP9" s="563" t="n"/>
-      <c r="AQ9" s="563" t="n"/>
-      <c r="AR9" s="563" t="n"/>
-      <c r="AS9" s="563" t="n"/>
-      <c r="AT9" s="563" t="n"/>
-      <c r="AU9" s="563" t="n"/>
-      <c r="AV9" s="563" t="n"/>
-      <c r="AW9" s="563" t="n"/>
-      <c r="AX9" s="563" t="n"/>
-      <c r="AY9" s="563" t="n"/>
-      <c r="AZ9" s="563" t="n"/>
-      <c r="BA9" s="563" t="n"/>
-      <c r="BB9" s="563" t="n"/>
-      <c r="BC9" s="563" t="n"/>
-      <c r="BD9" s="566" t="n"/>
+      <c r="AD9" s="276" t="n"/>
+      <c r="AE9" s="276" t="n"/>
+      <c r="AF9" s="276" t="n"/>
+      <c r="AG9" s="276" t="n"/>
+      <c r="AH9" s="276" t="n"/>
+      <c r="AI9" s="276" t="n"/>
+      <c r="AJ9" s="276" t="n"/>
+      <c r="AK9" s="276" t="n"/>
+      <c r="AL9" s="277" t="n"/>
+      <c r="AM9" s="621" t="n"/>
+      <c r="AN9" s="324" t="n"/>
+      <c r="AO9" s="324" t="n"/>
+      <c r="AP9" s="324" t="n"/>
+      <c r="AQ9" s="324" t="n"/>
+      <c r="AR9" s="324" t="n"/>
+      <c r="AS9" s="324" t="n"/>
+      <c r="AT9" s="324" t="n"/>
+      <c r="AU9" s="324" t="n"/>
+      <c r="AV9" s="324" t="n"/>
+      <c r="AW9" s="324" t="n"/>
+      <c r="AX9" s="324" t="n"/>
+      <c r="AY9" s="324" t="n"/>
+      <c r="AZ9" s="324" t="n"/>
+      <c r="BA9" s="324" t="n"/>
+      <c r="BB9" s="324" t="n"/>
+      <c r="BC9" s="324" t="n"/>
+      <c r="BD9" s="326" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="561" t="inlineStr">
+      <c r="A10" s="619" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="562" t="n"/>
-      <c r="L10" s="563" t="n"/>
-      <c r="M10" s="563" t="n"/>
-      <c r="N10" s="563" t="n"/>
-      <c r="O10" s="563" t="n"/>
-      <c r="P10" s="563" t="n"/>
-      <c r="Q10" s="563" t="n"/>
-      <c r="R10" s="563" t="n"/>
-      <c r="S10" s="563" t="n"/>
-      <c r="T10" s="563" t="n"/>
-      <c r="U10" s="563" t="n"/>
-      <c r="V10" s="563" t="n"/>
-      <c r="W10" s="563" t="n"/>
-      <c r="X10" s="563" t="n"/>
-      <c r="Y10" s="563" t="n"/>
-      <c r="Z10" s="563" t="n"/>
-      <c r="AA10" s="563" t="n"/>
-      <c r="AB10" s="564" t="n"/>
-      <c r="AC10" s="565" t="inlineStr">
+      <c r="B10" s="276" t="n"/>
+      <c r="C10" s="276" t="n"/>
+      <c r="D10" s="276" t="n"/>
+      <c r="E10" s="276" t="n"/>
+      <c r="F10" s="276" t="n"/>
+      <c r="G10" s="276" t="n"/>
+      <c r="H10" s="276" t="n"/>
+      <c r="I10" s="276" t="n"/>
+      <c r="J10" s="277" t="n"/>
+      <c r="K10" s="296" t="n"/>
+      <c r="L10" s="324" t="n"/>
+      <c r="M10" s="324" t="n"/>
+      <c r="N10" s="324" t="n"/>
+      <c r="O10" s="324" t="n"/>
+      <c r="P10" s="324" t="n"/>
+      <c r="Q10" s="324" t="n"/>
+      <c r="R10" s="324" t="n"/>
+      <c r="S10" s="324" t="n"/>
+      <c r="T10" s="324" t="n"/>
+      <c r="U10" s="324" t="n"/>
+      <c r="V10" s="324" t="n"/>
+      <c r="W10" s="324" t="n"/>
+      <c r="X10" s="324" t="n"/>
+      <c r="Y10" s="324" t="n"/>
+      <c r="Z10" s="324" t="n"/>
+      <c r="AA10" s="324" t="n"/>
+      <c r="AB10" s="325" t="n"/>
+      <c r="AC10" s="620" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="AD10" s="12" t="n"/>
-      <c r="AE10" s="12" t="n"/>
-      <c r="AF10" s="12" t="n"/>
-      <c r="AG10" s="12" t="n"/>
-      <c r="AH10" s="12" t="n"/>
-      <c r="AI10" s="12" t="n"/>
-      <c r="AJ10" s="12" t="n"/>
-      <c r="AK10" s="12" t="n"/>
-      <c r="AL10" s="13" t="n"/>
-      <c r="AM10" s="562" t="n"/>
-      <c r="AN10" s="563" t="n"/>
-      <c r="AO10" s="563" t="n"/>
-      <c r="AP10" s="563" t="n"/>
-      <c r="AQ10" s="563" t="n"/>
-      <c r="AR10" s="563" t="n"/>
-      <c r="AS10" s="563" t="n"/>
-      <c r="AT10" s="563" t="n"/>
-      <c r="AU10" s="563" t="n"/>
-      <c r="AV10" s="563" t="n"/>
-      <c r="AW10" s="563" t="n"/>
-      <c r="AX10" s="563" t="n"/>
-      <c r="AY10" s="563" t="n"/>
-      <c r="AZ10" s="563" t="n"/>
-      <c r="BA10" s="563" t="n"/>
-      <c r="BB10" s="563" t="n"/>
-      <c r="BC10" s="563" t="n"/>
-      <c r="BD10" s="566" t="n"/>
+      <c r="AD10" s="276" t="n"/>
+      <c r="AE10" s="276" t="n"/>
+      <c r="AF10" s="276" t="n"/>
+      <c r="AG10" s="276" t="n"/>
+      <c r="AH10" s="276" t="n"/>
+      <c r="AI10" s="276" t="n"/>
+      <c r="AJ10" s="276" t="n"/>
+      <c r="AK10" s="276" t="n"/>
+      <c r="AL10" s="277" t="n"/>
+      <c r="AM10" s="621" t="n"/>
+      <c r="AN10" s="324" t="n"/>
+      <c r="AO10" s="324" t="n"/>
+      <c r="AP10" s="324" t="n"/>
+      <c r="AQ10" s="324" t="n"/>
+      <c r="AR10" s="324" t="n"/>
+      <c r="AS10" s="324" t="n"/>
+      <c r="AT10" s="324" t="n"/>
+      <c r="AU10" s="324" t="n"/>
+      <c r="AV10" s="324" t="n"/>
+      <c r="AW10" s="324" t="n"/>
+      <c r="AX10" s="324" t="n"/>
+      <c r="AY10" s="324" t="n"/>
+      <c r="AZ10" s="324" t="n"/>
+      <c r="BA10" s="324" t="n"/>
+      <c r="BB10" s="324" t="n"/>
+      <c r="BC10" s="324" t="n"/>
+      <c r="BD10" s="326" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="561" t="inlineStr">
+      <c r="A11" s="619" t="inlineStr">
         <is>
           <t>Inspection Basis</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="562" t="n"/>
-      <c r="L11" s="563" t="n"/>
-      <c r="M11" s="563" t="n"/>
-      <c r="N11" s="563" t="n"/>
-      <c r="O11" s="563" t="n"/>
-      <c r="P11" s="563" t="n"/>
-      <c r="Q11" s="563" t="n"/>
-      <c r="R11" s="563" t="n"/>
-      <c r="S11" s="563" t="n"/>
-      <c r="T11" s="563" t="n"/>
-      <c r="U11" s="563" t="n"/>
-      <c r="V11" s="563" t="n"/>
-      <c r="W11" s="563" t="n"/>
-      <c r="X11" s="563" t="n"/>
-      <c r="Y11" s="563" t="n"/>
-      <c r="Z11" s="563" t="n"/>
-      <c r="AA11" s="563" t="n"/>
-      <c r="AB11" s="564" t="n"/>
-      <c r="AC11" s="565" t="inlineStr">
+      <c r="B11" s="276" t="n"/>
+      <c r="C11" s="276" t="n"/>
+      <c r="D11" s="276" t="n"/>
+      <c r="E11" s="276" t="n"/>
+      <c r="F11" s="276" t="n"/>
+      <c r="G11" s="276" t="n"/>
+      <c r="H11" s="276" t="n"/>
+      <c r="I11" s="276" t="n"/>
+      <c r="J11" s="277" t="n"/>
+      <c r="K11" s="296" t="n"/>
+      <c r="L11" s="324" t="n"/>
+      <c r="M11" s="324" t="n"/>
+      <c r="N11" s="324" t="n"/>
+      <c r="O11" s="324" t="n"/>
+      <c r="P11" s="324" t="n"/>
+      <c r="Q11" s="324" t="n"/>
+      <c r="R11" s="324" t="n"/>
+      <c r="S11" s="324" t="n"/>
+      <c r="T11" s="324" t="n"/>
+      <c r="U11" s="324" t="n"/>
+      <c r="V11" s="324" t="n"/>
+      <c r="W11" s="324" t="n"/>
+      <c r="X11" s="324" t="n"/>
+      <c r="Y11" s="324" t="n"/>
+      <c r="Z11" s="324" t="n"/>
+      <c r="AA11" s="324" t="n"/>
+      <c r="AB11" s="325" t="n"/>
+      <c r="AC11" s="620" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="AD11" s="12" t="n"/>
-      <c r="AE11" s="12" t="n"/>
-      <c r="AF11" s="12" t="n"/>
-      <c r="AG11" s="12" t="n"/>
-      <c r="AH11" s="12" t="n"/>
-      <c r="AI11" s="12" t="n"/>
-      <c r="AJ11" s="12" t="n"/>
-      <c r="AK11" s="12" t="n"/>
-      <c r="AL11" s="13" t="n"/>
-      <c r="AM11" s="562" t="n"/>
-      <c r="AN11" s="563" t="n"/>
-      <c r="AO11" s="563" t="n"/>
-      <c r="AP11" s="563" t="n"/>
-      <c r="AQ11" s="563" t="n"/>
-      <c r="AR11" s="563" t="n"/>
-      <c r="AS11" s="563" t="n"/>
-      <c r="AT11" s="563" t="n"/>
-      <c r="AU11" s="563" t="n"/>
-      <c r="AV11" s="563" t="n"/>
-      <c r="AW11" s="563" t="n"/>
-      <c r="AX11" s="563" t="n"/>
-      <c r="AY11" s="563" t="n"/>
-      <c r="AZ11" s="563" t="n"/>
-      <c r="BA11" s="563" t="n"/>
-      <c r="BB11" s="563" t="n"/>
-      <c r="BC11" s="563" t="n"/>
-      <c r="BD11" s="566" t="n"/>
+      <c r="AD11" s="276" t="n"/>
+      <c r="AE11" s="276" t="n"/>
+      <c r="AF11" s="276" t="n"/>
+      <c r="AG11" s="276" t="n"/>
+      <c r="AH11" s="276" t="n"/>
+      <c r="AI11" s="276" t="n"/>
+      <c r="AJ11" s="276" t="n"/>
+      <c r="AK11" s="276" t="n"/>
+      <c r="AL11" s="277" t="n"/>
+      <c r="AM11" s="621" t="n"/>
+      <c r="AN11" s="324" t="n"/>
+      <c r="AO11" s="324" t="n"/>
+      <c r="AP11" s="324" t="n"/>
+      <c r="AQ11" s="324" t="n"/>
+      <c r="AR11" s="324" t="n"/>
+      <c r="AS11" s="324" t="n"/>
+      <c r="AT11" s="324" t="n"/>
+      <c r="AU11" s="324" t="n"/>
+      <c r="AV11" s="324" t="n"/>
+      <c r="AW11" s="324" t="n"/>
+      <c r="AX11" s="324" t="n"/>
+      <c r="AY11" s="324" t="n"/>
+      <c r="AZ11" s="324" t="n"/>
+      <c r="BA11" s="324" t="n"/>
+      <c r="BB11" s="324" t="n"/>
+      <c r="BC11" s="324" t="n"/>
+      <c r="BD11" s="326" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="567" t="inlineStr">
+      <c r="A12" s="622" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n"/>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="22" t="n"/>
-      <c r="K12" s="568" t="n"/>
-      <c r="L12" s="569" t="n"/>
-      <c r="M12" s="569" t="n"/>
-      <c r="N12" s="569" t="n"/>
-      <c r="O12" s="569" t="n"/>
-      <c r="P12" s="569" t="n"/>
-      <c r="Q12" s="569" t="n"/>
-      <c r="R12" s="569" t="n"/>
-      <c r="S12" s="569" t="n"/>
-      <c r="T12" s="569" t="n"/>
-      <c r="U12" s="569" t="n"/>
-      <c r="V12" s="569" t="n"/>
-      <c r="W12" s="569" t="n"/>
-      <c r="X12" s="569" t="n"/>
-      <c r="Y12" s="569" t="n"/>
-      <c r="Z12" s="569" t="n"/>
-      <c r="AA12" s="569" t="n"/>
-      <c r="AB12" s="570" t="n"/>
-      <c r="AC12" s="571" t="inlineStr">
+      <c r="B12" s="281" t="n"/>
+      <c r="C12" s="281" t="n"/>
+      <c r="D12" s="281" t="n"/>
+      <c r="E12" s="281" t="n"/>
+      <c r="F12" s="281" t="n"/>
+      <c r="G12" s="281" t="n"/>
+      <c r="H12" s="281" t="n"/>
+      <c r="I12" s="281" t="n"/>
+      <c r="J12" s="282" t="n"/>
+      <c r="K12" s="623" t="n"/>
+      <c r="L12" s="335" t="n"/>
+      <c r="M12" s="335" t="n"/>
+      <c r="N12" s="335" t="n"/>
+      <c r="O12" s="335" t="n"/>
+      <c r="P12" s="335" t="n"/>
+      <c r="Q12" s="335" t="n"/>
+      <c r="R12" s="335" t="n"/>
+      <c r="S12" s="335" t="n"/>
+      <c r="T12" s="335" t="n"/>
+      <c r="U12" s="335" t="n"/>
+      <c r="V12" s="335" t="n"/>
+      <c r="W12" s="335" t="n"/>
+      <c r="X12" s="335" t="n"/>
+      <c r="Y12" s="335" t="n"/>
+      <c r="Z12" s="335" t="n"/>
+      <c r="AA12" s="335" t="n"/>
+      <c r="AB12" s="624" t="n"/>
+      <c r="AC12" s="625" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="19" t="n"/>
-      <c r="AE12" s="19" t="n"/>
-      <c r="AF12" s="19" t="n"/>
-      <c r="AG12" s="19" t="n"/>
-      <c r="AH12" s="19" t="n"/>
-      <c r="AI12" s="19" t="n"/>
-      <c r="AJ12" s="19" t="n"/>
-      <c r="AK12" s="19" t="n"/>
-      <c r="AL12" s="22" t="n"/>
-      <c r="AM12" s="568" t="n"/>
-      <c r="AN12" s="569" t="n"/>
-      <c r="AO12" s="569" t="n"/>
-      <c r="AP12" s="569" t="n"/>
-      <c r="AQ12" s="569" t="n"/>
-      <c r="AR12" s="569" t="n"/>
-      <c r="AS12" s="569" t="n"/>
-      <c r="AT12" s="569" t="n"/>
-      <c r="AU12" s="569" t="n"/>
-      <c r="AV12" s="569" t="n"/>
-      <c r="AW12" s="569" t="n"/>
-      <c r="AX12" s="569" t="n"/>
-      <c r="AY12" s="569" t="n"/>
-      <c r="AZ12" s="569" t="n"/>
-      <c r="BA12" s="569" t="n"/>
-      <c r="BB12" s="569" t="n"/>
-      <c r="BC12" s="569" t="n"/>
-      <c r="BD12" s="572" t="n"/>
+      <c r="AD12" s="281" t="n"/>
+      <c r="AE12" s="281" t="n"/>
+      <c r="AF12" s="281" t="n"/>
+      <c r="AG12" s="281" t="n"/>
+      <c r="AH12" s="281" t="n"/>
+      <c r="AI12" s="281" t="n"/>
+      <c r="AJ12" s="281" t="n"/>
+      <c r="AK12" s="281" t="n"/>
+      <c r="AL12" s="282" t="n"/>
+      <c r="AM12" s="626" t="n"/>
+      <c r="AN12" s="335" t="n"/>
+      <c r="AO12" s="335" t="n"/>
+      <c r="AP12" s="335" t="n"/>
+      <c r="AQ12" s="335" t="n"/>
+      <c r="AR12" s="335" t="n"/>
+      <c r="AS12" s="335" t="n"/>
+      <c r="AT12" s="335" t="n"/>
+      <c r="AU12" s="335" t="n"/>
+      <c r="AV12" s="335" t="n"/>
+      <c r="AW12" s="335" t="n"/>
+      <c r="AX12" s="335" t="n"/>
+      <c r="AY12" s="335" t="n"/>
+      <c r="AZ12" s="335" t="n"/>
+      <c r="BA12" s="335" t="n"/>
+      <c r="BB12" s="335" t="n"/>
+      <c r="BC12" s="335" t="n"/>
+      <c r="BD12" s="336" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="573" t="n"/>
@@ -7611,607 +7727,607 @@
       <c r="BD13" s="573" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="554" t="inlineStr">
+      <c r="A14" s="616" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="27" t="n"/>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
-      <c r="Q14" s="27" t="n"/>
-      <c r="R14" s="27" t="n"/>
-      <c r="S14" s="27" t="n"/>
-      <c r="T14" s="27" t="n"/>
-      <c r="U14" s="27" t="n"/>
-      <c r="V14" s="27" t="n"/>
-      <c r="W14" s="27" t="n"/>
-      <c r="X14" s="27" t="n"/>
-      <c r="Y14" s="27" t="n"/>
-      <c r="Z14" s="27" t="n"/>
-      <c r="AA14" s="27" t="n"/>
-      <c r="AB14" s="27" t="n"/>
-      <c r="AC14" s="27" t="n"/>
-      <c r="AD14" s="27" t="n"/>
-      <c r="AE14" s="27" t="n"/>
-      <c r="AF14" s="27" t="n"/>
-      <c r="AG14" s="27" t="n"/>
-      <c r="AH14" s="27" t="n"/>
-      <c r="AI14" s="27" t="n"/>
-      <c r="AJ14" s="27" t="n"/>
-      <c r="AK14" s="27" t="n"/>
-      <c r="AL14" s="27" t="n"/>
-      <c r="AM14" s="27" t="n"/>
-      <c r="AN14" s="27" t="n"/>
-      <c r="AO14" s="27" t="n"/>
-      <c r="AP14" s="27" t="n"/>
-      <c r="AQ14" s="27" t="n"/>
-      <c r="AR14" s="27" t="n"/>
-      <c r="AS14" s="27" t="n"/>
-      <c r="AT14" s="27" t="n"/>
-      <c r="AU14" s="27" t="n"/>
-      <c r="AV14" s="27" t="n"/>
-      <c r="AW14" s="27" t="n"/>
-      <c r="AX14" s="27" t="n"/>
-      <c r="AY14" s="27" t="n"/>
-      <c r="AZ14" s="27" t="n"/>
-      <c r="BA14" s="27" t="n"/>
-      <c r="BB14" s="27" t="n"/>
-      <c r="BC14" s="27" t="n"/>
-      <c r="BD14" s="28" t="n"/>
+      <c r="B14" s="285" t="n"/>
+      <c r="C14" s="285" t="n"/>
+      <c r="D14" s="285" t="n"/>
+      <c r="E14" s="285" t="n"/>
+      <c r="F14" s="285" t="n"/>
+      <c r="G14" s="285" t="n"/>
+      <c r="H14" s="285" t="n"/>
+      <c r="I14" s="285" t="n"/>
+      <c r="J14" s="285" t="n"/>
+      <c r="K14" s="285" t="n"/>
+      <c r="L14" s="285" t="n"/>
+      <c r="M14" s="285" t="n"/>
+      <c r="N14" s="285" t="n"/>
+      <c r="O14" s="285" t="n"/>
+      <c r="P14" s="285" t="n"/>
+      <c r="Q14" s="285" t="n"/>
+      <c r="R14" s="285" t="n"/>
+      <c r="S14" s="285" t="n"/>
+      <c r="T14" s="285" t="n"/>
+      <c r="U14" s="285" t="n"/>
+      <c r="V14" s="285" t="n"/>
+      <c r="W14" s="285" t="n"/>
+      <c r="X14" s="285" t="n"/>
+      <c r="Y14" s="285" t="n"/>
+      <c r="Z14" s="285" t="n"/>
+      <c r="AA14" s="285" t="n"/>
+      <c r="AB14" s="285" t="n"/>
+      <c r="AC14" s="285" t="n"/>
+      <c r="AD14" s="285" t="n"/>
+      <c r="AE14" s="285" t="n"/>
+      <c r="AF14" s="285" t="n"/>
+      <c r="AG14" s="285" t="n"/>
+      <c r="AH14" s="285" t="n"/>
+      <c r="AI14" s="285" t="n"/>
+      <c r="AJ14" s="285" t="n"/>
+      <c r="AK14" s="285" t="n"/>
+      <c r="AL14" s="285" t="n"/>
+      <c r="AM14" s="285" t="n"/>
+      <c r="AN14" s="285" t="n"/>
+      <c r="AO14" s="285" t="n"/>
+      <c r="AP14" s="285" t="n"/>
+      <c r="AQ14" s="285" t="n"/>
+      <c r="AR14" s="285" t="n"/>
+      <c r="AS14" s="285" t="n"/>
+      <c r="AT14" s="285" t="n"/>
+      <c r="AU14" s="285" t="n"/>
+      <c r="AV14" s="285" t="n"/>
+      <c r="AW14" s="285" t="n"/>
+      <c r="AX14" s="285" t="n"/>
+      <c r="AY14" s="285" t="n"/>
+      <c r="AZ14" s="285" t="n"/>
+      <c r="BA14" s="285" t="n"/>
+      <c r="BB14" s="285" t="n"/>
+      <c r="BC14" s="285" t="n"/>
+      <c r="BD14" s="286" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="291" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="37" t="inlineStr">
+      <c r="B15" s="271" t="n"/>
+      <c r="C15" s="272" t="n"/>
+      <c r="D15" s="292" t="inlineStr">
         <is>
           <t>Check Group</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="37" t="inlineStr">
+      <c r="E15" s="271" t="n"/>
+      <c r="F15" s="271" t="n"/>
+      <c r="G15" s="272" t="n"/>
+      <c r="H15" s="292" t="inlineStr">
         <is>
           <t>Characteristic / Requirement</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-      <c r="Y15" s="5" t="n"/>
-      <c r="Z15" s="6" t="n"/>
-      <c r="AA15" s="37" t="inlineStr">
+      <c r="I15" s="271" t="n"/>
+      <c r="J15" s="271" t="n"/>
+      <c r="K15" s="271" t="n"/>
+      <c r="L15" s="271" t="n"/>
+      <c r="M15" s="271" t="n"/>
+      <c r="N15" s="271" t="n"/>
+      <c r="O15" s="271" t="n"/>
+      <c r="P15" s="271" t="n"/>
+      <c r="Q15" s="271" t="n"/>
+      <c r="R15" s="271" t="n"/>
+      <c r="S15" s="271" t="n"/>
+      <c r="T15" s="271" t="n"/>
+      <c r="U15" s="271" t="n"/>
+      <c r="V15" s="271" t="n"/>
+      <c r="W15" s="271" t="n"/>
+      <c r="X15" s="271" t="n"/>
+      <c r="Y15" s="271" t="n"/>
+      <c r="Z15" s="272" t="n"/>
+      <c r="AA15" s="292" t="inlineStr">
         <is>
           <t>Method / Inspection Basis</t>
         </is>
       </c>
-      <c r="AB15" s="5" t="n"/>
-      <c r="AC15" s="5" t="n"/>
-      <c r="AD15" s="5" t="n"/>
-      <c r="AE15" s="5" t="n"/>
-      <c r="AF15" s="5" t="n"/>
-      <c r="AG15" s="5" t="n"/>
-      <c r="AH15" s="5" t="n"/>
-      <c r="AI15" s="5" t="n"/>
-      <c r="AJ15" s="5" t="n"/>
-      <c r="AK15" s="5" t="n"/>
-      <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="5" t="n"/>
-      <c r="AN15" s="5" t="n"/>
-      <c r="AO15" s="5" t="n"/>
-      <c r="AP15" s="5" t="n"/>
-      <c r="AQ15" s="6" t="n"/>
-      <c r="AR15" s="37" t="inlineStr">
+      <c r="AB15" s="271" t="n"/>
+      <c r="AC15" s="271" t="n"/>
+      <c r="AD15" s="271" t="n"/>
+      <c r="AE15" s="271" t="n"/>
+      <c r="AF15" s="271" t="n"/>
+      <c r="AG15" s="271" t="n"/>
+      <c r="AH15" s="271" t="n"/>
+      <c r="AI15" s="271" t="n"/>
+      <c r="AJ15" s="271" t="n"/>
+      <c r="AK15" s="271" t="n"/>
+      <c r="AL15" s="271" t="n"/>
+      <c r="AM15" s="271" t="n"/>
+      <c r="AN15" s="271" t="n"/>
+      <c r="AO15" s="271" t="n"/>
+      <c r="AP15" s="271" t="n"/>
+      <c r="AQ15" s="272" t="n"/>
+      <c r="AR15" s="292" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="5" t="n"/>
-      <c r="AT15" s="5" t="n"/>
-      <c r="AU15" s="5" t="n"/>
-      <c r="AV15" s="5" t="n"/>
-      <c r="AW15" s="6" t="n"/>
-      <c r="AX15" s="37" t="inlineStr">
+      <c r="AS15" s="271" t="n"/>
+      <c r="AT15" s="271" t="n"/>
+      <c r="AU15" s="271" t="n"/>
+      <c r="AV15" s="271" t="n"/>
+      <c r="AW15" s="272" t="n"/>
+      <c r="AX15" s="292" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY15" s="5" t="n"/>
-      <c r="AZ15" s="5" t="n"/>
-      <c r="BA15" s="6" t="n"/>
-      <c r="BB15" s="37" t="inlineStr">
+      <c r="AY15" s="271" t="n"/>
+      <c r="AZ15" s="271" t="n"/>
+      <c r="BA15" s="272" t="n"/>
+      <c r="BB15" s="293" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="5" t="n"/>
-      <c r="BD15" s="8" t="n"/>
+      <c r="BC15" s="271" t="n"/>
+      <c r="BD15" s="274" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="574">
+      <c r="A16" s="627">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="575" t="inlineStr">
+      <c r="B16" s="271" t="n"/>
+      <c r="C16" s="272" t="n"/>
+      <c r="D16" s="628" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="557" t="n"/>
-      <c r="F16" s="557" t="n"/>
-      <c r="G16" s="558" t="n"/>
-      <c r="H16" s="556" t="n"/>
-      <c r="I16" s="557" t="n"/>
-      <c r="J16" s="557" t="n"/>
-      <c r="K16" s="557" t="n"/>
-      <c r="L16" s="557" t="n"/>
-      <c r="M16" s="557" t="n"/>
-      <c r="N16" s="557" t="n"/>
-      <c r="O16" s="557" t="n"/>
-      <c r="P16" s="557" t="n"/>
-      <c r="Q16" s="557" t="n"/>
-      <c r="R16" s="557" t="n"/>
-      <c r="S16" s="557" t="n"/>
-      <c r="T16" s="557" t="n"/>
-      <c r="U16" s="557" t="n"/>
-      <c r="V16" s="557" t="n"/>
-      <c r="W16" s="557" t="n"/>
-      <c r="X16" s="557" t="n"/>
-      <c r="Y16" s="557" t="n"/>
-      <c r="Z16" s="558" t="n"/>
-      <c r="AA16" s="576" t="n"/>
-      <c r="AB16" s="557" t="n"/>
-      <c r="AC16" s="557" t="n"/>
-      <c r="AD16" s="557" t="n"/>
-      <c r="AE16" s="557" t="n"/>
-      <c r="AF16" s="557" t="n"/>
-      <c r="AG16" s="557" t="n"/>
-      <c r="AH16" s="557" t="n"/>
-      <c r="AI16" s="557" t="n"/>
-      <c r="AJ16" s="557" t="n"/>
-      <c r="AK16" s="557" t="n"/>
-      <c r="AL16" s="557" t="n"/>
-      <c r="AM16" s="557" t="n"/>
-      <c r="AN16" s="557" t="n"/>
-      <c r="AO16" s="557" t="n"/>
-      <c r="AP16" s="557" t="n"/>
-      <c r="AQ16" s="558" t="n"/>
-      <c r="AR16" s="556" t="n"/>
-      <c r="AS16" s="557" t="n"/>
-      <c r="AT16" s="557" t="n"/>
-      <c r="AU16" s="557" t="n"/>
-      <c r="AV16" s="557" t="n"/>
-      <c r="AW16" s="558" t="n"/>
-      <c r="AX16" s="556" t="n"/>
-      <c r="AY16" s="557" t="n"/>
-      <c r="AZ16" s="557" t="n"/>
-      <c r="BA16" s="558" t="n"/>
-      <c r="BB16" s="577" t="n"/>
-      <c r="BC16" s="557" t="n"/>
-      <c r="BD16" s="560" t="n"/>
+      <c r="E16" s="321" t="n"/>
+      <c r="F16" s="321" t="n"/>
+      <c r="G16" s="322" t="n"/>
+      <c r="H16" s="288" t="n"/>
+      <c r="I16" s="321" t="n"/>
+      <c r="J16" s="321" t="n"/>
+      <c r="K16" s="321" t="n"/>
+      <c r="L16" s="321" t="n"/>
+      <c r="M16" s="321" t="n"/>
+      <c r="N16" s="321" t="n"/>
+      <c r="O16" s="321" t="n"/>
+      <c r="P16" s="321" t="n"/>
+      <c r="Q16" s="321" t="n"/>
+      <c r="R16" s="321" t="n"/>
+      <c r="S16" s="321" t="n"/>
+      <c r="T16" s="321" t="n"/>
+      <c r="U16" s="321" t="n"/>
+      <c r="V16" s="321" t="n"/>
+      <c r="W16" s="321" t="n"/>
+      <c r="X16" s="321" t="n"/>
+      <c r="Y16" s="321" t="n"/>
+      <c r="Z16" s="322" t="n"/>
+      <c r="AA16" s="629" t="n"/>
+      <c r="AB16" s="321" t="n"/>
+      <c r="AC16" s="321" t="n"/>
+      <c r="AD16" s="321" t="n"/>
+      <c r="AE16" s="321" t="n"/>
+      <c r="AF16" s="321" t="n"/>
+      <c r="AG16" s="321" t="n"/>
+      <c r="AH16" s="321" t="n"/>
+      <c r="AI16" s="321" t="n"/>
+      <c r="AJ16" s="321" t="n"/>
+      <c r="AK16" s="321" t="n"/>
+      <c r="AL16" s="321" t="n"/>
+      <c r="AM16" s="321" t="n"/>
+      <c r="AN16" s="321" t="n"/>
+      <c r="AO16" s="321" t="n"/>
+      <c r="AP16" s="321" t="n"/>
+      <c r="AQ16" s="322" t="n"/>
+      <c r="AR16" s="288" t="n"/>
+      <c r="AS16" s="321" t="n"/>
+      <c r="AT16" s="321" t="n"/>
+      <c r="AU16" s="321" t="n"/>
+      <c r="AV16" s="321" t="n"/>
+      <c r="AW16" s="322" t="n"/>
+      <c r="AX16" s="288" t="n"/>
+      <c r="AY16" s="321" t="n"/>
+      <c r="AZ16" s="321" t="n"/>
+      <c r="BA16" s="322" t="n"/>
+      <c r="BB16" s="630" t="n"/>
+      <c r="BC16" s="321" t="n"/>
+      <c r="BD16" s="323" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="578">
+      <c r="A17" s="631">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="579" t="inlineStr">
+      <c r="B17" s="276" t="n"/>
+      <c r="C17" s="277" t="n"/>
+      <c r="D17" s="295" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="563" t="n"/>
-      <c r="F17" s="563" t="n"/>
-      <c r="G17" s="564" t="n"/>
-      <c r="H17" s="562" t="n"/>
-      <c r="I17" s="563" t="n"/>
-      <c r="J17" s="563" t="n"/>
-      <c r="K17" s="563" t="n"/>
-      <c r="L17" s="563" t="n"/>
-      <c r="M17" s="563" t="n"/>
-      <c r="N17" s="563" t="n"/>
-      <c r="O17" s="563" t="n"/>
-      <c r="P17" s="563" t="n"/>
-      <c r="Q17" s="563" t="n"/>
-      <c r="R17" s="563" t="n"/>
-      <c r="S17" s="563" t="n"/>
-      <c r="T17" s="563" t="n"/>
-      <c r="U17" s="563" t="n"/>
-      <c r="V17" s="563" t="n"/>
-      <c r="W17" s="563" t="n"/>
-      <c r="X17" s="563" t="n"/>
-      <c r="Y17" s="563" t="n"/>
-      <c r="Z17" s="564" t="n"/>
-      <c r="AA17" s="580" t="n"/>
-      <c r="AB17" s="563" t="n"/>
-      <c r="AC17" s="563" t="n"/>
-      <c r="AD17" s="563" t="n"/>
-      <c r="AE17" s="563" t="n"/>
-      <c r="AF17" s="563" t="n"/>
-      <c r="AG17" s="563" t="n"/>
-      <c r="AH17" s="563" t="n"/>
-      <c r="AI17" s="563" t="n"/>
-      <c r="AJ17" s="563" t="n"/>
-      <c r="AK17" s="563" t="n"/>
-      <c r="AL17" s="563" t="n"/>
-      <c r="AM17" s="563" t="n"/>
-      <c r="AN17" s="563" t="n"/>
-      <c r="AO17" s="563" t="n"/>
-      <c r="AP17" s="563" t="n"/>
-      <c r="AQ17" s="564" t="n"/>
-      <c r="AR17" s="562" t="n"/>
-      <c r="AS17" s="563" t="n"/>
-      <c r="AT17" s="563" t="n"/>
-      <c r="AU17" s="563" t="n"/>
-      <c r="AV17" s="563" t="n"/>
-      <c r="AW17" s="564" t="n"/>
-      <c r="AX17" s="562" t="n"/>
-      <c r="AY17" s="563" t="n"/>
-      <c r="AZ17" s="563" t="n"/>
-      <c r="BA17" s="564" t="n"/>
-      <c r="BB17" s="581" t="n"/>
-      <c r="BC17" s="563" t="n"/>
-      <c r="BD17" s="566" t="n"/>
+      <c r="E17" s="324" t="n"/>
+      <c r="F17" s="324" t="n"/>
+      <c r="G17" s="325" t="n"/>
+      <c r="H17" s="296" t="n"/>
+      <c r="I17" s="324" t="n"/>
+      <c r="J17" s="324" t="n"/>
+      <c r="K17" s="324" t="n"/>
+      <c r="L17" s="324" t="n"/>
+      <c r="M17" s="324" t="n"/>
+      <c r="N17" s="324" t="n"/>
+      <c r="O17" s="324" t="n"/>
+      <c r="P17" s="324" t="n"/>
+      <c r="Q17" s="324" t="n"/>
+      <c r="R17" s="324" t="n"/>
+      <c r="S17" s="324" t="n"/>
+      <c r="T17" s="324" t="n"/>
+      <c r="U17" s="324" t="n"/>
+      <c r="V17" s="324" t="n"/>
+      <c r="W17" s="324" t="n"/>
+      <c r="X17" s="324" t="n"/>
+      <c r="Y17" s="324" t="n"/>
+      <c r="Z17" s="325" t="n"/>
+      <c r="AA17" s="297" t="n"/>
+      <c r="AB17" s="324" t="n"/>
+      <c r="AC17" s="324" t="n"/>
+      <c r="AD17" s="324" t="n"/>
+      <c r="AE17" s="324" t="n"/>
+      <c r="AF17" s="324" t="n"/>
+      <c r="AG17" s="324" t="n"/>
+      <c r="AH17" s="324" t="n"/>
+      <c r="AI17" s="324" t="n"/>
+      <c r="AJ17" s="324" t="n"/>
+      <c r="AK17" s="324" t="n"/>
+      <c r="AL17" s="324" t="n"/>
+      <c r="AM17" s="324" t="n"/>
+      <c r="AN17" s="324" t="n"/>
+      <c r="AO17" s="324" t="n"/>
+      <c r="AP17" s="324" t="n"/>
+      <c r="AQ17" s="325" t="n"/>
+      <c r="AR17" s="296" t="n"/>
+      <c r="AS17" s="324" t="n"/>
+      <c r="AT17" s="324" t="n"/>
+      <c r="AU17" s="324" t="n"/>
+      <c r="AV17" s="324" t="n"/>
+      <c r="AW17" s="325" t="n"/>
+      <c r="AX17" s="296" t="n"/>
+      <c r="AY17" s="324" t="n"/>
+      <c r="AZ17" s="324" t="n"/>
+      <c r="BA17" s="325" t="n"/>
+      <c r="BB17" s="298" t="n"/>
+      <c r="BC17" s="324" t="n"/>
+      <c r="BD17" s="326" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="578">
+      <c r="A18" s="631">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="579" t="inlineStr">
+      <c r="B18" s="276" t="n"/>
+      <c r="C18" s="277" t="n"/>
+      <c r="D18" s="295" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="563" t="n"/>
-      <c r="F18" s="563" t="n"/>
-      <c r="G18" s="564" t="n"/>
-      <c r="H18" s="562" t="n"/>
-      <c r="I18" s="563" t="n"/>
-      <c r="J18" s="563" t="n"/>
-      <c r="K18" s="563" t="n"/>
-      <c r="L18" s="563" t="n"/>
-      <c r="M18" s="563" t="n"/>
-      <c r="N18" s="563" t="n"/>
-      <c r="O18" s="563" t="n"/>
-      <c r="P18" s="563" t="n"/>
-      <c r="Q18" s="563" t="n"/>
-      <c r="R18" s="563" t="n"/>
-      <c r="S18" s="563" t="n"/>
-      <c r="T18" s="563" t="n"/>
-      <c r="U18" s="563" t="n"/>
-      <c r="V18" s="563" t="n"/>
-      <c r="W18" s="563" t="n"/>
-      <c r="X18" s="563" t="n"/>
-      <c r="Y18" s="563" t="n"/>
-      <c r="Z18" s="564" t="n"/>
-      <c r="AA18" s="580" t="n"/>
-      <c r="AB18" s="563" t="n"/>
-      <c r="AC18" s="563" t="n"/>
-      <c r="AD18" s="563" t="n"/>
-      <c r="AE18" s="563" t="n"/>
-      <c r="AF18" s="563" t="n"/>
-      <c r="AG18" s="563" t="n"/>
-      <c r="AH18" s="563" t="n"/>
-      <c r="AI18" s="563" t="n"/>
-      <c r="AJ18" s="563" t="n"/>
-      <c r="AK18" s="563" t="n"/>
-      <c r="AL18" s="563" t="n"/>
-      <c r="AM18" s="563" t="n"/>
-      <c r="AN18" s="563" t="n"/>
-      <c r="AO18" s="563" t="n"/>
-      <c r="AP18" s="563" t="n"/>
-      <c r="AQ18" s="564" t="n"/>
-      <c r="AR18" s="562" t="n"/>
-      <c r="AS18" s="563" t="n"/>
-      <c r="AT18" s="563" t="n"/>
-      <c r="AU18" s="563" t="n"/>
-      <c r="AV18" s="563" t="n"/>
-      <c r="AW18" s="564" t="n"/>
-      <c r="AX18" s="562" t="n"/>
-      <c r="AY18" s="563" t="n"/>
-      <c r="AZ18" s="563" t="n"/>
-      <c r="BA18" s="564" t="n"/>
-      <c r="BB18" s="581" t="n"/>
-      <c r="BC18" s="563" t="n"/>
-      <c r="BD18" s="566" t="n"/>
+      <c r="E18" s="324" t="n"/>
+      <c r="F18" s="324" t="n"/>
+      <c r="G18" s="325" t="n"/>
+      <c r="H18" s="296" t="n"/>
+      <c r="I18" s="324" t="n"/>
+      <c r="J18" s="324" t="n"/>
+      <c r="K18" s="324" t="n"/>
+      <c r="L18" s="324" t="n"/>
+      <c r="M18" s="324" t="n"/>
+      <c r="N18" s="324" t="n"/>
+      <c r="O18" s="324" t="n"/>
+      <c r="P18" s="324" t="n"/>
+      <c r="Q18" s="324" t="n"/>
+      <c r="R18" s="324" t="n"/>
+      <c r="S18" s="324" t="n"/>
+      <c r="T18" s="324" t="n"/>
+      <c r="U18" s="324" t="n"/>
+      <c r="V18" s="324" t="n"/>
+      <c r="W18" s="324" t="n"/>
+      <c r="X18" s="324" t="n"/>
+      <c r="Y18" s="324" t="n"/>
+      <c r="Z18" s="325" t="n"/>
+      <c r="AA18" s="297" t="n"/>
+      <c r="AB18" s="324" t="n"/>
+      <c r="AC18" s="324" t="n"/>
+      <c r="AD18" s="324" t="n"/>
+      <c r="AE18" s="324" t="n"/>
+      <c r="AF18" s="324" t="n"/>
+      <c r="AG18" s="324" t="n"/>
+      <c r="AH18" s="324" t="n"/>
+      <c r="AI18" s="324" t="n"/>
+      <c r="AJ18" s="324" t="n"/>
+      <c r="AK18" s="324" t="n"/>
+      <c r="AL18" s="324" t="n"/>
+      <c r="AM18" s="324" t="n"/>
+      <c r="AN18" s="324" t="n"/>
+      <c r="AO18" s="324" t="n"/>
+      <c r="AP18" s="324" t="n"/>
+      <c r="AQ18" s="325" t="n"/>
+      <c r="AR18" s="296" t="n"/>
+      <c r="AS18" s="324" t="n"/>
+      <c r="AT18" s="324" t="n"/>
+      <c r="AU18" s="324" t="n"/>
+      <c r="AV18" s="324" t="n"/>
+      <c r="AW18" s="325" t="n"/>
+      <c r="AX18" s="296" t="n"/>
+      <c r="AY18" s="324" t="n"/>
+      <c r="AZ18" s="324" t="n"/>
+      <c r="BA18" s="325" t="n"/>
+      <c r="BB18" s="298" t="n"/>
+      <c r="BC18" s="324" t="n"/>
+      <c r="BD18" s="326" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="578">
+      <c r="A19" s="631">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="579" t="inlineStr">
+      <c r="B19" s="276" t="n"/>
+      <c r="C19" s="277" t="n"/>
+      <c r="D19" s="295" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="563" t="n"/>
-      <c r="F19" s="563" t="n"/>
-      <c r="G19" s="564" t="n"/>
-      <c r="H19" s="562" t="n"/>
-      <c r="I19" s="563" t="n"/>
-      <c r="J19" s="563" t="n"/>
-      <c r="K19" s="563" t="n"/>
-      <c r="L19" s="563" t="n"/>
-      <c r="M19" s="563" t="n"/>
-      <c r="N19" s="563" t="n"/>
-      <c r="O19" s="563" t="n"/>
-      <c r="P19" s="563" t="n"/>
-      <c r="Q19" s="563" t="n"/>
-      <c r="R19" s="563" t="n"/>
-      <c r="S19" s="563" t="n"/>
-      <c r="T19" s="563" t="n"/>
-      <c r="U19" s="563" t="n"/>
-      <c r="V19" s="563" t="n"/>
-      <c r="W19" s="563" t="n"/>
-      <c r="X19" s="563" t="n"/>
-      <c r="Y19" s="563" t="n"/>
-      <c r="Z19" s="564" t="n"/>
-      <c r="AA19" s="580" t="n"/>
-      <c r="AB19" s="563" t="n"/>
-      <c r="AC19" s="563" t="n"/>
-      <c r="AD19" s="563" t="n"/>
-      <c r="AE19" s="563" t="n"/>
-      <c r="AF19" s="563" t="n"/>
-      <c r="AG19" s="563" t="n"/>
-      <c r="AH19" s="563" t="n"/>
-      <c r="AI19" s="563" t="n"/>
-      <c r="AJ19" s="563" t="n"/>
-      <c r="AK19" s="563" t="n"/>
-      <c r="AL19" s="563" t="n"/>
-      <c r="AM19" s="563" t="n"/>
-      <c r="AN19" s="563" t="n"/>
-      <c r="AO19" s="563" t="n"/>
-      <c r="AP19" s="563" t="n"/>
-      <c r="AQ19" s="564" t="n"/>
-      <c r="AR19" s="562" t="n"/>
-      <c r="AS19" s="563" t="n"/>
-      <c r="AT19" s="563" t="n"/>
-      <c r="AU19" s="563" t="n"/>
-      <c r="AV19" s="563" t="n"/>
-      <c r="AW19" s="564" t="n"/>
-      <c r="AX19" s="562" t="n"/>
-      <c r="AY19" s="563" t="n"/>
-      <c r="AZ19" s="563" t="n"/>
-      <c r="BA19" s="564" t="n"/>
-      <c r="BB19" s="581" t="n"/>
-      <c r="BC19" s="563" t="n"/>
-      <c r="BD19" s="566" t="n"/>
+      <c r="E19" s="324" t="n"/>
+      <c r="F19" s="324" t="n"/>
+      <c r="G19" s="325" t="n"/>
+      <c r="H19" s="296" t="n"/>
+      <c r="I19" s="324" t="n"/>
+      <c r="J19" s="324" t="n"/>
+      <c r="K19" s="324" t="n"/>
+      <c r="L19" s="324" t="n"/>
+      <c r="M19" s="324" t="n"/>
+      <c r="N19" s="324" t="n"/>
+      <c r="O19" s="324" t="n"/>
+      <c r="P19" s="324" t="n"/>
+      <c r="Q19" s="324" t="n"/>
+      <c r="R19" s="324" t="n"/>
+      <c r="S19" s="324" t="n"/>
+      <c r="T19" s="324" t="n"/>
+      <c r="U19" s="324" t="n"/>
+      <c r="V19" s="324" t="n"/>
+      <c r="W19" s="324" t="n"/>
+      <c r="X19" s="324" t="n"/>
+      <c r="Y19" s="324" t="n"/>
+      <c r="Z19" s="325" t="n"/>
+      <c r="AA19" s="297" t="n"/>
+      <c r="AB19" s="324" t="n"/>
+      <c r="AC19" s="324" t="n"/>
+      <c r="AD19" s="324" t="n"/>
+      <c r="AE19" s="324" t="n"/>
+      <c r="AF19" s="324" t="n"/>
+      <c r="AG19" s="324" t="n"/>
+      <c r="AH19" s="324" t="n"/>
+      <c r="AI19" s="324" t="n"/>
+      <c r="AJ19" s="324" t="n"/>
+      <c r="AK19" s="324" t="n"/>
+      <c r="AL19" s="324" t="n"/>
+      <c r="AM19" s="324" t="n"/>
+      <c r="AN19" s="324" t="n"/>
+      <c r="AO19" s="324" t="n"/>
+      <c r="AP19" s="324" t="n"/>
+      <c r="AQ19" s="325" t="n"/>
+      <c r="AR19" s="296" t="n"/>
+      <c r="AS19" s="324" t="n"/>
+      <c r="AT19" s="324" t="n"/>
+      <c r="AU19" s="324" t="n"/>
+      <c r="AV19" s="324" t="n"/>
+      <c r="AW19" s="325" t="n"/>
+      <c r="AX19" s="296" t="n"/>
+      <c r="AY19" s="324" t="n"/>
+      <c r="AZ19" s="324" t="n"/>
+      <c r="BA19" s="325" t="n"/>
+      <c r="BB19" s="298" t="n"/>
+      <c r="BC19" s="324" t="n"/>
+      <c r="BD19" s="326" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="578">
+      <c r="A20" s="631">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="579" t="inlineStr">
+      <c r="B20" s="276" t="n"/>
+      <c r="C20" s="277" t="n"/>
+      <c r="D20" s="295" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="563" t="n"/>
-      <c r="F20" s="563" t="n"/>
-      <c r="G20" s="564" t="n"/>
-      <c r="H20" s="562" t="n"/>
-      <c r="I20" s="563" t="n"/>
-      <c r="J20" s="563" t="n"/>
-      <c r="K20" s="563" t="n"/>
-      <c r="L20" s="563" t="n"/>
-      <c r="M20" s="563" t="n"/>
-      <c r="N20" s="563" t="n"/>
-      <c r="O20" s="563" t="n"/>
-      <c r="P20" s="563" t="n"/>
-      <c r="Q20" s="563" t="n"/>
-      <c r="R20" s="563" t="n"/>
-      <c r="S20" s="563" t="n"/>
-      <c r="T20" s="563" t="n"/>
-      <c r="U20" s="563" t="n"/>
-      <c r="V20" s="563" t="n"/>
-      <c r="W20" s="563" t="n"/>
-      <c r="X20" s="563" t="n"/>
-      <c r="Y20" s="563" t="n"/>
-      <c r="Z20" s="564" t="n"/>
-      <c r="AA20" s="580" t="n"/>
-      <c r="AB20" s="563" t="n"/>
-      <c r="AC20" s="563" t="n"/>
-      <c r="AD20" s="563" t="n"/>
-      <c r="AE20" s="563" t="n"/>
-      <c r="AF20" s="563" t="n"/>
-      <c r="AG20" s="563" t="n"/>
-      <c r="AH20" s="563" t="n"/>
-      <c r="AI20" s="563" t="n"/>
-      <c r="AJ20" s="563" t="n"/>
-      <c r="AK20" s="563" t="n"/>
-      <c r="AL20" s="563" t="n"/>
-      <c r="AM20" s="563" t="n"/>
-      <c r="AN20" s="563" t="n"/>
-      <c r="AO20" s="563" t="n"/>
-      <c r="AP20" s="563" t="n"/>
-      <c r="AQ20" s="564" t="n"/>
-      <c r="AR20" s="562" t="n"/>
-      <c r="AS20" s="563" t="n"/>
-      <c r="AT20" s="563" t="n"/>
-      <c r="AU20" s="563" t="n"/>
-      <c r="AV20" s="563" t="n"/>
-      <c r="AW20" s="564" t="n"/>
-      <c r="AX20" s="562" t="n"/>
-      <c r="AY20" s="563" t="n"/>
-      <c r="AZ20" s="563" t="n"/>
-      <c r="BA20" s="564" t="n"/>
-      <c r="BB20" s="581" t="n"/>
-      <c r="BC20" s="563" t="n"/>
-      <c r="BD20" s="566" t="n"/>
+      <c r="E20" s="324" t="n"/>
+      <c r="F20" s="324" t="n"/>
+      <c r="G20" s="325" t="n"/>
+      <c r="H20" s="296" t="n"/>
+      <c r="I20" s="324" t="n"/>
+      <c r="J20" s="324" t="n"/>
+      <c r="K20" s="324" t="n"/>
+      <c r="L20" s="324" t="n"/>
+      <c r="M20" s="324" t="n"/>
+      <c r="N20" s="324" t="n"/>
+      <c r="O20" s="324" t="n"/>
+      <c r="P20" s="324" t="n"/>
+      <c r="Q20" s="324" t="n"/>
+      <c r="R20" s="324" t="n"/>
+      <c r="S20" s="324" t="n"/>
+      <c r="T20" s="324" t="n"/>
+      <c r="U20" s="324" t="n"/>
+      <c r="V20" s="324" t="n"/>
+      <c r="W20" s="324" t="n"/>
+      <c r="X20" s="324" t="n"/>
+      <c r="Y20" s="324" t="n"/>
+      <c r="Z20" s="325" t="n"/>
+      <c r="AA20" s="297" t="n"/>
+      <c r="AB20" s="324" t="n"/>
+      <c r="AC20" s="324" t="n"/>
+      <c r="AD20" s="324" t="n"/>
+      <c r="AE20" s="324" t="n"/>
+      <c r="AF20" s="324" t="n"/>
+      <c r="AG20" s="324" t="n"/>
+      <c r="AH20" s="324" t="n"/>
+      <c r="AI20" s="324" t="n"/>
+      <c r="AJ20" s="324" t="n"/>
+      <c r="AK20" s="324" t="n"/>
+      <c r="AL20" s="324" t="n"/>
+      <c r="AM20" s="324" t="n"/>
+      <c r="AN20" s="324" t="n"/>
+      <c r="AO20" s="324" t="n"/>
+      <c r="AP20" s="324" t="n"/>
+      <c r="AQ20" s="325" t="n"/>
+      <c r="AR20" s="296" t="n"/>
+      <c r="AS20" s="324" t="n"/>
+      <c r="AT20" s="324" t="n"/>
+      <c r="AU20" s="324" t="n"/>
+      <c r="AV20" s="324" t="n"/>
+      <c r="AW20" s="325" t="n"/>
+      <c r="AX20" s="296" t="n"/>
+      <c r="AY20" s="324" t="n"/>
+      <c r="AZ20" s="324" t="n"/>
+      <c r="BA20" s="325" t="n"/>
+      <c r="BB20" s="298" t="n"/>
+      <c r="BC20" s="324" t="n"/>
+      <c r="BD20" s="326" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="578">
+      <c r="A21" s="631">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="579" t="inlineStr">
+      <c r="B21" s="276" t="n"/>
+      <c r="C21" s="277" t="n"/>
+      <c r="D21" s="295" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="563" t="n"/>
-      <c r="F21" s="563" t="n"/>
-      <c r="G21" s="564" t="n"/>
-      <c r="H21" s="562" t="n"/>
-      <c r="I21" s="563" t="n"/>
-      <c r="J21" s="563" t="n"/>
-      <c r="K21" s="563" t="n"/>
-      <c r="L21" s="563" t="n"/>
-      <c r="M21" s="563" t="n"/>
-      <c r="N21" s="563" t="n"/>
-      <c r="O21" s="563" t="n"/>
-      <c r="P21" s="563" t="n"/>
-      <c r="Q21" s="563" t="n"/>
-      <c r="R21" s="563" t="n"/>
-      <c r="S21" s="563" t="n"/>
-      <c r="T21" s="563" t="n"/>
-      <c r="U21" s="563" t="n"/>
-      <c r="V21" s="563" t="n"/>
-      <c r="W21" s="563" t="n"/>
-      <c r="X21" s="563" t="n"/>
-      <c r="Y21" s="563" t="n"/>
-      <c r="Z21" s="564" t="n"/>
-      <c r="AA21" s="580" t="n"/>
-      <c r="AB21" s="563" t="n"/>
-      <c r="AC21" s="563" t="n"/>
-      <c r="AD21" s="563" t="n"/>
-      <c r="AE21" s="563" t="n"/>
-      <c r="AF21" s="563" t="n"/>
-      <c r="AG21" s="563" t="n"/>
-      <c r="AH21" s="563" t="n"/>
-      <c r="AI21" s="563" t="n"/>
-      <c r="AJ21" s="563" t="n"/>
-      <c r="AK21" s="563" t="n"/>
-      <c r="AL21" s="563" t="n"/>
-      <c r="AM21" s="563" t="n"/>
-      <c r="AN21" s="563" t="n"/>
-      <c r="AO21" s="563" t="n"/>
-      <c r="AP21" s="563" t="n"/>
-      <c r="AQ21" s="564" t="n"/>
-      <c r="AR21" s="562" t="n"/>
-      <c r="AS21" s="563" t="n"/>
-      <c r="AT21" s="563" t="n"/>
-      <c r="AU21" s="563" t="n"/>
-      <c r="AV21" s="563" t="n"/>
-      <c r="AW21" s="564" t="n"/>
-      <c r="AX21" s="562" t="n"/>
-      <c r="AY21" s="563" t="n"/>
-      <c r="AZ21" s="563" t="n"/>
-      <c r="BA21" s="564" t="n"/>
-      <c r="BB21" s="581" t="n"/>
-      <c r="BC21" s="563" t="n"/>
-      <c r="BD21" s="566" t="n"/>
+      <c r="E21" s="324" t="n"/>
+      <c r="F21" s="324" t="n"/>
+      <c r="G21" s="325" t="n"/>
+      <c r="H21" s="296" t="n"/>
+      <c r="I21" s="324" t="n"/>
+      <c r="J21" s="324" t="n"/>
+      <c r="K21" s="324" t="n"/>
+      <c r="L21" s="324" t="n"/>
+      <c r="M21" s="324" t="n"/>
+      <c r="N21" s="324" t="n"/>
+      <c r="O21" s="324" t="n"/>
+      <c r="P21" s="324" t="n"/>
+      <c r="Q21" s="324" t="n"/>
+      <c r="R21" s="324" t="n"/>
+      <c r="S21" s="324" t="n"/>
+      <c r="T21" s="324" t="n"/>
+      <c r="U21" s="324" t="n"/>
+      <c r="V21" s="324" t="n"/>
+      <c r="W21" s="324" t="n"/>
+      <c r="X21" s="324" t="n"/>
+      <c r="Y21" s="324" t="n"/>
+      <c r="Z21" s="325" t="n"/>
+      <c r="AA21" s="297" t="n"/>
+      <c r="AB21" s="324" t="n"/>
+      <c r="AC21" s="324" t="n"/>
+      <c r="AD21" s="324" t="n"/>
+      <c r="AE21" s="324" t="n"/>
+      <c r="AF21" s="324" t="n"/>
+      <c r="AG21" s="324" t="n"/>
+      <c r="AH21" s="324" t="n"/>
+      <c r="AI21" s="324" t="n"/>
+      <c r="AJ21" s="324" t="n"/>
+      <c r="AK21" s="324" t="n"/>
+      <c r="AL21" s="324" t="n"/>
+      <c r="AM21" s="324" t="n"/>
+      <c r="AN21" s="324" t="n"/>
+      <c r="AO21" s="324" t="n"/>
+      <c r="AP21" s="324" t="n"/>
+      <c r="AQ21" s="325" t="n"/>
+      <c r="AR21" s="296" t="n"/>
+      <c r="AS21" s="324" t="n"/>
+      <c r="AT21" s="324" t="n"/>
+      <c r="AU21" s="324" t="n"/>
+      <c r="AV21" s="324" t="n"/>
+      <c r="AW21" s="325" t="n"/>
+      <c r="AX21" s="296" t="n"/>
+      <c r="AY21" s="324" t="n"/>
+      <c r="AZ21" s="324" t="n"/>
+      <c r="BA21" s="325" t="n"/>
+      <c r="BB21" s="298" t="n"/>
+      <c r="BC21" s="324" t="n"/>
+      <c r="BD21" s="326" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="582">
+      <c r="A22" s="632">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="583" t="inlineStr">
+      <c r="B22" s="281" t="n"/>
+      <c r="C22" s="282" t="n"/>
+      <c r="D22" s="633" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="569" t="n"/>
-      <c r="F22" s="569" t="n"/>
-      <c r="G22" s="570" t="n"/>
-      <c r="H22" s="568" t="n"/>
-      <c r="I22" s="569" t="n"/>
-      <c r="J22" s="569" t="n"/>
-      <c r="K22" s="569" t="n"/>
-      <c r="L22" s="569" t="n"/>
-      <c r="M22" s="569" t="n"/>
-      <c r="N22" s="569" t="n"/>
-      <c r="O22" s="569" t="n"/>
-      <c r="P22" s="569" t="n"/>
-      <c r="Q22" s="569" t="n"/>
-      <c r="R22" s="569" t="n"/>
-      <c r="S22" s="569" t="n"/>
-      <c r="T22" s="569" t="n"/>
-      <c r="U22" s="569" t="n"/>
-      <c r="V22" s="569" t="n"/>
-      <c r="W22" s="569" t="n"/>
-      <c r="X22" s="569" t="n"/>
-      <c r="Y22" s="569" t="n"/>
-      <c r="Z22" s="570" t="n"/>
-      <c r="AA22" s="584" t="n"/>
-      <c r="AB22" s="569" t="n"/>
-      <c r="AC22" s="569" t="n"/>
-      <c r="AD22" s="569" t="n"/>
-      <c r="AE22" s="569" t="n"/>
-      <c r="AF22" s="569" t="n"/>
-      <c r="AG22" s="569" t="n"/>
-      <c r="AH22" s="569" t="n"/>
-      <c r="AI22" s="569" t="n"/>
-      <c r="AJ22" s="569" t="n"/>
-      <c r="AK22" s="569" t="n"/>
-      <c r="AL22" s="569" t="n"/>
-      <c r="AM22" s="569" t="n"/>
-      <c r="AN22" s="569" t="n"/>
-      <c r="AO22" s="569" t="n"/>
-      <c r="AP22" s="569" t="n"/>
-      <c r="AQ22" s="570" t="n"/>
-      <c r="AR22" s="568" t="n"/>
-      <c r="AS22" s="569" t="n"/>
-      <c r="AT22" s="569" t="n"/>
-      <c r="AU22" s="569" t="n"/>
-      <c r="AV22" s="569" t="n"/>
-      <c r="AW22" s="570" t="n"/>
-      <c r="AX22" s="568" t="n"/>
-      <c r="AY22" s="569" t="n"/>
-      <c r="AZ22" s="569" t="n"/>
-      <c r="BA22" s="570" t="n"/>
-      <c r="BB22" s="585" t="n"/>
-      <c r="BC22" s="569" t="n"/>
-      <c r="BD22" s="572" t="n"/>
+      <c r="E22" s="335" t="n"/>
+      <c r="F22" s="335" t="n"/>
+      <c r="G22" s="624" t="n"/>
+      <c r="H22" s="623" t="n"/>
+      <c r="I22" s="335" t="n"/>
+      <c r="J22" s="335" t="n"/>
+      <c r="K22" s="335" t="n"/>
+      <c r="L22" s="335" t="n"/>
+      <c r="M22" s="335" t="n"/>
+      <c r="N22" s="335" t="n"/>
+      <c r="O22" s="335" t="n"/>
+      <c r="P22" s="335" t="n"/>
+      <c r="Q22" s="335" t="n"/>
+      <c r="R22" s="335" t="n"/>
+      <c r="S22" s="335" t="n"/>
+      <c r="T22" s="335" t="n"/>
+      <c r="U22" s="335" t="n"/>
+      <c r="V22" s="335" t="n"/>
+      <c r="W22" s="335" t="n"/>
+      <c r="X22" s="335" t="n"/>
+      <c r="Y22" s="335" t="n"/>
+      <c r="Z22" s="624" t="n"/>
+      <c r="AA22" s="634" t="n"/>
+      <c r="AB22" s="335" t="n"/>
+      <c r="AC22" s="335" t="n"/>
+      <c r="AD22" s="335" t="n"/>
+      <c r="AE22" s="335" t="n"/>
+      <c r="AF22" s="335" t="n"/>
+      <c r="AG22" s="335" t="n"/>
+      <c r="AH22" s="335" t="n"/>
+      <c r="AI22" s="335" t="n"/>
+      <c r="AJ22" s="335" t="n"/>
+      <c r="AK22" s="335" t="n"/>
+      <c r="AL22" s="335" t="n"/>
+      <c r="AM22" s="335" t="n"/>
+      <c r="AN22" s="335" t="n"/>
+      <c r="AO22" s="335" t="n"/>
+      <c r="AP22" s="335" t="n"/>
+      <c r="AQ22" s="624" t="n"/>
+      <c r="AR22" s="623" t="n"/>
+      <c r="AS22" s="335" t="n"/>
+      <c r="AT22" s="335" t="n"/>
+      <c r="AU22" s="335" t="n"/>
+      <c r="AV22" s="335" t="n"/>
+      <c r="AW22" s="624" t="n"/>
+      <c r="AX22" s="623" t="n"/>
+      <c r="AY22" s="335" t="n"/>
+      <c r="AZ22" s="335" t="n"/>
+      <c r="BA22" s="624" t="n"/>
+      <c r="BB22" s="635" t="n"/>
+      <c r="BC22" s="335" t="n"/>
+      <c r="BD22" s="336" t="n"/>
     </row>
     <row r="23" ht="3" customHeight="1">
       <c r="A23" s="586" t="n"/>
@@ -8272,264 +8388,264 @@
       <c r="BD23" s="573" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="554" t="inlineStr">
+      <c r="A24" s="616" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
-      <c r="H24" s="27" t="n"/>
-      <c r="I24" s="27" t="n"/>
-      <c r="J24" s="27" t="n"/>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="27" t="n"/>
-      <c r="M24" s="27" t="n"/>
-      <c r="N24" s="27" t="n"/>
-      <c r="O24" s="27" t="n"/>
-      <c r="P24" s="27" t="n"/>
-      <c r="Q24" s="27" t="n"/>
-      <c r="R24" s="27" t="n"/>
-      <c r="S24" s="27" t="n"/>
-      <c r="T24" s="27" t="n"/>
-      <c r="U24" s="27" t="n"/>
-      <c r="V24" s="27" t="n"/>
-      <c r="W24" s="27" t="n"/>
-      <c r="X24" s="27" t="n"/>
-      <c r="Y24" s="27" t="n"/>
-      <c r="Z24" s="27" t="n"/>
-      <c r="AA24" s="27" t="n"/>
-      <c r="AB24" s="27" t="n"/>
-      <c r="AC24" s="27" t="n"/>
-      <c r="AD24" s="27" t="n"/>
-      <c r="AE24" s="27" t="n"/>
-      <c r="AF24" s="27" t="n"/>
-      <c r="AG24" s="27" t="n"/>
-      <c r="AH24" s="27" t="n"/>
-      <c r="AI24" s="27" t="n"/>
-      <c r="AJ24" s="27" t="n"/>
-      <c r="AK24" s="27" t="n"/>
-      <c r="AL24" s="27" t="n"/>
-      <c r="AM24" s="27" t="n"/>
-      <c r="AN24" s="27" t="n"/>
-      <c r="AO24" s="27" t="n"/>
-      <c r="AP24" s="27" t="n"/>
-      <c r="AQ24" s="27" t="n"/>
-      <c r="AR24" s="27" t="n"/>
-      <c r="AS24" s="27" t="n"/>
-      <c r="AT24" s="27" t="n"/>
-      <c r="AU24" s="27" t="n"/>
-      <c r="AV24" s="27" t="n"/>
-      <c r="AW24" s="27" t="n"/>
-      <c r="AX24" s="27" t="n"/>
-      <c r="AY24" s="27" t="n"/>
-      <c r="AZ24" s="27" t="n"/>
-      <c r="BA24" s="27" t="n"/>
-      <c r="BB24" s="27" t="n"/>
-      <c r="BC24" s="27" t="n"/>
-      <c r="BD24" s="28" t="n"/>
+      <c r="B24" s="285" t="n"/>
+      <c r="C24" s="285" t="n"/>
+      <c r="D24" s="285" t="n"/>
+      <c r="E24" s="285" t="n"/>
+      <c r="F24" s="285" t="n"/>
+      <c r="G24" s="285" t="n"/>
+      <c r="H24" s="285" t="n"/>
+      <c r="I24" s="285" t="n"/>
+      <c r="J24" s="285" t="n"/>
+      <c r="K24" s="285" t="n"/>
+      <c r="L24" s="285" t="n"/>
+      <c r="M24" s="285" t="n"/>
+      <c r="N24" s="285" t="n"/>
+      <c r="O24" s="285" t="n"/>
+      <c r="P24" s="285" t="n"/>
+      <c r="Q24" s="285" t="n"/>
+      <c r="R24" s="285" t="n"/>
+      <c r="S24" s="285" t="n"/>
+      <c r="T24" s="285" t="n"/>
+      <c r="U24" s="285" t="n"/>
+      <c r="V24" s="285" t="n"/>
+      <c r="W24" s="285" t="n"/>
+      <c r="X24" s="285" t="n"/>
+      <c r="Y24" s="285" t="n"/>
+      <c r="Z24" s="285" t="n"/>
+      <c r="AA24" s="285" t="n"/>
+      <c r="AB24" s="285" t="n"/>
+      <c r="AC24" s="285" t="n"/>
+      <c r="AD24" s="285" t="n"/>
+      <c r="AE24" s="285" t="n"/>
+      <c r="AF24" s="285" t="n"/>
+      <c r="AG24" s="285" t="n"/>
+      <c r="AH24" s="285" t="n"/>
+      <c r="AI24" s="285" t="n"/>
+      <c r="AJ24" s="285" t="n"/>
+      <c r="AK24" s="285" t="n"/>
+      <c r="AL24" s="285" t="n"/>
+      <c r="AM24" s="285" t="n"/>
+      <c r="AN24" s="285" t="n"/>
+      <c r="AO24" s="285" t="n"/>
+      <c r="AP24" s="285" t="n"/>
+      <c r="AQ24" s="285" t="n"/>
+      <c r="AR24" s="285" t="n"/>
+      <c r="AS24" s="285" t="n"/>
+      <c r="AT24" s="285" t="n"/>
+      <c r="AU24" s="285" t="n"/>
+      <c r="AV24" s="285" t="n"/>
+      <c r="AW24" s="285" t="n"/>
+      <c r="AX24" s="285" t="n"/>
+      <c r="AY24" s="285" t="n"/>
+      <c r="AZ24" s="285" t="n"/>
+      <c r="BA24" s="285" t="n"/>
+      <c r="BB24" s="285" t="n"/>
+      <c r="BC24" s="285" t="n"/>
+      <c r="BD24" s="286" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="555" t="inlineStr">
+      <c r="A25" s="617" t="inlineStr">
         <is>
           <t>Disposition / Release Decision</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="556" t="n"/>
-      <c r="L25" s="557" t="n"/>
-      <c r="M25" s="557" t="n"/>
-      <c r="N25" s="557" t="n"/>
-      <c r="O25" s="557" t="n"/>
-      <c r="P25" s="557" t="n"/>
-      <c r="Q25" s="557" t="n"/>
-      <c r="R25" s="557" t="n"/>
-      <c r="S25" s="557" t="n"/>
-      <c r="T25" s="557" t="n"/>
-      <c r="U25" s="557" t="n"/>
-      <c r="V25" s="557" t="n"/>
-      <c r="W25" s="557" t="n"/>
-      <c r="X25" s="557" t="n"/>
-      <c r="Y25" s="557" t="n"/>
-      <c r="Z25" s="557" t="n"/>
-      <c r="AA25" s="557" t="n"/>
-      <c r="AB25" s="558" t="n"/>
-      <c r="AC25" s="559" t="inlineStr">
+      <c r="B25" s="271" t="n"/>
+      <c r="C25" s="271" t="n"/>
+      <c r="D25" s="271" t="n"/>
+      <c r="E25" s="271" t="n"/>
+      <c r="F25" s="271" t="n"/>
+      <c r="G25" s="271" t="n"/>
+      <c r="H25" s="271" t="n"/>
+      <c r="I25" s="271" t="n"/>
+      <c r="J25" s="272" t="n"/>
+      <c r="K25" s="288" t="n"/>
+      <c r="L25" s="321" t="n"/>
+      <c r="M25" s="321" t="n"/>
+      <c r="N25" s="321" t="n"/>
+      <c r="O25" s="321" t="n"/>
+      <c r="P25" s="321" t="n"/>
+      <c r="Q25" s="321" t="n"/>
+      <c r="R25" s="321" t="n"/>
+      <c r="S25" s="321" t="n"/>
+      <c r="T25" s="321" t="n"/>
+      <c r="U25" s="321" t="n"/>
+      <c r="V25" s="321" t="n"/>
+      <c r="W25" s="321" t="n"/>
+      <c r="X25" s="321" t="n"/>
+      <c r="Y25" s="321" t="n"/>
+      <c r="Z25" s="321" t="n"/>
+      <c r="AA25" s="321" t="n"/>
+      <c r="AB25" s="322" t="n"/>
+      <c r="AC25" s="618" t="inlineStr">
         <is>
           <t>Linked NCR / Concession</t>
         </is>
       </c>
-      <c r="AD25" s="5" t="n"/>
-      <c r="AE25" s="5" t="n"/>
-      <c r="AF25" s="5" t="n"/>
-      <c r="AG25" s="5" t="n"/>
-      <c r="AH25" s="5" t="n"/>
-      <c r="AI25" s="5" t="n"/>
-      <c r="AJ25" s="5" t="n"/>
-      <c r="AK25" s="5" t="n"/>
-      <c r="AL25" s="6" t="n"/>
-      <c r="AM25" s="556" t="n"/>
-      <c r="AN25" s="557" t="n"/>
-      <c r="AO25" s="557" t="n"/>
-      <c r="AP25" s="557" t="n"/>
-      <c r="AQ25" s="557" t="n"/>
-      <c r="AR25" s="557" t="n"/>
-      <c r="AS25" s="557" t="n"/>
-      <c r="AT25" s="557" t="n"/>
-      <c r="AU25" s="557" t="n"/>
-      <c r="AV25" s="557" t="n"/>
-      <c r="AW25" s="557" t="n"/>
-      <c r="AX25" s="557" t="n"/>
-      <c r="AY25" s="557" t="n"/>
-      <c r="AZ25" s="557" t="n"/>
-      <c r="BA25" s="557" t="n"/>
-      <c r="BB25" s="557" t="n"/>
-      <c r="BC25" s="557" t="n"/>
-      <c r="BD25" s="560" t="n"/>
+      <c r="AD25" s="271" t="n"/>
+      <c r="AE25" s="271" t="n"/>
+      <c r="AF25" s="271" t="n"/>
+      <c r="AG25" s="271" t="n"/>
+      <c r="AH25" s="271" t="n"/>
+      <c r="AI25" s="271" t="n"/>
+      <c r="AJ25" s="271" t="n"/>
+      <c r="AK25" s="271" t="n"/>
+      <c r="AL25" s="272" t="n"/>
+      <c r="AM25" s="290" t="n"/>
+      <c r="AN25" s="321" t="n"/>
+      <c r="AO25" s="321" t="n"/>
+      <c r="AP25" s="321" t="n"/>
+      <c r="AQ25" s="321" t="n"/>
+      <c r="AR25" s="321" t="n"/>
+      <c r="AS25" s="321" t="n"/>
+      <c r="AT25" s="321" t="n"/>
+      <c r="AU25" s="321" t="n"/>
+      <c r="AV25" s="321" t="n"/>
+      <c r="AW25" s="321" t="n"/>
+      <c r="AX25" s="321" t="n"/>
+      <c r="AY25" s="321" t="n"/>
+      <c r="AZ25" s="321" t="n"/>
+      <c r="BA25" s="321" t="n"/>
+      <c r="BB25" s="321" t="n"/>
+      <c r="BC25" s="321" t="n"/>
+      <c r="BD25" s="323" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="561" t="inlineStr">
+      <c r="A26" s="619" t="inlineStr">
         <is>
           <t>Cleanliness / Packaging Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="562" t="n"/>
-      <c r="L26" s="563" t="n"/>
-      <c r="M26" s="563" t="n"/>
-      <c r="N26" s="563" t="n"/>
-      <c r="O26" s="563" t="n"/>
-      <c r="P26" s="563" t="n"/>
-      <c r="Q26" s="563" t="n"/>
-      <c r="R26" s="563" t="n"/>
-      <c r="S26" s="563" t="n"/>
-      <c r="T26" s="563" t="n"/>
-      <c r="U26" s="563" t="n"/>
-      <c r="V26" s="563" t="n"/>
-      <c r="W26" s="563" t="n"/>
-      <c r="X26" s="563" t="n"/>
-      <c r="Y26" s="563" t="n"/>
-      <c r="Z26" s="563" t="n"/>
-      <c r="AA26" s="563" t="n"/>
-      <c r="AB26" s="564" t="n"/>
-      <c r="AC26" s="565" t="inlineStr">
+      <c r="B26" s="276" t="n"/>
+      <c r="C26" s="276" t="n"/>
+      <c r="D26" s="276" t="n"/>
+      <c r="E26" s="276" t="n"/>
+      <c r="F26" s="276" t="n"/>
+      <c r="G26" s="276" t="n"/>
+      <c r="H26" s="276" t="n"/>
+      <c r="I26" s="276" t="n"/>
+      <c r="J26" s="277" t="n"/>
+      <c r="K26" s="296" t="n"/>
+      <c r="L26" s="324" t="n"/>
+      <c r="M26" s="324" t="n"/>
+      <c r="N26" s="324" t="n"/>
+      <c r="O26" s="324" t="n"/>
+      <c r="P26" s="324" t="n"/>
+      <c r="Q26" s="324" t="n"/>
+      <c r="R26" s="324" t="n"/>
+      <c r="S26" s="324" t="n"/>
+      <c r="T26" s="324" t="n"/>
+      <c r="U26" s="324" t="n"/>
+      <c r="V26" s="324" t="n"/>
+      <c r="W26" s="324" t="n"/>
+      <c r="X26" s="324" t="n"/>
+      <c r="Y26" s="324" t="n"/>
+      <c r="Z26" s="324" t="n"/>
+      <c r="AA26" s="324" t="n"/>
+      <c r="AB26" s="325" t="n"/>
+      <c r="AC26" s="620" t="inlineStr">
         <is>
           <t>Label / Doc Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="AD26" s="12" t="n"/>
-      <c r="AE26" s="12" t="n"/>
-      <c r="AF26" s="12" t="n"/>
-      <c r="AG26" s="12" t="n"/>
-      <c r="AH26" s="12" t="n"/>
-      <c r="AI26" s="12" t="n"/>
-      <c r="AJ26" s="12" t="n"/>
-      <c r="AK26" s="12" t="n"/>
-      <c r="AL26" s="13" t="n"/>
-      <c r="AM26" s="562" t="n"/>
-      <c r="AN26" s="563" t="n"/>
-      <c r="AO26" s="563" t="n"/>
-      <c r="AP26" s="563" t="n"/>
-      <c r="AQ26" s="563" t="n"/>
-      <c r="AR26" s="563" t="n"/>
-      <c r="AS26" s="563" t="n"/>
-      <c r="AT26" s="563" t="n"/>
-      <c r="AU26" s="563" t="n"/>
-      <c r="AV26" s="563" t="n"/>
-      <c r="AW26" s="563" t="n"/>
-      <c r="AX26" s="563" t="n"/>
-      <c r="AY26" s="563" t="n"/>
-      <c r="AZ26" s="563" t="n"/>
-      <c r="BA26" s="563" t="n"/>
-      <c r="BB26" s="563" t="n"/>
-      <c r="BC26" s="563" t="n"/>
-      <c r="BD26" s="566" t="n"/>
+      <c r="AD26" s="276" t="n"/>
+      <c r="AE26" s="276" t="n"/>
+      <c r="AF26" s="276" t="n"/>
+      <c r="AG26" s="276" t="n"/>
+      <c r="AH26" s="276" t="n"/>
+      <c r="AI26" s="276" t="n"/>
+      <c r="AJ26" s="276" t="n"/>
+      <c r="AK26" s="276" t="n"/>
+      <c r="AL26" s="277" t="n"/>
+      <c r="AM26" s="621" t="n"/>
+      <c r="AN26" s="324" t="n"/>
+      <c r="AO26" s="324" t="n"/>
+      <c r="AP26" s="324" t="n"/>
+      <c r="AQ26" s="324" t="n"/>
+      <c r="AR26" s="324" t="n"/>
+      <c r="AS26" s="324" t="n"/>
+      <c r="AT26" s="324" t="n"/>
+      <c r="AU26" s="324" t="n"/>
+      <c r="AV26" s="324" t="n"/>
+      <c r="AW26" s="324" t="n"/>
+      <c r="AX26" s="324" t="n"/>
+      <c r="AY26" s="324" t="n"/>
+      <c r="AZ26" s="324" t="n"/>
+      <c r="BA26" s="324" t="n"/>
+      <c r="BB26" s="324" t="n"/>
+      <c r="BC26" s="324" t="n"/>
+      <c r="BD26" s="326" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="567" t="inlineStr">
+      <c r="A27" s="622" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="22" t="n"/>
-      <c r="K27" s="568" t="n"/>
-      <c r="L27" s="569" t="n"/>
-      <c r="M27" s="569" t="n"/>
-      <c r="N27" s="569" t="n"/>
-      <c r="O27" s="569" t="n"/>
-      <c r="P27" s="569" t="n"/>
-      <c r="Q27" s="569" t="n"/>
-      <c r="R27" s="569" t="n"/>
-      <c r="S27" s="569" t="n"/>
-      <c r="T27" s="569" t="n"/>
-      <c r="U27" s="569" t="n"/>
-      <c r="V27" s="569" t="n"/>
-      <c r="W27" s="569" t="n"/>
-      <c r="X27" s="569" t="n"/>
-      <c r="Y27" s="569" t="n"/>
-      <c r="Z27" s="569" t="n"/>
-      <c r="AA27" s="569" t="n"/>
-      <c r="AB27" s="570" t="n"/>
-      <c r="AC27" s="571" t="inlineStr">
+      <c r="B27" s="281" t="n"/>
+      <c r="C27" s="281" t="n"/>
+      <c r="D27" s="281" t="n"/>
+      <c r="E27" s="281" t="n"/>
+      <c r="F27" s="281" t="n"/>
+      <c r="G27" s="281" t="n"/>
+      <c r="H27" s="281" t="n"/>
+      <c r="I27" s="281" t="n"/>
+      <c r="J27" s="282" t="n"/>
+      <c r="K27" s="623" t="n"/>
+      <c r="L27" s="335" t="n"/>
+      <c r="M27" s="335" t="n"/>
+      <c r="N27" s="335" t="n"/>
+      <c r="O27" s="335" t="n"/>
+      <c r="P27" s="335" t="n"/>
+      <c r="Q27" s="335" t="n"/>
+      <c r="R27" s="335" t="n"/>
+      <c r="S27" s="335" t="n"/>
+      <c r="T27" s="335" t="n"/>
+      <c r="U27" s="335" t="n"/>
+      <c r="V27" s="335" t="n"/>
+      <c r="W27" s="335" t="n"/>
+      <c r="X27" s="335" t="n"/>
+      <c r="Y27" s="335" t="n"/>
+      <c r="Z27" s="335" t="n"/>
+      <c r="AA27" s="335" t="n"/>
+      <c r="AB27" s="624" t="n"/>
+      <c r="AC27" s="625" t="inlineStr">
         <is>
           <t>Closeout Status</t>
         </is>
       </c>
-      <c r="AD27" s="19" t="n"/>
-      <c r="AE27" s="19" t="n"/>
-      <c r="AF27" s="19" t="n"/>
-      <c r="AG27" s="19" t="n"/>
-      <c r="AH27" s="19" t="n"/>
-      <c r="AI27" s="19" t="n"/>
-      <c r="AJ27" s="19" t="n"/>
-      <c r="AK27" s="19" t="n"/>
-      <c r="AL27" s="22" t="n"/>
-      <c r="AM27" s="568" t="n"/>
-      <c r="AN27" s="569" t="n"/>
-      <c r="AO27" s="569" t="n"/>
-      <c r="AP27" s="569" t="n"/>
-      <c r="AQ27" s="569" t="n"/>
-      <c r="AR27" s="569" t="n"/>
-      <c r="AS27" s="569" t="n"/>
-      <c r="AT27" s="569" t="n"/>
-      <c r="AU27" s="569" t="n"/>
-      <c r="AV27" s="569" t="n"/>
-      <c r="AW27" s="569" t="n"/>
-      <c r="AX27" s="569" t="n"/>
-      <c r="AY27" s="569" t="n"/>
-      <c r="AZ27" s="569" t="n"/>
-      <c r="BA27" s="569" t="n"/>
-      <c r="BB27" s="569" t="n"/>
-      <c r="BC27" s="569" t="n"/>
-      <c r="BD27" s="572" t="n"/>
+      <c r="AD27" s="281" t="n"/>
+      <c r="AE27" s="281" t="n"/>
+      <c r="AF27" s="281" t="n"/>
+      <c r="AG27" s="281" t="n"/>
+      <c r="AH27" s="281" t="n"/>
+      <c r="AI27" s="281" t="n"/>
+      <c r="AJ27" s="281" t="n"/>
+      <c r="AK27" s="281" t="n"/>
+      <c r="AL27" s="282" t="n"/>
+      <c r="AM27" s="626" t="n"/>
+      <c r="AN27" s="335" t="n"/>
+      <c r="AO27" s="335" t="n"/>
+      <c r="AP27" s="335" t="n"/>
+      <c r="AQ27" s="335" t="n"/>
+      <c r="AR27" s="335" t="n"/>
+      <c r="AS27" s="335" t="n"/>
+      <c r="AT27" s="335" t="n"/>
+      <c r="AU27" s="335" t="n"/>
+      <c r="AV27" s="335" t="n"/>
+      <c r="AW27" s="335" t="n"/>
+      <c r="AX27" s="335" t="n"/>
+      <c r="AY27" s="335" t="n"/>
+      <c r="AZ27" s="335" t="n"/>
+      <c r="BA27" s="335" t="n"/>
+      <c r="BB27" s="335" t="n"/>
+      <c r="BC27" s="335" t="n"/>
+      <c r="BD27" s="336" t="n"/>
     </row>
     <row r="28" ht="3" customHeight="1">
       <c r="A28" s="586" t="n"/>
@@ -8590,322 +8706,322 @@
       <c r="BD28" s="573" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="554" t="inlineStr">
+      <c r="A29" s="616" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="27" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
-      <c r="H29" s="27" t="n"/>
-      <c r="I29" s="27" t="n"/>
-      <c r="J29" s="27" t="n"/>
-      <c r="K29" s="27" t="n"/>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="27" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
-      <c r="Q29" s="27" t="n"/>
-      <c r="R29" s="27" t="n"/>
-      <c r="S29" s="27" t="n"/>
-      <c r="T29" s="27" t="n"/>
-      <c r="U29" s="27" t="n"/>
-      <c r="V29" s="27" t="n"/>
-      <c r="W29" s="27" t="n"/>
-      <c r="X29" s="27" t="n"/>
-      <c r="Y29" s="27" t="n"/>
-      <c r="Z29" s="27" t="n"/>
-      <c r="AA29" s="27" t="n"/>
-      <c r="AB29" s="27" t="n"/>
-      <c r="AC29" s="27" t="n"/>
-      <c r="AD29" s="27" t="n"/>
-      <c r="AE29" s="27" t="n"/>
-      <c r="AF29" s="27" t="n"/>
-      <c r="AG29" s="27" t="n"/>
-      <c r="AH29" s="27" t="n"/>
-      <c r="AI29" s="27" t="n"/>
-      <c r="AJ29" s="27" t="n"/>
-      <c r="AK29" s="27" t="n"/>
-      <c r="AL29" s="27" t="n"/>
-      <c r="AM29" s="27" t="n"/>
-      <c r="AN29" s="27" t="n"/>
-      <c r="AO29" s="27" t="n"/>
-      <c r="AP29" s="27" t="n"/>
-      <c r="AQ29" s="27" t="n"/>
-      <c r="AR29" s="27" t="n"/>
-      <c r="AS29" s="27" t="n"/>
-      <c r="AT29" s="27" t="n"/>
-      <c r="AU29" s="27" t="n"/>
-      <c r="AV29" s="27" t="n"/>
-      <c r="AW29" s="27" t="n"/>
-      <c r="AX29" s="27" t="n"/>
-      <c r="AY29" s="27" t="n"/>
-      <c r="AZ29" s="27" t="n"/>
-      <c r="BA29" s="27" t="n"/>
-      <c r="BB29" s="27" t="n"/>
-      <c r="BC29" s="27" t="n"/>
-      <c r="BD29" s="28" t="n"/>
+      <c r="B29" s="285" t="n"/>
+      <c r="C29" s="285" t="n"/>
+      <c r="D29" s="285" t="n"/>
+      <c r="E29" s="285" t="n"/>
+      <c r="F29" s="285" t="n"/>
+      <c r="G29" s="285" t="n"/>
+      <c r="H29" s="285" t="n"/>
+      <c r="I29" s="285" t="n"/>
+      <c r="J29" s="285" t="n"/>
+      <c r="K29" s="285" t="n"/>
+      <c r="L29" s="285" t="n"/>
+      <c r="M29" s="285" t="n"/>
+      <c r="N29" s="285" t="n"/>
+      <c r="O29" s="285" t="n"/>
+      <c r="P29" s="285" t="n"/>
+      <c r="Q29" s="285" t="n"/>
+      <c r="R29" s="285" t="n"/>
+      <c r="S29" s="285" t="n"/>
+      <c r="T29" s="285" t="n"/>
+      <c r="U29" s="285" t="n"/>
+      <c r="V29" s="285" t="n"/>
+      <c r="W29" s="285" t="n"/>
+      <c r="X29" s="285" t="n"/>
+      <c r="Y29" s="285" t="n"/>
+      <c r="Z29" s="285" t="n"/>
+      <c r="AA29" s="285" t="n"/>
+      <c r="AB29" s="285" t="n"/>
+      <c r="AC29" s="285" t="n"/>
+      <c r="AD29" s="285" t="n"/>
+      <c r="AE29" s="285" t="n"/>
+      <c r="AF29" s="285" t="n"/>
+      <c r="AG29" s="285" t="n"/>
+      <c r="AH29" s="285" t="n"/>
+      <c r="AI29" s="285" t="n"/>
+      <c r="AJ29" s="285" t="n"/>
+      <c r="AK29" s="285" t="n"/>
+      <c r="AL29" s="285" t="n"/>
+      <c r="AM29" s="285" t="n"/>
+      <c r="AN29" s="285" t="n"/>
+      <c r="AO29" s="285" t="n"/>
+      <c r="AP29" s="285" t="n"/>
+      <c r="AQ29" s="285" t="n"/>
+      <c r="AR29" s="285" t="n"/>
+      <c r="AS29" s="285" t="n"/>
+      <c r="AT29" s="285" t="n"/>
+      <c r="AU29" s="285" t="n"/>
+      <c r="AV29" s="285" t="n"/>
+      <c r="AW29" s="285" t="n"/>
+      <c r="AX29" s="285" t="n"/>
+      <c r="AY29" s="285" t="n"/>
+      <c r="AZ29" s="285" t="n"/>
+      <c r="BA29" s="285" t="n"/>
+      <c r="BB29" s="285" t="n"/>
+      <c r="BC29" s="285" t="n"/>
+      <c r="BD29" s="286" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="574" t="inlineStr">
+      <c r="A30" s="627" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="6" t="n"/>
-      <c r="S30" s="592" t="inlineStr">
+      <c r="B30" s="271" t="n"/>
+      <c r="C30" s="271" t="n"/>
+      <c r="D30" s="271" t="n"/>
+      <c r="E30" s="271" t="n"/>
+      <c r="F30" s="271" t="n"/>
+      <c r="G30" s="271" t="n"/>
+      <c r="H30" s="271" t="n"/>
+      <c r="I30" s="271" t="n"/>
+      <c r="J30" s="271" t="n"/>
+      <c r="K30" s="271" t="n"/>
+      <c r="L30" s="271" t="n"/>
+      <c r="M30" s="271" t="n"/>
+      <c r="N30" s="271" t="n"/>
+      <c r="O30" s="271" t="n"/>
+      <c r="P30" s="271" t="n"/>
+      <c r="Q30" s="271" t="n"/>
+      <c r="R30" s="272" t="n"/>
+      <c r="S30" s="636" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="5" t="n"/>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="n"/>
-      <c r="Y30" s="5" t="n"/>
-      <c r="Z30" s="5" t="n"/>
-      <c r="AA30" s="5" t="n"/>
-      <c r="AB30" s="5" t="n"/>
-      <c r="AC30" s="5" t="n"/>
-      <c r="AD30" s="5" t="n"/>
-      <c r="AE30" s="5" t="n"/>
-      <c r="AF30" s="5" t="n"/>
-      <c r="AG30" s="5" t="n"/>
-      <c r="AH30" s="5" t="n"/>
-      <c r="AI30" s="5" t="n"/>
-      <c r="AJ30" s="6" t="n"/>
-      <c r="AK30" s="592" t="inlineStr">
+      <c r="T30" s="271" t="n"/>
+      <c r="U30" s="271" t="n"/>
+      <c r="V30" s="271" t="n"/>
+      <c r="W30" s="271" t="n"/>
+      <c r="X30" s="271" t="n"/>
+      <c r="Y30" s="271" t="n"/>
+      <c r="Z30" s="271" t="n"/>
+      <c r="AA30" s="271" t="n"/>
+      <c r="AB30" s="271" t="n"/>
+      <c r="AC30" s="271" t="n"/>
+      <c r="AD30" s="271" t="n"/>
+      <c r="AE30" s="271" t="n"/>
+      <c r="AF30" s="271" t="n"/>
+      <c r="AG30" s="271" t="n"/>
+      <c r="AH30" s="271" t="n"/>
+      <c r="AI30" s="271" t="n"/>
+      <c r="AJ30" s="272" t="n"/>
+      <c r="AK30" s="637" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="5" t="n"/>
-      <c r="AM30" s="5" t="n"/>
-      <c r="AN30" s="5" t="n"/>
-      <c r="AO30" s="5" t="n"/>
-      <c r="AP30" s="5" t="n"/>
-      <c r="AQ30" s="5" t="n"/>
-      <c r="AR30" s="5" t="n"/>
-      <c r="AS30" s="5" t="n"/>
-      <c r="AT30" s="5" t="n"/>
-      <c r="AU30" s="5" t="n"/>
-      <c r="AV30" s="5" t="n"/>
-      <c r="AW30" s="5" t="n"/>
-      <c r="AX30" s="5" t="n"/>
-      <c r="AY30" s="5" t="n"/>
-      <c r="AZ30" s="5" t="n"/>
-      <c r="BA30" s="5" t="n"/>
-      <c r="BB30" s="5" t="n"/>
-      <c r="BC30" s="5" t="n"/>
-      <c r="BD30" s="8" t="n"/>
+      <c r="AL30" s="271" t="n"/>
+      <c r="AM30" s="271" t="n"/>
+      <c r="AN30" s="271" t="n"/>
+      <c r="AO30" s="271" t="n"/>
+      <c r="AP30" s="271" t="n"/>
+      <c r="AQ30" s="271" t="n"/>
+      <c r="AR30" s="271" t="n"/>
+      <c r="AS30" s="271" t="n"/>
+      <c r="AT30" s="271" t="n"/>
+      <c r="AU30" s="271" t="n"/>
+      <c r="AV30" s="271" t="n"/>
+      <c r="AW30" s="271" t="n"/>
+      <c r="AX30" s="271" t="n"/>
+      <c r="AY30" s="271" t="n"/>
+      <c r="AZ30" s="271" t="n"/>
+      <c r="BA30" s="271" t="n"/>
+      <c r="BB30" s="271" t="n"/>
+      <c r="BC30" s="271" t="n"/>
+      <c r="BD30" s="274" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="593" t="inlineStr">
+      <c r="A31" s="638" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="563" t="n"/>
-      <c r="C31" s="563" t="n"/>
-      <c r="D31" s="563" t="n"/>
-      <c r="E31" s="563" t="n"/>
-      <c r="F31" s="563" t="n"/>
-      <c r="G31" s="563" t="n"/>
-      <c r="H31" s="563" t="n"/>
-      <c r="I31" s="563" t="n"/>
-      <c r="J31" s="563" t="n"/>
-      <c r="K31" s="563" t="n"/>
-      <c r="L31" s="563" t="n"/>
-      <c r="M31" s="563" t="n"/>
-      <c r="N31" s="563" t="n"/>
-      <c r="O31" s="563" t="n"/>
-      <c r="P31" s="563" t="n"/>
-      <c r="Q31" s="563" t="n"/>
-      <c r="R31" s="564" t="n"/>
-      <c r="S31" s="594" t="inlineStr">
+      <c r="B31" s="332" t="n"/>
+      <c r="C31" s="332" t="n"/>
+      <c r="D31" s="332" t="n"/>
+      <c r="E31" s="332" t="n"/>
+      <c r="F31" s="332" t="n"/>
+      <c r="G31" s="332" t="n"/>
+      <c r="H31" s="332" t="n"/>
+      <c r="I31" s="332" t="n"/>
+      <c r="J31" s="332" t="n"/>
+      <c r="K31" s="332" t="n"/>
+      <c r="L31" s="332" t="n"/>
+      <c r="M31" s="332" t="n"/>
+      <c r="N31" s="332" t="n"/>
+      <c r="O31" s="332" t="n"/>
+      <c r="P31" s="332" t="n"/>
+      <c r="Q31" s="332" t="n"/>
+      <c r="R31" s="639" t="n"/>
+      <c r="S31" s="640" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="563" t="n"/>
-      <c r="U31" s="563" t="n"/>
-      <c r="V31" s="563" t="n"/>
-      <c r="W31" s="563" t="n"/>
-      <c r="X31" s="563" t="n"/>
-      <c r="Y31" s="563" t="n"/>
-      <c r="Z31" s="563" t="n"/>
-      <c r="AA31" s="563" t="n"/>
-      <c r="AB31" s="563" t="n"/>
-      <c r="AC31" s="563" t="n"/>
-      <c r="AD31" s="563" t="n"/>
-      <c r="AE31" s="563" t="n"/>
-      <c r="AF31" s="563" t="n"/>
-      <c r="AG31" s="563" t="n"/>
-      <c r="AH31" s="563" t="n"/>
-      <c r="AI31" s="563" t="n"/>
-      <c r="AJ31" s="564" t="n"/>
-      <c r="AK31" s="594" t="inlineStr">
+      <c r="T31" s="332" t="n"/>
+      <c r="U31" s="332" t="n"/>
+      <c r="V31" s="332" t="n"/>
+      <c r="W31" s="332" t="n"/>
+      <c r="X31" s="332" t="n"/>
+      <c r="Y31" s="332" t="n"/>
+      <c r="Z31" s="332" t="n"/>
+      <c r="AA31" s="332" t="n"/>
+      <c r="AB31" s="332" t="n"/>
+      <c r="AC31" s="332" t="n"/>
+      <c r="AD31" s="332" t="n"/>
+      <c r="AE31" s="332" t="n"/>
+      <c r="AF31" s="332" t="n"/>
+      <c r="AG31" s="332" t="n"/>
+      <c r="AH31" s="332" t="n"/>
+      <c r="AI31" s="332" t="n"/>
+      <c r="AJ31" s="639" t="n"/>
+      <c r="AK31" s="641" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="563" t="n"/>
-      <c r="AM31" s="563" t="n"/>
-      <c r="AN31" s="563" t="n"/>
-      <c r="AO31" s="563" t="n"/>
-      <c r="AP31" s="563" t="n"/>
-      <c r="AQ31" s="563" t="n"/>
-      <c r="AR31" s="563" t="n"/>
-      <c r="AS31" s="563" t="n"/>
-      <c r="AT31" s="563" t="n"/>
-      <c r="AU31" s="563" t="n"/>
-      <c r="AV31" s="563" t="n"/>
-      <c r="AW31" s="563" t="n"/>
-      <c r="AX31" s="563" t="n"/>
-      <c r="AY31" s="563" t="n"/>
-      <c r="AZ31" s="563" t="n"/>
-      <c r="BA31" s="563" t="n"/>
-      <c r="BB31" s="563" t="n"/>
-      <c r="BC31" s="563" t="n"/>
-      <c r="BD31" s="566" t="n"/>
+      <c r="AL31" s="332" t="n"/>
+      <c r="AM31" s="332" t="n"/>
+      <c r="AN31" s="332" t="n"/>
+      <c r="AO31" s="332" t="n"/>
+      <c r="AP31" s="332" t="n"/>
+      <c r="AQ31" s="332" t="n"/>
+      <c r="AR31" s="332" t="n"/>
+      <c r="AS31" s="332" t="n"/>
+      <c r="AT31" s="332" t="n"/>
+      <c r="AU31" s="332" t="n"/>
+      <c r="AV31" s="332" t="n"/>
+      <c r="AW31" s="332" t="n"/>
+      <c r="AX31" s="332" t="n"/>
+      <c r="AY31" s="332" t="n"/>
+      <c r="AZ31" s="332" t="n"/>
+      <c r="BA31" s="332" t="n"/>
+      <c r="BB31" s="332" t="n"/>
+      <c r="BC31" s="332" t="n"/>
+      <c r="BD31" s="333" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="595" t="n"/>
-      <c r="B32" s="563" t="n"/>
-      <c r="C32" s="563" t="n"/>
-      <c r="D32" s="563" t="n"/>
-      <c r="E32" s="563" t="n"/>
-      <c r="F32" s="563" t="n"/>
-      <c r="G32" s="563" t="n"/>
-      <c r="H32" s="563" t="n"/>
-      <c r="I32" s="563" t="n"/>
-      <c r="J32" s="563" t="n"/>
-      <c r="K32" s="563" t="n"/>
-      <c r="L32" s="563" t="n"/>
-      <c r="M32" s="563" t="n"/>
-      <c r="N32" s="563" t="n"/>
-      <c r="O32" s="563" t="n"/>
-      <c r="P32" s="563" t="n"/>
-      <c r="Q32" s="563" t="n"/>
-      <c r="R32" s="564" t="n"/>
-      <c r="S32" s="563" t="n"/>
-      <c r="T32" s="563" t="n"/>
-      <c r="U32" s="563" t="n"/>
-      <c r="V32" s="563" t="n"/>
-      <c r="W32" s="563" t="n"/>
-      <c r="X32" s="563" t="n"/>
-      <c r="Y32" s="563" t="n"/>
-      <c r="Z32" s="563" t="n"/>
-      <c r="AA32" s="563" t="n"/>
-      <c r="AB32" s="563" t="n"/>
-      <c r="AC32" s="563" t="n"/>
-      <c r="AD32" s="563" t="n"/>
-      <c r="AE32" s="563" t="n"/>
-      <c r="AF32" s="563" t="n"/>
-      <c r="AG32" s="563" t="n"/>
-      <c r="AH32" s="563" t="n"/>
-      <c r="AI32" s="563" t="n"/>
-      <c r="AJ32" s="564" t="n"/>
-      <c r="AK32" s="563" t="n"/>
-      <c r="AL32" s="563" t="n"/>
-      <c r="AM32" s="563" t="n"/>
-      <c r="AN32" s="563" t="n"/>
-      <c r="AO32" s="563" t="n"/>
-      <c r="AP32" s="563" t="n"/>
-      <c r="AQ32" s="563" t="n"/>
-      <c r="AR32" s="563" t="n"/>
-      <c r="AS32" s="563" t="n"/>
-      <c r="AT32" s="563" t="n"/>
-      <c r="AU32" s="563" t="n"/>
-      <c r="AV32" s="563" t="n"/>
-      <c r="AW32" s="563" t="n"/>
-      <c r="AX32" s="563" t="n"/>
-      <c r="AY32" s="563" t="n"/>
-      <c r="AZ32" s="563" t="n"/>
-      <c r="BA32" s="563" t="n"/>
-      <c r="BB32" s="563" t="n"/>
-      <c r="BC32" s="563" t="n"/>
-      <c r="BD32" s="566" t="n"/>
+      <c r="A32" s="331" t="n"/>
+      <c r="B32" s="332" t="n"/>
+      <c r="C32" s="332" t="n"/>
+      <c r="D32" s="332" t="n"/>
+      <c r="E32" s="332" t="n"/>
+      <c r="F32" s="332" t="n"/>
+      <c r="G32" s="332" t="n"/>
+      <c r="H32" s="332" t="n"/>
+      <c r="I32" s="332" t="n"/>
+      <c r="J32" s="332" t="n"/>
+      <c r="K32" s="332" t="n"/>
+      <c r="L32" s="332" t="n"/>
+      <c r="M32" s="332" t="n"/>
+      <c r="N32" s="332" t="n"/>
+      <c r="O32" s="332" t="n"/>
+      <c r="P32" s="332" t="n"/>
+      <c r="Q32" s="332" t="n"/>
+      <c r="R32" s="639" t="n"/>
+      <c r="S32" s="332" t="n"/>
+      <c r="T32" s="332" t="n"/>
+      <c r="U32" s="332" t="n"/>
+      <c r="V32" s="332" t="n"/>
+      <c r="W32" s="332" t="n"/>
+      <c r="X32" s="332" t="n"/>
+      <c r="Y32" s="332" t="n"/>
+      <c r="Z32" s="332" t="n"/>
+      <c r="AA32" s="332" t="n"/>
+      <c r="AB32" s="332" t="n"/>
+      <c r="AC32" s="332" t="n"/>
+      <c r="AD32" s="332" t="n"/>
+      <c r="AE32" s="332" t="n"/>
+      <c r="AF32" s="332" t="n"/>
+      <c r="AG32" s="332" t="n"/>
+      <c r="AH32" s="332" t="n"/>
+      <c r="AI32" s="332" t="n"/>
+      <c r="AJ32" s="639" t="n"/>
+      <c r="AK32" s="332" t="n"/>
+      <c r="AL32" s="332" t="n"/>
+      <c r="AM32" s="332" t="n"/>
+      <c r="AN32" s="332" t="n"/>
+      <c r="AO32" s="332" t="n"/>
+      <c r="AP32" s="332" t="n"/>
+      <c r="AQ32" s="332" t="n"/>
+      <c r="AR32" s="332" t="n"/>
+      <c r="AS32" s="332" t="n"/>
+      <c r="AT32" s="332" t="n"/>
+      <c r="AU32" s="332" t="n"/>
+      <c r="AV32" s="332" t="n"/>
+      <c r="AW32" s="332" t="n"/>
+      <c r="AX32" s="332" t="n"/>
+      <c r="AY32" s="332" t="n"/>
+      <c r="AZ32" s="332" t="n"/>
+      <c r="BA32" s="332" t="n"/>
+      <c r="BB32" s="332" t="n"/>
+      <c r="BC32" s="332" t="n"/>
+      <c r="BD32" s="333" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="596" t="n"/>
-      <c r="B33" s="569" t="n"/>
-      <c r="C33" s="569" t="n"/>
-      <c r="D33" s="569" t="n"/>
-      <c r="E33" s="569" t="n"/>
-      <c r="F33" s="569" t="n"/>
-      <c r="G33" s="569" t="n"/>
-      <c r="H33" s="569" t="n"/>
-      <c r="I33" s="569" t="n"/>
-      <c r="J33" s="569" t="n"/>
-      <c r="K33" s="569" t="n"/>
-      <c r="L33" s="569" t="n"/>
-      <c r="M33" s="569" t="n"/>
-      <c r="N33" s="569" t="n"/>
-      <c r="O33" s="569" t="n"/>
-      <c r="P33" s="569" t="n"/>
-      <c r="Q33" s="569" t="n"/>
-      <c r="R33" s="570" t="n"/>
-      <c r="S33" s="569" t="n"/>
-      <c r="T33" s="569" t="n"/>
-      <c r="U33" s="569" t="n"/>
-      <c r="V33" s="569" t="n"/>
-      <c r="W33" s="569" t="n"/>
-      <c r="X33" s="569" t="n"/>
-      <c r="Y33" s="569" t="n"/>
-      <c r="Z33" s="569" t="n"/>
-      <c r="AA33" s="569" t="n"/>
-      <c r="AB33" s="569" t="n"/>
-      <c r="AC33" s="569" t="n"/>
-      <c r="AD33" s="569" t="n"/>
-      <c r="AE33" s="569" t="n"/>
-      <c r="AF33" s="569" t="n"/>
-      <c r="AG33" s="569" t="n"/>
-      <c r="AH33" s="569" t="n"/>
-      <c r="AI33" s="569" t="n"/>
-      <c r="AJ33" s="570" t="n"/>
-      <c r="AK33" s="569" t="n"/>
-      <c r="AL33" s="569" t="n"/>
-      <c r="AM33" s="569" t="n"/>
-      <c r="AN33" s="569" t="n"/>
-      <c r="AO33" s="569" t="n"/>
-      <c r="AP33" s="569" t="n"/>
-      <c r="AQ33" s="569" t="n"/>
-      <c r="AR33" s="569" t="n"/>
-      <c r="AS33" s="569" t="n"/>
-      <c r="AT33" s="569" t="n"/>
-      <c r="AU33" s="569" t="n"/>
-      <c r="AV33" s="569" t="n"/>
-      <c r="AW33" s="569" t="n"/>
-      <c r="AX33" s="569" t="n"/>
-      <c r="AY33" s="569" t="n"/>
-      <c r="AZ33" s="569" t="n"/>
-      <c r="BA33" s="569" t="n"/>
-      <c r="BB33" s="569" t="n"/>
-      <c r="BC33" s="569" t="n"/>
-      <c r="BD33" s="572" t="n"/>
+      <c r="A33" s="642" t="n"/>
+      <c r="B33" s="324" t="n"/>
+      <c r="C33" s="324" t="n"/>
+      <c r="D33" s="324" t="n"/>
+      <c r="E33" s="324" t="n"/>
+      <c r="F33" s="324" t="n"/>
+      <c r="G33" s="324" t="n"/>
+      <c r="H33" s="324" t="n"/>
+      <c r="I33" s="324" t="n"/>
+      <c r="J33" s="324" t="n"/>
+      <c r="K33" s="324" t="n"/>
+      <c r="L33" s="324" t="n"/>
+      <c r="M33" s="324" t="n"/>
+      <c r="N33" s="324" t="n"/>
+      <c r="O33" s="324" t="n"/>
+      <c r="P33" s="324" t="n"/>
+      <c r="Q33" s="324" t="n"/>
+      <c r="R33" s="325" t="n"/>
+      <c r="S33" s="324" t="n"/>
+      <c r="T33" s="324" t="n"/>
+      <c r="U33" s="324" t="n"/>
+      <c r="V33" s="324" t="n"/>
+      <c r="W33" s="324" t="n"/>
+      <c r="X33" s="324" t="n"/>
+      <c r="Y33" s="324" t="n"/>
+      <c r="Z33" s="324" t="n"/>
+      <c r="AA33" s="324" t="n"/>
+      <c r="AB33" s="324" t="n"/>
+      <c r="AC33" s="324" t="n"/>
+      <c r="AD33" s="324" t="n"/>
+      <c r="AE33" s="324" t="n"/>
+      <c r="AF33" s="324" t="n"/>
+      <c r="AG33" s="324" t="n"/>
+      <c r="AH33" s="324" t="n"/>
+      <c r="AI33" s="324" t="n"/>
+      <c r="AJ33" s="325" t="n"/>
+      <c r="AK33" s="324" t="n"/>
+      <c r="AL33" s="324" t="n"/>
+      <c r="AM33" s="324" t="n"/>
+      <c r="AN33" s="324" t="n"/>
+      <c r="AO33" s="324" t="n"/>
+      <c r="AP33" s="324" t="n"/>
+      <c r="AQ33" s="324" t="n"/>
+      <c r="AR33" s="324" t="n"/>
+      <c r="AS33" s="324" t="n"/>
+      <c r="AT33" s="324" t="n"/>
+      <c r="AU33" s="324" t="n"/>
+      <c r="AV33" s="324" t="n"/>
+      <c r="AW33" s="324" t="n"/>
+      <c r="AX33" s="324" t="n"/>
+      <c r="AY33" s="324" t="n"/>
+      <c r="AZ33" s="324" t="n"/>
+      <c r="BA33" s="324" t="n"/>
+      <c r="BB33" s="324" t="n"/>
+      <c r="BC33" s="324" t="n"/>
+      <c r="BD33" s="326" t="n"/>
     </row>
     <row r="34" ht="3" customHeight="1">
       <c r="A34" s="597" t="n"/>
@@ -8966,66 +9082,66 @@
       <c r="BD34" s="573" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="598" t="inlineStr">
+      <c r="A35" s="643" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="27" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
-      <c r="H35" s="27" t="n"/>
-      <c r="I35" s="27" t="n"/>
-      <c r="J35" s="27" t="n"/>
-      <c r="K35" s="27" t="n"/>
-      <c r="L35" s="27" t="n"/>
-      <c r="M35" s="27" t="n"/>
-      <c r="N35" s="27" t="n"/>
-      <c r="O35" s="27" t="n"/>
-      <c r="P35" s="27" t="n"/>
-      <c r="Q35" s="27" t="n"/>
-      <c r="R35" s="27" t="n"/>
-      <c r="S35" s="27" t="n"/>
-      <c r="T35" s="27" t="n"/>
-      <c r="U35" s="27" t="n"/>
-      <c r="V35" s="27" t="n"/>
-      <c r="W35" s="27" t="n"/>
-      <c r="X35" s="27" t="n"/>
-      <c r="Y35" s="27" t="n"/>
-      <c r="Z35" s="27" t="n"/>
-      <c r="AA35" s="27" t="n"/>
-      <c r="AB35" s="27" t="n"/>
-      <c r="AC35" s="27" t="n"/>
-      <c r="AD35" s="27" t="n"/>
-      <c r="AE35" s="27" t="n"/>
-      <c r="AF35" s="27" t="n"/>
-      <c r="AG35" s="27" t="n"/>
-      <c r="AH35" s="27" t="n"/>
-      <c r="AI35" s="27" t="n"/>
-      <c r="AJ35" s="27" t="n"/>
-      <c r="AK35" s="27" t="n"/>
-      <c r="AL35" s="27" t="n"/>
-      <c r="AM35" s="27" t="n"/>
-      <c r="AN35" s="27" t="n"/>
-      <c r="AO35" s="27" t="n"/>
-      <c r="AP35" s="27" t="n"/>
-      <c r="AQ35" s="27" t="n"/>
-      <c r="AR35" s="27" t="n"/>
-      <c r="AS35" s="27" t="n"/>
-      <c r="AT35" s="27" t="n"/>
-      <c r="AU35" s="27" t="n"/>
-      <c r="AV35" s="27" t="n"/>
-      <c r="AW35" s="27" t="n"/>
-      <c r="AX35" s="27" t="n"/>
-      <c r="AY35" s="27" t="n"/>
-      <c r="AZ35" s="27" t="n"/>
-      <c r="BA35" s="27" t="n"/>
-      <c r="BB35" s="27" t="n"/>
-      <c r="BC35" s="27" t="n"/>
-      <c r="BD35" s="28" t="n"/>
+      <c r="B35" s="285" t="n"/>
+      <c r="C35" s="285" t="n"/>
+      <c r="D35" s="285" t="n"/>
+      <c r="E35" s="285" t="n"/>
+      <c r="F35" s="285" t="n"/>
+      <c r="G35" s="285" t="n"/>
+      <c r="H35" s="285" t="n"/>
+      <c r="I35" s="285" t="n"/>
+      <c r="J35" s="285" t="n"/>
+      <c r="K35" s="285" t="n"/>
+      <c r="L35" s="285" t="n"/>
+      <c r="M35" s="285" t="n"/>
+      <c r="N35" s="285" t="n"/>
+      <c r="O35" s="285" t="n"/>
+      <c r="P35" s="285" t="n"/>
+      <c r="Q35" s="285" t="n"/>
+      <c r="R35" s="285" t="n"/>
+      <c r="S35" s="285" t="n"/>
+      <c r="T35" s="285" t="n"/>
+      <c r="U35" s="285" t="n"/>
+      <c r="V35" s="285" t="n"/>
+      <c r="W35" s="285" t="n"/>
+      <c r="X35" s="285" t="n"/>
+      <c r="Y35" s="285" t="n"/>
+      <c r="Z35" s="285" t="n"/>
+      <c r="AA35" s="285" t="n"/>
+      <c r="AB35" s="285" t="n"/>
+      <c r="AC35" s="285" t="n"/>
+      <c r="AD35" s="285" t="n"/>
+      <c r="AE35" s="285" t="n"/>
+      <c r="AF35" s="285" t="n"/>
+      <c r="AG35" s="285" t="n"/>
+      <c r="AH35" s="285" t="n"/>
+      <c r="AI35" s="285" t="n"/>
+      <c r="AJ35" s="285" t="n"/>
+      <c r="AK35" s="285" t="n"/>
+      <c r="AL35" s="285" t="n"/>
+      <c r="AM35" s="285" t="n"/>
+      <c r="AN35" s="285" t="n"/>
+      <c r="AO35" s="285" t="n"/>
+      <c r="AP35" s="285" t="n"/>
+      <c r="AQ35" s="285" t="n"/>
+      <c r="AR35" s="285" t="n"/>
+      <c r="AS35" s="285" t="n"/>
+      <c r="AT35" s="285" t="n"/>
+      <c r="AU35" s="285" t="n"/>
+      <c r="AV35" s="285" t="n"/>
+      <c r="AW35" s="285" t="n"/>
+      <c r="AX35" s="285" t="n"/>
+      <c r="AY35" s="285" t="n"/>
+      <c r="AZ35" s="285" t="n"/>
+      <c r="BA35" s="285" t="n"/>
+      <c r="BB35" s="285" t="n"/>
+      <c r="BC35" s="285" t="n"/>
+      <c r="BD35" s="286" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -9199,7 +9315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9424,7 +9540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10368,7 +10484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU15"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11211,7 +11327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU8"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -22,10 +22,414 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+  <si>
+    <t>  1. LOT / PLAN / REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>  4. DISPOSITION / RELEASE</t>
+  </si>
+  <si>
+    <t>  5. APPROVAL / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$16)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$5)+1</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-001</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-002</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-003</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-004</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-006</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QA-007</t>
+  </si>
+  <si>
+    <t>ANNEX ANNEX-QMS-020</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
+  </si>
+  <si>
+    <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CLOSEOUT_STATE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>Characteristic / Requirement</t>
+  </si>
+  <si>
+    <t>Check Group</t>
+  </si>
+  <si>
+    <t>Cleanliness / Packaging Verified (YES/NO)</t>
+  </si>
+  <si>
+    <t>Close When</t>
+  </si>
+  <si>
+    <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
+  </si>
+  <si>
+    <t>Closeout Status</t>
+  </si>
+  <si>
+    <t>Cross-Reference Boundary</t>
+  </si>
+  <si>
+    <t>DISPOSITION_GATE</t>
+  </si>
+  <si>
+    <t>Disposition / Release Decision</t>
+  </si>
+  <si>
+    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Epicor transaction + M365 evidence</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>Evidence Package Ref</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Evidence Reference / Attachment Guidance</t>
+  </si>
+  <si>
+    <t>Evidence item 1</t>
+  </si>
+  <si>
+    <t>Evidence item 2</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FRM-641</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Final Inspection Report</t>
+  </si>
+  <si>
+    <t>Final Inspection Report ID</t>
+  </si>
+  <si>
+    <t>Final Release Status</t>
+  </si>
+  <si>
+    <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Inspection Basis</t>
+  </si>
+  <si>
+    <t>Inspector</t>
+  </si>
+  <si>
+    <t>Job / Shipment</t>
+  </si>
+  <si>
+    <t>Label / Doc Verified (YES/NO)</t>
+  </si>
+  <si>
+    <t>Link or reference ID</t>
+  </si>
+  <si>
+    <t>Linked NCR / Concession</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Method / Inspection Basis</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOT CLOSED</t>
+  </si>
+  <si>
+    <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OWNER_DEPT</t>
+  </si>
+  <si>
+    <t>Open When</t>
+  </si>
+  <si>
+    <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
+  </si>
+  <si>
+    <t>Operational trigger</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Part No. / Revision</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Prepared by / Date-Time</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Quality Authority</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Reference plan / lot / method / release documents from their owning source.</t>
+  </si>
+  <si>
+    <t>Reference to the correct evidence folder, shared location or dossier package.</t>
+  </si>
+  <si>
+    <t>Release / closure rule</t>
+  </si>
+  <si>
+    <t>Requirement / Characteristic</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Result Detail</t>
+  </si>
+  <si>
+    <t>Reviewed by</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SOP SOP-605</t>
+  </si>
+  <si>
+    <t>SOP-605 — Kiểm tra cuối, CoC và phê duyệt giao hàng | HESEM QMS</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>This form does not replace SOP-605; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-605; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+  </si>
+  <si>
+    <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
+  </si>
+  <si>
+    <t>Upstream References / Import Guidance</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>Value / Reference</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI WI-605</t>
+  </si>
+  <si>
+    <t>WI-605 — Kiểm cuối, CoC/CofC, bàn giao phát hành giao hàng</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-605-final-inspection-coc-and-shipment-release.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-605-final-inspection-coc-and-shipment-release-handoff.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="85">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -507,8 +911,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -765,8 +1174,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="371">
+  <borders count="374">
     <border>
       <left/>
       <right/>
@@ -4774,11 +5188,45 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="644">
+  <cellXfs count="647">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6418,6 +6866,15 @@
     </xf>
     <xf numFmtId="0" fontId="78" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9082,66 +9539,66 @@
       <c r="BD34" s="573" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="643" t="inlineStr">
+      <c r="A35" s="644" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B35" s="285" t="n"/>
-      <c r="C35" s="285" t="n"/>
-      <c r="D35" s="285" t="n"/>
-      <c r="E35" s="285" t="n"/>
-      <c r="F35" s="285" t="n"/>
-      <c r="G35" s="285" t="n"/>
-      <c r="H35" s="285" t="n"/>
-      <c r="I35" s="285" t="n"/>
-      <c r="J35" s="285" t="n"/>
-      <c r="K35" s="285" t="n"/>
-      <c r="L35" s="285" t="n"/>
-      <c r="M35" s="285" t="n"/>
-      <c r="N35" s="285" t="n"/>
-      <c r="O35" s="285" t="n"/>
-      <c r="P35" s="285" t="n"/>
-      <c r="Q35" s="285" t="n"/>
-      <c r="R35" s="285" t="n"/>
-      <c r="S35" s="285" t="n"/>
-      <c r="T35" s="285" t="n"/>
-      <c r="U35" s="285" t="n"/>
-      <c r="V35" s="285" t="n"/>
-      <c r="W35" s="285" t="n"/>
-      <c r="X35" s="285" t="n"/>
-      <c r="Y35" s="285" t="n"/>
-      <c r="Z35" s="285" t="n"/>
-      <c r="AA35" s="285" t="n"/>
-      <c r="AB35" s="285" t="n"/>
-      <c r="AC35" s="285" t="n"/>
-      <c r="AD35" s="285" t="n"/>
-      <c r="AE35" s="285" t="n"/>
-      <c r="AF35" s="285" t="n"/>
-      <c r="AG35" s="285" t="n"/>
-      <c r="AH35" s="285" t="n"/>
-      <c r="AI35" s="285" t="n"/>
-      <c r="AJ35" s="285" t="n"/>
-      <c r="AK35" s="285" t="n"/>
-      <c r="AL35" s="285" t="n"/>
-      <c r="AM35" s="285" t="n"/>
-      <c r="AN35" s="285" t="n"/>
-      <c r="AO35" s="285" t="n"/>
-      <c r="AP35" s="285" t="n"/>
-      <c r="AQ35" s="285" t="n"/>
-      <c r="AR35" s="285" t="n"/>
-      <c r="AS35" s="285" t="n"/>
-      <c r="AT35" s="285" t="n"/>
-      <c r="AU35" s="285" t="n"/>
-      <c r="AV35" s="285" t="n"/>
-      <c r="AW35" s="285" t="n"/>
-      <c r="AX35" s="285" t="n"/>
-      <c r="AY35" s="285" t="n"/>
-      <c r="AZ35" s="285" t="n"/>
-      <c r="BA35" s="285" t="n"/>
-      <c r="BB35" s="285" t="n"/>
-      <c r="BC35" s="285" t="n"/>
-      <c r="BD35" s="286" t="n"/>
+      <c r="B35" s="645" t="n"/>
+      <c r="C35" s="645" t="n"/>
+      <c r="D35" s="645" t="n"/>
+      <c r="E35" s="645" t="n"/>
+      <c r="F35" s="645" t="n"/>
+      <c r="G35" s="645" t="n"/>
+      <c r="H35" s="645" t="n"/>
+      <c r="I35" s="645" t="n"/>
+      <c r="J35" s="645" t="n"/>
+      <c r="K35" s="645" t="n"/>
+      <c r="L35" s="645" t="n"/>
+      <c r="M35" s="645" t="n"/>
+      <c r="N35" s="645" t="n"/>
+      <c r="O35" s="645" t="n"/>
+      <c r="P35" s="645" t="n"/>
+      <c r="Q35" s="645" t="n"/>
+      <c r="R35" s="645" t="n"/>
+      <c r="S35" s="645" t="n"/>
+      <c r="T35" s="645" t="n"/>
+      <c r="U35" s="645" t="n"/>
+      <c r="V35" s="645" t="n"/>
+      <c r="W35" s="645" t="n"/>
+      <c r="X35" s="645" t="n"/>
+      <c r="Y35" s="645" t="n"/>
+      <c r="Z35" s="645" t="n"/>
+      <c r="AA35" s="645" t="n"/>
+      <c r="AB35" s="645" t="n"/>
+      <c r="AC35" s="645" t="n"/>
+      <c r="AD35" s="645" t="n"/>
+      <c r="AE35" s="645" t="n"/>
+      <c r="AF35" s="645" t="n"/>
+      <c r="AG35" s="645" t="n"/>
+      <c r="AH35" s="645" t="n"/>
+      <c r="AI35" s="645" t="n"/>
+      <c r="AJ35" s="645" t="n"/>
+      <c r="AK35" s="645" t="n"/>
+      <c r="AL35" s="645" t="n"/>
+      <c r="AM35" s="645" t="n"/>
+      <c r="AN35" s="645" t="n"/>
+      <c r="AO35" s="645" t="n"/>
+      <c r="AP35" s="645" t="n"/>
+      <c r="AQ35" s="645" t="n"/>
+      <c r="AR35" s="645" t="n"/>
+      <c r="AS35" s="645" t="n"/>
+      <c r="AT35" s="645" t="n"/>
+      <c r="AU35" s="645" t="n"/>
+      <c r="AV35" s="645" t="n"/>
+      <c r="AW35" s="645" t="n"/>
+      <c r="AX35" s="645" t="n"/>
+      <c r="AY35" s="645" t="n"/>
+      <c r="AZ35" s="645" t="n"/>
+      <c r="BA35" s="645" t="n"/>
+      <c r="BB35" s="645" t="n"/>
+      <c r="BC35" s="645" t="n"/>
+      <c r="BD35" s="646" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -115,6 +115,9 @@
     <t>Cleanliness / Packaging Verified (YES/NO)</t>
   </si>
   <si>
+    <t>Cleanliness Verified?</t>
+  </si>
+  <si>
     <t>Close When</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>Closeout Status</t>
   </si>
   <si>
+    <t>CoC Number</t>
+  </si>
+  <si>
     <t>Cross-Reference Boundary</t>
   </si>
   <si>
@@ -148,9 +154,6 @@
     <t>Evaluation</t>
   </si>
   <si>
-    <t>Evidence Package Ref</t>
-  </si>
-  <si>
     <t>Evidence Ref</t>
   </si>
   <si>
@@ -311,9 +314,6 @@
   </si>
   <si>
     <t>RESULT</t>
-  </si>
-  <si>
-    <t>Record Status</t>
   </si>
   <si>
     <t>Ref.</t>
@@ -1180,7 +1180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="374">
+  <borders count="379">
     <border>
       <left/>
       <right/>
@@ -5222,11 +5222,69 @@
         <color rgb="00F9A825"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="647">
+  <cellXfs count="652">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6876,6 +6934,17 @@
     <xf numFmtId="0" fontId="85" fillId="52" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8026,9 +8095,9 @@
       <c r="Z11" s="324" t="n"/>
       <c r="AA11" s="324" t="n"/>
       <c r="AB11" s="325" t="n"/>
-      <c r="AC11" s="620" t="inlineStr">
-        <is>
-          <t>Evidence Package Ref</t>
+      <c r="AC11" s="647" t="inlineStr">
+        <is>
+          <t>CoC Number</t>
         </is>
       </c>
       <c r="AD11" s="276" t="n"/>
@@ -8092,9 +8161,9 @@
       <c r="Z12" s="335" t="n"/>
       <c r="AA12" s="335" t="n"/>
       <c r="AB12" s="624" t="n"/>
-      <c r="AC12" s="625" t="inlineStr">
-        <is>
-          <t>Record Status</t>
+      <c r="AC12" s="648" t="inlineStr">
+        <is>
+          <t>Cleanliness Verified?</t>
         </is>
       </c>
       <c r="AD12" s="281" t="n"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -22,414 +22,10 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
-  <si>
-    <t>  1. LOT / PLAN / REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
-  </si>
-  <si>
-    <t>  4. DISPOSITION / RELEASE</t>
-  </si>
-  <si>
-    <t>  5. APPROVAL / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$16)+1</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$5)+1</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-001</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-002</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-003</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-004</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-006</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QA-007</t>
-  </si>
-  <si>
-    <t>ANNEX ANNEX-QMS-020</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
-  </si>
-  <si>
-    <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CLOSEOUT_STATE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>Characteristic / Requirement</t>
-  </si>
-  <si>
-    <t>Check Group</t>
-  </si>
-  <si>
-    <t>Cleanliness / Packaging Verified (YES/NO)</t>
-  </si>
-  <si>
-    <t>Cleanliness Verified?</t>
-  </si>
-  <si>
-    <t>Close When</t>
-  </si>
-  <si>
-    <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
-  </si>
-  <si>
-    <t>Closeout Status</t>
-  </si>
-  <si>
-    <t>CoC Number</t>
-  </si>
-  <si>
-    <t>Cross-Reference Boundary</t>
-  </si>
-  <si>
-    <t>DISPOSITION_GATE</t>
-  </si>
-  <si>
-    <t>Disposition / Release Decision</t>
-  </si>
-  <si>
-    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Epicor transaction + M365 evidence</t>
-  </si>
-  <si>
-    <t>Evaluation</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Evidence Reference / Attachment Guidance</t>
-  </si>
-  <si>
-    <t>Evidence item 1</t>
-  </si>
-  <si>
-    <t>Evidence item 2</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FRM-641</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Final Inspection Report</t>
-  </si>
-  <si>
-    <t>Final Inspection Report ID</t>
-  </si>
-  <si>
-    <t>Final Release Status</t>
-  </si>
-  <si>
-    <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>General Manager</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Inspection Basis</t>
-  </si>
-  <si>
-    <t>Inspector</t>
-  </si>
-  <si>
-    <t>Job / Shipment</t>
-  </si>
-  <si>
-    <t>Label / Doc Verified (YES/NO)</t>
-  </si>
-  <si>
-    <t>Link or reference ID</t>
-  </si>
-  <si>
-    <t>Linked NCR / Concession</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Method / Inspection Basis</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NOT CLOSED</t>
-  </si>
-  <si>
-    <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OWNER_DEPT</t>
-  </si>
-  <si>
-    <t>Open When</t>
-  </si>
-  <si>
-    <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
-  </si>
-  <si>
-    <t>Operational trigger</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Part No. / Revision</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Prepared by / Date-Time</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>Quality Authority</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Reference plan / lot / method / release documents from their owning source.</t>
-  </si>
-  <si>
-    <t>Reference to the correct evidence folder, shared location or dossier package.</t>
-  </si>
-  <si>
-    <t>Release / closure rule</t>
-  </si>
-  <si>
-    <t>Requirement / Characteristic</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Result Detail</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SOP SOP-605</t>
-  </si>
-  <si>
-    <t>SOP-605 — Kiểm tra cuối, CoC và phê duyệt giao hàng | HESEM QMS</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
-  </si>
-  <si>
-    <t>This form does not replace SOP-605; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-605; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-  </si>
-  <si>
-    <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
-  </si>
-  <si>
-    <t>Upstream References / Import Guidance</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>Value / Reference</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>WI WI-605</t>
-  </si>
-  <si>
-    <t>WI-605 — Kiểm cuối, CoC/CofC, bàn giao phát hành giao hàng</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-605-final-inspection-coc-and-shipment-release.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-605-final-inspection-coc-and-shipment-release-handoff.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -916,6 +512,9 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="53">
     <fill>
@@ -1180,7 +779,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="379">
+  <borders count="387">
     <border>
       <left/>
       <right/>
@@ -5280,11 +4879,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="652">
+  <cellXfs count="750">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6945,6 +6635,250 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="48" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="47" borderId="271" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="271" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="382" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="383" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="384" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="383" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="384" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="383" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="385" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="359" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="383" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="386" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7026,11 +6960,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7044,9 +6978,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7063,7 +6994,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7077,9 +7008,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7096,7 +7024,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7110,9 +7038,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7129,7 +7054,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7143,9 +7068,36 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -7519,7 +7471,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="600" t="inlineStr"/>
       <c r="B1" s="268" t="n"/>
       <c r="C1" s="268" t="n"/>
@@ -7531,7 +7483,7 @@
       <c r="I1" s="268" t="n"/>
       <c r="J1" s="268" t="n"/>
       <c r="K1" s="601" t="n"/>
-      <c r="L1" s="539" t="inlineStr">
+      <c r="L1" s="749" t="inlineStr">
         <is>
           <t>Final Inspection Report</t>
         </is>
@@ -7565,7 +7517,7 @@
       <c r="AM1" s="268" t="n"/>
       <c r="AN1" s="268" t="n"/>
       <c r="AO1" s="268" t="n"/>
-      <c r="AP1" s="268" t="n"/>
+      <c r="AP1" s="601" t="n"/>
       <c r="AQ1" s="602" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -7590,279 +7542,392 @@
       <c r="BD1" s="601" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="K2" s="605" t="n"/>
-      <c r="L2" s="275" t="n"/>
-      <c r="AQ2" s="606" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="684" t="n"/>
+      <c r="C2" s="684" t="n"/>
+      <c r="D2" s="684" t="n"/>
+      <c r="E2" s="684" t="n"/>
+      <c r="F2" s="684" t="n"/>
+      <c r="G2" s="684" t="n"/>
+      <c r="H2" s="684" t="n"/>
+      <c r="I2" s="684" t="n"/>
+      <c r="J2" s="684" t="n"/>
+      <c r="K2" s="685" t="n"/>
+      <c r="L2" s="684" t="n"/>
+      <c r="M2" s="684" t="n"/>
+      <c r="N2" s="684" t="n"/>
+      <c r="O2" s="684" t="n"/>
+      <c r="P2" s="684" t="n"/>
+      <c r="Q2" s="684" t="n"/>
+      <c r="R2" s="684" t="n"/>
+      <c r="S2" s="684" t="n"/>
+      <c r="T2" s="684" t="n"/>
+      <c r="U2" s="684" t="n"/>
+      <c r="V2" s="684" t="n"/>
+      <c r="W2" s="684" t="n"/>
+      <c r="X2" s="684" t="n"/>
+      <c r="Y2" s="684" t="n"/>
+      <c r="Z2" s="684" t="n"/>
+      <c r="AA2" s="684" t="n"/>
+      <c r="AB2" s="684" t="n"/>
+      <c r="AC2" s="684" t="n"/>
+      <c r="AD2" s="684" t="n"/>
+      <c r="AE2" s="684" t="n"/>
+      <c r="AF2" s="684" t="n"/>
+      <c r="AG2" s="684" t="n"/>
+      <c r="AH2" s="684" t="n"/>
+      <c r="AI2" s="684" t="n"/>
+      <c r="AJ2" s="684" t="n"/>
+      <c r="AK2" s="684" t="n"/>
+      <c r="AL2" s="684" t="n"/>
+      <c r="AM2" s="684" t="n"/>
+      <c r="AN2" s="684" t="n"/>
+      <c r="AO2" s="684" t="n"/>
+      <c r="AP2" s="685" t="n"/>
+      <c r="AQ2" s="686" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="607" t="n"/>
-      <c r="AS2" s="607" t="n"/>
-      <c r="AT2" s="607" t="n"/>
-      <c r="AU2" s="607" t="n"/>
-      <c r="AV2" s="608" t="n"/>
-      <c r="AW2" s="609" t="inlineStr">
+      <c r="AR2" s="687" t="n"/>
+      <c r="AS2" s="687" t="n"/>
+      <c r="AT2" s="687" t="n"/>
+      <c r="AU2" s="687" t="n"/>
+      <c r="AV2" s="688" t="n"/>
+      <c r="AW2" s="7" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="607" t="n"/>
-      <c r="AY2" s="607" t="n"/>
-      <c r="AZ2" s="607" t="n"/>
-      <c r="BA2" s="607" t="n"/>
-      <c r="BB2" s="607" t="n"/>
-      <c r="BC2" s="607" t="n"/>
-      <c r="BD2" s="610" t="n"/>
+      <c r="AX2" s="689" t="n"/>
+      <c r="AY2" s="689" t="n"/>
+      <c r="AZ2" s="689" t="n"/>
+      <c r="BA2" s="689" t="n"/>
+      <c r="BB2" s="689" t="n"/>
+      <c r="BC2" s="689" t="n"/>
+      <c r="BD2" s="690" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="K3" s="605" t="n"/>
-      <c r="L3" s="275" t="n"/>
-      <c r="AQ3" s="606" t="inlineStr">
+      <c r="A3" s="691" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="692" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="25" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="25" t="n"/>
+      <c r="AH3" s="25" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="25" t="n"/>
+      <c r="AL3" s="25" t="n"/>
+      <c r="AM3" s="25" t="n"/>
+      <c r="AN3" s="25" t="n"/>
+      <c r="AO3" s="25" t="n"/>
+      <c r="AP3" s="692" t="n"/>
+      <c r="AQ3" s="693" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="607" t="n"/>
-      <c r="AS3" s="607" t="n"/>
-      <c r="AT3" s="607" t="n"/>
-      <c r="AU3" s="607" t="n"/>
-      <c r="AV3" s="608" t="n"/>
-      <c r="AW3" s="609" t="inlineStr">
+      <c r="AR3" s="694" t="n"/>
+      <c r="AS3" s="694" t="n"/>
+      <c r="AT3" s="694" t="n"/>
+      <c r="AU3" s="694" t="n"/>
+      <c r="AV3" s="695" t="n"/>
+      <c r="AW3" s="14" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="607" t="n"/>
-      <c r="AY3" s="607" t="n"/>
-      <c r="AZ3" s="607" t="n"/>
-      <c r="BA3" s="607" t="n"/>
-      <c r="BB3" s="607" t="n"/>
-      <c r="BC3" s="607" t="n"/>
-      <c r="BD3" s="610" t="n"/>
+      <c r="AX3" s="696" t="n"/>
+      <c r="AY3" s="696" t="n"/>
+      <c r="AZ3" s="696" t="n"/>
+      <c r="BA3" s="696" t="n"/>
+      <c r="BB3" s="696" t="n"/>
+      <c r="BC3" s="696" t="n"/>
+      <c r="BD3" s="697" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="K4" s="605" t="n"/>
-      <c r="L4" s="548" t="inlineStr">
+      <c r="A4" s="691" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="692" t="n"/>
+      <c r="L4" s="698" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="606" t="inlineStr">
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="25" t="n"/>
+      <c r="AE4" s="25" t="n"/>
+      <c r="AF4" s="25" t="n"/>
+      <c r="AG4" s="25" t="n"/>
+      <c r="AH4" s="25" t="n"/>
+      <c r="AI4" s="25" t="n"/>
+      <c r="AJ4" s="25" t="n"/>
+      <c r="AK4" s="25" t="n"/>
+      <c r="AL4" s="25" t="n"/>
+      <c r="AM4" s="25" t="n"/>
+      <c r="AN4" s="25" t="n"/>
+      <c r="AO4" s="25" t="n"/>
+      <c r="AP4" s="692" t="n"/>
+      <c r="AQ4" s="693" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="607" t="n"/>
-      <c r="AS4" s="607" t="n"/>
-      <c r="AT4" s="607" t="n"/>
-      <c r="AU4" s="607" t="n"/>
-      <c r="AV4" s="608" t="n"/>
-      <c r="AW4" s="609" t="inlineStr">
+      <c r="AR4" s="694" t="n"/>
+      <c r="AS4" s="694" t="n"/>
+      <c r="AT4" s="694" t="n"/>
+      <c r="AU4" s="694" t="n"/>
+      <c r="AV4" s="695" t="n"/>
+      <c r="AW4" s="14" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="AX4" s="607" t="n"/>
-      <c r="AY4" s="607" t="n"/>
-      <c r="AZ4" s="607" t="n"/>
-      <c r="BA4" s="607" t="n"/>
-      <c r="BB4" s="607" t="n"/>
-      <c r="BC4" s="607" t="n"/>
-      <c r="BD4" s="610" t="n"/>
+      <c r="AX4" s="696" t="n"/>
+      <c r="AY4" s="696" t="n"/>
+      <c r="AZ4" s="696" t="n"/>
+      <c r="BA4" s="696" t="n"/>
+      <c r="BB4" s="696" t="n"/>
+      <c r="BC4" s="696" t="n"/>
+      <c r="BD4" s="697" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="280" t="n"/>
-      <c r="B5" s="281" t="n"/>
-      <c r="C5" s="281" t="n"/>
-      <c r="D5" s="281" t="n"/>
-      <c r="E5" s="281" t="n"/>
-      <c r="F5" s="281" t="n"/>
-      <c r="G5" s="281" t="n"/>
-      <c r="H5" s="281" t="n"/>
-      <c r="I5" s="281" t="n"/>
-      <c r="J5" s="281" t="n"/>
-      <c r="K5" s="283" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="A5" s="691" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="692" t="n"/>
+      <c r="L5" s="699" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="281" t="n"/>
-      <c r="N5" s="281" t="n"/>
-      <c r="O5" s="281" t="n"/>
-      <c r="P5" s="281" t="n"/>
-      <c r="Q5" s="281" t="n"/>
-      <c r="R5" s="281" t="n"/>
-      <c r="S5" s="281" t="n"/>
-      <c r="T5" s="281" t="n"/>
-      <c r="U5" s="281" t="n"/>
-      <c r="V5" s="281" t="n"/>
-      <c r="W5" s="281" t="n"/>
-      <c r="X5" s="281" t="n"/>
-      <c r="Y5" s="281" t="n"/>
-      <c r="Z5" s="281" t="n"/>
-      <c r="AA5" s="281" t="n"/>
-      <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="n"/>
-      <c r="AD5" s="281" t="n"/>
-      <c r="AE5" s="281" t="n"/>
-      <c r="AF5" s="281" t="n"/>
-      <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
-      <c r="AI5" s="281" t="n"/>
-      <c r="AJ5" s="281" t="n"/>
-      <c r="AK5" s="281" t="n"/>
-      <c r="AL5" s="281" t="n"/>
-      <c r="AM5" s="281" t="n"/>
-      <c r="AN5" s="281" t="n"/>
-      <c r="AO5" s="281" t="n"/>
-      <c r="AP5" s="281" t="n"/>
-      <c r="AQ5" s="611" t="inlineStr">
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="25" t="n"/>
+      <c r="AE5" s="25" t="n"/>
+      <c r="AF5" s="25" t="n"/>
+      <c r="AG5" s="25" t="n"/>
+      <c r="AH5" s="25" t="n"/>
+      <c r="AI5" s="25" t="n"/>
+      <c r="AJ5" s="25" t="n"/>
+      <c r="AK5" s="25" t="n"/>
+      <c r="AL5" s="25" t="n"/>
+      <c r="AM5" s="25" t="n"/>
+      <c r="AN5" s="25" t="n"/>
+      <c r="AO5" s="25" t="n"/>
+      <c r="AP5" s="692" t="n"/>
+      <c r="AQ5" s="693" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="612" t="n"/>
-      <c r="AS5" s="612" t="n"/>
-      <c r="AT5" s="612" t="n"/>
-      <c r="AU5" s="612" t="n"/>
-      <c r="AV5" s="613" t="n"/>
-      <c r="AW5" s="614" t="inlineStr">
+      <c r="AR5" s="694" t="n"/>
+      <c r="AS5" s="694" t="n"/>
+      <c r="AT5" s="694" t="n"/>
+      <c r="AU5" s="694" t="n"/>
+      <c r="AV5" s="695" t="n"/>
+      <c r="AW5" s="14" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="612" t="n"/>
-      <c r="AY5" s="612" t="n"/>
-      <c r="AZ5" s="612" t="n"/>
-      <c r="BA5" s="612" t="n"/>
-      <c r="BB5" s="612" t="n"/>
-      <c r="BC5" s="612" t="n"/>
-      <c r="BD5" s="615" t="n"/>
+      <c r="AX5" s="696" t="n"/>
+      <c r="AY5" s="696" t="n"/>
+      <c r="AZ5" s="696" t="n"/>
+      <c r="BA5" s="696" t="n"/>
+      <c r="BB5" s="696" t="n"/>
+      <c r="BC5" s="696" t="n"/>
+      <c r="BD5" s="697" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="515" t="n"/>
-      <c r="B6" s="515" t="n"/>
-      <c r="C6" s="515" t="n"/>
-      <c r="D6" s="515" t="n"/>
-      <c r="E6" s="515" t="n"/>
-      <c r="F6" s="515" t="n"/>
-      <c r="G6" s="515" t="n"/>
-      <c r="H6" s="515" t="n"/>
-      <c r="I6" s="515" t="n"/>
-      <c r="J6" s="515" t="n"/>
-      <c r="K6" s="515" t="n"/>
-      <c r="L6" s="515" t="n"/>
-      <c r="M6" s="515" t="n"/>
-      <c r="N6" s="515" t="n"/>
-      <c r="O6" s="515" t="n"/>
-      <c r="P6" s="515" t="n"/>
-      <c r="Q6" s="515" t="n"/>
-      <c r="R6" s="515" t="n"/>
-      <c r="S6" s="515" t="n"/>
-      <c r="T6" s="515" t="n"/>
-      <c r="U6" s="515" t="n"/>
-      <c r="V6" s="515" t="n"/>
-      <c r="W6" s="515" t="n"/>
-      <c r="X6" s="515" t="n"/>
-      <c r="Y6" s="515" t="n"/>
-      <c r="Z6" s="515" t="n"/>
-      <c r="AA6" s="515" t="n"/>
-      <c r="AB6" s="515" t="n"/>
-      <c r="AC6" s="515" t="n"/>
-      <c r="AD6" s="515" t="n"/>
-      <c r="AE6" s="515" t="n"/>
-      <c r="AF6" s="515" t="n"/>
-      <c r="AG6" s="515" t="n"/>
-      <c r="AH6" s="515" t="n"/>
-      <c r="AI6" s="515" t="n"/>
-      <c r="AJ6" s="515" t="n"/>
-      <c r="AK6" s="515" t="n"/>
-      <c r="AL6" s="515" t="n"/>
-      <c r="AM6" s="515" t="n"/>
-      <c r="AN6" s="515" t="n"/>
-      <c r="AO6" s="515" t="n"/>
-      <c r="AP6" s="515" t="n"/>
-      <c r="AQ6" s="515" t="n"/>
-      <c r="AR6" s="515" t="n"/>
-      <c r="AS6" s="515" t="n"/>
-      <c r="AT6" s="515" t="n"/>
-      <c r="AU6" s="515" t="n"/>
-      <c r="AV6" s="515" t="n"/>
-      <c r="AW6" s="515" t="n"/>
-      <c r="AX6" s="515" t="n"/>
-      <c r="AY6" s="515" t="n"/>
-      <c r="AZ6" s="515" t="n"/>
-      <c r="BA6" s="515" t="n"/>
-      <c r="BB6" s="515" t="n"/>
-      <c r="BC6" s="515" t="n"/>
-      <c r="BD6" s="515" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="700" t="n"/>
+      <c r="B6" s="701" t="n"/>
+      <c r="C6" s="701" t="n"/>
+      <c r="D6" s="701" t="n"/>
+      <c r="E6" s="701" t="n"/>
+      <c r="F6" s="701" t="n"/>
+      <c r="G6" s="701" t="n"/>
+      <c r="H6" s="701" t="n"/>
+      <c r="I6" s="701" t="n"/>
+      <c r="J6" s="701" t="n"/>
+      <c r="K6" s="702" t="n"/>
+      <c r="L6" s="701" t="n"/>
+      <c r="M6" s="701" t="n"/>
+      <c r="N6" s="701" t="n"/>
+      <c r="O6" s="701" t="n"/>
+      <c r="P6" s="701" t="n"/>
+      <c r="Q6" s="701" t="n"/>
+      <c r="R6" s="701" t="n"/>
+      <c r="S6" s="701" t="n"/>
+      <c r="T6" s="701" t="n"/>
+      <c r="U6" s="701" t="n"/>
+      <c r="V6" s="701" t="n"/>
+      <c r="W6" s="701" t="n"/>
+      <c r="X6" s="701" t="n"/>
+      <c r="Y6" s="701" t="n"/>
+      <c r="Z6" s="701" t="n"/>
+      <c r="AA6" s="701" t="n"/>
+      <c r="AB6" s="701" t="n"/>
+      <c r="AC6" s="701" t="n"/>
+      <c r="AD6" s="701" t="n"/>
+      <c r="AE6" s="701" t="n"/>
+      <c r="AF6" s="701" t="n"/>
+      <c r="AG6" s="701" t="n"/>
+      <c r="AH6" s="701" t="n"/>
+      <c r="AI6" s="701" t="n"/>
+      <c r="AJ6" s="701" t="n"/>
+      <c r="AK6" s="701" t="n"/>
+      <c r="AL6" s="701" t="n"/>
+      <c r="AM6" s="701" t="n"/>
+      <c r="AN6" s="701" t="n"/>
+      <c r="AO6" s="701" t="n"/>
+      <c r="AP6" s="702" t="n"/>
+      <c r="AQ6" s="703" t="n"/>
+      <c r="AR6" s="703" t="n"/>
+      <c r="AS6" s="703" t="n"/>
+      <c r="AT6" s="703" t="n"/>
+      <c r="AU6" s="703" t="n"/>
+      <c r="AV6" s="704" t="n"/>
+      <c r="AW6" s="705" t="n"/>
+      <c r="AX6" s="705" t="n"/>
+      <c r="AY6" s="705" t="n"/>
+      <c r="AZ6" s="705" t="n"/>
+      <c r="BA6" s="705" t="n"/>
+      <c r="BB6" s="705" t="n"/>
+      <c r="BC6" s="705" t="n"/>
+      <c r="BD6" s="706" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="616" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. LOT / PLAN / REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="285" t="n"/>
-      <c r="AO7" s="285" t="n"/>
-      <c r="AP7" s="285" t="n"/>
-      <c r="AQ7" s="285" t="n"/>
-      <c r="AR7" s="285" t="n"/>
-      <c r="AS7" s="285" t="n"/>
-      <c r="AT7" s="285" t="n"/>
-      <c r="AU7" s="285" t="n"/>
-      <c r="AV7" s="285" t="n"/>
-      <c r="AW7" s="285" t="n"/>
-      <c r="AX7" s="285" t="n"/>
-      <c r="AY7" s="285" t="n"/>
-      <c r="AZ7" s="285" t="n"/>
-      <c r="BA7" s="285" t="n"/>
-      <c r="BB7" s="285" t="n"/>
-      <c r="BC7" s="285" t="n"/>
-      <c r="BD7" s="286" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="707" t="n"/>
+      <c r="B7" s="708" t="n"/>
+      <c r="C7" s="708" t="n"/>
+      <c r="D7" s="708" t="n"/>
+      <c r="E7" s="708" t="n"/>
+      <c r="F7" s="708" t="n"/>
+      <c r="G7" s="708" t="n"/>
+      <c r="H7" s="708" t="n"/>
+      <c r="I7" s="708" t="n"/>
+      <c r="J7" s="708" t="n"/>
+      <c r="K7" s="708" t="n"/>
+      <c r="L7" s="708" t="n"/>
+      <c r="M7" s="708" t="n"/>
+      <c r="N7" s="708" t="n"/>
+      <c r="O7" s="708" t="n"/>
+      <c r="P7" s="708" t="n"/>
+      <c r="Q7" s="708" t="n"/>
+      <c r="R7" s="708" t="n"/>
+      <c r="S7" s="708" t="n"/>
+      <c r="T7" s="708" t="n"/>
+      <c r="U7" s="708" t="n"/>
+      <c r="V7" s="708" t="n"/>
+      <c r="W7" s="708" t="n"/>
+      <c r="X7" s="708" t="n"/>
+      <c r="Y7" s="708" t="n"/>
+      <c r="Z7" s="708" t="n"/>
+      <c r="AA7" s="708" t="n"/>
+      <c r="AB7" s="708" t="n"/>
+      <c r="AC7" s="708" t="n"/>
+      <c r="AD7" s="708" t="n"/>
+      <c r="AE7" s="708" t="n"/>
+      <c r="AF7" s="708" t="n"/>
+      <c r="AG7" s="708" t="n"/>
+      <c r="AH7" s="708" t="n"/>
+      <c r="AI7" s="708" t="n"/>
+      <c r="AJ7" s="708" t="n"/>
+      <c r="AK7" s="708" t="n"/>
+      <c r="AL7" s="708" t="n"/>
+      <c r="AM7" s="708" t="n"/>
+      <c r="AN7" s="708" t="n"/>
+      <c r="AO7" s="708" t="n"/>
+      <c r="AP7" s="708" t="n"/>
+      <c r="AQ7" s="708" t="n"/>
+      <c r="AR7" s="708" t="n"/>
+      <c r="AS7" s="708" t="n"/>
+      <c r="AT7" s="708" t="n"/>
+      <c r="AU7" s="708" t="n"/>
+      <c r="AV7" s="708" t="n"/>
+      <c r="AW7" s="708" t="n"/>
+      <c r="AX7" s="708" t="n"/>
+      <c r="AY7" s="708" t="n"/>
+      <c r="AZ7" s="708" t="n"/>
+      <c r="BA7" s="708" t="n"/>
+      <c r="BB7" s="708" t="n"/>
+      <c r="BC7" s="708" t="n"/>
+      <c r="BD7" s="708" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="617" t="inlineStr">
@@ -8095,7 +8160,7 @@
       <c r="Z11" s="324" t="n"/>
       <c r="AA11" s="324" t="n"/>
       <c r="AB11" s="325" t="n"/>
-      <c r="AC11" s="647" t="inlineStr">
+      <c r="AC11" s="620" t="inlineStr">
         <is>
           <t>CoC Number</t>
         </is>
@@ -8161,7 +8226,7 @@
       <c r="Z12" s="335" t="n"/>
       <c r="AA12" s="335" t="n"/>
       <c r="AB12" s="624" t="n"/>
-      <c r="AC12" s="648" t="inlineStr">
+      <c r="AC12" s="625" t="inlineStr">
         <is>
           <t>Cleanliness Verified?</t>
         </is>
@@ -9607,67 +9672,67 @@
       <c r="BC34" s="573" t="n"/>
       <c r="BD34" s="573" t="n"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="644" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
         </is>
       </c>
-      <c r="B35" s="645" t="n"/>
-      <c r="C35" s="645" t="n"/>
-      <c r="D35" s="645" t="n"/>
-      <c r="E35" s="645" t="n"/>
-      <c r="F35" s="645" t="n"/>
-      <c r="G35" s="645" t="n"/>
-      <c r="H35" s="645" t="n"/>
-      <c r="I35" s="645" t="n"/>
-      <c r="J35" s="645" t="n"/>
-      <c r="K35" s="645" t="n"/>
-      <c r="L35" s="645" t="n"/>
-      <c r="M35" s="645" t="n"/>
-      <c r="N35" s="645" t="n"/>
-      <c r="O35" s="645" t="n"/>
-      <c r="P35" s="645" t="n"/>
-      <c r="Q35" s="645" t="n"/>
-      <c r="R35" s="645" t="n"/>
-      <c r="S35" s="645" t="n"/>
-      <c r="T35" s="645" t="n"/>
-      <c r="U35" s="645" t="n"/>
-      <c r="V35" s="645" t="n"/>
-      <c r="W35" s="645" t="n"/>
-      <c r="X35" s="645" t="n"/>
-      <c r="Y35" s="645" t="n"/>
-      <c r="Z35" s="645" t="n"/>
-      <c r="AA35" s="645" t="n"/>
-      <c r="AB35" s="645" t="n"/>
-      <c r="AC35" s="645" t="n"/>
-      <c r="AD35" s="645" t="n"/>
-      <c r="AE35" s="645" t="n"/>
-      <c r="AF35" s="645" t="n"/>
-      <c r="AG35" s="645" t="n"/>
-      <c r="AH35" s="645" t="n"/>
-      <c r="AI35" s="645" t="n"/>
-      <c r="AJ35" s="645" t="n"/>
-      <c r="AK35" s="645" t="n"/>
-      <c r="AL35" s="645" t="n"/>
-      <c r="AM35" s="645" t="n"/>
-      <c r="AN35" s="645" t="n"/>
-      <c r="AO35" s="645" t="n"/>
-      <c r="AP35" s="645" t="n"/>
-      <c r="AQ35" s="645" t="n"/>
-      <c r="AR35" s="645" t="n"/>
-      <c r="AS35" s="645" t="n"/>
-      <c r="AT35" s="645" t="n"/>
-      <c r="AU35" s="645" t="n"/>
-      <c r="AV35" s="645" t="n"/>
-      <c r="AW35" s="645" t="n"/>
-      <c r="AX35" s="645" t="n"/>
-      <c r="AY35" s="645" t="n"/>
-      <c r="AZ35" s="645" t="n"/>
-      <c r="BA35" s="645" t="n"/>
-      <c r="BB35" s="645" t="n"/>
-      <c r="BC35" s="645" t="n"/>
-      <c r="BD35" s="646" t="n"/>
+      <c r="B35" s="709" t="n"/>
+      <c r="C35" s="709" t="n"/>
+      <c r="D35" s="709" t="n"/>
+      <c r="E35" s="709" t="n"/>
+      <c r="F35" s="709" t="n"/>
+      <c r="G35" s="709" t="n"/>
+      <c r="H35" s="709" t="n"/>
+      <c r="I35" s="709" t="n"/>
+      <c r="J35" s="709" t="n"/>
+      <c r="K35" s="709" t="n"/>
+      <c r="L35" s="709" t="n"/>
+      <c r="M35" s="709" t="n"/>
+      <c r="N35" s="709" t="n"/>
+      <c r="O35" s="709" t="n"/>
+      <c r="P35" s="709" t="n"/>
+      <c r="Q35" s="709" t="n"/>
+      <c r="R35" s="709" t="n"/>
+      <c r="S35" s="709" t="n"/>
+      <c r="T35" s="709" t="n"/>
+      <c r="U35" s="709" t="n"/>
+      <c r="V35" s="709" t="n"/>
+      <c r="W35" s="709" t="n"/>
+      <c r="X35" s="709" t="n"/>
+      <c r="Y35" s="709" t="n"/>
+      <c r="Z35" s="709" t="n"/>
+      <c r="AA35" s="709" t="n"/>
+      <c r="AB35" s="709" t="n"/>
+      <c r="AC35" s="709" t="n"/>
+      <c r="AD35" s="709" t="n"/>
+      <c r="AE35" s="709" t="n"/>
+      <c r="AF35" s="709" t="n"/>
+      <c r="AG35" s="709" t="n"/>
+      <c r="AH35" s="709" t="n"/>
+      <c r="AI35" s="709" t="n"/>
+      <c r="AJ35" s="709" t="n"/>
+      <c r="AK35" s="709" t="n"/>
+      <c r="AL35" s="709" t="n"/>
+      <c r="AM35" s="709" t="n"/>
+      <c r="AN35" s="709" t="n"/>
+      <c r="AO35" s="709" t="n"/>
+      <c r="AP35" s="709" t="n"/>
+      <c r="AQ35" s="709" t="n"/>
+      <c r="AR35" s="709" t="n"/>
+      <c r="AS35" s="709" t="n"/>
+      <c r="AT35" s="709" t="n"/>
+      <c r="AU35" s="709" t="n"/>
+      <c r="AV35" s="709" t="n"/>
+      <c r="AW35" s="709" t="n"/>
+      <c r="AX35" s="709" t="n"/>
+      <c r="AY35" s="709" t="n"/>
+      <c r="AZ35" s="709" t="n"/>
+      <c r="BA35" s="709" t="n"/>
+      <c r="BB35" s="709" t="n"/>
+      <c r="BC35" s="709" t="n"/>
+      <c r="BD35" s="710" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -9841,232 +9906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="265" t="inlineStr">
-        <is>
-          <t>RESULT</t>
-        </is>
-      </c>
-      <c r="B1" s="265" t="inlineStr">
-        <is>
-          <t>DISPOSITION_GATE</t>
-        </is>
-      </c>
-      <c r="C1" s="265" t="inlineStr">
-        <is>
-          <t>OWNER_DEPT</t>
-        </is>
-      </c>
-      <c r="D1" s="265" t="inlineStr">
-        <is>
-          <t>CLOSEOUT_STATE</t>
-        </is>
-      </c>
-      <c r="E1" s="265" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="F1" s="265" t="inlineStr">
-        <is>
-          <t>YES_NO</t>
-        </is>
-      </c>
-      <c r="G1" s="265" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="266" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B2" s="266" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="C2" s="266" t="inlineStr">
-        <is>
-          <t>SALES</t>
-        </is>
-      </c>
-      <c r="D2" s="266" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="E2" s="266" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="F2" s="266" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G2" s="266" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="266" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B3" s="266" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="C3" s="266" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="D3" s="266" t="inlineStr">
-        <is>
-          <t>NOT CLOSED</t>
-        </is>
-      </c>
-      <c r="E3" s="266" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="F3" s="266" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G3" s="266" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="266" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B4" s="266" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C4" s="266" t="inlineStr">
-        <is>
-          <t>PLANNING</t>
-        </is>
-      </c>
-      <c r="D4" s="266" t="n"/>
-      <c r="E4" s="266" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="F4" s="266" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G4" s="266" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="266" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B5" s="266" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="C5" s="266" t="inlineStr">
-        <is>
-          <t>PROD</t>
-        </is>
-      </c>
-      <c r="D5" s="266" t="n"/>
-      <c r="E5" s="346" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="F5" s="266" t="n"/>
-      <c r="G5" s="266" t="n"/>
-    </row>
-    <row r="6">
-      <c r="C6" s="346" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="F6" s="266" t="n"/>
-      <c r="G6" s="266" t="n"/>
-    </row>
-    <row r="7">
-      <c r="C7" s="346" t="inlineStr">
-        <is>
-          <t>PUR</t>
-        </is>
-      </c>
-      <c r="F7" s="266" t="n"/>
-    </row>
-    <row r="8">
-      <c r="C8" s="346" t="inlineStr">
-        <is>
-          <t>WHS</t>
-        </is>
-      </c>
-      <c r="F8" s="266" t="n"/>
-    </row>
-    <row r="9">
-      <c r="C9" s="346" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F9" s="266" t="n"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="346" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="F10" s="266" t="n"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="346" t="inlineStr">
-        <is>
-          <t>MGT</t>
-        </is>
-      </c>
-      <c r="F11" s="266" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN19"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -10111,906 +9951,1036 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="510" t="inlineStr">
-        <is>
-          <t>Result Detail</t>
-        </is>
-      </c>
+    <row r="1" hidden="1">
+      <c r="A1" s="711" t="n"/>
       <c r="B1" s="599" t="n"/>
       <c r="C1" s="599" t="n"/>
       <c r="D1" s="599" t="n"/>
       <c r="E1" s="599" t="n"/>
       <c r="F1" s="599" t="n"/>
       <c r="G1" s="599" t="n"/>
-      <c r="H1" s="511" t="n"/>
-      <c r="I1" s="428" t="n"/>
-      <c r="J1" s="429" t="n"/>
-      <c r="K1" s="429" t="n"/>
-      <c r="L1" s="429" t="n"/>
-      <c r="M1" s="429" t="n"/>
-      <c r="N1" s="429" t="n"/>
-      <c r="O1" s="429" t="n"/>
-      <c r="P1" s="429" t="n"/>
-      <c r="Q1" s="429" t="n"/>
-      <c r="R1" s="429" t="n"/>
-      <c r="S1" s="429" t="n"/>
-      <c r="T1" s="429" t="n"/>
-      <c r="U1" s="429" t="n"/>
-      <c r="V1" s="429" t="n"/>
-      <c r="W1" s="429" t="n"/>
-      <c r="X1" s="429" t="n"/>
-      <c r="Y1" s="429" t="n"/>
-      <c r="Z1" s="429" t="n"/>
-      <c r="AA1" s="429" t="n"/>
-      <c r="AB1" s="429" t="n"/>
-      <c r="AC1" s="429" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="431" t="n"/>
-      <c r="AF1" s="432" t="n"/>
-      <c r="AG1" s="432" t="n"/>
-      <c r="AH1" s="433" t="n"/>
-      <c r="AI1" s="434" t="n"/>
-      <c r="AJ1" s="435" t="n"/>
-      <c r="AK1" s="435" t="n"/>
-      <c r="AL1" s="435" t="n"/>
-      <c r="AM1" s="435" t="n"/>
-      <c r="AN1" s="436" t="n"/>
+      <c r="H1" s="712" t="n"/>
+      <c r="I1" s="713" t="inlineStr">
+        <is>
+          <t>Final Inspection Report</t>
+        </is>
+      </c>
+      <c r="J1" s="599" t="n"/>
+      <c r="K1" s="599" t="n"/>
+      <c r="L1" s="599" t="n"/>
+      <c r="M1" s="599" t="n"/>
+      <c r="N1" s="599" t="n"/>
+      <c r="O1" s="599" t="n"/>
+      <c r="P1" s="599" t="n"/>
+      <c r="Q1" s="599" t="n"/>
+      <c r="R1" s="599" t="n"/>
+      <c r="S1" s="599" t="n"/>
+      <c r="T1" s="599" t="n"/>
+      <c r="U1" s="599" t="n"/>
+      <c r="V1" s="599" t="n"/>
+      <c r="W1" s="599" t="n"/>
+      <c r="X1" s="599" t="n"/>
+      <c r="Y1" s="599" t="n"/>
+      <c r="Z1" s="599" t="n"/>
+      <c r="AA1" s="599" t="n"/>
+      <c r="AB1" s="599" t="n"/>
+      <c r="AC1" s="599" t="n"/>
+      <c r="AD1" s="712" t="n"/>
+      <c r="AE1" s="433" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="599" t="n"/>
+      <c r="AG1" s="599" t="n"/>
+      <c r="AH1" s="714" t="n"/>
+      <c r="AI1" s="436" t="inlineStr">
+        <is>
+          <t>FRM-641</t>
+        </is>
+      </c>
+      <c r="AJ1" s="599" t="n"/>
+      <c r="AK1" s="599" t="n"/>
+      <c r="AL1" s="599" t="n"/>
+      <c r="AM1" s="599" t="n"/>
+      <c r="AN1" s="712" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="512" t="inlineStr">
-        <is>
-          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
-        </is>
-      </c>
-      <c r="H2" s="513" t="n"/>
-      <c r="I2" s="439" t="n"/>
-      <c r="J2" s="440" t="n"/>
-      <c r="K2" s="440" t="n"/>
-      <c r="L2" s="440" t="n"/>
-      <c r="M2" s="440" t="n"/>
-      <c r="N2" s="440" t="n"/>
-      <c r="O2" s="440" t="n"/>
-      <c r="P2" s="440" t="n"/>
-      <c r="Q2" s="440" t="n"/>
-      <c r="R2" s="440" t="n"/>
-      <c r="S2" s="440" t="n"/>
-      <c r="T2" s="440" t="n"/>
-      <c r="U2" s="440" t="n"/>
-      <c r="V2" s="440" t="n"/>
-      <c r="W2" s="440" t="n"/>
-      <c r="X2" s="440" t="n"/>
-      <c r="Y2" s="440" t="n"/>
-      <c r="Z2" s="440" t="n"/>
-      <c r="AA2" s="440" t="n"/>
-      <c r="AB2" s="440" t="n"/>
-      <c r="AC2" s="440" t="n"/>
-      <c r="AD2" s="441" t="n"/>
-      <c r="AE2" s="442" t="n"/>
-      <c r="AF2" s="443" t="n"/>
-      <c r="AG2" s="443" t="n"/>
-      <c r="AH2" s="444" t="n"/>
-      <c r="AI2" s="445" t="n"/>
-      <c r="AJ2" s="446" t="n"/>
-      <c r="AK2" s="446" t="n"/>
-      <c r="AL2" s="446" t="n"/>
-      <c r="AM2" s="446" t="n"/>
-      <c r="AN2" s="447" t="n"/>
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="684" t="n"/>
+      <c r="C2" s="684" t="n"/>
+      <c r="D2" s="684" t="n"/>
+      <c r="E2" s="684" t="n"/>
+      <c r="F2" s="684" t="n"/>
+      <c r="G2" s="684" t="n"/>
+      <c r="H2" s="685" t="n"/>
+      <c r="I2" s="684" t="n"/>
+      <c r="J2" s="684" t="n"/>
+      <c r="K2" s="684" t="n"/>
+      <c r="L2" s="684" t="n"/>
+      <c r="M2" s="684" t="n"/>
+      <c r="N2" s="684" t="n"/>
+      <c r="O2" s="684" t="n"/>
+      <c r="P2" s="684" t="n"/>
+      <c r="Q2" s="684" t="n"/>
+      <c r="R2" s="684" t="n"/>
+      <c r="S2" s="684" t="n"/>
+      <c r="T2" s="684" t="n"/>
+      <c r="U2" s="684" t="n"/>
+      <c r="V2" s="684" t="n"/>
+      <c r="W2" s="684" t="n"/>
+      <c r="X2" s="684" t="n"/>
+      <c r="Y2" s="684" t="n"/>
+      <c r="Z2" s="684" t="n"/>
+      <c r="AA2" s="684" t="n"/>
+      <c r="AB2" s="684" t="n"/>
+      <c r="AC2" s="684" t="n"/>
+      <c r="AD2" s="685" t="n"/>
+      <c r="AE2" s="686" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="687" t="n"/>
+      <c r="AG2" s="687" t="n"/>
+      <c r="AH2" s="688" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="689" t="n"/>
+      <c r="AK2" s="689" t="n"/>
+      <c r="AL2" s="689" t="n"/>
+      <c r="AM2" s="689" t="n"/>
+      <c r="AN2" s="690" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="514" t="n"/>
-      <c r="B3" s="515" t="n"/>
-      <c r="C3" s="515" t="n"/>
-      <c r="D3" s="515" t="n"/>
-      <c r="E3" s="515" t="n"/>
-      <c r="F3" s="515" t="n"/>
-      <c r="G3" s="515" t="n"/>
-      <c r="H3" s="513" t="n"/>
-      <c r="I3" s="439" t="n"/>
-      <c r="J3" s="440" t="n"/>
-      <c r="K3" s="440" t="n"/>
-      <c r="L3" s="440" t="n"/>
-      <c r="M3" s="440" t="n"/>
-      <c r="N3" s="440" t="n"/>
-      <c r="O3" s="440" t="n"/>
-      <c r="P3" s="440" t="n"/>
-      <c r="Q3" s="440" t="n"/>
-      <c r="R3" s="440" t="n"/>
-      <c r="S3" s="440" t="n"/>
-      <c r="T3" s="440" t="n"/>
-      <c r="U3" s="440" t="n"/>
-      <c r="V3" s="440" t="n"/>
-      <c r="W3" s="440" t="n"/>
-      <c r="X3" s="440" t="n"/>
-      <c r="Y3" s="440" t="n"/>
-      <c r="Z3" s="440" t="n"/>
-      <c r="AA3" s="440" t="n"/>
-      <c r="AB3" s="440" t="n"/>
-      <c r="AC3" s="440" t="n"/>
-      <c r="AD3" s="441" t="n"/>
-      <c r="AE3" s="442" t="n"/>
-      <c r="AF3" s="443" t="n"/>
-      <c r="AG3" s="443" t="n"/>
-      <c r="AH3" s="444" t="n"/>
-      <c r="AI3" s="445" t="n"/>
-      <c r="AJ3" s="446" t="n"/>
-      <c r="AK3" s="446" t="n"/>
-      <c r="AL3" s="446" t="n"/>
-      <c r="AM3" s="446" t="n"/>
-      <c r="AN3" s="447" t="n"/>
+      <c r="A3" s="691" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="692" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="692" t="n"/>
+      <c r="AE3" s="693" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="694" t="n"/>
+      <c r="AG3" s="694" t="n"/>
+      <c r="AH3" s="695" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="696" t="n"/>
+      <c r="AK3" s="696" t="n"/>
+      <c r="AL3" s="696" t="n"/>
+      <c r="AM3" s="696" t="n"/>
+      <c r="AN3" s="697" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="516" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="517" t="inlineStr">
-        <is>
-          <t>Requirement / Characteristic</t>
-        </is>
-      </c>
-      <c r="C4" s="517" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="D4" s="517" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="E4" s="517" t="inlineStr">
-        <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="F4" s="517" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="G4" s="517" t="inlineStr">
-        <is>
-          <t>Evidence Ref</t>
-        </is>
-      </c>
-      <c r="H4" s="513" t="n"/>
-      <c r="I4" s="448" t="n"/>
-      <c r="J4" s="449" t="n"/>
-      <c r="K4" s="449" t="n"/>
-      <c r="L4" s="449" t="n"/>
-      <c r="M4" s="449" t="n"/>
-      <c r="N4" s="449" t="n"/>
-      <c r="O4" s="449" t="n"/>
-      <c r="P4" s="449" t="n"/>
-      <c r="Q4" s="449" t="n"/>
-      <c r="R4" s="449" t="n"/>
-      <c r="S4" s="449" t="n"/>
-      <c r="T4" s="449" t="n"/>
-      <c r="U4" s="449" t="n"/>
-      <c r="V4" s="449" t="n"/>
-      <c r="W4" s="449" t="n"/>
-      <c r="X4" s="449" t="n"/>
-      <c r="Y4" s="449" t="n"/>
-      <c r="Z4" s="449" t="n"/>
-      <c r="AA4" s="449" t="n"/>
-      <c r="AB4" s="449" t="n"/>
-      <c r="AC4" s="449" t="n"/>
-      <c r="AD4" s="450" t="n"/>
-      <c r="AE4" s="442" t="n"/>
-      <c r="AF4" s="443" t="n"/>
-      <c r="AG4" s="443" t="n"/>
-      <c r="AH4" s="444" t="n"/>
-      <c r="AI4" s="445" t="n"/>
-      <c r="AJ4" s="446" t="n"/>
-      <c r="AK4" s="446" t="n"/>
-      <c r="AL4" s="446" t="n"/>
-      <c r="AM4" s="446" t="n"/>
-      <c r="AN4" s="447" t="n"/>
+      <c r="A4" s="691" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="692" t="n"/>
+      <c r="I4" s="698" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="692" t="n"/>
+      <c r="AE4" s="693" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="694" t="n"/>
+      <c r="AG4" s="694" t="n"/>
+      <c r="AH4" s="695" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="696" t="n"/>
+      <c r="AK4" s="696" t="n"/>
+      <c r="AL4" s="696" t="n"/>
+      <c r="AM4" s="696" t="n"/>
+      <c r="AN4" s="697" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="518">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B5" s="519" t="n"/>
-      <c r="C5" s="519" t="n"/>
-      <c r="D5" s="519" t="n"/>
-      <c r="E5" s="519" t="n"/>
-      <c r="F5" s="519" t="n"/>
-      <c r="G5" s="519" t="n"/>
-      <c r="H5" s="520" t="n"/>
-      <c r="I5" s="454" t="n"/>
-      <c r="J5" s="455" t="n"/>
-      <c r="K5" s="455" t="n"/>
-      <c r="L5" s="455" t="n"/>
-      <c r="M5" s="455" t="n"/>
-      <c r="N5" s="455" t="n"/>
-      <c r="O5" s="455" t="n"/>
-      <c r="P5" s="455" t="n"/>
-      <c r="Q5" s="455" t="n"/>
-      <c r="R5" s="455" t="n"/>
-      <c r="S5" s="455" t="n"/>
-      <c r="T5" s="455" t="n"/>
-      <c r="U5" s="455" t="n"/>
-      <c r="V5" s="455" t="n"/>
-      <c r="W5" s="455" t="n"/>
-      <c r="X5" s="455" t="n"/>
-      <c r="Y5" s="455" t="n"/>
-      <c r="Z5" s="455" t="n"/>
-      <c r="AA5" s="455" t="n"/>
-      <c r="AB5" s="455" t="n"/>
-      <c r="AC5" s="455" t="n"/>
-      <c r="AD5" s="456" t="n"/>
-      <c r="AE5" s="457" t="n"/>
-      <c r="AF5" s="458" t="n"/>
-      <c r="AG5" s="458" t="n"/>
-      <c r="AH5" s="459" t="n"/>
-      <c r="AI5" s="460" t="n"/>
-      <c r="AJ5" s="461" t="n"/>
-      <c r="AK5" s="461" t="n"/>
-      <c r="AL5" s="461" t="n"/>
-      <c r="AM5" s="461" t="n"/>
-      <c r="AN5" s="462" t="n"/>
+      <c r="A5" s="691" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="692" t="n"/>
+      <c r="I5" s="699" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="692" t="n"/>
+      <c r="AE5" s="693" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="694" t="n"/>
+      <c r="AG5" s="694" t="n"/>
+      <c r="AH5" s="695" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="696" t="n"/>
+      <c r="AK5" s="696" t="n"/>
+      <c r="AL5" s="696" t="n"/>
+      <c r="AM5" s="696" t="n"/>
+      <c r="AN5" s="697" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="521">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B6" s="522" t="n"/>
-      <c r="C6" s="523" t="n"/>
-      <c r="D6" s="523" t="n"/>
-      <c r="E6" s="523" t="n"/>
-      <c r="F6" s="523" t="n"/>
-      <c r="G6" s="523" t="n"/>
-      <c r="H6" s="468" t="n"/>
-      <c r="I6" s="468" t="n"/>
-      <c r="J6" s="468" t="n"/>
-      <c r="K6" s="468" t="n"/>
-      <c r="L6" s="468" t="n"/>
-      <c r="M6" s="468" t="n"/>
-      <c r="N6" s="468" t="n"/>
-      <c r="O6" s="468" t="n"/>
-      <c r="P6" s="468" t="n"/>
-      <c r="Q6" s="468" t="n"/>
-      <c r="R6" s="468" t="n"/>
-      <c r="S6" s="468" t="n"/>
-      <c r="T6" s="468" t="n"/>
-      <c r="U6" s="468" t="n"/>
-      <c r="V6" s="468" t="n"/>
-      <c r="W6" s="468" t="n"/>
-      <c r="X6" s="468" t="n"/>
-      <c r="Y6" s="468" t="n"/>
-      <c r="Z6" s="468" t="n"/>
-      <c r="AA6" s="468" t="n"/>
-      <c r="AB6" s="468" t="n"/>
-      <c r="AC6" s="468" t="n"/>
-      <c r="AD6" s="468" t="n"/>
-      <c r="AE6" s="468" t="n"/>
-      <c r="AF6" s="468" t="n"/>
-      <c r="AG6" s="468" t="n"/>
-      <c r="AH6" s="468" t="n"/>
-      <c r="AI6" s="468" t="n"/>
-      <c r="AJ6" s="468" t="n"/>
-      <c r="AK6" s="468" t="n"/>
-      <c r="AL6" s="468" t="n"/>
-      <c r="AM6" s="468" t="n"/>
-      <c r="AN6" s="500" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="715" t="n"/>
+      <c r="B6" s="716" t="n"/>
+      <c r="C6" s="716" t="n"/>
+      <c r="D6" s="716" t="n"/>
+      <c r="E6" s="716" t="n"/>
+      <c r="F6" s="716" t="n"/>
+      <c r="G6" s="716" t="n"/>
+      <c r="H6" s="717" t="n"/>
+      <c r="I6" s="716" t="n"/>
+      <c r="J6" s="716" t="n"/>
+      <c r="K6" s="716" t="n"/>
+      <c r="L6" s="716" t="n"/>
+      <c r="M6" s="716" t="n"/>
+      <c r="N6" s="716" t="n"/>
+      <c r="O6" s="716" t="n"/>
+      <c r="P6" s="716" t="n"/>
+      <c r="Q6" s="716" t="n"/>
+      <c r="R6" s="716" t="n"/>
+      <c r="S6" s="716" t="n"/>
+      <c r="T6" s="716" t="n"/>
+      <c r="U6" s="716" t="n"/>
+      <c r="V6" s="716" t="n"/>
+      <c r="W6" s="716" t="n"/>
+      <c r="X6" s="716" t="n"/>
+      <c r="Y6" s="716" t="n"/>
+      <c r="Z6" s="716" t="n"/>
+      <c r="AA6" s="716" t="n"/>
+      <c r="AB6" s="716" t="n"/>
+      <c r="AC6" s="716" t="n"/>
+      <c r="AD6" s="717" t="n"/>
+      <c r="AE6" s="718" t="n"/>
+      <c r="AF6" s="718" t="n"/>
+      <c r="AG6" s="718" t="n"/>
+      <c r="AH6" s="719" t="n"/>
+      <c r="AI6" s="720" t="n"/>
+      <c r="AJ6" s="720" t="n"/>
+      <c r="AK6" s="720" t="n"/>
+      <c r="AL6" s="720" t="n"/>
+      <c r="AM6" s="720" t="n"/>
+      <c r="AN6" s="721" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="524">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B7" s="525" t="n"/>
-      <c r="C7" s="526" t="n"/>
-      <c r="D7" s="526" t="n"/>
-      <c r="E7" s="526" t="n"/>
-      <c r="F7" s="526" t="n"/>
-      <c r="G7" s="526" t="n"/>
-      <c r="H7" s="342" t="n"/>
-      <c r="I7" s="342" t="n"/>
-      <c r="J7" s="342" t="n"/>
-      <c r="K7" s="342" t="n"/>
-      <c r="L7" s="342" t="n"/>
-      <c r="M7" s="342" t="n"/>
-      <c r="N7" s="342" t="n"/>
-      <c r="O7" s="342" t="n"/>
-      <c r="P7" s="342" t="n"/>
-      <c r="Q7" s="342" t="n"/>
-      <c r="R7" s="342" t="n"/>
-      <c r="S7" s="342" t="n"/>
-      <c r="T7" s="342" t="n"/>
-      <c r="U7" s="342" t="n"/>
-      <c r="V7" s="342" t="n"/>
-      <c r="W7" s="342" t="n"/>
-      <c r="X7" s="342" t="n"/>
-      <c r="Y7" s="342" t="n"/>
-      <c r="Z7" s="342" t="n"/>
-      <c r="AA7" s="342" t="n"/>
-      <c r="AB7" s="342" t="n"/>
-      <c r="AC7" s="342" t="n"/>
-      <c r="AD7" s="342" t="n"/>
-      <c r="AE7" s="342" t="n"/>
-      <c r="AF7" s="342" t="n"/>
-      <c r="AG7" s="342" t="n"/>
-      <c r="AH7" s="342" t="n"/>
-      <c r="AI7" s="342" t="n"/>
-      <c r="AJ7" s="342" t="n"/>
-      <c r="AK7" s="342" t="n"/>
-      <c r="AL7" s="342" t="n"/>
-      <c r="AM7" s="342" t="n"/>
-      <c r="AN7" s="527" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="722" t="n"/>
+      <c r="B7" s="722" t="n"/>
+      <c r="C7" s="722" t="n"/>
+      <c r="D7" s="722" t="n"/>
+      <c r="E7" s="722" t="n"/>
+      <c r="F7" s="722" t="n"/>
+      <c r="G7" s="723" t="n"/>
+      <c r="H7" s="723" t="n"/>
+      <c r="I7" s="723" t="n"/>
+      <c r="J7" s="723" t="n"/>
+      <c r="K7" s="723" t="n"/>
+      <c r="L7" s="723" t="n"/>
+      <c r="M7" s="723" t="n"/>
+      <c r="N7" s="723" t="n"/>
+      <c r="O7" s="723" t="n"/>
+      <c r="P7" s="723" t="n"/>
+      <c r="Q7" s="723" t="n"/>
+      <c r="R7" s="723" t="n"/>
+      <c r="S7" s="723" t="n"/>
+      <c r="T7" s="723" t="n"/>
+      <c r="U7" s="723" t="n"/>
+      <c r="V7" s="723" t="n"/>
+      <c r="W7" s="723" t="n"/>
+      <c r="X7" s="723" t="n"/>
+      <c r="Y7" s="723" t="n"/>
+      <c r="Z7" s="723" t="n"/>
+      <c r="AA7" s="723" t="n"/>
+      <c r="AB7" s="723" t="n"/>
+      <c r="AC7" s="723" t="n"/>
+      <c r="AD7" s="723" t="n"/>
+      <c r="AE7" s="723" t="n"/>
+      <c r="AF7" s="723" t="n"/>
+      <c r="AG7" s="723" t="n"/>
+      <c r="AH7" s="723" t="n"/>
+      <c r="AI7" s="723" t="n"/>
+      <c r="AJ7" s="723" t="n"/>
+      <c r="AK7" s="723" t="n"/>
+      <c r="AL7" s="723" t="n"/>
+      <c r="AM7" s="723" t="n"/>
+      <c r="AN7" s="723" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B8" s="529" t="n"/>
-      <c r="C8" s="530" t="n"/>
-      <c r="D8" s="530" t="n"/>
-      <c r="E8" s="530" t="n"/>
-      <c r="F8" s="530" t="n"/>
-      <c r="G8" s="530" t="n"/>
-      <c r="H8" s="354" t="n"/>
-      <c r="I8" s="354" t="n"/>
-      <c r="J8" s="354" t="n"/>
-      <c r="K8" s="354" t="n"/>
-      <c r="L8" s="354" t="n"/>
-      <c r="M8" s="354" t="n"/>
-      <c r="N8" s="354" t="n"/>
-      <c r="O8" s="354" t="n"/>
-      <c r="P8" s="354" t="n"/>
-      <c r="Q8" s="354" t="n"/>
-      <c r="R8" s="354" t="n"/>
-      <c r="S8" s="354" t="n"/>
-      <c r="T8" s="354" t="n"/>
-      <c r="U8" s="354" t="n"/>
-      <c r="V8" s="354" t="n"/>
-      <c r="W8" s="354" t="n"/>
-      <c r="X8" s="354" t="n"/>
-      <c r="Y8" s="354" t="n"/>
-      <c r="Z8" s="354" t="n"/>
-      <c r="AA8" s="354" t="n"/>
-      <c r="AB8" s="354" t="n"/>
-      <c r="AC8" s="354" t="n"/>
-      <c r="AD8" s="354" t="n"/>
-      <c r="AE8" s="354" t="n"/>
-      <c r="AF8" s="354" t="n"/>
-      <c r="AG8" s="354" t="n"/>
-      <c r="AH8" s="354" t="n"/>
-      <c r="AI8" s="354" t="n"/>
-      <c r="AJ8" s="354" t="n"/>
-      <c r="AK8" s="354" t="n"/>
-      <c r="AL8" s="354" t="n"/>
-      <c r="AM8" s="354" t="n"/>
-      <c r="AN8" s="531" t="n"/>
+    <row r="8">
+      <c r="A8" s="266" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="266" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="C8" s="266" t="inlineStr">
+        <is>
+          <t>SALES</t>
+        </is>
+      </c>
+      <c r="D8" s="266" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E8" s="266" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F8" s="266" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G8" s="671" t="n"/>
+      <c r="H8" s="671" t="n"/>
+      <c r="I8" s="671" t="n"/>
+      <c r="J8" s="671" t="n"/>
+      <c r="K8" s="671" t="n"/>
+      <c r="L8" s="671" t="n"/>
+      <c r="M8" s="671" t="n"/>
+      <c r="N8" s="671" t="n"/>
+      <c r="O8" s="671" t="n"/>
+      <c r="P8" s="671" t="n"/>
+      <c r="Q8" s="671" t="n"/>
+      <c r="R8" s="671" t="n"/>
+      <c r="S8" s="671" t="n"/>
+      <c r="T8" s="671" t="n"/>
+      <c r="U8" s="671" t="n"/>
+      <c r="V8" s="671" t="n"/>
+      <c r="W8" s="671" t="n"/>
+      <c r="X8" s="671" t="n"/>
+      <c r="Y8" s="671" t="n"/>
+      <c r="Z8" s="671" t="n"/>
+      <c r="AA8" s="671" t="n"/>
+      <c r="AB8" s="671" t="n"/>
+      <c r="AC8" s="671" t="n"/>
+      <c r="AD8" s="671" t="n"/>
+      <c r="AE8" s="671" t="n"/>
+      <c r="AF8" s="671" t="n"/>
+      <c r="AG8" s="671" t="n"/>
+      <c r="AH8" s="671" t="n"/>
+      <c r="AI8" s="671" t="n"/>
+      <c r="AJ8" s="671" t="n"/>
+      <c r="AK8" s="671" t="n"/>
+      <c r="AL8" s="671" t="n"/>
+      <c r="AM8" s="671" t="n"/>
+      <c r="AN8" s="671" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B9" s="529" t="n"/>
-      <c r="C9" s="530" t="n"/>
-      <c r="D9" s="530" t="n"/>
-      <c r="E9" s="530" t="n"/>
-      <c r="F9" s="530" t="n"/>
-      <c r="G9" s="530" t="n"/>
-      <c r="H9" s="354" t="n"/>
-      <c r="I9" s="354" t="n"/>
-      <c r="J9" s="354" t="n"/>
-      <c r="K9" s="354" t="n"/>
-      <c r="L9" s="354" t="n"/>
-      <c r="M9" s="354" t="n"/>
-      <c r="N9" s="354" t="n"/>
-      <c r="O9" s="354" t="n"/>
-      <c r="P9" s="354" t="n"/>
-      <c r="Q9" s="354" t="n"/>
-      <c r="R9" s="354" t="n"/>
-      <c r="S9" s="354" t="n"/>
-      <c r="T9" s="354" t="n"/>
-      <c r="U9" s="354" t="n"/>
-      <c r="V9" s="354" t="n"/>
-      <c r="W9" s="354" t="n"/>
-      <c r="X9" s="354" t="n"/>
-      <c r="Y9" s="354" t="n"/>
-      <c r="Z9" s="354" t="n"/>
-      <c r="AA9" s="354" t="n"/>
-      <c r="AB9" s="354" t="n"/>
-      <c r="AC9" s="354" t="n"/>
-      <c r="AD9" s="354" t="n"/>
-      <c r="AE9" s="354" t="n"/>
-      <c r="AF9" s="354" t="n"/>
-      <c r="AG9" s="354" t="n"/>
-      <c r="AH9" s="354" t="n"/>
-      <c r="AI9" s="354" t="n"/>
-      <c r="AJ9" s="354" t="n"/>
-      <c r="AK9" s="354" t="n"/>
-      <c r="AL9" s="354" t="n"/>
-      <c r="AM9" s="354" t="n"/>
-      <c r="AN9" s="531" t="n"/>
+    <row r="9">
+      <c r="A9" s="266" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B9" s="266" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="C9" s="266" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="D9" s="266" t="inlineStr">
+        <is>
+          <t>NOT CLOSED</t>
+        </is>
+      </c>
+      <c r="E9" s="266" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F9" s="266" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" s="671" t="n"/>
+      <c r="H9" s="671" t="n"/>
+      <c r="I9" s="671" t="n"/>
+      <c r="J9" s="671" t="n"/>
+      <c r="K9" s="671" t="n"/>
+      <c r="L9" s="671" t="n"/>
+      <c r="M9" s="671" t="n"/>
+      <c r="N9" s="671" t="n"/>
+      <c r="O9" s="671" t="n"/>
+      <c r="P9" s="671" t="n"/>
+      <c r="Q9" s="671" t="n"/>
+      <c r="R9" s="671" t="n"/>
+      <c r="S9" s="671" t="n"/>
+      <c r="T9" s="671" t="n"/>
+      <c r="U9" s="671" t="n"/>
+      <c r="V9" s="671" t="n"/>
+      <c r="W9" s="671" t="n"/>
+      <c r="X9" s="671" t="n"/>
+      <c r="Y9" s="671" t="n"/>
+      <c r="Z9" s="671" t="n"/>
+      <c r="AA9" s="671" t="n"/>
+      <c r="AB9" s="671" t="n"/>
+      <c r="AC9" s="671" t="n"/>
+      <c r="AD9" s="671" t="n"/>
+      <c r="AE9" s="671" t="n"/>
+      <c r="AF9" s="671" t="n"/>
+      <c r="AG9" s="671" t="n"/>
+      <c r="AH9" s="671" t="n"/>
+      <c r="AI9" s="671" t="n"/>
+      <c r="AJ9" s="671" t="n"/>
+      <c r="AK9" s="671" t="n"/>
+      <c r="AL9" s="671" t="n"/>
+      <c r="AM9" s="671" t="n"/>
+      <c r="AN9" s="671" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B10" s="529" t="n"/>
-      <c r="C10" s="530" t="n"/>
-      <c r="D10" s="530" t="n"/>
-      <c r="E10" s="530" t="n"/>
-      <c r="F10" s="530" t="n"/>
-      <c r="G10" s="530" t="n"/>
-      <c r="H10" s="354" t="n"/>
-      <c r="I10" s="354" t="n"/>
-      <c r="J10" s="354" t="n"/>
-      <c r="K10" s="354" t="n"/>
-      <c r="L10" s="354" t="n"/>
-      <c r="M10" s="354" t="n"/>
-      <c r="N10" s="354" t="n"/>
-      <c r="O10" s="354" t="n"/>
-      <c r="P10" s="354" t="n"/>
-      <c r="Q10" s="354" t="n"/>
-      <c r="R10" s="354" t="n"/>
-      <c r="S10" s="354" t="n"/>
-      <c r="T10" s="354" t="n"/>
-      <c r="U10" s="354" t="n"/>
-      <c r="V10" s="354" t="n"/>
-      <c r="W10" s="354" t="n"/>
-      <c r="X10" s="354" t="n"/>
-      <c r="Y10" s="354" t="n"/>
-      <c r="Z10" s="354" t="n"/>
-      <c r="AA10" s="354" t="n"/>
-      <c r="AB10" s="354" t="n"/>
-      <c r="AC10" s="354" t="n"/>
-      <c r="AD10" s="354" t="n"/>
-      <c r="AE10" s="354" t="n"/>
-      <c r="AF10" s="354" t="n"/>
-      <c r="AG10" s="354" t="n"/>
-      <c r="AH10" s="354" t="n"/>
-      <c r="AI10" s="354" t="n"/>
-      <c r="AJ10" s="354" t="n"/>
-      <c r="AK10" s="354" t="n"/>
-      <c r="AL10" s="354" t="n"/>
-      <c r="AM10" s="354" t="n"/>
-      <c r="AN10" s="531" t="n"/>
+    <row r="10">
+      <c r="A10" s="266" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B10" s="266" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C10" s="266" t="inlineStr">
+        <is>
+          <t>PLANNING</t>
+        </is>
+      </c>
+      <c r="D10" s="671" t="n"/>
+      <c r="E10" s="266" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="F10" s="266" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G10" s="671" t="n"/>
+      <c r="H10" s="671" t="n"/>
+      <c r="I10" s="671" t="n"/>
+      <c r="J10" s="671" t="n"/>
+      <c r="K10" s="671" t="n"/>
+      <c r="L10" s="671" t="n"/>
+      <c r="M10" s="671" t="n"/>
+      <c r="N10" s="671" t="n"/>
+      <c r="O10" s="671" t="n"/>
+      <c r="P10" s="671" t="n"/>
+      <c r="Q10" s="671" t="n"/>
+      <c r="R10" s="671" t="n"/>
+      <c r="S10" s="671" t="n"/>
+      <c r="T10" s="671" t="n"/>
+      <c r="U10" s="671" t="n"/>
+      <c r="V10" s="671" t="n"/>
+      <c r="W10" s="671" t="n"/>
+      <c r="X10" s="671" t="n"/>
+      <c r="Y10" s="671" t="n"/>
+      <c r="Z10" s="671" t="n"/>
+      <c r="AA10" s="671" t="n"/>
+      <c r="AB10" s="671" t="n"/>
+      <c r="AC10" s="671" t="n"/>
+      <c r="AD10" s="671" t="n"/>
+      <c r="AE10" s="671" t="n"/>
+      <c r="AF10" s="671" t="n"/>
+      <c r="AG10" s="671" t="n"/>
+      <c r="AH10" s="671" t="n"/>
+      <c r="AI10" s="671" t="n"/>
+      <c r="AJ10" s="671" t="n"/>
+      <c r="AK10" s="671" t="n"/>
+      <c r="AL10" s="671" t="n"/>
+      <c r="AM10" s="671" t="n"/>
+      <c r="AN10" s="671" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B11" s="529" t="n"/>
-      <c r="C11" s="530" t="n"/>
-      <c r="D11" s="530" t="n"/>
-      <c r="E11" s="530" t="n"/>
-      <c r="F11" s="530" t="n"/>
-      <c r="G11" s="530" t="n"/>
-      <c r="H11" s="354" t="n"/>
-      <c r="I11" s="354" t="n"/>
-      <c r="J11" s="354" t="n"/>
-      <c r="K11" s="354" t="n"/>
-      <c r="L11" s="354" t="n"/>
-      <c r="M11" s="354" t="n"/>
-      <c r="N11" s="354" t="n"/>
-      <c r="O11" s="354" t="n"/>
-      <c r="P11" s="354" t="n"/>
-      <c r="Q11" s="354" t="n"/>
-      <c r="R11" s="354" t="n"/>
-      <c r="S11" s="354" t="n"/>
-      <c r="T11" s="354" t="n"/>
-      <c r="U11" s="354" t="n"/>
-      <c r="V11" s="354" t="n"/>
-      <c r="W11" s="354" t="n"/>
-      <c r="X11" s="354" t="n"/>
-      <c r="Y11" s="354" t="n"/>
-      <c r="Z11" s="354" t="n"/>
-      <c r="AA11" s="354" t="n"/>
-      <c r="AB11" s="354" t="n"/>
-      <c r="AC11" s="354" t="n"/>
-      <c r="AD11" s="354" t="n"/>
-      <c r="AE11" s="354" t="n"/>
-      <c r="AF11" s="354" t="n"/>
-      <c r="AG11" s="354" t="n"/>
-      <c r="AH11" s="354" t="n"/>
-      <c r="AI11" s="354" t="n"/>
-      <c r="AJ11" s="354" t="n"/>
-      <c r="AK11" s="354" t="n"/>
-      <c r="AL11" s="354" t="n"/>
-      <c r="AM11" s="354" t="n"/>
-      <c r="AN11" s="531" t="n"/>
+    <row r="11">
+      <c r="A11" s="266" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B11" s="266" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="C11" s="266" t="inlineStr">
+        <is>
+          <t>PROD</t>
+        </is>
+      </c>
+      <c r="D11" s="671" t="n"/>
+      <c r="E11" s="346" t="inlineStr">
+        <is>
+          <t>MONITORING</t>
+        </is>
+      </c>
+      <c r="F11" s="671" t="n"/>
+      <c r="G11" s="671" t="n"/>
+      <c r="H11" s="671" t="n"/>
+      <c r="I11" s="671" t="n"/>
+      <c r="J11" s="671" t="n"/>
+      <c r="K11" s="671" t="n"/>
+      <c r="L11" s="671" t="n"/>
+      <c r="M11" s="671" t="n"/>
+      <c r="N11" s="671" t="n"/>
+      <c r="O11" s="671" t="n"/>
+      <c r="P11" s="671" t="n"/>
+      <c r="Q11" s="671" t="n"/>
+      <c r="R11" s="671" t="n"/>
+      <c r="S11" s="671" t="n"/>
+      <c r="T11" s="671" t="n"/>
+      <c r="U11" s="671" t="n"/>
+      <c r="V11" s="671" t="n"/>
+      <c r="W11" s="671" t="n"/>
+      <c r="X11" s="671" t="n"/>
+      <c r="Y11" s="671" t="n"/>
+      <c r="Z11" s="671" t="n"/>
+      <c r="AA11" s="671" t="n"/>
+      <c r="AB11" s="671" t="n"/>
+      <c r="AC11" s="671" t="n"/>
+      <c r="AD11" s="671" t="n"/>
+      <c r="AE11" s="671" t="n"/>
+      <c r="AF11" s="671" t="n"/>
+      <c r="AG11" s="671" t="n"/>
+      <c r="AH11" s="671" t="n"/>
+      <c r="AI11" s="671" t="n"/>
+      <c r="AJ11" s="671" t="n"/>
+      <c r="AK11" s="671" t="n"/>
+      <c r="AL11" s="671" t="n"/>
+      <c r="AM11" s="671" t="n"/>
+      <c r="AN11" s="671" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B12" s="529" t="n"/>
-      <c r="C12" s="530" t="n"/>
-      <c r="D12" s="530" t="n"/>
-      <c r="E12" s="530" t="n"/>
-      <c r="F12" s="530" t="n"/>
-      <c r="G12" s="530" t="n"/>
-      <c r="H12" s="354" t="n"/>
-      <c r="I12" s="354" t="n"/>
-      <c r="J12" s="354" t="n"/>
-      <c r="K12" s="354" t="n"/>
-      <c r="L12" s="354" t="n"/>
-      <c r="M12" s="354" t="n"/>
-      <c r="N12" s="354" t="n"/>
-      <c r="O12" s="354" t="n"/>
-      <c r="P12" s="354" t="n"/>
-      <c r="Q12" s="354" t="n"/>
-      <c r="R12" s="354" t="n"/>
-      <c r="S12" s="354" t="n"/>
-      <c r="T12" s="354" t="n"/>
-      <c r="U12" s="354" t="n"/>
-      <c r="V12" s="354" t="n"/>
-      <c r="W12" s="354" t="n"/>
-      <c r="X12" s="354" t="n"/>
-      <c r="Y12" s="354" t="n"/>
-      <c r="Z12" s="354" t="n"/>
-      <c r="AA12" s="354" t="n"/>
-      <c r="AB12" s="354" t="n"/>
-      <c r="AC12" s="354" t="n"/>
-      <c r="AD12" s="354" t="n"/>
-      <c r="AE12" s="354" t="n"/>
-      <c r="AF12" s="354" t="n"/>
-      <c r="AG12" s="354" t="n"/>
-      <c r="AH12" s="354" t="n"/>
-      <c r="AI12" s="354" t="n"/>
-      <c r="AJ12" s="354" t="n"/>
-      <c r="AK12" s="354" t="n"/>
-      <c r="AL12" s="354" t="n"/>
-      <c r="AM12" s="354" t="n"/>
-      <c r="AN12" s="531" t="n"/>
+    <row r="12">
+      <c r="A12" s="671" t="n"/>
+      <c r="B12" s="671" t="n"/>
+      <c r="C12" s="346" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D12" s="671" t="n"/>
+      <c r="E12" s="671" t="n"/>
+      <c r="F12" s="671" t="n"/>
+      <c r="G12" s="671" t="n"/>
+      <c r="H12" s="671" t="n"/>
+      <c r="I12" s="671" t="n"/>
+      <c r="J12" s="671" t="n"/>
+      <c r="K12" s="671" t="n"/>
+      <c r="L12" s="671" t="n"/>
+      <c r="M12" s="671" t="n"/>
+      <c r="N12" s="671" t="n"/>
+      <c r="O12" s="671" t="n"/>
+      <c r="P12" s="671" t="n"/>
+      <c r="Q12" s="671" t="n"/>
+      <c r="R12" s="671" t="n"/>
+      <c r="S12" s="671" t="n"/>
+      <c r="T12" s="671" t="n"/>
+      <c r="U12" s="671" t="n"/>
+      <c r="V12" s="671" t="n"/>
+      <c r="W12" s="671" t="n"/>
+      <c r="X12" s="671" t="n"/>
+      <c r="Y12" s="671" t="n"/>
+      <c r="Z12" s="671" t="n"/>
+      <c r="AA12" s="671" t="n"/>
+      <c r="AB12" s="671" t="n"/>
+      <c r="AC12" s="671" t="n"/>
+      <c r="AD12" s="671" t="n"/>
+      <c r="AE12" s="671" t="n"/>
+      <c r="AF12" s="671" t="n"/>
+      <c r="AG12" s="671" t="n"/>
+      <c r="AH12" s="671" t="n"/>
+      <c r="AI12" s="671" t="n"/>
+      <c r="AJ12" s="671" t="n"/>
+      <c r="AK12" s="671" t="n"/>
+      <c r="AL12" s="671" t="n"/>
+      <c r="AM12" s="671" t="n"/>
+      <c r="AN12" s="671" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B13" s="529" t="n"/>
-      <c r="C13" s="530" t="n"/>
-      <c r="D13" s="530" t="n"/>
-      <c r="E13" s="530" t="n"/>
-      <c r="F13" s="530" t="n"/>
-      <c r="G13" s="530" t="n"/>
-      <c r="H13" s="354" t="n"/>
-      <c r="I13" s="354" t="n"/>
-      <c r="J13" s="354" t="n"/>
-      <c r="K13" s="354" t="n"/>
-      <c r="L13" s="354" t="n"/>
-      <c r="M13" s="354" t="n"/>
-      <c r="N13" s="354" t="n"/>
-      <c r="O13" s="354" t="n"/>
-      <c r="P13" s="354" t="n"/>
-      <c r="Q13" s="354" t="n"/>
-      <c r="R13" s="354" t="n"/>
-      <c r="S13" s="354" t="n"/>
-      <c r="T13" s="354" t="n"/>
-      <c r="U13" s="354" t="n"/>
-      <c r="V13" s="354" t="n"/>
-      <c r="W13" s="354" t="n"/>
-      <c r="X13" s="354" t="n"/>
-      <c r="Y13" s="354" t="n"/>
-      <c r="Z13" s="354" t="n"/>
-      <c r="AA13" s="354" t="n"/>
-      <c r="AB13" s="354" t="n"/>
-      <c r="AC13" s="354" t="n"/>
-      <c r="AD13" s="354" t="n"/>
-      <c r="AE13" s="354" t="n"/>
-      <c r="AF13" s="354" t="n"/>
-      <c r="AG13" s="354" t="n"/>
-      <c r="AH13" s="354" t="n"/>
-      <c r="AI13" s="354" t="n"/>
-      <c r="AJ13" s="354" t="n"/>
-      <c r="AK13" s="354" t="n"/>
-      <c r="AL13" s="354" t="n"/>
-      <c r="AM13" s="354" t="n"/>
-      <c r="AN13" s="531" t="n"/>
+    <row r="13">
+      <c r="A13" s="671" t="n"/>
+      <c r="B13" s="671" t="n"/>
+      <c r="C13" s="346" t="inlineStr">
+        <is>
+          <t>PUR</t>
+        </is>
+      </c>
+      <c r="D13" s="671" t="n"/>
+      <c r="E13" s="671" t="n"/>
+      <c r="F13" s="671" t="n"/>
+      <c r="G13" s="671" t="n"/>
+      <c r="H13" s="671" t="n"/>
+      <c r="I13" s="671" t="n"/>
+      <c r="J13" s="671" t="n"/>
+      <c r="K13" s="671" t="n"/>
+      <c r="L13" s="671" t="n"/>
+      <c r="M13" s="671" t="n"/>
+      <c r="N13" s="671" t="n"/>
+      <c r="O13" s="671" t="n"/>
+      <c r="P13" s="671" t="n"/>
+      <c r="Q13" s="671" t="n"/>
+      <c r="R13" s="671" t="n"/>
+      <c r="S13" s="671" t="n"/>
+      <c r="T13" s="671" t="n"/>
+      <c r="U13" s="671" t="n"/>
+      <c r="V13" s="671" t="n"/>
+      <c r="W13" s="671" t="n"/>
+      <c r="X13" s="671" t="n"/>
+      <c r="Y13" s="671" t="n"/>
+      <c r="Z13" s="671" t="n"/>
+      <c r="AA13" s="671" t="n"/>
+      <c r="AB13" s="671" t="n"/>
+      <c r="AC13" s="671" t="n"/>
+      <c r="AD13" s="671" t="n"/>
+      <c r="AE13" s="671" t="n"/>
+      <c r="AF13" s="671" t="n"/>
+      <c r="AG13" s="671" t="n"/>
+      <c r="AH13" s="671" t="n"/>
+      <c r="AI13" s="671" t="n"/>
+      <c r="AJ13" s="671" t="n"/>
+      <c r="AK13" s="671" t="n"/>
+      <c r="AL13" s="671" t="n"/>
+      <c r="AM13" s="671" t="n"/>
+      <c r="AN13" s="671" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B14" s="529" t="n"/>
-      <c r="C14" s="530" t="n"/>
-      <c r="D14" s="530" t="n"/>
-      <c r="E14" s="530" t="n"/>
-      <c r="F14" s="530" t="n"/>
-      <c r="G14" s="530" t="n"/>
-      <c r="H14" s="354" t="n"/>
-      <c r="I14" s="354" t="n"/>
-      <c r="J14" s="354" t="n"/>
-      <c r="K14" s="354" t="n"/>
-      <c r="L14" s="354" t="n"/>
-      <c r="M14" s="354" t="n"/>
-      <c r="N14" s="354" t="n"/>
-      <c r="O14" s="354" t="n"/>
-      <c r="P14" s="354" t="n"/>
-      <c r="Q14" s="354" t="n"/>
-      <c r="R14" s="354" t="n"/>
-      <c r="S14" s="354" t="n"/>
-      <c r="T14" s="354" t="n"/>
-      <c r="U14" s="354" t="n"/>
-      <c r="V14" s="354" t="n"/>
-      <c r="W14" s="354" t="n"/>
-      <c r="X14" s="354" t="n"/>
-      <c r="Y14" s="354" t="n"/>
-      <c r="Z14" s="354" t="n"/>
-      <c r="AA14" s="354" t="n"/>
-      <c r="AB14" s="354" t="n"/>
-      <c r="AC14" s="354" t="n"/>
-      <c r="AD14" s="354" t="n"/>
-      <c r="AE14" s="354" t="n"/>
-      <c r="AF14" s="354" t="n"/>
-      <c r="AG14" s="354" t="n"/>
-      <c r="AH14" s="354" t="n"/>
-      <c r="AI14" s="354" t="n"/>
-      <c r="AJ14" s="354" t="n"/>
-      <c r="AK14" s="354" t="n"/>
-      <c r="AL14" s="354" t="n"/>
-      <c r="AM14" s="354" t="n"/>
-      <c r="AN14" s="531" t="n"/>
+    <row r="14">
+      <c r="A14" s="671" t="n"/>
+      <c r="B14" s="671" t="n"/>
+      <c r="C14" s="346" t="inlineStr">
+        <is>
+          <t>WHS</t>
+        </is>
+      </c>
+      <c r="D14" s="671" t="n"/>
+      <c r="E14" s="671" t="n"/>
+      <c r="F14" s="671" t="n"/>
+      <c r="G14" s="671" t="n"/>
+      <c r="H14" s="671" t="n"/>
+      <c r="I14" s="671" t="n"/>
+      <c r="J14" s="671" t="n"/>
+      <c r="K14" s="671" t="n"/>
+      <c r="L14" s="671" t="n"/>
+      <c r="M14" s="671" t="n"/>
+      <c r="N14" s="671" t="n"/>
+      <c r="O14" s="671" t="n"/>
+      <c r="P14" s="671" t="n"/>
+      <c r="Q14" s="671" t="n"/>
+      <c r="R14" s="671" t="n"/>
+      <c r="S14" s="671" t="n"/>
+      <c r="T14" s="671" t="n"/>
+      <c r="U14" s="671" t="n"/>
+      <c r="V14" s="671" t="n"/>
+      <c r="W14" s="671" t="n"/>
+      <c r="X14" s="671" t="n"/>
+      <c r="Y14" s="671" t="n"/>
+      <c r="Z14" s="671" t="n"/>
+      <c r="AA14" s="671" t="n"/>
+      <c r="AB14" s="671" t="n"/>
+      <c r="AC14" s="671" t="n"/>
+      <c r="AD14" s="671" t="n"/>
+      <c r="AE14" s="671" t="n"/>
+      <c r="AF14" s="671" t="n"/>
+      <c r="AG14" s="671" t="n"/>
+      <c r="AH14" s="671" t="n"/>
+      <c r="AI14" s="671" t="n"/>
+      <c r="AJ14" s="671" t="n"/>
+      <c r="AK14" s="671" t="n"/>
+      <c r="AL14" s="671" t="n"/>
+      <c r="AM14" s="671" t="n"/>
+      <c r="AN14" s="671" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B15" s="529" t="n"/>
-      <c r="C15" s="530" t="n"/>
-      <c r="D15" s="530" t="n"/>
-      <c r="E15" s="530" t="n"/>
-      <c r="F15" s="530" t="n"/>
-      <c r="G15" s="530" t="n"/>
-      <c r="H15" s="354" t="n"/>
-      <c r="I15" s="354" t="n"/>
-      <c r="J15" s="354" t="n"/>
-      <c r="K15" s="354" t="n"/>
-      <c r="L15" s="354" t="n"/>
-      <c r="M15" s="354" t="n"/>
-      <c r="N15" s="354" t="n"/>
-      <c r="O15" s="354" t="n"/>
-      <c r="P15" s="354" t="n"/>
-      <c r="Q15" s="354" t="n"/>
-      <c r="R15" s="354" t="n"/>
-      <c r="S15" s="354" t="n"/>
-      <c r="T15" s="354" t="n"/>
-      <c r="U15" s="354" t="n"/>
-      <c r="V15" s="354" t="n"/>
-      <c r="W15" s="354" t="n"/>
-      <c r="X15" s="354" t="n"/>
-      <c r="Y15" s="354" t="n"/>
-      <c r="Z15" s="354" t="n"/>
-      <c r="AA15" s="354" t="n"/>
-      <c r="AB15" s="354" t="n"/>
-      <c r="AC15" s="354" t="n"/>
-      <c r="AD15" s="354" t="n"/>
-      <c r="AE15" s="354" t="n"/>
-      <c r="AF15" s="354" t="n"/>
-      <c r="AG15" s="354" t="n"/>
-      <c r="AH15" s="354" t="n"/>
-      <c r="AI15" s="354" t="n"/>
-      <c r="AJ15" s="354" t="n"/>
-      <c r="AK15" s="354" t="n"/>
-      <c r="AL15" s="354" t="n"/>
-      <c r="AM15" s="354" t="n"/>
-      <c r="AN15" s="531" t="n"/>
+    <row r="15">
+      <c r="A15" s="671" t="n"/>
+      <c r="B15" s="671" t="n"/>
+      <c r="C15" s="346" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D15" s="671" t="n"/>
+      <c r="E15" s="671" t="n"/>
+      <c r="F15" s="671" t="n"/>
+      <c r="G15" s="671" t="n"/>
+      <c r="H15" s="671" t="n"/>
+      <c r="I15" s="671" t="n"/>
+      <c r="J15" s="671" t="n"/>
+      <c r="K15" s="671" t="n"/>
+      <c r="L15" s="671" t="n"/>
+      <c r="M15" s="671" t="n"/>
+      <c r="N15" s="671" t="n"/>
+      <c r="O15" s="671" t="n"/>
+      <c r="P15" s="671" t="n"/>
+      <c r="Q15" s="671" t="n"/>
+      <c r="R15" s="671" t="n"/>
+      <c r="S15" s="671" t="n"/>
+      <c r="T15" s="671" t="n"/>
+      <c r="U15" s="671" t="n"/>
+      <c r="V15" s="671" t="n"/>
+      <c r="W15" s="671" t="n"/>
+      <c r="X15" s="671" t="n"/>
+      <c r="Y15" s="671" t="n"/>
+      <c r="Z15" s="671" t="n"/>
+      <c r="AA15" s="671" t="n"/>
+      <c r="AB15" s="671" t="n"/>
+      <c r="AC15" s="671" t="n"/>
+      <c r="AD15" s="671" t="n"/>
+      <c r="AE15" s="671" t="n"/>
+      <c r="AF15" s="671" t="n"/>
+      <c r="AG15" s="671" t="n"/>
+      <c r="AH15" s="671" t="n"/>
+      <c r="AI15" s="671" t="n"/>
+      <c r="AJ15" s="671" t="n"/>
+      <c r="AK15" s="671" t="n"/>
+      <c r="AL15" s="671" t="n"/>
+      <c r="AM15" s="671" t="n"/>
+      <c r="AN15" s="671" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B16" s="529" t="n"/>
-      <c r="C16" s="530" t="n"/>
-      <c r="D16" s="530" t="n"/>
-      <c r="E16" s="530" t="n"/>
-      <c r="F16" s="530" t="n"/>
-      <c r="G16" s="530" t="n"/>
-      <c r="H16" s="354" t="n"/>
-      <c r="I16" s="354" t="n"/>
-      <c r="J16" s="354" t="n"/>
-      <c r="K16" s="354" t="n"/>
-      <c r="L16" s="354" t="n"/>
-      <c r="M16" s="354" t="n"/>
-      <c r="N16" s="354" t="n"/>
-      <c r="O16" s="354" t="n"/>
-      <c r="P16" s="354" t="n"/>
-      <c r="Q16" s="354" t="n"/>
-      <c r="R16" s="354" t="n"/>
-      <c r="S16" s="354" t="n"/>
-      <c r="T16" s="354" t="n"/>
-      <c r="U16" s="354" t="n"/>
-      <c r="V16" s="354" t="n"/>
-      <c r="W16" s="354" t="n"/>
-      <c r="X16" s="354" t="n"/>
-      <c r="Y16" s="354" t="n"/>
-      <c r="Z16" s="354" t="n"/>
-      <c r="AA16" s="354" t="n"/>
-      <c r="AB16" s="354" t="n"/>
-      <c r="AC16" s="354" t="n"/>
-      <c r="AD16" s="354" t="n"/>
-      <c r="AE16" s="354" t="n"/>
-      <c r="AF16" s="354" t="n"/>
-      <c r="AG16" s="354" t="n"/>
-      <c r="AH16" s="354" t="n"/>
-      <c r="AI16" s="354" t="n"/>
-      <c r="AJ16" s="354" t="n"/>
-      <c r="AK16" s="354" t="n"/>
-      <c r="AL16" s="354" t="n"/>
-      <c r="AM16" s="354" t="n"/>
-      <c r="AN16" s="531" t="n"/>
+    <row r="16">
+      <c r="A16" s="671" t="n"/>
+      <c r="B16" s="671" t="n"/>
+      <c r="C16" s="346" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D16" s="671" t="n"/>
+      <c r="E16" s="671" t="n"/>
+      <c r="F16" s="671" t="n"/>
+      <c r="G16" s="671" t="n"/>
+      <c r="H16" s="671" t="n"/>
+      <c r="I16" s="671" t="n"/>
+      <c r="J16" s="671" t="n"/>
+      <c r="K16" s="671" t="n"/>
+      <c r="L16" s="671" t="n"/>
+      <c r="M16" s="671" t="n"/>
+      <c r="N16" s="671" t="n"/>
+      <c r="O16" s="671" t="n"/>
+      <c r="P16" s="671" t="n"/>
+      <c r="Q16" s="671" t="n"/>
+      <c r="R16" s="671" t="n"/>
+      <c r="S16" s="671" t="n"/>
+      <c r="T16" s="671" t="n"/>
+      <c r="U16" s="671" t="n"/>
+      <c r="V16" s="671" t="n"/>
+      <c r="W16" s="671" t="n"/>
+      <c r="X16" s="671" t="n"/>
+      <c r="Y16" s="671" t="n"/>
+      <c r="Z16" s="671" t="n"/>
+      <c r="AA16" s="671" t="n"/>
+      <c r="AB16" s="671" t="n"/>
+      <c r="AC16" s="671" t="n"/>
+      <c r="AD16" s="671" t="n"/>
+      <c r="AE16" s="671" t="n"/>
+      <c r="AF16" s="671" t="n"/>
+      <c r="AG16" s="671" t="n"/>
+      <c r="AH16" s="671" t="n"/>
+      <c r="AI16" s="671" t="n"/>
+      <c r="AJ16" s="671" t="n"/>
+      <c r="AK16" s="671" t="n"/>
+      <c r="AL16" s="671" t="n"/>
+      <c r="AM16" s="671" t="n"/>
+      <c r="AN16" s="671" t="n"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B17" s="529" t="n"/>
-      <c r="C17" s="530" t="n"/>
-      <c r="D17" s="530" t="n"/>
-      <c r="E17" s="530" t="n"/>
-      <c r="F17" s="530" t="n"/>
-      <c r="G17" s="530" t="n"/>
-      <c r="H17" s="354" t="n"/>
-      <c r="I17" s="354" t="n"/>
-      <c r="J17" s="354" t="n"/>
-      <c r="K17" s="354" t="n"/>
-      <c r="L17" s="354" t="n"/>
-      <c r="M17" s="354" t="n"/>
-      <c r="N17" s="354" t="n"/>
-      <c r="O17" s="354" t="n"/>
-      <c r="P17" s="354" t="n"/>
-      <c r="Q17" s="354" t="n"/>
-      <c r="R17" s="354" t="n"/>
-      <c r="S17" s="354" t="n"/>
-      <c r="T17" s="354" t="n"/>
-      <c r="U17" s="354" t="n"/>
-      <c r="V17" s="354" t="n"/>
-      <c r="W17" s="354" t="n"/>
-      <c r="X17" s="354" t="n"/>
-      <c r="Y17" s="354" t="n"/>
-      <c r="Z17" s="354" t="n"/>
-      <c r="AA17" s="354" t="n"/>
-      <c r="AB17" s="354" t="n"/>
-      <c r="AC17" s="354" t="n"/>
-      <c r="AD17" s="354" t="n"/>
-      <c r="AE17" s="354" t="n"/>
-      <c r="AF17" s="354" t="n"/>
-      <c r="AG17" s="354" t="n"/>
-      <c r="AH17" s="354" t="n"/>
-      <c r="AI17" s="354" t="n"/>
-      <c r="AJ17" s="354" t="n"/>
-      <c r="AK17" s="354" t="n"/>
-      <c r="AL17" s="354" t="n"/>
-      <c r="AM17" s="354" t="n"/>
-      <c r="AN17" s="531" t="n"/>
+    <row r="17">
+      <c r="A17" s="671" t="n"/>
+      <c r="B17" s="671" t="n"/>
+      <c r="C17" s="346" t="inlineStr">
+        <is>
+          <t>MGT</t>
+        </is>
+      </c>
+      <c r="D17" s="671" t="n"/>
+      <c r="E17" s="671" t="n"/>
+      <c r="F17" s="671" t="n"/>
+      <c r="G17" s="671" t="n"/>
+      <c r="H17" s="671" t="n"/>
+      <c r="I17" s="671" t="n"/>
+      <c r="J17" s="671" t="n"/>
+      <c r="K17" s="671" t="n"/>
+      <c r="L17" s="671" t="n"/>
+      <c r="M17" s="671" t="n"/>
+      <c r="N17" s="671" t="n"/>
+      <c r="O17" s="671" t="n"/>
+      <c r="P17" s="671" t="n"/>
+      <c r="Q17" s="671" t="n"/>
+      <c r="R17" s="671" t="n"/>
+      <c r="S17" s="671" t="n"/>
+      <c r="T17" s="671" t="n"/>
+      <c r="U17" s="671" t="n"/>
+      <c r="V17" s="671" t="n"/>
+      <c r="W17" s="671" t="n"/>
+      <c r="X17" s="671" t="n"/>
+      <c r="Y17" s="671" t="n"/>
+      <c r="Z17" s="671" t="n"/>
+      <c r="AA17" s="671" t="n"/>
+      <c r="AB17" s="671" t="n"/>
+      <c r="AC17" s="671" t="n"/>
+      <c r="AD17" s="671" t="n"/>
+      <c r="AE17" s="671" t="n"/>
+      <c r="AF17" s="671" t="n"/>
+      <c r="AG17" s="671" t="n"/>
+      <c r="AH17" s="671" t="n"/>
+      <c r="AI17" s="671" t="n"/>
+      <c r="AJ17" s="671" t="n"/>
+      <c r="AK17" s="671" t="n"/>
+      <c r="AL17" s="671" t="n"/>
+      <c r="AM17" s="671" t="n"/>
+      <c r="AN17" s="671" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B18" s="529" t="n"/>
-      <c r="C18" s="530" t="n"/>
-      <c r="D18" s="530" t="n"/>
-      <c r="E18" s="530" t="n"/>
-      <c r="F18" s="530" t="n"/>
-      <c r="G18" s="530" t="n"/>
-      <c r="H18" s="354" t="n"/>
-      <c r="I18" s="354" t="n"/>
-      <c r="J18" s="354" t="n"/>
-      <c r="K18" s="354" t="n"/>
-      <c r="L18" s="354" t="n"/>
-      <c r="M18" s="354" t="n"/>
-      <c r="N18" s="354" t="n"/>
-      <c r="O18" s="354" t="n"/>
-      <c r="P18" s="354" t="n"/>
-      <c r="Q18" s="354" t="n"/>
-      <c r="R18" s="354" t="n"/>
-      <c r="S18" s="354" t="n"/>
-      <c r="T18" s="354" t="n"/>
-      <c r="U18" s="354" t="n"/>
-      <c r="V18" s="354" t="n"/>
-      <c r="W18" s="354" t="n"/>
-      <c r="X18" s="354" t="n"/>
-      <c r="Y18" s="354" t="n"/>
-      <c r="Z18" s="354" t="n"/>
-      <c r="AA18" s="354" t="n"/>
-      <c r="AB18" s="354" t="n"/>
-      <c r="AC18" s="354" t="n"/>
-      <c r="AD18" s="354" t="n"/>
-      <c r="AE18" s="354" t="n"/>
-      <c r="AF18" s="354" t="n"/>
-      <c r="AG18" s="354" t="n"/>
-      <c r="AH18" s="354" t="n"/>
-      <c r="AI18" s="354" t="n"/>
-      <c r="AJ18" s="354" t="n"/>
-      <c r="AK18" s="354" t="n"/>
-      <c r="AL18" s="354" t="n"/>
-      <c r="AM18" s="354" t="n"/>
-      <c r="AN18" s="531" t="n"/>
+    <row r="18">
+      <c r="A18" s="671" t="n"/>
+      <c r="B18" s="671" t="n"/>
+      <c r="C18" s="671" t="n"/>
+      <c r="D18" s="671" t="n"/>
+      <c r="E18" s="671" t="n"/>
+      <c r="F18" s="671" t="n"/>
+      <c r="G18" s="671" t="n"/>
+      <c r="H18" s="671" t="n"/>
+      <c r="I18" s="671" t="n"/>
+      <c r="J18" s="671" t="n"/>
+      <c r="K18" s="671" t="n"/>
+      <c r="L18" s="671" t="n"/>
+      <c r="M18" s="671" t="n"/>
+      <c r="N18" s="671" t="n"/>
+      <c r="O18" s="671" t="n"/>
+      <c r="P18" s="671" t="n"/>
+      <c r="Q18" s="671" t="n"/>
+      <c r="R18" s="671" t="n"/>
+      <c r="S18" s="671" t="n"/>
+      <c r="T18" s="671" t="n"/>
+      <c r="U18" s="671" t="n"/>
+      <c r="V18" s="671" t="n"/>
+      <c r="W18" s="671" t="n"/>
+      <c r="X18" s="671" t="n"/>
+      <c r="Y18" s="671" t="n"/>
+      <c r="Z18" s="671" t="n"/>
+      <c r="AA18" s="671" t="n"/>
+      <c r="AB18" s="671" t="n"/>
+      <c r="AC18" s="671" t="n"/>
+      <c r="AD18" s="671" t="n"/>
+      <c r="AE18" s="671" t="n"/>
+      <c r="AF18" s="671" t="n"/>
+      <c r="AG18" s="671" t="n"/>
+      <c r="AH18" s="671" t="n"/>
+      <c r="AI18" s="671" t="n"/>
+      <c r="AJ18" s="671" t="n"/>
+      <c r="AK18" s="671" t="n"/>
+      <c r="AL18" s="671" t="n"/>
+      <c r="AM18" s="671" t="n"/>
+      <c r="AN18" s="671" t="n"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="532">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B19" s="533" t="n"/>
-      <c r="C19" s="534" t="n"/>
-      <c r="D19" s="534" t="n"/>
-      <c r="E19" s="534" t="n"/>
-      <c r="F19" s="534" t="n"/>
-      <c r="G19" s="534" t="n"/>
-      <c r="H19" s="535" t="n"/>
-      <c r="I19" s="535" t="n"/>
-      <c r="J19" s="535" t="n"/>
-      <c r="K19" s="535" t="n"/>
-      <c r="L19" s="535" t="n"/>
-      <c r="M19" s="535" t="n"/>
-      <c r="N19" s="535" t="n"/>
-      <c r="O19" s="535" t="n"/>
-      <c r="P19" s="535" t="n"/>
-      <c r="Q19" s="535" t="n"/>
-      <c r="R19" s="535" t="n"/>
-      <c r="S19" s="535" t="n"/>
-      <c r="T19" s="535" t="n"/>
-      <c r="U19" s="535" t="n"/>
-      <c r="V19" s="535" t="n"/>
-      <c r="W19" s="535" t="n"/>
-      <c r="X19" s="535" t="n"/>
-      <c r="Y19" s="535" t="n"/>
-      <c r="Z19" s="535" t="n"/>
-      <c r="AA19" s="535" t="n"/>
-      <c r="AB19" s="535" t="n"/>
-      <c r="AC19" s="535" t="n"/>
-      <c r="AD19" s="535" t="n"/>
-      <c r="AE19" s="535" t="n"/>
-      <c r="AF19" s="535" t="n"/>
-      <c r="AG19" s="535" t="n"/>
-      <c r="AH19" s="535" t="n"/>
-      <c r="AI19" s="535" t="n"/>
-      <c r="AJ19" s="535" t="n"/>
-      <c r="AK19" s="535" t="n"/>
-      <c r="AL19" s="535" t="n"/>
-      <c r="AM19" s="535" t="n"/>
-      <c r="AN19" s="536" t="n"/>
+    <row r="19">
+      <c r="A19" s="671" t="n"/>
+      <c r="B19" s="671" t="n"/>
+      <c r="C19" s="671" t="n"/>
+      <c r="D19" s="671" t="n"/>
+      <c r="E19" s="671" t="n"/>
+      <c r="F19" s="671" t="n"/>
+      <c r="G19" s="671" t="n"/>
+      <c r="H19" s="671" t="n"/>
+      <c r="I19" s="671" t="n"/>
+      <c r="J19" s="671" t="n"/>
+      <c r="K19" s="671" t="n"/>
+      <c r="L19" s="671" t="n"/>
+      <c r="M19" s="671" t="n"/>
+      <c r="N19" s="671" t="n"/>
+      <c r="O19" s="671" t="n"/>
+      <c r="P19" s="671" t="n"/>
+      <c r="Q19" s="671" t="n"/>
+      <c r="R19" s="671" t="n"/>
+      <c r="S19" s="671" t="n"/>
+      <c r="T19" s="671" t="n"/>
+      <c r="U19" s="671" t="n"/>
+      <c r="V19" s="671" t="n"/>
+      <c r="W19" s="671" t="n"/>
+      <c r="X19" s="671" t="n"/>
+      <c r="Y19" s="671" t="n"/>
+      <c r="Z19" s="671" t="n"/>
+      <c r="AA19" s="671" t="n"/>
+      <c r="AB19" s="671" t="n"/>
+      <c r="AC19" s="671" t="n"/>
+      <c r="AD19" s="671" t="n"/>
+      <c r="AE19" s="671" t="n"/>
+      <c r="AF19" s="671" t="n"/>
+      <c r="AG19" s="671" t="n"/>
+      <c r="AH19" s="671" t="n"/>
+      <c r="AI19" s="671" t="n"/>
+      <c r="AJ19" s="671" t="n"/>
+      <c r="AK19" s="671" t="n"/>
+      <c r="AL19" s="671" t="n"/>
+      <c r="AM19" s="671" t="n"/>
+      <c r="AN19" s="671" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="671" t="n"/>
+      <c r="B20" s="671" t="n"/>
+      <c r="C20" s="671" t="n"/>
+      <c r="D20" s="671" t="n"/>
+      <c r="E20" s="671" t="n"/>
+      <c r="F20" s="671" t="n"/>
+      <c r="G20" s="671" t="n"/>
+      <c r="H20" s="671" t="n"/>
+      <c r="I20" s="671" t="n"/>
+      <c r="J20" s="671" t="n"/>
+      <c r="K20" s="671" t="n"/>
+      <c r="L20" s="671" t="n"/>
+      <c r="M20" s="671" t="n"/>
+      <c r="N20" s="671" t="n"/>
+      <c r="O20" s="671" t="n"/>
+      <c r="P20" s="671" t="n"/>
+      <c r="Q20" s="671" t="n"/>
+      <c r="R20" s="671" t="n"/>
+      <c r="S20" s="671" t="n"/>
+      <c r="T20" s="671" t="n"/>
+      <c r="U20" s="671" t="n"/>
+      <c r="V20" s="671" t="n"/>
+      <c r="W20" s="671" t="n"/>
+      <c r="X20" s="671" t="n"/>
+      <c r="Y20" s="671" t="n"/>
+      <c r="Z20" s="671" t="n"/>
+      <c r="AA20" s="671" t="n"/>
+      <c r="AB20" s="671" t="n"/>
+      <c r="AC20" s="671" t="n"/>
+      <c r="AD20" s="671" t="n"/>
+      <c r="AE20" s="671" t="n"/>
+      <c r="AF20" s="671" t="n"/>
+      <c r="AG20" s="671" t="n"/>
+      <c r="AH20" s="671" t="n"/>
+      <c r="AI20" s="671" t="n"/>
+      <c r="AJ20" s="671" t="n"/>
+      <c r="AK20" s="671" t="n"/>
+      <c r="AL20" s="671" t="n"/>
+      <c r="AM20" s="671" t="n"/>
+      <c r="AN20" s="671" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D5:D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
-      <formula1>'LISTS'!$A$2:$A$5</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11055,805 +11025,1346 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="510" t="inlineStr">
-        <is>
-          <t>Upstream References / Import Guidance</t>
-        </is>
-      </c>
+    <row r="1" hidden="1">
+      <c r="A1" s="711" t="n"/>
       <c r="B1" s="599" t="n"/>
       <c r="C1" s="599" t="n"/>
       <c r="D1" s="599" t="n"/>
       <c r="E1" s="599" t="n"/>
       <c r="F1" s="599" t="n"/>
       <c r="G1" s="599" t="n"/>
-      <c r="H1" s="511" t="n"/>
-      <c r="I1" s="428" t="n"/>
-      <c r="J1" s="429" t="n"/>
-      <c r="K1" s="429" t="n"/>
-      <c r="L1" s="429" t="n"/>
-      <c r="M1" s="429" t="n"/>
-      <c r="N1" s="429" t="n"/>
-      <c r="O1" s="429" t="n"/>
-      <c r="P1" s="429" t="n"/>
-      <c r="Q1" s="429" t="n"/>
-      <c r="R1" s="429" t="n"/>
-      <c r="S1" s="429" t="n"/>
-      <c r="T1" s="429" t="n"/>
-      <c r="U1" s="429" t="n"/>
-      <c r="V1" s="429" t="n"/>
-      <c r="W1" s="429" t="n"/>
-      <c r="X1" s="429" t="n"/>
-      <c r="Y1" s="429" t="n"/>
-      <c r="Z1" s="429" t="n"/>
-      <c r="AA1" s="429" t="n"/>
-      <c r="AB1" s="429" t="n"/>
-      <c r="AC1" s="429" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="431" t="n"/>
-      <c r="AF1" s="432" t="n"/>
-      <c r="AG1" s="432" t="n"/>
-      <c r="AH1" s="433" t="n"/>
-      <c r="AI1" s="434" t="n"/>
-      <c r="AJ1" s="435" t="n"/>
-      <c r="AK1" s="435" t="n"/>
-      <c r="AL1" s="435" t="n"/>
-      <c r="AM1" s="435" t="n"/>
-      <c r="AN1" s="436" t="n"/>
+      <c r="H1" s="712" t="n"/>
+      <c r="I1" s="713" t="inlineStr">
+        <is>
+          <t>Final Inspection Report</t>
+        </is>
+      </c>
+      <c r="J1" s="599" t="n"/>
+      <c r="K1" s="599" t="n"/>
+      <c r="L1" s="599" t="n"/>
+      <c r="M1" s="599" t="n"/>
+      <c r="N1" s="599" t="n"/>
+      <c r="O1" s="599" t="n"/>
+      <c r="P1" s="599" t="n"/>
+      <c r="Q1" s="599" t="n"/>
+      <c r="R1" s="599" t="n"/>
+      <c r="S1" s="599" t="n"/>
+      <c r="T1" s="599" t="n"/>
+      <c r="U1" s="599" t="n"/>
+      <c r="V1" s="599" t="n"/>
+      <c r="W1" s="599" t="n"/>
+      <c r="X1" s="599" t="n"/>
+      <c r="Y1" s="599" t="n"/>
+      <c r="Z1" s="599" t="n"/>
+      <c r="AA1" s="599" t="n"/>
+      <c r="AB1" s="599" t="n"/>
+      <c r="AC1" s="599" t="n"/>
+      <c r="AD1" s="712" t="n"/>
+      <c r="AE1" s="433" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="599" t="n"/>
+      <c r="AG1" s="599" t="n"/>
+      <c r="AH1" s="714" t="n"/>
+      <c r="AI1" s="436" t="inlineStr">
+        <is>
+          <t>FRM-641</t>
+        </is>
+      </c>
+      <c r="AJ1" s="599" t="n"/>
+      <c r="AK1" s="599" t="n"/>
+      <c r="AL1" s="599" t="n"/>
+      <c r="AM1" s="599" t="n"/>
+      <c r="AN1" s="712" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="512" t="inlineStr">
-        <is>
-          <t>Reference plan / lot / method / release documents from their owning source.</t>
-        </is>
-      </c>
-      <c r="H2" s="513" t="n"/>
-      <c r="I2" s="439" t="n"/>
-      <c r="J2" s="440" t="n"/>
-      <c r="K2" s="440" t="n"/>
-      <c r="L2" s="440" t="n"/>
-      <c r="M2" s="440" t="n"/>
-      <c r="N2" s="440" t="n"/>
-      <c r="O2" s="440" t="n"/>
-      <c r="P2" s="440" t="n"/>
-      <c r="Q2" s="440" t="n"/>
-      <c r="R2" s="440" t="n"/>
-      <c r="S2" s="440" t="n"/>
-      <c r="T2" s="440" t="n"/>
-      <c r="U2" s="440" t="n"/>
-      <c r="V2" s="440" t="n"/>
-      <c r="W2" s="440" t="n"/>
-      <c r="X2" s="440" t="n"/>
-      <c r="Y2" s="440" t="n"/>
-      <c r="Z2" s="440" t="n"/>
-      <c r="AA2" s="440" t="n"/>
-      <c r="AB2" s="440" t="n"/>
-      <c r="AC2" s="440" t="n"/>
-      <c r="AD2" s="441" t="n"/>
-      <c r="AE2" s="442" t="n"/>
-      <c r="AF2" s="443" t="n"/>
-      <c r="AG2" s="443" t="n"/>
-      <c r="AH2" s="444" t="n"/>
-      <c r="AI2" s="445" t="n"/>
-      <c r="AJ2" s="446" t="n"/>
-      <c r="AK2" s="446" t="n"/>
-      <c r="AL2" s="446" t="n"/>
-      <c r="AM2" s="446" t="n"/>
-      <c r="AN2" s="447" t="n"/>
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="684" t="n"/>
+      <c r="C2" s="684" t="n"/>
+      <c r="D2" s="684" t="n"/>
+      <c r="E2" s="684" t="n"/>
+      <c r="F2" s="684" t="n"/>
+      <c r="G2" s="684" t="n"/>
+      <c r="H2" s="685" t="n"/>
+      <c r="I2" s="684" t="n"/>
+      <c r="J2" s="684" t="n"/>
+      <c r="K2" s="684" t="n"/>
+      <c r="L2" s="684" t="n"/>
+      <c r="M2" s="684" t="n"/>
+      <c r="N2" s="684" t="n"/>
+      <c r="O2" s="684" t="n"/>
+      <c r="P2" s="684" t="n"/>
+      <c r="Q2" s="684" t="n"/>
+      <c r="R2" s="684" t="n"/>
+      <c r="S2" s="684" t="n"/>
+      <c r="T2" s="684" t="n"/>
+      <c r="U2" s="684" t="n"/>
+      <c r="V2" s="684" t="n"/>
+      <c r="W2" s="684" t="n"/>
+      <c r="X2" s="684" t="n"/>
+      <c r="Y2" s="684" t="n"/>
+      <c r="Z2" s="684" t="n"/>
+      <c r="AA2" s="684" t="n"/>
+      <c r="AB2" s="684" t="n"/>
+      <c r="AC2" s="684" t="n"/>
+      <c r="AD2" s="685" t="n"/>
+      <c r="AE2" s="686" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="687" t="n"/>
+      <c r="AG2" s="687" t="n"/>
+      <c r="AH2" s="688" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="689" t="n"/>
+      <c r="AK2" s="689" t="n"/>
+      <c r="AL2" s="689" t="n"/>
+      <c r="AM2" s="689" t="n"/>
+      <c r="AN2" s="690" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="514" t="n"/>
-      <c r="B3" s="515" t="n"/>
-      <c r="C3" s="515" t="n"/>
-      <c r="D3" s="515" t="n"/>
-      <c r="E3" s="515" t="n"/>
-      <c r="F3" s="515" t="n"/>
-      <c r="G3" s="515" t="n"/>
-      <c r="H3" s="513" t="n"/>
-      <c r="I3" s="439" t="n"/>
-      <c r="J3" s="440" t="n"/>
-      <c r="K3" s="440" t="n"/>
-      <c r="L3" s="440" t="n"/>
-      <c r="M3" s="440" t="n"/>
-      <c r="N3" s="440" t="n"/>
-      <c r="O3" s="440" t="n"/>
-      <c r="P3" s="440" t="n"/>
-      <c r="Q3" s="440" t="n"/>
-      <c r="R3" s="440" t="n"/>
-      <c r="S3" s="440" t="n"/>
-      <c r="T3" s="440" t="n"/>
-      <c r="U3" s="440" t="n"/>
-      <c r="V3" s="440" t="n"/>
-      <c r="W3" s="440" t="n"/>
-      <c r="X3" s="440" t="n"/>
-      <c r="Y3" s="440" t="n"/>
-      <c r="Z3" s="440" t="n"/>
-      <c r="AA3" s="440" t="n"/>
-      <c r="AB3" s="440" t="n"/>
-      <c r="AC3" s="440" t="n"/>
-      <c r="AD3" s="441" t="n"/>
-      <c r="AE3" s="442" t="n"/>
-      <c r="AF3" s="443" t="n"/>
-      <c r="AG3" s="443" t="n"/>
-      <c r="AH3" s="444" t="n"/>
-      <c r="AI3" s="445" t="n"/>
-      <c r="AJ3" s="446" t="n"/>
-      <c r="AK3" s="446" t="n"/>
-      <c r="AL3" s="446" t="n"/>
-      <c r="AM3" s="446" t="n"/>
-      <c r="AN3" s="447" t="n"/>
+      <c r="A3" s="691" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="692" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="692" t="n"/>
+      <c r="AE3" s="693" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="694" t="n"/>
+      <c r="AG3" s="694" t="n"/>
+      <c r="AH3" s="695" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="696" t="n"/>
+      <c r="AK3" s="696" t="n"/>
+      <c r="AL3" s="696" t="n"/>
+      <c r="AM3" s="696" t="n"/>
+      <c r="AN3" s="697" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="516" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="517" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="517" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="515" t="n"/>
-      <c r="E4" s="515" t="n"/>
-      <c r="F4" s="515" t="n"/>
-      <c r="G4" s="515" t="n"/>
-      <c r="H4" s="513" t="n"/>
-      <c r="I4" s="448" t="n"/>
-      <c r="J4" s="449" t="n"/>
-      <c r="K4" s="449" t="n"/>
-      <c r="L4" s="449" t="n"/>
-      <c r="M4" s="449" t="n"/>
-      <c r="N4" s="449" t="n"/>
-      <c r="O4" s="449" t="n"/>
-      <c r="P4" s="449" t="n"/>
-      <c r="Q4" s="449" t="n"/>
-      <c r="R4" s="449" t="n"/>
-      <c r="S4" s="449" t="n"/>
-      <c r="T4" s="449" t="n"/>
-      <c r="U4" s="449" t="n"/>
-      <c r="V4" s="449" t="n"/>
-      <c r="W4" s="449" t="n"/>
-      <c r="X4" s="449" t="n"/>
-      <c r="Y4" s="449" t="n"/>
-      <c r="Z4" s="449" t="n"/>
-      <c r="AA4" s="449" t="n"/>
-      <c r="AB4" s="449" t="n"/>
-      <c r="AC4" s="449" t="n"/>
-      <c r="AD4" s="450" t="n"/>
-      <c r="AE4" s="442" t="n"/>
-      <c r="AF4" s="443" t="n"/>
-      <c r="AG4" s="443" t="n"/>
-      <c r="AH4" s="444" t="n"/>
-      <c r="AI4" s="445" t="n"/>
-      <c r="AJ4" s="446" t="n"/>
-      <c r="AK4" s="446" t="n"/>
-      <c r="AL4" s="446" t="n"/>
-      <c r="AM4" s="446" t="n"/>
-      <c r="AN4" s="447" t="n"/>
+      <c r="A4" s="691" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="692" t="n"/>
+      <c r="I4" s="698" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="692" t="n"/>
+      <c r="AE4" s="693" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="694" t="n"/>
+      <c r="AG4" s="694" t="n"/>
+      <c r="AH4" s="695" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="696" t="n"/>
+      <c r="AK4" s="696" t="n"/>
+      <c r="AL4" s="696" t="n"/>
+      <c r="AM4" s="696" t="n"/>
+      <c r="AN4" s="697" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="518" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="519" t="inlineStr">
-        <is>
-          <t>Epicor transaction + M365 evidence</t>
-        </is>
-      </c>
-      <c r="C5" s="519" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="537" t="n"/>
-      <c r="E5" s="537" t="n"/>
-      <c r="F5" s="537" t="n"/>
-      <c r="G5" s="537" t="n"/>
-      <c r="H5" s="520" t="n"/>
-      <c r="I5" s="454" t="n"/>
-      <c r="J5" s="455" t="n"/>
-      <c r="K5" s="455" t="n"/>
-      <c r="L5" s="455" t="n"/>
-      <c r="M5" s="455" t="n"/>
-      <c r="N5" s="455" t="n"/>
-      <c r="O5" s="455" t="n"/>
-      <c r="P5" s="455" t="n"/>
-      <c r="Q5" s="455" t="n"/>
-      <c r="R5" s="455" t="n"/>
-      <c r="S5" s="455" t="n"/>
-      <c r="T5" s="455" t="n"/>
-      <c r="U5" s="455" t="n"/>
-      <c r="V5" s="455" t="n"/>
-      <c r="W5" s="455" t="n"/>
-      <c r="X5" s="455" t="n"/>
-      <c r="Y5" s="455" t="n"/>
-      <c r="Z5" s="455" t="n"/>
-      <c r="AA5" s="455" t="n"/>
-      <c r="AB5" s="455" t="n"/>
-      <c r="AC5" s="455" t="n"/>
-      <c r="AD5" s="456" t="n"/>
-      <c r="AE5" s="457" t="n"/>
-      <c r="AF5" s="458" t="n"/>
-      <c r="AG5" s="458" t="n"/>
-      <c r="AH5" s="459" t="n"/>
-      <c r="AI5" s="460" t="n"/>
-      <c r="AJ5" s="461" t="n"/>
-      <c r="AK5" s="461" t="n"/>
-      <c r="AL5" s="461" t="n"/>
-      <c r="AM5" s="461" t="n"/>
-      <c r="AN5" s="462" t="n"/>
+      <c r="A5" s="691" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="692" t="n"/>
+      <c r="I5" s="699" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="692" t="n"/>
+      <c r="AE5" s="693" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="694" t="n"/>
+      <c r="AG5" s="694" t="n"/>
+      <c r="AH5" s="695" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="696" t="n"/>
+      <c r="AK5" s="696" t="n"/>
+      <c r="AL5" s="696" t="n"/>
+      <c r="AM5" s="696" t="n"/>
+      <c r="AN5" s="697" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="521" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="522" t="inlineStr">
-        <is>
-          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
-        </is>
-      </c>
-      <c r="C6" s="523" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-605; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-605; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="468" t="n"/>
-      <c r="E6" s="468" t="n"/>
-      <c r="F6" s="468" t="n"/>
-      <c r="G6" s="468" t="n"/>
-      <c r="H6" s="468" t="n"/>
-      <c r="I6" s="468" t="n"/>
-      <c r="J6" s="468" t="n"/>
-      <c r="K6" s="468" t="n"/>
-      <c r="L6" s="468" t="n"/>
-      <c r="M6" s="468" t="n"/>
-      <c r="N6" s="468" t="n"/>
-      <c r="O6" s="468" t="n"/>
-      <c r="P6" s="468" t="n"/>
-      <c r="Q6" s="468" t="n"/>
-      <c r="R6" s="468" t="n"/>
-      <c r="S6" s="468" t="n"/>
-      <c r="T6" s="468" t="n"/>
-      <c r="U6" s="468" t="n"/>
-      <c r="V6" s="468" t="n"/>
-      <c r="W6" s="468" t="n"/>
-      <c r="X6" s="468" t="n"/>
-      <c r="Y6" s="468" t="n"/>
-      <c r="Z6" s="468" t="n"/>
-      <c r="AA6" s="468" t="n"/>
-      <c r="AB6" s="468" t="n"/>
-      <c r="AC6" s="468" t="n"/>
-      <c r="AD6" s="468" t="n"/>
-      <c r="AE6" s="468" t="n"/>
-      <c r="AF6" s="468" t="n"/>
-      <c r="AG6" s="468" t="n"/>
-      <c r="AH6" s="468" t="n"/>
-      <c r="AI6" s="468" t="n"/>
-      <c r="AJ6" s="468" t="n"/>
-      <c r="AK6" s="468" t="n"/>
-      <c r="AL6" s="468" t="n"/>
-      <c r="AM6" s="468" t="n"/>
-      <c r="AN6" s="500" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="715" t="n"/>
+      <c r="B6" s="724" t="n"/>
+      <c r="C6" s="724" t="n"/>
+      <c r="D6" s="724" t="n"/>
+      <c r="E6" s="724" t="n"/>
+      <c r="F6" s="724" t="n"/>
+      <c r="G6" s="724" t="n"/>
+      <c r="H6" s="717" t="n"/>
+      <c r="I6" s="716" t="n"/>
+      <c r="J6" s="716" t="n"/>
+      <c r="K6" s="716" t="n"/>
+      <c r="L6" s="716" t="n"/>
+      <c r="M6" s="716" t="n"/>
+      <c r="N6" s="716" t="n"/>
+      <c r="O6" s="716" t="n"/>
+      <c r="P6" s="716" t="n"/>
+      <c r="Q6" s="716" t="n"/>
+      <c r="R6" s="716" t="n"/>
+      <c r="S6" s="716" t="n"/>
+      <c r="T6" s="716" t="n"/>
+      <c r="U6" s="716" t="n"/>
+      <c r="V6" s="716" t="n"/>
+      <c r="W6" s="716" t="n"/>
+      <c r="X6" s="716" t="n"/>
+      <c r="Y6" s="716" t="n"/>
+      <c r="Z6" s="716" t="n"/>
+      <c r="AA6" s="716" t="n"/>
+      <c r="AB6" s="716" t="n"/>
+      <c r="AC6" s="716" t="n"/>
+      <c r="AD6" s="717" t="n"/>
+      <c r="AE6" s="718" t="n"/>
+      <c r="AF6" s="718" t="n"/>
+      <c r="AG6" s="718" t="n"/>
+      <c r="AH6" s="719" t="n"/>
+      <c r="AI6" s="720" t="n"/>
+      <c r="AJ6" s="720" t="n"/>
+      <c r="AK6" s="720" t="n"/>
+      <c r="AL6" s="720" t="n"/>
+      <c r="AM6" s="720" t="n"/>
+      <c r="AN6" s="721" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="524" t="inlineStr">
-        <is>
-          <t>SOP SOP-605</t>
-        </is>
-      </c>
-      <c r="B7" s="525" t="inlineStr">
-        <is>
-          <t>SOP-605 — Kiểm tra cuối, CoC và phê duyệt giao hàng | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="526" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-605-final-inspection-coc-and-shipment-release.html</t>
-        </is>
-      </c>
-      <c r="D7" s="342" t="n"/>
-      <c r="E7" s="342" t="n"/>
-      <c r="F7" s="342" t="n"/>
-      <c r="G7" s="342" t="n"/>
-      <c r="H7" s="342" t="n"/>
-      <c r="I7" s="342" t="n"/>
-      <c r="J7" s="342" t="n"/>
-      <c r="K7" s="342" t="n"/>
-      <c r="L7" s="342" t="n"/>
-      <c r="M7" s="342" t="n"/>
-      <c r="N7" s="342" t="n"/>
-      <c r="O7" s="342" t="n"/>
-      <c r="P7" s="342" t="n"/>
-      <c r="Q7" s="342" t="n"/>
-      <c r="R7" s="342" t="n"/>
-      <c r="S7" s="342" t="n"/>
-      <c r="T7" s="342" t="n"/>
-      <c r="U7" s="342" t="n"/>
-      <c r="V7" s="342" t="n"/>
-      <c r="W7" s="342" t="n"/>
-      <c r="X7" s="342" t="n"/>
-      <c r="Y7" s="342" t="n"/>
-      <c r="Z7" s="342" t="n"/>
-      <c r="AA7" s="342" t="n"/>
-      <c r="AB7" s="342" t="n"/>
-      <c r="AC7" s="342" t="n"/>
-      <c r="AD7" s="342" t="n"/>
-      <c r="AE7" s="342" t="n"/>
-      <c r="AF7" s="342" t="n"/>
-      <c r="AG7" s="342" t="n"/>
-      <c r="AH7" s="342" t="n"/>
-      <c r="AI7" s="342" t="n"/>
-      <c r="AJ7" s="342" t="n"/>
-      <c r="AK7" s="342" t="n"/>
-      <c r="AL7" s="342" t="n"/>
-      <c r="AM7" s="342" t="n"/>
-      <c r="AN7" s="527" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="725" t="n"/>
+      <c r="B7" s="708" t="n"/>
+      <c r="C7" s="708" t="n"/>
+      <c r="D7" s="708" t="n"/>
+      <c r="E7" s="708" t="n"/>
+      <c r="F7" s="708" t="n"/>
+      <c r="G7" s="708" t="n"/>
+      <c r="H7" s="723" t="n"/>
+      <c r="I7" s="723" t="n"/>
+      <c r="J7" s="723" t="n"/>
+      <c r="K7" s="723" t="n"/>
+      <c r="L7" s="723" t="n"/>
+      <c r="M7" s="723" t="n"/>
+      <c r="N7" s="723" t="n"/>
+      <c r="O7" s="723" t="n"/>
+      <c r="P7" s="723" t="n"/>
+      <c r="Q7" s="723" t="n"/>
+      <c r="R7" s="723" t="n"/>
+      <c r="S7" s="723" t="n"/>
+      <c r="T7" s="723" t="n"/>
+      <c r="U7" s="723" t="n"/>
+      <c r="V7" s="723" t="n"/>
+      <c r="W7" s="723" t="n"/>
+      <c r="X7" s="723" t="n"/>
+      <c r="Y7" s="723" t="n"/>
+      <c r="Z7" s="723" t="n"/>
+      <c r="AA7" s="723" t="n"/>
+      <c r="AB7" s="723" t="n"/>
+      <c r="AC7" s="723" t="n"/>
+      <c r="AD7" s="723" t="n"/>
+      <c r="AE7" s="723" t="n"/>
+      <c r="AF7" s="723" t="n"/>
+      <c r="AG7" s="723" t="n"/>
+      <c r="AH7" s="723" t="n"/>
+      <c r="AI7" s="723" t="n"/>
+      <c r="AJ7" s="723" t="n"/>
+      <c r="AK7" s="723" t="n"/>
+      <c r="AL7" s="723" t="n"/>
+      <c r="AM7" s="723" t="n"/>
+      <c r="AN7" s="723" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="528" t="inlineStr">
-        <is>
-          <t>WI WI-605</t>
-        </is>
-      </c>
-      <c r="B8" s="529" t="inlineStr">
-        <is>
-          <t>WI-605 — Kiểm cuối, CoC/CofC, bàn giao phát hành giao hàng</t>
-        </is>
-      </c>
-      <c r="C8" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-605-final-inspection-coc-and-shipment-release-handoff.html</t>
-        </is>
-      </c>
-      <c r="D8" s="354" t="n"/>
-      <c r="E8" s="354" t="n"/>
-      <c r="F8" s="354" t="n"/>
-      <c r="G8" s="354" t="n"/>
-      <c r="H8" s="354" t="n"/>
-      <c r="I8" s="354" t="n"/>
-      <c r="J8" s="354" t="n"/>
-      <c r="K8" s="354" t="n"/>
-      <c r="L8" s="354" t="n"/>
-      <c r="M8" s="354" t="n"/>
-      <c r="N8" s="354" t="n"/>
-      <c r="O8" s="354" t="n"/>
-      <c r="P8" s="354" t="n"/>
-      <c r="Q8" s="354" t="n"/>
-      <c r="R8" s="354" t="n"/>
-      <c r="S8" s="354" t="n"/>
-      <c r="T8" s="354" t="n"/>
-      <c r="U8" s="354" t="n"/>
-      <c r="V8" s="354" t="n"/>
-      <c r="W8" s="354" t="n"/>
-      <c r="X8" s="354" t="n"/>
-      <c r="Y8" s="354" t="n"/>
-      <c r="Z8" s="354" t="n"/>
-      <c r="AA8" s="354" t="n"/>
-      <c r="AB8" s="354" t="n"/>
-      <c r="AC8" s="354" t="n"/>
-      <c r="AD8" s="354" t="n"/>
-      <c r="AE8" s="354" t="n"/>
-      <c r="AF8" s="354" t="n"/>
-      <c r="AG8" s="354" t="n"/>
-      <c r="AH8" s="354" t="n"/>
-      <c r="AI8" s="354" t="n"/>
-      <c r="AJ8" s="354" t="n"/>
-      <c r="AK8" s="354" t="n"/>
-      <c r="AL8" s="354" t="n"/>
-      <c r="AM8" s="354" t="n"/>
-      <c r="AN8" s="531" t="n"/>
+      <c r="A8" s="726" t="inlineStr">
+        <is>
+          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
+        </is>
+      </c>
+      <c r="H8" s="671" t="n"/>
+      <c r="I8" s="671" t="n"/>
+      <c r="J8" s="671" t="n"/>
+      <c r="K8" s="671" t="n"/>
+      <c r="L8" s="671" t="n"/>
+      <c r="M8" s="671" t="n"/>
+      <c r="N8" s="671" t="n"/>
+      <c r="O8" s="671" t="n"/>
+      <c r="P8" s="671" t="n"/>
+      <c r="Q8" s="671" t="n"/>
+      <c r="R8" s="671" t="n"/>
+      <c r="S8" s="671" t="n"/>
+      <c r="T8" s="671" t="n"/>
+      <c r="U8" s="671" t="n"/>
+      <c r="V8" s="671" t="n"/>
+      <c r="W8" s="671" t="n"/>
+      <c r="X8" s="671" t="n"/>
+      <c r="Y8" s="671" t="n"/>
+      <c r="Z8" s="671" t="n"/>
+      <c r="AA8" s="671" t="n"/>
+      <c r="AB8" s="671" t="n"/>
+      <c r="AC8" s="671" t="n"/>
+      <c r="AD8" s="671" t="n"/>
+      <c r="AE8" s="671" t="n"/>
+      <c r="AF8" s="671" t="n"/>
+      <c r="AG8" s="671" t="n"/>
+      <c r="AH8" s="671" t="n"/>
+      <c r="AI8" s="671" t="n"/>
+      <c r="AJ8" s="671" t="n"/>
+      <c r="AK8" s="671" t="n"/>
+      <c r="AL8" s="671" t="n"/>
+      <c r="AM8" s="671" t="n"/>
+      <c r="AN8" s="671" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="528" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-001</t>
-        </is>
-      </c>
-      <c r="B9" s="529" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
-        </is>
-      </c>
-      <c r="C9" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
-        </is>
-      </c>
-      <c r="D9" s="354" t="n"/>
-      <c r="E9" s="354" t="n"/>
-      <c r="F9" s="354" t="n"/>
-      <c r="G9" s="354" t="n"/>
-      <c r="H9" s="354" t="n"/>
-      <c r="I9" s="354" t="n"/>
-      <c r="J9" s="354" t="n"/>
-      <c r="K9" s="354" t="n"/>
-      <c r="L9" s="354" t="n"/>
-      <c r="M9" s="354" t="n"/>
-      <c r="N9" s="354" t="n"/>
-      <c r="O9" s="354" t="n"/>
-      <c r="P9" s="354" t="n"/>
-      <c r="Q9" s="354" t="n"/>
-      <c r="R9" s="354" t="n"/>
-      <c r="S9" s="354" t="n"/>
-      <c r="T9" s="354" t="n"/>
-      <c r="U9" s="354" t="n"/>
-      <c r="V9" s="354" t="n"/>
-      <c r="W9" s="354" t="n"/>
-      <c r="X9" s="354" t="n"/>
-      <c r="Y9" s="354" t="n"/>
-      <c r="Z9" s="354" t="n"/>
-      <c r="AA9" s="354" t="n"/>
-      <c r="AB9" s="354" t="n"/>
-      <c r="AC9" s="354" t="n"/>
-      <c r="AD9" s="354" t="n"/>
-      <c r="AE9" s="354" t="n"/>
-      <c r="AF9" s="354" t="n"/>
-      <c r="AG9" s="354" t="n"/>
-      <c r="AH9" s="354" t="n"/>
-      <c r="AI9" s="354" t="n"/>
-      <c r="AJ9" s="354" t="n"/>
-      <c r="AK9" s="354" t="n"/>
-      <c r="AL9" s="354" t="n"/>
-      <c r="AM9" s="354" t="n"/>
-      <c r="AN9" s="531" t="n"/>
+      <c r="A9" s="671" t="n"/>
+      <c r="B9" s="673" t="n"/>
+      <c r="C9" s="673" t="n"/>
+      <c r="D9" s="673" t="n"/>
+      <c r="E9" s="673" t="n"/>
+      <c r="F9" s="673" t="n"/>
+      <c r="G9" s="673" t="n"/>
+      <c r="H9" s="671" t="n"/>
+      <c r="I9" s="671" t="n"/>
+      <c r="J9" s="671" t="n"/>
+      <c r="K9" s="671" t="n"/>
+      <c r="L9" s="671" t="n"/>
+      <c r="M9" s="671" t="n"/>
+      <c r="N9" s="671" t="n"/>
+      <c r="O9" s="671" t="n"/>
+      <c r="P9" s="671" t="n"/>
+      <c r="Q9" s="671" t="n"/>
+      <c r="R9" s="671" t="n"/>
+      <c r="S9" s="671" t="n"/>
+      <c r="T9" s="671" t="n"/>
+      <c r="U9" s="671" t="n"/>
+      <c r="V9" s="671" t="n"/>
+      <c r="W9" s="671" t="n"/>
+      <c r="X9" s="671" t="n"/>
+      <c r="Y9" s="671" t="n"/>
+      <c r="Z9" s="671" t="n"/>
+      <c r="AA9" s="671" t="n"/>
+      <c r="AB9" s="671" t="n"/>
+      <c r="AC9" s="671" t="n"/>
+      <c r="AD9" s="671" t="n"/>
+      <c r="AE9" s="671" t="n"/>
+      <c r="AF9" s="671" t="n"/>
+      <c r="AG9" s="671" t="n"/>
+      <c r="AH9" s="671" t="n"/>
+      <c r="AI9" s="671" t="n"/>
+      <c r="AJ9" s="671" t="n"/>
+      <c r="AK9" s="671" t="n"/>
+      <c r="AL9" s="671" t="n"/>
+      <c r="AM9" s="671" t="n"/>
+      <c r="AN9" s="671" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="528" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-002</t>
-        </is>
-      </c>
-      <c r="B10" s="529" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
-        </is>
-      </c>
-      <c r="C10" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
-        </is>
-      </c>
-      <c r="D10" s="354" t="n"/>
-      <c r="E10" s="354" t="n"/>
-      <c r="F10" s="354" t="n"/>
-      <c r="G10" s="354" t="n"/>
-      <c r="H10" s="354" t="n"/>
-      <c r="I10" s="354" t="n"/>
-      <c r="J10" s="354" t="n"/>
-      <c r="K10" s="354" t="n"/>
-      <c r="L10" s="354" t="n"/>
-      <c r="M10" s="354" t="n"/>
-      <c r="N10" s="354" t="n"/>
-      <c r="O10" s="354" t="n"/>
-      <c r="P10" s="354" t="n"/>
-      <c r="Q10" s="354" t="n"/>
-      <c r="R10" s="354" t="n"/>
-      <c r="S10" s="354" t="n"/>
-      <c r="T10" s="354" t="n"/>
-      <c r="U10" s="354" t="n"/>
-      <c r="V10" s="354" t="n"/>
-      <c r="W10" s="354" t="n"/>
-      <c r="X10" s="354" t="n"/>
-      <c r="Y10" s="354" t="n"/>
-      <c r="Z10" s="354" t="n"/>
-      <c r="AA10" s="354" t="n"/>
-      <c r="AB10" s="354" t="n"/>
-      <c r="AC10" s="354" t="n"/>
-      <c r="AD10" s="354" t="n"/>
-      <c r="AE10" s="354" t="n"/>
-      <c r="AF10" s="354" t="n"/>
-      <c r="AG10" s="354" t="n"/>
-      <c r="AH10" s="354" t="n"/>
-      <c r="AI10" s="354" t="n"/>
-      <c r="AJ10" s="354" t="n"/>
-      <c r="AK10" s="354" t="n"/>
-      <c r="AL10" s="354" t="n"/>
-      <c r="AM10" s="354" t="n"/>
-      <c r="AN10" s="531" t="n"/>
+      <c r="A10" s="727" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B10" s="674" t="inlineStr">
+        <is>
+          <t>Requirement / Characteristic</t>
+        </is>
+      </c>
+      <c r="C10" s="674" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D10" s="674" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E10" s="674" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+      <c r="F10" s="674" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G10" s="674" t="inlineStr">
+        <is>
+          <t>Evidence Ref</t>
+        </is>
+      </c>
+      <c r="H10" s="671" t="n"/>
+      <c r="I10" s="671" t="n"/>
+      <c r="J10" s="671" t="n"/>
+      <c r="K10" s="671" t="n"/>
+      <c r="L10" s="671" t="n"/>
+      <c r="M10" s="671" t="n"/>
+      <c r="N10" s="671" t="n"/>
+      <c r="O10" s="671" t="n"/>
+      <c r="P10" s="671" t="n"/>
+      <c r="Q10" s="671" t="n"/>
+      <c r="R10" s="671" t="n"/>
+      <c r="S10" s="671" t="n"/>
+      <c r="T10" s="671" t="n"/>
+      <c r="U10" s="671" t="n"/>
+      <c r="V10" s="671" t="n"/>
+      <c r="W10" s="671" t="n"/>
+      <c r="X10" s="671" t="n"/>
+      <c r="Y10" s="671" t="n"/>
+      <c r="Z10" s="671" t="n"/>
+      <c r="AA10" s="671" t="n"/>
+      <c r="AB10" s="671" t="n"/>
+      <c r="AC10" s="671" t="n"/>
+      <c r="AD10" s="671" t="n"/>
+      <c r="AE10" s="671" t="n"/>
+      <c r="AF10" s="671" t="n"/>
+      <c r="AG10" s="671" t="n"/>
+      <c r="AH10" s="671" t="n"/>
+      <c r="AI10" s="671" t="n"/>
+      <c r="AJ10" s="671" t="n"/>
+      <c r="AK10" s="671" t="n"/>
+      <c r="AL10" s="671" t="n"/>
+      <c r="AM10" s="671" t="n"/>
+      <c r="AN10" s="671" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="528" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-003</t>
-        </is>
-      </c>
-      <c r="B11" s="529" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
-        </is>
-      </c>
-      <c r="C11" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
-        </is>
-      </c>
-      <c r="D11" s="354" t="n"/>
-      <c r="E11" s="354" t="n"/>
-      <c r="F11" s="354" t="n"/>
-      <c r="G11" s="354" t="n"/>
-      <c r="H11" s="354" t="n"/>
-      <c r="I11" s="354" t="n"/>
-      <c r="J11" s="354" t="n"/>
-      <c r="K11" s="354" t="n"/>
-      <c r="L11" s="354" t="n"/>
-      <c r="M11" s="354" t="n"/>
-      <c r="N11" s="354" t="n"/>
-      <c r="O11" s="354" t="n"/>
-      <c r="P11" s="354" t="n"/>
-      <c r="Q11" s="354" t="n"/>
-      <c r="R11" s="354" t="n"/>
-      <c r="S11" s="354" t="n"/>
-      <c r="T11" s="354" t="n"/>
-      <c r="U11" s="354" t="n"/>
-      <c r="V11" s="354" t="n"/>
-      <c r="W11" s="354" t="n"/>
-      <c r="X11" s="354" t="n"/>
-      <c r="Y11" s="354" t="n"/>
-      <c r="Z11" s="354" t="n"/>
-      <c r="AA11" s="354" t="n"/>
-      <c r="AB11" s="354" t="n"/>
-      <c r="AC11" s="354" t="n"/>
-      <c r="AD11" s="354" t="n"/>
-      <c r="AE11" s="354" t="n"/>
-      <c r="AF11" s="354" t="n"/>
-      <c r="AG11" s="354" t="n"/>
-      <c r="AH11" s="354" t="n"/>
-      <c r="AI11" s="354" t="n"/>
-      <c r="AJ11" s="354" t="n"/>
-      <c r="AK11" s="354" t="n"/>
-      <c r="AL11" s="354" t="n"/>
-      <c r="AM11" s="354" t="n"/>
-      <c r="AN11" s="531" t="n"/>
+      <c r="A11" s="728">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B11" s="673" t="n"/>
+      <c r="C11" s="673" t="n"/>
+      <c r="D11" s="673" t="n"/>
+      <c r="E11" s="673" t="n"/>
+      <c r="F11" s="673" t="n"/>
+      <c r="G11" s="673" t="n"/>
+      <c r="H11" s="671" t="n"/>
+      <c r="I11" s="671" t="n"/>
+      <c r="J11" s="671" t="n"/>
+      <c r="K11" s="671" t="n"/>
+      <c r="L11" s="671" t="n"/>
+      <c r="M11" s="671" t="n"/>
+      <c r="N11" s="671" t="n"/>
+      <c r="O11" s="671" t="n"/>
+      <c r="P11" s="671" t="n"/>
+      <c r="Q11" s="671" t="n"/>
+      <c r="R11" s="671" t="n"/>
+      <c r="S11" s="671" t="n"/>
+      <c r="T11" s="671" t="n"/>
+      <c r="U11" s="671" t="n"/>
+      <c r="V11" s="671" t="n"/>
+      <c r="W11" s="671" t="n"/>
+      <c r="X11" s="671" t="n"/>
+      <c r="Y11" s="671" t="n"/>
+      <c r="Z11" s="671" t="n"/>
+      <c r="AA11" s="671" t="n"/>
+      <c r="AB11" s="671" t="n"/>
+      <c r="AC11" s="671" t="n"/>
+      <c r="AD11" s="671" t="n"/>
+      <c r="AE11" s="671" t="n"/>
+      <c r="AF11" s="671" t="n"/>
+      <c r="AG11" s="671" t="n"/>
+      <c r="AH11" s="671" t="n"/>
+      <c r="AI11" s="671" t="n"/>
+      <c r="AJ11" s="671" t="n"/>
+      <c r="AK11" s="671" t="n"/>
+      <c r="AL11" s="671" t="n"/>
+      <c r="AM11" s="671" t="n"/>
+      <c r="AN11" s="671" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="528" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-004</t>
-        </is>
-      </c>
-      <c r="B12" s="529" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
-        </is>
-      </c>
-      <c r="C12" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
-        </is>
-      </c>
-      <c r="D12" s="354" t="n"/>
-      <c r="E12" s="354" t="n"/>
-      <c r="F12" s="354" t="n"/>
-      <c r="G12" s="354" t="n"/>
-      <c r="H12" s="354" t="n"/>
-      <c r="I12" s="354" t="n"/>
-      <c r="J12" s="354" t="n"/>
-      <c r="K12" s="354" t="n"/>
-      <c r="L12" s="354" t="n"/>
-      <c r="M12" s="354" t="n"/>
-      <c r="N12" s="354" t="n"/>
-      <c r="O12" s="354" t="n"/>
-      <c r="P12" s="354" t="n"/>
-      <c r="Q12" s="354" t="n"/>
-      <c r="R12" s="354" t="n"/>
-      <c r="S12" s="354" t="n"/>
-      <c r="T12" s="354" t="n"/>
-      <c r="U12" s="354" t="n"/>
-      <c r="V12" s="354" t="n"/>
-      <c r="W12" s="354" t="n"/>
-      <c r="X12" s="354" t="n"/>
-      <c r="Y12" s="354" t="n"/>
-      <c r="Z12" s="354" t="n"/>
-      <c r="AA12" s="354" t="n"/>
-      <c r="AB12" s="354" t="n"/>
-      <c r="AC12" s="354" t="n"/>
-      <c r="AD12" s="354" t="n"/>
-      <c r="AE12" s="354" t="n"/>
-      <c r="AF12" s="354" t="n"/>
-      <c r="AG12" s="354" t="n"/>
-      <c r="AH12" s="354" t="n"/>
-      <c r="AI12" s="354" t="n"/>
-      <c r="AJ12" s="354" t="n"/>
-      <c r="AK12" s="354" t="n"/>
-      <c r="AL12" s="354" t="n"/>
-      <c r="AM12" s="354" t="n"/>
-      <c r="AN12" s="531" t="n"/>
+      <c r="A12" s="729">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B12" s="673" t="n"/>
+      <c r="C12" s="673" t="n"/>
+      <c r="D12" s="673" t="n"/>
+      <c r="E12" s="673" t="n"/>
+      <c r="F12" s="673" t="n"/>
+      <c r="G12" s="673" t="n"/>
+      <c r="H12" s="671" t="n"/>
+      <c r="I12" s="671" t="n"/>
+      <c r="J12" s="671" t="n"/>
+      <c r="K12" s="671" t="n"/>
+      <c r="L12" s="671" t="n"/>
+      <c r="M12" s="671" t="n"/>
+      <c r="N12" s="671" t="n"/>
+      <c r="O12" s="671" t="n"/>
+      <c r="P12" s="671" t="n"/>
+      <c r="Q12" s="671" t="n"/>
+      <c r="R12" s="671" t="n"/>
+      <c r="S12" s="671" t="n"/>
+      <c r="T12" s="671" t="n"/>
+      <c r="U12" s="671" t="n"/>
+      <c r="V12" s="671" t="n"/>
+      <c r="W12" s="671" t="n"/>
+      <c r="X12" s="671" t="n"/>
+      <c r="Y12" s="671" t="n"/>
+      <c r="Z12" s="671" t="n"/>
+      <c r="AA12" s="671" t="n"/>
+      <c r="AB12" s="671" t="n"/>
+      <c r="AC12" s="671" t="n"/>
+      <c r="AD12" s="671" t="n"/>
+      <c r="AE12" s="671" t="n"/>
+      <c r="AF12" s="671" t="n"/>
+      <c r="AG12" s="671" t="n"/>
+      <c r="AH12" s="671" t="n"/>
+      <c r="AI12" s="671" t="n"/>
+      <c r="AJ12" s="671" t="n"/>
+      <c r="AK12" s="671" t="n"/>
+      <c r="AL12" s="671" t="n"/>
+      <c r="AM12" s="671" t="n"/>
+      <c r="AN12" s="671" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="528" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-006</t>
-        </is>
-      </c>
-      <c r="B13" s="529" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
-        </is>
-      </c>
-      <c r="C13" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
-        </is>
-      </c>
-      <c r="D13" s="354" t="n"/>
-      <c r="E13" s="354" t="n"/>
-      <c r="F13" s="354" t="n"/>
-      <c r="G13" s="354" t="n"/>
-      <c r="H13" s="354" t="n"/>
-      <c r="I13" s="354" t="n"/>
-      <c r="J13" s="354" t="n"/>
-      <c r="K13" s="354" t="n"/>
-      <c r="L13" s="354" t="n"/>
-      <c r="M13" s="354" t="n"/>
-      <c r="N13" s="354" t="n"/>
-      <c r="O13" s="354" t="n"/>
-      <c r="P13" s="354" t="n"/>
-      <c r="Q13" s="354" t="n"/>
-      <c r="R13" s="354" t="n"/>
-      <c r="S13" s="354" t="n"/>
-      <c r="T13" s="354" t="n"/>
-      <c r="U13" s="354" t="n"/>
-      <c r="V13" s="354" t="n"/>
-      <c r="W13" s="354" t="n"/>
-      <c r="X13" s="354" t="n"/>
-      <c r="Y13" s="354" t="n"/>
-      <c r="Z13" s="354" t="n"/>
-      <c r="AA13" s="354" t="n"/>
-      <c r="AB13" s="354" t="n"/>
-      <c r="AC13" s="354" t="n"/>
-      <c r="AD13" s="354" t="n"/>
-      <c r="AE13" s="354" t="n"/>
-      <c r="AF13" s="354" t="n"/>
-      <c r="AG13" s="354" t="n"/>
-      <c r="AH13" s="354" t="n"/>
-      <c r="AI13" s="354" t="n"/>
-      <c r="AJ13" s="354" t="n"/>
-      <c r="AK13" s="354" t="n"/>
-      <c r="AL13" s="354" t="n"/>
-      <c r="AM13" s="354" t="n"/>
-      <c r="AN13" s="531" t="n"/>
+      <c r="A13" s="730">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B13" s="673" t="n"/>
+      <c r="C13" s="673" t="n"/>
+      <c r="D13" s="673" t="n"/>
+      <c r="E13" s="673" t="n"/>
+      <c r="F13" s="673" t="n"/>
+      <c r="G13" s="673" t="n"/>
+      <c r="H13" s="671" t="n"/>
+      <c r="I13" s="671" t="n"/>
+      <c r="J13" s="671" t="n"/>
+      <c r="K13" s="671" t="n"/>
+      <c r="L13" s="671" t="n"/>
+      <c r="M13" s="671" t="n"/>
+      <c r="N13" s="671" t="n"/>
+      <c r="O13" s="671" t="n"/>
+      <c r="P13" s="671" t="n"/>
+      <c r="Q13" s="671" t="n"/>
+      <c r="R13" s="671" t="n"/>
+      <c r="S13" s="671" t="n"/>
+      <c r="T13" s="671" t="n"/>
+      <c r="U13" s="671" t="n"/>
+      <c r="V13" s="671" t="n"/>
+      <c r="W13" s="671" t="n"/>
+      <c r="X13" s="671" t="n"/>
+      <c r="Y13" s="671" t="n"/>
+      <c r="Z13" s="671" t="n"/>
+      <c r="AA13" s="671" t="n"/>
+      <c r="AB13" s="671" t="n"/>
+      <c r="AC13" s="671" t="n"/>
+      <c r="AD13" s="671" t="n"/>
+      <c r="AE13" s="671" t="n"/>
+      <c r="AF13" s="671" t="n"/>
+      <c r="AG13" s="671" t="n"/>
+      <c r="AH13" s="671" t="n"/>
+      <c r="AI13" s="671" t="n"/>
+      <c r="AJ13" s="671" t="n"/>
+      <c r="AK13" s="671" t="n"/>
+      <c r="AL13" s="671" t="n"/>
+      <c r="AM13" s="671" t="n"/>
+      <c r="AN13" s="671" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="528" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QA-007</t>
-        </is>
-      </c>
-      <c r="B14" s="529" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
-        </is>
-      </c>
-      <c r="C14" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
-        </is>
-      </c>
-      <c r="D14" s="354" t="n"/>
-      <c r="E14" s="354" t="n"/>
-      <c r="F14" s="354" t="n"/>
-      <c r="G14" s="354" t="n"/>
-      <c r="H14" s="354" t="n"/>
-      <c r="I14" s="354" t="n"/>
-      <c r="J14" s="354" t="n"/>
-      <c r="K14" s="354" t="n"/>
-      <c r="L14" s="354" t="n"/>
-      <c r="M14" s="354" t="n"/>
-      <c r="N14" s="354" t="n"/>
-      <c r="O14" s="354" t="n"/>
-      <c r="P14" s="354" t="n"/>
-      <c r="Q14" s="354" t="n"/>
-      <c r="R14" s="354" t="n"/>
-      <c r="S14" s="354" t="n"/>
-      <c r="T14" s="354" t="n"/>
-      <c r="U14" s="354" t="n"/>
-      <c r="V14" s="354" t="n"/>
-      <c r="W14" s="354" t="n"/>
-      <c r="X14" s="354" t="n"/>
-      <c r="Y14" s="354" t="n"/>
-      <c r="Z14" s="354" t="n"/>
-      <c r="AA14" s="354" t="n"/>
-      <c r="AB14" s="354" t="n"/>
-      <c r="AC14" s="354" t="n"/>
-      <c r="AD14" s="354" t="n"/>
-      <c r="AE14" s="354" t="n"/>
-      <c r="AF14" s="354" t="n"/>
-      <c r="AG14" s="354" t="n"/>
-      <c r="AH14" s="354" t="n"/>
-      <c r="AI14" s="354" t="n"/>
-      <c r="AJ14" s="354" t="n"/>
-      <c r="AK14" s="354" t="n"/>
-      <c r="AL14" s="354" t="n"/>
-      <c r="AM14" s="354" t="n"/>
-      <c r="AN14" s="531" t="n"/>
+      <c r="A14" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B14" s="673" t="n"/>
+      <c r="C14" s="673" t="n"/>
+      <c r="D14" s="673" t="n"/>
+      <c r="E14" s="673" t="n"/>
+      <c r="F14" s="673" t="n"/>
+      <c r="G14" s="673" t="n"/>
+      <c r="H14" s="671" t="n"/>
+      <c r="I14" s="671" t="n"/>
+      <c r="J14" s="671" t="n"/>
+      <c r="K14" s="671" t="n"/>
+      <c r="L14" s="671" t="n"/>
+      <c r="M14" s="671" t="n"/>
+      <c r="N14" s="671" t="n"/>
+      <c r="O14" s="671" t="n"/>
+      <c r="P14" s="671" t="n"/>
+      <c r="Q14" s="671" t="n"/>
+      <c r="R14" s="671" t="n"/>
+      <c r="S14" s="671" t="n"/>
+      <c r="T14" s="671" t="n"/>
+      <c r="U14" s="671" t="n"/>
+      <c r="V14" s="671" t="n"/>
+      <c r="W14" s="671" t="n"/>
+      <c r="X14" s="671" t="n"/>
+      <c r="Y14" s="671" t="n"/>
+      <c r="Z14" s="671" t="n"/>
+      <c r="AA14" s="671" t="n"/>
+      <c r="AB14" s="671" t="n"/>
+      <c r="AC14" s="671" t="n"/>
+      <c r="AD14" s="671" t="n"/>
+      <c r="AE14" s="671" t="n"/>
+      <c r="AF14" s="671" t="n"/>
+      <c r="AG14" s="671" t="n"/>
+      <c r="AH14" s="671" t="n"/>
+      <c r="AI14" s="671" t="n"/>
+      <c r="AJ14" s="671" t="n"/>
+      <c r="AK14" s="671" t="n"/>
+      <c r="AL14" s="671" t="n"/>
+      <c r="AM14" s="671" t="n"/>
+      <c r="AN14" s="671" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX ANNEX-QMS-020</t>
-        </is>
-      </c>
-      <c r="B15" s="533" t="inlineStr">
-        <is>
-          <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
-        </is>
-      </c>
-      <c r="C15" s="534" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
-        </is>
-      </c>
-      <c r="D15" s="535" t="n"/>
-      <c r="E15" s="535" t="n"/>
-      <c r="F15" s="535" t="n"/>
-      <c r="G15" s="535" t="n"/>
-      <c r="H15" s="535" t="n"/>
-      <c r="I15" s="535" t="n"/>
-      <c r="J15" s="535" t="n"/>
-      <c r="K15" s="535" t="n"/>
-      <c r="L15" s="535" t="n"/>
-      <c r="M15" s="535" t="n"/>
-      <c r="N15" s="535" t="n"/>
-      <c r="O15" s="535" t="n"/>
-      <c r="P15" s="535" t="n"/>
-      <c r="Q15" s="535" t="n"/>
-      <c r="R15" s="535" t="n"/>
-      <c r="S15" s="535" t="n"/>
-      <c r="T15" s="535" t="n"/>
-      <c r="U15" s="535" t="n"/>
-      <c r="V15" s="535" t="n"/>
-      <c r="W15" s="535" t="n"/>
-      <c r="X15" s="535" t="n"/>
-      <c r="Y15" s="535" t="n"/>
-      <c r="Z15" s="535" t="n"/>
-      <c r="AA15" s="535" t="n"/>
-      <c r="AB15" s="535" t="n"/>
-      <c r="AC15" s="535" t="n"/>
-      <c r="AD15" s="535" t="n"/>
-      <c r="AE15" s="535" t="n"/>
-      <c r="AF15" s="535" t="n"/>
-      <c r="AG15" s="535" t="n"/>
-      <c r="AH15" s="535" t="n"/>
-      <c r="AI15" s="535" t="n"/>
-      <c r="AJ15" s="535" t="n"/>
-      <c r="AK15" s="535" t="n"/>
-      <c r="AL15" s="535" t="n"/>
-      <c r="AM15" s="535" t="n"/>
-      <c r="AN15" s="536" t="n"/>
+      <c r="A15" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B15" s="673" t="n"/>
+      <c r="C15" s="673" t="n"/>
+      <c r="D15" s="673" t="n"/>
+      <c r="E15" s="673" t="n"/>
+      <c r="F15" s="673" t="n"/>
+      <c r="G15" s="673" t="n"/>
+      <c r="H15" s="671" t="n"/>
+      <c r="I15" s="671" t="n"/>
+      <c r="J15" s="671" t="n"/>
+      <c r="K15" s="671" t="n"/>
+      <c r="L15" s="671" t="n"/>
+      <c r="M15" s="671" t="n"/>
+      <c r="N15" s="671" t="n"/>
+      <c r="O15" s="671" t="n"/>
+      <c r="P15" s="671" t="n"/>
+      <c r="Q15" s="671" t="n"/>
+      <c r="R15" s="671" t="n"/>
+      <c r="S15" s="671" t="n"/>
+      <c r="T15" s="671" t="n"/>
+      <c r="U15" s="671" t="n"/>
+      <c r="V15" s="671" t="n"/>
+      <c r="W15" s="671" t="n"/>
+      <c r="X15" s="671" t="n"/>
+      <c r="Y15" s="671" t="n"/>
+      <c r="Z15" s="671" t="n"/>
+      <c r="AA15" s="671" t="n"/>
+      <c r="AB15" s="671" t="n"/>
+      <c r="AC15" s="671" t="n"/>
+      <c r="AD15" s="671" t="n"/>
+      <c r="AE15" s="671" t="n"/>
+      <c r="AF15" s="671" t="n"/>
+      <c r="AG15" s="671" t="n"/>
+      <c r="AH15" s="671" t="n"/>
+      <c r="AI15" s="671" t="n"/>
+      <c r="AJ15" s="671" t="n"/>
+      <c r="AK15" s="671" t="n"/>
+      <c r="AL15" s="671" t="n"/>
+      <c r="AM15" s="671" t="n"/>
+      <c r="AN15" s="671" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B16" s="673" t="n"/>
+      <c r="C16" s="673" t="n"/>
+      <c r="D16" s="673" t="n"/>
+      <c r="E16" s="673" t="n"/>
+      <c r="F16" s="673" t="n"/>
+      <c r="G16" s="673" t="n"/>
+      <c r="H16" s="671" t="n"/>
+      <c r="I16" s="671" t="n"/>
+      <c r="J16" s="671" t="n"/>
+      <c r="K16" s="671" t="n"/>
+      <c r="L16" s="671" t="n"/>
+      <c r="M16" s="671" t="n"/>
+      <c r="N16" s="671" t="n"/>
+      <c r="O16" s="671" t="n"/>
+      <c r="P16" s="671" t="n"/>
+      <c r="Q16" s="671" t="n"/>
+      <c r="R16" s="671" t="n"/>
+      <c r="S16" s="671" t="n"/>
+      <c r="T16" s="671" t="n"/>
+      <c r="U16" s="671" t="n"/>
+      <c r="V16" s="671" t="n"/>
+      <c r="W16" s="671" t="n"/>
+      <c r="X16" s="671" t="n"/>
+      <c r="Y16" s="671" t="n"/>
+      <c r="Z16" s="671" t="n"/>
+      <c r="AA16" s="671" t="n"/>
+      <c r="AB16" s="671" t="n"/>
+      <c r="AC16" s="671" t="n"/>
+      <c r="AD16" s="671" t="n"/>
+      <c r="AE16" s="671" t="n"/>
+      <c r="AF16" s="671" t="n"/>
+      <c r="AG16" s="671" t="n"/>
+      <c r="AH16" s="671" t="n"/>
+      <c r="AI16" s="671" t="n"/>
+      <c r="AJ16" s="671" t="n"/>
+      <c r="AK16" s="671" t="n"/>
+      <c r="AL16" s="671" t="n"/>
+      <c r="AM16" s="671" t="n"/>
+      <c r="AN16" s="671" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B17" s="673" t="n"/>
+      <c r="C17" s="673" t="n"/>
+      <c r="D17" s="673" t="n"/>
+      <c r="E17" s="673" t="n"/>
+      <c r="F17" s="673" t="n"/>
+      <c r="G17" s="673" t="n"/>
+      <c r="H17" s="671" t="n"/>
+      <c r="I17" s="671" t="n"/>
+      <c r="J17" s="671" t="n"/>
+      <c r="K17" s="671" t="n"/>
+      <c r="L17" s="671" t="n"/>
+      <c r="M17" s="671" t="n"/>
+      <c r="N17" s="671" t="n"/>
+      <c r="O17" s="671" t="n"/>
+      <c r="P17" s="671" t="n"/>
+      <c r="Q17" s="671" t="n"/>
+      <c r="R17" s="671" t="n"/>
+      <c r="S17" s="671" t="n"/>
+      <c r="T17" s="671" t="n"/>
+      <c r="U17" s="671" t="n"/>
+      <c r="V17" s="671" t="n"/>
+      <c r="W17" s="671" t="n"/>
+      <c r="X17" s="671" t="n"/>
+      <c r="Y17" s="671" t="n"/>
+      <c r="Z17" s="671" t="n"/>
+      <c r="AA17" s="671" t="n"/>
+      <c r="AB17" s="671" t="n"/>
+      <c r="AC17" s="671" t="n"/>
+      <c r="AD17" s="671" t="n"/>
+      <c r="AE17" s="671" t="n"/>
+      <c r="AF17" s="671" t="n"/>
+      <c r="AG17" s="671" t="n"/>
+      <c r="AH17" s="671" t="n"/>
+      <c r="AI17" s="671" t="n"/>
+      <c r="AJ17" s="671" t="n"/>
+      <c r="AK17" s="671" t="n"/>
+      <c r="AL17" s="671" t="n"/>
+      <c r="AM17" s="671" t="n"/>
+      <c r="AN17" s="671" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B18" s="673" t="n"/>
+      <c r="C18" s="673" t="n"/>
+      <c r="D18" s="673" t="n"/>
+      <c r="E18" s="673" t="n"/>
+      <c r="F18" s="673" t="n"/>
+      <c r="G18" s="673" t="n"/>
+      <c r="H18" s="671" t="n"/>
+      <c r="I18" s="671" t="n"/>
+      <c r="J18" s="671" t="n"/>
+      <c r="K18" s="671" t="n"/>
+      <c r="L18" s="671" t="n"/>
+      <c r="M18" s="671" t="n"/>
+      <c r="N18" s="671" t="n"/>
+      <c r="O18" s="671" t="n"/>
+      <c r="P18" s="671" t="n"/>
+      <c r="Q18" s="671" t="n"/>
+      <c r="R18" s="671" t="n"/>
+      <c r="S18" s="671" t="n"/>
+      <c r="T18" s="671" t="n"/>
+      <c r="U18" s="671" t="n"/>
+      <c r="V18" s="671" t="n"/>
+      <c r="W18" s="671" t="n"/>
+      <c r="X18" s="671" t="n"/>
+      <c r="Y18" s="671" t="n"/>
+      <c r="Z18" s="671" t="n"/>
+      <c r="AA18" s="671" t="n"/>
+      <c r="AB18" s="671" t="n"/>
+      <c r="AC18" s="671" t="n"/>
+      <c r="AD18" s="671" t="n"/>
+      <c r="AE18" s="671" t="n"/>
+      <c r="AF18" s="671" t="n"/>
+      <c r="AG18" s="671" t="n"/>
+      <c r="AH18" s="671" t="n"/>
+      <c r="AI18" s="671" t="n"/>
+      <c r="AJ18" s="671" t="n"/>
+      <c r="AK18" s="671" t="n"/>
+      <c r="AL18" s="671" t="n"/>
+      <c r="AM18" s="671" t="n"/>
+      <c r="AN18" s="671" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B19" s="673" t="n"/>
+      <c r="C19" s="673" t="n"/>
+      <c r="D19" s="673" t="n"/>
+      <c r="E19" s="673" t="n"/>
+      <c r="F19" s="673" t="n"/>
+      <c r="G19" s="673" t="n"/>
+      <c r="H19" s="671" t="n"/>
+      <c r="I19" s="671" t="n"/>
+      <c r="J19" s="671" t="n"/>
+      <c r="K19" s="671" t="n"/>
+      <c r="L19" s="671" t="n"/>
+      <c r="M19" s="671" t="n"/>
+      <c r="N19" s="671" t="n"/>
+      <c r="O19" s="671" t="n"/>
+      <c r="P19" s="671" t="n"/>
+      <c r="Q19" s="671" t="n"/>
+      <c r="R19" s="671" t="n"/>
+      <c r="S19" s="671" t="n"/>
+      <c r="T19" s="671" t="n"/>
+      <c r="U19" s="671" t="n"/>
+      <c r="V19" s="671" t="n"/>
+      <c r="W19" s="671" t="n"/>
+      <c r="X19" s="671" t="n"/>
+      <c r="Y19" s="671" t="n"/>
+      <c r="Z19" s="671" t="n"/>
+      <c r="AA19" s="671" t="n"/>
+      <c r="AB19" s="671" t="n"/>
+      <c r="AC19" s="671" t="n"/>
+      <c r="AD19" s="671" t="n"/>
+      <c r="AE19" s="671" t="n"/>
+      <c r="AF19" s="671" t="n"/>
+      <c r="AG19" s="671" t="n"/>
+      <c r="AH19" s="671" t="n"/>
+      <c r="AI19" s="671" t="n"/>
+      <c r="AJ19" s="671" t="n"/>
+      <c r="AK19" s="671" t="n"/>
+      <c r="AL19" s="671" t="n"/>
+      <c r="AM19" s="671" t="n"/>
+      <c r="AN19" s="671" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B20" s="671" t="n"/>
+      <c r="C20" s="671" t="n"/>
+      <c r="D20" s="671" t="n"/>
+      <c r="E20" s="671" t="n"/>
+      <c r="F20" s="671" t="n"/>
+      <c r="G20" s="671" t="n"/>
+      <c r="H20" s="671" t="n"/>
+      <c r="I20" s="671" t="n"/>
+      <c r="J20" s="671" t="n"/>
+      <c r="K20" s="671" t="n"/>
+      <c r="L20" s="671" t="n"/>
+      <c r="M20" s="671" t="n"/>
+      <c r="N20" s="671" t="n"/>
+      <c r="O20" s="671" t="n"/>
+      <c r="P20" s="671" t="n"/>
+      <c r="Q20" s="671" t="n"/>
+      <c r="R20" s="671" t="n"/>
+      <c r="S20" s="671" t="n"/>
+      <c r="T20" s="671" t="n"/>
+      <c r="U20" s="671" t="n"/>
+      <c r="V20" s="671" t="n"/>
+      <c r="W20" s="671" t="n"/>
+      <c r="X20" s="671" t="n"/>
+      <c r="Y20" s="671" t="n"/>
+      <c r="Z20" s="671" t="n"/>
+      <c r="AA20" s="671" t="n"/>
+      <c r="AB20" s="671" t="n"/>
+      <c r="AC20" s="671" t="n"/>
+      <c r="AD20" s="671" t="n"/>
+      <c r="AE20" s="671" t="n"/>
+      <c r="AF20" s="671" t="n"/>
+      <c r="AG20" s="671" t="n"/>
+      <c r="AH20" s="671" t="n"/>
+      <c r="AI20" s="671" t="n"/>
+      <c r="AJ20" s="671" t="n"/>
+      <c r="AK20" s="671" t="n"/>
+      <c r="AL20" s="671" t="n"/>
+      <c r="AM20" s="671" t="n"/>
+      <c r="AN20" s="671" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B21" s="671" t="n"/>
+      <c r="C21" s="671" t="n"/>
+      <c r="D21" s="671" t="n"/>
+      <c r="E21" s="671" t="n"/>
+      <c r="F21" s="671" t="n"/>
+      <c r="G21" s="671" t="n"/>
+      <c r="H21" s="671" t="n"/>
+      <c r="I21" s="671" t="n"/>
+      <c r="J21" s="671" t="n"/>
+      <c r="K21" s="671" t="n"/>
+      <c r="L21" s="671" t="n"/>
+      <c r="M21" s="671" t="n"/>
+      <c r="N21" s="671" t="n"/>
+      <c r="O21" s="671" t="n"/>
+      <c r="P21" s="671" t="n"/>
+      <c r="Q21" s="671" t="n"/>
+      <c r="R21" s="671" t="n"/>
+      <c r="S21" s="671" t="n"/>
+      <c r="T21" s="671" t="n"/>
+      <c r="U21" s="671" t="n"/>
+      <c r="V21" s="671" t="n"/>
+      <c r="W21" s="671" t="n"/>
+      <c r="X21" s="671" t="n"/>
+      <c r="Y21" s="671" t="n"/>
+      <c r="Z21" s="671" t="n"/>
+      <c r="AA21" s="671" t="n"/>
+      <c r="AB21" s="671" t="n"/>
+      <c r="AC21" s="671" t="n"/>
+      <c r="AD21" s="671" t="n"/>
+      <c r="AE21" s="671" t="n"/>
+      <c r="AF21" s="671" t="n"/>
+      <c r="AG21" s="671" t="n"/>
+      <c r="AH21" s="671" t="n"/>
+      <c r="AI21" s="671" t="n"/>
+      <c r="AJ21" s="671" t="n"/>
+      <c r="AK21" s="671" t="n"/>
+      <c r="AL21" s="671" t="n"/>
+      <c r="AM21" s="671" t="n"/>
+      <c r="AN21" s="671" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B22" s="671" t="n"/>
+      <c r="C22" s="671" t="n"/>
+      <c r="D22" s="671" t="n"/>
+      <c r="E22" s="671" t="n"/>
+      <c r="F22" s="671" t="n"/>
+      <c r="G22" s="671" t="n"/>
+      <c r="H22" s="671" t="n"/>
+      <c r="I22" s="671" t="n"/>
+      <c r="J22" s="671" t="n"/>
+      <c r="K22" s="671" t="n"/>
+      <c r="L22" s="671" t="n"/>
+      <c r="M22" s="671" t="n"/>
+      <c r="N22" s="671" t="n"/>
+      <c r="O22" s="671" t="n"/>
+      <c r="P22" s="671" t="n"/>
+      <c r="Q22" s="671" t="n"/>
+      <c r="R22" s="671" t="n"/>
+      <c r="S22" s="671" t="n"/>
+      <c r="T22" s="671" t="n"/>
+      <c r="U22" s="671" t="n"/>
+      <c r="V22" s="671" t="n"/>
+      <c r="W22" s="671" t="n"/>
+      <c r="X22" s="671" t="n"/>
+      <c r="Y22" s="671" t="n"/>
+      <c r="Z22" s="671" t="n"/>
+      <c r="AA22" s="671" t="n"/>
+      <c r="AB22" s="671" t="n"/>
+      <c r="AC22" s="671" t="n"/>
+      <c r="AD22" s="671" t="n"/>
+      <c r="AE22" s="671" t="n"/>
+      <c r="AF22" s="671" t="n"/>
+      <c r="AG22" s="671" t="n"/>
+      <c r="AH22" s="671" t="n"/>
+      <c r="AI22" s="671" t="n"/>
+      <c r="AJ22" s="671" t="n"/>
+      <c r="AK22" s="671" t="n"/>
+      <c r="AL22" s="671" t="n"/>
+      <c r="AM22" s="671" t="n"/>
+      <c r="AN22" s="671" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B23" s="671" t="n"/>
+      <c r="C23" s="671" t="n"/>
+      <c r="D23" s="671" t="n"/>
+      <c r="E23" s="671" t="n"/>
+      <c r="F23" s="671" t="n"/>
+      <c r="G23" s="671" t="n"/>
+      <c r="H23" s="671" t="n"/>
+      <c r="I23" s="671" t="n"/>
+      <c r="J23" s="671" t="n"/>
+      <c r="K23" s="671" t="n"/>
+      <c r="L23" s="671" t="n"/>
+      <c r="M23" s="671" t="n"/>
+      <c r="N23" s="671" t="n"/>
+      <c r="O23" s="671" t="n"/>
+      <c r="P23" s="671" t="n"/>
+      <c r="Q23" s="671" t="n"/>
+      <c r="R23" s="671" t="n"/>
+      <c r="S23" s="671" t="n"/>
+      <c r="T23" s="671" t="n"/>
+      <c r="U23" s="671" t="n"/>
+      <c r="V23" s="671" t="n"/>
+      <c r="W23" s="671" t="n"/>
+      <c r="X23" s="671" t="n"/>
+      <c r="Y23" s="671" t="n"/>
+      <c r="Z23" s="671" t="n"/>
+      <c r="AA23" s="671" t="n"/>
+      <c r="AB23" s="671" t="n"/>
+      <c r="AC23" s="671" t="n"/>
+      <c r="AD23" s="671" t="n"/>
+      <c r="AE23" s="671" t="n"/>
+      <c r="AF23" s="671" t="n"/>
+      <c r="AG23" s="671" t="n"/>
+      <c r="AH23" s="671" t="n"/>
+      <c r="AI23" s="671" t="n"/>
+      <c r="AJ23" s="671" t="n"/>
+      <c r="AK23" s="671" t="n"/>
+      <c r="AL23" s="671" t="n"/>
+      <c r="AM23" s="671" t="n"/>
+      <c r="AN23" s="671" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="731">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B24" s="671" t="n"/>
+      <c r="C24" s="671" t="n"/>
+      <c r="D24" s="671" t="n"/>
+      <c r="E24" s="671" t="n"/>
+      <c r="F24" s="671" t="n"/>
+      <c r="G24" s="671" t="n"/>
+      <c r="H24" s="671" t="n"/>
+      <c r="I24" s="671" t="n"/>
+      <c r="J24" s="671" t="n"/>
+      <c r="K24" s="671" t="n"/>
+      <c r="L24" s="671" t="n"/>
+      <c r="M24" s="671" t="n"/>
+      <c r="N24" s="671" t="n"/>
+      <c r="O24" s="671" t="n"/>
+      <c r="P24" s="671" t="n"/>
+      <c r="Q24" s="671" t="n"/>
+      <c r="R24" s="671" t="n"/>
+      <c r="S24" s="671" t="n"/>
+      <c r="T24" s="671" t="n"/>
+      <c r="U24" s="671" t="n"/>
+      <c r="V24" s="671" t="n"/>
+      <c r="W24" s="671" t="n"/>
+      <c r="X24" s="671" t="n"/>
+      <c r="Y24" s="671" t="n"/>
+      <c r="Z24" s="671" t="n"/>
+      <c r="AA24" s="671" t="n"/>
+      <c r="AB24" s="671" t="n"/>
+      <c r="AC24" s="671" t="n"/>
+      <c r="AD24" s="671" t="n"/>
+      <c r="AE24" s="671" t="n"/>
+      <c r="AF24" s="671" t="n"/>
+      <c r="AG24" s="671" t="n"/>
+      <c r="AH24" s="671" t="n"/>
+      <c r="AI24" s="671" t="n"/>
+      <c r="AJ24" s="671" t="n"/>
+      <c r="AK24" s="671" t="n"/>
+      <c r="AL24" s="671" t="n"/>
+      <c r="AM24" s="671" t="n"/>
+      <c r="AN24" s="671" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="732">
+        <f>ROW()-ROW($A$5)+1</f>
+        <v/>
+      </c>
+      <c r="B25" s="671" t="n"/>
+      <c r="C25" s="671" t="n"/>
+      <c r="D25" s="671" t="n"/>
+      <c r="E25" s="671" t="n"/>
+      <c r="F25" s="671" t="n"/>
+      <c r="G25" s="671" t="n"/>
+      <c r="H25" s="671" t="n"/>
+      <c r="I25" s="671" t="n"/>
+      <c r="J25" s="671" t="n"/>
+      <c r="K25" s="671" t="n"/>
+      <c r="L25" s="671" t="n"/>
+      <c r="M25" s="671" t="n"/>
+      <c r="N25" s="671" t="n"/>
+      <c r="O25" s="671" t="n"/>
+      <c r="P25" s="671" t="n"/>
+      <c r="Q25" s="671" t="n"/>
+      <c r="R25" s="671" t="n"/>
+      <c r="S25" s="671" t="n"/>
+      <c r="T25" s="671" t="n"/>
+      <c r="U25" s="671" t="n"/>
+      <c r="V25" s="671" t="n"/>
+      <c r="W25" s="671" t="n"/>
+      <c r="X25" s="671" t="n"/>
+      <c r="Y25" s="671" t="n"/>
+      <c r="Z25" s="671" t="n"/>
+      <c r="AA25" s="671" t="n"/>
+      <c r="AB25" s="671" t="n"/>
+      <c r="AC25" s="671" t="n"/>
+      <c r="AD25" s="671" t="n"/>
+      <c r="AE25" s="671" t="n"/>
+      <c r="AF25" s="671" t="n"/>
+      <c r="AG25" s="671" t="n"/>
+      <c r="AH25" s="671" t="n"/>
+      <c r="AI25" s="671" t="n"/>
+      <c r="AJ25" s="671" t="n"/>
+      <c r="AK25" s="671" t="n"/>
+      <c r="AL25" s="671" t="n"/>
+      <c r="AM25" s="671" t="n"/>
+      <c r="AN25" s="671" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="671" t="n"/>
+      <c r="B26" s="671" t="n"/>
+      <c r="C26" s="671" t="n"/>
+      <c r="D26" s="671" t="n"/>
+      <c r="E26" s="671" t="n"/>
+      <c r="F26" s="671" t="n"/>
+      <c r="G26" s="671" t="n"/>
+      <c r="H26" s="671" t="n"/>
+      <c r="I26" s="671" t="n"/>
+      <c r="J26" s="671" t="n"/>
+      <c r="K26" s="671" t="n"/>
+      <c r="L26" s="671" t="n"/>
+      <c r="M26" s="671" t="n"/>
+      <c r="N26" s="671" t="n"/>
+      <c r="O26" s="671" t="n"/>
+      <c r="P26" s="671" t="n"/>
+      <c r="Q26" s="671" t="n"/>
+      <c r="R26" s="671" t="n"/>
+      <c r="S26" s="671" t="n"/>
+      <c r="T26" s="671" t="n"/>
+      <c r="U26" s="671" t="n"/>
+      <c r="V26" s="671" t="n"/>
+      <c r="W26" s="671" t="n"/>
+      <c r="X26" s="671" t="n"/>
+      <c r="Y26" s="671" t="n"/>
+      <c r="Z26" s="671" t="n"/>
+      <c r="AA26" s="671" t="n"/>
+      <c r="AB26" s="671" t="n"/>
+      <c r="AC26" s="671" t="n"/>
+      <c r="AD26" s="671" t="n"/>
+      <c r="AE26" s="671" t="n"/>
+      <c r="AF26" s="671" t="n"/>
+      <c r="AG26" s="671" t="n"/>
+      <c r="AH26" s="671" t="n"/>
+      <c r="AI26" s="671" t="n"/>
+      <c r="AJ26" s="671" t="n"/>
+      <c r="AK26" s="671" t="n"/>
+      <c r="AL26" s="671" t="n"/>
+      <c r="AM26" s="671" t="n"/>
+      <c r="AN26" s="671" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="671" t="n"/>
+      <c r="B27" s="671" t="n"/>
+      <c r="C27" s="671" t="n"/>
+      <c r="D27" s="671" t="n"/>
+      <c r="E27" s="671" t="n"/>
+      <c r="F27" s="671" t="n"/>
+      <c r="G27" s="671" t="n"/>
+      <c r="H27" s="671" t="n"/>
+      <c r="I27" s="671" t="n"/>
+      <c r="J27" s="671" t="n"/>
+      <c r="K27" s="671" t="n"/>
+      <c r="L27" s="671" t="n"/>
+      <c r="M27" s="671" t="n"/>
+      <c r="N27" s="671" t="n"/>
+      <c r="O27" s="671" t="n"/>
+      <c r="P27" s="671" t="n"/>
+      <c r="Q27" s="671" t="n"/>
+      <c r="R27" s="671" t="n"/>
+      <c r="S27" s="671" t="n"/>
+      <c r="T27" s="671" t="n"/>
+      <c r="U27" s="671" t="n"/>
+      <c r="V27" s="671" t="n"/>
+      <c r="W27" s="671" t="n"/>
+      <c r="X27" s="671" t="n"/>
+      <c r="Y27" s="671" t="n"/>
+      <c r="Z27" s="671" t="n"/>
+      <c r="AA27" s="671" t="n"/>
+      <c r="AB27" s="671" t="n"/>
+      <c r="AC27" s="671" t="n"/>
+      <c r="AD27" s="671" t="n"/>
+      <c r="AE27" s="671" t="n"/>
+      <c r="AF27" s="671" t="n"/>
+      <c r="AG27" s="671" t="n"/>
+      <c r="AH27" s="671" t="n"/>
+      <c r="AI27" s="671" t="n"/>
+      <c r="AJ27" s="671" t="n"/>
+      <c r="AK27" s="671" t="n"/>
+      <c r="AL27" s="671" t="n"/>
+      <c r="AM27" s="671" t="n"/>
+      <c r="AN27" s="671" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="671" t="n"/>
+      <c r="B28" s="671" t="n"/>
+      <c r="C28" s="671" t="n"/>
+      <c r="D28" s="671" t="n"/>
+      <c r="E28" s="671" t="n"/>
+      <c r="F28" s="671" t="n"/>
+      <c r="G28" s="671" t="n"/>
+      <c r="H28" s="671" t="n"/>
+      <c r="I28" s="671" t="n"/>
+      <c r="J28" s="671" t="n"/>
+      <c r="K28" s="671" t="n"/>
+      <c r="L28" s="671" t="n"/>
+      <c r="M28" s="671" t="n"/>
+      <c r="N28" s="671" t="n"/>
+      <c r="O28" s="671" t="n"/>
+      <c r="P28" s="671" t="n"/>
+      <c r="Q28" s="671" t="n"/>
+      <c r="R28" s="671" t="n"/>
+      <c r="S28" s="671" t="n"/>
+      <c r="T28" s="671" t="n"/>
+      <c r="U28" s="671" t="n"/>
+      <c r="V28" s="671" t="n"/>
+      <c r="W28" s="671" t="n"/>
+      <c r="X28" s="671" t="n"/>
+      <c r="Y28" s="671" t="n"/>
+      <c r="Z28" s="671" t="n"/>
+      <c r="AA28" s="671" t="n"/>
+      <c r="AB28" s="671" t="n"/>
+      <c r="AC28" s="671" t="n"/>
+      <c r="AD28" s="671" t="n"/>
+      <c r="AE28" s="671" t="n"/>
+      <c r="AF28" s="671" t="n"/>
+      <c r="AG28" s="671" t="n"/>
+      <c r="AH28" s="671" t="n"/>
+      <c r="AI28" s="671" t="n"/>
+      <c r="AJ28" s="671" t="n"/>
+      <c r="AK28" s="671" t="n"/>
+      <c r="AL28" s="671" t="n"/>
+      <c r="AM28" s="671" t="n"/>
+      <c r="AN28" s="671" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <autoFilter ref="A4:C15"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
+      <formula1>'LISTS'!$A$2:$A$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11898,410 +12409,2133 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="510" t="inlineStr">
-        <is>
-          <t>Evidence Reference / Attachment Guidance</t>
-        </is>
-      </c>
+    <row r="1" hidden="1">
+      <c r="A1" s="711" t="n"/>
       <c r="B1" s="599" t="n"/>
       <c r="C1" s="599" t="n"/>
       <c r="D1" s="599" t="n"/>
       <c r="E1" s="599" t="n"/>
       <c r="F1" s="599" t="n"/>
       <c r="G1" s="599" t="n"/>
-      <c r="H1" s="511" t="n"/>
-      <c r="I1" s="428" t="n"/>
-      <c r="J1" s="429" t="n"/>
-      <c r="K1" s="429" t="n"/>
-      <c r="L1" s="429" t="n"/>
-      <c r="M1" s="429" t="n"/>
-      <c r="N1" s="429" t="n"/>
-      <c r="O1" s="429" t="n"/>
-      <c r="P1" s="429" t="n"/>
-      <c r="Q1" s="429" t="n"/>
-      <c r="R1" s="429" t="n"/>
-      <c r="S1" s="429" t="n"/>
-      <c r="T1" s="429" t="n"/>
-      <c r="U1" s="429" t="n"/>
-      <c r="V1" s="429" t="n"/>
-      <c r="W1" s="429" t="n"/>
-      <c r="X1" s="429" t="n"/>
-      <c r="Y1" s="429" t="n"/>
-      <c r="Z1" s="429" t="n"/>
-      <c r="AA1" s="429" t="n"/>
-      <c r="AB1" s="429" t="n"/>
-      <c r="AC1" s="429" t="n"/>
-      <c r="AD1" s="430" t="n"/>
-      <c r="AE1" s="431" t="n"/>
-      <c r="AF1" s="432" t="n"/>
-      <c r="AG1" s="432" t="n"/>
-      <c r="AH1" s="433" t="n"/>
-      <c r="AI1" s="434" t="n"/>
-      <c r="AJ1" s="435" t="n"/>
-      <c r="AK1" s="435" t="n"/>
-      <c r="AL1" s="435" t="n"/>
-      <c r="AM1" s="435" t="n"/>
-      <c r="AN1" s="436" t="n"/>
+      <c r="H1" s="712" t="n"/>
+      <c r="I1" s="713" t="inlineStr">
+        <is>
+          <t>Final Inspection Report</t>
+        </is>
+      </c>
+      <c r="J1" s="599" t="n"/>
+      <c r="K1" s="599" t="n"/>
+      <c r="L1" s="599" t="n"/>
+      <c r="M1" s="599" t="n"/>
+      <c r="N1" s="599" t="n"/>
+      <c r="O1" s="599" t="n"/>
+      <c r="P1" s="599" t="n"/>
+      <c r="Q1" s="599" t="n"/>
+      <c r="R1" s="599" t="n"/>
+      <c r="S1" s="599" t="n"/>
+      <c r="T1" s="599" t="n"/>
+      <c r="U1" s="599" t="n"/>
+      <c r="V1" s="599" t="n"/>
+      <c r="W1" s="599" t="n"/>
+      <c r="X1" s="599" t="n"/>
+      <c r="Y1" s="599" t="n"/>
+      <c r="Z1" s="599" t="n"/>
+      <c r="AA1" s="599" t="n"/>
+      <c r="AB1" s="599" t="n"/>
+      <c r="AC1" s="599" t="n"/>
+      <c r="AD1" s="712" t="n"/>
+      <c r="AE1" s="433" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="599" t="n"/>
+      <c r="AG1" s="599" t="n"/>
+      <c r="AH1" s="714" t="n"/>
+      <c r="AI1" s="436" t="inlineStr">
+        <is>
+          <t>FRM-641</t>
+        </is>
+      </c>
+      <c r="AJ1" s="599" t="n"/>
+      <c r="AK1" s="599" t="n"/>
+      <c r="AL1" s="599" t="n"/>
+      <c r="AM1" s="599" t="n"/>
+      <c r="AN1" s="712" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="512" t="inlineStr">
-        <is>
-          <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
-        </is>
-      </c>
-      <c r="H2" s="513" t="n"/>
-      <c r="I2" s="439" t="n"/>
-      <c r="J2" s="440" t="n"/>
-      <c r="K2" s="440" t="n"/>
-      <c r="L2" s="440" t="n"/>
-      <c r="M2" s="440" t="n"/>
-      <c r="N2" s="440" t="n"/>
-      <c r="O2" s="440" t="n"/>
-      <c r="P2" s="440" t="n"/>
-      <c r="Q2" s="440" t="n"/>
-      <c r="R2" s="440" t="n"/>
-      <c r="S2" s="440" t="n"/>
-      <c r="T2" s="440" t="n"/>
-      <c r="U2" s="440" t="n"/>
-      <c r="V2" s="440" t="n"/>
-      <c r="W2" s="440" t="n"/>
-      <c r="X2" s="440" t="n"/>
-      <c r="Y2" s="440" t="n"/>
-      <c r="Z2" s="440" t="n"/>
-      <c r="AA2" s="440" t="n"/>
-      <c r="AB2" s="440" t="n"/>
-      <c r="AC2" s="440" t="n"/>
-      <c r="AD2" s="441" t="n"/>
-      <c r="AE2" s="442" t="n"/>
-      <c r="AF2" s="443" t="n"/>
-      <c r="AG2" s="443" t="n"/>
-      <c r="AH2" s="444" t="n"/>
-      <c r="AI2" s="445" t="n"/>
-      <c r="AJ2" s="446" t="n"/>
-      <c r="AK2" s="446" t="n"/>
-      <c r="AL2" s="446" t="n"/>
-      <c r="AM2" s="446" t="n"/>
-      <c r="AN2" s="447" t="n"/>
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="684" t="n"/>
+      <c r="C2" s="684" t="n"/>
+      <c r="D2" s="684" t="n"/>
+      <c r="E2" s="684" t="n"/>
+      <c r="F2" s="684" t="n"/>
+      <c r="G2" s="684" t="n"/>
+      <c r="H2" s="685" t="n"/>
+      <c r="I2" s="684" t="n"/>
+      <c r="J2" s="684" t="n"/>
+      <c r="K2" s="684" t="n"/>
+      <c r="L2" s="684" t="n"/>
+      <c r="M2" s="684" t="n"/>
+      <c r="N2" s="684" t="n"/>
+      <c r="O2" s="684" t="n"/>
+      <c r="P2" s="684" t="n"/>
+      <c r="Q2" s="684" t="n"/>
+      <c r="R2" s="684" t="n"/>
+      <c r="S2" s="684" t="n"/>
+      <c r="T2" s="684" t="n"/>
+      <c r="U2" s="684" t="n"/>
+      <c r="V2" s="684" t="n"/>
+      <c r="W2" s="684" t="n"/>
+      <c r="X2" s="684" t="n"/>
+      <c r="Y2" s="684" t="n"/>
+      <c r="Z2" s="684" t="n"/>
+      <c r="AA2" s="684" t="n"/>
+      <c r="AB2" s="684" t="n"/>
+      <c r="AC2" s="684" t="n"/>
+      <c r="AD2" s="685" t="n"/>
+      <c r="AE2" s="686" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="687" t="n"/>
+      <c r="AG2" s="687" t="n"/>
+      <c r="AH2" s="688" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="689" t="n"/>
+      <c r="AK2" s="689" t="n"/>
+      <c r="AL2" s="689" t="n"/>
+      <c r="AM2" s="689" t="n"/>
+      <c r="AN2" s="690" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="514" t="n"/>
-      <c r="B3" s="515" t="n"/>
-      <c r="C3" s="515" t="n"/>
-      <c r="D3" s="515" t="n"/>
-      <c r="E3" s="515" t="n"/>
-      <c r="F3" s="515" t="n"/>
-      <c r="G3" s="515" t="n"/>
-      <c r="H3" s="513" t="n"/>
-      <c r="I3" s="439" t="n"/>
-      <c r="J3" s="440" t="n"/>
-      <c r="K3" s="440" t="n"/>
-      <c r="L3" s="440" t="n"/>
-      <c r="M3" s="440" t="n"/>
-      <c r="N3" s="440" t="n"/>
-      <c r="O3" s="440" t="n"/>
-      <c r="P3" s="440" t="n"/>
-      <c r="Q3" s="440" t="n"/>
-      <c r="R3" s="440" t="n"/>
-      <c r="S3" s="440" t="n"/>
-      <c r="T3" s="440" t="n"/>
-      <c r="U3" s="440" t="n"/>
-      <c r="V3" s="440" t="n"/>
-      <c r="W3" s="440" t="n"/>
-      <c r="X3" s="440" t="n"/>
-      <c r="Y3" s="440" t="n"/>
-      <c r="Z3" s="440" t="n"/>
-      <c r="AA3" s="440" t="n"/>
-      <c r="AB3" s="440" t="n"/>
-      <c r="AC3" s="440" t="n"/>
-      <c r="AD3" s="441" t="n"/>
-      <c r="AE3" s="442" t="n"/>
-      <c r="AF3" s="443" t="n"/>
-      <c r="AG3" s="443" t="n"/>
-      <c r="AH3" s="444" t="n"/>
-      <c r="AI3" s="445" t="n"/>
-      <c r="AJ3" s="446" t="n"/>
-      <c r="AK3" s="446" t="n"/>
-      <c r="AL3" s="446" t="n"/>
-      <c r="AM3" s="446" t="n"/>
-      <c r="AN3" s="447" t="n"/>
+      <c r="A3" s="691" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="692" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="692" t="n"/>
+      <c r="AE3" s="693" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="694" t="n"/>
+      <c r="AG3" s="694" t="n"/>
+      <c r="AH3" s="695" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="696" t="n"/>
+      <c r="AK3" s="696" t="n"/>
+      <c r="AL3" s="696" t="n"/>
+      <c r="AM3" s="696" t="n"/>
+      <c r="AN3" s="697" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="516" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="517" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="517" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="515" t="n"/>
-      <c r="E4" s="515" t="n"/>
-      <c r="F4" s="515" t="n"/>
-      <c r="G4" s="515" t="n"/>
-      <c r="H4" s="513" t="n"/>
-      <c r="I4" s="448" t="n"/>
-      <c r="J4" s="449" t="n"/>
-      <c r="K4" s="449" t="n"/>
-      <c r="L4" s="449" t="n"/>
-      <c r="M4" s="449" t="n"/>
-      <c r="N4" s="449" t="n"/>
-      <c r="O4" s="449" t="n"/>
-      <c r="P4" s="449" t="n"/>
-      <c r="Q4" s="449" t="n"/>
-      <c r="R4" s="449" t="n"/>
-      <c r="S4" s="449" t="n"/>
-      <c r="T4" s="449" t="n"/>
-      <c r="U4" s="449" t="n"/>
-      <c r="V4" s="449" t="n"/>
-      <c r="W4" s="449" t="n"/>
-      <c r="X4" s="449" t="n"/>
-      <c r="Y4" s="449" t="n"/>
-      <c r="Z4" s="449" t="n"/>
-      <c r="AA4" s="449" t="n"/>
-      <c r="AB4" s="449" t="n"/>
-      <c r="AC4" s="449" t="n"/>
-      <c r="AD4" s="450" t="n"/>
-      <c r="AE4" s="442" t="n"/>
-      <c r="AF4" s="443" t="n"/>
-      <c r="AG4" s="443" t="n"/>
-      <c r="AH4" s="444" t="n"/>
-      <c r="AI4" s="445" t="n"/>
-      <c r="AJ4" s="446" t="n"/>
-      <c r="AK4" s="446" t="n"/>
-      <c r="AL4" s="446" t="n"/>
-      <c r="AM4" s="446" t="n"/>
-      <c r="AN4" s="447" t="n"/>
+      <c r="A4" s="691" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="692" t="n"/>
+      <c r="I4" s="698" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="692" t="n"/>
+      <c r="AE4" s="693" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="694" t="n"/>
+      <c r="AG4" s="694" t="n"/>
+      <c r="AH4" s="695" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="696" t="n"/>
+      <c r="AK4" s="696" t="n"/>
+      <c r="AL4" s="696" t="n"/>
+      <c r="AM4" s="696" t="n"/>
+      <c r="AN4" s="697" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="518" t="inlineStr">
-        <is>
-          <t>Evidence item 1</t>
-        </is>
-      </c>
-      <c r="B5" s="519" t="inlineStr">
-        <is>
-          <t>Reference to the correct evidence folder, shared location or dossier package.</t>
-        </is>
-      </c>
-      <c r="C5" s="519" t="inlineStr">
-        <is>
-          <t>Link or reference ID</t>
-        </is>
-      </c>
-      <c r="D5" s="537" t="n"/>
-      <c r="E5" s="537" t="n"/>
-      <c r="F5" s="537" t="n"/>
-      <c r="G5" s="537" t="n"/>
-      <c r="H5" s="520" t="n"/>
-      <c r="I5" s="454" t="n"/>
-      <c r="J5" s="455" t="n"/>
-      <c r="K5" s="455" t="n"/>
-      <c r="L5" s="455" t="n"/>
-      <c r="M5" s="455" t="n"/>
-      <c r="N5" s="455" t="n"/>
-      <c r="O5" s="455" t="n"/>
-      <c r="P5" s="455" t="n"/>
-      <c r="Q5" s="455" t="n"/>
-      <c r="R5" s="455" t="n"/>
-      <c r="S5" s="455" t="n"/>
-      <c r="T5" s="455" t="n"/>
-      <c r="U5" s="455" t="n"/>
-      <c r="V5" s="455" t="n"/>
-      <c r="W5" s="455" t="n"/>
-      <c r="X5" s="455" t="n"/>
-      <c r="Y5" s="455" t="n"/>
-      <c r="Z5" s="455" t="n"/>
-      <c r="AA5" s="455" t="n"/>
-      <c r="AB5" s="455" t="n"/>
-      <c r="AC5" s="455" t="n"/>
-      <c r="AD5" s="456" t="n"/>
-      <c r="AE5" s="457" t="n"/>
-      <c r="AF5" s="458" t="n"/>
-      <c r="AG5" s="458" t="n"/>
-      <c r="AH5" s="459" t="n"/>
-      <c r="AI5" s="460" t="n"/>
-      <c r="AJ5" s="461" t="n"/>
-      <c r="AK5" s="461" t="n"/>
-      <c r="AL5" s="461" t="n"/>
-      <c r="AM5" s="461" t="n"/>
-      <c r="AN5" s="462" t="n"/>
+      <c r="A5" s="691" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="692" t="n"/>
+      <c r="I5" s="699" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="692" t="n"/>
+      <c r="AE5" s="693" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="694" t="n"/>
+      <c r="AG5" s="694" t="n"/>
+      <c r="AH5" s="695" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="696" t="n"/>
+      <c r="AK5" s="696" t="n"/>
+      <c r="AL5" s="696" t="n"/>
+      <c r="AM5" s="696" t="n"/>
+      <c r="AN5" s="697" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="521" t="inlineStr">
-        <is>
-          <t>Evidence item 2</t>
-        </is>
-      </c>
-      <c r="B6" s="522" t="inlineStr">
-        <is>
-          <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
-        </is>
-      </c>
-      <c r="C6" s="523" t="inlineStr">
-        <is>
-          <t>Link or reference ID</t>
-        </is>
-      </c>
-      <c r="D6" s="468" t="n"/>
-      <c r="E6" s="468" t="n"/>
-      <c r="F6" s="468" t="n"/>
-      <c r="G6" s="468" t="n"/>
-      <c r="H6" s="468" t="n"/>
-      <c r="I6" s="468" t="n"/>
-      <c r="J6" s="468" t="n"/>
-      <c r="K6" s="468" t="n"/>
-      <c r="L6" s="468" t="n"/>
-      <c r="M6" s="468" t="n"/>
-      <c r="N6" s="468" t="n"/>
-      <c r="O6" s="468" t="n"/>
-      <c r="P6" s="468" t="n"/>
-      <c r="Q6" s="468" t="n"/>
-      <c r="R6" s="468" t="n"/>
-      <c r="S6" s="468" t="n"/>
-      <c r="T6" s="468" t="n"/>
-      <c r="U6" s="468" t="n"/>
-      <c r="V6" s="468" t="n"/>
-      <c r="W6" s="468" t="n"/>
-      <c r="X6" s="468" t="n"/>
-      <c r="Y6" s="468" t="n"/>
-      <c r="Z6" s="468" t="n"/>
-      <c r="AA6" s="468" t="n"/>
-      <c r="AB6" s="468" t="n"/>
-      <c r="AC6" s="468" t="n"/>
-      <c r="AD6" s="468" t="n"/>
-      <c r="AE6" s="468" t="n"/>
-      <c r="AF6" s="468" t="n"/>
-      <c r="AG6" s="468" t="n"/>
-      <c r="AH6" s="468" t="n"/>
-      <c r="AI6" s="468" t="n"/>
-      <c r="AJ6" s="468" t="n"/>
-      <c r="AK6" s="468" t="n"/>
-      <c r="AL6" s="468" t="n"/>
-      <c r="AM6" s="468" t="n"/>
-      <c r="AN6" s="500" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="715" t="n"/>
+      <c r="B6" s="724" t="n"/>
+      <c r="C6" s="724" t="n"/>
+      <c r="D6" s="716" t="n"/>
+      <c r="E6" s="716" t="n"/>
+      <c r="F6" s="716" t="n"/>
+      <c r="G6" s="716" t="n"/>
+      <c r="H6" s="717" t="n"/>
+      <c r="I6" s="716" t="n"/>
+      <c r="J6" s="716" t="n"/>
+      <c r="K6" s="716" t="n"/>
+      <c r="L6" s="716" t="n"/>
+      <c r="M6" s="716" t="n"/>
+      <c r="N6" s="716" t="n"/>
+      <c r="O6" s="716" t="n"/>
+      <c r="P6" s="716" t="n"/>
+      <c r="Q6" s="716" t="n"/>
+      <c r="R6" s="716" t="n"/>
+      <c r="S6" s="716" t="n"/>
+      <c r="T6" s="716" t="n"/>
+      <c r="U6" s="716" t="n"/>
+      <c r="V6" s="716" t="n"/>
+      <c r="W6" s="716" t="n"/>
+      <c r="X6" s="716" t="n"/>
+      <c r="Y6" s="716" t="n"/>
+      <c r="Z6" s="716" t="n"/>
+      <c r="AA6" s="716" t="n"/>
+      <c r="AB6" s="716" t="n"/>
+      <c r="AC6" s="716" t="n"/>
+      <c r="AD6" s="717" t="n"/>
+      <c r="AE6" s="718" t="n"/>
+      <c r="AF6" s="718" t="n"/>
+      <c r="AG6" s="718" t="n"/>
+      <c r="AH6" s="719" t="n"/>
+      <c r="AI6" s="720" t="n"/>
+      <c r="AJ6" s="720" t="n"/>
+      <c r="AK6" s="720" t="n"/>
+      <c r="AL6" s="720" t="n"/>
+      <c r="AM6" s="720" t="n"/>
+      <c r="AN6" s="721" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="524" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B7" s="525" t="inlineStr">
-        <is>
-          <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
-        </is>
-      </c>
-      <c r="C7" s="526" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D7" s="342" t="n"/>
-      <c r="E7" s="342" t="n"/>
-      <c r="F7" s="342" t="n"/>
-      <c r="G7" s="342" t="n"/>
-      <c r="H7" s="342" t="n"/>
-      <c r="I7" s="342" t="n"/>
-      <c r="J7" s="342" t="n"/>
-      <c r="K7" s="342" t="n"/>
-      <c r="L7" s="342" t="n"/>
-      <c r="M7" s="342" t="n"/>
-      <c r="N7" s="342" t="n"/>
-      <c r="O7" s="342" t="n"/>
-      <c r="P7" s="342" t="n"/>
-      <c r="Q7" s="342" t="n"/>
-      <c r="R7" s="342" t="n"/>
-      <c r="S7" s="342" t="n"/>
-      <c r="T7" s="342" t="n"/>
-      <c r="U7" s="342" t="n"/>
-      <c r="V7" s="342" t="n"/>
-      <c r="W7" s="342" t="n"/>
-      <c r="X7" s="342" t="n"/>
-      <c r="Y7" s="342" t="n"/>
-      <c r="Z7" s="342" t="n"/>
-      <c r="AA7" s="342" t="n"/>
-      <c r="AB7" s="342" t="n"/>
-      <c r="AC7" s="342" t="n"/>
-      <c r="AD7" s="342" t="n"/>
-      <c r="AE7" s="342" t="n"/>
-      <c r="AF7" s="342" t="n"/>
-      <c r="AG7" s="342" t="n"/>
-      <c r="AH7" s="342" t="n"/>
-      <c r="AI7" s="342" t="n"/>
-      <c r="AJ7" s="342" t="n"/>
-      <c r="AK7" s="342" t="n"/>
-      <c r="AL7" s="342" t="n"/>
-      <c r="AM7" s="342" t="n"/>
-      <c r="AN7" s="527" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="725" t="n"/>
+      <c r="B7" s="708" t="n"/>
+      <c r="C7" s="708" t="n"/>
+      <c r="D7" s="708" t="n"/>
+      <c r="E7" s="708" t="n"/>
+      <c r="F7" s="708" t="n"/>
+      <c r="G7" s="708" t="n"/>
+      <c r="H7" s="723" t="n"/>
+      <c r="I7" s="723" t="n"/>
+      <c r="J7" s="723" t="n"/>
+      <c r="K7" s="723" t="n"/>
+      <c r="L7" s="723" t="n"/>
+      <c r="M7" s="723" t="n"/>
+      <c r="N7" s="723" t="n"/>
+      <c r="O7" s="723" t="n"/>
+      <c r="P7" s="723" t="n"/>
+      <c r="Q7" s="723" t="n"/>
+      <c r="R7" s="723" t="n"/>
+      <c r="S7" s="723" t="n"/>
+      <c r="T7" s="723" t="n"/>
+      <c r="U7" s="723" t="n"/>
+      <c r="V7" s="723" t="n"/>
+      <c r="W7" s="723" t="n"/>
+      <c r="X7" s="723" t="n"/>
+      <c r="Y7" s="723" t="n"/>
+      <c r="Z7" s="723" t="n"/>
+      <c r="AA7" s="723" t="n"/>
+      <c r="AB7" s="723" t="n"/>
+      <c r="AC7" s="723" t="n"/>
+      <c r="AD7" s="723" t="n"/>
+      <c r="AE7" s="723" t="n"/>
+      <c r="AF7" s="723" t="n"/>
+      <c r="AG7" s="723" t="n"/>
+      <c r="AH7" s="723" t="n"/>
+      <c r="AI7" s="723" t="n"/>
+      <c r="AJ7" s="723" t="n"/>
+      <c r="AK7" s="723" t="n"/>
+      <c r="AL7" s="723" t="n"/>
+      <c r="AM7" s="723" t="n"/>
+      <c r="AN7" s="723" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="532" t="inlineStr">
+      <c r="A8" s="726" t="inlineStr">
+        <is>
+          <t>Reference plan / lot / method / release documents from their owning source.</t>
+        </is>
+      </c>
+      <c r="H8" s="671" t="n"/>
+      <c r="I8" s="671" t="n"/>
+      <c r="J8" s="671" t="n"/>
+      <c r="K8" s="671" t="n"/>
+      <c r="L8" s="671" t="n"/>
+      <c r="M8" s="671" t="n"/>
+      <c r="N8" s="671" t="n"/>
+      <c r="O8" s="671" t="n"/>
+      <c r="P8" s="671" t="n"/>
+      <c r="Q8" s="671" t="n"/>
+      <c r="R8" s="671" t="n"/>
+      <c r="S8" s="671" t="n"/>
+      <c r="T8" s="671" t="n"/>
+      <c r="U8" s="671" t="n"/>
+      <c r="V8" s="671" t="n"/>
+      <c r="W8" s="671" t="n"/>
+      <c r="X8" s="671" t="n"/>
+      <c r="Y8" s="671" t="n"/>
+      <c r="Z8" s="671" t="n"/>
+      <c r="AA8" s="671" t="n"/>
+      <c r="AB8" s="671" t="n"/>
+      <c r="AC8" s="671" t="n"/>
+      <c r="AD8" s="671" t="n"/>
+      <c r="AE8" s="671" t="n"/>
+      <c r="AF8" s="671" t="n"/>
+      <c r="AG8" s="671" t="n"/>
+      <c r="AH8" s="671" t="n"/>
+      <c r="AI8" s="671" t="n"/>
+      <c r="AJ8" s="671" t="n"/>
+      <c r="AK8" s="671" t="n"/>
+      <c r="AL8" s="671" t="n"/>
+      <c r="AM8" s="671" t="n"/>
+      <c r="AN8" s="671" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="671" t="n"/>
+      <c r="B9" s="673" t="n"/>
+      <c r="C9" s="673" t="n"/>
+      <c r="D9" s="671" t="n"/>
+      <c r="E9" s="671" t="n"/>
+      <c r="F9" s="671" t="n"/>
+      <c r="G9" s="671" t="n"/>
+      <c r="H9" s="671" t="n"/>
+      <c r="I9" s="671" t="n"/>
+      <c r="J9" s="671" t="n"/>
+      <c r="K9" s="671" t="n"/>
+      <c r="L9" s="671" t="n"/>
+      <c r="M9" s="671" t="n"/>
+      <c r="N9" s="671" t="n"/>
+      <c r="O9" s="671" t="n"/>
+      <c r="P9" s="671" t="n"/>
+      <c r="Q9" s="671" t="n"/>
+      <c r="R9" s="671" t="n"/>
+      <c r="S9" s="671" t="n"/>
+      <c r="T9" s="671" t="n"/>
+      <c r="U9" s="671" t="n"/>
+      <c r="V9" s="671" t="n"/>
+      <c r="W9" s="671" t="n"/>
+      <c r="X9" s="671" t="n"/>
+      <c r="Y9" s="671" t="n"/>
+      <c r="Z9" s="671" t="n"/>
+      <c r="AA9" s="671" t="n"/>
+      <c r="AB9" s="671" t="n"/>
+      <c r="AC9" s="671" t="n"/>
+      <c r="AD9" s="671" t="n"/>
+      <c r="AE9" s="671" t="n"/>
+      <c r="AF9" s="671" t="n"/>
+      <c r="AG9" s="671" t="n"/>
+      <c r="AH9" s="671" t="n"/>
+      <c r="AI9" s="671" t="n"/>
+      <c r="AJ9" s="671" t="n"/>
+      <c r="AK9" s="671" t="n"/>
+      <c r="AL9" s="671" t="n"/>
+      <c r="AM9" s="671" t="n"/>
+      <c r="AN9" s="671" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="727" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B10" s="674" t="inlineStr">
+        <is>
+          <t>Value / Reference</t>
+        </is>
+      </c>
+      <c r="C10" s="674" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D10" s="671" t="n"/>
+      <c r="E10" s="671" t="n"/>
+      <c r="F10" s="671" t="n"/>
+      <c r="G10" s="671" t="n"/>
+      <c r="H10" s="671" t="n"/>
+      <c r="I10" s="671" t="n"/>
+      <c r="J10" s="671" t="n"/>
+      <c r="K10" s="671" t="n"/>
+      <c r="L10" s="671" t="n"/>
+      <c r="M10" s="671" t="n"/>
+      <c r="N10" s="671" t="n"/>
+      <c r="O10" s="671" t="n"/>
+      <c r="P10" s="671" t="n"/>
+      <c r="Q10" s="671" t="n"/>
+      <c r="R10" s="671" t="n"/>
+      <c r="S10" s="671" t="n"/>
+      <c r="T10" s="671" t="n"/>
+      <c r="U10" s="671" t="n"/>
+      <c r="V10" s="671" t="n"/>
+      <c r="W10" s="671" t="n"/>
+      <c r="X10" s="671" t="n"/>
+      <c r="Y10" s="671" t="n"/>
+      <c r="Z10" s="671" t="n"/>
+      <c r="AA10" s="671" t="n"/>
+      <c r="AB10" s="671" t="n"/>
+      <c r="AC10" s="671" t="n"/>
+      <c r="AD10" s="671" t="n"/>
+      <c r="AE10" s="671" t="n"/>
+      <c r="AF10" s="671" t="n"/>
+      <c r="AG10" s="671" t="n"/>
+      <c r="AH10" s="671" t="n"/>
+      <c r="AI10" s="671" t="n"/>
+      <c r="AJ10" s="671" t="n"/>
+      <c r="AK10" s="671" t="n"/>
+      <c r="AL10" s="671" t="n"/>
+      <c r="AM10" s="671" t="n"/>
+      <c r="AN10" s="671" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="728" t="inlineStr">
+        <is>
+          <t>Source of Truth</t>
+        </is>
+      </c>
+      <c r="B11" s="733" t="inlineStr">
+        <is>
+          <t>Epicor transaction + M365 evidence</t>
+        </is>
+      </c>
+      <c r="C11" s="733" t="inlineStr">
+        <is>
+          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+        </is>
+      </c>
+      <c r="D11" s="671" t="n"/>
+      <c r="E11" s="671" t="n"/>
+      <c r="F11" s="671" t="n"/>
+      <c r="G11" s="671" t="n"/>
+      <c r="H11" s="671" t="n"/>
+      <c r="I11" s="671" t="n"/>
+      <c r="J11" s="671" t="n"/>
+      <c r="K11" s="671" t="n"/>
+      <c r="L11" s="671" t="n"/>
+      <c r="M11" s="671" t="n"/>
+      <c r="N11" s="671" t="n"/>
+      <c r="O11" s="671" t="n"/>
+      <c r="P11" s="671" t="n"/>
+      <c r="Q11" s="671" t="n"/>
+      <c r="R11" s="671" t="n"/>
+      <c r="S11" s="671" t="n"/>
+      <c r="T11" s="671" t="n"/>
+      <c r="U11" s="671" t="n"/>
+      <c r="V11" s="671" t="n"/>
+      <c r="W11" s="671" t="n"/>
+      <c r="X11" s="671" t="n"/>
+      <c r="Y11" s="671" t="n"/>
+      <c r="Z11" s="671" t="n"/>
+      <c r="AA11" s="671" t="n"/>
+      <c r="AB11" s="671" t="n"/>
+      <c r="AC11" s="671" t="n"/>
+      <c r="AD11" s="671" t="n"/>
+      <c r="AE11" s="671" t="n"/>
+      <c r="AF11" s="671" t="n"/>
+      <c r="AG11" s="671" t="n"/>
+      <c r="AH11" s="671" t="n"/>
+      <c r="AI11" s="671" t="n"/>
+      <c r="AJ11" s="671" t="n"/>
+      <c r="AK11" s="671" t="n"/>
+      <c r="AL11" s="671" t="n"/>
+      <c r="AM11" s="671" t="n"/>
+      <c r="AN11" s="671" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="729" t="inlineStr">
+        <is>
+          <t>Cross-Reference Boundary</t>
+        </is>
+      </c>
+      <c r="B12" s="734" t="inlineStr">
+        <is>
+          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
+        </is>
+      </c>
+      <c r="C12" s="735" t="inlineStr">
+        <is>
+          <t>This form does not replace SOP-605; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-605; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-001/002/003/004/006/007 + ANNEX-QMS-020; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+        </is>
+      </c>
+      <c r="D12" s="671" t="n"/>
+      <c r="E12" s="671" t="n"/>
+      <c r="F12" s="671" t="n"/>
+      <c r="G12" s="671" t="n"/>
+      <c r="H12" s="671" t="n"/>
+      <c r="I12" s="671" t="n"/>
+      <c r="J12" s="671" t="n"/>
+      <c r="K12" s="671" t="n"/>
+      <c r="L12" s="671" t="n"/>
+      <c r="M12" s="671" t="n"/>
+      <c r="N12" s="671" t="n"/>
+      <c r="O12" s="671" t="n"/>
+      <c r="P12" s="671" t="n"/>
+      <c r="Q12" s="671" t="n"/>
+      <c r="R12" s="671" t="n"/>
+      <c r="S12" s="671" t="n"/>
+      <c r="T12" s="671" t="n"/>
+      <c r="U12" s="671" t="n"/>
+      <c r="V12" s="671" t="n"/>
+      <c r="W12" s="671" t="n"/>
+      <c r="X12" s="671" t="n"/>
+      <c r="Y12" s="671" t="n"/>
+      <c r="Z12" s="671" t="n"/>
+      <c r="AA12" s="671" t="n"/>
+      <c r="AB12" s="671" t="n"/>
+      <c r="AC12" s="671" t="n"/>
+      <c r="AD12" s="671" t="n"/>
+      <c r="AE12" s="671" t="n"/>
+      <c r="AF12" s="671" t="n"/>
+      <c r="AG12" s="671" t="n"/>
+      <c r="AH12" s="671" t="n"/>
+      <c r="AI12" s="671" t="n"/>
+      <c r="AJ12" s="671" t="n"/>
+      <c r="AK12" s="671" t="n"/>
+      <c r="AL12" s="671" t="n"/>
+      <c r="AM12" s="671" t="n"/>
+      <c r="AN12" s="671" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="730" t="inlineStr">
+        <is>
+          <t>SOP SOP-605</t>
+        </is>
+      </c>
+      <c r="B13" s="736" t="inlineStr">
+        <is>
+          <t>SOP-605 — Kiểm tra cuối, CoC và phê duyệt giao hàng | HESEM QMS</t>
+        </is>
+      </c>
+      <c r="C13" s="737" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/06-SOP-600/sop-605-final-inspection-coc-and-shipment-release.html</t>
+        </is>
+      </c>
+      <c r="D13" s="671" t="n"/>
+      <c r="E13" s="671" t="n"/>
+      <c r="F13" s="671" t="n"/>
+      <c r="G13" s="671" t="n"/>
+      <c r="H13" s="671" t="n"/>
+      <c r="I13" s="671" t="n"/>
+      <c r="J13" s="671" t="n"/>
+      <c r="K13" s="671" t="n"/>
+      <c r="L13" s="671" t="n"/>
+      <c r="M13" s="671" t="n"/>
+      <c r="N13" s="671" t="n"/>
+      <c r="O13" s="671" t="n"/>
+      <c r="P13" s="671" t="n"/>
+      <c r="Q13" s="671" t="n"/>
+      <c r="R13" s="671" t="n"/>
+      <c r="S13" s="671" t="n"/>
+      <c r="T13" s="671" t="n"/>
+      <c r="U13" s="671" t="n"/>
+      <c r="V13" s="671" t="n"/>
+      <c r="W13" s="671" t="n"/>
+      <c r="X13" s="671" t="n"/>
+      <c r="Y13" s="671" t="n"/>
+      <c r="Z13" s="671" t="n"/>
+      <c r="AA13" s="671" t="n"/>
+      <c r="AB13" s="671" t="n"/>
+      <c r="AC13" s="671" t="n"/>
+      <c r="AD13" s="671" t="n"/>
+      <c r="AE13" s="671" t="n"/>
+      <c r="AF13" s="671" t="n"/>
+      <c r="AG13" s="671" t="n"/>
+      <c r="AH13" s="671" t="n"/>
+      <c r="AI13" s="671" t="n"/>
+      <c r="AJ13" s="671" t="n"/>
+      <c r="AK13" s="671" t="n"/>
+      <c r="AL13" s="671" t="n"/>
+      <c r="AM13" s="671" t="n"/>
+      <c r="AN13" s="671" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="731" t="inlineStr">
+        <is>
+          <t>WI WI-605</t>
+        </is>
+      </c>
+      <c r="B14" s="738" t="inlineStr">
+        <is>
+          <t>WI-605 — Kiểm cuối, CoC/CofC, bàn giao phát hành giao hàng</t>
+        </is>
+      </c>
+      <c r="C14" s="739" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/06-WI-600/wi-605-final-inspection-coc-and-shipment-release-handoff.html</t>
+        </is>
+      </c>
+      <c r="D14" s="671" t="n"/>
+      <c r="E14" s="671" t="n"/>
+      <c r="F14" s="671" t="n"/>
+      <c r="G14" s="671" t="n"/>
+      <c r="H14" s="671" t="n"/>
+      <c r="I14" s="671" t="n"/>
+      <c r="J14" s="671" t="n"/>
+      <c r="K14" s="671" t="n"/>
+      <c r="L14" s="671" t="n"/>
+      <c r="M14" s="671" t="n"/>
+      <c r="N14" s="671" t="n"/>
+      <c r="O14" s="671" t="n"/>
+      <c r="P14" s="671" t="n"/>
+      <c r="Q14" s="671" t="n"/>
+      <c r="R14" s="671" t="n"/>
+      <c r="S14" s="671" t="n"/>
+      <c r="T14" s="671" t="n"/>
+      <c r="U14" s="671" t="n"/>
+      <c r="V14" s="671" t="n"/>
+      <c r="W14" s="671" t="n"/>
+      <c r="X14" s="671" t="n"/>
+      <c r="Y14" s="671" t="n"/>
+      <c r="Z14" s="671" t="n"/>
+      <c r="AA14" s="671" t="n"/>
+      <c r="AB14" s="671" t="n"/>
+      <c r="AC14" s="671" t="n"/>
+      <c r="AD14" s="671" t="n"/>
+      <c r="AE14" s="671" t="n"/>
+      <c r="AF14" s="671" t="n"/>
+      <c r="AG14" s="671" t="n"/>
+      <c r="AH14" s="671" t="n"/>
+      <c r="AI14" s="671" t="n"/>
+      <c r="AJ14" s="671" t="n"/>
+      <c r="AK14" s="671" t="n"/>
+      <c r="AL14" s="671" t="n"/>
+      <c r="AM14" s="671" t="n"/>
+      <c r="AN14" s="671" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="731" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-001</t>
+        </is>
+      </c>
+      <c r="B15" s="738" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-001 — Quy tắc áp dụng AQL, cỡ mẫu và chuyển chế độ kiểm</t>
+        </is>
+      </c>
+      <c r="C15" s="739" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-001-aql-method-reference.html</t>
+        </is>
+      </c>
+      <c r="D15" s="671" t="n"/>
+      <c r="E15" s="671" t="n"/>
+      <c r="F15" s="671" t="n"/>
+      <c r="G15" s="671" t="n"/>
+      <c r="H15" s="671" t="n"/>
+      <c r="I15" s="671" t="n"/>
+      <c r="J15" s="671" t="n"/>
+      <c r="K15" s="671" t="n"/>
+      <c r="L15" s="671" t="n"/>
+      <c r="M15" s="671" t="n"/>
+      <c r="N15" s="671" t="n"/>
+      <c r="O15" s="671" t="n"/>
+      <c r="P15" s="671" t="n"/>
+      <c r="Q15" s="671" t="n"/>
+      <c r="R15" s="671" t="n"/>
+      <c r="S15" s="671" t="n"/>
+      <c r="T15" s="671" t="n"/>
+      <c r="U15" s="671" t="n"/>
+      <c r="V15" s="671" t="n"/>
+      <c r="W15" s="671" t="n"/>
+      <c r="X15" s="671" t="n"/>
+      <c r="Y15" s="671" t="n"/>
+      <c r="Z15" s="671" t="n"/>
+      <c r="AA15" s="671" t="n"/>
+      <c r="AB15" s="671" t="n"/>
+      <c r="AC15" s="671" t="n"/>
+      <c r="AD15" s="671" t="n"/>
+      <c r="AE15" s="671" t="n"/>
+      <c r="AF15" s="671" t="n"/>
+      <c r="AG15" s="671" t="n"/>
+      <c r="AH15" s="671" t="n"/>
+      <c r="AI15" s="671" t="n"/>
+      <c r="AJ15" s="671" t="n"/>
+      <c r="AK15" s="671" t="n"/>
+      <c r="AL15" s="671" t="n"/>
+      <c r="AM15" s="671" t="n"/>
+      <c r="AN15" s="671" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="731" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-002</t>
+        </is>
+      </c>
+      <c r="B16" s="740" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-002 — Tiêu chí chấp nhận MSA, GRR, bias, linearity, stability và attribute agreement</t>
+        </is>
+      </c>
+      <c r="C16" s="741" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-002-msa-acceptance-criteria.html</t>
+        </is>
+      </c>
+      <c r="D16" s="671" t="n"/>
+      <c r="E16" s="671" t="n"/>
+      <c r="F16" s="671" t="n"/>
+      <c r="G16" s="671" t="n"/>
+      <c r="H16" s="671" t="n"/>
+      <c r="I16" s="671" t="n"/>
+      <c r="J16" s="671" t="n"/>
+      <c r="K16" s="671" t="n"/>
+      <c r="L16" s="671" t="n"/>
+      <c r="M16" s="671" t="n"/>
+      <c r="N16" s="671" t="n"/>
+      <c r="O16" s="671" t="n"/>
+      <c r="P16" s="671" t="n"/>
+      <c r="Q16" s="671" t="n"/>
+      <c r="R16" s="671" t="n"/>
+      <c r="S16" s="671" t="n"/>
+      <c r="T16" s="671" t="n"/>
+      <c r="U16" s="671" t="n"/>
+      <c r="V16" s="671" t="n"/>
+      <c r="W16" s="671" t="n"/>
+      <c r="X16" s="671" t="n"/>
+      <c r="Y16" s="671" t="n"/>
+      <c r="Z16" s="671" t="n"/>
+      <c r="AA16" s="671" t="n"/>
+      <c r="AB16" s="671" t="n"/>
+      <c r="AC16" s="671" t="n"/>
+      <c r="AD16" s="671" t="n"/>
+      <c r="AE16" s="671" t="n"/>
+      <c r="AF16" s="671" t="n"/>
+      <c r="AG16" s="671" t="n"/>
+      <c r="AH16" s="671" t="n"/>
+      <c r="AI16" s="671" t="n"/>
+      <c r="AJ16" s="671" t="n"/>
+      <c r="AK16" s="671" t="n"/>
+      <c r="AL16" s="671" t="n"/>
+      <c r="AM16" s="671" t="n"/>
+      <c r="AN16" s="671" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="731" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-003</t>
+        </is>
+      </c>
+      <c r="B17" s="740" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-003 — QPL-1 đến QPL-4, bộ bằng chứng bắt buộc và quy tắc nâng/hạ cấp</t>
+        </is>
+      </c>
+      <c r="C17" s="741" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-003-quality-package-levels-qpl.html</t>
+        </is>
+      </c>
+      <c r="D17" s="671" t="n"/>
+      <c r="E17" s="671" t="n"/>
+      <c r="F17" s="671" t="n"/>
+      <c r="G17" s="671" t="n"/>
+      <c r="H17" s="671" t="n"/>
+      <c r="I17" s="671" t="n"/>
+      <c r="J17" s="671" t="n"/>
+      <c r="K17" s="671" t="n"/>
+      <c r="L17" s="671" t="n"/>
+      <c r="M17" s="671" t="n"/>
+      <c r="N17" s="671" t="n"/>
+      <c r="O17" s="671" t="n"/>
+      <c r="P17" s="671" t="n"/>
+      <c r="Q17" s="671" t="n"/>
+      <c r="R17" s="671" t="n"/>
+      <c r="S17" s="671" t="n"/>
+      <c r="T17" s="671" t="n"/>
+      <c r="U17" s="671" t="n"/>
+      <c r="V17" s="671" t="n"/>
+      <c r="W17" s="671" t="n"/>
+      <c r="X17" s="671" t="n"/>
+      <c r="Y17" s="671" t="n"/>
+      <c r="Z17" s="671" t="n"/>
+      <c r="AA17" s="671" t="n"/>
+      <c r="AB17" s="671" t="n"/>
+      <c r="AC17" s="671" t="n"/>
+      <c r="AD17" s="671" t="n"/>
+      <c r="AE17" s="671" t="n"/>
+      <c r="AF17" s="671" t="n"/>
+      <c r="AG17" s="671" t="n"/>
+      <c r="AH17" s="671" t="n"/>
+      <c r="AI17" s="671" t="n"/>
+      <c r="AJ17" s="671" t="n"/>
+      <c r="AK17" s="671" t="n"/>
+      <c r="AL17" s="671" t="n"/>
+      <c r="AM17" s="671" t="n"/>
+      <c r="AN17" s="671" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="731" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-004</t>
+        </is>
+      </c>
+      <c r="B18" s="740" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-004 — Chuẩn lập Control Plan cho Job order CNC</t>
+        </is>
+      </c>
+      <c r="C18" s="741" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-004-control-plan-guide.html</t>
+        </is>
+      </c>
+      <c r="D18" s="671" t="n"/>
+      <c r="E18" s="671" t="n"/>
+      <c r="F18" s="671" t="n"/>
+      <c r="G18" s="671" t="n"/>
+      <c r="H18" s="671" t="n"/>
+      <c r="I18" s="671" t="n"/>
+      <c r="J18" s="671" t="n"/>
+      <c r="K18" s="671" t="n"/>
+      <c r="L18" s="671" t="n"/>
+      <c r="M18" s="671" t="n"/>
+      <c r="N18" s="671" t="n"/>
+      <c r="O18" s="671" t="n"/>
+      <c r="P18" s="671" t="n"/>
+      <c r="Q18" s="671" t="n"/>
+      <c r="R18" s="671" t="n"/>
+      <c r="S18" s="671" t="n"/>
+      <c r="T18" s="671" t="n"/>
+      <c r="U18" s="671" t="n"/>
+      <c r="V18" s="671" t="n"/>
+      <c r="W18" s="671" t="n"/>
+      <c r="X18" s="671" t="n"/>
+      <c r="Y18" s="671" t="n"/>
+      <c r="Z18" s="671" t="n"/>
+      <c r="AA18" s="671" t="n"/>
+      <c r="AB18" s="671" t="n"/>
+      <c r="AC18" s="671" t="n"/>
+      <c r="AD18" s="671" t="n"/>
+      <c r="AE18" s="671" t="n"/>
+      <c r="AF18" s="671" t="n"/>
+      <c r="AG18" s="671" t="n"/>
+      <c r="AH18" s="671" t="n"/>
+      <c r="AI18" s="671" t="n"/>
+      <c r="AJ18" s="671" t="n"/>
+      <c r="AK18" s="671" t="n"/>
+      <c r="AL18" s="671" t="n"/>
+      <c r="AM18" s="671" t="n"/>
+      <c r="AN18" s="671" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="731" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-006</t>
+        </is>
+      </c>
+      <c r="B19" s="740" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-006 — Thông số SPC, chọn biểu đồ, capability và reaction plan</t>
+        </is>
+      </c>
+      <c r="C19" s="741" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-006-spc-lite-and-reaction-plan.html</t>
+        </is>
+      </c>
+      <c r="D19" s="671" t="n"/>
+      <c r="E19" s="671" t="n"/>
+      <c r="F19" s="671" t="n"/>
+      <c r="G19" s="671" t="n"/>
+      <c r="H19" s="671" t="n"/>
+      <c r="I19" s="671" t="n"/>
+      <c r="J19" s="671" t="n"/>
+      <c r="K19" s="671" t="n"/>
+      <c r="L19" s="671" t="n"/>
+      <c r="M19" s="671" t="n"/>
+      <c r="N19" s="671" t="n"/>
+      <c r="O19" s="671" t="n"/>
+      <c r="P19" s="671" t="n"/>
+      <c r="Q19" s="671" t="n"/>
+      <c r="R19" s="671" t="n"/>
+      <c r="S19" s="671" t="n"/>
+      <c r="T19" s="671" t="n"/>
+      <c r="U19" s="671" t="n"/>
+      <c r="V19" s="671" t="n"/>
+      <c r="W19" s="671" t="n"/>
+      <c r="X19" s="671" t="n"/>
+      <c r="Y19" s="671" t="n"/>
+      <c r="Z19" s="671" t="n"/>
+      <c r="AA19" s="671" t="n"/>
+      <c r="AB19" s="671" t="n"/>
+      <c r="AC19" s="671" t="n"/>
+      <c r="AD19" s="671" t="n"/>
+      <c r="AE19" s="671" t="n"/>
+      <c r="AF19" s="671" t="n"/>
+      <c r="AG19" s="671" t="n"/>
+      <c r="AH19" s="671" t="n"/>
+      <c r="AI19" s="671" t="n"/>
+      <c r="AJ19" s="671" t="n"/>
+      <c r="AK19" s="671" t="n"/>
+      <c r="AL19" s="671" t="n"/>
+      <c r="AM19" s="671" t="n"/>
+      <c r="AN19" s="671" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="731" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QA-007</t>
+        </is>
+      </c>
+      <c r="B20" s="740" t="inlineStr">
+        <is>
+          <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
+        </is>
+      </c>
+      <c r="C20" s="741" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
+        </is>
+      </c>
+      <c r="D20" s="671" t="n"/>
+      <c r="E20" s="671" t="n"/>
+      <c r="F20" s="671" t="n"/>
+      <c r="G20" s="671" t="n"/>
+      <c r="H20" s="671" t="n"/>
+      <c r="I20" s="671" t="n"/>
+      <c r="J20" s="671" t="n"/>
+      <c r="K20" s="671" t="n"/>
+      <c r="L20" s="671" t="n"/>
+      <c r="M20" s="671" t="n"/>
+      <c r="N20" s="671" t="n"/>
+      <c r="O20" s="671" t="n"/>
+      <c r="P20" s="671" t="n"/>
+      <c r="Q20" s="671" t="n"/>
+      <c r="R20" s="671" t="n"/>
+      <c r="S20" s="671" t="n"/>
+      <c r="T20" s="671" t="n"/>
+      <c r="U20" s="671" t="n"/>
+      <c r="V20" s="671" t="n"/>
+      <c r="W20" s="671" t="n"/>
+      <c r="X20" s="671" t="n"/>
+      <c r="Y20" s="671" t="n"/>
+      <c r="Z20" s="671" t="n"/>
+      <c r="AA20" s="671" t="n"/>
+      <c r="AB20" s="671" t="n"/>
+      <c r="AC20" s="671" t="n"/>
+      <c r="AD20" s="671" t="n"/>
+      <c r="AE20" s="671" t="n"/>
+      <c r="AF20" s="671" t="n"/>
+      <c r="AG20" s="671" t="n"/>
+      <c r="AH20" s="671" t="n"/>
+      <c r="AI20" s="671" t="n"/>
+      <c r="AJ20" s="671" t="n"/>
+      <c r="AK20" s="671" t="n"/>
+      <c r="AL20" s="671" t="n"/>
+      <c r="AM20" s="671" t="n"/>
+      <c r="AN20" s="671" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="732" t="inlineStr">
+        <is>
+          <t>ANNEX ANNEX-QMS-020</t>
+        </is>
+      </c>
+      <c r="B21" s="742" t="inlineStr">
+        <is>
+          <t>ANNEX-QMS-020 — Ma trận escalation, SLA phản ứng, liên lạc theo cấp và quyền quyết định</t>
+        </is>
+      </c>
+      <c r="C21" s="743" t="inlineStr">
+        <is>
+          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/01-ANNEX-System/annex-qms-020-escalation-matrix-and-sla.html</t>
+        </is>
+      </c>
+      <c r="D21" s="671" t="n"/>
+      <c r="E21" s="671" t="n"/>
+      <c r="F21" s="671" t="n"/>
+      <c r="G21" s="671" t="n"/>
+      <c r="H21" s="671" t="n"/>
+      <c r="I21" s="671" t="n"/>
+      <c r="J21" s="671" t="n"/>
+      <c r="K21" s="671" t="n"/>
+      <c r="L21" s="671" t="n"/>
+      <c r="M21" s="671" t="n"/>
+      <c r="N21" s="671" t="n"/>
+      <c r="O21" s="671" t="n"/>
+      <c r="P21" s="671" t="n"/>
+      <c r="Q21" s="671" t="n"/>
+      <c r="R21" s="671" t="n"/>
+      <c r="S21" s="671" t="n"/>
+      <c r="T21" s="671" t="n"/>
+      <c r="U21" s="671" t="n"/>
+      <c r="V21" s="671" t="n"/>
+      <c r="W21" s="671" t="n"/>
+      <c r="X21" s="671" t="n"/>
+      <c r="Y21" s="671" t="n"/>
+      <c r="Z21" s="671" t="n"/>
+      <c r="AA21" s="671" t="n"/>
+      <c r="AB21" s="671" t="n"/>
+      <c r="AC21" s="671" t="n"/>
+      <c r="AD21" s="671" t="n"/>
+      <c r="AE21" s="671" t="n"/>
+      <c r="AF21" s="671" t="n"/>
+      <c r="AG21" s="671" t="n"/>
+      <c r="AH21" s="671" t="n"/>
+      <c r="AI21" s="671" t="n"/>
+      <c r="AJ21" s="671" t="n"/>
+      <c r="AK21" s="671" t="n"/>
+      <c r="AL21" s="671" t="n"/>
+      <c r="AM21" s="671" t="n"/>
+      <c r="AN21" s="671" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="671" t="n"/>
+      <c r="B22" s="671" t="n"/>
+      <c r="C22" s="671" t="n"/>
+      <c r="D22" s="671" t="n"/>
+      <c r="E22" s="671" t="n"/>
+      <c r="F22" s="671" t="n"/>
+      <c r="G22" s="671" t="n"/>
+      <c r="H22" s="671" t="n"/>
+      <c r="I22" s="671" t="n"/>
+      <c r="J22" s="671" t="n"/>
+      <c r="K22" s="671" t="n"/>
+      <c r="L22" s="671" t="n"/>
+      <c r="M22" s="671" t="n"/>
+      <c r="N22" s="671" t="n"/>
+      <c r="O22" s="671" t="n"/>
+      <c r="P22" s="671" t="n"/>
+      <c r="Q22" s="671" t="n"/>
+      <c r="R22" s="671" t="n"/>
+      <c r="S22" s="671" t="n"/>
+      <c r="T22" s="671" t="n"/>
+      <c r="U22" s="671" t="n"/>
+      <c r="V22" s="671" t="n"/>
+      <c r="W22" s="671" t="n"/>
+      <c r="X22" s="671" t="n"/>
+      <c r="Y22" s="671" t="n"/>
+      <c r="Z22" s="671" t="n"/>
+      <c r="AA22" s="671" t="n"/>
+      <c r="AB22" s="671" t="n"/>
+      <c r="AC22" s="671" t="n"/>
+      <c r="AD22" s="671" t="n"/>
+      <c r="AE22" s="671" t="n"/>
+      <c r="AF22" s="671" t="n"/>
+      <c r="AG22" s="671" t="n"/>
+      <c r="AH22" s="671" t="n"/>
+      <c r="AI22" s="671" t="n"/>
+      <c r="AJ22" s="671" t="n"/>
+      <c r="AK22" s="671" t="n"/>
+      <c r="AL22" s="671" t="n"/>
+      <c r="AM22" s="671" t="n"/>
+      <c r="AN22" s="671" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="671" t="n"/>
+      <c r="B23" s="671" t="n"/>
+      <c r="C23" s="671" t="n"/>
+      <c r="D23" s="671" t="n"/>
+      <c r="E23" s="671" t="n"/>
+      <c r="F23" s="671" t="n"/>
+      <c r="G23" s="671" t="n"/>
+      <c r="H23" s="671" t="n"/>
+      <c r="I23" s="671" t="n"/>
+      <c r="J23" s="671" t="n"/>
+      <c r="K23" s="671" t="n"/>
+      <c r="L23" s="671" t="n"/>
+      <c r="M23" s="671" t="n"/>
+      <c r="N23" s="671" t="n"/>
+      <c r="O23" s="671" t="n"/>
+      <c r="P23" s="671" t="n"/>
+      <c r="Q23" s="671" t="n"/>
+      <c r="R23" s="671" t="n"/>
+      <c r="S23" s="671" t="n"/>
+      <c r="T23" s="671" t="n"/>
+      <c r="U23" s="671" t="n"/>
+      <c r="V23" s="671" t="n"/>
+      <c r="W23" s="671" t="n"/>
+      <c r="X23" s="671" t="n"/>
+      <c r="Y23" s="671" t="n"/>
+      <c r="Z23" s="671" t="n"/>
+      <c r="AA23" s="671" t="n"/>
+      <c r="AB23" s="671" t="n"/>
+      <c r="AC23" s="671" t="n"/>
+      <c r="AD23" s="671" t="n"/>
+      <c r="AE23" s="671" t="n"/>
+      <c r="AF23" s="671" t="n"/>
+      <c r="AG23" s="671" t="n"/>
+      <c r="AH23" s="671" t="n"/>
+      <c r="AI23" s="671" t="n"/>
+      <c r="AJ23" s="671" t="n"/>
+      <c r="AK23" s="671" t="n"/>
+      <c r="AL23" s="671" t="n"/>
+      <c r="AM23" s="671" t="n"/>
+      <c r="AN23" s="671" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="671" t="n"/>
+      <c r="B24" s="671" t="n"/>
+      <c r="C24" s="671" t="n"/>
+      <c r="D24" s="671" t="n"/>
+      <c r="E24" s="671" t="n"/>
+      <c r="F24" s="671" t="n"/>
+      <c r="G24" s="671" t="n"/>
+      <c r="H24" s="671" t="n"/>
+      <c r="I24" s="671" t="n"/>
+      <c r="J24" s="671" t="n"/>
+      <c r="K24" s="671" t="n"/>
+      <c r="L24" s="671" t="n"/>
+      <c r="M24" s="671" t="n"/>
+      <c r="N24" s="671" t="n"/>
+      <c r="O24" s="671" t="n"/>
+      <c r="P24" s="671" t="n"/>
+      <c r="Q24" s="671" t="n"/>
+      <c r="R24" s="671" t="n"/>
+      <c r="S24" s="671" t="n"/>
+      <c r="T24" s="671" t="n"/>
+      <c r="U24" s="671" t="n"/>
+      <c r="V24" s="671" t="n"/>
+      <c r="W24" s="671" t="n"/>
+      <c r="X24" s="671" t="n"/>
+      <c r="Y24" s="671" t="n"/>
+      <c r="Z24" s="671" t="n"/>
+      <c r="AA24" s="671" t="n"/>
+      <c r="AB24" s="671" t="n"/>
+      <c r="AC24" s="671" t="n"/>
+      <c r="AD24" s="671" t="n"/>
+      <c r="AE24" s="671" t="n"/>
+      <c r="AF24" s="671" t="n"/>
+      <c r="AG24" s="671" t="n"/>
+      <c r="AH24" s="671" t="n"/>
+      <c r="AI24" s="671" t="n"/>
+      <c r="AJ24" s="671" t="n"/>
+      <c r="AK24" s="671" t="n"/>
+      <c r="AL24" s="671" t="n"/>
+      <c r="AM24" s="671" t="n"/>
+      <c r="AN24" s="671" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C15"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" hidden="1">
+      <c r="A1" s="711" t="n"/>
+      <c r="B1" s="599" t="n"/>
+      <c r="C1" s="599" t="n"/>
+      <c r="D1" s="599" t="n"/>
+      <c r="E1" s="599" t="n"/>
+      <c r="F1" s="599" t="n"/>
+      <c r="G1" s="599" t="n"/>
+      <c r="H1" s="712" t="n"/>
+      <c r="I1" s="713" t="inlineStr">
+        <is>
+          <t>Final Inspection Report</t>
+        </is>
+      </c>
+      <c r="J1" s="599" t="n"/>
+      <c r="K1" s="599" t="n"/>
+      <c r="L1" s="599" t="n"/>
+      <c r="M1" s="599" t="n"/>
+      <c r="N1" s="599" t="n"/>
+      <c r="O1" s="599" t="n"/>
+      <c r="P1" s="599" t="n"/>
+      <c r="Q1" s="599" t="n"/>
+      <c r="R1" s="599" t="n"/>
+      <c r="S1" s="599" t="n"/>
+      <c r="T1" s="599" t="n"/>
+      <c r="U1" s="599" t="n"/>
+      <c r="V1" s="599" t="n"/>
+      <c r="W1" s="599" t="n"/>
+      <c r="X1" s="599" t="n"/>
+      <c r="Y1" s="599" t="n"/>
+      <c r="Z1" s="599" t="n"/>
+      <c r="AA1" s="599" t="n"/>
+      <c r="AB1" s="599" t="n"/>
+      <c r="AC1" s="599" t="n"/>
+      <c r="AD1" s="712" t="n"/>
+      <c r="AE1" s="433" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="599" t="n"/>
+      <c r="AG1" s="599" t="n"/>
+      <c r="AH1" s="714" t="n"/>
+      <c r="AI1" s="436" t="inlineStr">
+        <is>
+          <t>FRM-641</t>
+        </is>
+      </c>
+      <c r="AJ1" s="599" t="n"/>
+      <c r="AK1" s="599" t="n"/>
+      <c r="AL1" s="599" t="n"/>
+      <c r="AM1" s="599" t="n"/>
+      <c r="AN1" s="712" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="684" t="n"/>
+      <c r="C2" s="684" t="n"/>
+      <c r="D2" s="684" t="n"/>
+      <c r="E2" s="684" t="n"/>
+      <c r="F2" s="684" t="n"/>
+      <c r="G2" s="684" t="n"/>
+      <c r="H2" s="685" t="n"/>
+      <c r="I2" s="684" t="n"/>
+      <c r="J2" s="684" t="n"/>
+      <c r="K2" s="684" t="n"/>
+      <c r="L2" s="684" t="n"/>
+      <c r="M2" s="684" t="n"/>
+      <c r="N2" s="684" t="n"/>
+      <c r="O2" s="684" t="n"/>
+      <c r="P2" s="684" t="n"/>
+      <c r="Q2" s="684" t="n"/>
+      <c r="R2" s="684" t="n"/>
+      <c r="S2" s="684" t="n"/>
+      <c r="T2" s="684" t="n"/>
+      <c r="U2" s="684" t="n"/>
+      <c r="V2" s="684" t="n"/>
+      <c r="W2" s="684" t="n"/>
+      <c r="X2" s="684" t="n"/>
+      <c r="Y2" s="684" t="n"/>
+      <c r="Z2" s="684" t="n"/>
+      <c r="AA2" s="684" t="n"/>
+      <c r="AB2" s="684" t="n"/>
+      <c r="AC2" s="684" t="n"/>
+      <c r="AD2" s="685" t="n"/>
+      <c r="AE2" s="686" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="687" t="n"/>
+      <c r="AG2" s="687" t="n"/>
+      <c r="AH2" s="688" t="n"/>
+      <c r="AI2" s="7" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="689" t="n"/>
+      <c r="AK2" s="689" t="n"/>
+      <c r="AL2" s="689" t="n"/>
+      <c r="AM2" s="689" t="n"/>
+      <c r="AN2" s="690" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="691" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="692" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="692" t="n"/>
+      <c r="AE3" s="693" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="694" t="n"/>
+      <c r="AG3" s="694" t="n"/>
+      <c r="AH3" s="695" t="n"/>
+      <c r="AI3" s="14" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="696" t="n"/>
+      <c r="AK3" s="696" t="n"/>
+      <c r="AL3" s="696" t="n"/>
+      <c r="AM3" s="696" t="n"/>
+      <c r="AN3" s="697" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="691" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="692" t="n"/>
+      <c r="I4" s="698" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="692" t="n"/>
+      <c r="AE4" s="693" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="694" t="n"/>
+      <c r="AG4" s="694" t="n"/>
+      <c r="AH4" s="695" t="n"/>
+      <c r="AI4" s="14" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="696" t="n"/>
+      <c r="AK4" s="696" t="n"/>
+      <c r="AL4" s="696" t="n"/>
+      <c r="AM4" s="696" t="n"/>
+      <c r="AN4" s="697" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="691" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="692" t="n"/>
+      <c r="I5" s="699" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="692" t="n"/>
+      <c r="AE5" s="693" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="694" t="n"/>
+      <c r="AG5" s="694" t="n"/>
+      <c r="AH5" s="695" t="n"/>
+      <c r="AI5" s="14" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="696" t="n"/>
+      <c r="AK5" s="696" t="n"/>
+      <c r="AL5" s="696" t="n"/>
+      <c r="AM5" s="696" t="n"/>
+      <c r="AN5" s="697" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="715" t="n"/>
+      <c r="B6" s="724" t="n"/>
+      <c r="C6" s="724" t="n"/>
+      <c r="D6" s="716" t="n"/>
+      <c r="E6" s="716" t="n"/>
+      <c r="F6" s="716" t="n"/>
+      <c r="G6" s="716" t="n"/>
+      <c r="H6" s="717" t="n"/>
+      <c r="I6" s="716" t="n"/>
+      <c r="J6" s="716" t="n"/>
+      <c r="K6" s="716" t="n"/>
+      <c r="L6" s="716" t="n"/>
+      <c r="M6" s="716" t="n"/>
+      <c r="N6" s="716" t="n"/>
+      <c r="O6" s="716" t="n"/>
+      <c r="P6" s="716" t="n"/>
+      <c r="Q6" s="716" t="n"/>
+      <c r="R6" s="716" t="n"/>
+      <c r="S6" s="716" t="n"/>
+      <c r="T6" s="716" t="n"/>
+      <c r="U6" s="716" t="n"/>
+      <c r="V6" s="716" t="n"/>
+      <c r="W6" s="716" t="n"/>
+      <c r="X6" s="716" t="n"/>
+      <c r="Y6" s="716" t="n"/>
+      <c r="Z6" s="716" t="n"/>
+      <c r="AA6" s="716" t="n"/>
+      <c r="AB6" s="716" t="n"/>
+      <c r="AC6" s="716" t="n"/>
+      <c r="AD6" s="717" t="n"/>
+      <c r="AE6" s="718" t="n"/>
+      <c r="AF6" s="718" t="n"/>
+      <c r="AG6" s="718" t="n"/>
+      <c r="AH6" s="719" t="n"/>
+      <c r="AI6" s="720" t="n"/>
+      <c r="AJ6" s="720" t="n"/>
+      <c r="AK6" s="720" t="n"/>
+      <c r="AL6" s="720" t="n"/>
+      <c r="AM6" s="720" t="n"/>
+      <c r="AN6" s="721" t="n"/>
+    </row>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="725" t="n"/>
+      <c r="B7" s="708" t="n"/>
+      <c r="C7" s="708" t="n"/>
+      <c r="D7" s="708" t="n"/>
+      <c r="E7" s="708" t="n"/>
+      <c r="F7" s="708" t="n"/>
+      <c r="G7" s="708" t="n"/>
+      <c r="H7" s="723" t="n"/>
+      <c r="I7" s="723" t="n"/>
+      <c r="J7" s="723" t="n"/>
+      <c r="K7" s="723" t="n"/>
+      <c r="L7" s="723" t="n"/>
+      <c r="M7" s="723" t="n"/>
+      <c r="N7" s="723" t="n"/>
+      <c r="O7" s="723" t="n"/>
+      <c r="P7" s="723" t="n"/>
+      <c r="Q7" s="723" t="n"/>
+      <c r="R7" s="723" t="n"/>
+      <c r="S7" s="723" t="n"/>
+      <c r="T7" s="723" t="n"/>
+      <c r="U7" s="723" t="n"/>
+      <c r="V7" s="723" t="n"/>
+      <c r="W7" s="723" t="n"/>
+      <c r="X7" s="723" t="n"/>
+      <c r="Y7" s="723" t="n"/>
+      <c r="Z7" s="723" t="n"/>
+      <c r="AA7" s="723" t="n"/>
+      <c r="AB7" s="723" t="n"/>
+      <c r="AC7" s="723" t="n"/>
+      <c r="AD7" s="723" t="n"/>
+      <c r="AE7" s="723" t="n"/>
+      <c r="AF7" s="723" t="n"/>
+      <c r="AG7" s="723" t="n"/>
+      <c r="AH7" s="723" t="n"/>
+      <c r="AI7" s="723" t="n"/>
+      <c r="AJ7" s="723" t="n"/>
+      <c r="AK7" s="723" t="n"/>
+      <c r="AL7" s="723" t="n"/>
+      <c r="AM7" s="723" t="n"/>
+      <c r="AN7" s="723" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="726" t="inlineStr">
+        <is>
+          <t>Tie every acceptance or rejection decision to a unique evidence package.</t>
+        </is>
+      </c>
+      <c r="H8" s="671" t="n"/>
+      <c r="I8" s="671" t="n"/>
+      <c r="J8" s="671" t="n"/>
+      <c r="K8" s="671" t="n"/>
+      <c r="L8" s="671" t="n"/>
+      <c r="M8" s="671" t="n"/>
+      <c r="N8" s="671" t="n"/>
+      <c r="O8" s="671" t="n"/>
+      <c r="P8" s="671" t="n"/>
+      <c r="Q8" s="671" t="n"/>
+      <c r="R8" s="671" t="n"/>
+      <c r="S8" s="671" t="n"/>
+      <c r="T8" s="671" t="n"/>
+      <c r="U8" s="671" t="n"/>
+      <c r="V8" s="671" t="n"/>
+      <c r="W8" s="671" t="n"/>
+      <c r="X8" s="671" t="n"/>
+      <c r="Y8" s="671" t="n"/>
+      <c r="Z8" s="671" t="n"/>
+      <c r="AA8" s="671" t="n"/>
+      <c r="AB8" s="671" t="n"/>
+      <c r="AC8" s="671" t="n"/>
+      <c r="AD8" s="671" t="n"/>
+      <c r="AE8" s="671" t="n"/>
+      <c r="AF8" s="671" t="n"/>
+      <c r="AG8" s="671" t="n"/>
+      <c r="AH8" s="671" t="n"/>
+      <c r="AI8" s="671" t="n"/>
+      <c r="AJ8" s="671" t="n"/>
+      <c r="AK8" s="671" t="n"/>
+      <c r="AL8" s="671" t="n"/>
+      <c r="AM8" s="671" t="n"/>
+      <c r="AN8" s="671" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="671" t="n"/>
+      <c r="B9" s="671" t="n"/>
+      <c r="C9" s="671" t="n"/>
+      <c r="D9" s="671" t="n"/>
+      <c r="E9" s="671" t="n"/>
+      <c r="F9" s="671" t="n"/>
+      <c r="G9" s="671" t="n"/>
+      <c r="H9" s="671" t="n"/>
+      <c r="I9" s="671" t="n"/>
+      <c r="J9" s="671" t="n"/>
+      <c r="K9" s="671" t="n"/>
+      <c r="L9" s="671" t="n"/>
+      <c r="M9" s="671" t="n"/>
+      <c r="N9" s="671" t="n"/>
+      <c r="O9" s="671" t="n"/>
+      <c r="P9" s="671" t="n"/>
+      <c r="Q9" s="671" t="n"/>
+      <c r="R9" s="671" t="n"/>
+      <c r="S9" s="671" t="n"/>
+      <c r="T9" s="671" t="n"/>
+      <c r="U9" s="671" t="n"/>
+      <c r="V9" s="671" t="n"/>
+      <c r="W9" s="671" t="n"/>
+      <c r="X9" s="671" t="n"/>
+      <c r="Y9" s="671" t="n"/>
+      <c r="Z9" s="671" t="n"/>
+      <c r="AA9" s="671" t="n"/>
+      <c r="AB9" s="671" t="n"/>
+      <c r="AC9" s="671" t="n"/>
+      <c r="AD9" s="671" t="n"/>
+      <c r="AE9" s="671" t="n"/>
+      <c r="AF9" s="671" t="n"/>
+      <c r="AG9" s="671" t="n"/>
+      <c r="AH9" s="671" t="n"/>
+      <c r="AI9" s="671" t="n"/>
+      <c r="AJ9" s="671" t="n"/>
+      <c r="AK9" s="671" t="n"/>
+      <c r="AL9" s="671" t="n"/>
+      <c r="AM9" s="671" t="n"/>
+      <c r="AN9" s="671" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="727" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B10" s="517" t="inlineStr">
+        <is>
+          <t>Value / Reference</t>
+        </is>
+      </c>
+      <c r="C10" s="517" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D10" s="671" t="n"/>
+      <c r="E10" s="671" t="n"/>
+      <c r="F10" s="671" t="n"/>
+      <c r="G10" s="671" t="n"/>
+      <c r="H10" s="671" t="n"/>
+      <c r="I10" s="671" t="n"/>
+      <c r="J10" s="671" t="n"/>
+      <c r="K10" s="671" t="n"/>
+      <c r="L10" s="671" t="n"/>
+      <c r="M10" s="671" t="n"/>
+      <c r="N10" s="671" t="n"/>
+      <c r="O10" s="671" t="n"/>
+      <c r="P10" s="671" t="n"/>
+      <c r="Q10" s="671" t="n"/>
+      <c r="R10" s="671" t="n"/>
+      <c r="S10" s="671" t="n"/>
+      <c r="T10" s="671" t="n"/>
+      <c r="U10" s="671" t="n"/>
+      <c r="V10" s="671" t="n"/>
+      <c r="W10" s="671" t="n"/>
+      <c r="X10" s="671" t="n"/>
+      <c r="Y10" s="671" t="n"/>
+      <c r="Z10" s="671" t="n"/>
+      <c r="AA10" s="671" t="n"/>
+      <c r="AB10" s="671" t="n"/>
+      <c r="AC10" s="671" t="n"/>
+      <c r="AD10" s="671" t="n"/>
+      <c r="AE10" s="671" t="n"/>
+      <c r="AF10" s="671" t="n"/>
+      <c r="AG10" s="671" t="n"/>
+      <c r="AH10" s="671" t="n"/>
+      <c r="AI10" s="671" t="n"/>
+      <c r="AJ10" s="671" t="n"/>
+      <c r="AK10" s="671" t="n"/>
+      <c r="AL10" s="671" t="n"/>
+      <c r="AM10" s="671" t="n"/>
+      <c r="AN10" s="671" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="728" t="inlineStr">
+        <is>
+          <t>Evidence item 1</t>
+        </is>
+      </c>
+      <c r="B11" s="744" t="inlineStr">
+        <is>
+          <t>Reference to the correct evidence folder, shared location or dossier package.</t>
+        </is>
+      </c>
+      <c r="C11" s="744" t="inlineStr">
+        <is>
+          <t>Link or reference ID</t>
+        </is>
+      </c>
+      <c r="D11" s="671" t="n"/>
+      <c r="E11" s="671" t="n"/>
+      <c r="F11" s="671" t="n"/>
+      <c r="G11" s="671" t="n"/>
+      <c r="H11" s="671" t="n"/>
+      <c r="I11" s="671" t="n"/>
+      <c r="J11" s="671" t="n"/>
+      <c r="K11" s="671" t="n"/>
+      <c r="L11" s="671" t="n"/>
+      <c r="M11" s="671" t="n"/>
+      <c r="N11" s="671" t="n"/>
+      <c r="O11" s="671" t="n"/>
+      <c r="P11" s="671" t="n"/>
+      <c r="Q11" s="671" t="n"/>
+      <c r="R11" s="671" t="n"/>
+      <c r="S11" s="671" t="n"/>
+      <c r="T11" s="671" t="n"/>
+      <c r="U11" s="671" t="n"/>
+      <c r="V11" s="671" t="n"/>
+      <c r="W11" s="671" t="n"/>
+      <c r="X11" s="671" t="n"/>
+      <c r="Y11" s="671" t="n"/>
+      <c r="Z11" s="671" t="n"/>
+      <c r="AA11" s="671" t="n"/>
+      <c r="AB11" s="671" t="n"/>
+      <c r="AC11" s="671" t="n"/>
+      <c r="AD11" s="671" t="n"/>
+      <c r="AE11" s="671" t="n"/>
+      <c r="AF11" s="671" t="n"/>
+      <c r="AG11" s="671" t="n"/>
+      <c r="AH11" s="671" t="n"/>
+      <c r="AI11" s="671" t="n"/>
+      <c r="AJ11" s="671" t="n"/>
+      <c r="AK11" s="671" t="n"/>
+      <c r="AL11" s="671" t="n"/>
+      <c r="AM11" s="671" t="n"/>
+      <c r="AN11" s="671" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="729" t="inlineStr">
+        <is>
+          <t>Evidence item 2</t>
+        </is>
+      </c>
+      <c r="B12" s="745" t="inlineStr">
+        <is>
+          <t>Measurement raw data, certificates, study files, inspection reports, nonconformity evidence and closure evidence as applicable.</t>
+        </is>
+      </c>
+      <c r="C12" s="746" t="inlineStr">
+        <is>
+          <t>Link or reference ID</t>
+        </is>
+      </c>
+      <c r="D12" s="671" t="n"/>
+      <c r="E12" s="671" t="n"/>
+      <c r="F12" s="671" t="n"/>
+      <c r="G12" s="671" t="n"/>
+      <c r="H12" s="671" t="n"/>
+      <c r="I12" s="671" t="n"/>
+      <c r="J12" s="671" t="n"/>
+      <c r="K12" s="671" t="n"/>
+      <c r="L12" s="671" t="n"/>
+      <c r="M12" s="671" t="n"/>
+      <c r="N12" s="671" t="n"/>
+      <c r="O12" s="671" t="n"/>
+      <c r="P12" s="671" t="n"/>
+      <c r="Q12" s="671" t="n"/>
+      <c r="R12" s="671" t="n"/>
+      <c r="S12" s="671" t="n"/>
+      <c r="T12" s="671" t="n"/>
+      <c r="U12" s="671" t="n"/>
+      <c r="V12" s="671" t="n"/>
+      <c r="W12" s="671" t="n"/>
+      <c r="X12" s="671" t="n"/>
+      <c r="Y12" s="671" t="n"/>
+      <c r="Z12" s="671" t="n"/>
+      <c r="AA12" s="671" t="n"/>
+      <c r="AB12" s="671" t="n"/>
+      <c r="AC12" s="671" t="n"/>
+      <c r="AD12" s="671" t="n"/>
+      <c r="AE12" s="671" t="n"/>
+      <c r="AF12" s="671" t="n"/>
+      <c r="AG12" s="671" t="n"/>
+      <c r="AH12" s="671" t="n"/>
+      <c r="AI12" s="671" t="n"/>
+      <c r="AJ12" s="671" t="n"/>
+      <c r="AK12" s="671" t="n"/>
+      <c r="AL12" s="671" t="n"/>
+      <c r="AM12" s="671" t="n"/>
+      <c r="AN12" s="671" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="730" t="inlineStr">
+        <is>
+          <t>Open When</t>
+        </is>
+      </c>
+      <c r="B13" s="747" t="inlineStr">
+        <is>
+          <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
+        </is>
+      </c>
+      <c r="C13" s="748" t="inlineStr">
+        <is>
+          <t>Operational trigger</t>
+        </is>
+      </c>
+      <c r="D13" s="671" t="n"/>
+      <c r="E13" s="671" t="n"/>
+      <c r="F13" s="671" t="n"/>
+      <c r="G13" s="671" t="n"/>
+      <c r="H13" s="671" t="n"/>
+      <c r="I13" s="671" t="n"/>
+      <c r="J13" s="671" t="n"/>
+      <c r="K13" s="671" t="n"/>
+      <c r="L13" s="671" t="n"/>
+      <c r="M13" s="671" t="n"/>
+      <c r="N13" s="671" t="n"/>
+      <c r="O13" s="671" t="n"/>
+      <c r="P13" s="671" t="n"/>
+      <c r="Q13" s="671" t="n"/>
+      <c r="R13" s="671" t="n"/>
+      <c r="S13" s="671" t="n"/>
+      <c r="T13" s="671" t="n"/>
+      <c r="U13" s="671" t="n"/>
+      <c r="V13" s="671" t="n"/>
+      <c r="W13" s="671" t="n"/>
+      <c r="X13" s="671" t="n"/>
+      <c r="Y13" s="671" t="n"/>
+      <c r="Z13" s="671" t="n"/>
+      <c r="AA13" s="671" t="n"/>
+      <c r="AB13" s="671" t="n"/>
+      <c r="AC13" s="671" t="n"/>
+      <c r="AD13" s="671" t="n"/>
+      <c r="AE13" s="671" t="n"/>
+      <c r="AF13" s="671" t="n"/>
+      <c r="AG13" s="671" t="n"/>
+      <c r="AH13" s="671" t="n"/>
+      <c r="AI13" s="671" t="n"/>
+      <c r="AJ13" s="671" t="n"/>
+      <c r="AK13" s="671" t="n"/>
+      <c r="AL13" s="671" t="n"/>
+      <c r="AM13" s="671" t="n"/>
+      <c r="AN13" s="671" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="732" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B8" s="533" t="inlineStr">
+      <c r="B14" s="742" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C8" s="534" t="inlineStr">
+      <c r="C14" s="743" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D8" s="535" t="n"/>
-      <c r="E8" s="535" t="n"/>
-      <c r="F8" s="535" t="n"/>
-      <c r="G8" s="535" t="n"/>
-      <c r="H8" s="535" t="n"/>
-      <c r="I8" s="535" t="n"/>
-      <c r="J8" s="535" t="n"/>
-      <c r="K8" s="535" t="n"/>
-      <c r="L8" s="535" t="n"/>
-      <c r="M8" s="535" t="n"/>
-      <c r="N8" s="535" t="n"/>
-      <c r="O8" s="535" t="n"/>
-      <c r="P8" s="535" t="n"/>
-      <c r="Q8" s="535" t="n"/>
-      <c r="R8" s="535" t="n"/>
-      <c r="S8" s="535" t="n"/>
-      <c r="T8" s="535" t="n"/>
-      <c r="U8" s="535" t="n"/>
-      <c r="V8" s="535" t="n"/>
-      <c r="W8" s="535" t="n"/>
-      <c r="X8" s="535" t="n"/>
-      <c r="Y8" s="535" t="n"/>
-      <c r="Z8" s="535" t="n"/>
-      <c r="AA8" s="535" t="n"/>
-      <c r="AB8" s="535" t="n"/>
-      <c r="AC8" s="535" t="n"/>
-      <c r="AD8" s="535" t="n"/>
-      <c r="AE8" s="535" t="n"/>
-      <c r="AF8" s="535" t="n"/>
-      <c r="AG8" s="535" t="n"/>
-      <c r="AH8" s="535" t="n"/>
-      <c r="AI8" s="535" t="n"/>
-      <c r="AJ8" s="535" t="n"/>
-      <c r="AK8" s="535" t="n"/>
-      <c r="AL8" s="535" t="n"/>
-      <c r="AM8" s="535" t="n"/>
-      <c r="AN8" s="536" t="n"/>
+      <c r="D14" s="671" t="n"/>
+      <c r="E14" s="671" t="n"/>
+      <c r="F14" s="671" t="n"/>
+      <c r="G14" s="671" t="n"/>
+      <c r="H14" s="671" t="n"/>
+      <c r="I14" s="671" t="n"/>
+      <c r="J14" s="671" t="n"/>
+      <c r="K14" s="671" t="n"/>
+      <c r="L14" s="671" t="n"/>
+      <c r="M14" s="671" t="n"/>
+      <c r="N14" s="671" t="n"/>
+      <c r="O14" s="671" t="n"/>
+      <c r="P14" s="671" t="n"/>
+      <c r="Q14" s="671" t="n"/>
+      <c r="R14" s="671" t="n"/>
+      <c r="S14" s="671" t="n"/>
+      <c r="T14" s="671" t="n"/>
+      <c r="U14" s="671" t="n"/>
+      <c r="V14" s="671" t="n"/>
+      <c r="W14" s="671" t="n"/>
+      <c r="X14" s="671" t="n"/>
+      <c r="Y14" s="671" t="n"/>
+      <c r="Z14" s="671" t="n"/>
+      <c r="AA14" s="671" t="n"/>
+      <c r="AB14" s="671" t="n"/>
+      <c r="AC14" s="671" t="n"/>
+      <c r="AD14" s="671" t="n"/>
+      <c r="AE14" s="671" t="n"/>
+      <c r="AF14" s="671" t="n"/>
+      <c r="AG14" s="671" t="n"/>
+      <c r="AH14" s="671" t="n"/>
+      <c r="AI14" s="671" t="n"/>
+      <c r="AJ14" s="671" t="n"/>
+      <c r="AK14" s="671" t="n"/>
+      <c r="AL14" s="671" t="n"/>
+      <c r="AM14" s="671" t="n"/>
+      <c r="AN14" s="671" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="671" t="n"/>
+      <c r="B15" s="671" t="n"/>
+      <c r="C15" s="671" t="n"/>
+      <c r="D15" s="671" t="n"/>
+      <c r="E15" s="671" t="n"/>
+      <c r="F15" s="671" t="n"/>
+      <c r="G15" s="671" t="n"/>
+      <c r="H15" s="671" t="n"/>
+      <c r="I15" s="671" t="n"/>
+      <c r="J15" s="671" t="n"/>
+      <c r="K15" s="671" t="n"/>
+      <c r="L15" s="671" t="n"/>
+      <c r="M15" s="671" t="n"/>
+      <c r="N15" s="671" t="n"/>
+      <c r="O15" s="671" t="n"/>
+      <c r="P15" s="671" t="n"/>
+      <c r="Q15" s="671" t="n"/>
+      <c r="R15" s="671" t="n"/>
+      <c r="S15" s="671" t="n"/>
+      <c r="T15" s="671" t="n"/>
+      <c r="U15" s="671" t="n"/>
+      <c r="V15" s="671" t="n"/>
+      <c r="W15" s="671" t="n"/>
+      <c r="X15" s="671" t="n"/>
+      <c r="Y15" s="671" t="n"/>
+      <c r="Z15" s="671" t="n"/>
+      <c r="AA15" s="671" t="n"/>
+      <c r="AB15" s="671" t="n"/>
+      <c r="AC15" s="671" t="n"/>
+      <c r="AD15" s="671" t="n"/>
+      <c r="AE15" s="671" t="n"/>
+      <c r="AF15" s="671" t="n"/>
+      <c r="AG15" s="671" t="n"/>
+      <c r="AH15" s="671" t="n"/>
+      <c r="AI15" s="671" t="n"/>
+      <c r="AJ15" s="671" t="n"/>
+      <c r="AK15" s="671" t="n"/>
+      <c r="AL15" s="671" t="n"/>
+      <c r="AM15" s="671" t="n"/>
+      <c r="AN15" s="671" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="671" t="n"/>
+      <c r="B16" s="671" t="n"/>
+      <c r="C16" s="671" t="n"/>
+      <c r="D16" s="671" t="n"/>
+      <c r="E16" s="671" t="n"/>
+      <c r="F16" s="671" t="n"/>
+      <c r="G16" s="671" t="n"/>
+      <c r="H16" s="671" t="n"/>
+      <c r="I16" s="671" t="n"/>
+      <c r="J16" s="671" t="n"/>
+      <c r="K16" s="671" t="n"/>
+      <c r="L16" s="671" t="n"/>
+      <c r="M16" s="671" t="n"/>
+      <c r="N16" s="671" t="n"/>
+      <c r="O16" s="671" t="n"/>
+      <c r="P16" s="671" t="n"/>
+      <c r="Q16" s="671" t="n"/>
+      <c r="R16" s="671" t="n"/>
+      <c r="S16" s="671" t="n"/>
+      <c r="T16" s="671" t="n"/>
+      <c r="U16" s="671" t="n"/>
+      <c r="V16" s="671" t="n"/>
+      <c r="W16" s="671" t="n"/>
+      <c r="X16" s="671" t="n"/>
+      <c r="Y16" s="671" t="n"/>
+      <c r="Z16" s="671" t="n"/>
+      <c r="AA16" s="671" t="n"/>
+      <c r="AB16" s="671" t="n"/>
+      <c r="AC16" s="671" t="n"/>
+      <c r="AD16" s="671" t="n"/>
+      <c r="AE16" s="671" t="n"/>
+      <c r="AF16" s="671" t="n"/>
+      <c r="AG16" s="671" t="n"/>
+      <c r="AH16" s="671" t="n"/>
+      <c r="AI16" s="671" t="n"/>
+      <c r="AJ16" s="671" t="n"/>
+      <c r="AK16" s="671" t="n"/>
+      <c r="AL16" s="671" t="n"/>
+      <c r="AM16" s="671" t="n"/>
+      <c r="AN16" s="671" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="671" t="n"/>
+      <c r="B17" s="671" t="n"/>
+      <c r="C17" s="671" t="n"/>
+      <c r="D17" s="671" t="n"/>
+      <c r="E17" s="671" t="n"/>
+      <c r="F17" s="671" t="n"/>
+      <c r="G17" s="671" t="n"/>
+      <c r="H17" s="671" t="n"/>
+      <c r="I17" s="671" t="n"/>
+      <c r="J17" s="671" t="n"/>
+      <c r="K17" s="671" t="n"/>
+      <c r="L17" s="671" t="n"/>
+      <c r="M17" s="671" t="n"/>
+      <c r="N17" s="671" t="n"/>
+      <c r="O17" s="671" t="n"/>
+      <c r="P17" s="671" t="n"/>
+      <c r="Q17" s="671" t="n"/>
+      <c r="R17" s="671" t="n"/>
+      <c r="S17" s="671" t="n"/>
+      <c r="T17" s="671" t="n"/>
+      <c r="U17" s="671" t="n"/>
+      <c r="V17" s="671" t="n"/>
+      <c r="W17" s="671" t="n"/>
+      <c r="X17" s="671" t="n"/>
+      <c r="Y17" s="671" t="n"/>
+      <c r="Z17" s="671" t="n"/>
+      <c r="AA17" s="671" t="n"/>
+      <c r="AB17" s="671" t="n"/>
+      <c r="AC17" s="671" t="n"/>
+      <c r="AD17" s="671" t="n"/>
+      <c r="AE17" s="671" t="n"/>
+      <c r="AF17" s="671" t="n"/>
+      <c r="AG17" s="671" t="n"/>
+      <c r="AH17" s="671" t="n"/>
+      <c r="AI17" s="671" t="n"/>
+      <c r="AJ17" s="671" t="n"/>
+      <c r="AK17" s="671" t="n"/>
+      <c r="AL17" s="671" t="n"/>
+      <c r="AM17" s="671" t="n"/>
+      <c r="AN17" s="671" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C8"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -4530,6 +4530,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4560,6 +4563,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4590,6 +4596,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6896,7 +6905,6 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="114">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AX18:BA18"/>
@@ -7313,6 +7321,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="318" t="inlineStr">
         <is>
@@ -7531,7 +7540,6 @@
       <c r="G19" s="320" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -7587,6 +7595,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="318" t="inlineStr">
         <is>
@@ -7795,7 +7804,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
@@ -7844,6 +7852,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="318" t="inlineStr">
         <is>
@@ -7930,7 +7939,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINAL_INSP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="veryHidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FINAL_INSP'!$A$1:$BD$35</definedName>
@@ -7321,7 +7321,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="318" t="inlineStr">
         <is>
@@ -7595,7 +7594,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="318" t="inlineStr">
         <is>
@@ -7852,7 +7850,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="318" t="inlineStr">
         <is>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -15,8 +15,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FINAL_INSP'!$A$1:$BD$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REF_IMPORT'!$A$4:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EVIDENCE_REF'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7802,7 +7800,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -7936,7 +7933,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_REVHIST" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FINAL_INSP'!$A$1:$BD$35</definedName>
@@ -463,7 +464,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="47">
+  <fills count="50">
     <fill>
       <patternFill/>
     </fill>
@@ -695,8 +696,26 @@
         <fgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00005A9E"/>
+        <bgColor rgb="00005A9E"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="271">
+  <borders count="273">
     <border>
       <left/>
       <right/>
@@ -3614,12 +3633,40 @@
         <color rgb="000078D4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="338">
+  <cellXfs count="346">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4396,10 +4443,64 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="47" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="48" borderId="271" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="47" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="48" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="47" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="47" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00CC0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFCCCC"/>
+          <bgColor rgb="00FFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF3C4"/>
+          <bgColor rgb="00FFF3C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D7F0E2"/>
+          <bgColor rgb="00D7F0E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -4909,7 +5010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BD35"/>
+  <dimension ref="A1:BD40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -5055,7 +5156,7 @@
       <c r="AV2" s="272" t="n"/>
       <c r="AW2" s="273" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AX2" s="271" t="n"/>
@@ -5111,7 +5212,7 @@
       <c r="AV3" s="272" t="n"/>
       <c r="AW3" s="273" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AX3" s="271" t="n"/>
@@ -5488,7 +5589,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="287" t="inlineStr">
         <is>
-          <t>Inspection Basis</t>
+          <t>Inspection Basis / CMM Program</t>
         </is>
       </c>
       <c r="B11" s="271" t="n"/>
@@ -5520,7 +5621,7 @@
       <c r="AB11" s="322" t="n"/>
       <c r="AC11" s="289" t="inlineStr">
         <is>
-          <t>Evidence Package Ref</t>
+          <t>CoC Number / FRM-642 Ref</t>
         </is>
       </c>
       <c r="AD11" s="271" t="n"/>
@@ -5617,351 +5718,206 @@
       <c r="BC12" s="321" t="n"/>
       <c r="BD12" s="323" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="25" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="284" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="338" t="inlineStr">
+        <is>
+          <t>CMM Report Attached?</t>
+        </is>
+      </c>
+      <c r="K13" s="339" t="n"/>
+      <c r="AC13" s="340" t="inlineStr">
+        <is>
+          <t>Customer Source Insp. Required?</t>
+        </is>
+      </c>
+      <c r="AJ13" s="341" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="338" t="inlineStr">
+        <is>
+          <t>Linked NCR Refs (FRM-651)</t>
+        </is>
+      </c>
+      <c r="K14" s="339" t="n"/>
+      <c r="AC14" s="340" t="inlineStr">
+        <is>
+          <t>Linked Setup Sheet (FRM-302)</t>
+        </is>
+      </c>
+      <c r="AJ14" s="341" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="338" t="inlineStr">
+        <is>
+          <t>Ref: SOP-605 / WI-605</t>
+        </is>
+      </c>
+      <c r="K15" s="342" t="inlineStr">
+        <is>
+          <t>SOP-605 (Final Inspection and Release)</t>
+        </is>
+      </c>
+      <c r="AC15" s="340" t="inlineStr">
+        <is>
+          <t>Retain: 10 years</t>
+        </is>
+      </c>
+      <c r="AJ15" s="343" t="inlineStr">
+        <is>
+          <t>Per QMS retention schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="25" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="284" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
         </is>
       </c>
-      <c r="B14" s="285" t="n"/>
-      <c r="C14" s="285" t="n"/>
-      <c r="D14" s="285" t="n"/>
-      <c r="E14" s="285" t="n"/>
-      <c r="F14" s="285" t="n"/>
-      <c r="G14" s="285" t="n"/>
-      <c r="H14" s="285" t="n"/>
-      <c r="I14" s="285" t="n"/>
-      <c r="J14" s="285" t="n"/>
-      <c r="K14" s="285" t="n"/>
-      <c r="L14" s="285" t="n"/>
-      <c r="M14" s="285" t="n"/>
-      <c r="N14" s="285" t="n"/>
-      <c r="O14" s="285" t="n"/>
-      <c r="P14" s="285" t="n"/>
-      <c r="Q14" s="285" t="n"/>
-      <c r="R14" s="285" t="n"/>
-      <c r="S14" s="285" t="n"/>
-      <c r="T14" s="285" t="n"/>
-      <c r="U14" s="285" t="n"/>
-      <c r="V14" s="285" t="n"/>
-      <c r="W14" s="285" t="n"/>
-      <c r="X14" s="285" t="n"/>
-      <c r="Y14" s="285" t="n"/>
-      <c r="Z14" s="285" t="n"/>
-      <c r="AA14" s="285" t="n"/>
-      <c r="AB14" s="285" t="n"/>
-      <c r="AC14" s="285" t="n"/>
-      <c r="AD14" s="285" t="n"/>
-      <c r="AE14" s="285" t="n"/>
-      <c r="AF14" s="285" t="n"/>
-      <c r="AG14" s="285" t="n"/>
-      <c r="AH14" s="285" t="n"/>
-      <c r="AI14" s="285" t="n"/>
-      <c r="AJ14" s="285" t="n"/>
-      <c r="AK14" s="285" t="n"/>
-      <c r="AL14" s="285" t="n"/>
-      <c r="AM14" s="285" t="n"/>
-      <c r="AN14" s="285" t="n"/>
-      <c r="AO14" s="285" t="n"/>
-      <c r="AP14" s="285" t="n"/>
-      <c r="AQ14" s="285" t="n"/>
-      <c r="AR14" s="285" t="n"/>
-      <c r="AS14" s="285" t="n"/>
-      <c r="AT14" s="285" t="n"/>
-      <c r="AU14" s="285" t="n"/>
-      <c r="AV14" s="285" t="n"/>
-      <c r="AW14" s="285" t="n"/>
-      <c r="AX14" s="285" t="n"/>
-      <c r="AY14" s="285" t="n"/>
-      <c r="AZ14" s="285" t="n"/>
-      <c r="BA14" s="285" t="n"/>
-      <c r="BB14" s="285" t="n"/>
-      <c r="BC14" s="285" t="n"/>
-      <c r="BD14" s="286" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="291" t="inlineStr">
+      <c r="B17" s="285" t="n"/>
+      <c r="C17" s="285" t="n"/>
+      <c r="D17" s="285" t="n"/>
+      <c r="E17" s="285" t="n"/>
+      <c r="F17" s="285" t="n"/>
+      <c r="G17" s="285" t="n"/>
+      <c r="H17" s="285" t="n"/>
+      <c r="I17" s="285" t="n"/>
+      <c r="J17" s="285" t="n"/>
+      <c r="K17" s="285" t="n"/>
+      <c r="L17" s="285" t="n"/>
+      <c r="M17" s="285" t="n"/>
+      <c r="N17" s="285" t="n"/>
+      <c r="O17" s="285" t="n"/>
+      <c r="P17" s="285" t="n"/>
+      <c r="Q17" s="285" t="n"/>
+      <c r="R17" s="285" t="n"/>
+      <c r="S17" s="285" t="n"/>
+      <c r="T17" s="285" t="n"/>
+      <c r="U17" s="285" t="n"/>
+      <c r="V17" s="285" t="n"/>
+      <c r="W17" s="285" t="n"/>
+      <c r="X17" s="285" t="n"/>
+      <c r="Y17" s="285" t="n"/>
+      <c r="Z17" s="285" t="n"/>
+      <c r="AA17" s="285" t="n"/>
+      <c r="AB17" s="285" t="n"/>
+      <c r="AC17" s="285" t="n"/>
+      <c r="AD17" s="285" t="n"/>
+      <c r="AE17" s="285" t="n"/>
+      <c r="AF17" s="285" t="n"/>
+      <c r="AG17" s="285" t="n"/>
+      <c r="AH17" s="285" t="n"/>
+      <c r="AI17" s="285" t="n"/>
+      <c r="AJ17" s="285" t="n"/>
+      <c r="AK17" s="285" t="n"/>
+      <c r="AL17" s="285" t="n"/>
+      <c r="AM17" s="285" t="n"/>
+      <c r="AN17" s="285" t="n"/>
+      <c r="AO17" s="285" t="n"/>
+      <c r="AP17" s="285" t="n"/>
+      <c r="AQ17" s="285" t="n"/>
+      <c r="AR17" s="285" t="n"/>
+      <c r="AS17" s="285" t="n"/>
+      <c r="AT17" s="285" t="n"/>
+      <c r="AU17" s="285" t="n"/>
+      <c r="AV17" s="285" t="n"/>
+      <c r="AW17" s="285" t="n"/>
+      <c r="AX17" s="285" t="n"/>
+      <c r="AY17" s="285" t="n"/>
+      <c r="AZ17" s="285" t="n"/>
+      <c r="BA17" s="285" t="n"/>
+      <c r="BB17" s="285" t="n"/>
+      <c r="BC17" s="285" t="n"/>
+      <c r="BD17" s="286" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="291" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="271" t="n"/>
-      <c r="C15" s="272" t="n"/>
-      <c r="D15" s="292" t="inlineStr">
+      <c r="B18" s="271" t="n"/>
+      <c r="C18" s="272" t="n"/>
+      <c r="D18" s="292" t="inlineStr">
         <is>
           <t>Check Group</t>
         </is>
       </c>
-      <c r="E15" s="271" t="n"/>
-      <c r="F15" s="271" t="n"/>
-      <c r="G15" s="272" t="n"/>
-      <c r="H15" s="292" t="inlineStr">
+      <c r="E18" s="271" t="n"/>
+      <c r="F18" s="271" t="n"/>
+      <c r="G18" s="272" t="n"/>
+      <c r="H18" s="292" t="inlineStr">
         <is>
           <t>Characteristic / Requirement</t>
         </is>
       </c>
-      <c r="I15" s="271" t="n"/>
-      <c r="J15" s="271" t="n"/>
-      <c r="K15" s="271" t="n"/>
-      <c r="L15" s="271" t="n"/>
-      <c r="M15" s="271" t="n"/>
-      <c r="N15" s="271" t="n"/>
-      <c r="O15" s="271" t="n"/>
-      <c r="P15" s="271" t="n"/>
-      <c r="Q15" s="271" t="n"/>
-      <c r="R15" s="271" t="n"/>
-      <c r="S15" s="271" t="n"/>
-      <c r="T15" s="271" t="n"/>
-      <c r="U15" s="271" t="n"/>
-      <c r="V15" s="271" t="n"/>
-      <c r="W15" s="271" t="n"/>
-      <c r="X15" s="271" t="n"/>
-      <c r="Y15" s="271" t="n"/>
-      <c r="Z15" s="272" t="n"/>
-      <c r="AA15" s="292" t="inlineStr">
+      <c r="I18" s="271" t="n"/>
+      <c r="J18" s="271" t="n"/>
+      <c r="K18" s="271" t="n"/>
+      <c r="L18" s="271" t="n"/>
+      <c r="M18" s="271" t="n"/>
+      <c r="N18" s="271" t="n"/>
+      <c r="O18" s="271" t="n"/>
+      <c r="P18" s="271" t="n"/>
+      <c r="Q18" s="271" t="n"/>
+      <c r="R18" s="271" t="n"/>
+      <c r="S18" s="271" t="n"/>
+      <c r="T18" s="271" t="n"/>
+      <c r="U18" s="271" t="n"/>
+      <c r="V18" s="271" t="n"/>
+      <c r="W18" s="271" t="n"/>
+      <c r="X18" s="271" t="n"/>
+      <c r="Y18" s="271" t="n"/>
+      <c r="Z18" s="272" t="n"/>
+      <c r="AA18" s="292" t="inlineStr">
         <is>
           <t>Method / Inspection Basis</t>
         </is>
       </c>
-      <c r="AB15" s="271" t="n"/>
-      <c r="AC15" s="271" t="n"/>
-      <c r="AD15" s="271" t="n"/>
-      <c r="AE15" s="271" t="n"/>
-      <c r="AF15" s="271" t="n"/>
-      <c r="AG15" s="271" t="n"/>
-      <c r="AH15" s="271" t="n"/>
-      <c r="AI15" s="271" t="n"/>
-      <c r="AJ15" s="271" t="n"/>
-      <c r="AK15" s="271" t="n"/>
-      <c r="AL15" s="271" t="n"/>
-      <c r="AM15" s="271" t="n"/>
-      <c r="AN15" s="271" t="n"/>
-      <c r="AO15" s="271" t="n"/>
-      <c r="AP15" s="271" t="n"/>
-      <c r="AQ15" s="272" t="n"/>
-      <c r="AR15" s="292" t="inlineStr">
+      <c r="AB18" s="271" t="n"/>
+      <c r="AC18" s="271" t="n"/>
+      <c r="AD18" s="271" t="n"/>
+      <c r="AE18" s="271" t="n"/>
+      <c r="AF18" s="271" t="n"/>
+      <c r="AG18" s="271" t="n"/>
+      <c r="AH18" s="271" t="n"/>
+      <c r="AI18" s="271" t="n"/>
+      <c r="AJ18" s="271" t="n"/>
+      <c r="AK18" s="271" t="n"/>
+      <c r="AL18" s="271" t="n"/>
+      <c r="AM18" s="271" t="n"/>
+      <c r="AN18" s="271" t="n"/>
+      <c r="AO18" s="271" t="n"/>
+      <c r="AP18" s="271" t="n"/>
+      <c r="AQ18" s="272" t="n"/>
+      <c r="AR18" s="292" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="271" t="n"/>
-      <c r="AT15" s="271" t="n"/>
-      <c r="AU15" s="271" t="n"/>
-      <c r="AV15" s="271" t="n"/>
-      <c r="AW15" s="272" t="n"/>
-      <c r="AX15" s="292" t="inlineStr">
+      <c r="AS18" s="271" t="n"/>
+      <c r="AT18" s="271" t="n"/>
+      <c r="AU18" s="271" t="n"/>
+      <c r="AV18" s="271" t="n"/>
+      <c r="AW18" s="272" t="n"/>
+      <c r="AX18" s="292" t="inlineStr">
         <is>
           <t>Inspector</t>
         </is>
       </c>
-      <c r="AY15" s="271" t="n"/>
-      <c r="AZ15" s="271" t="n"/>
-      <c r="BA15" s="272" t="n"/>
-      <c r="BB15" s="293" t="inlineStr">
+      <c r="AY18" s="271" t="n"/>
+      <c r="AZ18" s="271" t="n"/>
+      <c r="BA18" s="272" t="n"/>
+      <c r="BB18" s="293" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="271" t="n"/>
-      <c r="BD15" s="274" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="294">
-        <f>ROW()-ROW($A$16)+1</f>
-        <v/>
-      </c>
-      <c r="B16" s="276" t="n"/>
-      <c r="C16" s="277" t="n"/>
-      <c r="D16" s="295" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="324" t="n"/>
-      <c r="F16" s="324" t="n"/>
-      <c r="G16" s="325" t="n"/>
-      <c r="H16" s="296" t="n"/>
-      <c r="I16" s="324" t="n"/>
-      <c r="J16" s="324" t="n"/>
-      <c r="K16" s="324" t="n"/>
-      <c r="L16" s="324" t="n"/>
-      <c r="M16" s="324" t="n"/>
-      <c r="N16" s="324" t="n"/>
-      <c r="O16" s="324" t="n"/>
-      <c r="P16" s="324" t="n"/>
-      <c r="Q16" s="324" t="n"/>
-      <c r="R16" s="324" t="n"/>
-      <c r="S16" s="324" t="n"/>
-      <c r="T16" s="324" t="n"/>
-      <c r="U16" s="324" t="n"/>
-      <c r="V16" s="324" t="n"/>
-      <c r="W16" s="324" t="n"/>
-      <c r="X16" s="324" t="n"/>
-      <c r="Y16" s="324" t="n"/>
-      <c r="Z16" s="325" t="n"/>
-      <c r="AA16" s="297" t="n"/>
-      <c r="AB16" s="324" t="n"/>
-      <c r="AC16" s="324" t="n"/>
-      <c r="AD16" s="324" t="n"/>
-      <c r="AE16" s="324" t="n"/>
-      <c r="AF16" s="324" t="n"/>
-      <c r="AG16" s="324" t="n"/>
-      <c r="AH16" s="324" t="n"/>
-      <c r="AI16" s="324" t="n"/>
-      <c r="AJ16" s="324" t="n"/>
-      <c r="AK16" s="324" t="n"/>
-      <c r="AL16" s="324" t="n"/>
-      <c r="AM16" s="324" t="n"/>
-      <c r="AN16" s="324" t="n"/>
-      <c r="AO16" s="324" t="n"/>
-      <c r="AP16" s="324" t="n"/>
-      <c r="AQ16" s="325" t="n"/>
-      <c r="AR16" s="296" t="n"/>
-      <c r="AS16" s="324" t="n"/>
-      <c r="AT16" s="324" t="n"/>
-      <c r="AU16" s="324" t="n"/>
-      <c r="AV16" s="324" t="n"/>
-      <c r="AW16" s="325" t="n"/>
-      <c r="AX16" s="296" t="n"/>
-      <c r="AY16" s="324" t="n"/>
-      <c r="AZ16" s="324" t="n"/>
-      <c r="BA16" s="325" t="n"/>
-      <c r="BB16" s="298" t="n"/>
-      <c r="BC16" s="324" t="n"/>
-      <c r="BD16" s="326" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="294">
-        <f>ROW()-ROW($A$16)+1</f>
-        <v/>
-      </c>
-      <c r="B17" s="276" t="n"/>
-      <c r="C17" s="277" t="n"/>
-      <c r="D17" s="295" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="324" t="n"/>
-      <c r="F17" s="324" t="n"/>
-      <c r="G17" s="325" t="n"/>
-      <c r="H17" s="296" t="n"/>
-      <c r="I17" s="324" t="n"/>
-      <c r="J17" s="324" t="n"/>
-      <c r="K17" s="324" t="n"/>
-      <c r="L17" s="324" t="n"/>
-      <c r="M17" s="324" t="n"/>
-      <c r="N17" s="324" t="n"/>
-      <c r="O17" s="324" t="n"/>
-      <c r="P17" s="324" t="n"/>
-      <c r="Q17" s="324" t="n"/>
-      <c r="R17" s="324" t="n"/>
-      <c r="S17" s="324" t="n"/>
-      <c r="T17" s="324" t="n"/>
-      <c r="U17" s="324" t="n"/>
-      <c r="V17" s="324" t="n"/>
-      <c r="W17" s="324" t="n"/>
-      <c r="X17" s="324" t="n"/>
-      <c r="Y17" s="324" t="n"/>
-      <c r="Z17" s="325" t="n"/>
-      <c r="AA17" s="297" t="n"/>
-      <c r="AB17" s="324" t="n"/>
-      <c r="AC17" s="324" t="n"/>
-      <c r="AD17" s="324" t="n"/>
-      <c r="AE17" s="324" t="n"/>
-      <c r="AF17" s="324" t="n"/>
-      <c r="AG17" s="324" t="n"/>
-      <c r="AH17" s="324" t="n"/>
-      <c r="AI17" s="324" t="n"/>
-      <c r="AJ17" s="324" t="n"/>
-      <c r="AK17" s="324" t="n"/>
-      <c r="AL17" s="324" t="n"/>
-      <c r="AM17" s="324" t="n"/>
-      <c r="AN17" s="324" t="n"/>
-      <c r="AO17" s="324" t="n"/>
-      <c r="AP17" s="324" t="n"/>
-      <c r="AQ17" s="325" t="n"/>
-      <c r="AR17" s="296" t="n"/>
-      <c r="AS17" s="324" t="n"/>
-      <c r="AT17" s="324" t="n"/>
-      <c r="AU17" s="324" t="n"/>
-      <c r="AV17" s="324" t="n"/>
-      <c r="AW17" s="325" t="n"/>
-      <c r="AX17" s="296" t="n"/>
-      <c r="AY17" s="324" t="n"/>
-      <c r="AZ17" s="324" t="n"/>
-      <c r="BA17" s="325" t="n"/>
-      <c r="BB17" s="298" t="n"/>
-      <c r="BC17" s="324" t="n"/>
-      <c r="BD17" s="326" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="294">
-        <f>ROW()-ROW($A$16)+1</f>
-        <v/>
-      </c>
-      <c r="B18" s="276" t="n"/>
-      <c r="C18" s="277" t="n"/>
-      <c r="D18" s="295" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="324" t="n"/>
-      <c r="F18" s="324" t="n"/>
-      <c r="G18" s="325" t="n"/>
-      <c r="H18" s="296" t="n"/>
-      <c r="I18" s="324" t="n"/>
-      <c r="J18" s="324" t="n"/>
-      <c r="K18" s="324" t="n"/>
-      <c r="L18" s="324" t="n"/>
-      <c r="M18" s="324" t="n"/>
-      <c r="N18" s="324" t="n"/>
-      <c r="O18" s="324" t="n"/>
-      <c r="P18" s="324" t="n"/>
-      <c r="Q18" s="324" t="n"/>
-      <c r="R18" s="324" t="n"/>
-      <c r="S18" s="324" t="n"/>
-      <c r="T18" s="324" t="n"/>
-      <c r="U18" s="324" t="n"/>
-      <c r="V18" s="324" t="n"/>
-      <c r="W18" s="324" t="n"/>
-      <c r="X18" s="324" t="n"/>
-      <c r="Y18" s="324" t="n"/>
-      <c r="Z18" s="325" t="n"/>
-      <c r="AA18" s="297" t="n"/>
-      <c r="AB18" s="324" t="n"/>
-      <c r="AC18" s="324" t="n"/>
-      <c r="AD18" s="324" t="n"/>
-      <c r="AE18" s="324" t="n"/>
-      <c r="AF18" s="324" t="n"/>
-      <c r="AG18" s="324" t="n"/>
-      <c r="AH18" s="324" t="n"/>
-      <c r="AI18" s="324" t="n"/>
-      <c r="AJ18" s="324" t="n"/>
-      <c r="AK18" s="324" t="n"/>
-      <c r="AL18" s="324" t="n"/>
-      <c r="AM18" s="324" t="n"/>
-      <c r="AN18" s="324" t="n"/>
-      <c r="AO18" s="324" t="n"/>
-      <c r="AP18" s="324" t="n"/>
-      <c r="AQ18" s="325" t="n"/>
-      <c r="AR18" s="296" t="n"/>
-      <c r="AS18" s="324" t="n"/>
-      <c r="AT18" s="324" t="n"/>
-      <c r="AU18" s="324" t="n"/>
-      <c r="AV18" s="324" t="n"/>
-      <c r="AW18" s="325" t="n"/>
-      <c r="AX18" s="296" t="n"/>
-      <c r="AY18" s="324" t="n"/>
-      <c r="AZ18" s="324" t="n"/>
-      <c r="BA18" s="325" t="n"/>
-      <c r="BB18" s="298" t="n"/>
-      <c r="BC18" s="324" t="n"/>
-      <c r="BD18" s="326" t="n"/>
+      <c r="BC18" s="271" t="n"/>
+      <c r="BD18" s="274" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="294">
@@ -6224,677 +6180,895 @@
       <c r="BD22" s="326" t="n"/>
     </row>
     <row r="23" ht="4" customHeight="1">
-      <c r="A23" s="294" t="n"/>
-      <c r="D23" s="299" t="n"/>
-      <c r="H23" s="300" t="n"/>
-      <c r="AA23" s="301" t="n"/>
-      <c r="AR23" s="302" t="n"/>
-      <c r="AX23" s="302" t="n"/>
-      <c r="BB23" s="303" t="n"/>
+      <c r="A23" s="294">
+        <f>ROW()-ROW($A$16)+1</f>
+        <v/>
+      </c>
+      <c r="B23" s="276" t="n"/>
+      <c r="C23" s="277" t="n"/>
+      <c r="D23" s="295" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="324" t="n"/>
+      <c r="F23" s="324" t="n"/>
+      <c r="G23" s="325" t="n"/>
+      <c r="H23" s="296" t="n"/>
+      <c r="I23" s="324" t="n"/>
+      <c r="J23" s="324" t="n"/>
+      <c r="K23" s="324" t="n"/>
+      <c r="L23" s="324" t="n"/>
+      <c r="M23" s="324" t="n"/>
+      <c r="N23" s="324" t="n"/>
+      <c r="O23" s="324" t="n"/>
+      <c r="P23" s="324" t="n"/>
+      <c r="Q23" s="324" t="n"/>
+      <c r="R23" s="324" t="n"/>
+      <c r="S23" s="324" t="n"/>
+      <c r="T23" s="324" t="n"/>
+      <c r="U23" s="324" t="n"/>
+      <c r="V23" s="324" t="n"/>
+      <c r="W23" s="324" t="n"/>
+      <c r="X23" s="324" t="n"/>
+      <c r="Y23" s="324" t="n"/>
+      <c r="Z23" s="325" t="n"/>
+      <c r="AA23" s="297" t="n"/>
+      <c r="AB23" s="324" t="n"/>
+      <c r="AC23" s="324" t="n"/>
+      <c r="AD23" s="324" t="n"/>
+      <c r="AE23" s="324" t="n"/>
+      <c r="AF23" s="324" t="n"/>
+      <c r="AG23" s="324" t="n"/>
+      <c r="AH23" s="324" t="n"/>
+      <c r="AI23" s="324" t="n"/>
+      <c r="AJ23" s="324" t="n"/>
+      <c r="AK23" s="324" t="n"/>
+      <c r="AL23" s="324" t="n"/>
+      <c r="AM23" s="324" t="n"/>
+      <c r="AN23" s="324" t="n"/>
+      <c r="AO23" s="324" t="n"/>
+      <c r="AP23" s="324" t="n"/>
+      <c r="AQ23" s="325" t="n"/>
+      <c r="AR23" s="296" t="n"/>
+      <c r="AS23" s="324" t="n"/>
+      <c r="AT23" s="324" t="n"/>
+      <c r="AU23" s="324" t="n"/>
+      <c r="AV23" s="324" t="n"/>
+      <c r="AW23" s="325" t="n"/>
+      <c r="AX23" s="296" t="n"/>
+      <c r="AY23" s="324" t="n"/>
+      <c r="AZ23" s="324" t="n"/>
+      <c r="BA23" s="325" t="n"/>
+      <c r="BB23" s="298" t="n"/>
+      <c r="BC23" s="324" t="n"/>
+      <c r="BD23" s="326" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="284" t="inlineStr">
+      <c r="A24" s="294">
+        <f>ROW()-ROW($A$16)+1</f>
+        <v/>
+      </c>
+      <c r="B24" s="276" t="n"/>
+      <c r="C24" s="277" t="n"/>
+      <c r="D24" s="295" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="324" t="n"/>
+      <c r="F24" s="324" t="n"/>
+      <c r="G24" s="325" t="n"/>
+      <c r="H24" s="296" t="n"/>
+      <c r="I24" s="324" t="n"/>
+      <c r="J24" s="324" t="n"/>
+      <c r="K24" s="324" t="n"/>
+      <c r="L24" s="324" t="n"/>
+      <c r="M24" s="324" t="n"/>
+      <c r="N24" s="324" t="n"/>
+      <c r="O24" s="324" t="n"/>
+      <c r="P24" s="324" t="n"/>
+      <c r="Q24" s="324" t="n"/>
+      <c r="R24" s="324" t="n"/>
+      <c r="S24" s="324" t="n"/>
+      <c r="T24" s="324" t="n"/>
+      <c r="U24" s="324" t="n"/>
+      <c r="V24" s="324" t="n"/>
+      <c r="W24" s="324" t="n"/>
+      <c r="X24" s="324" t="n"/>
+      <c r="Y24" s="324" t="n"/>
+      <c r="Z24" s="325" t="n"/>
+      <c r="AA24" s="297" t="n"/>
+      <c r="AB24" s="324" t="n"/>
+      <c r="AC24" s="324" t="n"/>
+      <c r="AD24" s="324" t="n"/>
+      <c r="AE24" s="324" t="n"/>
+      <c r="AF24" s="324" t="n"/>
+      <c r="AG24" s="324" t="n"/>
+      <c r="AH24" s="324" t="n"/>
+      <c r="AI24" s="324" t="n"/>
+      <c r="AJ24" s="324" t="n"/>
+      <c r="AK24" s="324" t="n"/>
+      <c r="AL24" s="324" t="n"/>
+      <c r="AM24" s="324" t="n"/>
+      <c r="AN24" s="324" t="n"/>
+      <c r="AO24" s="324" t="n"/>
+      <c r="AP24" s="324" t="n"/>
+      <c r="AQ24" s="325" t="n"/>
+      <c r="AR24" s="296" t="n"/>
+      <c r="AS24" s="324" t="n"/>
+      <c r="AT24" s="324" t="n"/>
+      <c r="AU24" s="324" t="n"/>
+      <c r="AV24" s="324" t="n"/>
+      <c r="AW24" s="325" t="n"/>
+      <c r="AX24" s="296" t="n"/>
+      <c r="AY24" s="324" t="n"/>
+      <c r="AZ24" s="324" t="n"/>
+      <c r="BA24" s="325" t="n"/>
+      <c r="BB24" s="298" t="n"/>
+      <c r="BC24" s="324" t="n"/>
+      <c r="BD24" s="326" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="294">
+        <f>ROW()-ROW($A$16)+1</f>
+        <v/>
+      </c>
+      <c r="B25" s="276" t="n"/>
+      <c r="C25" s="277" t="n"/>
+      <c r="D25" s="295" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="324" t="n"/>
+      <c r="F25" s="324" t="n"/>
+      <c r="G25" s="325" t="n"/>
+      <c r="H25" s="296" t="n"/>
+      <c r="I25" s="324" t="n"/>
+      <c r="J25" s="324" t="n"/>
+      <c r="K25" s="324" t="n"/>
+      <c r="L25" s="324" t="n"/>
+      <c r="M25" s="324" t="n"/>
+      <c r="N25" s="324" t="n"/>
+      <c r="O25" s="324" t="n"/>
+      <c r="P25" s="324" t="n"/>
+      <c r="Q25" s="324" t="n"/>
+      <c r="R25" s="324" t="n"/>
+      <c r="S25" s="324" t="n"/>
+      <c r="T25" s="324" t="n"/>
+      <c r="U25" s="324" t="n"/>
+      <c r="V25" s="324" t="n"/>
+      <c r="W25" s="324" t="n"/>
+      <c r="X25" s="324" t="n"/>
+      <c r="Y25" s="324" t="n"/>
+      <c r="Z25" s="325" t="n"/>
+      <c r="AA25" s="297" t="n"/>
+      <c r="AB25" s="324" t="n"/>
+      <c r="AC25" s="324" t="n"/>
+      <c r="AD25" s="324" t="n"/>
+      <c r="AE25" s="324" t="n"/>
+      <c r="AF25" s="324" t="n"/>
+      <c r="AG25" s="324" t="n"/>
+      <c r="AH25" s="324" t="n"/>
+      <c r="AI25" s="324" t="n"/>
+      <c r="AJ25" s="324" t="n"/>
+      <c r="AK25" s="324" t="n"/>
+      <c r="AL25" s="324" t="n"/>
+      <c r="AM25" s="324" t="n"/>
+      <c r="AN25" s="324" t="n"/>
+      <c r="AO25" s="324" t="n"/>
+      <c r="AP25" s="324" t="n"/>
+      <c r="AQ25" s="325" t="n"/>
+      <c r="AR25" s="296" t="n"/>
+      <c r="AS25" s="324" t="n"/>
+      <c r="AT25" s="324" t="n"/>
+      <c r="AU25" s="324" t="n"/>
+      <c r="AV25" s="324" t="n"/>
+      <c r="AW25" s="325" t="n"/>
+      <c r="AX25" s="296" t="n"/>
+      <c r="AY25" s="324" t="n"/>
+      <c r="AZ25" s="324" t="n"/>
+      <c r="BA25" s="325" t="n"/>
+      <c r="BB25" s="298" t="n"/>
+      <c r="BC25" s="324" t="n"/>
+      <c r="BD25" s="326" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="294" t="n"/>
+      <c r="D26" s="299" t="n"/>
+      <c r="H26" s="300" t="n"/>
+      <c r="AA26" s="301" t="n"/>
+      <c r="AR26" s="302" t="n"/>
+      <c r="AX26" s="302" t="n"/>
+      <c r="BB26" s="303" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="284" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
         </is>
       </c>
-      <c r="B24" s="285" t="n"/>
-      <c r="C24" s="285" t="n"/>
-      <c r="D24" s="285" t="n"/>
-      <c r="E24" s="285" t="n"/>
-      <c r="F24" s="285" t="n"/>
-      <c r="G24" s="285" t="n"/>
-      <c r="H24" s="285" t="n"/>
-      <c r="I24" s="285" t="n"/>
-      <c r="J24" s="285" t="n"/>
-      <c r="K24" s="285" t="n"/>
-      <c r="L24" s="285" t="n"/>
-      <c r="M24" s="285" t="n"/>
-      <c r="N24" s="285" t="n"/>
-      <c r="O24" s="285" t="n"/>
-      <c r="P24" s="285" t="n"/>
-      <c r="Q24" s="285" t="n"/>
-      <c r="R24" s="285" t="n"/>
-      <c r="S24" s="285" t="n"/>
-      <c r="T24" s="285" t="n"/>
-      <c r="U24" s="285" t="n"/>
-      <c r="V24" s="285" t="n"/>
-      <c r="W24" s="285" t="n"/>
-      <c r="X24" s="285" t="n"/>
-      <c r="Y24" s="285" t="n"/>
-      <c r="Z24" s="285" t="n"/>
-      <c r="AA24" s="285" t="n"/>
-      <c r="AB24" s="285" t="n"/>
-      <c r="AC24" s="285" t="n"/>
-      <c r="AD24" s="285" t="n"/>
-      <c r="AE24" s="285" t="n"/>
-      <c r="AF24" s="285" t="n"/>
-      <c r="AG24" s="285" t="n"/>
-      <c r="AH24" s="285" t="n"/>
-      <c r="AI24" s="285" t="n"/>
-      <c r="AJ24" s="285" t="n"/>
-      <c r="AK24" s="285" t="n"/>
-      <c r="AL24" s="285" t="n"/>
-      <c r="AM24" s="285" t="n"/>
-      <c r="AN24" s="285" t="n"/>
-      <c r="AO24" s="285" t="n"/>
-      <c r="AP24" s="285" t="n"/>
-      <c r="AQ24" s="285" t="n"/>
-      <c r="AR24" s="285" t="n"/>
-      <c r="AS24" s="285" t="n"/>
-      <c r="AT24" s="285" t="n"/>
-      <c r="AU24" s="285" t="n"/>
-      <c r="AV24" s="285" t="n"/>
-      <c r="AW24" s="285" t="n"/>
-      <c r="AX24" s="285" t="n"/>
-      <c r="AY24" s="285" t="n"/>
-      <c r="AZ24" s="285" t="n"/>
-      <c r="BA24" s="285" t="n"/>
-      <c r="BB24" s="285" t="n"/>
-      <c r="BC24" s="285" t="n"/>
-      <c r="BD24" s="286" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="287" t="inlineStr">
+      <c r="B27" s="285" t="n"/>
+      <c r="C27" s="285" t="n"/>
+      <c r="D27" s="285" t="n"/>
+      <c r="E27" s="285" t="n"/>
+      <c r="F27" s="285" t="n"/>
+      <c r="G27" s="285" t="n"/>
+      <c r="H27" s="285" t="n"/>
+      <c r="I27" s="285" t="n"/>
+      <c r="J27" s="285" t="n"/>
+      <c r="K27" s="285" t="n"/>
+      <c r="L27" s="285" t="n"/>
+      <c r="M27" s="285" t="n"/>
+      <c r="N27" s="285" t="n"/>
+      <c r="O27" s="285" t="n"/>
+      <c r="P27" s="285" t="n"/>
+      <c r="Q27" s="285" t="n"/>
+      <c r="R27" s="285" t="n"/>
+      <c r="S27" s="285" t="n"/>
+      <c r="T27" s="285" t="n"/>
+      <c r="U27" s="285" t="n"/>
+      <c r="V27" s="285" t="n"/>
+      <c r="W27" s="285" t="n"/>
+      <c r="X27" s="285" t="n"/>
+      <c r="Y27" s="285" t="n"/>
+      <c r="Z27" s="285" t="n"/>
+      <c r="AA27" s="285" t="n"/>
+      <c r="AB27" s="285" t="n"/>
+      <c r="AC27" s="285" t="n"/>
+      <c r="AD27" s="285" t="n"/>
+      <c r="AE27" s="285" t="n"/>
+      <c r="AF27" s="285" t="n"/>
+      <c r="AG27" s="285" t="n"/>
+      <c r="AH27" s="285" t="n"/>
+      <c r="AI27" s="285" t="n"/>
+      <c r="AJ27" s="285" t="n"/>
+      <c r="AK27" s="285" t="n"/>
+      <c r="AL27" s="285" t="n"/>
+      <c r="AM27" s="285" t="n"/>
+      <c r="AN27" s="285" t="n"/>
+      <c r="AO27" s="285" t="n"/>
+      <c r="AP27" s="285" t="n"/>
+      <c r="AQ27" s="285" t="n"/>
+      <c r="AR27" s="285" t="n"/>
+      <c r="AS27" s="285" t="n"/>
+      <c r="AT27" s="285" t="n"/>
+      <c r="AU27" s="285" t="n"/>
+      <c r="AV27" s="285" t="n"/>
+      <c r="AW27" s="285" t="n"/>
+      <c r="AX27" s="285" t="n"/>
+      <c r="AY27" s="285" t="n"/>
+      <c r="AZ27" s="285" t="n"/>
+      <c r="BA27" s="285" t="n"/>
+      <c r="BB27" s="285" t="n"/>
+      <c r="BC27" s="285" t="n"/>
+      <c r="BD27" s="286" t="n"/>
+    </row>
+    <row r="28" ht="4" customHeight="1">
+      <c r="A28" s="287" t="inlineStr">
         <is>
           <t>Disposition / Release Decision</t>
         </is>
       </c>
-      <c r="B25" s="271" t="n"/>
-      <c r="C25" s="271" t="n"/>
-      <c r="D25" s="271" t="n"/>
-      <c r="E25" s="271" t="n"/>
-      <c r="F25" s="271" t="n"/>
-      <c r="G25" s="271" t="n"/>
-      <c r="H25" s="271" t="n"/>
-      <c r="I25" s="271" t="n"/>
-      <c r="J25" s="272" t="n"/>
-      <c r="K25" s="288" t="n"/>
-      <c r="L25" s="321" t="n"/>
-      <c r="M25" s="321" t="n"/>
-      <c r="N25" s="321" t="n"/>
-      <c r="O25" s="321" t="n"/>
-      <c r="P25" s="321" t="n"/>
-      <c r="Q25" s="321" t="n"/>
-      <c r="R25" s="321" t="n"/>
-      <c r="S25" s="321" t="n"/>
-      <c r="T25" s="321" t="n"/>
-      <c r="U25" s="321" t="n"/>
-      <c r="V25" s="321" t="n"/>
-      <c r="W25" s="321" t="n"/>
-      <c r="X25" s="321" t="n"/>
-      <c r="Y25" s="321" t="n"/>
-      <c r="Z25" s="321" t="n"/>
-      <c r="AA25" s="321" t="n"/>
-      <c r="AB25" s="322" t="n"/>
-      <c r="AC25" s="289" t="inlineStr">
+      <c r="B28" s="271" t="n"/>
+      <c r="C28" s="271" t="n"/>
+      <c r="D28" s="271" t="n"/>
+      <c r="E28" s="271" t="n"/>
+      <c r="F28" s="271" t="n"/>
+      <c r="G28" s="271" t="n"/>
+      <c r="H28" s="271" t="n"/>
+      <c r="I28" s="271" t="n"/>
+      <c r="J28" s="272" t="n"/>
+      <c r="K28" s="288" t="n"/>
+      <c r="L28" s="321" t="n"/>
+      <c r="M28" s="321" t="n"/>
+      <c r="N28" s="321" t="n"/>
+      <c r="O28" s="321" t="n"/>
+      <c r="P28" s="321" t="n"/>
+      <c r="Q28" s="321" t="n"/>
+      <c r="R28" s="321" t="n"/>
+      <c r="S28" s="321" t="n"/>
+      <c r="T28" s="321" t="n"/>
+      <c r="U28" s="321" t="n"/>
+      <c r="V28" s="321" t="n"/>
+      <c r="W28" s="321" t="n"/>
+      <c r="X28" s="321" t="n"/>
+      <c r="Y28" s="321" t="n"/>
+      <c r="Z28" s="321" t="n"/>
+      <c r="AA28" s="321" t="n"/>
+      <c r="AB28" s="322" t="n"/>
+      <c r="AC28" s="289" t="inlineStr">
         <is>
           <t>Linked NCR / Concession</t>
         </is>
       </c>
-      <c r="AD25" s="271" t="n"/>
-      <c r="AE25" s="271" t="n"/>
-      <c r="AF25" s="271" t="n"/>
-      <c r="AG25" s="271" t="n"/>
-      <c r="AH25" s="271" t="n"/>
-      <c r="AI25" s="271" t="n"/>
-      <c r="AJ25" s="271" t="n"/>
-      <c r="AK25" s="271" t="n"/>
-      <c r="AL25" s="272" t="n"/>
-      <c r="AM25" s="290" t="n"/>
-      <c r="AN25" s="321" t="n"/>
-      <c r="AO25" s="321" t="n"/>
-      <c r="AP25" s="321" t="n"/>
-      <c r="AQ25" s="321" t="n"/>
-      <c r="AR25" s="321" t="n"/>
-      <c r="AS25" s="321" t="n"/>
-      <c r="AT25" s="321" t="n"/>
-      <c r="AU25" s="321" t="n"/>
-      <c r="AV25" s="321" t="n"/>
-      <c r="AW25" s="321" t="n"/>
-      <c r="AX25" s="321" t="n"/>
-      <c r="AY25" s="321" t="n"/>
-      <c r="AZ25" s="321" t="n"/>
-      <c r="BA25" s="321" t="n"/>
-      <c r="BB25" s="321" t="n"/>
-      <c r="BC25" s="321" t="n"/>
-      <c r="BD25" s="323" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="287" t="inlineStr">
+      <c r="AD28" s="271" t="n"/>
+      <c r="AE28" s="271" t="n"/>
+      <c r="AF28" s="271" t="n"/>
+      <c r="AG28" s="271" t="n"/>
+      <c r="AH28" s="271" t="n"/>
+      <c r="AI28" s="271" t="n"/>
+      <c r="AJ28" s="271" t="n"/>
+      <c r="AK28" s="271" t="n"/>
+      <c r="AL28" s="272" t="n"/>
+      <c r="AM28" s="290" t="n"/>
+      <c r="AN28" s="321" t="n"/>
+      <c r="AO28" s="321" t="n"/>
+      <c r="AP28" s="321" t="n"/>
+      <c r="AQ28" s="321" t="n"/>
+      <c r="AR28" s="321" t="n"/>
+      <c r="AS28" s="321" t="n"/>
+      <c r="AT28" s="321" t="n"/>
+      <c r="AU28" s="321" t="n"/>
+      <c r="AV28" s="321" t="n"/>
+      <c r="AW28" s="321" t="n"/>
+      <c r="AX28" s="321" t="n"/>
+      <c r="AY28" s="321" t="n"/>
+      <c r="AZ28" s="321" t="n"/>
+      <c r="BA28" s="321" t="n"/>
+      <c r="BB28" s="321" t="n"/>
+      <c r="BC28" s="321" t="n"/>
+      <c r="BD28" s="323" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="287" t="inlineStr">
         <is>
           <t>Cleanliness / Packaging Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="271" t="n"/>
-      <c r="C26" s="271" t="n"/>
-      <c r="D26" s="271" t="n"/>
-      <c r="E26" s="271" t="n"/>
-      <c r="F26" s="271" t="n"/>
-      <c r="G26" s="271" t="n"/>
-      <c r="H26" s="271" t="n"/>
-      <c r="I26" s="271" t="n"/>
-      <c r="J26" s="272" t="n"/>
-      <c r="K26" s="288" t="n"/>
-      <c r="L26" s="321" t="n"/>
-      <c r="M26" s="321" t="n"/>
-      <c r="N26" s="321" t="n"/>
-      <c r="O26" s="321" t="n"/>
-      <c r="P26" s="321" t="n"/>
-      <c r="Q26" s="321" t="n"/>
-      <c r="R26" s="321" t="n"/>
-      <c r="S26" s="321" t="n"/>
-      <c r="T26" s="321" t="n"/>
-      <c r="U26" s="321" t="n"/>
-      <c r="V26" s="321" t="n"/>
-      <c r="W26" s="321" t="n"/>
-      <c r="X26" s="321" t="n"/>
-      <c r="Y26" s="321" t="n"/>
-      <c r="Z26" s="321" t="n"/>
-      <c r="AA26" s="321" t="n"/>
-      <c r="AB26" s="322" t="n"/>
-      <c r="AC26" s="289" t="inlineStr">
+      <c r="B29" s="271" t="n"/>
+      <c r="C29" s="271" t="n"/>
+      <c r="D29" s="271" t="n"/>
+      <c r="E29" s="271" t="n"/>
+      <c r="F29" s="271" t="n"/>
+      <c r="G29" s="271" t="n"/>
+      <c r="H29" s="271" t="n"/>
+      <c r="I29" s="271" t="n"/>
+      <c r="J29" s="272" t="n"/>
+      <c r="K29" s="288" t="n"/>
+      <c r="L29" s="321" t="n"/>
+      <c r="M29" s="321" t="n"/>
+      <c r="N29" s="321" t="n"/>
+      <c r="O29" s="321" t="n"/>
+      <c r="P29" s="321" t="n"/>
+      <c r="Q29" s="321" t="n"/>
+      <c r="R29" s="321" t="n"/>
+      <c r="S29" s="321" t="n"/>
+      <c r="T29" s="321" t="n"/>
+      <c r="U29" s="321" t="n"/>
+      <c r="V29" s="321" t="n"/>
+      <c r="W29" s="321" t="n"/>
+      <c r="X29" s="321" t="n"/>
+      <c r="Y29" s="321" t="n"/>
+      <c r="Z29" s="321" t="n"/>
+      <c r="AA29" s="321" t="n"/>
+      <c r="AB29" s="322" t="n"/>
+      <c r="AC29" s="289" t="inlineStr">
         <is>
           <t>Label / Doc Verified (YES/NO)</t>
         </is>
       </c>
-      <c r="AD26" s="271" t="n"/>
-      <c r="AE26" s="271" t="n"/>
-      <c r="AF26" s="271" t="n"/>
-      <c r="AG26" s="271" t="n"/>
-      <c r="AH26" s="271" t="n"/>
-      <c r="AI26" s="271" t="n"/>
-      <c r="AJ26" s="271" t="n"/>
-      <c r="AK26" s="271" t="n"/>
-      <c r="AL26" s="272" t="n"/>
-      <c r="AM26" s="290" t="n"/>
-      <c r="AN26" s="321" t="n"/>
-      <c r="AO26" s="321" t="n"/>
-      <c r="AP26" s="321" t="n"/>
-      <c r="AQ26" s="321" t="n"/>
-      <c r="AR26" s="321" t="n"/>
-      <c r="AS26" s="321" t="n"/>
-      <c r="AT26" s="321" t="n"/>
-      <c r="AU26" s="321" t="n"/>
-      <c r="AV26" s="321" t="n"/>
-      <c r="AW26" s="321" t="n"/>
-      <c r="AX26" s="321" t="n"/>
-      <c r="AY26" s="321" t="n"/>
-      <c r="AZ26" s="321" t="n"/>
-      <c r="BA26" s="321" t="n"/>
-      <c r="BB26" s="321" t="n"/>
-      <c r="BC26" s="321" t="n"/>
-      <c r="BD26" s="323" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="287" t="inlineStr">
+      <c r="AD29" s="271" t="n"/>
+      <c r="AE29" s="271" t="n"/>
+      <c r="AF29" s="271" t="n"/>
+      <c r="AG29" s="271" t="n"/>
+      <c r="AH29" s="271" t="n"/>
+      <c r="AI29" s="271" t="n"/>
+      <c r="AJ29" s="271" t="n"/>
+      <c r="AK29" s="271" t="n"/>
+      <c r="AL29" s="272" t="n"/>
+      <c r="AM29" s="290" t="n"/>
+      <c r="AN29" s="321" t="n"/>
+      <c r="AO29" s="321" t="n"/>
+      <c r="AP29" s="321" t="n"/>
+      <c r="AQ29" s="321" t="n"/>
+      <c r="AR29" s="321" t="n"/>
+      <c r="AS29" s="321" t="n"/>
+      <c r="AT29" s="321" t="n"/>
+      <c r="AU29" s="321" t="n"/>
+      <c r="AV29" s="321" t="n"/>
+      <c r="AW29" s="321" t="n"/>
+      <c r="AX29" s="321" t="n"/>
+      <c r="AY29" s="321" t="n"/>
+      <c r="AZ29" s="321" t="n"/>
+      <c r="BA29" s="321" t="n"/>
+      <c r="BB29" s="321" t="n"/>
+      <c r="BC29" s="321" t="n"/>
+      <c r="BD29" s="323" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="287" t="inlineStr">
         <is>
           <t>Quality Authority</t>
         </is>
       </c>
-      <c r="B27" s="271" t="n"/>
-      <c r="C27" s="271" t="n"/>
-      <c r="D27" s="271" t="n"/>
-      <c r="E27" s="271" t="n"/>
-      <c r="F27" s="271" t="n"/>
-      <c r="G27" s="271" t="n"/>
-      <c r="H27" s="271" t="n"/>
-      <c r="I27" s="271" t="n"/>
-      <c r="J27" s="272" t="n"/>
-      <c r="K27" s="288" t="n"/>
-      <c r="L27" s="321" t="n"/>
-      <c r="M27" s="321" t="n"/>
-      <c r="N27" s="321" t="n"/>
-      <c r="O27" s="321" t="n"/>
-      <c r="P27" s="321" t="n"/>
-      <c r="Q27" s="321" t="n"/>
-      <c r="R27" s="321" t="n"/>
-      <c r="S27" s="321" t="n"/>
-      <c r="T27" s="321" t="n"/>
-      <c r="U27" s="321" t="n"/>
-      <c r="V27" s="321" t="n"/>
-      <c r="W27" s="321" t="n"/>
-      <c r="X27" s="321" t="n"/>
-      <c r="Y27" s="321" t="n"/>
-      <c r="Z27" s="321" t="n"/>
-      <c r="AA27" s="321" t="n"/>
-      <c r="AB27" s="322" t="n"/>
-      <c r="AC27" s="289" t="inlineStr">
+      <c r="B30" s="271" t="n"/>
+      <c r="C30" s="271" t="n"/>
+      <c r="D30" s="271" t="n"/>
+      <c r="E30" s="271" t="n"/>
+      <c r="F30" s="271" t="n"/>
+      <c r="G30" s="271" t="n"/>
+      <c r="H30" s="271" t="n"/>
+      <c r="I30" s="271" t="n"/>
+      <c r="J30" s="272" t="n"/>
+      <c r="K30" s="288" t="n"/>
+      <c r="L30" s="321" t="n"/>
+      <c r="M30" s="321" t="n"/>
+      <c r="N30" s="321" t="n"/>
+      <c r="O30" s="321" t="n"/>
+      <c r="P30" s="321" t="n"/>
+      <c r="Q30" s="321" t="n"/>
+      <c r="R30" s="321" t="n"/>
+      <c r="S30" s="321" t="n"/>
+      <c r="T30" s="321" t="n"/>
+      <c r="U30" s="321" t="n"/>
+      <c r="V30" s="321" t="n"/>
+      <c r="W30" s="321" t="n"/>
+      <c r="X30" s="321" t="n"/>
+      <c r="Y30" s="321" t="n"/>
+      <c r="Z30" s="321" t="n"/>
+      <c r="AA30" s="321" t="n"/>
+      <c r="AB30" s="322" t="n"/>
+      <c r="AC30" s="289" t="inlineStr">
         <is>
           <t>Closeout Status</t>
         </is>
       </c>
-      <c r="AD27" s="271" t="n"/>
-      <c r="AE27" s="271" t="n"/>
-      <c r="AF27" s="271" t="n"/>
-      <c r="AG27" s="271" t="n"/>
-      <c r="AH27" s="271" t="n"/>
-      <c r="AI27" s="271" t="n"/>
-      <c r="AJ27" s="271" t="n"/>
-      <c r="AK27" s="271" t="n"/>
-      <c r="AL27" s="272" t="n"/>
-      <c r="AM27" s="290" t="n"/>
-      <c r="AN27" s="321" t="n"/>
-      <c r="AO27" s="321" t="n"/>
-      <c r="AP27" s="321" t="n"/>
-      <c r="AQ27" s="321" t="n"/>
-      <c r="AR27" s="321" t="n"/>
-      <c r="AS27" s="321" t="n"/>
-      <c r="AT27" s="321" t="n"/>
-      <c r="AU27" s="321" t="n"/>
-      <c r="AV27" s="321" t="n"/>
-      <c r="AW27" s="321" t="n"/>
-      <c r="AX27" s="321" t="n"/>
-      <c r="AY27" s="321" t="n"/>
-      <c r="AZ27" s="321" t="n"/>
-      <c r="BA27" s="321" t="n"/>
-      <c r="BB27" s="321" t="n"/>
-      <c r="BC27" s="321" t="n"/>
-      <c r="BD27" s="323" t="n"/>
-    </row>
-    <row r="28" ht="4" customHeight="1">
-      <c r="A28" s="294" t="n"/>
-      <c r="D28" s="299" t="n"/>
-      <c r="H28" s="304" t="n"/>
-      <c r="AA28" s="301" t="n"/>
-      <c r="AR28" s="302" t="n"/>
-      <c r="AX28" s="302" t="n"/>
-      <c r="BB28" s="303" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="284" t="inlineStr">
+      <c r="AD30" s="271" t="n"/>
+      <c r="AE30" s="271" t="n"/>
+      <c r="AF30" s="271" t="n"/>
+      <c r="AG30" s="271" t="n"/>
+      <c r="AH30" s="271" t="n"/>
+      <c r="AI30" s="271" t="n"/>
+      <c r="AJ30" s="271" t="n"/>
+      <c r="AK30" s="271" t="n"/>
+      <c r="AL30" s="272" t="n"/>
+      <c r="AM30" s="290" t="n"/>
+      <c r="AN30" s="321" t="n"/>
+      <c r="AO30" s="321" t="n"/>
+      <c r="AP30" s="321" t="n"/>
+      <c r="AQ30" s="321" t="n"/>
+      <c r="AR30" s="321" t="n"/>
+      <c r="AS30" s="321" t="n"/>
+      <c r="AT30" s="321" t="n"/>
+      <c r="AU30" s="321" t="n"/>
+      <c r="AV30" s="321" t="n"/>
+      <c r="AW30" s="321" t="n"/>
+      <c r="AX30" s="321" t="n"/>
+      <c r="AY30" s="321" t="n"/>
+      <c r="AZ30" s="321" t="n"/>
+      <c r="BA30" s="321" t="n"/>
+      <c r="BB30" s="321" t="n"/>
+      <c r="BC30" s="321" t="n"/>
+      <c r="BD30" s="323" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="338" t="inlineStr">
+        <is>
+          <t>Concession / Deviation Ref</t>
+        </is>
+      </c>
+      <c r="K31" s="339" t="n"/>
+      <c r="AC31" s="340" t="inlineStr">
+        <is>
+          <t>Packaging Instruction Ref (FRM-707/709)</t>
+        </is>
+      </c>
+      <c r="AJ31" s="341" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="338" t="inlineStr">
+        <is>
+          <t>Safety/Special Char. Verified?</t>
+        </is>
+      </c>
+      <c r="K32" s="339" t="n"/>
+      <c r="AC32" s="340" t="inlineStr">
+        <is>
+          <t>Measurement Uncertainty Noted?</t>
+        </is>
+      </c>
+      <c r="AJ32" s="341" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="294" t="n"/>
+      <c r="D33" s="299" t="n"/>
+      <c r="H33" s="304" t="n"/>
+      <c r="AA33" s="301" t="n"/>
+      <c r="AR33" s="302" t="n"/>
+      <c r="AX33" s="302" t="n"/>
+      <c r="BB33" s="303" t="n"/>
+    </row>
+    <row r="34" ht="4" customHeight="1">
+      <c r="A34" s="284" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="285" t="n"/>
-      <c r="C29" s="285" t="n"/>
-      <c r="D29" s="285" t="n"/>
-      <c r="E29" s="285" t="n"/>
-      <c r="F29" s="285" t="n"/>
-      <c r="G29" s="285" t="n"/>
-      <c r="H29" s="285" t="n"/>
-      <c r="I29" s="285" t="n"/>
-      <c r="J29" s="285" t="n"/>
-      <c r="K29" s="285" t="n"/>
-      <c r="L29" s="285" t="n"/>
-      <c r="M29" s="285" t="n"/>
-      <c r="N29" s="285" t="n"/>
-      <c r="O29" s="285" t="n"/>
-      <c r="P29" s="285" t="n"/>
-      <c r="Q29" s="285" t="n"/>
-      <c r="R29" s="285" t="n"/>
-      <c r="S29" s="285" t="n"/>
-      <c r="T29" s="285" t="n"/>
-      <c r="U29" s="285" t="n"/>
-      <c r="V29" s="285" t="n"/>
-      <c r="W29" s="285" t="n"/>
-      <c r="X29" s="285" t="n"/>
-      <c r="Y29" s="285" t="n"/>
-      <c r="Z29" s="285" t="n"/>
-      <c r="AA29" s="285" t="n"/>
-      <c r="AB29" s="285" t="n"/>
-      <c r="AC29" s="285" t="n"/>
-      <c r="AD29" s="285" t="n"/>
-      <c r="AE29" s="285" t="n"/>
-      <c r="AF29" s="285" t="n"/>
-      <c r="AG29" s="285" t="n"/>
-      <c r="AH29" s="285" t="n"/>
-      <c r="AI29" s="285" t="n"/>
-      <c r="AJ29" s="285" t="n"/>
-      <c r="AK29" s="285" t="n"/>
-      <c r="AL29" s="285" t="n"/>
-      <c r="AM29" s="285" t="n"/>
-      <c r="AN29" s="285" t="n"/>
-      <c r="AO29" s="285" t="n"/>
-      <c r="AP29" s="285" t="n"/>
-      <c r="AQ29" s="285" t="n"/>
-      <c r="AR29" s="285" t="n"/>
-      <c r="AS29" s="285" t="n"/>
-      <c r="AT29" s="285" t="n"/>
-      <c r="AU29" s="285" t="n"/>
-      <c r="AV29" s="285" t="n"/>
-      <c r="AW29" s="285" t="n"/>
-      <c r="AX29" s="285" t="n"/>
-      <c r="AY29" s="285" t="n"/>
-      <c r="AZ29" s="285" t="n"/>
-      <c r="BA29" s="285" t="n"/>
-      <c r="BB29" s="285" t="n"/>
-      <c r="BC29" s="285" t="n"/>
-      <c r="BD29" s="286" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="327" t="inlineStr">
+      <c r="B34" s="285" t="n"/>
+      <c r="C34" s="285" t="n"/>
+      <c r="D34" s="285" t="n"/>
+      <c r="E34" s="285" t="n"/>
+      <c r="F34" s="285" t="n"/>
+      <c r="G34" s="285" t="n"/>
+      <c r="H34" s="285" t="n"/>
+      <c r="I34" s="285" t="n"/>
+      <c r="J34" s="285" t="n"/>
+      <c r="K34" s="285" t="n"/>
+      <c r="L34" s="285" t="n"/>
+      <c r="M34" s="285" t="n"/>
+      <c r="N34" s="285" t="n"/>
+      <c r="O34" s="285" t="n"/>
+      <c r="P34" s="285" t="n"/>
+      <c r="Q34" s="285" t="n"/>
+      <c r="R34" s="285" t="n"/>
+      <c r="S34" s="285" t="n"/>
+      <c r="T34" s="285" t="n"/>
+      <c r="U34" s="285" t="n"/>
+      <c r="V34" s="285" t="n"/>
+      <c r="W34" s="285" t="n"/>
+      <c r="X34" s="285" t="n"/>
+      <c r="Y34" s="285" t="n"/>
+      <c r="Z34" s="285" t="n"/>
+      <c r="AA34" s="285" t="n"/>
+      <c r="AB34" s="285" t="n"/>
+      <c r="AC34" s="285" t="n"/>
+      <c r="AD34" s="285" t="n"/>
+      <c r="AE34" s="285" t="n"/>
+      <c r="AF34" s="285" t="n"/>
+      <c r="AG34" s="285" t="n"/>
+      <c r="AH34" s="285" t="n"/>
+      <c r="AI34" s="285" t="n"/>
+      <c r="AJ34" s="285" t="n"/>
+      <c r="AK34" s="285" t="n"/>
+      <c r="AL34" s="285" t="n"/>
+      <c r="AM34" s="285" t="n"/>
+      <c r="AN34" s="285" t="n"/>
+      <c r="AO34" s="285" t="n"/>
+      <c r="AP34" s="285" t="n"/>
+      <c r="AQ34" s="285" t="n"/>
+      <c r="AR34" s="285" t="n"/>
+      <c r="AS34" s="285" t="n"/>
+      <c r="AT34" s="285" t="n"/>
+      <c r="AU34" s="285" t="n"/>
+      <c r="AV34" s="285" t="n"/>
+      <c r="AW34" s="285" t="n"/>
+      <c r="AX34" s="285" t="n"/>
+      <c r="AY34" s="285" t="n"/>
+      <c r="AZ34" s="285" t="n"/>
+      <c r="BA34" s="285" t="n"/>
+      <c r="BB34" s="285" t="n"/>
+      <c r="BC34" s="285" t="n"/>
+      <c r="BD34" s="286" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="327" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="285" t="n"/>
-      <c r="C30" s="285" t="n"/>
-      <c r="D30" s="285" t="n"/>
-      <c r="E30" s="285" t="n"/>
-      <c r="F30" s="285" t="n"/>
-      <c r="G30" s="285" t="n"/>
-      <c r="H30" s="285" t="n"/>
-      <c r="I30" s="285" t="n"/>
-      <c r="J30" s="285" t="n"/>
-      <c r="K30" s="285" t="n"/>
-      <c r="L30" s="285" t="n"/>
-      <c r="M30" s="285" t="n"/>
-      <c r="N30" s="285" t="n"/>
-      <c r="O30" s="285" t="n"/>
-      <c r="P30" s="285" t="n"/>
-      <c r="Q30" s="285" t="n"/>
-      <c r="R30" s="328" t="n"/>
-      <c r="S30" s="51" t="inlineStr">
+      <c r="B35" s="285" t="n"/>
+      <c r="C35" s="285" t="n"/>
+      <c r="D35" s="285" t="n"/>
+      <c r="E35" s="285" t="n"/>
+      <c r="F35" s="285" t="n"/>
+      <c r="G35" s="285" t="n"/>
+      <c r="H35" s="285" t="n"/>
+      <c r="I35" s="285" t="n"/>
+      <c r="J35" s="285" t="n"/>
+      <c r="K35" s="285" t="n"/>
+      <c r="L35" s="285" t="n"/>
+      <c r="M35" s="285" t="n"/>
+      <c r="N35" s="285" t="n"/>
+      <c r="O35" s="285" t="n"/>
+      <c r="P35" s="285" t="n"/>
+      <c r="Q35" s="285" t="n"/>
+      <c r="R35" s="328" t="n"/>
+      <c r="S35" s="51" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="285" t="n"/>
-      <c r="U30" s="285" t="n"/>
-      <c r="V30" s="285" t="n"/>
-      <c r="W30" s="285" t="n"/>
-      <c r="X30" s="285" t="n"/>
-      <c r="Y30" s="285" t="n"/>
-      <c r="Z30" s="285" t="n"/>
-      <c r="AA30" s="285" t="n"/>
-      <c r="AB30" s="285" t="n"/>
-      <c r="AC30" s="285" t="n"/>
-      <c r="AD30" s="285" t="n"/>
-      <c r="AE30" s="285" t="n"/>
-      <c r="AF30" s="285" t="n"/>
-      <c r="AG30" s="285" t="n"/>
-      <c r="AH30" s="285" t="n"/>
-      <c r="AI30" s="285" t="n"/>
-      <c r="AJ30" s="285" t="n"/>
-      <c r="AK30" s="305" t="inlineStr">
+      <c r="T35" s="285" t="n"/>
+      <c r="U35" s="285" t="n"/>
+      <c r="V35" s="285" t="n"/>
+      <c r="W35" s="285" t="n"/>
+      <c r="X35" s="285" t="n"/>
+      <c r="Y35" s="285" t="n"/>
+      <c r="Z35" s="285" t="n"/>
+      <c r="AA35" s="285" t="n"/>
+      <c r="AB35" s="285" t="n"/>
+      <c r="AC35" s="285" t="n"/>
+      <c r="AD35" s="285" t="n"/>
+      <c r="AE35" s="285" t="n"/>
+      <c r="AF35" s="285" t="n"/>
+      <c r="AG35" s="285" t="n"/>
+      <c r="AH35" s="285" t="n"/>
+      <c r="AI35" s="285" t="n"/>
+      <c r="AJ35" s="285" t="n"/>
+      <c r="AK35" s="305" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="285" t="n"/>
-      <c r="AM30" s="285" t="n"/>
-      <c r="AN30" s="285" t="n"/>
-      <c r="AO30" s="285" t="n"/>
-      <c r="AP30" s="285" t="n"/>
-      <c r="AQ30" s="285" t="n"/>
-      <c r="AR30" s="285" t="n"/>
-      <c r="AS30" s="285" t="n"/>
-      <c r="AT30" s="285" t="n"/>
-      <c r="AU30" s="285" t="n"/>
-      <c r="AV30" s="285" t="n"/>
-      <c r="AW30" s="285" t="n"/>
-      <c r="AX30" s="285" t="n"/>
-      <c r="AY30" s="285" t="n"/>
-      <c r="AZ30" s="285" t="n"/>
-      <c r="BA30" s="285" t="n"/>
-      <c r="BB30" s="285" t="n"/>
-      <c r="BC30" s="285" t="n"/>
-      <c r="BD30" s="286" t="n"/>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="306" t="inlineStr">
+      <c r="AL35" s="285" t="n"/>
+      <c r="AM35" s="285" t="n"/>
+      <c r="AN35" s="285" t="n"/>
+      <c r="AO35" s="285" t="n"/>
+      <c r="AP35" s="285" t="n"/>
+      <c r="AQ35" s="285" t="n"/>
+      <c r="AR35" s="285" t="n"/>
+      <c r="AS35" s="285" t="n"/>
+      <c r="AT35" s="285" t="n"/>
+      <c r="AU35" s="285" t="n"/>
+      <c r="AV35" s="285" t="n"/>
+      <c r="AW35" s="285" t="n"/>
+      <c r="AX35" s="285" t="n"/>
+      <c r="AY35" s="285" t="n"/>
+      <c r="AZ35" s="285" t="n"/>
+      <c r="BA35" s="285" t="n"/>
+      <c r="BB35" s="285" t="n"/>
+      <c r="BC35" s="285" t="n"/>
+      <c r="BD35" s="286" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="306" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="329" t="n"/>
-      <c r="C31" s="329" t="n"/>
-      <c r="D31" s="329" t="n"/>
-      <c r="E31" s="329" t="n"/>
-      <c r="F31" s="329" t="n"/>
-      <c r="G31" s="329" t="n"/>
-      <c r="H31" s="329" t="n"/>
-      <c r="I31" s="329" t="n"/>
-      <c r="J31" s="329" t="n"/>
-      <c r="K31" s="329" t="n"/>
-      <c r="L31" s="329" t="n"/>
-      <c r="M31" s="329" t="n"/>
-      <c r="N31" s="329" t="n"/>
-      <c r="O31" s="329" t="n"/>
-      <c r="P31" s="329" t="n"/>
-      <c r="Q31" s="329" t="n"/>
-      <c r="R31" s="330" t="n"/>
-      <c r="S31" s="306" t="inlineStr">
+      <c r="B36" s="329" t="n"/>
+      <c r="C36" s="329" t="n"/>
+      <c r="D36" s="329" t="n"/>
+      <c r="E36" s="329" t="n"/>
+      <c r="F36" s="329" t="n"/>
+      <c r="G36" s="329" t="n"/>
+      <c r="H36" s="329" t="n"/>
+      <c r="I36" s="329" t="n"/>
+      <c r="J36" s="329" t="n"/>
+      <c r="K36" s="329" t="n"/>
+      <c r="L36" s="329" t="n"/>
+      <c r="M36" s="329" t="n"/>
+      <c r="N36" s="329" t="n"/>
+      <c r="O36" s="329" t="n"/>
+      <c r="P36" s="329" t="n"/>
+      <c r="Q36" s="329" t="n"/>
+      <c r="R36" s="330" t="n"/>
+      <c r="S36" s="306" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="329" t="n"/>
-      <c r="U31" s="329" t="n"/>
-      <c r="V31" s="329" t="n"/>
-      <c r="W31" s="329" t="n"/>
-      <c r="X31" s="329" t="n"/>
-      <c r="Y31" s="329" t="n"/>
-      <c r="Z31" s="329" t="n"/>
-      <c r="AA31" s="329" t="n"/>
-      <c r="AB31" s="329" t="n"/>
-      <c r="AC31" s="329" t="n"/>
-      <c r="AD31" s="329" t="n"/>
-      <c r="AE31" s="329" t="n"/>
-      <c r="AF31" s="329" t="n"/>
-      <c r="AG31" s="329" t="n"/>
-      <c r="AH31" s="329" t="n"/>
-      <c r="AI31" s="329" t="n"/>
-      <c r="AJ31" s="330" t="n"/>
-      <c r="AK31" s="306" t="inlineStr">
+      <c r="T36" s="329" t="n"/>
+      <c r="U36" s="329" t="n"/>
+      <c r="V36" s="329" t="n"/>
+      <c r="W36" s="329" t="n"/>
+      <c r="X36" s="329" t="n"/>
+      <c r="Y36" s="329" t="n"/>
+      <c r="Z36" s="329" t="n"/>
+      <c r="AA36" s="329" t="n"/>
+      <c r="AB36" s="329" t="n"/>
+      <c r="AC36" s="329" t="n"/>
+      <c r="AD36" s="329" t="n"/>
+      <c r="AE36" s="329" t="n"/>
+      <c r="AF36" s="329" t="n"/>
+      <c r="AG36" s="329" t="n"/>
+      <c r="AH36" s="329" t="n"/>
+      <c r="AI36" s="329" t="n"/>
+      <c r="AJ36" s="330" t="n"/>
+      <c r="AK36" s="306" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="329" t="n"/>
-      <c r="AM31" s="329" t="n"/>
-      <c r="AN31" s="329" t="n"/>
-      <c r="AO31" s="329" t="n"/>
-      <c r="AP31" s="329" t="n"/>
-      <c r="AQ31" s="329" t="n"/>
-      <c r="AR31" s="329" t="n"/>
-      <c r="AS31" s="329" t="n"/>
-      <c r="AT31" s="329" t="n"/>
-      <c r="AU31" s="329" t="n"/>
-      <c r="AV31" s="329" t="n"/>
-      <c r="AW31" s="329" t="n"/>
-      <c r="AX31" s="329" t="n"/>
-      <c r="AY31" s="329" t="n"/>
-      <c r="AZ31" s="329" t="n"/>
-      <c r="BA31" s="329" t="n"/>
-      <c r="BB31" s="329" t="n"/>
-      <c r="BC31" s="329" t="n"/>
-      <c r="BD31" s="330" t="n"/>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="331" t="n"/>
-      <c r="B32" s="332" t="n"/>
-      <c r="C32" s="332" t="n"/>
-      <c r="D32" s="332" t="n"/>
-      <c r="E32" s="332" t="n"/>
-      <c r="F32" s="332" t="n"/>
-      <c r="G32" s="332" t="n"/>
-      <c r="H32" s="332" t="n"/>
-      <c r="I32" s="332" t="n"/>
-      <c r="J32" s="332" t="n"/>
-      <c r="K32" s="332" t="n"/>
-      <c r="L32" s="332" t="n"/>
-      <c r="M32" s="332" t="n"/>
-      <c r="N32" s="332" t="n"/>
-      <c r="O32" s="332" t="n"/>
-      <c r="P32" s="332" t="n"/>
-      <c r="Q32" s="332" t="n"/>
-      <c r="R32" s="333" t="n"/>
-      <c r="S32" s="331" t="n"/>
-      <c r="T32" s="332" t="n"/>
-      <c r="U32" s="332" t="n"/>
-      <c r="V32" s="332" t="n"/>
-      <c r="W32" s="332" t="n"/>
-      <c r="X32" s="332" t="n"/>
-      <c r="Y32" s="332" t="n"/>
-      <c r="Z32" s="332" t="n"/>
-      <c r="AA32" s="332" t="n"/>
-      <c r="AB32" s="332" t="n"/>
-      <c r="AC32" s="332" t="n"/>
-      <c r="AD32" s="332" t="n"/>
-      <c r="AE32" s="332" t="n"/>
-      <c r="AF32" s="332" t="n"/>
-      <c r="AG32" s="332" t="n"/>
-      <c r="AH32" s="332" t="n"/>
-      <c r="AI32" s="332" t="n"/>
-      <c r="AJ32" s="333" t="n"/>
-      <c r="AK32" s="331" t="n"/>
-      <c r="AL32" s="332" t="n"/>
-      <c r="AM32" s="332" t="n"/>
-      <c r="AN32" s="332" t="n"/>
-      <c r="AO32" s="332" t="n"/>
-      <c r="AP32" s="332" t="n"/>
-      <c r="AQ32" s="332" t="n"/>
-      <c r="AR32" s="332" t="n"/>
-      <c r="AS32" s="332" t="n"/>
-      <c r="AT32" s="332" t="n"/>
-      <c r="AU32" s="332" t="n"/>
-      <c r="AV32" s="332" t="n"/>
-      <c r="AW32" s="332" t="n"/>
-      <c r="AX32" s="332" t="n"/>
-      <c r="AY32" s="332" t="n"/>
-      <c r="AZ32" s="332" t="n"/>
-      <c r="BA32" s="332" t="n"/>
-      <c r="BB32" s="332" t="n"/>
-      <c r="BC32" s="332" t="n"/>
-      <c r="BD32" s="333" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="334" t="n"/>
-      <c r="B33" s="335" t="n"/>
-      <c r="C33" s="335" t="n"/>
-      <c r="D33" s="335" t="n"/>
-      <c r="E33" s="335" t="n"/>
-      <c r="F33" s="335" t="n"/>
-      <c r="G33" s="335" t="n"/>
-      <c r="H33" s="335" t="n"/>
-      <c r="I33" s="335" t="n"/>
-      <c r="J33" s="335" t="n"/>
-      <c r="K33" s="335" t="n"/>
-      <c r="L33" s="335" t="n"/>
-      <c r="M33" s="335" t="n"/>
-      <c r="N33" s="335" t="n"/>
-      <c r="O33" s="335" t="n"/>
-      <c r="P33" s="335" t="n"/>
-      <c r="Q33" s="335" t="n"/>
-      <c r="R33" s="336" t="n"/>
-      <c r="S33" s="334" t="n"/>
-      <c r="T33" s="335" t="n"/>
-      <c r="U33" s="335" t="n"/>
-      <c r="V33" s="335" t="n"/>
-      <c r="W33" s="335" t="n"/>
-      <c r="X33" s="335" t="n"/>
-      <c r="Y33" s="335" t="n"/>
-      <c r="Z33" s="335" t="n"/>
-      <c r="AA33" s="335" t="n"/>
-      <c r="AB33" s="335" t="n"/>
-      <c r="AC33" s="335" t="n"/>
-      <c r="AD33" s="335" t="n"/>
-      <c r="AE33" s="335" t="n"/>
-      <c r="AF33" s="335" t="n"/>
-      <c r="AG33" s="335" t="n"/>
-      <c r="AH33" s="335" t="n"/>
-      <c r="AI33" s="335" t="n"/>
-      <c r="AJ33" s="336" t="n"/>
-      <c r="AK33" s="334" t="n"/>
-      <c r="AL33" s="335" t="n"/>
-      <c r="AM33" s="335" t="n"/>
-      <c r="AN33" s="335" t="n"/>
-      <c r="AO33" s="335" t="n"/>
-      <c r="AP33" s="335" t="n"/>
-      <c r="AQ33" s="335" t="n"/>
-      <c r="AR33" s="335" t="n"/>
-      <c r="AS33" s="335" t="n"/>
-      <c r="AT33" s="335" t="n"/>
-      <c r="AU33" s="335" t="n"/>
-      <c r="AV33" s="335" t="n"/>
-      <c r="AW33" s="335" t="n"/>
-      <c r="AX33" s="335" t="n"/>
-      <c r="AY33" s="335" t="n"/>
-      <c r="AZ33" s="335" t="n"/>
-      <c r="BA33" s="335" t="n"/>
-      <c r="BB33" s="335" t="n"/>
-      <c r="BC33" s="335" t="n"/>
-      <c r="BD33" s="336" t="n"/>
-    </row>
-    <row r="34" ht="4" customHeight="1">
-      <c r="A34" s="291" t="n"/>
-      <c r="D34" s="292" t="n"/>
-      <c r="R34" s="292" t="n"/>
-      <c r="AI34" s="292" t="n"/>
-      <c r="AP34" s="292" t="n"/>
-      <c r="AW34" s="292" t="n"/>
-      <c r="BA34" s="293" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="337" t="inlineStr">
-        <is>
-          <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
-        </is>
-      </c>
-      <c r="B35" s="276" t="n"/>
-      <c r="C35" s="276" t="n"/>
-      <c r="D35" s="276" t="n"/>
-      <c r="E35" s="276" t="n"/>
-      <c r="F35" s="276" t="n"/>
-      <c r="G35" s="276" t="n"/>
-      <c r="H35" s="276" t="n"/>
-      <c r="I35" s="276" t="n"/>
-      <c r="J35" s="276" t="n"/>
-      <c r="K35" s="276" t="n"/>
-      <c r="L35" s="276" t="n"/>
-      <c r="M35" s="276" t="n"/>
-      <c r="N35" s="276" t="n"/>
-      <c r="O35" s="276" t="n"/>
-      <c r="P35" s="276" t="n"/>
-      <c r="Q35" s="276" t="n"/>
-      <c r="R35" s="276" t="n"/>
-      <c r="S35" s="276" t="n"/>
-      <c r="T35" s="276" t="n"/>
-      <c r="U35" s="276" t="n"/>
-      <c r="V35" s="276" t="n"/>
-      <c r="W35" s="276" t="n"/>
-      <c r="X35" s="276" t="n"/>
-      <c r="Y35" s="276" t="n"/>
-      <c r="Z35" s="276" t="n"/>
-      <c r="AA35" s="276" t="n"/>
-      <c r="AB35" s="276" t="n"/>
-      <c r="AC35" s="276" t="n"/>
-      <c r="AD35" s="276" t="n"/>
-      <c r="AE35" s="276" t="n"/>
-      <c r="AF35" s="276" t="n"/>
-      <c r="AG35" s="276" t="n"/>
-      <c r="AH35" s="276" t="n"/>
-      <c r="AI35" s="276" t="n"/>
-      <c r="AJ35" s="276" t="n"/>
-      <c r="AK35" s="276" t="n"/>
-      <c r="AL35" s="276" t="n"/>
-      <c r="AM35" s="276" t="n"/>
-      <c r="AN35" s="276" t="n"/>
-      <c r="AO35" s="276" t="n"/>
-      <c r="AP35" s="276" t="n"/>
-      <c r="AQ35" s="276" t="n"/>
-      <c r="AR35" s="276" t="n"/>
-      <c r="AS35" s="276" t="n"/>
-      <c r="AT35" s="276" t="n"/>
-      <c r="AU35" s="276" t="n"/>
-      <c r="AV35" s="276" t="n"/>
-      <c r="AW35" s="276" t="n"/>
-      <c r="AX35" s="276" t="n"/>
-      <c r="AY35" s="276" t="n"/>
-      <c r="AZ35" s="276" t="n"/>
-      <c r="BA35" s="276" t="n"/>
-      <c r="BB35" s="276" t="n"/>
-      <c r="BC35" s="276" t="n"/>
-      <c r="BD35" s="277" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1"/>
-    <row r="38" ht="20" customHeight="1"/>
-    <row r="39" ht="20" customHeight="1"/>
-    <row r="40" ht="4" customHeight="1"/>
+      <c r="AL36" s="329" t="n"/>
+      <c r="AM36" s="329" t="n"/>
+      <c r="AN36" s="329" t="n"/>
+      <c r="AO36" s="329" t="n"/>
+      <c r="AP36" s="329" t="n"/>
+      <c r="AQ36" s="329" t="n"/>
+      <c r="AR36" s="329" t="n"/>
+      <c r="AS36" s="329" t="n"/>
+      <c r="AT36" s="329" t="n"/>
+      <c r="AU36" s="329" t="n"/>
+      <c r="AV36" s="329" t="n"/>
+      <c r="AW36" s="329" t="n"/>
+      <c r="AX36" s="329" t="n"/>
+      <c r="AY36" s="329" t="n"/>
+      <c r="AZ36" s="329" t="n"/>
+      <c r="BA36" s="329" t="n"/>
+      <c r="BB36" s="329" t="n"/>
+      <c r="BC36" s="329" t="n"/>
+      <c r="BD36" s="330" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="331" t="n"/>
+      <c r="B37" s="332" t="n"/>
+      <c r="C37" s="332" t="n"/>
+      <c r="D37" s="332" t="n"/>
+      <c r="E37" s="332" t="n"/>
+      <c r="F37" s="332" t="n"/>
+      <c r="G37" s="332" t="n"/>
+      <c r="H37" s="332" t="n"/>
+      <c r="I37" s="332" t="n"/>
+      <c r="J37" s="332" t="n"/>
+      <c r="K37" s="332" t="n"/>
+      <c r="L37" s="332" t="n"/>
+      <c r="M37" s="332" t="n"/>
+      <c r="N37" s="332" t="n"/>
+      <c r="O37" s="332" t="n"/>
+      <c r="P37" s="332" t="n"/>
+      <c r="Q37" s="332" t="n"/>
+      <c r="R37" s="333" t="n"/>
+      <c r="S37" s="331" t="n"/>
+      <c r="T37" s="332" t="n"/>
+      <c r="U37" s="332" t="n"/>
+      <c r="V37" s="332" t="n"/>
+      <c r="W37" s="332" t="n"/>
+      <c r="X37" s="332" t="n"/>
+      <c r="Y37" s="332" t="n"/>
+      <c r="Z37" s="332" t="n"/>
+      <c r="AA37" s="332" t="n"/>
+      <c r="AB37" s="332" t="n"/>
+      <c r="AC37" s="332" t="n"/>
+      <c r="AD37" s="332" t="n"/>
+      <c r="AE37" s="332" t="n"/>
+      <c r="AF37" s="332" t="n"/>
+      <c r="AG37" s="332" t="n"/>
+      <c r="AH37" s="332" t="n"/>
+      <c r="AI37" s="332" t="n"/>
+      <c r="AJ37" s="333" t="n"/>
+      <c r="AK37" s="331" t="n"/>
+      <c r="AL37" s="332" t="n"/>
+      <c r="AM37" s="332" t="n"/>
+      <c r="AN37" s="332" t="n"/>
+      <c r="AO37" s="332" t="n"/>
+      <c r="AP37" s="332" t="n"/>
+      <c r="AQ37" s="332" t="n"/>
+      <c r="AR37" s="332" t="n"/>
+      <c r="AS37" s="332" t="n"/>
+      <c r="AT37" s="332" t="n"/>
+      <c r="AU37" s="332" t="n"/>
+      <c r="AV37" s="332" t="n"/>
+      <c r="AW37" s="332" t="n"/>
+      <c r="AX37" s="332" t="n"/>
+      <c r="AY37" s="332" t="n"/>
+      <c r="AZ37" s="332" t="n"/>
+      <c r="BA37" s="332" t="n"/>
+      <c r="BB37" s="332" t="n"/>
+      <c r="BC37" s="332" t="n"/>
+      <c r="BD37" s="333" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="334" t="n"/>
+      <c r="B38" s="335" t="n"/>
+      <c r="C38" s="335" t="n"/>
+      <c r="D38" s="335" t="n"/>
+      <c r="E38" s="335" t="n"/>
+      <c r="F38" s="335" t="n"/>
+      <c r="G38" s="335" t="n"/>
+      <c r="H38" s="335" t="n"/>
+      <c r="I38" s="335" t="n"/>
+      <c r="J38" s="335" t="n"/>
+      <c r="K38" s="335" t="n"/>
+      <c r="L38" s="335" t="n"/>
+      <c r="M38" s="335" t="n"/>
+      <c r="N38" s="335" t="n"/>
+      <c r="O38" s="335" t="n"/>
+      <c r="P38" s="335" t="n"/>
+      <c r="Q38" s="335" t="n"/>
+      <c r="R38" s="336" t="n"/>
+      <c r="S38" s="334" t="n"/>
+      <c r="T38" s="335" t="n"/>
+      <c r="U38" s="335" t="n"/>
+      <c r="V38" s="335" t="n"/>
+      <c r="W38" s="335" t="n"/>
+      <c r="X38" s="335" t="n"/>
+      <c r="Y38" s="335" t="n"/>
+      <c r="Z38" s="335" t="n"/>
+      <c r="AA38" s="335" t="n"/>
+      <c r="AB38" s="335" t="n"/>
+      <c r="AC38" s="335" t="n"/>
+      <c r="AD38" s="335" t="n"/>
+      <c r="AE38" s="335" t="n"/>
+      <c r="AF38" s="335" t="n"/>
+      <c r="AG38" s="335" t="n"/>
+      <c r="AH38" s="335" t="n"/>
+      <c r="AI38" s="335" t="n"/>
+      <c r="AJ38" s="336" t="n"/>
+      <c r="AK38" s="334" t="n"/>
+      <c r="AL38" s="335" t="n"/>
+      <c r="AM38" s="335" t="n"/>
+      <c r="AN38" s="335" t="n"/>
+      <c r="AO38" s="335" t="n"/>
+      <c r="AP38" s="335" t="n"/>
+      <c r="AQ38" s="335" t="n"/>
+      <c r="AR38" s="335" t="n"/>
+      <c r="AS38" s="335" t="n"/>
+      <c r="AT38" s="335" t="n"/>
+      <c r="AU38" s="335" t="n"/>
+      <c r="AV38" s="335" t="n"/>
+      <c r="AW38" s="335" t="n"/>
+      <c r="AX38" s="335" t="n"/>
+      <c r="AY38" s="335" t="n"/>
+      <c r="AZ38" s="335" t="n"/>
+      <c r="BA38" s="335" t="n"/>
+      <c r="BB38" s="335" t="n"/>
+      <c r="BC38" s="335" t="n"/>
+      <c r="BD38" s="336" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="291" t="n"/>
+      <c r="D39" s="292" t="n"/>
+      <c r="R39" s="292" t="n"/>
+      <c r="AI39" s="292" t="n"/>
+      <c r="AP39" s="292" t="n"/>
+      <c r="AW39" s="292" t="n"/>
+      <c r="BA39" s="293" t="n"/>
+    </row>
+    <row r="40" ht="4" customHeight="1">
+      <c r="A40" s="337" t="inlineStr">
+        <is>
+          <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Ref: SOP-605 / WI-605. Retain 10 years. Flag SC dimensions. Note U(k=2) for tight tolerances. File: FRM-641_{JobNo}_{PartNo}.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" s="276" t="n"/>
+      <c r="C40" s="276" t="n"/>
+      <c r="D40" s="276" t="n"/>
+      <c r="E40" s="276" t="n"/>
+      <c r="F40" s="276" t="n"/>
+      <c r="G40" s="276" t="n"/>
+      <c r="H40" s="276" t="n"/>
+      <c r="I40" s="276" t="n"/>
+      <c r="J40" s="276" t="n"/>
+      <c r="K40" s="276" t="n"/>
+      <c r="L40" s="276" t="n"/>
+      <c r="M40" s="276" t="n"/>
+      <c r="N40" s="276" t="n"/>
+      <c r="O40" s="276" t="n"/>
+      <c r="P40" s="276" t="n"/>
+      <c r="Q40" s="276" t="n"/>
+      <c r="R40" s="276" t="n"/>
+      <c r="S40" s="276" t="n"/>
+      <c r="T40" s="276" t="n"/>
+      <c r="U40" s="276" t="n"/>
+      <c r="V40" s="276" t="n"/>
+      <c r="W40" s="276" t="n"/>
+      <c r="X40" s="276" t="n"/>
+      <c r="Y40" s="276" t="n"/>
+      <c r="Z40" s="276" t="n"/>
+      <c r="AA40" s="276" t="n"/>
+      <c r="AB40" s="276" t="n"/>
+      <c r="AC40" s="276" t="n"/>
+      <c r="AD40" s="276" t="n"/>
+      <c r="AE40" s="276" t="n"/>
+      <c r="AF40" s="276" t="n"/>
+      <c r="AG40" s="276" t="n"/>
+      <c r="AH40" s="276" t="n"/>
+      <c r="AI40" s="276" t="n"/>
+      <c r="AJ40" s="276" t="n"/>
+      <c r="AK40" s="276" t="n"/>
+      <c r="AL40" s="276" t="n"/>
+      <c r="AM40" s="276" t="n"/>
+      <c r="AN40" s="276" t="n"/>
+      <c r="AO40" s="276" t="n"/>
+      <c r="AP40" s="276" t="n"/>
+      <c r="AQ40" s="276" t="n"/>
+      <c r="AR40" s="276" t="n"/>
+      <c r="AS40" s="276" t="n"/>
+      <c r="AT40" s="276" t="n"/>
+      <c r="AU40" s="276" t="n"/>
+      <c r="AV40" s="276" t="n"/>
+      <c r="AW40" s="276" t="n"/>
+      <c r="AX40" s="276" t="n"/>
+      <c r="AY40" s="276" t="n"/>
+      <c r="AZ40" s="276" t="n"/>
+      <c r="BA40" s="276" t="n"/>
+      <c r="BB40" s="276" t="n"/>
+      <c r="BC40" s="276" t="n"/>
+      <c r="BD40" s="277" t="n"/>
+    </row>
     <row r="41" ht="17" customHeight="1"/>
     <row r="42" ht="17" customHeight="1"/>
     <row r="43" ht="26" customHeight="1"/>
@@ -6903,7 +7077,7 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="125">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AX18:BA18"/>
     <mergeCell ref="H19:Z19"/>
@@ -6920,8 +7094,11 @@
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AA20:AQ20"/>
     <mergeCell ref="D21:G21"/>
+    <mergeCell ref="K13:AB13"/>
     <mergeCell ref="H21:Z21"/>
+    <mergeCell ref="AJ31:BD31"/>
     <mergeCell ref="A30:R30"/>
+    <mergeCell ref="K15:AB15"/>
     <mergeCell ref="AA21:AQ21"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="S31:AJ33"/>
@@ -6932,9 +7109,11 @@
     <mergeCell ref="L1:AP3"/>
     <mergeCell ref="AX15:BA15"/>
     <mergeCell ref="AQ2:AV2"/>
+    <mergeCell ref="A13:J13"/>
     <mergeCell ref="AR15:AW15"/>
     <mergeCell ref="A24:BD24"/>
     <mergeCell ref="K27:AB27"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="AM10:BD10"/>
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="A1:K5"/>
@@ -6958,14 +7137,17 @@
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="AC9:AL9"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="K32:AB32"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="AX20:BA20"/>
+    <mergeCell ref="AJ13:BD13"/>
     <mergeCell ref="AC11:AL11"/>
     <mergeCell ref="AX16:BA16"/>
     <mergeCell ref="H18:Z18"/>
     <mergeCell ref="K8:AB8"/>
     <mergeCell ref="AW4:BD4"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="AJ15:BD15"/>
     <mergeCell ref="AQ1:AV1"/>
     <mergeCell ref="AA15:AQ15"/>
     <mergeCell ref="AK30:BD30"/>
@@ -6992,6 +7174,7 @@
     <mergeCell ref="AA19:AQ19"/>
     <mergeCell ref="AM9:BD9"/>
     <mergeCell ref="A10:J10"/>
+    <mergeCell ref="K31:AB31"/>
     <mergeCell ref="AC27:AL27"/>
     <mergeCell ref="AR16:AW16"/>
     <mergeCell ref="K12:AB12"/>
@@ -7005,10 +7188,12 @@
     <mergeCell ref="AR17:AW17"/>
     <mergeCell ref="AX22:BA22"/>
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="AC13:AI13"/>
     <mergeCell ref="AM12:BD12"/>
     <mergeCell ref="AC12:AL12"/>
     <mergeCell ref="AR22:AW22"/>
     <mergeCell ref="AX21:BA21"/>
+    <mergeCell ref="AJ32:BD32"/>
     <mergeCell ref="BB16:BD16"/>
     <mergeCell ref="AM26:BD26"/>
     <mergeCell ref="D16:G16"/>
@@ -7019,7 +7204,29 @@
     <mergeCell ref="A14:BD14"/>
     <mergeCell ref="K26:AB26"/>
   </mergeCells>
-  <dataValidations count="7">
+  <conditionalFormatting sqref="AR19:AW25">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28:AB28">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="12">
     <dataValidation sqref="AM8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
       <formula1>'LISTS'!$B$2:$B$5</formula1>
     </dataValidation>
@@ -7040,6 +7247,21 @@
     </dataValidation>
     <dataValidation sqref="AM27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
       <formula1>'LISTS'!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AJ13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"YES,NO,NA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"YES,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"YES,NO,NA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"YES,NO,NA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AJ32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"YES,NO,NA"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
@@ -7062,7 +7284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7105,7 +7327,16 @@
           <t>YES_NO</t>
         </is>
       </c>
-      <c r="G1" s="265" t="n"/>
+      <c r="G1" s="265" t="inlineStr">
+        <is>
+          <t>RISK_LEVEL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>DISCOVERY_STAGE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="266" t="inlineStr">
@@ -7138,7 +7369,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G2" s="266" t="n"/>
+      <c r="G2" s="266" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>INCOMING</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="266" t="inlineStr">
@@ -7171,7 +7411,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G3" s="266" t="n"/>
+      <c r="G3" s="266" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SETUP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="266" t="inlineStr">
@@ -7200,7 +7449,16 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="G4" s="266" t="n"/>
+      <c r="G4" s="266" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FIRST PIECE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="266" t="inlineStr">
@@ -7225,7 +7483,16 @@
         </is>
       </c>
       <c r="F5" s="266" t="n"/>
-      <c r="G5" s="266" t="n"/>
+      <c r="G5" s="266" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>IN-PROCESS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -7235,6 +7502,11 @@
       </c>
       <c r="F6" s="266" t="n"/>
       <c r="G6" s="266" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FINAL INSPECTION</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -7243,6 +7515,11 @@
         </is>
       </c>
       <c r="F7" s="266" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PACKAGING</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -7251,6 +7528,11 @@
         </is>
       </c>
       <c r="F8" s="266" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SHIPPING</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
@@ -7259,6 +7541,11 @@
         </is>
       </c>
       <c r="F9" s="266" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CUSTOMER</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="C10" t="inlineStr">
@@ -7315,7 +7602,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="317" t="inlineStr">
         <is>
-          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
+          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709. For tight-tolerance features, note U(k=2) in Notes column. Flag Safety/Special Characteristics with SC prefix in Characteristic column.</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7634,7 @@
       </c>
       <c r="F4" s="318" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes / U(k=2)</t>
         </is>
       </c>
       <c r="G4" s="318" t="inlineStr">
@@ -7940,4 +8227,106 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="344" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" s="344" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="344" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="344" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="E1" s="344" t="inlineStr">
+        <is>
+          <t>Approved By</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="345" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" s="345" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" s="345" t="inlineStr">
+        <is>
+          <t>Initial controlled baseline</t>
+        </is>
+      </c>
+      <c r="D2" s="345" t="inlineStr">
+        <is>
+          <t>QMS</t>
+        </is>
+      </c>
+      <c r="E2" s="345" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="345" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" s="345" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="C3" s="345" t="inlineStr">
+        <is>
+          <t>Upgrade: CNC fields, cross-form linkage, conditional formatting, parent procedure ref</t>
+        </is>
+      </c>
+      <c r="D3" s="345" t="inlineStr">
+        <is>
+          <t>QMS</t>
+        </is>
+      </c>
+      <c r="E3" s="345" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINAL_INSP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_REVHIST" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULT_DETAIL" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FINAL_INSP'!$A$1:$BD$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REF_IMPORT'!$A$4:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EVIDENCE_REF'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +466,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="47">
     <fill>
       <patternFill/>
     </fill>
@@ -696,26 +698,8 @@
         <fgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00005A9E"/>
-        <bgColor rgb="00005A9E"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="273">
+  <borders count="271">
     <border>
       <left/>
       <right/>
@@ -3633,40 +3617,12 @@
         <color rgb="000078D4"/>
       </bottom>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="000078D4"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="000078D4"/>
-      </right>
-      <top style="thin">
-        <color rgb="000078D4"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000078D4"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="346">
+  <cellXfs count="338">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4443,64 +4399,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="47" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="48" borderId="271" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="47" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="48" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="47" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="47" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00CC0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFCCCC"/>
-          <bgColor rgb="00FFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFF3C4"/>
-          <bgColor rgb="00FFF3C4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D7F0E2"/>
-          <bgColor rgb="00D7F0E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -4583,105 +4485,6 @@
       <rowOff>257175</rowOff>
     </from>
     <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -5010,7 +4813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BD40"/>
+  <dimension ref="A1:BD35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -5212,7 +5015,7 @@
       <c r="AV3" s="272" t="n"/>
       <c r="AW3" s="273" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AX3" s="271" t="n"/>
@@ -5589,7 +5392,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="287" t="inlineStr">
         <is>
-          <t>Inspection Basis / CMM Program</t>
+          <t>Inspection Basis</t>
         </is>
       </c>
       <c r="B11" s="271" t="n"/>
@@ -5621,7 +5424,7 @@
       <c r="AB11" s="322" t="n"/>
       <c r="AC11" s="289" t="inlineStr">
         <is>
-          <t>CoC Number / FRM-642 Ref</t>
+          <t>Evidence Package Ref</t>
         </is>
       </c>
       <c r="AD11" s="271" t="n"/>
@@ -5655,7 +5458,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="287" t="inlineStr">
         <is>
-          <t>Prepared by / Date-Time</t>
+          <t>Linked FRM-642 / FRM-651</t>
         </is>
       </c>
       <c r="B12" s="271" t="n"/>
@@ -5687,7 +5490,7 @@
       <c r="AB12" s="322" t="n"/>
       <c r="AC12" s="289" t="inlineStr">
         <is>
-          <t>Record Status</t>
+          <t>Ref: SOP-605</t>
         </is>
       </c>
       <c r="AD12" s="271" t="n"/>
@@ -5699,7 +5502,11 @@
       <c r="AJ12" s="271" t="n"/>
       <c r="AK12" s="271" t="n"/>
       <c r="AL12" s="272" t="n"/>
-      <c r="AM12" s="290" t="n"/>
+      <c r="AM12" s="290" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AN12" s="321" t="n"/>
       <c r="AO12" s="321" t="n"/>
       <c r="AP12" s="321" t="n"/>
@@ -5718,206 +5525,351 @@
       <c r="BC12" s="321" t="n"/>
       <c r="BD12" s="323" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="338" t="inlineStr">
-        <is>
-          <t>CMM Report Attached?</t>
-        </is>
-      </c>
-      <c r="K13" s="339" t="n"/>
-      <c r="AC13" s="340" t="inlineStr">
-        <is>
-          <t>Customer Source Insp. Required?</t>
-        </is>
-      </c>
-      <c r="AJ13" s="341" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="338" t="inlineStr">
-        <is>
-          <t>Linked NCR Refs (FRM-651)</t>
-        </is>
-      </c>
-      <c r="K14" s="339" t="n"/>
-      <c r="AC14" s="340" t="inlineStr">
-        <is>
-          <t>Linked Setup Sheet (FRM-302)</t>
-        </is>
-      </c>
-      <c r="AJ14" s="341" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="338" t="inlineStr">
-        <is>
-          <t>Ref: SOP-605 / WI-605</t>
-        </is>
-      </c>
-      <c r="K15" s="342" t="inlineStr">
-        <is>
-          <t>SOP-605 (Final Inspection and Release)</t>
-        </is>
-      </c>
-      <c r="AC15" s="340" t="inlineStr">
-        <is>
-          <t>Retain: 10 years</t>
-        </is>
-      </c>
-      <c r="AJ15" s="343" t="inlineStr">
-        <is>
-          <t>Per QMS retention schedule</t>
-        </is>
-      </c>
+    <row r="13" ht="4" customHeight="1">
+      <c r="A13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
+        </is>
+      </c>
+      <c r="B14" s="285" t="n"/>
+      <c r="C14" s="285" t="n"/>
+      <c r="D14" s="285" t="n"/>
+      <c r="E14" s="285" t="n"/>
+      <c r="F14" s="285" t="n"/>
+      <c r="G14" s="285" t="n"/>
+      <c r="H14" s="285" t="n"/>
+      <c r="I14" s="285" t="n"/>
+      <c r="J14" s="285" t="n"/>
+      <c r="K14" s="285" t="n"/>
+      <c r="L14" s="285" t="n"/>
+      <c r="M14" s="285" t="n"/>
+      <c r="N14" s="285" t="n"/>
+      <c r="O14" s="285" t="n"/>
+      <c r="P14" s="285" t="n"/>
+      <c r="Q14" s="285" t="n"/>
+      <c r="R14" s="285" t="n"/>
+      <c r="S14" s="285" t="n"/>
+      <c r="T14" s="285" t="n"/>
+      <c r="U14" s="285" t="n"/>
+      <c r="V14" s="285" t="n"/>
+      <c r="W14" s="285" t="n"/>
+      <c r="X14" s="285" t="n"/>
+      <c r="Y14" s="285" t="n"/>
+      <c r="Z14" s="285" t="n"/>
+      <c r="AA14" s="285" t="n"/>
+      <c r="AB14" s="285" t="n"/>
+      <c r="AC14" s="285" t="n"/>
+      <c r="AD14" s="285" t="n"/>
+      <c r="AE14" s="285" t="n"/>
+      <c r="AF14" s="285" t="n"/>
+      <c r="AG14" s="285" t="n"/>
+      <c r="AH14" s="285" t="n"/>
+      <c r="AI14" s="285" t="n"/>
+      <c r="AJ14" s="285" t="n"/>
+      <c r="AK14" s="285" t="n"/>
+      <c r="AL14" s="285" t="n"/>
+      <c r="AM14" s="285" t="n"/>
+      <c r="AN14" s="285" t="n"/>
+      <c r="AO14" s="285" t="n"/>
+      <c r="AP14" s="285" t="n"/>
+      <c r="AQ14" s="285" t="n"/>
+      <c r="AR14" s="285" t="n"/>
+      <c r="AS14" s="285" t="n"/>
+      <c r="AT14" s="285" t="n"/>
+      <c r="AU14" s="285" t="n"/>
+      <c r="AV14" s="285" t="n"/>
+      <c r="AW14" s="285" t="n"/>
+      <c r="AX14" s="285" t="n"/>
+      <c r="AY14" s="285" t="n"/>
+      <c r="AZ14" s="285" t="n"/>
+      <c r="BA14" s="285" t="n"/>
+      <c r="BB14" s="285" t="n"/>
+      <c r="BC14" s="285" t="n"/>
+      <c r="BD14" s="286" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="291" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B15" s="271" t="n"/>
+      <c r="C15" s="272" t="n"/>
+      <c r="D15" s="292" t="inlineStr">
+        <is>
+          <t>Check Group</t>
+        </is>
+      </c>
+      <c r="E15" s="271" t="n"/>
+      <c r="F15" s="271" t="n"/>
+      <c r="G15" s="272" t="n"/>
+      <c r="H15" s="292" t="inlineStr">
+        <is>
+          <t>Characteristic / Requirement</t>
+        </is>
+      </c>
+      <c r="I15" s="271" t="n"/>
+      <c r="J15" s="271" t="n"/>
+      <c r="K15" s="271" t="n"/>
+      <c r="L15" s="271" t="n"/>
+      <c r="M15" s="271" t="n"/>
+      <c r="N15" s="271" t="n"/>
+      <c r="O15" s="271" t="n"/>
+      <c r="P15" s="271" t="n"/>
+      <c r="Q15" s="271" t="n"/>
+      <c r="R15" s="271" t="n"/>
+      <c r="S15" s="271" t="n"/>
+      <c r="T15" s="271" t="n"/>
+      <c r="U15" s="271" t="n"/>
+      <c r="V15" s="271" t="n"/>
+      <c r="W15" s="271" t="n"/>
+      <c r="X15" s="271" t="n"/>
+      <c r="Y15" s="271" t="n"/>
+      <c r="Z15" s="272" t="n"/>
+      <c r="AA15" s="292" t="inlineStr">
+        <is>
+          <t>Method / Inspection Basis</t>
+        </is>
+      </c>
+      <c r="AB15" s="271" t="n"/>
+      <c r="AC15" s="271" t="n"/>
+      <c r="AD15" s="271" t="n"/>
+      <c r="AE15" s="271" t="n"/>
+      <c r="AF15" s="271" t="n"/>
+      <c r="AG15" s="271" t="n"/>
+      <c r="AH15" s="271" t="n"/>
+      <c r="AI15" s="271" t="n"/>
+      <c r="AJ15" s="271" t="n"/>
+      <c r="AK15" s="271" t="n"/>
+      <c r="AL15" s="271" t="n"/>
+      <c r="AM15" s="271" t="n"/>
+      <c r="AN15" s="271" t="n"/>
+      <c r="AO15" s="271" t="n"/>
+      <c r="AP15" s="271" t="n"/>
+      <c r="AQ15" s="272" t="n"/>
+      <c r="AR15" s="292" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="AS15" s="271" t="n"/>
+      <c r="AT15" s="271" t="n"/>
+      <c r="AU15" s="271" t="n"/>
+      <c r="AV15" s="271" t="n"/>
+      <c r="AW15" s="272" t="n"/>
+      <c r="AX15" s="292" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="AY15" s="271" t="n"/>
+      <c r="AZ15" s="271" t="n"/>
+      <c r="BA15" s="272" t="n"/>
+      <c r="BB15" s="293" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="BC15" s="271" t="n"/>
+      <c r="BD15" s="274" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="25" t="n"/>
+      <c r="A16" s="294">
+        <f>ROW()-ROW($A$16)+1</f>
+        <v/>
+      </c>
+      <c r="B16" s="276" t="n"/>
+      <c r="C16" s="277" t="n"/>
+      <c r="D16" s="295" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="324" t="n"/>
+      <c r="F16" s="324" t="n"/>
+      <c r="G16" s="325" t="n"/>
+      <c r="H16" s="296" t="n"/>
+      <c r="I16" s="324" t="n"/>
+      <c r="J16" s="324" t="n"/>
+      <c r="K16" s="324" t="n"/>
+      <c r="L16" s="324" t="n"/>
+      <c r="M16" s="324" t="n"/>
+      <c r="N16" s="324" t="n"/>
+      <c r="O16" s="324" t="n"/>
+      <c r="P16" s="324" t="n"/>
+      <c r="Q16" s="324" t="n"/>
+      <c r="R16" s="324" t="n"/>
+      <c r="S16" s="324" t="n"/>
+      <c r="T16" s="324" t="n"/>
+      <c r="U16" s="324" t="n"/>
+      <c r="V16" s="324" t="n"/>
+      <c r="W16" s="324" t="n"/>
+      <c r="X16" s="324" t="n"/>
+      <c r="Y16" s="324" t="n"/>
+      <c r="Z16" s="325" t="n"/>
+      <c r="AA16" s="297" t="n"/>
+      <c r="AB16" s="324" t="n"/>
+      <c r="AC16" s="324" t="n"/>
+      <c r="AD16" s="324" t="n"/>
+      <c r="AE16" s="324" t="n"/>
+      <c r="AF16" s="324" t="n"/>
+      <c r="AG16" s="324" t="n"/>
+      <c r="AH16" s="324" t="n"/>
+      <c r="AI16" s="324" t="n"/>
+      <c r="AJ16" s="324" t="n"/>
+      <c r="AK16" s="324" t="n"/>
+      <c r="AL16" s="324" t="n"/>
+      <c r="AM16" s="324" t="n"/>
+      <c r="AN16" s="324" t="n"/>
+      <c r="AO16" s="324" t="n"/>
+      <c r="AP16" s="324" t="n"/>
+      <c r="AQ16" s="325" t="n"/>
+      <c r="AR16" s="296" t="n"/>
+      <c r="AS16" s="324" t="n"/>
+      <c r="AT16" s="324" t="n"/>
+      <c r="AU16" s="324" t="n"/>
+      <c r="AV16" s="324" t="n"/>
+      <c r="AW16" s="325" t="n"/>
+      <c r="AX16" s="296" t="n"/>
+      <c r="AY16" s="324" t="n"/>
+      <c r="AZ16" s="324" t="n"/>
+      <c r="BA16" s="325" t="n"/>
+      <c r="BB16" s="298" t="n"/>
+      <c r="BC16" s="324" t="n"/>
+      <c r="BD16" s="326" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. RESULT / SAMPLE EXECUTION SUMMARY</t>
-        </is>
-      </c>
-      <c r="B17" s="285" t="n"/>
-      <c r="C17" s="285" t="n"/>
-      <c r="D17" s="285" t="n"/>
-      <c r="E17" s="285" t="n"/>
-      <c r="F17" s="285" t="n"/>
-      <c r="G17" s="285" t="n"/>
-      <c r="H17" s="285" t="n"/>
-      <c r="I17" s="285" t="n"/>
-      <c r="J17" s="285" t="n"/>
-      <c r="K17" s="285" t="n"/>
-      <c r="L17" s="285" t="n"/>
-      <c r="M17" s="285" t="n"/>
-      <c r="N17" s="285" t="n"/>
-      <c r="O17" s="285" t="n"/>
-      <c r="P17" s="285" t="n"/>
-      <c r="Q17" s="285" t="n"/>
-      <c r="R17" s="285" t="n"/>
-      <c r="S17" s="285" t="n"/>
-      <c r="T17" s="285" t="n"/>
-      <c r="U17" s="285" t="n"/>
-      <c r="V17" s="285" t="n"/>
-      <c r="W17" s="285" t="n"/>
-      <c r="X17" s="285" t="n"/>
-      <c r="Y17" s="285" t="n"/>
-      <c r="Z17" s="285" t="n"/>
-      <c r="AA17" s="285" t="n"/>
-      <c r="AB17" s="285" t="n"/>
-      <c r="AC17" s="285" t="n"/>
-      <c r="AD17" s="285" t="n"/>
-      <c r="AE17" s="285" t="n"/>
-      <c r="AF17" s="285" t="n"/>
-      <c r="AG17" s="285" t="n"/>
-      <c r="AH17" s="285" t="n"/>
-      <c r="AI17" s="285" t="n"/>
-      <c r="AJ17" s="285" t="n"/>
-      <c r="AK17" s="285" t="n"/>
-      <c r="AL17" s="285" t="n"/>
-      <c r="AM17" s="285" t="n"/>
-      <c r="AN17" s="285" t="n"/>
-      <c r="AO17" s="285" t="n"/>
-      <c r="AP17" s="285" t="n"/>
-      <c r="AQ17" s="285" t="n"/>
-      <c r="AR17" s="285" t="n"/>
-      <c r="AS17" s="285" t="n"/>
-      <c r="AT17" s="285" t="n"/>
-      <c r="AU17" s="285" t="n"/>
-      <c r="AV17" s="285" t="n"/>
-      <c r="AW17" s="285" t="n"/>
-      <c r="AX17" s="285" t="n"/>
-      <c r="AY17" s="285" t="n"/>
-      <c r="AZ17" s="285" t="n"/>
-      <c r="BA17" s="285" t="n"/>
-      <c r="BB17" s="285" t="n"/>
-      <c r="BC17" s="285" t="n"/>
-      <c r="BD17" s="286" t="n"/>
+      <c r="A17" s="294">
+        <f>ROW()-ROW($A$16)+1</f>
+        <v/>
+      </c>
+      <c r="B17" s="276" t="n"/>
+      <c r="C17" s="277" t="n"/>
+      <c r="D17" s="295" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="324" t="n"/>
+      <c r="F17" s="324" t="n"/>
+      <c r="G17" s="325" t="n"/>
+      <c r="H17" s="296" t="n"/>
+      <c r="I17" s="324" t="n"/>
+      <c r="J17" s="324" t="n"/>
+      <c r="K17" s="324" t="n"/>
+      <c r="L17" s="324" t="n"/>
+      <c r="M17" s="324" t="n"/>
+      <c r="N17" s="324" t="n"/>
+      <c r="O17" s="324" t="n"/>
+      <c r="P17" s="324" t="n"/>
+      <c r="Q17" s="324" t="n"/>
+      <c r="R17" s="324" t="n"/>
+      <c r="S17" s="324" t="n"/>
+      <c r="T17" s="324" t="n"/>
+      <c r="U17" s="324" t="n"/>
+      <c r="V17" s="324" t="n"/>
+      <c r="W17" s="324" t="n"/>
+      <c r="X17" s="324" t="n"/>
+      <c r="Y17" s="324" t="n"/>
+      <c r="Z17" s="325" t="n"/>
+      <c r="AA17" s="297" t="n"/>
+      <c r="AB17" s="324" t="n"/>
+      <c r="AC17" s="324" t="n"/>
+      <c r="AD17" s="324" t="n"/>
+      <c r="AE17" s="324" t="n"/>
+      <c r="AF17" s="324" t="n"/>
+      <c r="AG17" s="324" t="n"/>
+      <c r="AH17" s="324" t="n"/>
+      <c r="AI17" s="324" t="n"/>
+      <c r="AJ17" s="324" t="n"/>
+      <c r="AK17" s="324" t="n"/>
+      <c r="AL17" s="324" t="n"/>
+      <c r="AM17" s="324" t="n"/>
+      <c r="AN17" s="324" t="n"/>
+      <c r="AO17" s="324" t="n"/>
+      <c r="AP17" s="324" t="n"/>
+      <c r="AQ17" s="325" t="n"/>
+      <c r="AR17" s="296" t="n"/>
+      <c r="AS17" s="324" t="n"/>
+      <c r="AT17" s="324" t="n"/>
+      <c r="AU17" s="324" t="n"/>
+      <c r="AV17" s="324" t="n"/>
+      <c r="AW17" s="325" t="n"/>
+      <c r="AX17" s="296" t="n"/>
+      <c r="AY17" s="324" t="n"/>
+      <c r="AZ17" s="324" t="n"/>
+      <c r="BA17" s="325" t="n"/>
+      <c r="BB17" s="298" t="n"/>
+      <c r="BC17" s="324" t="n"/>
+      <c r="BD17" s="326" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="291" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B18" s="271" t="n"/>
-      <c r="C18" s="272" t="n"/>
-      <c r="D18" s="292" t="inlineStr">
-        <is>
-          <t>Check Group</t>
-        </is>
-      </c>
-      <c r="E18" s="271" t="n"/>
-      <c r="F18" s="271" t="n"/>
-      <c r="G18" s="272" t="n"/>
-      <c r="H18" s="292" t="inlineStr">
-        <is>
-          <t>Characteristic / Requirement</t>
-        </is>
-      </c>
-      <c r="I18" s="271" t="n"/>
-      <c r="J18" s="271" t="n"/>
-      <c r="K18" s="271" t="n"/>
-      <c r="L18" s="271" t="n"/>
-      <c r="M18" s="271" t="n"/>
-      <c r="N18" s="271" t="n"/>
-      <c r="O18" s="271" t="n"/>
-      <c r="P18" s="271" t="n"/>
-      <c r="Q18" s="271" t="n"/>
-      <c r="R18" s="271" t="n"/>
-      <c r="S18" s="271" t="n"/>
-      <c r="T18" s="271" t="n"/>
-      <c r="U18" s="271" t="n"/>
-      <c r="V18" s="271" t="n"/>
-      <c r="W18" s="271" t="n"/>
-      <c r="X18" s="271" t="n"/>
-      <c r="Y18" s="271" t="n"/>
-      <c r="Z18" s="272" t="n"/>
-      <c r="AA18" s="292" t="inlineStr">
-        <is>
-          <t>Method / Inspection Basis</t>
-        </is>
-      </c>
-      <c r="AB18" s="271" t="n"/>
-      <c r="AC18" s="271" t="n"/>
-      <c r="AD18" s="271" t="n"/>
-      <c r="AE18" s="271" t="n"/>
-      <c r="AF18" s="271" t="n"/>
-      <c r="AG18" s="271" t="n"/>
-      <c r="AH18" s="271" t="n"/>
-      <c r="AI18" s="271" t="n"/>
-      <c r="AJ18" s="271" t="n"/>
-      <c r="AK18" s="271" t="n"/>
-      <c r="AL18" s="271" t="n"/>
-      <c r="AM18" s="271" t="n"/>
-      <c r="AN18" s="271" t="n"/>
-      <c r="AO18" s="271" t="n"/>
-      <c r="AP18" s="271" t="n"/>
-      <c r="AQ18" s="272" t="n"/>
-      <c r="AR18" s="292" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="AS18" s="271" t="n"/>
-      <c r="AT18" s="271" t="n"/>
-      <c r="AU18" s="271" t="n"/>
-      <c r="AV18" s="271" t="n"/>
-      <c r="AW18" s="272" t="n"/>
-      <c r="AX18" s="292" t="inlineStr">
-        <is>
-          <t>Inspector</t>
-        </is>
-      </c>
-      <c r="AY18" s="271" t="n"/>
-      <c r="AZ18" s="271" t="n"/>
-      <c r="BA18" s="272" t="n"/>
-      <c r="BB18" s="293" t="inlineStr">
-        <is>
-          <t>Ref.</t>
-        </is>
-      </c>
-      <c r="BC18" s="271" t="n"/>
-      <c r="BD18" s="274" t="n"/>
+      <c r="A18" s="294">
+        <f>ROW()-ROW($A$16)+1</f>
+        <v/>
+      </c>
+      <c r="B18" s="276" t="n"/>
+      <c r="C18" s="277" t="n"/>
+      <c r="D18" s="295" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="324" t="n"/>
+      <c r="F18" s="324" t="n"/>
+      <c r="G18" s="325" t="n"/>
+      <c r="H18" s="296" t="n"/>
+      <c r="I18" s="324" t="n"/>
+      <c r="J18" s="324" t="n"/>
+      <c r="K18" s="324" t="n"/>
+      <c r="L18" s="324" t="n"/>
+      <c r="M18" s="324" t="n"/>
+      <c r="N18" s="324" t="n"/>
+      <c r="O18" s="324" t="n"/>
+      <c r="P18" s="324" t="n"/>
+      <c r="Q18" s="324" t="n"/>
+      <c r="R18" s="324" t="n"/>
+      <c r="S18" s="324" t="n"/>
+      <c r="T18" s="324" t="n"/>
+      <c r="U18" s="324" t="n"/>
+      <c r="V18" s="324" t="n"/>
+      <c r="W18" s="324" t="n"/>
+      <c r="X18" s="324" t="n"/>
+      <c r="Y18" s="324" t="n"/>
+      <c r="Z18" s="325" t="n"/>
+      <c r="AA18" s="297" t="n"/>
+      <c r="AB18" s="324" t="n"/>
+      <c r="AC18" s="324" t="n"/>
+      <c r="AD18" s="324" t="n"/>
+      <c r="AE18" s="324" t="n"/>
+      <c r="AF18" s="324" t="n"/>
+      <c r="AG18" s="324" t="n"/>
+      <c r="AH18" s="324" t="n"/>
+      <c r="AI18" s="324" t="n"/>
+      <c r="AJ18" s="324" t="n"/>
+      <c r="AK18" s="324" t="n"/>
+      <c r="AL18" s="324" t="n"/>
+      <c r="AM18" s="324" t="n"/>
+      <c r="AN18" s="324" t="n"/>
+      <c r="AO18" s="324" t="n"/>
+      <c r="AP18" s="324" t="n"/>
+      <c r="AQ18" s="325" t="n"/>
+      <c r="AR18" s="296" t="n"/>
+      <c r="AS18" s="324" t="n"/>
+      <c r="AT18" s="324" t="n"/>
+      <c r="AU18" s="324" t="n"/>
+      <c r="AV18" s="324" t="n"/>
+      <c r="AW18" s="325" t="n"/>
+      <c r="AX18" s="296" t="n"/>
+      <c r="AY18" s="324" t="n"/>
+      <c r="AZ18" s="324" t="n"/>
+      <c r="BA18" s="325" t="n"/>
+      <c r="BB18" s="298" t="n"/>
+      <c r="BC18" s="324" t="n"/>
+      <c r="BD18" s="326" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="294">
@@ -6180,895 +6132,677 @@
       <c r="BD22" s="326" t="n"/>
     </row>
     <row r="23" ht="4" customHeight="1">
-      <c r="A23" s="294">
-        <f>ROW()-ROW($A$16)+1</f>
-        <v/>
-      </c>
-      <c r="B23" s="276" t="n"/>
-      <c r="C23" s="277" t="n"/>
-      <c r="D23" s="295" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="324" t="n"/>
-      <c r="F23" s="324" t="n"/>
-      <c r="G23" s="325" t="n"/>
-      <c r="H23" s="296" t="n"/>
-      <c r="I23" s="324" t="n"/>
-      <c r="J23" s="324" t="n"/>
-      <c r="K23" s="324" t="n"/>
-      <c r="L23" s="324" t="n"/>
-      <c r="M23" s="324" t="n"/>
-      <c r="N23" s="324" t="n"/>
-      <c r="O23" s="324" t="n"/>
-      <c r="P23" s="324" t="n"/>
-      <c r="Q23" s="324" t="n"/>
-      <c r="R23" s="324" t="n"/>
-      <c r="S23" s="324" t="n"/>
-      <c r="T23" s="324" t="n"/>
-      <c r="U23" s="324" t="n"/>
-      <c r="V23" s="324" t="n"/>
-      <c r="W23" s="324" t="n"/>
-      <c r="X23" s="324" t="n"/>
-      <c r="Y23" s="324" t="n"/>
-      <c r="Z23" s="325" t="n"/>
-      <c r="AA23" s="297" t="n"/>
-      <c r="AB23" s="324" t="n"/>
-      <c r="AC23" s="324" t="n"/>
-      <c r="AD23" s="324" t="n"/>
-      <c r="AE23" s="324" t="n"/>
-      <c r="AF23" s="324" t="n"/>
-      <c r="AG23" s="324" t="n"/>
-      <c r="AH23" s="324" t="n"/>
-      <c r="AI23" s="324" t="n"/>
-      <c r="AJ23" s="324" t="n"/>
-      <c r="AK23" s="324" t="n"/>
-      <c r="AL23" s="324" t="n"/>
-      <c r="AM23" s="324" t="n"/>
-      <c r="AN23" s="324" t="n"/>
-      <c r="AO23" s="324" t="n"/>
-      <c r="AP23" s="324" t="n"/>
-      <c r="AQ23" s="325" t="n"/>
-      <c r="AR23" s="296" t="n"/>
-      <c r="AS23" s="324" t="n"/>
-      <c r="AT23" s="324" t="n"/>
-      <c r="AU23" s="324" t="n"/>
-      <c r="AV23" s="324" t="n"/>
-      <c r="AW23" s="325" t="n"/>
-      <c r="AX23" s="296" t="n"/>
-      <c r="AY23" s="324" t="n"/>
-      <c r="AZ23" s="324" t="n"/>
-      <c r="BA23" s="325" t="n"/>
-      <c r="BB23" s="298" t="n"/>
-      <c r="BC23" s="324" t="n"/>
-      <c r="BD23" s="326" t="n"/>
+      <c r="A23" s="294" t="n"/>
+      <c r="D23" s="299" t="n"/>
+      <c r="H23" s="300" t="n"/>
+      <c r="AA23" s="301" t="n"/>
+      <c r="AR23" s="302" t="n"/>
+      <c r="AX23" s="302" t="n"/>
+      <c r="BB23" s="303" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="294">
-        <f>ROW()-ROW($A$16)+1</f>
-        <v/>
-      </c>
-      <c r="B24" s="276" t="n"/>
-      <c r="C24" s="277" t="n"/>
-      <c r="D24" s="295" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="324" t="n"/>
-      <c r="F24" s="324" t="n"/>
-      <c r="G24" s="325" t="n"/>
-      <c r="H24" s="296" t="n"/>
-      <c r="I24" s="324" t="n"/>
-      <c r="J24" s="324" t="n"/>
-      <c r="K24" s="324" t="n"/>
-      <c r="L24" s="324" t="n"/>
-      <c r="M24" s="324" t="n"/>
-      <c r="N24" s="324" t="n"/>
-      <c r="O24" s="324" t="n"/>
-      <c r="P24" s="324" t="n"/>
-      <c r="Q24" s="324" t="n"/>
-      <c r="R24" s="324" t="n"/>
-      <c r="S24" s="324" t="n"/>
-      <c r="T24" s="324" t="n"/>
-      <c r="U24" s="324" t="n"/>
-      <c r="V24" s="324" t="n"/>
-      <c r="W24" s="324" t="n"/>
-      <c r="X24" s="324" t="n"/>
-      <c r="Y24" s="324" t="n"/>
-      <c r="Z24" s="325" t="n"/>
-      <c r="AA24" s="297" t="n"/>
-      <c r="AB24" s="324" t="n"/>
-      <c r="AC24" s="324" t="n"/>
-      <c r="AD24" s="324" t="n"/>
-      <c r="AE24" s="324" t="n"/>
-      <c r="AF24" s="324" t="n"/>
-      <c r="AG24" s="324" t="n"/>
-      <c r="AH24" s="324" t="n"/>
-      <c r="AI24" s="324" t="n"/>
-      <c r="AJ24" s="324" t="n"/>
-      <c r="AK24" s="324" t="n"/>
-      <c r="AL24" s="324" t="n"/>
-      <c r="AM24" s="324" t="n"/>
-      <c r="AN24" s="324" t="n"/>
-      <c r="AO24" s="324" t="n"/>
-      <c r="AP24" s="324" t="n"/>
-      <c r="AQ24" s="325" t="n"/>
-      <c r="AR24" s="296" t="n"/>
-      <c r="AS24" s="324" t="n"/>
-      <c r="AT24" s="324" t="n"/>
-      <c r="AU24" s="324" t="n"/>
-      <c r="AV24" s="324" t="n"/>
-      <c r="AW24" s="325" t="n"/>
-      <c r="AX24" s="296" t="n"/>
-      <c r="AY24" s="324" t="n"/>
-      <c r="AZ24" s="324" t="n"/>
-      <c r="BA24" s="325" t="n"/>
-      <c r="BB24" s="298" t="n"/>
-      <c r="BC24" s="324" t="n"/>
-      <c r="BD24" s="326" t="n"/>
+      <c r="A24" s="284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
+        </is>
+      </c>
+      <c r="B24" s="285" t="n"/>
+      <c r="C24" s="285" t="n"/>
+      <c r="D24" s="285" t="n"/>
+      <c r="E24" s="285" t="n"/>
+      <c r="F24" s="285" t="n"/>
+      <c r="G24" s="285" t="n"/>
+      <c r="H24" s="285" t="n"/>
+      <c r="I24" s="285" t="n"/>
+      <c r="J24" s="285" t="n"/>
+      <c r="K24" s="285" t="n"/>
+      <c r="L24" s="285" t="n"/>
+      <c r="M24" s="285" t="n"/>
+      <c r="N24" s="285" t="n"/>
+      <c r="O24" s="285" t="n"/>
+      <c r="P24" s="285" t="n"/>
+      <c r="Q24" s="285" t="n"/>
+      <c r="R24" s="285" t="n"/>
+      <c r="S24" s="285" t="n"/>
+      <c r="T24" s="285" t="n"/>
+      <c r="U24" s="285" t="n"/>
+      <c r="V24" s="285" t="n"/>
+      <c r="W24" s="285" t="n"/>
+      <c r="X24" s="285" t="n"/>
+      <c r="Y24" s="285" t="n"/>
+      <c r="Z24" s="285" t="n"/>
+      <c r="AA24" s="285" t="n"/>
+      <c r="AB24" s="285" t="n"/>
+      <c r="AC24" s="285" t="n"/>
+      <c r="AD24" s="285" t="n"/>
+      <c r="AE24" s="285" t="n"/>
+      <c r="AF24" s="285" t="n"/>
+      <c r="AG24" s="285" t="n"/>
+      <c r="AH24" s="285" t="n"/>
+      <c r="AI24" s="285" t="n"/>
+      <c r="AJ24" s="285" t="n"/>
+      <c r="AK24" s="285" t="n"/>
+      <c r="AL24" s="285" t="n"/>
+      <c r="AM24" s="285" t="n"/>
+      <c r="AN24" s="285" t="n"/>
+      <c r="AO24" s="285" t="n"/>
+      <c r="AP24" s="285" t="n"/>
+      <c r="AQ24" s="285" t="n"/>
+      <c r="AR24" s="285" t="n"/>
+      <c r="AS24" s="285" t="n"/>
+      <c r="AT24" s="285" t="n"/>
+      <c r="AU24" s="285" t="n"/>
+      <c r="AV24" s="285" t="n"/>
+      <c r="AW24" s="285" t="n"/>
+      <c r="AX24" s="285" t="n"/>
+      <c r="AY24" s="285" t="n"/>
+      <c r="AZ24" s="285" t="n"/>
+      <c r="BA24" s="285" t="n"/>
+      <c r="BB24" s="285" t="n"/>
+      <c r="BC24" s="285" t="n"/>
+      <c r="BD24" s="286" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="294">
-        <f>ROW()-ROW($A$16)+1</f>
-        <v/>
-      </c>
-      <c r="B25" s="276" t="n"/>
-      <c r="C25" s="277" t="n"/>
-      <c r="D25" s="295" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="324" t="n"/>
-      <c r="F25" s="324" t="n"/>
-      <c r="G25" s="325" t="n"/>
-      <c r="H25" s="296" t="n"/>
-      <c r="I25" s="324" t="n"/>
-      <c r="J25" s="324" t="n"/>
-      <c r="K25" s="324" t="n"/>
-      <c r="L25" s="324" t="n"/>
-      <c r="M25" s="324" t="n"/>
-      <c r="N25" s="324" t="n"/>
-      <c r="O25" s="324" t="n"/>
-      <c r="P25" s="324" t="n"/>
-      <c r="Q25" s="324" t="n"/>
-      <c r="R25" s="324" t="n"/>
-      <c r="S25" s="324" t="n"/>
-      <c r="T25" s="324" t="n"/>
-      <c r="U25" s="324" t="n"/>
-      <c r="V25" s="324" t="n"/>
-      <c r="W25" s="324" t="n"/>
-      <c r="X25" s="324" t="n"/>
-      <c r="Y25" s="324" t="n"/>
-      <c r="Z25" s="325" t="n"/>
-      <c r="AA25" s="297" t="n"/>
-      <c r="AB25" s="324" t="n"/>
-      <c r="AC25" s="324" t="n"/>
-      <c r="AD25" s="324" t="n"/>
-      <c r="AE25" s="324" t="n"/>
-      <c r="AF25" s="324" t="n"/>
-      <c r="AG25" s="324" t="n"/>
-      <c r="AH25" s="324" t="n"/>
-      <c r="AI25" s="324" t="n"/>
-      <c r="AJ25" s="324" t="n"/>
-      <c r="AK25" s="324" t="n"/>
-      <c r="AL25" s="324" t="n"/>
-      <c r="AM25" s="324" t="n"/>
-      <c r="AN25" s="324" t="n"/>
-      <c r="AO25" s="324" t="n"/>
-      <c r="AP25" s="324" t="n"/>
-      <c r="AQ25" s="325" t="n"/>
-      <c r="AR25" s="296" t="n"/>
-      <c r="AS25" s="324" t="n"/>
-      <c r="AT25" s="324" t="n"/>
-      <c r="AU25" s="324" t="n"/>
-      <c r="AV25" s="324" t="n"/>
-      <c r="AW25" s="325" t="n"/>
-      <c r="AX25" s="296" t="n"/>
-      <c r="AY25" s="324" t="n"/>
-      <c r="AZ25" s="324" t="n"/>
-      <c r="BA25" s="325" t="n"/>
-      <c r="BB25" s="298" t="n"/>
-      <c r="BC25" s="324" t="n"/>
-      <c r="BD25" s="326" t="n"/>
+      <c r="A25" s="287" t="inlineStr">
+        <is>
+          <t>Disposition / Release Decision</t>
+        </is>
+      </c>
+      <c r="B25" s="271" t="n"/>
+      <c r="C25" s="271" t="n"/>
+      <c r="D25" s="271" t="n"/>
+      <c r="E25" s="271" t="n"/>
+      <c r="F25" s="271" t="n"/>
+      <c r="G25" s="271" t="n"/>
+      <c r="H25" s="271" t="n"/>
+      <c r="I25" s="271" t="n"/>
+      <c r="J25" s="272" t="n"/>
+      <c r="K25" s="288" t="n"/>
+      <c r="L25" s="321" t="n"/>
+      <c r="M25" s="321" t="n"/>
+      <c r="N25" s="321" t="n"/>
+      <c r="O25" s="321" t="n"/>
+      <c r="P25" s="321" t="n"/>
+      <c r="Q25" s="321" t="n"/>
+      <c r="R25" s="321" t="n"/>
+      <c r="S25" s="321" t="n"/>
+      <c r="T25" s="321" t="n"/>
+      <c r="U25" s="321" t="n"/>
+      <c r="V25" s="321" t="n"/>
+      <c r="W25" s="321" t="n"/>
+      <c r="X25" s="321" t="n"/>
+      <c r="Y25" s="321" t="n"/>
+      <c r="Z25" s="321" t="n"/>
+      <c r="AA25" s="321" t="n"/>
+      <c r="AB25" s="322" t="n"/>
+      <c r="AC25" s="289" t="inlineStr">
+        <is>
+          <t>Linked NCR / Concession</t>
+        </is>
+      </c>
+      <c r="AD25" s="271" t="n"/>
+      <c r="AE25" s="271" t="n"/>
+      <c r="AF25" s="271" t="n"/>
+      <c r="AG25" s="271" t="n"/>
+      <c r="AH25" s="271" t="n"/>
+      <c r="AI25" s="271" t="n"/>
+      <c r="AJ25" s="271" t="n"/>
+      <c r="AK25" s="271" t="n"/>
+      <c r="AL25" s="272" t="n"/>
+      <c r="AM25" s="290" t="n"/>
+      <c r="AN25" s="321" t="n"/>
+      <c r="AO25" s="321" t="n"/>
+      <c r="AP25" s="321" t="n"/>
+      <c r="AQ25" s="321" t="n"/>
+      <c r="AR25" s="321" t="n"/>
+      <c r="AS25" s="321" t="n"/>
+      <c r="AT25" s="321" t="n"/>
+      <c r="AU25" s="321" t="n"/>
+      <c r="AV25" s="321" t="n"/>
+      <c r="AW25" s="321" t="n"/>
+      <c r="AX25" s="321" t="n"/>
+      <c r="AY25" s="321" t="n"/>
+      <c r="AZ25" s="321" t="n"/>
+      <c r="BA25" s="321" t="n"/>
+      <c r="BB25" s="321" t="n"/>
+      <c r="BC25" s="321" t="n"/>
+      <c r="BD25" s="323" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="294" t="n"/>
-      <c r="D26" s="299" t="n"/>
-      <c r="H26" s="300" t="n"/>
-      <c r="AA26" s="301" t="n"/>
-      <c r="AR26" s="302" t="n"/>
-      <c r="AX26" s="302" t="n"/>
-      <c r="BB26" s="303" t="n"/>
+      <c r="A26" s="287" t="inlineStr">
+        <is>
+          <t>Cleanliness / Packaging Verified (YES/NO)</t>
+        </is>
+      </c>
+      <c r="B26" s="271" t="n"/>
+      <c r="C26" s="271" t="n"/>
+      <c r="D26" s="271" t="n"/>
+      <c r="E26" s="271" t="n"/>
+      <c r="F26" s="271" t="n"/>
+      <c r="G26" s="271" t="n"/>
+      <c r="H26" s="271" t="n"/>
+      <c r="I26" s="271" t="n"/>
+      <c r="J26" s="272" t="n"/>
+      <c r="K26" s="288" t="n"/>
+      <c r="L26" s="321" t="n"/>
+      <c r="M26" s="321" t="n"/>
+      <c r="N26" s="321" t="n"/>
+      <c r="O26" s="321" t="n"/>
+      <c r="P26" s="321" t="n"/>
+      <c r="Q26" s="321" t="n"/>
+      <c r="R26" s="321" t="n"/>
+      <c r="S26" s="321" t="n"/>
+      <c r="T26" s="321" t="n"/>
+      <c r="U26" s="321" t="n"/>
+      <c r="V26" s="321" t="n"/>
+      <c r="W26" s="321" t="n"/>
+      <c r="X26" s="321" t="n"/>
+      <c r="Y26" s="321" t="n"/>
+      <c r="Z26" s="321" t="n"/>
+      <c r="AA26" s="321" t="n"/>
+      <c r="AB26" s="322" t="n"/>
+      <c r="AC26" s="289" t="inlineStr">
+        <is>
+          <t>Label / Doc Verified (YES/NO)</t>
+        </is>
+      </c>
+      <c r="AD26" s="271" t="n"/>
+      <c r="AE26" s="271" t="n"/>
+      <c r="AF26" s="271" t="n"/>
+      <c r="AG26" s="271" t="n"/>
+      <c r="AH26" s="271" t="n"/>
+      <c r="AI26" s="271" t="n"/>
+      <c r="AJ26" s="271" t="n"/>
+      <c r="AK26" s="271" t="n"/>
+      <c r="AL26" s="272" t="n"/>
+      <c r="AM26" s="290" t="n"/>
+      <c r="AN26" s="321" t="n"/>
+      <c r="AO26" s="321" t="n"/>
+      <c r="AP26" s="321" t="n"/>
+      <c r="AQ26" s="321" t="n"/>
+      <c r="AR26" s="321" t="n"/>
+      <c r="AS26" s="321" t="n"/>
+      <c r="AT26" s="321" t="n"/>
+      <c r="AU26" s="321" t="n"/>
+      <c r="AV26" s="321" t="n"/>
+      <c r="AW26" s="321" t="n"/>
+      <c r="AX26" s="321" t="n"/>
+      <c r="AY26" s="321" t="n"/>
+      <c r="AZ26" s="321" t="n"/>
+      <c r="BA26" s="321" t="n"/>
+      <c r="BB26" s="321" t="n"/>
+      <c r="BC26" s="321" t="n"/>
+      <c r="BD26" s="323" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. DISPOSITION / RELEASE</t>
-        </is>
-      </c>
-      <c r="B27" s="285" t="n"/>
-      <c r="C27" s="285" t="n"/>
-      <c r="D27" s="285" t="n"/>
-      <c r="E27" s="285" t="n"/>
-      <c r="F27" s="285" t="n"/>
-      <c r="G27" s="285" t="n"/>
-      <c r="H27" s="285" t="n"/>
-      <c r="I27" s="285" t="n"/>
-      <c r="J27" s="285" t="n"/>
-      <c r="K27" s="285" t="n"/>
-      <c r="L27" s="285" t="n"/>
-      <c r="M27" s="285" t="n"/>
-      <c r="N27" s="285" t="n"/>
-      <c r="O27" s="285" t="n"/>
-      <c r="P27" s="285" t="n"/>
-      <c r="Q27" s="285" t="n"/>
-      <c r="R27" s="285" t="n"/>
-      <c r="S27" s="285" t="n"/>
-      <c r="T27" s="285" t="n"/>
-      <c r="U27" s="285" t="n"/>
-      <c r="V27" s="285" t="n"/>
-      <c r="W27" s="285" t="n"/>
-      <c r="X27" s="285" t="n"/>
-      <c r="Y27" s="285" t="n"/>
-      <c r="Z27" s="285" t="n"/>
-      <c r="AA27" s="285" t="n"/>
-      <c r="AB27" s="285" t="n"/>
-      <c r="AC27" s="285" t="n"/>
-      <c r="AD27" s="285" t="n"/>
-      <c r="AE27" s="285" t="n"/>
-      <c r="AF27" s="285" t="n"/>
-      <c r="AG27" s="285" t="n"/>
-      <c r="AH27" s="285" t="n"/>
-      <c r="AI27" s="285" t="n"/>
-      <c r="AJ27" s="285" t="n"/>
-      <c r="AK27" s="285" t="n"/>
-      <c r="AL27" s="285" t="n"/>
-      <c r="AM27" s="285" t="n"/>
-      <c r="AN27" s="285" t="n"/>
-      <c r="AO27" s="285" t="n"/>
-      <c r="AP27" s="285" t="n"/>
-      <c r="AQ27" s="285" t="n"/>
-      <c r="AR27" s="285" t="n"/>
-      <c r="AS27" s="285" t="n"/>
-      <c r="AT27" s="285" t="n"/>
-      <c r="AU27" s="285" t="n"/>
-      <c r="AV27" s="285" t="n"/>
-      <c r="AW27" s="285" t="n"/>
-      <c r="AX27" s="285" t="n"/>
-      <c r="AY27" s="285" t="n"/>
-      <c r="AZ27" s="285" t="n"/>
-      <c r="BA27" s="285" t="n"/>
-      <c r="BB27" s="285" t="n"/>
-      <c r="BC27" s="285" t="n"/>
-      <c r="BD27" s="286" t="n"/>
+      <c r="A27" s="287" t="inlineStr">
+        <is>
+          <t>Quality Authority</t>
+        </is>
+      </c>
+      <c r="B27" s="271" t="n"/>
+      <c r="C27" s="271" t="n"/>
+      <c r="D27" s="271" t="n"/>
+      <c r="E27" s="271" t="n"/>
+      <c r="F27" s="271" t="n"/>
+      <c r="G27" s="271" t="n"/>
+      <c r="H27" s="271" t="n"/>
+      <c r="I27" s="271" t="n"/>
+      <c r="J27" s="272" t="n"/>
+      <c r="K27" s="288" t="n"/>
+      <c r="L27" s="321" t="n"/>
+      <c r="M27" s="321" t="n"/>
+      <c r="N27" s="321" t="n"/>
+      <c r="O27" s="321" t="n"/>
+      <c r="P27" s="321" t="n"/>
+      <c r="Q27" s="321" t="n"/>
+      <c r="R27" s="321" t="n"/>
+      <c r="S27" s="321" t="n"/>
+      <c r="T27" s="321" t="n"/>
+      <c r="U27" s="321" t="n"/>
+      <c r="V27" s="321" t="n"/>
+      <c r="W27" s="321" t="n"/>
+      <c r="X27" s="321" t="n"/>
+      <c r="Y27" s="321" t="n"/>
+      <c r="Z27" s="321" t="n"/>
+      <c r="AA27" s="321" t="n"/>
+      <c r="AB27" s="322" t="n"/>
+      <c r="AC27" s="289" t="inlineStr">
+        <is>
+          <t>Closeout Status</t>
+        </is>
+      </c>
+      <c r="AD27" s="271" t="n"/>
+      <c r="AE27" s="271" t="n"/>
+      <c r="AF27" s="271" t="n"/>
+      <c r="AG27" s="271" t="n"/>
+      <c r="AH27" s="271" t="n"/>
+      <c r="AI27" s="271" t="n"/>
+      <c r="AJ27" s="271" t="n"/>
+      <c r="AK27" s="271" t="n"/>
+      <c r="AL27" s="272" t="n"/>
+      <c r="AM27" s="290" t="n"/>
+      <c r="AN27" s="321" t="n"/>
+      <c r="AO27" s="321" t="n"/>
+      <c r="AP27" s="321" t="n"/>
+      <c r="AQ27" s="321" t="n"/>
+      <c r="AR27" s="321" t="n"/>
+      <c r="AS27" s="321" t="n"/>
+      <c r="AT27" s="321" t="n"/>
+      <c r="AU27" s="321" t="n"/>
+      <c r="AV27" s="321" t="n"/>
+      <c r="AW27" s="321" t="n"/>
+      <c r="AX27" s="321" t="n"/>
+      <c r="AY27" s="321" t="n"/>
+      <c r="AZ27" s="321" t="n"/>
+      <c r="BA27" s="321" t="n"/>
+      <c r="BB27" s="321" t="n"/>
+      <c r="BC27" s="321" t="n"/>
+      <c r="BD27" s="323" t="n"/>
     </row>
     <row r="28" ht="4" customHeight="1">
-      <c r="A28" s="287" t="inlineStr">
-        <is>
-          <t>Disposition / Release Decision</t>
-        </is>
-      </c>
-      <c r="B28" s="271" t="n"/>
-      <c r="C28" s="271" t="n"/>
-      <c r="D28" s="271" t="n"/>
-      <c r="E28" s="271" t="n"/>
-      <c r="F28" s="271" t="n"/>
-      <c r="G28" s="271" t="n"/>
-      <c r="H28" s="271" t="n"/>
-      <c r="I28" s="271" t="n"/>
-      <c r="J28" s="272" t="n"/>
-      <c r="K28" s="288" t="n"/>
-      <c r="L28" s="321" t="n"/>
-      <c r="M28" s="321" t="n"/>
-      <c r="N28" s="321" t="n"/>
-      <c r="O28" s="321" t="n"/>
-      <c r="P28" s="321" t="n"/>
-      <c r="Q28" s="321" t="n"/>
-      <c r="R28" s="321" t="n"/>
-      <c r="S28" s="321" t="n"/>
-      <c r="T28" s="321" t="n"/>
-      <c r="U28" s="321" t="n"/>
-      <c r="V28" s="321" t="n"/>
-      <c r="W28" s="321" t="n"/>
-      <c r="X28" s="321" t="n"/>
-      <c r="Y28" s="321" t="n"/>
-      <c r="Z28" s="321" t="n"/>
-      <c r="AA28" s="321" t="n"/>
-      <c r="AB28" s="322" t="n"/>
-      <c r="AC28" s="289" t="inlineStr">
-        <is>
-          <t>Linked NCR / Concession</t>
-        </is>
-      </c>
-      <c r="AD28" s="271" t="n"/>
-      <c r="AE28" s="271" t="n"/>
-      <c r="AF28" s="271" t="n"/>
-      <c r="AG28" s="271" t="n"/>
-      <c r="AH28" s="271" t="n"/>
-      <c r="AI28" s="271" t="n"/>
-      <c r="AJ28" s="271" t="n"/>
-      <c r="AK28" s="271" t="n"/>
-      <c r="AL28" s="272" t="n"/>
-      <c r="AM28" s="290" t="n"/>
-      <c r="AN28" s="321" t="n"/>
-      <c r="AO28" s="321" t="n"/>
-      <c r="AP28" s="321" t="n"/>
-      <c r="AQ28" s="321" t="n"/>
-      <c r="AR28" s="321" t="n"/>
-      <c r="AS28" s="321" t="n"/>
-      <c r="AT28" s="321" t="n"/>
-      <c r="AU28" s="321" t="n"/>
-      <c r="AV28" s="321" t="n"/>
-      <c r="AW28" s="321" t="n"/>
-      <c r="AX28" s="321" t="n"/>
-      <c r="AY28" s="321" t="n"/>
-      <c r="AZ28" s="321" t="n"/>
-      <c r="BA28" s="321" t="n"/>
-      <c r="BB28" s="321" t="n"/>
-      <c r="BC28" s="321" t="n"/>
-      <c r="BD28" s="323" t="n"/>
+      <c r="A28" s="294" t="n"/>
+      <c r="D28" s="299" t="n"/>
+      <c r="H28" s="304" t="n"/>
+      <c r="AA28" s="301" t="n"/>
+      <c r="AR28" s="302" t="n"/>
+      <c r="AX28" s="302" t="n"/>
+      <c r="BB28" s="303" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="287" t="inlineStr">
-        <is>
-          <t>Cleanliness / Packaging Verified (YES/NO)</t>
-        </is>
-      </c>
-      <c r="B29" s="271" t="n"/>
-      <c r="C29" s="271" t="n"/>
-      <c r="D29" s="271" t="n"/>
-      <c r="E29" s="271" t="n"/>
-      <c r="F29" s="271" t="n"/>
-      <c r="G29" s="271" t="n"/>
-      <c r="H29" s="271" t="n"/>
-      <c r="I29" s="271" t="n"/>
-      <c r="J29" s="272" t="n"/>
-      <c r="K29" s="288" t="n"/>
-      <c r="L29" s="321" t="n"/>
-      <c r="M29" s="321" t="n"/>
-      <c r="N29" s="321" t="n"/>
-      <c r="O29" s="321" t="n"/>
-      <c r="P29" s="321" t="n"/>
-      <c r="Q29" s="321" t="n"/>
-      <c r="R29" s="321" t="n"/>
-      <c r="S29" s="321" t="n"/>
-      <c r="T29" s="321" t="n"/>
-      <c r="U29" s="321" t="n"/>
-      <c r="V29" s="321" t="n"/>
-      <c r="W29" s="321" t="n"/>
-      <c r="X29" s="321" t="n"/>
-      <c r="Y29" s="321" t="n"/>
-      <c r="Z29" s="321" t="n"/>
-      <c r="AA29" s="321" t="n"/>
-      <c r="AB29" s="322" t="n"/>
-      <c r="AC29" s="289" t="inlineStr">
-        <is>
-          <t>Label / Doc Verified (YES/NO)</t>
-        </is>
-      </c>
-      <c r="AD29" s="271" t="n"/>
-      <c r="AE29" s="271" t="n"/>
-      <c r="AF29" s="271" t="n"/>
-      <c r="AG29" s="271" t="n"/>
-      <c r="AH29" s="271" t="n"/>
-      <c r="AI29" s="271" t="n"/>
-      <c r="AJ29" s="271" t="n"/>
-      <c r="AK29" s="271" t="n"/>
-      <c r="AL29" s="272" t="n"/>
-      <c r="AM29" s="290" t="n"/>
-      <c r="AN29" s="321" t="n"/>
-      <c r="AO29" s="321" t="n"/>
-      <c r="AP29" s="321" t="n"/>
-      <c r="AQ29" s="321" t="n"/>
-      <c r="AR29" s="321" t="n"/>
-      <c r="AS29" s="321" t="n"/>
-      <c r="AT29" s="321" t="n"/>
-      <c r="AU29" s="321" t="n"/>
-      <c r="AV29" s="321" t="n"/>
-      <c r="AW29" s="321" t="n"/>
-      <c r="AX29" s="321" t="n"/>
-      <c r="AY29" s="321" t="n"/>
-      <c r="AZ29" s="321" t="n"/>
-      <c r="BA29" s="321" t="n"/>
-      <c r="BB29" s="321" t="n"/>
-      <c r="BC29" s="321" t="n"/>
-      <c r="BD29" s="323" t="n"/>
+      <c r="A29" s="284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
+        </is>
+      </c>
+      <c r="B29" s="285" t="n"/>
+      <c r="C29" s="285" t="n"/>
+      <c r="D29" s="285" t="n"/>
+      <c r="E29" s="285" t="n"/>
+      <c r="F29" s="285" t="n"/>
+      <c r="G29" s="285" t="n"/>
+      <c r="H29" s="285" t="n"/>
+      <c r="I29" s="285" t="n"/>
+      <c r="J29" s="285" t="n"/>
+      <c r="K29" s="285" t="n"/>
+      <c r="L29" s="285" t="n"/>
+      <c r="M29" s="285" t="n"/>
+      <c r="N29" s="285" t="n"/>
+      <c r="O29" s="285" t="n"/>
+      <c r="P29" s="285" t="n"/>
+      <c r="Q29" s="285" t="n"/>
+      <c r="R29" s="285" t="n"/>
+      <c r="S29" s="285" t="n"/>
+      <c r="T29" s="285" t="n"/>
+      <c r="U29" s="285" t="n"/>
+      <c r="V29" s="285" t="n"/>
+      <c r="W29" s="285" t="n"/>
+      <c r="X29" s="285" t="n"/>
+      <c r="Y29" s="285" t="n"/>
+      <c r="Z29" s="285" t="n"/>
+      <c r="AA29" s="285" t="n"/>
+      <c r="AB29" s="285" t="n"/>
+      <c r="AC29" s="285" t="n"/>
+      <c r="AD29" s="285" t="n"/>
+      <c r="AE29" s="285" t="n"/>
+      <c r="AF29" s="285" t="n"/>
+      <c r="AG29" s="285" t="n"/>
+      <c r="AH29" s="285" t="n"/>
+      <c r="AI29" s="285" t="n"/>
+      <c r="AJ29" s="285" t="n"/>
+      <c r="AK29" s="285" t="n"/>
+      <c r="AL29" s="285" t="n"/>
+      <c r="AM29" s="285" t="n"/>
+      <c r="AN29" s="285" t="n"/>
+      <c r="AO29" s="285" t="n"/>
+      <c r="AP29" s="285" t="n"/>
+      <c r="AQ29" s="285" t="n"/>
+      <c r="AR29" s="285" t="n"/>
+      <c r="AS29" s="285" t="n"/>
+      <c r="AT29" s="285" t="n"/>
+      <c r="AU29" s="285" t="n"/>
+      <c r="AV29" s="285" t="n"/>
+      <c r="AW29" s="285" t="n"/>
+      <c r="AX29" s="285" t="n"/>
+      <c r="AY29" s="285" t="n"/>
+      <c r="AZ29" s="285" t="n"/>
+      <c r="BA29" s="285" t="n"/>
+      <c r="BB29" s="285" t="n"/>
+      <c r="BC29" s="285" t="n"/>
+      <c r="BD29" s="286" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="287" t="inlineStr">
-        <is>
-          <t>Quality Authority</t>
-        </is>
-      </c>
-      <c r="B30" s="271" t="n"/>
-      <c r="C30" s="271" t="n"/>
-      <c r="D30" s="271" t="n"/>
-      <c r="E30" s="271" t="n"/>
-      <c r="F30" s="271" t="n"/>
-      <c r="G30" s="271" t="n"/>
-      <c r="H30" s="271" t="n"/>
-      <c r="I30" s="271" t="n"/>
-      <c r="J30" s="272" t="n"/>
-      <c r="K30" s="288" t="n"/>
-      <c r="L30" s="321" t="n"/>
-      <c r="M30" s="321" t="n"/>
-      <c r="N30" s="321" t="n"/>
-      <c r="O30" s="321" t="n"/>
-      <c r="P30" s="321" t="n"/>
-      <c r="Q30" s="321" t="n"/>
-      <c r="R30" s="321" t="n"/>
-      <c r="S30" s="321" t="n"/>
-      <c r="T30" s="321" t="n"/>
-      <c r="U30" s="321" t="n"/>
-      <c r="V30" s="321" t="n"/>
-      <c r="W30" s="321" t="n"/>
-      <c r="X30" s="321" t="n"/>
-      <c r="Y30" s="321" t="n"/>
-      <c r="Z30" s="321" t="n"/>
-      <c r="AA30" s="321" t="n"/>
-      <c r="AB30" s="322" t="n"/>
-      <c r="AC30" s="289" t="inlineStr">
-        <is>
-          <t>Closeout Status</t>
-        </is>
-      </c>
-      <c r="AD30" s="271" t="n"/>
-      <c r="AE30" s="271" t="n"/>
-      <c r="AF30" s="271" t="n"/>
-      <c r="AG30" s="271" t="n"/>
-      <c r="AH30" s="271" t="n"/>
-      <c r="AI30" s="271" t="n"/>
-      <c r="AJ30" s="271" t="n"/>
-      <c r="AK30" s="271" t="n"/>
-      <c r="AL30" s="272" t="n"/>
-      <c r="AM30" s="290" t="n"/>
-      <c r="AN30" s="321" t="n"/>
-      <c r="AO30" s="321" t="n"/>
-      <c r="AP30" s="321" t="n"/>
-      <c r="AQ30" s="321" t="n"/>
-      <c r="AR30" s="321" t="n"/>
-      <c r="AS30" s="321" t="n"/>
-      <c r="AT30" s="321" t="n"/>
-      <c r="AU30" s="321" t="n"/>
-      <c r="AV30" s="321" t="n"/>
-      <c r="AW30" s="321" t="n"/>
-      <c r="AX30" s="321" t="n"/>
-      <c r="AY30" s="321" t="n"/>
-      <c r="AZ30" s="321" t="n"/>
-      <c r="BA30" s="321" t="n"/>
-      <c r="BB30" s="321" t="n"/>
-      <c r="BC30" s="321" t="n"/>
-      <c r="BD30" s="323" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="338" t="inlineStr">
-        <is>
-          <t>Concession / Deviation Ref</t>
-        </is>
-      </c>
-      <c r="K31" s="339" t="n"/>
-      <c r="AC31" s="340" t="inlineStr">
-        <is>
-          <t>Packaging Instruction Ref (FRM-707/709)</t>
-        </is>
-      </c>
-      <c r="AJ31" s="341" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="338" t="inlineStr">
-        <is>
-          <t>Safety/Special Char. Verified?</t>
-        </is>
-      </c>
-      <c r="K32" s="339" t="n"/>
-      <c r="AC32" s="340" t="inlineStr">
-        <is>
-          <t>Measurement Uncertainty Noted?</t>
-        </is>
-      </c>
-      <c r="AJ32" s="341" t="n"/>
+      <c r="A30" s="327" t="inlineStr">
+        <is>
+          <t>Prepared by</t>
+        </is>
+      </c>
+      <c r="B30" s="285" t="n"/>
+      <c r="C30" s="285" t="n"/>
+      <c r="D30" s="285" t="n"/>
+      <c r="E30" s="285" t="n"/>
+      <c r="F30" s="285" t="n"/>
+      <c r="G30" s="285" t="n"/>
+      <c r="H30" s="285" t="n"/>
+      <c r="I30" s="285" t="n"/>
+      <c r="J30" s="285" t="n"/>
+      <c r="K30" s="285" t="n"/>
+      <c r="L30" s="285" t="n"/>
+      <c r="M30" s="285" t="n"/>
+      <c r="N30" s="285" t="n"/>
+      <c r="O30" s="285" t="n"/>
+      <c r="P30" s="285" t="n"/>
+      <c r="Q30" s="285" t="n"/>
+      <c r="R30" s="328" t="n"/>
+      <c r="S30" s="51" t="inlineStr">
+        <is>
+          <t>Reviewed by</t>
+        </is>
+      </c>
+      <c r="T30" s="285" t="n"/>
+      <c r="U30" s="285" t="n"/>
+      <c r="V30" s="285" t="n"/>
+      <c r="W30" s="285" t="n"/>
+      <c r="X30" s="285" t="n"/>
+      <c r="Y30" s="285" t="n"/>
+      <c r="Z30" s="285" t="n"/>
+      <c r="AA30" s="285" t="n"/>
+      <c r="AB30" s="285" t="n"/>
+      <c r="AC30" s="285" t="n"/>
+      <c r="AD30" s="285" t="n"/>
+      <c r="AE30" s="285" t="n"/>
+      <c r="AF30" s="285" t="n"/>
+      <c r="AG30" s="285" t="n"/>
+      <c r="AH30" s="285" t="n"/>
+      <c r="AI30" s="285" t="n"/>
+      <c r="AJ30" s="285" t="n"/>
+      <c r="AK30" s="305" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="AL30" s="285" t="n"/>
+      <c r="AM30" s="285" t="n"/>
+      <c r="AN30" s="285" t="n"/>
+      <c r="AO30" s="285" t="n"/>
+      <c r="AP30" s="285" t="n"/>
+      <c r="AQ30" s="285" t="n"/>
+      <c r="AR30" s="285" t="n"/>
+      <c r="AS30" s="285" t="n"/>
+      <c r="AT30" s="285" t="n"/>
+      <c r="AU30" s="285" t="n"/>
+      <c r="AV30" s="285" t="n"/>
+      <c r="AW30" s="285" t="n"/>
+      <c r="AX30" s="285" t="n"/>
+      <c r="AY30" s="285" t="n"/>
+      <c r="AZ30" s="285" t="n"/>
+      <c r="BA30" s="285" t="n"/>
+      <c r="BB30" s="285" t="n"/>
+      <c r="BC30" s="285" t="n"/>
+      <c r="BD30" s="286" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="306" t="inlineStr">
+        <is>
+          <t>Name / Signature / Date</t>
+        </is>
+      </c>
+      <c r="B31" s="329" t="n"/>
+      <c r="C31" s="329" t="n"/>
+      <c r="D31" s="329" t="n"/>
+      <c r="E31" s="329" t="n"/>
+      <c r="F31" s="329" t="n"/>
+      <c r="G31" s="329" t="n"/>
+      <c r="H31" s="329" t="n"/>
+      <c r="I31" s="329" t="n"/>
+      <c r="J31" s="329" t="n"/>
+      <c r="K31" s="329" t="n"/>
+      <c r="L31" s="329" t="n"/>
+      <c r="M31" s="329" t="n"/>
+      <c r="N31" s="329" t="n"/>
+      <c r="O31" s="329" t="n"/>
+      <c r="P31" s="329" t="n"/>
+      <c r="Q31" s="329" t="n"/>
+      <c r="R31" s="330" t="n"/>
+      <c r="S31" s="306" t="inlineStr">
+        <is>
+          <t>Name / Signature / Date</t>
+        </is>
+      </c>
+      <c r="T31" s="329" t="n"/>
+      <c r="U31" s="329" t="n"/>
+      <c r="V31" s="329" t="n"/>
+      <c r="W31" s="329" t="n"/>
+      <c r="X31" s="329" t="n"/>
+      <c r="Y31" s="329" t="n"/>
+      <c r="Z31" s="329" t="n"/>
+      <c r="AA31" s="329" t="n"/>
+      <c r="AB31" s="329" t="n"/>
+      <c r="AC31" s="329" t="n"/>
+      <c r="AD31" s="329" t="n"/>
+      <c r="AE31" s="329" t="n"/>
+      <c r="AF31" s="329" t="n"/>
+      <c r="AG31" s="329" t="n"/>
+      <c r="AH31" s="329" t="n"/>
+      <c r="AI31" s="329" t="n"/>
+      <c r="AJ31" s="330" t="n"/>
+      <c r="AK31" s="306" t="inlineStr">
+        <is>
+          <t>Name / Signature / Date</t>
+        </is>
+      </c>
+      <c r="AL31" s="329" t="n"/>
+      <c r="AM31" s="329" t="n"/>
+      <c r="AN31" s="329" t="n"/>
+      <c r="AO31" s="329" t="n"/>
+      <c r="AP31" s="329" t="n"/>
+      <c r="AQ31" s="329" t="n"/>
+      <c r="AR31" s="329" t="n"/>
+      <c r="AS31" s="329" t="n"/>
+      <c r="AT31" s="329" t="n"/>
+      <c r="AU31" s="329" t="n"/>
+      <c r="AV31" s="329" t="n"/>
+      <c r="AW31" s="329" t="n"/>
+      <c r="AX31" s="329" t="n"/>
+      <c r="AY31" s="329" t="n"/>
+      <c r="AZ31" s="329" t="n"/>
+      <c r="BA31" s="329" t="n"/>
+      <c r="BB31" s="329" t="n"/>
+      <c r="BC31" s="329" t="n"/>
+      <c r="BD31" s="330" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="331" t="n"/>
+      <c r="B32" s="332" t="n"/>
+      <c r="C32" s="332" t="n"/>
+      <c r="D32" s="332" t="n"/>
+      <c r="E32" s="332" t="n"/>
+      <c r="F32" s="332" t="n"/>
+      <c r="G32" s="332" t="n"/>
+      <c r="H32" s="332" t="n"/>
+      <c r="I32" s="332" t="n"/>
+      <c r="J32" s="332" t="n"/>
+      <c r="K32" s="332" t="n"/>
+      <c r="L32" s="332" t="n"/>
+      <c r="M32" s="332" t="n"/>
+      <c r="N32" s="332" t="n"/>
+      <c r="O32" s="332" t="n"/>
+      <c r="P32" s="332" t="n"/>
+      <c r="Q32" s="332" t="n"/>
+      <c r="R32" s="333" t="n"/>
+      <c r="S32" s="331" t="n"/>
+      <c r="T32" s="332" t="n"/>
+      <c r="U32" s="332" t="n"/>
+      <c r="V32" s="332" t="n"/>
+      <c r="W32" s="332" t="n"/>
+      <c r="X32" s="332" t="n"/>
+      <c r="Y32" s="332" t="n"/>
+      <c r="Z32" s="332" t="n"/>
+      <c r="AA32" s="332" t="n"/>
+      <c r="AB32" s="332" t="n"/>
+      <c r="AC32" s="332" t="n"/>
+      <c r="AD32" s="332" t="n"/>
+      <c r="AE32" s="332" t="n"/>
+      <c r="AF32" s="332" t="n"/>
+      <c r="AG32" s="332" t="n"/>
+      <c r="AH32" s="332" t="n"/>
+      <c r="AI32" s="332" t="n"/>
+      <c r="AJ32" s="333" t="n"/>
+      <c r="AK32" s="331" t="n"/>
+      <c r="AL32" s="332" t="n"/>
+      <c r="AM32" s="332" t="n"/>
+      <c r="AN32" s="332" t="n"/>
+      <c r="AO32" s="332" t="n"/>
+      <c r="AP32" s="332" t="n"/>
+      <c r="AQ32" s="332" t="n"/>
+      <c r="AR32" s="332" t="n"/>
+      <c r="AS32" s="332" t="n"/>
+      <c r="AT32" s="332" t="n"/>
+      <c r="AU32" s="332" t="n"/>
+      <c r="AV32" s="332" t="n"/>
+      <c r="AW32" s="332" t="n"/>
+      <c r="AX32" s="332" t="n"/>
+      <c r="AY32" s="332" t="n"/>
+      <c r="AZ32" s="332" t="n"/>
+      <c r="BA32" s="332" t="n"/>
+      <c r="BB32" s="332" t="n"/>
+      <c r="BC32" s="332" t="n"/>
+      <c r="BD32" s="333" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="294" t="n"/>
-      <c r="D33" s="299" t="n"/>
-      <c r="H33" s="304" t="n"/>
-      <c r="AA33" s="301" t="n"/>
-      <c r="AR33" s="302" t="n"/>
-      <c r="AX33" s="302" t="n"/>
-      <c r="BB33" s="303" t="n"/>
+      <c r="A33" s="334" t="n"/>
+      <c r="B33" s="335" t="n"/>
+      <c r="C33" s="335" t="n"/>
+      <c r="D33" s="335" t="n"/>
+      <c r="E33" s="335" t="n"/>
+      <c r="F33" s="335" t="n"/>
+      <c r="G33" s="335" t="n"/>
+      <c r="H33" s="335" t="n"/>
+      <c r="I33" s="335" t="n"/>
+      <c r="J33" s="335" t="n"/>
+      <c r="K33" s="335" t="n"/>
+      <c r="L33" s="335" t="n"/>
+      <c r="M33" s="335" t="n"/>
+      <c r="N33" s="335" t="n"/>
+      <c r="O33" s="335" t="n"/>
+      <c r="P33" s="335" t="n"/>
+      <c r="Q33" s="335" t="n"/>
+      <c r="R33" s="336" t="n"/>
+      <c r="S33" s="334" t="n"/>
+      <c r="T33" s="335" t="n"/>
+      <c r="U33" s="335" t="n"/>
+      <c r="V33" s="335" t="n"/>
+      <c r="W33" s="335" t="n"/>
+      <c r="X33" s="335" t="n"/>
+      <c r="Y33" s="335" t="n"/>
+      <c r="Z33" s="335" t="n"/>
+      <c r="AA33" s="335" t="n"/>
+      <c r="AB33" s="335" t="n"/>
+      <c r="AC33" s="335" t="n"/>
+      <c r="AD33" s="335" t="n"/>
+      <c r="AE33" s="335" t="n"/>
+      <c r="AF33" s="335" t="n"/>
+      <c r="AG33" s="335" t="n"/>
+      <c r="AH33" s="335" t="n"/>
+      <c r="AI33" s="335" t="n"/>
+      <c r="AJ33" s="336" t="n"/>
+      <c r="AK33" s="334" t="n"/>
+      <c r="AL33" s="335" t="n"/>
+      <c r="AM33" s="335" t="n"/>
+      <c r="AN33" s="335" t="n"/>
+      <c r="AO33" s="335" t="n"/>
+      <c r="AP33" s="335" t="n"/>
+      <c r="AQ33" s="335" t="n"/>
+      <c r="AR33" s="335" t="n"/>
+      <c r="AS33" s="335" t="n"/>
+      <c r="AT33" s="335" t="n"/>
+      <c r="AU33" s="335" t="n"/>
+      <c r="AV33" s="335" t="n"/>
+      <c r="AW33" s="335" t="n"/>
+      <c r="AX33" s="335" t="n"/>
+      <c r="AY33" s="335" t="n"/>
+      <c r="AZ33" s="335" t="n"/>
+      <c r="BA33" s="335" t="n"/>
+      <c r="BB33" s="335" t="n"/>
+      <c r="BC33" s="335" t="n"/>
+      <c r="BD33" s="336" t="n"/>
     </row>
     <row r="34" ht="4" customHeight="1">
-      <c r="A34" s="284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
-        </is>
-      </c>
-      <c r="B34" s="285" t="n"/>
-      <c r="C34" s="285" t="n"/>
-      <c r="D34" s="285" t="n"/>
-      <c r="E34" s="285" t="n"/>
-      <c r="F34" s="285" t="n"/>
-      <c r="G34" s="285" t="n"/>
-      <c r="H34" s="285" t="n"/>
-      <c r="I34" s="285" t="n"/>
-      <c r="J34" s="285" t="n"/>
-      <c r="K34" s="285" t="n"/>
-      <c r="L34" s="285" t="n"/>
-      <c r="M34" s="285" t="n"/>
-      <c r="N34" s="285" t="n"/>
-      <c r="O34" s="285" t="n"/>
-      <c r="P34" s="285" t="n"/>
-      <c r="Q34" s="285" t="n"/>
-      <c r="R34" s="285" t="n"/>
-      <c r="S34" s="285" t="n"/>
-      <c r="T34" s="285" t="n"/>
-      <c r="U34" s="285" t="n"/>
-      <c r="V34" s="285" t="n"/>
-      <c r="W34" s="285" t="n"/>
-      <c r="X34" s="285" t="n"/>
-      <c r="Y34" s="285" t="n"/>
-      <c r="Z34" s="285" t="n"/>
-      <c r="AA34" s="285" t="n"/>
-      <c r="AB34" s="285" t="n"/>
-      <c r="AC34" s="285" t="n"/>
-      <c r="AD34" s="285" t="n"/>
-      <c r="AE34" s="285" t="n"/>
-      <c r="AF34" s="285" t="n"/>
-      <c r="AG34" s="285" t="n"/>
-      <c r="AH34" s="285" t="n"/>
-      <c r="AI34" s="285" t="n"/>
-      <c r="AJ34" s="285" t="n"/>
-      <c r="AK34" s="285" t="n"/>
-      <c r="AL34" s="285" t="n"/>
-      <c r="AM34" s="285" t="n"/>
-      <c r="AN34" s="285" t="n"/>
-      <c r="AO34" s="285" t="n"/>
-      <c r="AP34" s="285" t="n"/>
-      <c r="AQ34" s="285" t="n"/>
-      <c r="AR34" s="285" t="n"/>
-      <c r="AS34" s="285" t="n"/>
-      <c r="AT34" s="285" t="n"/>
-      <c r="AU34" s="285" t="n"/>
-      <c r="AV34" s="285" t="n"/>
-      <c r="AW34" s="285" t="n"/>
-      <c r="AX34" s="285" t="n"/>
-      <c r="AY34" s="285" t="n"/>
-      <c r="AZ34" s="285" t="n"/>
-      <c r="BA34" s="285" t="n"/>
-      <c r="BB34" s="285" t="n"/>
-      <c r="BC34" s="285" t="n"/>
-      <c r="BD34" s="286" t="n"/>
+      <c r="A34" s="291" t="n"/>
+      <c r="D34" s="292" t="n"/>
+      <c r="R34" s="292" t="n"/>
+      <c r="AI34" s="292" t="n"/>
+      <c r="AP34" s="292" t="n"/>
+      <c r="AW34" s="292" t="n"/>
+      <c r="BA34" s="293" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="327" t="inlineStr">
-        <is>
-          <t>Prepared by</t>
-        </is>
-      </c>
-      <c r="B35" s="285" t="n"/>
-      <c r="C35" s="285" t="n"/>
-      <c r="D35" s="285" t="n"/>
-      <c r="E35" s="285" t="n"/>
-      <c r="F35" s="285" t="n"/>
-      <c r="G35" s="285" t="n"/>
-      <c r="H35" s="285" t="n"/>
-      <c r="I35" s="285" t="n"/>
-      <c r="J35" s="285" t="n"/>
-      <c r="K35" s="285" t="n"/>
-      <c r="L35" s="285" t="n"/>
-      <c r="M35" s="285" t="n"/>
-      <c r="N35" s="285" t="n"/>
-      <c r="O35" s="285" t="n"/>
-      <c r="P35" s="285" t="n"/>
-      <c r="Q35" s="285" t="n"/>
-      <c r="R35" s="328" t="n"/>
-      <c r="S35" s="51" t="inlineStr">
-        <is>
-          <t>Reviewed by</t>
-        </is>
-      </c>
-      <c r="T35" s="285" t="n"/>
-      <c r="U35" s="285" t="n"/>
-      <c r="V35" s="285" t="n"/>
-      <c r="W35" s="285" t="n"/>
-      <c r="X35" s="285" t="n"/>
-      <c r="Y35" s="285" t="n"/>
-      <c r="Z35" s="285" t="n"/>
-      <c r="AA35" s="285" t="n"/>
-      <c r="AB35" s="285" t="n"/>
-      <c r="AC35" s="285" t="n"/>
-      <c r="AD35" s="285" t="n"/>
-      <c r="AE35" s="285" t="n"/>
-      <c r="AF35" s="285" t="n"/>
-      <c r="AG35" s="285" t="n"/>
-      <c r="AH35" s="285" t="n"/>
-      <c r="AI35" s="285" t="n"/>
-      <c r="AJ35" s="285" t="n"/>
-      <c r="AK35" s="305" t="inlineStr">
-        <is>
-          <t>Approved by</t>
-        </is>
-      </c>
-      <c r="AL35" s="285" t="n"/>
-      <c r="AM35" s="285" t="n"/>
-      <c r="AN35" s="285" t="n"/>
-      <c r="AO35" s="285" t="n"/>
-      <c r="AP35" s="285" t="n"/>
-      <c r="AQ35" s="285" t="n"/>
-      <c r="AR35" s="285" t="n"/>
-      <c r="AS35" s="285" t="n"/>
-      <c r="AT35" s="285" t="n"/>
-      <c r="AU35" s="285" t="n"/>
-      <c r="AV35" s="285" t="n"/>
-      <c r="AW35" s="285" t="n"/>
-      <c r="AX35" s="285" t="n"/>
-      <c r="AY35" s="285" t="n"/>
-      <c r="AZ35" s="285" t="n"/>
-      <c r="BA35" s="285" t="n"/>
-      <c r="BB35" s="285" t="n"/>
-      <c r="BC35" s="285" t="n"/>
-      <c r="BD35" s="286" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="306" t="inlineStr">
-        <is>
-          <t>Name / Signature / Date</t>
-        </is>
-      </c>
-      <c r="B36" s="329" t="n"/>
-      <c r="C36" s="329" t="n"/>
-      <c r="D36" s="329" t="n"/>
-      <c r="E36" s="329" t="n"/>
-      <c r="F36" s="329" t="n"/>
-      <c r="G36" s="329" t="n"/>
-      <c r="H36" s="329" t="n"/>
-      <c r="I36" s="329" t="n"/>
-      <c r="J36" s="329" t="n"/>
-      <c r="K36" s="329" t="n"/>
-      <c r="L36" s="329" t="n"/>
-      <c r="M36" s="329" t="n"/>
-      <c r="N36" s="329" t="n"/>
-      <c r="O36" s="329" t="n"/>
-      <c r="P36" s="329" t="n"/>
-      <c r="Q36" s="329" t="n"/>
-      <c r="R36" s="330" t="n"/>
-      <c r="S36" s="306" t="inlineStr">
-        <is>
-          <t>Name / Signature / Date</t>
-        </is>
-      </c>
-      <c r="T36" s="329" t="n"/>
-      <c r="U36" s="329" t="n"/>
-      <c r="V36" s="329" t="n"/>
-      <c r="W36" s="329" t="n"/>
-      <c r="X36" s="329" t="n"/>
-      <c r="Y36" s="329" t="n"/>
-      <c r="Z36" s="329" t="n"/>
-      <c r="AA36" s="329" t="n"/>
-      <c r="AB36" s="329" t="n"/>
-      <c r="AC36" s="329" t="n"/>
-      <c r="AD36" s="329" t="n"/>
-      <c r="AE36" s="329" t="n"/>
-      <c r="AF36" s="329" t="n"/>
-      <c r="AG36" s="329" t="n"/>
-      <c r="AH36" s="329" t="n"/>
-      <c r="AI36" s="329" t="n"/>
-      <c r="AJ36" s="330" t="n"/>
-      <c r="AK36" s="306" t="inlineStr">
-        <is>
-          <t>Name / Signature / Date</t>
-        </is>
-      </c>
-      <c r="AL36" s="329" t="n"/>
-      <c r="AM36" s="329" t="n"/>
-      <c r="AN36" s="329" t="n"/>
-      <c r="AO36" s="329" t="n"/>
-      <c r="AP36" s="329" t="n"/>
-      <c r="AQ36" s="329" t="n"/>
-      <c r="AR36" s="329" t="n"/>
-      <c r="AS36" s="329" t="n"/>
-      <c r="AT36" s="329" t="n"/>
-      <c r="AU36" s="329" t="n"/>
-      <c r="AV36" s="329" t="n"/>
-      <c r="AW36" s="329" t="n"/>
-      <c r="AX36" s="329" t="n"/>
-      <c r="AY36" s="329" t="n"/>
-      <c r="AZ36" s="329" t="n"/>
-      <c r="BA36" s="329" t="n"/>
-      <c r="BB36" s="329" t="n"/>
-      <c r="BC36" s="329" t="n"/>
-      <c r="BD36" s="330" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="331" t="n"/>
-      <c r="B37" s="332" t="n"/>
-      <c r="C37" s="332" t="n"/>
-      <c r="D37" s="332" t="n"/>
-      <c r="E37" s="332" t="n"/>
-      <c r="F37" s="332" t="n"/>
-      <c r="G37" s="332" t="n"/>
-      <c r="H37" s="332" t="n"/>
-      <c r="I37" s="332" t="n"/>
-      <c r="J37" s="332" t="n"/>
-      <c r="K37" s="332" t="n"/>
-      <c r="L37" s="332" t="n"/>
-      <c r="M37" s="332" t="n"/>
-      <c r="N37" s="332" t="n"/>
-      <c r="O37" s="332" t="n"/>
-      <c r="P37" s="332" t="n"/>
-      <c r="Q37" s="332" t="n"/>
-      <c r="R37" s="333" t="n"/>
-      <c r="S37" s="331" t="n"/>
-      <c r="T37" s="332" t="n"/>
-      <c r="U37" s="332" t="n"/>
-      <c r="V37" s="332" t="n"/>
-      <c r="W37" s="332" t="n"/>
-      <c r="X37" s="332" t="n"/>
-      <c r="Y37" s="332" t="n"/>
-      <c r="Z37" s="332" t="n"/>
-      <c r="AA37" s="332" t="n"/>
-      <c r="AB37" s="332" t="n"/>
-      <c r="AC37" s="332" t="n"/>
-      <c r="AD37" s="332" t="n"/>
-      <c r="AE37" s="332" t="n"/>
-      <c r="AF37" s="332" t="n"/>
-      <c r="AG37" s="332" t="n"/>
-      <c r="AH37" s="332" t="n"/>
-      <c r="AI37" s="332" t="n"/>
-      <c r="AJ37" s="333" t="n"/>
-      <c r="AK37" s="331" t="n"/>
-      <c r="AL37" s="332" t="n"/>
-      <c r="AM37" s="332" t="n"/>
-      <c r="AN37" s="332" t="n"/>
-      <c r="AO37" s="332" t="n"/>
-      <c r="AP37" s="332" t="n"/>
-      <c r="AQ37" s="332" t="n"/>
-      <c r="AR37" s="332" t="n"/>
-      <c r="AS37" s="332" t="n"/>
-      <c r="AT37" s="332" t="n"/>
-      <c r="AU37" s="332" t="n"/>
-      <c r="AV37" s="332" t="n"/>
-      <c r="AW37" s="332" t="n"/>
-      <c r="AX37" s="332" t="n"/>
-      <c r="AY37" s="332" t="n"/>
-      <c r="AZ37" s="332" t="n"/>
-      <c r="BA37" s="332" t="n"/>
-      <c r="BB37" s="332" t="n"/>
-      <c r="BC37" s="332" t="n"/>
-      <c r="BD37" s="333" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="334" t="n"/>
-      <c r="B38" s="335" t="n"/>
-      <c r="C38" s="335" t="n"/>
-      <c r="D38" s="335" t="n"/>
-      <c r="E38" s="335" t="n"/>
-      <c r="F38" s="335" t="n"/>
-      <c r="G38" s="335" t="n"/>
-      <c r="H38" s="335" t="n"/>
-      <c r="I38" s="335" t="n"/>
-      <c r="J38" s="335" t="n"/>
-      <c r="K38" s="335" t="n"/>
-      <c r="L38" s="335" t="n"/>
-      <c r="M38" s="335" t="n"/>
-      <c r="N38" s="335" t="n"/>
-      <c r="O38" s="335" t="n"/>
-      <c r="P38" s="335" t="n"/>
-      <c r="Q38" s="335" t="n"/>
-      <c r="R38" s="336" t="n"/>
-      <c r="S38" s="334" t="n"/>
-      <c r="T38" s="335" t="n"/>
-      <c r="U38" s="335" t="n"/>
-      <c r="V38" s="335" t="n"/>
-      <c r="W38" s="335" t="n"/>
-      <c r="X38" s="335" t="n"/>
-      <c r="Y38" s="335" t="n"/>
-      <c r="Z38" s="335" t="n"/>
-      <c r="AA38" s="335" t="n"/>
-      <c r="AB38" s="335" t="n"/>
-      <c r="AC38" s="335" t="n"/>
-      <c r="AD38" s="335" t="n"/>
-      <c r="AE38" s="335" t="n"/>
-      <c r="AF38" s="335" t="n"/>
-      <c r="AG38" s="335" t="n"/>
-      <c r="AH38" s="335" t="n"/>
-      <c r="AI38" s="335" t="n"/>
-      <c r="AJ38" s="336" t="n"/>
-      <c r="AK38" s="334" t="n"/>
-      <c r="AL38" s="335" t="n"/>
-      <c r="AM38" s="335" t="n"/>
-      <c r="AN38" s="335" t="n"/>
-      <c r="AO38" s="335" t="n"/>
-      <c r="AP38" s="335" t="n"/>
-      <c r="AQ38" s="335" t="n"/>
-      <c r="AR38" s="335" t="n"/>
-      <c r="AS38" s="335" t="n"/>
-      <c r="AT38" s="335" t="n"/>
-      <c r="AU38" s="335" t="n"/>
-      <c r="AV38" s="335" t="n"/>
-      <c r="AW38" s="335" t="n"/>
-      <c r="AX38" s="335" t="n"/>
-      <c r="AY38" s="335" t="n"/>
-      <c r="AZ38" s="335" t="n"/>
-      <c r="BA38" s="335" t="n"/>
-      <c r="BB38" s="335" t="n"/>
-      <c r="BC38" s="335" t="n"/>
-      <c r="BD38" s="336" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="291" t="n"/>
-      <c r="D39" s="292" t="n"/>
-      <c r="R39" s="292" t="n"/>
-      <c r="AI39" s="292" t="n"/>
-      <c r="AP39" s="292" t="n"/>
-      <c r="AW39" s="292" t="n"/>
-      <c r="BA39" s="293" t="n"/>
-    </row>
-    <row r="40" ht="4" customHeight="1">
-      <c r="A40" s="337" t="inlineStr">
-        <is>
-          <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Ref: SOP-605 / WI-605. Retain 10 years. Flag SC dimensions. Note U(k=2) for tight tolerances. File: FRM-641_{JobNo}_{PartNo}.xlsx</t>
-        </is>
-      </c>
-      <c r="B40" s="276" t="n"/>
-      <c r="C40" s="276" t="n"/>
-      <c r="D40" s="276" t="n"/>
-      <c r="E40" s="276" t="n"/>
-      <c r="F40" s="276" t="n"/>
-      <c r="G40" s="276" t="n"/>
-      <c r="H40" s="276" t="n"/>
-      <c r="I40" s="276" t="n"/>
-      <c r="J40" s="276" t="n"/>
-      <c r="K40" s="276" t="n"/>
-      <c r="L40" s="276" t="n"/>
-      <c r="M40" s="276" t="n"/>
-      <c r="N40" s="276" t="n"/>
-      <c r="O40" s="276" t="n"/>
-      <c r="P40" s="276" t="n"/>
-      <c r="Q40" s="276" t="n"/>
-      <c r="R40" s="276" t="n"/>
-      <c r="S40" s="276" t="n"/>
-      <c r="T40" s="276" t="n"/>
-      <c r="U40" s="276" t="n"/>
-      <c r="V40" s="276" t="n"/>
-      <c r="W40" s="276" t="n"/>
-      <c r="X40" s="276" t="n"/>
-      <c r="Y40" s="276" t="n"/>
-      <c r="Z40" s="276" t="n"/>
-      <c r="AA40" s="276" t="n"/>
-      <c r="AB40" s="276" t="n"/>
-      <c r="AC40" s="276" t="n"/>
-      <c r="AD40" s="276" t="n"/>
-      <c r="AE40" s="276" t="n"/>
-      <c r="AF40" s="276" t="n"/>
-      <c r="AG40" s="276" t="n"/>
-      <c r="AH40" s="276" t="n"/>
-      <c r="AI40" s="276" t="n"/>
-      <c r="AJ40" s="276" t="n"/>
-      <c r="AK40" s="276" t="n"/>
-      <c r="AL40" s="276" t="n"/>
-      <c r="AM40" s="276" t="n"/>
-      <c r="AN40" s="276" t="n"/>
-      <c r="AO40" s="276" t="n"/>
-      <c r="AP40" s="276" t="n"/>
-      <c r="AQ40" s="276" t="n"/>
-      <c r="AR40" s="276" t="n"/>
-      <c r="AS40" s="276" t="n"/>
-      <c r="AT40" s="276" t="n"/>
-      <c r="AU40" s="276" t="n"/>
-      <c r="AV40" s="276" t="n"/>
-      <c r="AW40" s="276" t="n"/>
-      <c r="AX40" s="276" t="n"/>
-      <c r="AY40" s="276" t="n"/>
-      <c r="AZ40" s="276" t="n"/>
-      <c r="BA40" s="276" t="n"/>
-      <c r="BB40" s="276" t="n"/>
-      <c r="BC40" s="276" t="n"/>
-      <c r="BD40" s="277" t="n"/>
-    </row>
+      <c r="A35" s="337" t="inlineStr">
+        <is>
+          <t>NOTICE: Complete in English. No back-dating, history deletion, proxy-signing or vague comments. Record result, owner and evidence reference.</t>
+        </is>
+      </c>
+      <c r="B35" s="276" t="n"/>
+      <c r="C35" s="276" t="n"/>
+      <c r="D35" s="276" t="n"/>
+      <c r="E35" s="276" t="n"/>
+      <c r="F35" s="276" t="n"/>
+      <c r="G35" s="276" t="n"/>
+      <c r="H35" s="276" t="n"/>
+      <c r="I35" s="276" t="n"/>
+      <c r="J35" s="276" t="n"/>
+      <c r="K35" s="276" t="n"/>
+      <c r="L35" s="276" t="n"/>
+      <c r="M35" s="276" t="n"/>
+      <c r="N35" s="276" t="n"/>
+      <c r="O35" s="276" t="n"/>
+      <c r="P35" s="276" t="n"/>
+      <c r="Q35" s="276" t="n"/>
+      <c r="R35" s="276" t="n"/>
+      <c r="S35" s="276" t="n"/>
+      <c r="T35" s="276" t="n"/>
+      <c r="U35" s="276" t="n"/>
+      <c r="V35" s="276" t="n"/>
+      <c r="W35" s="276" t="n"/>
+      <c r="X35" s="276" t="n"/>
+      <c r="Y35" s="276" t="n"/>
+      <c r="Z35" s="276" t="n"/>
+      <c r="AA35" s="276" t="n"/>
+      <c r="AB35" s="276" t="n"/>
+      <c r="AC35" s="276" t="n"/>
+      <c r="AD35" s="276" t="n"/>
+      <c r="AE35" s="276" t="n"/>
+      <c r="AF35" s="276" t="n"/>
+      <c r="AG35" s="276" t="n"/>
+      <c r="AH35" s="276" t="n"/>
+      <c r="AI35" s="276" t="n"/>
+      <c r="AJ35" s="276" t="n"/>
+      <c r="AK35" s="276" t="n"/>
+      <c r="AL35" s="276" t="n"/>
+      <c r="AM35" s="276" t="n"/>
+      <c r="AN35" s="276" t="n"/>
+      <c r="AO35" s="276" t="n"/>
+      <c r="AP35" s="276" t="n"/>
+      <c r="AQ35" s="276" t="n"/>
+      <c r="AR35" s="276" t="n"/>
+      <c r="AS35" s="276" t="n"/>
+      <c r="AT35" s="276" t="n"/>
+      <c r="AU35" s="276" t="n"/>
+      <c r="AV35" s="276" t="n"/>
+      <c r="AW35" s="276" t="n"/>
+      <c r="AX35" s="276" t="n"/>
+      <c r="AY35" s="276" t="n"/>
+      <c r="AZ35" s="276" t="n"/>
+      <c r="BA35" s="276" t="n"/>
+      <c r="BB35" s="276" t="n"/>
+      <c r="BC35" s="276" t="n"/>
+      <c r="BD35" s="277" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="4" customHeight="1"/>
     <row r="41" ht="17" customHeight="1"/>
     <row r="42" ht="17" customHeight="1"/>
     <row r="43" ht="26" customHeight="1"/>
@@ -7077,7 +6811,8 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
-  <mergeCells count="125">
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <mergeCells count="114">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AX18:BA18"/>
     <mergeCell ref="H19:Z19"/>
@@ -7094,11 +6829,8 @@
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AA20:AQ20"/>
     <mergeCell ref="D21:G21"/>
-    <mergeCell ref="K13:AB13"/>
     <mergeCell ref="H21:Z21"/>
-    <mergeCell ref="AJ31:BD31"/>
     <mergeCell ref="A30:R30"/>
-    <mergeCell ref="K15:AB15"/>
     <mergeCell ref="AA21:AQ21"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="S31:AJ33"/>
@@ -7109,11 +6841,9 @@
     <mergeCell ref="L1:AP3"/>
     <mergeCell ref="AX15:BA15"/>
     <mergeCell ref="AQ2:AV2"/>
-    <mergeCell ref="A13:J13"/>
     <mergeCell ref="AR15:AW15"/>
     <mergeCell ref="A24:BD24"/>
     <mergeCell ref="K27:AB27"/>
-    <mergeCell ref="A15:J15"/>
     <mergeCell ref="AM10:BD10"/>
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="A1:K5"/>
@@ -7137,17 +6867,14 @@
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="AC9:AL9"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="K32:AB32"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="AX20:BA20"/>
-    <mergeCell ref="AJ13:BD13"/>
     <mergeCell ref="AC11:AL11"/>
     <mergeCell ref="AX16:BA16"/>
     <mergeCell ref="H18:Z18"/>
     <mergeCell ref="K8:AB8"/>
     <mergeCell ref="AW4:BD4"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="AJ15:BD15"/>
     <mergeCell ref="AQ1:AV1"/>
     <mergeCell ref="AA15:AQ15"/>
     <mergeCell ref="AK30:BD30"/>
@@ -7174,7 +6901,6 @@
     <mergeCell ref="AA19:AQ19"/>
     <mergeCell ref="AM9:BD9"/>
     <mergeCell ref="A10:J10"/>
-    <mergeCell ref="K31:AB31"/>
     <mergeCell ref="AC27:AL27"/>
     <mergeCell ref="AR16:AW16"/>
     <mergeCell ref="K12:AB12"/>
@@ -7188,12 +6914,10 @@
     <mergeCell ref="AR17:AW17"/>
     <mergeCell ref="AX22:BA22"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="AC13:AI13"/>
     <mergeCell ref="AM12:BD12"/>
     <mergeCell ref="AC12:AL12"/>
     <mergeCell ref="AR22:AW22"/>
     <mergeCell ref="AX21:BA21"/>
-    <mergeCell ref="AJ32:BD32"/>
     <mergeCell ref="BB16:BD16"/>
     <mergeCell ref="AM26:BD26"/>
     <mergeCell ref="D16:G16"/>
@@ -7204,29 +6928,7 @@
     <mergeCell ref="A14:BD14"/>
     <mergeCell ref="K26:AB26"/>
   </mergeCells>
-  <conditionalFormatting sqref="AR19:AW25">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"FAIL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"HOLD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"PASS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K28:AB28">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
-      <formula>"FAIL"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
-      <formula>"HOLD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
-      <formula>"PASS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="12">
+  <dataValidations count="7">
     <dataValidation sqref="AM8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
       <formula1>'LISTS'!$B$2:$B$5</formula1>
     </dataValidation>
@@ -7247,21 +6949,6 @@
     </dataValidation>
     <dataValidation sqref="AM27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
       <formula1>'LISTS'!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="AJ13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"YES,NO,NA"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"YES,NO"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"YES,NO,NA"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"YES,NO,NA"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AJ32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"YES,NO,NA"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
@@ -7284,7 +6971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7327,16 +7014,7 @@
           <t>YES_NO</t>
         </is>
       </c>
-      <c r="G1" s="265" t="inlineStr">
-        <is>
-          <t>RISK_LEVEL</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>DISCOVERY_STAGE</t>
-        </is>
-      </c>
+      <c r="G1" s="265" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="266" t="inlineStr">
@@ -7369,16 +7047,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G2" s="266" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>INCOMING</t>
-        </is>
-      </c>
+      <c r="G2" s="266" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="266" t="inlineStr">
@@ -7411,16 +7080,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G3" s="266" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SETUP</t>
-        </is>
-      </c>
+      <c r="G3" s="266" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="266" t="inlineStr">
@@ -7449,16 +7109,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="G4" s="266" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>FIRST PIECE</t>
-        </is>
-      </c>
+      <c r="G4" s="266" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="266" t="inlineStr">
@@ -7483,16 +7134,7 @@
         </is>
       </c>
       <c r="F5" s="266" t="n"/>
-      <c r="G5" s="266" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>IN-PROCESS</t>
-        </is>
-      </c>
+      <c r="G5" s="266" t="n"/>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -7502,11 +7144,6 @@
       </c>
       <c r="F6" s="266" t="n"/>
       <c r="G6" s="266" t="n"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>FINAL INSPECTION</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -7515,11 +7152,6 @@
         </is>
       </c>
       <c r="F7" s="266" t="n"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PACKAGING</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -7528,11 +7160,6 @@
         </is>
       </c>
       <c r="F8" s="266" t="n"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SHIPPING</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
@@ -7541,11 +7168,6 @@
         </is>
       </c>
       <c r="F9" s="266" t="n"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CUSTOMER</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="C10" t="inlineStr">
@@ -7602,7 +7224,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="317" t="inlineStr">
         <is>
-          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709. For tight-tolerance features, note U(k=2) in Notes column. Flag Safety/Special Characteristics with SC prefix in Characteristic column.</t>
+          <t>Final inspection event record. Consumes outputs from FRM-621/631/643/712/707/709 as needed and hands shipment readiness to FRM-642/702.</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7256,7 @@
       </c>
       <c r="F4" s="318" t="inlineStr">
         <is>
-          <t>Notes / U(k=2)</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="G4" s="318" t="inlineStr">
@@ -7824,6 +7446,7 @@
       <c r="G19" s="320" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -7834,9 +7457,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8087,12 +7709,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8220,12 +7843,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8235,94 +7859,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="344" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
       </c>
-      <c r="B1" s="344" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="344" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="344" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
       </c>
-      <c r="E1" s="344" t="inlineStr">
-        <is>
-          <t>Approved By</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="345" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="B2" s="345" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="C2" s="345" t="inlineStr">
-        <is>
-          <t>Initial controlled baseline</t>
-        </is>
-      </c>
-      <c r="D2" s="345" t="inlineStr">
-        <is>
-          <t>QMS</t>
-        </is>
-      </c>
-      <c r="E2" s="345" t="inlineStr">
-        <is>
-          <t>General Manager</t>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="345" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>V1</t>
         </is>
       </c>
-      <c r="B3" s="345" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="C3" s="345" t="inlineStr">
-        <is>
-          <t>Upgrade: CNC fields, cross-form linkage, conditional formatting, parent procedure ref</t>
-        </is>
-      </c>
-      <c r="D3" s="345" t="inlineStr">
-        <is>
-          <t>QMS</t>
-        </is>
-      </c>
-      <c r="E3" s="345" t="inlineStr">
-        <is>
-          <t>General Manager</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-642, FRM-651; Parent ref: SOP-605</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
         </is>
       </c>
     </row>

--- a/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
+++ b/04-Bieu-Mau/06-FRM-600/FRM-641_Final_Inspection_Report.xlsx
@@ -4954,6 +4954,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số công việc
+Job đang kiểm tra cuối.</t>
+      </text>
+    </comment>
+    <comment ref="AC9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã chi tiết / Phiên bản
+Part number và drawing revision.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Số lượng kiểm tra / Đạt
+Ghi tổng số kiểm tra và số đạt.
+Ví dụ: 50 inspected / 49 accepted.</t>
+      </text>
+    </comment>
+    <comment ref="AC10" authorId="0" shapeId="0">
+      <text>
+        <t>Người kiểm tra / Ngày
+Inspector thực hiện và ngày kiểm tra.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả kiểm tra
+Ghi TẤT CẢ dimensions từ bản vẽ.
+ISO 9001 cl.8.6 — bằng chứng conformity trước khi giao hàng.</t>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <t>Đặc tính
+Ghi kích thước + dung sai từ bản vẽ.
+Ví dụ: OD 25.00 ±0.02, Ra 0.8 max.</t>
+      </text>
+    </comment>
+    <comment ref="AD13" authorId="0" shapeId="0">
+      <text>
+        <t>Phương pháp / Dụng cụ
+Ghi tool đo và ID.
+Ví dụ: CMM #C-003 Prog R02.</t>
+      </text>
+    </comment>
+    <comment ref="AR13" authorId="0" shapeId="0">
+      <text>
+        <t>Kết quả
+PASS / FAIL. Nếu FAIL → NCR.</t>
+      </text>
+    </comment>
+    <comment ref="AX13" authorId="0" shapeId="0">
+      <text>
+        <t>Người kiểm tra
+Ký tắt.</t>
+      </text>
+    </comment>
+    <comment ref="A31" authorId="0" shapeId="0">
+      <text>
+        <t>Quyết định release
+Quyết định cuối cùng trước khi giao hàng.</t>
+      </text>
+    </comment>
+    <comment ref="A32" authorId="0" shapeId="0">
+      <text>
+        <t>Quyết định xử lý
+ACCEPT = giao hàng.
+CONDITIONAL = giao với nhượng bộ (cần concession).
+REJECT = không giao → NCR (FRM-651).</t>
+      </text>
+    </comment>
+    <comment ref="AC32" authorId="0" shapeId="0">
+      <text>
+        <t>Số CoC
+Mã Certificate of Conformance.
+Liên kết đến FRM-642 CoC Register.</t>
+      </text>
+    </comment>
+    <comment ref="A33" authorId="0" shapeId="0">
+      <text>
+        <t>Tham chiếu nhượng bộ
+Nếu CONDITIONAL → ghi mã concession/deviation.
+Cần phê duyệt của khách hàng.</t>
+      </text>
+    </comment>
+    <comment ref="AC33" authorId="0" shapeId="0">
+      <text>
+        <t>Tham chiếu đóng gói
+FRM-707 (standard) hoặc FRM-709 (clean).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5778,7 +5880,7 @@
     <row r="10" ht="20" customHeight="1" s="264">
       <c r="A10" s="480" t="inlineStr">
         <is>
-          <t>Qty Inspected / Qty Accepted</t>
+          <t>Qty Inspected / Accepted</t>
         </is>
       </c>
       <c r="B10" s="481" t="n"/>
@@ -6044,8 +6146,9 @@
       <c r="BD13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="n"/>
@@ -6116,8 +6219,9 @@
       <c r="BD14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="492" t="n"/>
@@ -6188,8 +6292,9 @@
       <c r="BD15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="492" t="n"/>
@@ -6260,8 +6365,9 @@
       <c r="BD16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="492" t="n"/>
@@ -6275,7 +6381,7 @@
       <c r="G17" s="492" t="n"/>
       <c r="H17" s="499" t="inlineStr">
         <is>
-          <t>GD&amp;T / profile / position (if applicable).</t>
+          <t>GD&amp;T / profile / position.</t>
         </is>
       </c>
       <c r="I17" s="491" t="n"/>
@@ -6301,7 +6407,7 @@
       <c r="AC17" s="492" t="n"/>
       <c r="AD17" s="495" t="inlineStr">
         <is>
-          <t>CMM report ref.</t>
+          <t>CMM report reference.</t>
         </is>
       </c>
       <c r="AE17" s="491" t="n"/>
@@ -6332,8 +6438,9 @@
       <c r="BD17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="n"/>
@@ -6404,8 +6511,9 @@
       <c r="BD18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="n"/>
@@ -6476,8 +6584,9 @@
       <c r="BD19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="492" t="n"/>
@@ -6517,7 +6626,7 @@
       <c r="AC20" s="492" t="n"/>
       <c r="AD20" s="495" t="inlineStr">
         <is>
-          <t>Cert match, marking correct.</t>
+          <t>Cert match, marking per drawing.</t>
         </is>
       </c>
       <c r="AE20" s="491" t="n"/>
@@ -6548,8 +6657,9 @@
       <c r="BD20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="490" t="n">
-        <v>8</v>
+      <c r="A21" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="491" t="n"/>
       <c r="C21" s="492" t="n"/>
@@ -6563,7 +6673,7 @@
       <c r="G21" s="492" t="n"/>
       <c r="H21" s="499" t="inlineStr">
         <is>
-          <t>Cleanliness (if semiconductor part).</t>
+          <t>Cleanliness (if semiconductor).</t>
         </is>
       </c>
       <c r="I21" s="491" t="n"/>
@@ -6589,7 +6699,7 @@
       <c r="AC21" s="492" t="n"/>
       <c r="AD21" s="495" t="inlineStr">
         <is>
-          <t>FRM-711 ref.</t>
+          <t>FRM-711 reference.</t>
         </is>
       </c>
       <c r="AE21" s="491" t="n"/>
@@ -6620,8 +6730,9 @@
       <c r="BD21" s="498" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="490" t="n">
-        <v>9</v>
+      <c r="A22" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B22" s="491" t="n"/>
       <c r="C22" s="492" t="n"/>
@@ -6680,8 +6791,9 @@
       <c r="BD22" s="498" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="490" t="n">
-        <v>10</v>
+      <c r="A23" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B23" s="491" t="n"/>
       <c r="C23" s="492" t="n"/>
@@ -6740,8 +6852,9 @@
       <c r="BD23" s="498" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="264">
-      <c r="A24" s="490" t="n">
-        <v>11</v>
+      <c r="A24" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B24" s="491" t="n"/>
       <c r="C24" s="492" t="n"/>
@@ -6800,8 +6913,9 @@
       <c r="BD24" s="498" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="264">
-      <c r="A25" s="490" t="n">
-        <v>12</v>
+      <c r="A25" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B25" s="491" t="n"/>
       <c r="C25" s="492" t="n"/>
@@ -6860,8 +6974,9 @@
       <c r="BD25" s="498" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="264">
-      <c r="A26" s="490" t="n">
-        <v>13</v>
+      <c r="A26" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B26" s="491" t="n"/>
       <c r="C26" s="492" t="n"/>
@@ -6920,8 +7035,9 @@
       <c r="BD26" s="498" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="264">
-      <c r="A27" s="490" t="n">
-        <v>14</v>
+      <c r="A27" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B27" s="491" t="n"/>
       <c r="C27" s="492" t="n"/>
@@ -6980,8 +7096,9 @@
       <c r="BD27" s="498" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="264">
-      <c r="A28" s="490" t="n">
-        <v>15</v>
+      <c r="A28" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B28" s="491" t="n"/>
       <c r="C28" s="492" t="n"/>
@@ -7040,8 +7157,9 @@
       <c r="BD28" s="498" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="264">
-      <c r="A29" s="503" t="n">
-        <v>16</v>
+      <c r="A29" s="503">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B29" s="481" t="n"/>
       <c r="C29" s="482" t="n"/>
@@ -7728,7 +7846,7 @@
     <row r="41" ht="24" customHeight="1" s="264">
       <c r="A41" s="515" t="inlineStr">
         <is>
-          <t>NOTICE — One form per job final inspection. Ref: SOP-605. Retain: 10 years.</t>
+          <t>NOTICE — ISO 9001 cl.8.6. Gate before delivery. All FAIL → NCR. Ref: SOP-605. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B41" s="471" t="n"/>
@@ -7955,6 +8073,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
